--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="82">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -218,12 +218,57 @@
   </si>
   <si>
     <t>Nº</t>
+  </si>
+  <si>
+    <t>South Korea K League 2</t>
+  </si>
+  <si>
+    <t>2025</t>
+  </si>
+  <si>
+    <t>Incheon United</t>
+  </si>
+  <si>
+    <t>Cheonan City</t>
+  </si>
+  <si>
+    <t>Busan I'Park</t>
+  </si>
+  <si>
+    <t>Ansan Greeners</t>
+  </si>
+  <si>
+    <t>Gyeongnam</t>
+  </si>
+  <si>
+    <t>Jeonnam Dragons</t>
+  </si>
+  <si>
+    <t>Gimpo Citizen</t>
+  </si>
+  <si>
+    <t>Suwon Bluewings</t>
+  </si>
+  <si>
+    <t>['80', '90+3']</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>['1', '6']</t>
+  </si>
+  <si>
+    <t>['67']</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -276,11 +321,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -575,7 +621,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP1"/>
+  <dimension ref="A1:BP5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -784,6 +830,830 @@
         <v>66</v>
       </c>
     </row>
+    <row r="2" spans="1:68">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>7813821</v>
+      </c>
+      <c r="C2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E2" s="2">
+        <v>45710.08333333334</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>2</v>
+      </c>
+      <c r="O2" t="s">
+        <v>78</v>
+      </c>
+      <c r="P2" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q2">
+        <v>1.91</v>
+      </c>
+      <c r="R2">
+        <v>2.4</v>
+      </c>
+      <c r="S2">
+        <v>7</v>
+      </c>
+      <c r="T2">
+        <v>1.33</v>
+      </c>
+      <c r="U2">
+        <v>3.25</v>
+      </c>
+      <c r="V2">
+        <v>2.63</v>
+      </c>
+      <c r="W2">
+        <v>1.44</v>
+      </c>
+      <c r="X2">
+        <v>6.5</v>
+      </c>
+      <c r="Y2">
+        <v>1.11</v>
+      </c>
+      <c r="Z2">
+        <v>1.41</v>
+      </c>
+      <c r="AA2">
+        <v>5.1</v>
+      </c>
+      <c r="AB2">
+        <v>6.2</v>
+      </c>
+      <c r="AC2">
+        <v>1.03</v>
+      </c>
+      <c r="AD2">
+        <v>11</v>
+      </c>
+      <c r="AE2">
+        <v>1.24</v>
+      </c>
+      <c r="AF2">
+        <v>3.7</v>
+      </c>
+      <c r="AG2">
+        <v>1.8</v>
+      </c>
+      <c r="AH2">
+        <v>1.94</v>
+      </c>
+      <c r="AI2">
+        <v>1.91</v>
+      </c>
+      <c r="AJ2">
+        <v>1.8</v>
+      </c>
+      <c r="AK2">
+        <v>1.13</v>
+      </c>
+      <c r="AL2">
+        <v>1.18</v>
+      </c>
+      <c r="AM2">
+        <v>2.42</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <v>3</v>
+      </c>
+      <c r="AQ2">
+        <v>0</v>
+      </c>
+      <c r="AR2">
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <v>11</v>
+      </c>
+      <c r="AV2">
+        <v>0</v>
+      </c>
+      <c r="AW2">
+        <v>8</v>
+      </c>
+      <c r="AX2">
+        <v>4</v>
+      </c>
+      <c r="AY2">
+        <v>19</v>
+      </c>
+      <c r="AZ2">
+        <v>4</v>
+      </c>
+      <c r="BA2">
+        <v>9</v>
+      </c>
+      <c r="BB2">
+        <v>2</v>
+      </c>
+      <c r="BC2">
+        <v>11</v>
+      </c>
+      <c r="BD2">
+        <v>1.34</v>
+      </c>
+      <c r="BE2">
+        <v>8.9</v>
+      </c>
+      <c r="BF2">
+        <v>3.86</v>
+      </c>
+      <c r="BG2">
+        <v>1.37</v>
+      </c>
+      <c r="BH2">
+        <v>2.66</v>
+      </c>
+      <c r="BI2">
+        <v>1.75</v>
+      </c>
+      <c r="BJ2">
+        <v>2.03</v>
+      </c>
+      <c r="BK2">
+        <v>2.25</v>
+      </c>
+      <c r="BL2">
+        <v>1.62</v>
+      </c>
+      <c r="BM2">
+        <v>2.92</v>
+      </c>
+      <c r="BN2">
+        <v>1.31</v>
+      </c>
+      <c r="BO2">
+        <v>3.9</v>
+      </c>
+      <c r="BP2">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:68">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>7813822</v>
+      </c>
+      <c r="C3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E3" s="2">
+        <v>45710.08333333334</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H3" t="s">
+        <v>75</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+      <c r="N3">
+        <v>2</v>
+      </c>
+      <c r="O3" t="s">
+        <v>79</v>
+      </c>
+      <c r="P3" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q3">
+        <v>3.8</v>
+      </c>
+      <c r="R3">
+        <v>2.27</v>
+      </c>
+      <c r="S3">
+        <v>2.49</v>
+      </c>
+      <c r="T3">
+        <v>1.31</v>
+      </c>
+      <c r="U3">
+        <v>3.2</v>
+      </c>
+      <c r="V3">
+        <v>2.4</v>
+      </c>
+      <c r="W3">
+        <v>1.5</v>
+      </c>
+      <c r="X3">
+        <v>5.8</v>
+      </c>
+      <c r="Y3">
+        <v>1.08</v>
+      </c>
+      <c r="Z3">
+        <v>3.41</v>
+      </c>
+      <c r="AA3">
+        <v>3.78</v>
+      </c>
+      <c r="AB3">
+        <v>1.95</v>
+      </c>
+      <c r="AC3">
+        <v>1.01</v>
+      </c>
+      <c r="AD3">
+        <v>11</v>
+      </c>
+      <c r="AE3">
+        <v>1.22</v>
+      </c>
+      <c r="AF3">
+        <v>4</v>
+      </c>
+      <c r="AG3">
+        <v>1.65</v>
+      </c>
+      <c r="AH3">
+        <v>2</v>
+      </c>
+      <c r="AI3">
+        <v>1.59</v>
+      </c>
+      <c r="AJ3">
+        <v>2.2</v>
+      </c>
+      <c r="AK3">
+        <v>1.73</v>
+      </c>
+      <c r="AL3">
+        <v>1.26</v>
+      </c>
+      <c r="AM3">
+        <v>1.29</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <v>3</v>
+      </c>
+      <c r="AR3">
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <v>3</v>
+      </c>
+      <c r="AV3">
+        <v>10</v>
+      </c>
+      <c r="AW3">
+        <v>6</v>
+      </c>
+      <c r="AX3">
+        <v>9</v>
+      </c>
+      <c r="AY3">
+        <v>14</v>
+      </c>
+      <c r="AZ3">
+        <v>22</v>
+      </c>
+      <c r="BA3">
+        <v>1</v>
+      </c>
+      <c r="BB3">
+        <v>4</v>
+      </c>
+      <c r="BC3">
+        <v>5</v>
+      </c>
+      <c r="BD3">
+        <v>2.35</v>
+      </c>
+      <c r="BE3">
+        <v>8.1</v>
+      </c>
+      <c r="BF3">
+        <v>1.76</v>
+      </c>
+      <c r="BG3">
+        <v>1.31</v>
+      </c>
+      <c r="BH3">
+        <v>3.15</v>
+      </c>
+      <c r="BI3">
+        <v>1.57</v>
+      </c>
+      <c r="BJ3">
+        <v>2.32</v>
+      </c>
+      <c r="BK3">
+        <v>2</v>
+      </c>
+      <c r="BL3">
+        <v>1.8</v>
+      </c>
+      <c r="BM3">
+        <v>2.44</v>
+      </c>
+      <c r="BN3">
+        <v>1.49</v>
+      </c>
+      <c r="BO3">
+        <v>3.22</v>
+      </c>
+      <c r="BP3">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:68">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>7813823</v>
+      </c>
+      <c r="C4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E4" s="2">
+        <v>45710.1875</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
+        <v>72</v>
+      </c>
+      <c r="H4" t="s">
+        <v>76</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4" t="s">
+        <v>79</v>
+      </c>
+      <c r="P4" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q4">
+        <v>2.75</v>
+      </c>
+      <c r="R4">
+        <v>2.01</v>
+      </c>
+      <c r="S4">
+        <v>4.1</v>
+      </c>
+      <c r="T4">
+        <v>1.5</v>
+      </c>
+      <c r="U4">
+        <v>2.45</v>
+      </c>
+      <c r="V4">
+        <v>3.26</v>
+      </c>
+      <c r="W4">
+        <v>1.3</v>
+      </c>
+      <c r="X4">
+        <v>8.5</v>
+      </c>
+      <c r="Y4">
+        <v>1.02</v>
+      </c>
+      <c r="Z4">
+        <v>2.04</v>
+      </c>
+      <c r="AA4">
+        <v>3.3</v>
+      </c>
+      <c r="AB4">
+        <v>3.62</v>
+      </c>
+      <c r="AC4">
+        <v>1.03</v>
+      </c>
+      <c r="AD4">
+        <v>7.5</v>
+      </c>
+      <c r="AE4">
+        <v>1.4</v>
+      </c>
+      <c r="AF4">
+        <v>2.8</v>
+      </c>
+      <c r="AG4">
+        <v>2.15</v>
+      </c>
+      <c r="AH4">
+        <v>1.57</v>
+      </c>
+      <c r="AI4">
+        <v>1.93</v>
+      </c>
+      <c r="AJ4">
+        <v>1.78</v>
+      </c>
+      <c r="AK4">
+        <v>1.28</v>
+      </c>
+      <c r="AL4">
+        <v>1.31</v>
+      </c>
+      <c r="AM4">
+        <v>1.65</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>1</v>
+      </c>
+      <c r="AQ4">
+        <v>1</v>
+      </c>
+      <c r="AR4">
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <v>5</v>
+      </c>
+      <c r="AV4">
+        <v>4</v>
+      </c>
+      <c r="AW4">
+        <v>4</v>
+      </c>
+      <c r="AX4">
+        <v>5</v>
+      </c>
+      <c r="AY4">
+        <v>9</v>
+      </c>
+      <c r="AZ4">
+        <v>9</v>
+      </c>
+      <c r="BA4">
+        <v>7</v>
+      </c>
+      <c r="BB4">
+        <v>6</v>
+      </c>
+      <c r="BC4">
+        <v>13</v>
+      </c>
+      <c r="BD4">
+        <v>1.57</v>
+      </c>
+      <c r="BE4">
+        <v>6.15</v>
+      </c>
+      <c r="BF4">
+        <v>3.14</v>
+      </c>
+      <c r="BG4">
+        <v>1.64</v>
+      </c>
+      <c r="BH4">
+        <v>2.22</v>
+      </c>
+      <c r="BI4">
+        <v>2.08</v>
+      </c>
+      <c r="BJ4">
+        <v>1.72</v>
+      </c>
+      <c r="BK4">
+        <v>2.7</v>
+      </c>
+      <c r="BL4">
+        <v>1.36</v>
+      </c>
+      <c r="BM4">
+        <v>3.88</v>
+      </c>
+      <c r="BN4">
+        <v>1.18</v>
+      </c>
+      <c r="BO4">
+        <v>5.15</v>
+      </c>
+      <c r="BP4">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:68">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>7813824</v>
+      </c>
+      <c r="C5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="2">
+        <v>45710.1875</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>73</v>
+      </c>
+      <c r="H5" t="s">
+        <v>77</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+      <c r="N5">
+        <v>1</v>
+      </c>
+      <c r="O5" t="s">
+        <v>79</v>
+      </c>
+      <c r="P5" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q5">
+        <v>4.5</v>
+      </c>
+      <c r="R5">
+        <v>2</v>
+      </c>
+      <c r="S5">
+        <v>2.75</v>
+      </c>
+      <c r="T5">
+        <v>1.53</v>
+      </c>
+      <c r="U5">
+        <v>2.38</v>
+      </c>
+      <c r="V5">
+        <v>3.5</v>
+      </c>
+      <c r="W5">
+        <v>1.29</v>
+      </c>
+      <c r="X5">
+        <v>11</v>
+      </c>
+      <c r="Y5">
+        <v>1.05</v>
+      </c>
+      <c r="Z5">
+        <v>3.99</v>
+      </c>
+      <c r="AA5">
+        <v>3.06</v>
+      </c>
+      <c r="AB5">
+        <v>2.03</v>
+      </c>
+      <c r="AC5">
+        <v>1.08</v>
+      </c>
+      <c r="AD5">
+        <v>7</v>
+      </c>
+      <c r="AE5">
+        <v>1.41</v>
+      </c>
+      <c r="AF5">
+        <v>2.75</v>
+      </c>
+      <c r="AG5">
+        <v>2.2</v>
+      </c>
+      <c r="AH5">
+        <v>1.55</v>
+      </c>
+      <c r="AI5">
+        <v>2</v>
+      </c>
+      <c r="AJ5">
+        <v>1.73</v>
+      </c>
+      <c r="AK5">
+        <v>1.82</v>
+      </c>
+      <c r="AL5">
+        <v>1.32</v>
+      </c>
+      <c r="AM5">
+        <v>1.22</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>0</v>
+      </c>
+      <c r="AQ5">
+        <v>3</v>
+      </c>
+      <c r="AR5">
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <v>2</v>
+      </c>
+      <c r="AV5">
+        <v>12</v>
+      </c>
+      <c r="AW5">
+        <v>4</v>
+      </c>
+      <c r="AX5">
+        <v>10</v>
+      </c>
+      <c r="AY5">
+        <v>6</v>
+      </c>
+      <c r="AZ5">
+        <v>22</v>
+      </c>
+      <c r="BA5">
+        <v>0</v>
+      </c>
+      <c r="BB5">
+        <v>6</v>
+      </c>
+      <c r="BC5">
+        <v>6</v>
+      </c>
+      <c r="BD5">
+        <v>2.89</v>
+      </c>
+      <c r="BE5">
+        <v>7.9</v>
+      </c>
+      <c r="BF5">
+        <v>1.55</v>
+      </c>
+      <c r="BG5">
+        <v>1.56</v>
+      </c>
+      <c r="BH5">
+        <v>2.39</v>
+      </c>
+      <c r="BI5">
+        <v>1.94</v>
+      </c>
+      <c r="BJ5">
+        <v>1.86</v>
+      </c>
+      <c r="BK5">
+        <v>2.48</v>
+      </c>
+      <c r="BL5">
+        <v>1.52</v>
+      </c>
+      <c r="BM5">
+        <v>3.34</v>
+      </c>
+      <c r="BN5">
+        <v>1.24</v>
+      </c>
+      <c r="BO5">
+        <v>5.4</v>
+      </c>
+      <c r="BP5">
+        <v>1.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="93">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -238,6 +238,15 @@
     <t>Ansan Greeners</t>
   </si>
   <si>
+    <t>Seongnam</t>
+  </si>
+  <si>
+    <t>Seoul E-Land</t>
+  </si>
+  <si>
+    <t>Bucheon 1995</t>
+  </si>
+  <si>
     <t>Gyeongnam</t>
   </si>
   <si>
@@ -250,16 +259,40 @@
     <t>Suwon Bluewings</t>
   </si>
   <si>
+    <t>Hwaseong</t>
+  </si>
+  <si>
+    <t>Asan Mugunghwa</t>
+  </si>
+  <si>
+    <t>Cheongju</t>
+  </si>
+  <si>
     <t>['80', '90+3']</t>
   </si>
   <si>
     <t>[]</t>
   </si>
   <si>
+    <t>['19', '52']</t>
+  </si>
+  <si>
+    <t>['20', '49']</t>
+  </si>
+  <si>
+    <t>['39', '44', '90+7']</t>
+  </si>
+  <si>
     <t>['1', '6']</t>
   </si>
   <si>
     <t>['67']</t>
+  </si>
+  <si>
+    <t>['89']</t>
+  </si>
+  <si>
+    <t>['85']</t>
   </si>
 </sst>
 </file>
@@ -621,7 +654,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP5"/>
+  <dimension ref="A1:BP8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -853,7 +886,7 @@
         <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -874,10 +907,10 @@
         <v>2</v>
       </c>
       <c r="O2" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="P2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="Q2">
         <v>1.91</v>
@@ -1059,7 +1092,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1080,10 +1113,10 @@
         <v>2</v>
       </c>
       <c r="O3" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="P3" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="Q3">
         <v>3.8</v>
@@ -1265,7 +1298,7 @@
         <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1286,10 +1319,10 @@
         <v>0</v>
       </c>
       <c r="O4" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="P4" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -1471,7 +1504,7 @@
         <v>73</v>
       </c>
       <c r="H5" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1492,10 +1525,10 @@
         <v>1</v>
       </c>
       <c r="O5" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="Q5">
         <v>4.5</v>
@@ -1652,6 +1685,624 @@
       </c>
       <c r="BP5">
         <v>1.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:68">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>7813825</v>
+      </c>
+      <c r="C6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" s="2">
+        <v>45711.08333333334</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H6" t="s">
+        <v>81</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>2</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>2</v>
+      </c>
+      <c r="O6" t="s">
+        <v>86</v>
+      </c>
+      <c r="P6" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q6">
+        <v>3.5</v>
+      </c>
+      <c r="R6">
+        <v>2</v>
+      </c>
+      <c r="S6">
+        <v>3.4</v>
+      </c>
+      <c r="T6">
+        <v>1.5</v>
+      </c>
+      <c r="U6">
+        <v>2.5</v>
+      </c>
+      <c r="V6">
+        <v>3.4</v>
+      </c>
+      <c r="W6">
+        <v>1.3</v>
+      </c>
+      <c r="X6">
+        <v>10</v>
+      </c>
+      <c r="Y6">
+        <v>1.06</v>
+      </c>
+      <c r="Z6">
+        <v>2.32</v>
+      </c>
+      <c r="AA6">
+        <v>3.23</v>
+      </c>
+      <c r="AB6">
+        <v>3.03</v>
+      </c>
+      <c r="AC6">
+        <v>1.01</v>
+      </c>
+      <c r="AD6">
+        <v>8.6</v>
+      </c>
+      <c r="AE6">
+        <v>1.38</v>
+      </c>
+      <c r="AF6">
+        <v>2.9</v>
+      </c>
+      <c r="AG6">
+        <v>2.15</v>
+      </c>
+      <c r="AH6">
+        <v>1.63</v>
+      </c>
+      <c r="AI6">
+        <v>1.83</v>
+      </c>
+      <c r="AJ6">
+        <v>1.83</v>
+      </c>
+      <c r="AK6">
+        <v>1.53</v>
+      </c>
+      <c r="AL6">
+        <v>1.34</v>
+      </c>
+      <c r="AM6">
+        <v>1.37</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>3</v>
+      </c>
+      <c r="AQ6">
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <v>3</v>
+      </c>
+      <c r="AV6">
+        <v>2</v>
+      </c>
+      <c r="AW6">
+        <v>3</v>
+      </c>
+      <c r="AX6">
+        <v>1</v>
+      </c>
+      <c r="AY6">
+        <v>6</v>
+      </c>
+      <c r="AZ6">
+        <v>3</v>
+      </c>
+      <c r="BA6">
+        <v>2</v>
+      </c>
+      <c r="BB6">
+        <v>9</v>
+      </c>
+      <c r="BC6">
+        <v>11</v>
+      </c>
+      <c r="BD6">
+        <v>2.28</v>
+      </c>
+      <c r="BE6">
+        <v>6</v>
+      </c>
+      <c r="BF6">
+        <v>1.95</v>
+      </c>
+      <c r="BG6">
+        <v>1.47</v>
+      </c>
+      <c r="BH6">
+        <v>2.5</v>
+      </c>
+      <c r="BI6">
+        <v>1.85</v>
+      </c>
+      <c r="BJ6">
+        <v>1.95</v>
+      </c>
+      <c r="BK6">
+        <v>2.33</v>
+      </c>
+      <c r="BL6">
+        <v>1.56</v>
+      </c>
+      <c r="BM6">
+        <v>3.02</v>
+      </c>
+      <c r="BN6">
+        <v>1.33</v>
+      </c>
+      <c r="BO6">
+        <v>4.2</v>
+      </c>
+      <c r="BP6">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:68">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>7813826</v>
+      </c>
+      <c r="C7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45711.1875</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7" t="s">
+        <v>75</v>
+      </c>
+      <c r="H7" t="s">
+        <v>82</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>2</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>3</v>
+      </c>
+      <c r="O7" t="s">
+        <v>87</v>
+      </c>
+      <c r="P7" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q7">
+        <v>2.85</v>
+      </c>
+      <c r="R7">
+        <v>2.13</v>
+      </c>
+      <c r="S7">
+        <v>3.55</v>
+      </c>
+      <c r="T7">
+        <v>1.37</v>
+      </c>
+      <c r="U7">
+        <v>2.89</v>
+      </c>
+      <c r="V7">
+        <v>2.7</v>
+      </c>
+      <c r="W7">
+        <v>1.41</v>
+      </c>
+      <c r="X7">
+        <v>7.8</v>
+      </c>
+      <c r="Y7">
+        <v>1.03</v>
+      </c>
+      <c r="Z7">
+        <v>2.32</v>
+      </c>
+      <c r="AA7">
+        <v>3.26</v>
+      </c>
+      <c r="AB7">
+        <v>3.01</v>
+      </c>
+      <c r="AC7">
+        <v>1.01</v>
+      </c>
+      <c r="AD7">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AE7">
+        <v>1.29</v>
+      </c>
+      <c r="AF7">
+        <v>3.35</v>
+      </c>
+      <c r="AG7">
+        <v>1.91</v>
+      </c>
+      <c r="AH7">
+        <v>1.83</v>
+      </c>
+      <c r="AI7">
+        <v>1.71</v>
+      </c>
+      <c r="AJ7">
+        <v>2.02</v>
+      </c>
+      <c r="AK7">
+        <v>1.36</v>
+      </c>
+      <c r="AL7">
+        <v>1.29</v>
+      </c>
+      <c r="AM7">
+        <v>1.56</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>3</v>
+      </c>
+      <c r="AQ7">
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <v>4</v>
+      </c>
+      <c r="AV7">
+        <v>2</v>
+      </c>
+      <c r="AW7">
+        <v>2</v>
+      </c>
+      <c r="AX7">
+        <v>4</v>
+      </c>
+      <c r="AY7">
+        <v>6</v>
+      </c>
+      <c r="AZ7">
+        <v>6</v>
+      </c>
+      <c r="BA7">
+        <v>6</v>
+      </c>
+      <c r="BB7">
+        <v>3</v>
+      </c>
+      <c r="BC7">
+        <v>9</v>
+      </c>
+      <c r="BD7">
+        <v>1.86</v>
+      </c>
+      <c r="BE7">
+        <v>6</v>
+      </c>
+      <c r="BF7">
+        <v>2.42</v>
+      </c>
+      <c r="BG7">
+        <v>1.5</v>
+      </c>
+      <c r="BH7">
+        <v>2.51</v>
+      </c>
+      <c r="BI7">
+        <v>1.9</v>
+      </c>
+      <c r="BJ7">
+        <v>1.9</v>
+      </c>
+      <c r="BK7">
+        <v>2.38</v>
+      </c>
+      <c r="BL7">
+        <v>1.55</v>
+      </c>
+      <c r="BM7">
+        <v>3.28</v>
+      </c>
+      <c r="BN7">
+        <v>1.25</v>
+      </c>
+      <c r="BO7">
+        <v>4.5</v>
+      </c>
+      <c r="BP7">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:68">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>7813827</v>
+      </c>
+      <c r="C8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D8" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" s="2">
+        <v>45711.1875</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8" t="s">
+        <v>76</v>
+      </c>
+      <c r="H8" t="s">
+        <v>83</v>
+      </c>
+      <c r="I8">
+        <v>2</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>2</v>
+      </c>
+      <c r="L8">
+        <v>3</v>
+      </c>
+      <c r="M8">
+        <v>1</v>
+      </c>
+      <c r="N8">
+        <v>4</v>
+      </c>
+      <c r="O8" t="s">
+        <v>88</v>
+      </c>
+      <c r="P8" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q8">
+        <v>2.39</v>
+      </c>
+      <c r="R8">
+        <v>2</v>
+      </c>
+      <c r="S8">
+        <v>5.05</v>
+      </c>
+      <c r="T8">
+        <v>1.45</v>
+      </c>
+      <c r="U8">
+        <v>2.59</v>
+      </c>
+      <c r="V8">
+        <v>3.2</v>
+      </c>
+      <c r="W8">
+        <v>1.31</v>
+      </c>
+      <c r="X8">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Y8">
+        <v>1.01</v>
+      </c>
+      <c r="Z8">
+        <v>1.8</v>
+      </c>
+      <c r="AA8">
+        <v>3.55</v>
+      </c>
+      <c r="AB8">
+        <v>4.3</v>
+      </c>
+      <c r="AC8">
+        <v>1.01</v>
+      </c>
+      <c r="AD8">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AE8">
+        <v>1.33</v>
+      </c>
+      <c r="AF8">
+        <v>2.81</v>
+      </c>
+      <c r="AG8">
+        <v>2.1</v>
+      </c>
+      <c r="AH8">
+        <v>1.6</v>
+      </c>
+      <c r="AI8">
+        <v>1.98</v>
+      </c>
+      <c r="AJ8">
+        <v>1.7</v>
+      </c>
+      <c r="AK8">
+        <v>1.16</v>
+      </c>
+      <c r="AL8">
+        <v>1.26</v>
+      </c>
+      <c r="AM8">
+        <v>1.92</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <v>3</v>
+      </c>
+      <c r="AQ8">
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <v>8</v>
+      </c>
+      <c r="AV8">
+        <v>2</v>
+      </c>
+      <c r="AW8">
+        <v>4</v>
+      </c>
+      <c r="AX8">
+        <v>5</v>
+      </c>
+      <c r="AY8">
+        <v>13</v>
+      </c>
+      <c r="AZ8">
+        <v>7</v>
+      </c>
+      <c r="BA8">
+        <v>3</v>
+      </c>
+      <c r="BB8">
+        <v>5</v>
+      </c>
+      <c r="BC8">
+        <v>8</v>
+      </c>
+      <c r="BD8">
+        <v>1.64</v>
+      </c>
+      <c r="BE8">
+        <v>7.7</v>
+      </c>
+      <c r="BF8">
+        <v>2.65</v>
+      </c>
+      <c r="BG8">
+        <v>1.57</v>
+      </c>
+      <c r="BH8">
+        <v>2.33</v>
+      </c>
+      <c r="BI8">
+        <v>2</v>
+      </c>
+      <c r="BJ8">
+        <v>1.81</v>
+      </c>
+      <c r="BK8">
+        <v>2.58</v>
+      </c>
+      <c r="BL8">
+        <v>1.48</v>
+      </c>
+      <c r="BM8">
+        <v>3.5</v>
+      </c>
+      <c r="BN8">
+        <v>1.22</v>
+      </c>
+      <c r="BO8">
+        <v>4.95</v>
+      </c>
+      <c r="BP8">
+        <v>1.12</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="97">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -283,6 +283,12 @@
     <t>['39', '44', '90+7']</t>
   </si>
   <si>
+    <t>['51', '68']</t>
+  </si>
+  <si>
+    <t>['61']</t>
+  </si>
+  <si>
     <t>['1', '6']</t>
   </si>
   <si>
@@ -293,6 +299,12 @@
   </si>
   <si>
     <t>['85']</t>
+  </si>
+  <si>
+    <t>['48', '74']</t>
+  </si>
+  <si>
+    <t>['64']</t>
   </si>
 </sst>
 </file>
@@ -654,7 +666,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP8"/>
+  <dimension ref="A1:BP11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1116,7 +1128,7 @@
         <v>85</v>
       </c>
       <c r="P3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="Q3">
         <v>3.8</v>
@@ -1197,7 +1209,7 @@
         <v>0</v>
       </c>
       <c r="AQ3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1403,7 +1415,7 @@
         <v>1</v>
       </c>
       <c r="AQ4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1528,7 +1540,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="Q5">
         <v>4.5</v>
@@ -1609,7 +1621,7 @@
         <v>0</v>
       </c>
       <c r="AQ5">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -1940,7 +1952,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="Q7">
         <v>2.85</v>
@@ -2018,7 +2030,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ7">
         <v>0</v>
@@ -2146,7 +2158,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="Q8">
         <v>2.39</v>
@@ -2303,6 +2315,624 @@
       </c>
       <c r="BP8">
         <v>1.12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:68">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>7813828</v>
+      </c>
+      <c r="C9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" s="2">
+        <v>45717.08333333334</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9" t="s">
+        <v>70</v>
+      </c>
+      <c r="H9" t="s">
+        <v>80</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>2</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>2</v>
+      </c>
+      <c r="O9" t="s">
+        <v>89</v>
+      </c>
+      <c r="P9" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q9">
+        <v>3.2</v>
+      </c>
+      <c r="R9">
+        <v>2.05</v>
+      </c>
+      <c r="S9">
+        <v>3.6</v>
+      </c>
+      <c r="T9">
+        <v>1.44</v>
+      </c>
+      <c r="U9">
+        <v>2.63</v>
+      </c>
+      <c r="V9">
+        <v>3.4</v>
+      </c>
+      <c r="W9">
+        <v>1.3</v>
+      </c>
+      <c r="X9">
+        <v>10</v>
+      </c>
+      <c r="Y9">
+        <v>1.06</v>
+      </c>
+      <c r="Z9">
+        <v>2.39</v>
+      </c>
+      <c r="AA9">
+        <v>3.32</v>
+      </c>
+      <c r="AB9">
+        <v>2.85</v>
+      </c>
+      <c r="AC9">
+        <v>1.07</v>
+      </c>
+      <c r="AD9">
+        <v>7.5</v>
+      </c>
+      <c r="AE9">
+        <v>1.32</v>
+      </c>
+      <c r="AF9">
+        <v>3.2</v>
+      </c>
+      <c r="AG9">
+        <v>1.92</v>
+      </c>
+      <c r="AH9">
+        <v>1.78</v>
+      </c>
+      <c r="AI9">
+        <v>1.83</v>
+      </c>
+      <c r="AJ9">
+        <v>1.83</v>
+      </c>
+      <c r="AK9">
+        <v>1.36</v>
+      </c>
+      <c r="AL9">
+        <v>1.34</v>
+      </c>
+      <c r="AM9">
+        <v>1.49</v>
+      </c>
+      <c r="AN9">
+        <v>3</v>
+      </c>
+      <c r="AO9">
+        <v>3</v>
+      </c>
+      <c r="AP9">
+        <v>3</v>
+      </c>
+      <c r="AQ9">
+        <v>1.5</v>
+      </c>
+      <c r="AR9">
+        <v>2.58</v>
+      </c>
+      <c r="AS9">
+        <v>2.7</v>
+      </c>
+      <c r="AT9">
+        <v>5.28</v>
+      </c>
+      <c r="AU9">
+        <v>3</v>
+      </c>
+      <c r="AV9">
+        <v>4</v>
+      </c>
+      <c r="AW9">
+        <v>8</v>
+      </c>
+      <c r="AX9">
+        <v>3</v>
+      </c>
+      <c r="AY9">
+        <v>11</v>
+      </c>
+      <c r="AZ9">
+        <v>7</v>
+      </c>
+      <c r="BA9">
+        <v>5</v>
+      </c>
+      <c r="BB9">
+        <v>6</v>
+      </c>
+      <c r="BC9">
+        <v>11</v>
+      </c>
+      <c r="BD9">
+        <v>1.75</v>
+      </c>
+      <c r="BE9">
+        <v>7.7</v>
+      </c>
+      <c r="BF9">
+        <v>2.4</v>
+      </c>
+      <c r="BG9">
+        <v>1.45</v>
+      </c>
+      <c r="BH9">
+        <v>2.55</v>
+      </c>
+      <c r="BI9">
+        <v>1.8</v>
+      </c>
+      <c r="BJ9">
+        <v>2</v>
+      </c>
+      <c r="BK9">
+        <v>2.28</v>
+      </c>
+      <c r="BL9">
+        <v>1.59</v>
+      </c>
+      <c r="BM9">
+        <v>2.95</v>
+      </c>
+      <c r="BN9">
+        <v>1.35</v>
+      </c>
+      <c r="BO9">
+        <v>4.05</v>
+      </c>
+      <c r="BP9">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:68">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>7813830</v>
+      </c>
+      <c r="C10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" t="s">
+        <v>69</v>
+      </c>
+      <c r="E10" s="2">
+        <v>45717.1875</v>
+      </c>
+      <c r="F10">
+        <v>2</v>
+      </c>
+      <c r="G10" t="s">
+        <v>73</v>
+      </c>
+      <c r="H10" t="s">
+        <v>79</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>2</v>
+      </c>
+      <c r="N10">
+        <v>2</v>
+      </c>
+      <c r="O10" t="s">
+        <v>85</v>
+      </c>
+      <c r="P10" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q10">
+        <v>4.3</v>
+      </c>
+      <c r="R10">
+        <v>2.02</v>
+      </c>
+      <c r="S10">
+        <v>2.65</v>
+      </c>
+      <c r="T10">
+        <v>1.5</v>
+      </c>
+      <c r="U10">
+        <v>2.45</v>
+      </c>
+      <c r="V10">
+        <v>3.26</v>
+      </c>
+      <c r="W10">
+        <v>1.3</v>
+      </c>
+      <c r="X10">
+        <v>8.9</v>
+      </c>
+      <c r="Y10">
+        <v>1.01</v>
+      </c>
+      <c r="Z10">
+        <v>3.7</v>
+      </c>
+      <c r="AA10">
+        <v>3.32</v>
+      </c>
+      <c r="AB10">
+        <v>2.01</v>
+      </c>
+      <c r="AC10">
+        <v>1.02</v>
+      </c>
+      <c r="AD10">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AE10">
+        <v>1.39</v>
+      </c>
+      <c r="AF10">
+        <v>2.85</v>
+      </c>
+      <c r="AG10">
+        <v>2.1</v>
+      </c>
+      <c r="AH10">
+        <v>1.6</v>
+      </c>
+      <c r="AI10">
+        <v>1.94</v>
+      </c>
+      <c r="AJ10">
+        <v>1.77</v>
+      </c>
+      <c r="AK10">
+        <v>1.7</v>
+      </c>
+      <c r="AL10">
+        <v>1.3</v>
+      </c>
+      <c r="AM10">
+        <v>1.26</v>
+      </c>
+      <c r="AN10">
+        <v>0</v>
+      </c>
+      <c r="AO10">
+        <v>1</v>
+      </c>
+      <c r="AP10">
+        <v>0</v>
+      </c>
+      <c r="AQ10">
+        <v>2</v>
+      </c>
+      <c r="AR10">
+        <v>0.82</v>
+      </c>
+      <c r="AS10">
+        <v>1.27</v>
+      </c>
+      <c r="AT10">
+        <v>2.09</v>
+      </c>
+      <c r="AU10">
+        <v>6</v>
+      </c>
+      <c r="AV10">
+        <v>5</v>
+      </c>
+      <c r="AW10">
+        <v>8</v>
+      </c>
+      <c r="AX10">
+        <v>8</v>
+      </c>
+      <c r="AY10">
+        <v>14</v>
+      </c>
+      <c r="AZ10">
+        <v>13</v>
+      </c>
+      <c r="BA10">
+        <v>2</v>
+      </c>
+      <c r="BB10">
+        <v>4</v>
+      </c>
+      <c r="BC10">
+        <v>6</v>
+      </c>
+      <c r="BD10">
+        <v>2.72</v>
+      </c>
+      <c r="BE10">
+        <v>6.05</v>
+      </c>
+      <c r="BF10">
+        <v>1.71</v>
+      </c>
+      <c r="BG10">
+        <v>1.53</v>
+      </c>
+      <c r="BH10">
+        <v>2.21</v>
+      </c>
+      <c r="BI10">
+        <v>1.97</v>
+      </c>
+      <c r="BJ10">
+        <v>1.71</v>
+      </c>
+      <c r="BK10">
+        <v>2.59</v>
+      </c>
+      <c r="BL10">
+        <v>1.39</v>
+      </c>
+      <c r="BM10">
+        <v>3.7</v>
+      </c>
+      <c r="BN10">
+        <v>1.2</v>
+      </c>
+      <c r="BO10">
+        <v>6.25</v>
+      </c>
+      <c r="BP10">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="11" spans="1:68">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>7813829</v>
+      </c>
+      <c r="C11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D11" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11" s="2">
+        <v>45717.1875</v>
+      </c>
+      <c r="F11">
+        <v>2</v>
+      </c>
+      <c r="G11" t="s">
+        <v>75</v>
+      </c>
+      <c r="H11" t="s">
+        <v>78</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+      <c r="M11">
+        <v>1</v>
+      </c>
+      <c r="N11">
+        <v>2</v>
+      </c>
+      <c r="O11" t="s">
+        <v>90</v>
+      </c>
+      <c r="P11" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q11">
+        <v>2.8</v>
+      </c>
+      <c r="R11">
+        <v>2.1</v>
+      </c>
+      <c r="S11">
+        <v>3.4</v>
+      </c>
+      <c r="T11">
+        <v>1.32</v>
+      </c>
+      <c r="U11">
+        <v>3.19</v>
+      </c>
+      <c r="V11">
+        <v>2.5</v>
+      </c>
+      <c r="W11">
+        <v>1.47</v>
+      </c>
+      <c r="X11">
+        <v>6.4</v>
+      </c>
+      <c r="Y11">
+        <v>1.06</v>
+      </c>
+      <c r="Z11">
+        <v>2.33</v>
+      </c>
+      <c r="AA11">
+        <v>3.41</v>
+      </c>
+      <c r="AB11">
+        <v>2.87</v>
+      </c>
+      <c r="AC11">
+        <v>1.02</v>
+      </c>
+      <c r="AD11">
+        <v>10</v>
+      </c>
+      <c r="AE11">
+        <v>1.2</v>
+      </c>
+      <c r="AF11">
+        <v>4</v>
+      </c>
+      <c r="AG11">
+        <v>1.95</v>
+      </c>
+      <c r="AH11">
+        <v>1.79</v>
+      </c>
+      <c r="AI11">
+        <v>1.57</v>
+      </c>
+      <c r="AJ11">
+        <v>2.25</v>
+      </c>
+      <c r="AK11">
+        <v>1.39</v>
+      </c>
+      <c r="AL11">
+        <v>1.27</v>
+      </c>
+      <c r="AM11">
+        <v>1.56</v>
+      </c>
+      <c r="AN11">
+        <v>3</v>
+      </c>
+      <c r="AO11">
+        <v>3</v>
+      </c>
+      <c r="AP11">
+        <v>2</v>
+      </c>
+      <c r="AQ11">
+        <v>2</v>
+      </c>
+      <c r="AR11">
+        <v>1.04</v>
+      </c>
+      <c r="AS11">
+        <v>2.29</v>
+      </c>
+      <c r="AT11">
+        <v>3.33</v>
+      </c>
+      <c r="AU11">
+        <v>4</v>
+      </c>
+      <c r="AV11">
+        <v>3</v>
+      </c>
+      <c r="AW11">
+        <v>4</v>
+      </c>
+      <c r="AX11">
+        <v>5</v>
+      </c>
+      <c r="AY11">
+        <v>8</v>
+      </c>
+      <c r="AZ11">
+        <v>8</v>
+      </c>
+      <c r="BA11">
+        <v>2</v>
+      </c>
+      <c r="BB11">
+        <v>3</v>
+      </c>
+      <c r="BC11">
+        <v>5</v>
+      </c>
+      <c r="BD11">
+        <v>1.7</v>
+      </c>
+      <c r="BE11">
+        <v>6.3</v>
+      </c>
+      <c r="BF11">
+        <v>2.7</v>
+      </c>
+      <c r="BG11">
+        <v>1.31</v>
+      </c>
+      <c r="BH11">
+        <v>2.92</v>
+      </c>
+      <c r="BI11">
+        <v>1.57</v>
+      </c>
+      <c r="BJ11">
+        <v>2.13</v>
+      </c>
+      <c r="BK11">
+        <v>2.01</v>
+      </c>
+      <c r="BL11">
+        <v>1.68</v>
+      </c>
+      <c r="BM11">
+        <v>2.62</v>
+      </c>
+      <c r="BN11">
+        <v>1.38</v>
+      </c>
+      <c r="BO11">
+        <v>3.68</v>
+      </c>
+      <c r="BP11">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="102">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -247,6 +247,9 @@
     <t>Bucheon 1995</t>
   </si>
   <si>
+    <t>Hwaseong</t>
+  </si>
+  <si>
     <t>Gyeongnam</t>
   </si>
   <si>
@@ -259,9 +262,6 @@
     <t>Suwon Bluewings</t>
   </si>
   <si>
-    <t>Hwaseong</t>
-  </si>
-  <si>
     <t>Asan Mugunghwa</t>
   </si>
   <si>
@@ -289,6 +289,12 @@
     <t>['61']</t>
   </si>
   <si>
+    <t>['86']</t>
+  </si>
+  <si>
+    <t>['60']</t>
+  </si>
+  <si>
     <t>['1', '6']</t>
   </si>
   <si>
@@ -305,6 +311,15 @@
   </si>
   <si>
     <t>['64']</t>
+  </si>
+  <si>
+    <t>['45+3']</t>
+  </si>
+  <si>
+    <t>['81']</t>
+  </si>
+  <si>
+    <t>['85', '88']</t>
   </si>
 </sst>
 </file>
@@ -666,7 +681,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP11"/>
+  <dimension ref="A1:BP14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -898,7 +913,7 @@
         <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -1003,7 +1018,7 @@
         <v>3</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1104,7 +1119,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1128,7 +1143,7 @@
         <v>85</v>
       </c>
       <c r="P3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="Q3">
         <v>3.8</v>
@@ -1310,7 +1325,7 @@
         <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1412,7 +1427,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AQ4">
         <v>2</v>
@@ -1516,7 +1531,7 @@
         <v>73</v>
       </c>
       <c r="H5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1540,7 +1555,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="Q5">
         <v>4.5</v>
@@ -1722,7 +1737,7 @@
         <v>74</v>
       </c>
       <c r="H6" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -1952,7 +1967,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="Q7">
         <v>2.85</v>
@@ -2033,7 +2048,7 @@
         <v>2</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2158,7 +2173,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="Q8">
         <v>2.39</v>
@@ -2340,7 +2355,7 @@
         <v>70</v>
       </c>
       <c r="H9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -2546,7 +2561,7 @@
         <v>73</v>
       </c>
       <c r="H10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -2570,7 +2585,7 @@
         <v>85</v>
       </c>
       <c r="P10" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="Q10">
         <v>4.3</v>
@@ -2752,7 +2767,7 @@
         <v>75</v>
       </c>
       <c r="H11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -2776,7 +2791,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q11">
         <v>2.8</v>
@@ -2933,6 +2948,624 @@
       </c>
       <c r="BP11">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:68">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>7813831</v>
+      </c>
+      <c r="C12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E12" s="2">
+        <v>45718.08333333334</v>
+      </c>
+      <c r="F12">
+        <v>2</v>
+      </c>
+      <c r="G12" t="s">
+        <v>77</v>
+      </c>
+      <c r="H12" t="s">
+        <v>82</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12">
+        <v>1</v>
+      </c>
+      <c r="N12">
+        <v>2</v>
+      </c>
+      <c r="O12" t="s">
+        <v>91</v>
+      </c>
+      <c r="P12" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q12">
+        <v>3.6</v>
+      </c>
+      <c r="R12">
+        <v>2.2</v>
+      </c>
+      <c r="S12">
+        <v>3</v>
+      </c>
+      <c r="T12">
+        <v>1.4</v>
+      </c>
+      <c r="U12">
+        <v>2.75</v>
+      </c>
+      <c r="V12">
+        <v>2.75</v>
+      </c>
+      <c r="W12">
+        <v>1.4</v>
+      </c>
+      <c r="X12">
+        <v>8</v>
+      </c>
+      <c r="Y12">
+        <v>1.08</v>
+      </c>
+      <c r="Z12">
+        <v>2.82</v>
+      </c>
+      <c r="AA12">
+        <v>3.29</v>
+      </c>
+      <c r="AB12">
+        <v>2.43</v>
+      </c>
+      <c r="AC12">
+        <v>1.05</v>
+      </c>
+      <c r="AD12">
+        <v>8.5</v>
+      </c>
+      <c r="AE12">
+        <v>1.28</v>
+      </c>
+      <c r="AF12">
+        <v>3.45</v>
+      </c>
+      <c r="AG12">
+        <v>1.87</v>
+      </c>
+      <c r="AH12">
+        <v>1.87</v>
+      </c>
+      <c r="AI12">
+        <v>1.73</v>
+      </c>
+      <c r="AJ12">
+        <v>2</v>
+      </c>
+      <c r="AK12">
+        <v>1.56</v>
+      </c>
+      <c r="AL12">
+        <v>1.29</v>
+      </c>
+      <c r="AM12">
+        <v>1.37</v>
+      </c>
+      <c r="AN12">
+        <v>0</v>
+      </c>
+      <c r="AO12">
+        <v>0</v>
+      </c>
+      <c r="AP12">
+        <v>1</v>
+      </c>
+      <c r="AQ12">
+        <v>0.5</v>
+      </c>
+      <c r="AR12">
+        <v>0</v>
+      </c>
+      <c r="AS12">
+        <v>0.92</v>
+      </c>
+      <c r="AT12">
+        <v>0.92</v>
+      </c>
+      <c r="AU12">
+        <v>6</v>
+      </c>
+      <c r="AV12">
+        <v>5</v>
+      </c>
+      <c r="AW12">
+        <v>5</v>
+      </c>
+      <c r="AX12">
+        <v>7</v>
+      </c>
+      <c r="AY12">
+        <v>11</v>
+      </c>
+      <c r="AZ12">
+        <v>12</v>
+      </c>
+      <c r="BA12">
+        <v>6</v>
+      </c>
+      <c r="BB12">
+        <v>10</v>
+      </c>
+      <c r="BC12">
+        <v>16</v>
+      </c>
+      <c r="BD12">
+        <v>2.14</v>
+      </c>
+      <c r="BE12">
+        <v>5.9</v>
+      </c>
+      <c r="BF12">
+        <v>2.08</v>
+      </c>
+      <c r="BG12">
+        <v>1.57</v>
+      </c>
+      <c r="BH12">
+        <v>2.32</v>
+      </c>
+      <c r="BI12">
+        <v>2</v>
+      </c>
+      <c r="BJ12">
+        <v>1.8</v>
+      </c>
+      <c r="BK12">
+        <v>2.52</v>
+      </c>
+      <c r="BL12">
+        <v>1.46</v>
+      </c>
+      <c r="BM12">
+        <v>3.4</v>
+      </c>
+      <c r="BN12">
+        <v>1.25</v>
+      </c>
+      <c r="BO12">
+        <v>4.75</v>
+      </c>
+      <c r="BP12">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:68">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>7813832</v>
+      </c>
+      <c r="C13" t="s">
+        <v>68</v>
+      </c>
+      <c r="D13" t="s">
+        <v>69</v>
+      </c>
+      <c r="E13" s="2">
+        <v>45718.08333333334</v>
+      </c>
+      <c r="F13">
+        <v>2</v>
+      </c>
+      <c r="G13" t="s">
+        <v>72</v>
+      </c>
+      <c r="H13" t="s">
+        <v>78</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>1</v>
+      </c>
+      <c r="N13">
+        <v>1</v>
+      </c>
+      <c r="O13" t="s">
+        <v>85</v>
+      </c>
+      <c r="P13" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q13">
+        <v>2.43</v>
+      </c>
+      <c r="R13">
+        <v>2.2</v>
+      </c>
+      <c r="S13">
+        <v>4.2</v>
+      </c>
+      <c r="T13">
+        <v>1.36</v>
+      </c>
+      <c r="U13">
+        <v>3</v>
+      </c>
+      <c r="V13">
+        <v>2.6</v>
+      </c>
+      <c r="W13">
+        <v>1.44</v>
+      </c>
+      <c r="X13">
+        <v>7</v>
+      </c>
+      <c r="Y13">
+        <v>1.1</v>
+      </c>
+      <c r="Z13">
+        <v>1.89</v>
+      </c>
+      <c r="AA13">
+        <v>3.32</v>
+      </c>
+      <c r="AB13">
+        <v>4.2</v>
+      </c>
+      <c r="AC13">
+        <v>1.03</v>
+      </c>
+      <c r="AD13">
+        <v>9</v>
+      </c>
+      <c r="AE13">
+        <v>1.27</v>
+      </c>
+      <c r="AF13">
+        <v>3.55</v>
+      </c>
+      <c r="AG13">
+        <v>1.85</v>
+      </c>
+      <c r="AH13">
+        <v>1.89</v>
+      </c>
+      <c r="AI13">
+        <v>1.7</v>
+      </c>
+      <c r="AJ13">
+        <v>2.03</v>
+      </c>
+      <c r="AK13">
+        <v>1.24</v>
+      </c>
+      <c r="AL13">
+        <v>1.28</v>
+      </c>
+      <c r="AM13">
+        <v>1.78</v>
+      </c>
+      <c r="AN13">
+        <v>1</v>
+      </c>
+      <c r="AO13">
+        <v>0</v>
+      </c>
+      <c r="AP13">
+        <v>0.5</v>
+      </c>
+      <c r="AQ13">
+        <v>1.5</v>
+      </c>
+      <c r="AR13">
+        <v>1.4</v>
+      </c>
+      <c r="AS13">
+        <v>0.47</v>
+      </c>
+      <c r="AT13">
+        <v>1.87</v>
+      </c>
+      <c r="AU13">
+        <v>4</v>
+      </c>
+      <c r="AV13">
+        <v>4</v>
+      </c>
+      <c r="AW13">
+        <v>6</v>
+      </c>
+      <c r="AX13">
+        <v>7</v>
+      </c>
+      <c r="AY13">
+        <v>10</v>
+      </c>
+      <c r="AZ13">
+        <v>11</v>
+      </c>
+      <c r="BA13">
+        <v>10</v>
+      </c>
+      <c r="BB13">
+        <v>2</v>
+      </c>
+      <c r="BC13">
+        <v>12</v>
+      </c>
+      <c r="BD13">
+        <v>1.49</v>
+      </c>
+      <c r="BE13">
+        <v>6.7</v>
+      </c>
+      <c r="BF13">
+        <v>3.36</v>
+      </c>
+      <c r="BG13">
+        <v>1.32</v>
+      </c>
+      <c r="BH13">
+        <v>2.88</v>
+      </c>
+      <c r="BI13">
+        <v>1.59</v>
+      </c>
+      <c r="BJ13">
+        <v>2.1</v>
+      </c>
+      <c r="BK13">
+        <v>2.04</v>
+      </c>
+      <c r="BL13">
+        <v>1.66</v>
+      </c>
+      <c r="BM13">
+        <v>2.66</v>
+      </c>
+      <c r="BN13">
+        <v>1.37</v>
+      </c>
+      <c r="BO13">
+        <v>3.74</v>
+      </c>
+      <c r="BP13">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:68">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>7813833</v>
+      </c>
+      <c r="C14" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" t="s">
+        <v>69</v>
+      </c>
+      <c r="E14" s="2">
+        <v>45718.1875</v>
+      </c>
+      <c r="F14">
+        <v>2</v>
+      </c>
+      <c r="G14" t="s">
+        <v>71</v>
+      </c>
+      <c r="H14" t="s">
+        <v>76</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
+      <c r="M14">
+        <v>2</v>
+      </c>
+      <c r="N14">
+        <v>3</v>
+      </c>
+      <c r="O14" t="s">
+        <v>92</v>
+      </c>
+      <c r="P14" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q14">
+        <v>3.9</v>
+      </c>
+      <c r="R14">
+        <v>2.13</v>
+      </c>
+      <c r="S14">
+        <v>2.65</v>
+      </c>
+      <c r="T14">
+        <v>1.36</v>
+      </c>
+      <c r="U14">
+        <v>2.9</v>
+      </c>
+      <c r="V14">
+        <v>2.75</v>
+      </c>
+      <c r="W14">
+        <v>1.4</v>
+      </c>
+      <c r="X14">
+        <v>7.5</v>
+      </c>
+      <c r="Y14">
+        <v>1.08</v>
+      </c>
+      <c r="Z14">
+        <v>3.31</v>
+      </c>
+      <c r="AA14">
+        <v>3.47</v>
+      </c>
+      <c r="AB14">
+        <v>2.09</v>
+      </c>
+      <c r="AC14">
+        <v>1</v>
+      </c>
+      <c r="AD14">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE14">
+        <v>1.3</v>
+      </c>
+      <c r="AF14">
+        <v>3.35</v>
+      </c>
+      <c r="AG14">
+        <v>1.91</v>
+      </c>
+      <c r="AH14">
+        <v>1.83</v>
+      </c>
+      <c r="AI14">
+        <v>1.74</v>
+      </c>
+      <c r="AJ14">
+        <v>1.98</v>
+      </c>
+      <c r="AK14">
+        <v>1.67</v>
+      </c>
+      <c r="AL14">
+        <v>1.28</v>
+      </c>
+      <c r="AM14">
+        <v>1.3</v>
+      </c>
+      <c r="AN14">
+        <v>0</v>
+      </c>
+      <c r="AO14">
+        <v>0</v>
+      </c>
+      <c r="AP14">
+        <v>0</v>
+      </c>
+      <c r="AQ14">
+        <v>3</v>
+      </c>
+      <c r="AR14">
+        <v>1.15</v>
+      </c>
+      <c r="AS14">
+        <v>0</v>
+      </c>
+      <c r="AT14">
+        <v>1.15</v>
+      </c>
+      <c r="AU14">
+        <v>3</v>
+      </c>
+      <c r="AV14">
+        <v>7</v>
+      </c>
+      <c r="AW14">
+        <v>5</v>
+      </c>
+      <c r="AX14">
+        <v>5</v>
+      </c>
+      <c r="AY14">
+        <v>8</v>
+      </c>
+      <c r="AZ14">
+        <v>12</v>
+      </c>
+      <c r="BA14">
+        <v>4</v>
+      </c>
+      <c r="BB14">
+        <v>3</v>
+      </c>
+      <c r="BC14">
+        <v>7</v>
+      </c>
+      <c r="BD14">
+        <v>3.5</v>
+      </c>
+      <c r="BE14">
+        <v>6.8</v>
+      </c>
+      <c r="BF14">
+        <v>1.46</v>
+      </c>
+      <c r="BG14">
+        <v>1.28</v>
+      </c>
+      <c r="BH14">
+        <v>3.08</v>
+      </c>
+      <c r="BI14">
+        <v>1.52</v>
+      </c>
+      <c r="BJ14">
+        <v>2.24</v>
+      </c>
+      <c r="BK14">
+        <v>1.92</v>
+      </c>
+      <c r="BL14">
+        <v>1.75</v>
+      </c>
+      <c r="BM14">
+        <v>2.49</v>
+      </c>
+      <c r="BN14">
+        <v>1.42</v>
+      </c>
+      <c r="BO14">
+        <v>3.42</v>
+      </c>
+      <c r="BP14">
+        <v>1.23</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="104">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -295,6 +295,9 @@
     <t>['60']</t>
   </si>
   <si>
+    <t>['31']</t>
+  </si>
+  <si>
     <t>['1', '6']</t>
   </si>
   <si>
@@ -320,6 +323,9 @@
   </si>
   <si>
     <t>['85', '88']</t>
+  </si>
+  <si>
+    <t>['7']</t>
   </si>
 </sst>
 </file>
@@ -681,7 +687,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP14"/>
+  <dimension ref="A1:BP15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1143,7 +1149,7 @@
         <v>85</v>
       </c>
       <c r="P3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q3">
         <v>3.8</v>
@@ -1555,7 +1561,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q5">
         <v>4.5</v>
@@ -1839,7 +1845,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ6">
         <v>0</v>
@@ -1967,7 +1973,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q7">
         <v>2.85</v>
@@ -2173,7 +2179,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q8">
         <v>2.39</v>
@@ -2254,7 +2260,7 @@
         <v>3</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2585,7 +2591,7 @@
         <v>85</v>
       </c>
       <c r="P10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q10">
         <v>4.3</v>
@@ -2791,7 +2797,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q11">
         <v>2.8</v>
@@ -2997,7 +3003,7 @@
         <v>91</v>
       </c>
       <c r="P12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q12">
         <v>3.6</v>
@@ -3203,7 +3209,7 @@
         <v>85</v>
       </c>
       <c r="P13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q13">
         <v>2.43</v>
@@ -3409,7 +3415,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q14">
         <v>3.9</v>
@@ -3566,6 +3572,212 @@
       </c>
       <c r="BP14">
         <v>1.23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:68">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>7813834</v>
+      </c>
+      <c r="C15" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" s="2">
+        <v>45719.08333333334</v>
+      </c>
+      <c r="F15">
+        <v>2</v>
+      </c>
+      <c r="G15" t="s">
+        <v>74</v>
+      </c>
+      <c r="H15" t="s">
+        <v>83</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="K15">
+        <v>2</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
+      <c r="M15">
+        <v>1</v>
+      </c>
+      <c r="N15">
+        <v>2</v>
+      </c>
+      <c r="O15" t="s">
+        <v>93</v>
+      </c>
+      <c r="P15" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q15">
+        <v>3.4</v>
+      </c>
+      <c r="R15">
+        <v>1.95</v>
+      </c>
+      <c r="S15">
+        <v>3.6</v>
+      </c>
+      <c r="T15">
+        <v>1.53</v>
+      </c>
+      <c r="U15">
+        <v>2.38</v>
+      </c>
+      <c r="V15">
+        <v>3.5</v>
+      </c>
+      <c r="W15">
+        <v>1.29</v>
+      </c>
+      <c r="X15">
+        <v>11</v>
+      </c>
+      <c r="Y15">
+        <v>1.05</v>
+      </c>
+      <c r="Z15">
+        <v>2.6</v>
+      </c>
+      <c r="AA15">
+        <v>3.03</v>
+      </c>
+      <c r="AB15">
+        <v>2.82</v>
+      </c>
+      <c r="AC15">
+        <v>1.04</v>
+      </c>
+      <c r="AD15">
+        <v>7</v>
+      </c>
+      <c r="AE15">
+        <v>1.45</v>
+      </c>
+      <c r="AF15">
+        <v>2.65</v>
+      </c>
+      <c r="AG15">
+        <v>2.25</v>
+      </c>
+      <c r="AH15">
+        <v>1.53</v>
+      </c>
+      <c r="AI15">
+        <v>2</v>
+      </c>
+      <c r="AJ15">
+        <v>1.73</v>
+      </c>
+      <c r="AK15">
+        <v>1.4</v>
+      </c>
+      <c r="AL15">
+        <v>1.33</v>
+      </c>
+      <c r="AM15">
+        <v>1.46</v>
+      </c>
+      <c r="AN15">
+        <v>3</v>
+      </c>
+      <c r="AO15">
+        <v>0</v>
+      </c>
+      <c r="AP15">
+        <v>2</v>
+      </c>
+      <c r="AQ15">
+        <v>0.5</v>
+      </c>
+      <c r="AR15">
+        <v>0.82</v>
+      </c>
+      <c r="AS15">
+        <v>0.82</v>
+      </c>
+      <c r="AT15">
+        <v>1.64</v>
+      </c>
+      <c r="AU15">
+        <v>4</v>
+      </c>
+      <c r="AV15">
+        <v>2</v>
+      </c>
+      <c r="AW15">
+        <v>3</v>
+      </c>
+      <c r="AX15">
+        <v>4</v>
+      </c>
+      <c r="AY15">
+        <v>7</v>
+      </c>
+      <c r="AZ15">
+        <v>6</v>
+      </c>
+      <c r="BA15">
+        <v>3</v>
+      </c>
+      <c r="BB15">
+        <v>1</v>
+      </c>
+      <c r="BC15">
+        <v>4</v>
+      </c>
+      <c r="BD15">
+        <v>2.03</v>
+      </c>
+      <c r="BE15">
+        <v>5.95</v>
+      </c>
+      <c r="BF15">
+        <v>2.19</v>
+      </c>
+      <c r="BG15">
+        <v>1.48</v>
+      </c>
+      <c r="BH15">
+        <v>2.33</v>
+      </c>
+      <c r="BI15">
+        <v>1.88</v>
+      </c>
+      <c r="BJ15">
+        <v>1.78</v>
+      </c>
+      <c r="BK15">
+        <v>2.46</v>
+      </c>
+      <c r="BL15">
+        <v>1.43</v>
+      </c>
+      <c r="BM15">
+        <v>3.42</v>
+      </c>
+      <c r="BN15">
+        <v>1.23</v>
+      </c>
+      <c r="BO15">
+        <v>4.75</v>
+      </c>
+      <c r="BP15">
+        <v>1.13</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="109">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -250,15 +250,15 @@
     <t>Hwaseong</t>
   </si>
   <si>
+    <t>Gimpo Citizen</t>
+  </si>
+  <si>
     <t>Gyeongnam</t>
   </si>
   <si>
     <t>Jeonnam Dragons</t>
   </si>
   <si>
-    <t>Gimpo Citizen</t>
-  </si>
-  <si>
     <t>Suwon Bluewings</t>
   </si>
   <si>
@@ -298,6 +298,12 @@
     <t>['31']</t>
   </si>
   <si>
+    <t>['78']</t>
+  </si>
+  <si>
+    <t>['13', '70']</t>
+  </si>
+  <si>
     <t>['1', '6']</t>
   </si>
   <si>
@@ -326,6 +332,15 @@
   </si>
   <si>
     <t>['7']</t>
+  </si>
+  <si>
+    <t>['12', '23']</t>
+  </si>
+  <si>
+    <t>['50']</t>
+  </si>
+  <si>
+    <t>['17', '30', '56']</t>
   </si>
 </sst>
 </file>
@@ -687,7 +702,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP15"/>
+  <dimension ref="A1:BP19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -919,7 +934,7 @@
         <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -1024,7 +1039,7 @@
         <v>3</v>
       </c>
       <c r="AQ2">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1125,7 +1140,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1149,7 +1164,7 @@
         <v>85</v>
       </c>
       <c r="P3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="Q3">
         <v>3.8</v>
@@ -1230,7 +1245,7 @@
         <v>0</v>
       </c>
       <c r="AQ3">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1331,7 +1346,7 @@
         <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1561,7 +1576,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="Q5">
         <v>4.5</v>
@@ -1973,7 +1988,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q7">
         <v>2.85</v>
@@ -2179,7 +2194,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="Q8">
         <v>2.39</v>
@@ -2257,10 +2272,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AQ8">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2567,7 +2582,7 @@
         <v>73</v>
       </c>
       <c r="H10" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -2591,7 +2606,7 @@
         <v>85</v>
       </c>
       <c r="P10" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="Q10">
         <v>4.3</v>
@@ -2773,7 +2788,7 @@
         <v>75</v>
       </c>
       <c r="H11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -2797,7 +2812,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="Q11">
         <v>2.8</v>
@@ -2878,7 +2893,7 @@
         <v>2</v>
       </c>
       <c r="AQ11">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AR11">
         <v>1.04</v>
@@ -3003,7 +3018,7 @@
         <v>91</v>
       </c>
       <c r="P12" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="Q12">
         <v>3.6</v>
@@ -3185,7 +3200,7 @@
         <v>72</v>
       </c>
       <c r="H13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -3209,7 +3224,7 @@
         <v>85</v>
       </c>
       <c r="P13" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="Q13">
         <v>2.43</v>
@@ -3290,7 +3305,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ13">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR13">
         <v>1.4</v>
@@ -3415,7 +3430,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="Q14">
         <v>3.9</v>
@@ -3621,7 +3636,7 @@
         <v>93</v>
       </c>
       <c r="P15" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="Q15">
         <v>3.4</v>
@@ -3702,7 +3717,7 @@
         <v>2</v>
       </c>
       <c r="AQ15">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR15">
         <v>0.82</v>
@@ -3778,6 +3793,830 @@
       </c>
       <c r="BP15">
         <v>1.13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:68">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>7813835</v>
+      </c>
+      <c r="C16" t="s">
+        <v>68</v>
+      </c>
+      <c r="D16" t="s">
+        <v>69</v>
+      </c>
+      <c r="E16" s="2">
+        <v>45724.08333333334</v>
+      </c>
+      <c r="F16">
+        <v>3</v>
+      </c>
+      <c r="G16" t="s">
+        <v>76</v>
+      </c>
+      <c r="H16" t="s">
+        <v>72</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>2</v>
+      </c>
+      <c r="K16">
+        <v>2</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>2</v>
+      </c>
+      <c r="N16">
+        <v>2</v>
+      </c>
+      <c r="O16" t="s">
+        <v>85</v>
+      </c>
+      <c r="P16" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q16">
+        <v>3.18</v>
+      </c>
+      <c r="R16">
+        <v>1.98</v>
+      </c>
+      <c r="S16">
+        <v>3.36</v>
+      </c>
+      <c r="T16">
+        <v>1.45</v>
+      </c>
+      <c r="U16">
+        <v>2.55</v>
+      </c>
+      <c r="V16">
+        <v>3.14</v>
+      </c>
+      <c r="W16">
+        <v>1.31</v>
+      </c>
+      <c r="X16">
+        <v>7.6</v>
+      </c>
+      <c r="Y16">
+        <v>1.03</v>
+      </c>
+      <c r="Z16">
+        <v>2.61</v>
+      </c>
+      <c r="AA16">
+        <v>3.17</v>
+      </c>
+      <c r="AB16">
+        <v>2.7</v>
+      </c>
+      <c r="AC16">
+        <v>1.03</v>
+      </c>
+      <c r="AD16">
+        <v>7.4</v>
+      </c>
+      <c r="AE16">
+        <v>1.35</v>
+      </c>
+      <c r="AF16">
+        <v>2.74</v>
+      </c>
+      <c r="AG16">
+        <v>2.1</v>
+      </c>
+      <c r="AH16">
+        <v>1.6</v>
+      </c>
+      <c r="AI16">
+        <v>1.85</v>
+      </c>
+      <c r="AJ16">
+        <v>1.81</v>
+      </c>
+      <c r="AK16">
+        <v>1.41</v>
+      </c>
+      <c r="AL16">
+        <v>1.3</v>
+      </c>
+      <c r="AM16">
+        <v>1.44</v>
+      </c>
+      <c r="AN16">
+        <v>3</v>
+      </c>
+      <c r="AO16">
+        <v>0</v>
+      </c>
+      <c r="AP16">
+        <v>1.5</v>
+      </c>
+      <c r="AQ16">
+        <v>3</v>
+      </c>
+      <c r="AR16">
+        <v>1.61</v>
+      </c>
+      <c r="AS16">
+        <v>0</v>
+      </c>
+      <c r="AT16">
+        <v>1.61</v>
+      </c>
+      <c r="AU16">
+        <v>2</v>
+      </c>
+      <c r="AV16">
+        <v>3</v>
+      </c>
+      <c r="AW16">
+        <v>3</v>
+      </c>
+      <c r="AX16">
+        <v>4</v>
+      </c>
+      <c r="AY16">
+        <v>5</v>
+      </c>
+      <c r="AZ16">
+        <v>7</v>
+      </c>
+      <c r="BA16">
+        <v>5</v>
+      </c>
+      <c r="BB16">
+        <v>1</v>
+      </c>
+      <c r="BC16">
+        <v>6</v>
+      </c>
+      <c r="BD16">
+        <v>1.91</v>
+      </c>
+      <c r="BE16">
+        <v>7.5</v>
+      </c>
+      <c r="BF16">
+        <v>2.25</v>
+      </c>
+      <c r="BG16">
+        <v>1.5</v>
+      </c>
+      <c r="BH16">
+        <v>2.41</v>
+      </c>
+      <c r="BI16">
+        <v>1.87</v>
+      </c>
+      <c r="BJ16">
+        <v>1.87</v>
+      </c>
+      <c r="BK16">
+        <v>2.42</v>
+      </c>
+      <c r="BL16">
+        <v>1.53</v>
+      </c>
+      <c r="BM16">
+        <v>3.25</v>
+      </c>
+      <c r="BN16">
+        <v>1.29</v>
+      </c>
+      <c r="BO16">
+        <v>4.4</v>
+      </c>
+      <c r="BP16">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:68">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>7813836</v>
+      </c>
+      <c r="C17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D17" t="s">
+        <v>69</v>
+      </c>
+      <c r="E17" s="2">
+        <v>45724.08333333334</v>
+      </c>
+      <c r="F17">
+        <v>3</v>
+      </c>
+      <c r="G17" t="s">
+        <v>77</v>
+      </c>
+      <c r="H17" t="s">
+        <v>79</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>1</v>
+      </c>
+      <c r="M17">
+        <v>1</v>
+      </c>
+      <c r="N17">
+        <v>2</v>
+      </c>
+      <c r="O17" t="s">
+        <v>94</v>
+      </c>
+      <c r="P17" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q17">
+        <v>3</v>
+      </c>
+      <c r="R17">
+        <v>2.2</v>
+      </c>
+      <c r="S17">
+        <v>3.5</v>
+      </c>
+      <c r="T17">
+        <v>1.4</v>
+      </c>
+      <c r="U17">
+        <v>2.75</v>
+      </c>
+      <c r="V17">
+        <v>2.75</v>
+      </c>
+      <c r="W17">
+        <v>1.4</v>
+      </c>
+      <c r="X17">
+        <v>8</v>
+      </c>
+      <c r="Y17">
+        <v>1.08</v>
+      </c>
+      <c r="Z17">
+        <v>2.34</v>
+      </c>
+      <c r="AA17">
+        <v>3.28</v>
+      </c>
+      <c r="AB17">
+        <v>2.96</v>
+      </c>
+      <c r="AC17">
+        <v>1.05</v>
+      </c>
+      <c r="AD17">
+        <v>8.5</v>
+      </c>
+      <c r="AE17">
+        <v>1.28</v>
+      </c>
+      <c r="AF17">
+        <v>3.4</v>
+      </c>
+      <c r="AG17">
+        <v>1.85</v>
+      </c>
+      <c r="AH17">
+        <v>1.89</v>
+      </c>
+      <c r="AI17">
+        <v>1.67</v>
+      </c>
+      <c r="AJ17">
+        <v>2.1</v>
+      </c>
+      <c r="AK17">
+        <v>1.38</v>
+      </c>
+      <c r="AL17">
+        <v>1.3</v>
+      </c>
+      <c r="AM17">
+        <v>1.57</v>
+      </c>
+      <c r="AN17">
+        <v>1</v>
+      </c>
+      <c r="AO17">
+        <v>1.5</v>
+      </c>
+      <c r="AP17">
+        <v>1</v>
+      </c>
+      <c r="AQ17">
+        <v>1.33</v>
+      </c>
+      <c r="AR17">
+        <v>1.52</v>
+      </c>
+      <c r="AS17">
+        <v>0.89</v>
+      </c>
+      <c r="AT17">
+        <v>2.41</v>
+      </c>
+      <c r="AU17">
+        <v>4</v>
+      </c>
+      <c r="AV17">
+        <v>3</v>
+      </c>
+      <c r="AW17">
+        <v>6</v>
+      </c>
+      <c r="AX17">
+        <v>8</v>
+      </c>
+      <c r="AY17">
+        <v>11</v>
+      </c>
+      <c r="AZ17">
+        <v>15</v>
+      </c>
+      <c r="BA17">
+        <v>4</v>
+      </c>
+      <c r="BB17">
+        <v>4</v>
+      </c>
+      <c r="BC17">
+        <v>8</v>
+      </c>
+      <c r="BD17">
+        <v>1.91</v>
+      </c>
+      <c r="BE17">
+        <v>7.5</v>
+      </c>
+      <c r="BF17">
+        <v>2.2</v>
+      </c>
+      <c r="BG17">
+        <v>1.47</v>
+      </c>
+      <c r="BH17">
+        <v>2.5</v>
+      </c>
+      <c r="BI17">
+        <v>1.82</v>
+      </c>
+      <c r="BJ17">
+        <v>1.93</v>
+      </c>
+      <c r="BK17">
+        <v>2.34</v>
+      </c>
+      <c r="BL17">
+        <v>1.56</v>
+      </c>
+      <c r="BM17">
+        <v>3.02</v>
+      </c>
+      <c r="BN17">
+        <v>1.33</v>
+      </c>
+      <c r="BO17">
+        <v>4.2</v>
+      </c>
+      <c r="BP17">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:68">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>7813838</v>
+      </c>
+      <c r="C18" t="s">
+        <v>68</v>
+      </c>
+      <c r="D18" t="s">
+        <v>69</v>
+      </c>
+      <c r="E18" s="2">
+        <v>45724.1875</v>
+      </c>
+      <c r="F18">
+        <v>3</v>
+      </c>
+      <c r="G18" t="s">
+        <v>73</v>
+      </c>
+      <c r="H18" t="s">
+        <v>80</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>1</v>
+      </c>
+      <c r="N18">
+        <v>1</v>
+      </c>
+      <c r="O18" t="s">
+        <v>85</v>
+      </c>
+      <c r="P18" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q18">
+        <v>4.9</v>
+      </c>
+      <c r="R18">
+        <v>2.09</v>
+      </c>
+      <c r="S18">
+        <v>2.3</v>
+      </c>
+      <c r="T18">
+        <v>1.41</v>
+      </c>
+      <c r="U18">
+        <v>2.69</v>
+      </c>
+      <c r="V18">
+        <v>2.93</v>
+      </c>
+      <c r="W18">
+        <v>1.35</v>
+      </c>
+      <c r="X18">
+        <v>6.95</v>
+      </c>
+      <c r="Y18">
+        <v>1.04</v>
+      </c>
+      <c r="Z18">
+        <v>4.4</v>
+      </c>
+      <c r="AA18">
+        <v>3.64</v>
+      </c>
+      <c r="AB18">
+        <v>1.76</v>
+      </c>
+      <c r="AC18">
+        <v>1.02</v>
+      </c>
+      <c r="AD18">
+        <v>8.1</v>
+      </c>
+      <c r="AE18">
+        <v>1.3</v>
+      </c>
+      <c r="AF18">
+        <v>2.97</v>
+      </c>
+      <c r="AG18">
+        <v>1.98</v>
+      </c>
+      <c r="AH18">
+        <v>1.77</v>
+      </c>
+      <c r="AI18">
+        <v>1.87</v>
+      </c>
+      <c r="AJ18">
+        <v>1.79</v>
+      </c>
+      <c r="AK18">
+        <v>1.94</v>
+      </c>
+      <c r="AL18">
+        <v>1.25</v>
+      </c>
+      <c r="AM18">
+        <v>1.17</v>
+      </c>
+      <c r="AN18">
+        <v>0</v>
+      </c>
+      <c r="AO18">
+        <v>2</v>
+      </c>
+      <c r="AP18">
+        <v>0</v>
+      </c>
+      <c r="AQ18">
+        <v>2.33</v>
+      </c>
+      <c r="AR18">
+        <v>1.29</v>
+      </c>
+      <c r="AS18">
+        <v>1.62</v>
+      </c>
+      <c r="AT18">
+        <v>2.91</v>
+      </c>
+      <c r="AU18">
+        <v>2</v>
+      </c>
+      <c r="AV18">
+        <v>2</v>
+      </c>
+      <c r="AW18">
+        <v>8</v>
+      </c>
+      <c r="AX18">
+        <v>1</v>
+      </c>
+      <c r="AY18">
+        <v>10</v>
+      </c>
+      <c r="AZ18">
+        <v>3</v>
+      </c>
+      <c r="BA18">
+        <v>1</v>
+      </c>
+      <c r="BB18">
+        <v>1</v>
+      </c>
+      <c r="BC18">
+        <v>2</v>
+      </c>
+      <c r="BD18">
+        <v>2.75</v>
+      </c>
+      <c r="BE18">
+        <v>7.75</v>
+      </c>
+      <c r="BF18">
+        <v>1.65</v>
+      </c>
+      <c r="BG18">
+        <v>1.5</v>
+      </c>
+      <c r="BH18">
+        <v>2.41</v>
+      </c>
+      <c r="BI18">
+        <v>1.87</v>
+      </c>
+      <c r="BJ18">
+        <v>1.87</v>
+      </c>
+      <c r="BK18">
+        <v>2.42</v>
+      </c>
+      <c r="BL18">
+        <v>1.53</v>
+      </c>
+      <c r="BM18">
+        <v>3.25</v>
+      </c>
+      <c r="BN18">
+        <v>1.29</v>
+      </c>
+      <c r="BO18">
+        <v>4.4</v>
+      </c>
+      <c r="BP18">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:68">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>7813837</v>
+      </c>
+      <c r="C19" t="s">
+        <v>68</v>
+      </c>
+      <c r="D19" t="s">
+        <v>69</v>
+      </c>
+      <c r="E19" s="2">
+        <v>45724.1875</v>
+      </c>
+      <c r="F19">
+        <v>3</v>
+      </c>
+      <c r="G19" t="s">
+        <v>78</v>
+      </c>
+      <c r="H19" t="s">
+        <v>83</v>
+      </c>
+      <c r="I19">
+        <v>1</v>
+      </c>
+      <c r="J19">
+        <v>2</v>
+      </c>
+      <c r="K19">
+        <v>3</v>
+      </c>
+      <c r="L19">
+        <v>2</v>
+      </c>
+      <c r="M19">
+        <v>3</v>
+      </c>
+      <c r="N19">
+        <v>5</v>
+      </c>
+      <c r="O19" t="s">
+        <v>95</v>
+      </c>
+      <c r="P19" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q19">
+        <v>2.71</v>
+      </c>
+      <c r="R19">
+        <v>1.89</v>
+      </c>
+      <c r="S19">
+        <v>4.55</v>
+      </c>
+      <c r="T19">
+        <v>1.51</v>
+      </c>
+      <c r="U19">
+        <v>2.39</v>
+      </c>
+      <c r="V19">
+        <v>3.64</v>
+      </c>
+      <c r="W19">
+        <v>1.24</v>
+      </c>
+      <c r="X19">
+        <v>8.9</v>
+      </c>
+      <c r="Y19">
+        <v>1.01</v>
+      </c>
+      <c r="Z19">
+        <v>2.02</v>
+      </c>
+      <c r="AA19">
+        <v>3.12</v>
+      </c>
+      <c r="AB19">
+        <v>3.78</v>
+      </c>
+      <c r="AC19">
+        <v>1.03</v>
+      </c>
+      <c r="AD19">
+        <v>7.5</v>
+      </c>
+      <c r="AE19">
+        <v>1.42</v>
+      </c>
+      <c r="AF19">
+        <v>2.49</v>
+      </c>
+      <c r="AG19">
+        <v>2.48</v>
+      </c>
+      <c r="AH19">
+        <v>1.48</v>
+      </c>
+      <c r="AI19">
+        <v>2.1</v>
+      </c>
+      <c r="AJ19">
+        <v>1.62</v>
+      </c>
+      <c r="AK19">
+        <v>1.22</v>
+      </c>
+      <c r="AL19">
+        <v>1.3</v>
+      </c>
+      <c r="AM19">
+        <v>1.71</v>
+      </c>
+      <c r="AN19">
+        <v>0</v>
+      </c>
+      <c r="AO19">
+        <v>0.5</v>
+      </c>
+      <c r="AP19">
+        <v>0</v>
+      </c>
+      <c r="AQ19">
+        <v>1.33</v>
+      </c>
+      <c r="AR19">
+        <v>0</v>
+      </c>
+      <c r="AS19">
+        <v>0.73</v>
+      </c>
+      <c r="AT19">
+        <v>0.73</v>
+      </c>
+      <c r="AU19">
+        <v>9</v>
+      </c>
+      <c r="AV19">
+        <v>6</v>
+      </c>
+      <c r="AW19">
+        <v>6</v>
+      </c>
+      <c r="AX19">
+        <v>2</v>
+      </c>
+      <c r="AY19">
+        <v>15</v>
+      </c>
+      <c r="AZ19">
+        <v>8</v>
+      </c>
+      <c r="BA19">
+        <v>5</v>
+      </c>
+      <c r="BB19">
+        <v>2</v>
+      </c>
+      <c r="BC19">
+        <v>7</v>
+      </c>
+      <c r="BD19">
+        <v>1.75</v>
+      </c>
+      <c r="BE19">
+        <v>7</v>
+      </c>
+      <c r="BF19">
+        <v>2.54</v>
+      </c>
+      <c r="BG19">
+        <v>1.74</v>
+      </c>
+      <c r="BH19">
+        <v>2.02</v>
+      </c>
+      <c r="BI19">
+        <v>2.25</v>
+      </c>
+      <c r="BJ19">
+        <v>1.6</v>
+      </c>
+      <c r="BK19">
+        <v>2.95</v>
+      </c>
+      <c r="BL19">
+        <v>1.35</v>
+      </c>
+      <c r="BM19">
+        <v>4.15</v>
+      </c>
+      <c r="BN19">
+        <v>1.17</v>
+      </c>
+      <c r="BO19">
+        <v>5.85</v>
+      </c>
+      <c r="BP19">
+        <v>1.08</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="113">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -304,6 +304,12 @@
     <t>['13', '70']</t>
   </si>
   <si>
+    <t>['12', '37', '45+3', '76']</t>
+  </si>
+  <si>
+    <t>['80', '90+5']</t>
+  </si>
+  <si>
     <t>['1', '6']</t>
   </si>
   <si>
@@ -341,6 +347,12 @@
   </si>
   <si>
     <t>['17', '30', '56']</t>
+  </si>
+  <si>
+    <t>['20', '90+6']</t>
+  </si>
+  <si>
+    <t>['71']</t>
   </si>
 </sst>
 </file>
@@ -702,7 +714,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP19"/>
+  <dimension ref="A1:BP22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1164,7 +1176,7 @@
         <v>85</v>
       </c>
       <c r="P3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q3">
         <v>3.8</v>
@@ -1242,7 +1254,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ3">
         <v>2.33</v>
@@ -1576,7 +1588,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="Q5">
         <v>4.5</v>
@@ -1657,7 +1669,7 @@
         <v>0</v>
       </c>
       <c r="AQ5">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -1860,7 +1872,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ6">
         <v>0</v>
@@ -1988,7 +2000,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="Q7">
         <v>2.85</v>
@@ -2066,10 +2078,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ7">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2194,7 +2206,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="Q8">
         <v>2.39</v>
@@ -2481,7 +2493,7 @@
         <v>3</v>
       </c>
       <c r="AQ9">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AR9">
         <v>2.58</v>
@@ -2606,7 +2618,7 @@
         <v>85</v>
       </c>
       <c r="P10" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="Q10">
         <v>4.3</v>
@@ -2812,7 +2824,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="Q11">
         <v>2.8</v>
@@ -2890,7 +2902,7 @@
         <v>3</v>
       </c>
       <c r="AP11">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ11">
         <v>2.33</v>
@@ -3018,7 +3030,7 @@
         <v>91</v>
       </c>
       <c r="P12" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="Q12">
         <v>3.6</v>
@@ -3099,7 +3111,7 @@
         <v>1</v>
       </c>
       <c r="AQ12">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3224,7 +3236,7 @@
         <v>85</v>
       </c>
       <c r="P13" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="Q13">
         <v>2.43</v>
@@ -3430,7 +3442,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="Q14">
         <v>3.9</v>
@@ -3508,7 +3520,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ14">
         <v>3</v>
@@ -3636,7 +3648,7 @@
         <v>93</v>
       </c>
       <c r="P15" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="Q15">
         <v>3.4</v>
@@ -3714,7 +3726,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ15">
         <v>1.33</v>
@@ -3842,7 +3854,7 @@
         <v>85</v>
       </c>
       <c r="P16" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="Q16">
         <v>3.18</v>
@@ -4048,7 +4060,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="Q17">
         <v>3</v>
@@ -4254,7 +4266,7 @@
         <v>85</v>
       </c>
       <c r="P18" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="Q18">
         <v>4.9</v>
@@ -4460,7 +4472,7 @@
         <v>95</v>
       </c>
       <c r="P19" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="Q19">
         <v>2.71</v>
@@ -4617,6 +4629,624 @@
       </c>
       <c r="BP19">
         <v>1.08</v>
+      </c>
+    </row>
+    <row r="20" spans="1:68">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>7813839</v>
+      </c>
+      <c r="C20" t="s">
+        <v>68</v>
+      </c>
+      <c r="D20" t="s">
+        <v>69</v>
+      </c>
+      <c r="E20" s="2">
+        <v>45725.08333333334</v>
+      </c>
+      <c r="F20">
+        <v>3</v>
+      </c>
+      <c r="G20" t="s">
+        <v>75</v>
+      </c>
+      <c r="H20" t="s">
+        <v>81</v>
+      </c>
+      <c r="I20">
+        <v>3</v>
+      </c>
+      <c r="J20">
+        <v>1</v>
+      </c>
+      <c r="K20">
+        <v>4</v>
+      </c>
+      <c r="L20">
+        <v>4</v>
+      </c>
+      <c r="M20">
+        <v>2</v>
+      </c>
+      <c r="N20">
+        <v>6</v>
+      </c>
+      <c r="O20" t="s">
+        <v>96</v>
+      </c>
+      <c r="P20" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q20">
+        <v>3.5</v>
+      </c>
+      <c r="R20">
+        <v>2.1</v>
+      </c>
+      <c r="S20">
+        <v>3.1</v>
+      </c>
+      <c r="T20">
+        <v>1.44</v>
+      </c>
+      <c r="U20">
+        <v>2.63</v>
+      </c>
+      <c r="V20">
+        <v>3</v>
+      </c>
+      <c r="W20">
+        <v>1.36</v>
+      </c>
+      <c r="X20">
+        <v>9</v>
+      </c>
+      <c r="Y20">
+        <v>1.07</v>
+      </c>
+      <c r="Z20">
+        <v>2.84</v>
+      </c>
+      <c r="AA20">
+        <v>3.25</v>
+      </c>
+      <c r="AB20">
+        <v>2.44</v>
+      </c>
+      <c r="AC20">
+        <v>1.06</v>
+      </c>
+      <c r="AD20">
+        <v>8</v>
+      </c>
+      <c r="AE20">
+        <v>1.35</v>
+      </c>
+      <c r="AF20">
+        <v>3</v>
+      </c>
+      <c r="AG20">
+        <v>1.98</v>
+      </c>
+      <c r="AH20">
+        <v>1.77</v>
+      </c>
+      <c r="AI20">
+        <v>1.8</v>
+      </c>
+      <c r="AJ20">
+        <v>1.91</v>
+      </c>
+      <c r="AK20">
+        <v>1.53</v>
+      </c>
+      <c r="AL20">
+        <v>1.28</v>
+      </c>
+      <c r="AM20">
+        <v>1.4</v>
+      </c>
+      <c r="AN20">
+        <v>2</v>
+      </c>
+      <c r="AO20">
+        <v>1.5</v>
+      </c>
+      <c r="AP20">
+        <v>2.33</v>
+      </c>
+      <c r="AQ20">
+        <v>1</v>
+      </c>
+      <c r="AR20">
+        <v>1.06</v>
+      </c>
+      <c r="AS20">
+        <v>1.89</v>
+      </c>
+      <c r="AT20">
+        <v>2.95</v>
+      </c>
+      <c r="AU20">
+        <v>6</v>
+      </c>
+      <c r="AV20">
+        <v>4</v>
+      </c>
+      <c r="AW20">
+        <v>1</v>
+      </c>
+      <c r="AX20">
+        <v>5</v>
+      </c>
+      <c r="AY20">
+        <v>7</v>
+      </c>
+      <c r="AZ20">
+        <v>9</v>
+      </c>
+      <c r="BA20">
+        <v>4</v>
+      </c>
+      <c r="BB20">
+        <v>3</v>
+      </c>
+      <c r="BC20">
+        <v>7</v>
+      </c>
+      <c r="BD20">
+        <v>1.95</v>
+      </c>
+      <c r="BE20">
+        <v>7.5</v>
+      </c>
+      <c r="BF20">
+        <v>2.1</v>
+      </c>
+      <c r="BG20">
+        <v>1.47</v>
+      </c>
+      <c r="BH20">
+        <v>2.5</v>
+      </c>
+      <c r="BI20">
+        <v>1.82</v>
+      </c>
+      <c r="BJ20">
+        <v>1.93</v>
+      </c>
+      <c r="BK20">
+        <v>2.34</v>
+      </c>
+      <c r="BL20">
+        <v>1.56</v>
+      </c>
+      <c r="BM20">
+        <v>3.02</v>
+      </c>
+      <c r="BN20">
+        <v>1.33</v>
+      </c>
+      <c r="BO20">
+        <v>4.2</v>
+      </c>
+      <c r="BP20">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:68">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>7813840</v>
+      </c>
+      <c r="C21" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" t="s">
+        <v>69</v>
+      </c>
+      <c r="E21" s="2">
+        <v>45725.08333333334</v>
+      </c>
+      <c r="F21">
+        <v>3</v>
+      </c>
+      <c r="G21" t="s">
+        <v>71</v>
+      </c>
+      <c r="H21" t="s">
+        <v>82</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>1</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>1</v>
+      </c>
+      <c r="O21" t="s">
+        <v>94</v>
+      </c>
+      <c r="P21" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q21">
+        <v>4.15</v>
+      </c>
+      <c r="R21">
+        <v>2.09</v>
+      </c>
+      <c r="S21">
+        <v>2.52</v>
+      </c>
+      <c r="T21">
+        <v>1.37</v>
+      </c>
+      <c r="U21">
+        <v>2.84</v>
+      </c>
+      <c r="V21">
+        <v>2.84</v>
+      </c>
+      <c r="W21">
+        <v>1.37</v>
+      </c>
+      <c r="X21">
+        <v>7.2</v>
+      </c>
+      <c r="Y21">
+        <v>1.03</v>
+      </c>
+      <c r="Z21">
+        <v>3.52</v>
+      </c>
+      <c r="AA21">
+        <v>3.63</v>
+      </c>
+      <c r="AB21">
+        <v>1.96</v>
+      </c>
+      <c r="AC21">
+        <v>1.01</v>
+      </c>
+      <c r="AD21">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AE21">
+        <v>1.25</v>
+      </c>
+      <c r="AF21">
+        <v>3.28</v>
+      </c>
+      <c r="AG21">
+        <v>1.92</v>
+      </c>
+      <c r="AH21">
+        <v>1.82</v>
+      </c>
+      <c r="AI21">
+        <v>1.74</v>
+      </c>
+      <c r="AJ21">
+        <v>1.93</v>
+      </c>
+      <c r="AK21">
+        <v>1.75</v>
+      </c>
+      <c r="AL21">
+        <v>1.26</v>
+      </c>
+      <c r="AM21">
+        <v>1.25</v>
+      </c>
+      <c r="AN21">
+        <v>0</v>
+      </c>
+      <c r="AO21">
+        <v>0.5</v>
+      </c>
+      <c r="AP21">
+        <v>1</v>
+      </c>
+      <c r="AQ21">
+        <v>0.33</v>
+      </c>
+      <c r="AR21">
+        <v>1.02</v>
+      </c>
+      <c r="AS21">
+        <v>1.3</v>
+      </c>
+      <c r="AT21">
+        <v>2.32</v>
+      </c>
+      <c r="AU21">
+        <v>3</v>
+      </c>
+      <c r="AV21">
+        <v>6</v>
+      </c>
+      <c r="AW21">
+        <v>1</v>
+      </c>
+      <c r="AX21">
+        <v>7</v>
+      </c>
+      <c r="AY21">
+        <v>4</v>
+      </c>
+      <c r="AZ21">
+        <v>13</v>
+      </c>
+      <c r="BA21">
+        <v>3</v>
+      </c>
+      <c r="BB21">
+        <v>6</v>
+      </c>
+      <c r="BC21">
+        <v>9</v>
+      </c>
+      <c r="BD21">
+        <v>2.53</v>
+      </c>
+      <c r="BE21">
+        <v>7.5</v>
+      </c>
+      <c r="BF21">
+        <v>1.75</v>
+      </c>
+      <c r="BG21">
+        <v>1.5</v>
+      </c>
+      <c r="BH21">
+        <v>2.41</v>
+      </c>
+      <c r="BI21">
+        <v>1.87</v>
+      </c>
+      <c r="BJ21">
+        <v>1.87</v>
+      </c>
+      <c r="BK21">
+        <v>2.42</v>
+      </c>
+      <c r="BL21">
+        <v>1.53</v>
+      </c>
+      <c r="BM21">
+        <v>3.25</v>
+      </c>
+      <c r="BN21">
+        <v>1.29</v>
+      </c>
+      <c r="BO21">
+        <v>4.4</v>
+      </c>
+      <c r="BP21">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:68">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>7813841</v>
+      </c>
+      <c r="C22" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E22" s="2">
+        <v>45725.1875</v>
+      </c>
+      <c r="F22">
+        <v>3</v>
+      </c>
+      <c r="G22" t="s">
+        <v>74</v>
+      </c>
+      <c r="H22" t="s">
+        <v>70</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>2</v>
+      </c>
+      <c r="M22">
+        <v>1</v>
+      </c>
+      <c r="N22">
+        <v>3</v>
+      </c>
+      <c r="O22" t="s">
+        <v>97</v>
+      </c>
+      <c r="P22" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q22">
+        <v>5</v>
+      </c>
+      <c r="R22">
+        <v>2.1</v>
+      </c>
+      <c r="S22">
+        <v>2.4</v>
+      </c>
+      <c r="T22">
+        <v>1.44</v>
+      </c>
+      <c r="U22">
+        <v>2.63</v>
+      </c>
+      <c r="V22">
+        <v>3</v>
+      </c>
+      <c r="W22">
+        <v>1.36</v>
+      </c>
+      <c r="X22">
+        <v>9</v>
+      </c>
+      <c r="Y22">
+        <v>1.07</v>
+      </c>
+      <c r="Z22">
+        <v>5.3</v>
+      </c>
+      <c r="AA22">
+        <v>3.34</v>
+      </c>
+      <c r="AB22">
+        <v>1.72</v>
+      </c>
+      <c r="AC22">
+        <v>1.06</v>
+      </c>
+      <c r="AD22">
+        <v>8</v>
+      </c>
+      <c r="AE22">
+        <v>1.33</v>
+      </c>
+      <c r="AF22">
+        <v>3.1</v>
+      </c>
+      <c r="AG22">
+        <v>1.87</v>
+      </c>
+      <c r="AH22">
+        <v>1.87</v>
+      </c>
+      <c r="AI22">
+        <v>1.91</v>
+      </c>
+      <c r="AJ22">
+        <v>1.8</v>
+      </c>
+      <c r="AK22">
+        <v>1.95</v>
+      </c>
+      <c r="AL22">
+        <v>1.25</v>
+      </c>
+      <c r="AM22">
+        <v>1.17</v>
+      </c>
+      <c r="AN22">
+        <v>2</v>
+      </c>
+      <c r="AO22">
+        <v>0</v>
+      </c>
+      <c r="AP22">
+        <v>2.33</v>
+      </c>
+      <c r="AQ22">
+        <v>0</v>
+      </c>
+      <c r="AR22">
+        <v>0.92</v>
+      </c>
+      <c r="AS22">
+        <v>0</v>
+      </c>
+      <c r="AT22">
+        <v>0.92</v>
+      </c>
+      <c r="AU22">
+        <v>5</v>
+      </c>
+      <c r="AV22">
+        <v>4</v>
+      </c>
+      <c r="AW22">
+        <v>3</v>
+      </c>
+      <c r="AX22">
+        <v>3</v>
+      </c>
+      <c r="AY22">
+        <v>8</v>
+      </c>
+      <c r="AZ22">
+        <v>7</v>
+      </c>
+      <c r="BA22">
+        <v>3</v>
+      </c>
+      <c r="BB22">
+        <v>6</v>
+      </c>
+      <c r="BC22">
+        <v>9</v>
+      </c>
+      <c r="BD22">
+        <v>3.02</v>
+      </c>
+      <c r="BE22">
+        <v>8</v>
+      </c>
+      <c r="BF22">
+        <v>1.55</v>
+      </c>
+      <c r="BG22">
+        <v>1.42</v>
+      </c>
+      <c r="BH22">
+        <v>2.65</v>
+      </c>
+      <c r="BI22">
+        <v>1.73</v>
+      </c>
+      <c r="BJ22">
+        <v>2.03</v>
+      </c>
+      <c r="BK22">
+        <v>2.2</v>
+      </c>
+      <c r="BL22">
+        <v>1.63</v>
+      </c>
+      <c r="BM22">
+        <v>2.83</v>
+      </c>
+      <c r="BN22">
+        <v>1.37</v>
+      </c>
+      <c r="BO22">
+        <v>3.85</v>
+      </c>
+      <c r="BP22">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="116">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -253,15 +253,15 @@
     <t>Gimpo Citizen</t>
   </si>
   <si>
+    <t>Suwon Bluewings</t>
+  </si>
+  <si>
     <t>Gyeongnam</t>
   </si>
   <si>
     <t>Jeonnam Dragons</t>
   </si>
   <si>
-    <t>Suwon Bluewings</t>
-  </si>
-  <si>
     <t>Asan Mugunghwa</t>
   </si>
   <si>
@@ -310,6 +310,12 @@
     <t>['80', '90+5']</t>
   </si>
   <si>
+    <t>['76']</t>
+  </si>
+  <si>
+    <t>['66', '77']</t>
+  </si>
+  <si>
     <t>['1', '6']</t>
   </si>
   <si>
@@ -353,6 +359,9 @@
   </si>
   <si>
     <t>['71']</t>
+  </si>
+  <si>
+    <t>['90+5']</t>
   </si>
 </sst>
 </file>
@@ -714,7 +723,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP22"/>
+  <dimension ref="A1:BP26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -946,7 +955,7 @@
         <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -1152,7 +1161,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1176,7 +1185,7 @@
         <v>85</v>
       </c>
       <c r="P3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="Q3">
         <v>3.8</v>
@@ -1564,7 +1573,7 @@
         <v>73</v>
       </c>
       <c r="H5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1588,7 +1597,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="Q5">
         <v>4.5</v>
@@ -2000,7 +2009,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="Q7">
         <v>2.85</v>
@@ -2081,7 +2090,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ7">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2206,7 +2215,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="Q8">
         <v>2.39</v>
@@ -2287,7 +2296,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ8">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2388,7 +2397,7 @@
         <v>70</v>
       </c>
       <c r="H9" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -2618,7 +2627,7 @@
         <v>85</v>
       </c>
       <c r="P10" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="Q10">
         <v>4.3</v>
@@ -2800,7 +2809,7 @@
         <v>75</v>
       </c>
       <c r="H11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -2824,7 +2833,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="Q11">
         <v>2.8</v>
@@ -3030,7 +3039,7 @@
         <v>91</v>
       </c>
       <c r="P12" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="Q12">
         <v>3.6</v>
@@ -3108,10 +3117,10 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AQ12">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3212,7 +3221,7 @@
         <v>72</v>
       </c>
       <c r="H13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -3236,7 +3245,7 @@
         <v>85</v>
       </c>
       <c r="P13" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="Q13">
         <v>2.43</v>
@@ -3442,7 +3451,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="Q14">
         <v>3.9</v>
@@ -3648,7 +3657,7 @@
         <v>93</v>
       </c>
       <c r="P15" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="Q15">
         <v>3.4</v>
@@ -3729,7 +3738,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ15">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AR15">
         <v>0.82</v>
@@ -3854,7 +3863,7 @@
         <v>85</v>
       </c>
       <c r="P16" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="Q16">
         <v>3.18</v>
@@ -4036,7 +4045,7 @@
         <v>77</v>
       </c>
       <c r="H17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -4060,7 +4069,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="Q17">
         <v>3</v>
@@ -4138,7 +4147,7 @@
         <v>1.5</v>
       </c>
       <c r="AP17">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AQ17">
         <v>1.33</v>
@@ -4242,7 +4251,7 @@
         <v>73</v>
       </c>
       <c r="H18" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -4266,7 +4275,7 @@
         <v>85</v>
       </c>
       <c r="P18" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="Q18">
         <v>4.9</v>
@@ -4472,7 +4481,7 @@
         <v>95</v>
       </c>
       <c r="P19" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="Q19">
         <v>2.71</v>
@@ -4550,10 +4559,10 @@
         <v>0.5</v>
       </c>
       <c r="AP19">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AQ19">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -4654,7 +4663,7 @@
         <v>75</v>
       </c>
       <c r="H20" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="I20">
         <v>3</v>
@@ -4678,7 +4687,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="Q20">
         <v>3.5</v>
@@ -4965,7 +4974,7 @@
         <v>1</v>
       </c>
       <c r="AQ21">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AR21">
         <v>1.02</v>
@@ -5090,7 +5099,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="Q22">
         <v>5</v>
@@ -5247,6 +5256,830 @@
       </c>
       <c r="BP22">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:68">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>7813842</v>
+      </c>
+      <c r="C23" t="s">
+        <v>68</v>
+      </c>
+      <c r="D23" t="s">
+        <v>69</v>
+      </c>
+      <c r="E23" s="2">
+        <v>45731.08333333334</v>
+      </c>
+      <c r="F23">
+        <v>4</v>
+      </c>
+      <c r="G23" t="s">
+        <v>70</v>
+      </c>
+      <c r="H23" t="s">
+        <v>75</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>1</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>1</v>
+      </c>
+      <c r="O23" t="s">
+        <v>98</v>
+      </c>
+      <c r="P23" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q23">
+        <v>2.75</v>
+      </c>
+      <c r="R23">
+        <v>2.2</v>
+      </c>
+      <c r="S23">
+        <v>4</v>
+      </c>
+      <c r="T23">
+        <v>1.4</v>
+      </c>
+      <c r="U23">
+        <v>2.75</v>
+      </c>
+      <c r="V23">
+        <v>2.75</v>
+      </c>
+      <c r="W23">
+        <v>1.4</v>
+      </c>
+      <c r="X23">
+        <v>8</v>
+      </c>
+      <c r="Y23">
+        <v>1.08</v>
+      </c>
+      <c r="Z23">
+        <v>2.3</v>
+      </c>
+      <c r="AA23">
+        <v>3.1</v>
+      </c>
+      <c r="AB23">
+        <v>3.2</v>
+      </c>
+      <c r="AC23">
+        <v>1.06</v>
+      </c>
+      <c r="AD23">
+        <v>8</v>
+      </c>
+      <c r="AE23">
+        <v>1.3</v>
+      </c>
+      <c r="AF23">
+        <v>3.3</v>
+      </c>
+      <c r="AG23">
+        <v>1.87</v>
+      </c>
+      <c r="AH23">
+        <v>1.87</v>
+      </c>
+      <c r="AI23">
+        <v>1.67</v>
+      </c>
+      <c r="AJ23">
+        <v>2.1</v>
+      </c>
+      <c r="AK23">
+        <v>1.3</v>
+      </c>
+      <c r="AL23">
+        <v>1.3</v>
+      </c>
+      <c r="AM23">
+        <v>1.7</v>
+      </c>
+      <c r="AN23">
+        <v>3</v>
+      </c>
+      <c r="AO23">
+        <v>0</v>
+      </c>
+      <c r="AP23">
+        <v>3</v>
+      </c>
+      <c r="AQ23">
+        <v>0</v>
+      </c>
+      <c r="AR23">
+        <v>1.93</v>
+      </c>
+      <c r="AS23">
+        <v>0</v>
+      </c>
+      <c r="AT23">
+        <v>1.93</v>
+      </c>
+      <c r="AU23">
+        <v>2</v>
+      </c>
+      <c r="AV23">
+        <v>0</v>
+      </c>
+      <c r="AW23">
+        <v>9</v>
+      </c>
+      <c r="AX23">
+        <v>3</v>
+      </c>
+      <c r="AY23">
+        <v>11</v>
+      </c>
+      <c r="AZ23">
+        <v>3</v>
+      </c>
+      <c r="BA23">
+        <v>6</v>
+      </c>
+      <c r="BB23">
+        <v>2</v>
+      </c>
+      <c r="BC23">
+        <v>8</v>
+      </c>
+      <c r="BD23">
+        <v>1.72</v>
+      </c>
+      <c r="BE23">
+        <v>7.1</v>
+      </c>
+      <c r="BF23">
+        <v>2.72</v>
+      </c>
+      <c r="BG23">
+        <v>1.5</v>
+      </c>
+      <c r="BH23">
+        <v>2.42</v>
+      </c>
+      <c r="BI23">
+        <v>1.9</v>
+      </c>
+      <c r="BJ23">
+        <v>1.9</v>
+      </c>
+      <c r="BK23">
+        <v>2.41</v>
+      </c>
+      <c r="BL23">
+        <v>1.53</v>
+      </c>
+      <c r="BM23">
+        <v>3.22</v>
+      </c>
+      <c r="BN23">
+        <v>1.3</v>
+      </c>
+      <c r="BO23">
+        <v>4.4</v>
+      </c>
+      <c r="BP23">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:68">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>7813843</v>
+      </c>
+      <c r="C24" t="s">
+        <v>68</v>
+      </c>
+      <c r="D24" t="s">
+        <v>69</v>
+      </c>
+      <c r="E24" s="2">
+        <v>45731.08333333334</v>
+      </c>
+      <c r="F24">
+        <v>4</v>
+      </c>
+      <c r="G24" t="s">
+        <v>77</v>
+      </c>
+      <c r="H24" t="s">
+        <v>83</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>2</v>
+      </c>
+      <c r="M24">
+        <v>1</v>
+      </c>
+      <c r="N24">
+        <v>3</v>
+      </c>
+      <c r="O24" t="s">
+        <v>99</v>
+      </c>
+      <c r="P24" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q24">
+        <v>3</v>
+      </c>
+      <c r="R24">
+        <v>2.1</v>
+      </c>
+      <c r="S24">
+        <v>3.75</v>
+      </c>
+      <c r="T24">
+        <v>1.44</v>
+      </c>
+      <c r="U24">
+        <v>2.63</v>
+      </c>
+      <c r="V24">
+        <v>3.25</v>
+      </c>
+      <c r="W24">
+        <v>1.33</v>
+      </c>
+      <c r="X24">
+        <v>9</v>
+      </c>
+      <c r="Y24">
+        <v>1.07</v>
+      </c>
+      <c r="Z24">
+        <v>2.46</v>
+      </c>
+      <c r="AA24">
+        <v>3.26</v>
+      </c>
+      <c r="AB24">
+        <v>2.81</v>
+      </c>
+      <c r="AC24">
+        <v>1.06</v>
+      </c>
+      <c r="AD24">
+        <v>8</v>
+      </c>
+      <c r="AE24">
+        <v>1.36</v>
+      </c>
+      <c r="AF24">
+        <v>3</v>
+      </c>
+      <c r="AG24">
+        <v>1.98</v>
+      </c>
+      <c r="AH24">
+        <v>1.77</v>
+      </c>
+      <c r="AI24">
+        <v>1.83</v>
+      </c>
+      <c r="AJ24">
+        <v>1.83</v>
+      </c>
+      <c r="AK24">
+        <v>1.34</v>
+      </c>
+      <c r="AL24">
+        <v>1.32</v>
+      </c>
+      <c r="AM24">
+        <v>1.61</v>
+      </c>
+      <c r="AN24">
+        <v>1</v>
+      </c>
+      <c r="AO24">
+        <v>1.33</v>
+      </c>
+      <c r="AP24">
+        <v>1.67</v>
+      </c>
+      <c r="AQ24">
+        <v>1</v>
+      </c>
+      <c r="AR24">
+        <v>1.41</v>
+      </c>
+      <c r="AS24">
+        <v>0.87</v>
+      </c>
+      <c r="AT24">
+        <v>2.28</v>
+      </c>
+      <c r="AU24">
+        <v>9</v>
+      </c>
+      <c r="AV24">
+        <v>7</v>
+      </c>
+      <c r="AW24">
+        <v>6</v>
+      </c>
+      <c r="AX24">
+        <v>9</v>
+      </c>
+      <c r="AY24">
+        <v>18</v>
+      </c>
+      <c r="AZ24">
+        <v>16</v>
+      </c>
+      <c r="BA24">
+        <v>9</v>
+      </c>
+      <c r="BB24">
+        <v>8</v>
+      </c>
+      <c r="BC24">
+        <v>17</v>
+      </c>
+      <c r="BD24">
+        <v>1.65</v>
+      </c>
+      <c r="BE24">
+        <v>7.1</v>
+      </c>
+      <c r="BF24">
+        <v>2.91</v>
+      </c>
+      <c r="BG24">
+        <v>1.5</v>
+      </c>
+      <c r="BH24">
+        <v>2.41</v>
+      </c>
+      <c r="BI24">
+        <v>1.9</v>
+      </c>
+      <c r="BJ24">
+        <v>1.9</v>
+      </c>
+      <c r="BK24">
+        <v>2.42</v>
+      </c>
+      <c r="BL24">
+        <v>1.53</v>
+      </c>
+      <c r="BM24">
+        <v>3.25</v>
+      </c>
+      <c r="BN24">
+        <v>1.29</v>
+      </c>
+      <c r="BO24">
+        <v>4.4</v>
+      </c>
+      <c r="BP24">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="25" spans="1:68">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>7813844</v>
+      </c>
+      <c r="C25" t="s">
+        <v>68</v>
+      </c>
+      <c r="D25" t="s">
+        <v>69</v>
+      </c>
+      <c r="E25" s="2">
+        <v>45731.1875</v>
+      </c>
+      <c r="F25">
+        <v>4</v>
+      </c>
+      <c r="G25" t="s">
+        <v>78</v>
+      </c>
+      <c r="H25" t="s">
+        <v>74</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25" t="s">
+        <v>85</v>
+      </c>
+      <c r="P25" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q25">
+        <v>2.63</v>
+      </c>
+      <c r="R25">
+        <v>2.05</v>
+      </c>
+      <c r="S25">
+        <v>4.75</v>
+      </c>
+      <c r="T25">
+        <v>1.5</v>
+      </c>
+      <c r="U25">
+        <v>2.5</v>
+      </c>
+      <c r="V25">
+        <v>3.4</v>
+      </c>
+      <c r="W25">
+        <v>1.3</v>
+      </c>
+      <c r="X25">
+        <v>10</v>
+      </c>
+      <c r="Y25">
+        <v>1.06</v>
+      </c>
+      <c r="Z25">
+        <v>2.08</v>
+      </c>
+      <c r="AA25">
+        <v>3</v>
+      </c>
+      <c r="AB25">
+        <v>3.91</v>
+      </c>
+      <c r="AC25">
+        <v>1.08</v>
+      </c>
+      <c r="AD25">
+        <v>7</v>
+      </c>
+      <c r="AE25">
+        <v>1.42</v>
+      </c>
+      <c r="AF25">
+        <v>2.75</v>
+      </c>
+      <c r="AG25">
+        <v>2.2</v>
+      </c>
+      <c r="AH25">
+        <v>1.55</v>
+      </c>
+      <c r="AI25">
+        <v>2</v>
+      </c>
+      <c r="AJ25">
+        <v>1.73</v>
+      </c>
+      <c r="AK25">
+        <v>1.22</v>
+      </c>
+      <c r="AL25">
+        <v>1.28</v>
+      </c>
+      <c r="AM25">
+        <v>1.8</v>
+      </c>
+      <c r="AN25">
+        <v>0</v>
+      </c>
+      <c r="AO25">
+        <v>0</v>
+      </c>
+      <c r="AP25">
+        <v>0.5</v>
+      </c>
+      <c r="AQ25">
+        <v>1</v>
+      </c>
+      <c r="AR25">
+        <v>2.07</v>
+      </c>
+      <c r="AS25">
+        <v>0</v>
+      </c>
+      <c r="AT25">
+        <v>2.07</v>
+      </c>
+      <c r="AU25">
+        <v>3</v>
+      </c>
+      <c r="AV25">
+        <v>3</v>
+      </c>
+      <c r="AW25">
+        <v>5</v>
+      </c>
+      <c r="AX25">
+        <v>3</v>
+      </c>
+      <c r="AY25">
+        <v>8</v>
+      </c>
+      <c r="AZ25">
+        <v>6</v>
+      </c>
+      <c r="BA25">
+        <v>5</v>
+      </c>
+      <c r="BB25">
+        <v>2</v>
+      </c>
+      <c r="BC25">
+        <v>7</v>
+      </c>
+      <c r="BD25">
+        <v>1.59</v>
+      </c>
+      <c r="BE25">
+        <v>6.2</v>
+      </c>
+      <c r="BF25">
+        <v>3.05</v>
+      </c>
+      <c r="BG25">
+        <v>1.53</v>
+      </c>
+      <c r="BH25">
+        <v>2.21</v>
+      </c>
+      <c r="BI25">
+        <v>1.97</v>
+      </c>
+      <c r="BJ25">
+        <v>1.71</v>
+      </c>
+      <c r="BK25">
+        <v>2.59</v>
+      </c>
+      <c r="BL25">
+        <v>1.39</v>
+      </c>
+      <c r="BM25">
+        <v>3.7</v>
+      </c>
+      <c r="BN25">
+        <v>1.2</v>
+      </c>
+      <c r="BO25">
+        <v>4.75</v>
+      </c>
+      <c r="BP25">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:68">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>7813845</v>
+      </c>
+      <c r="C26" t="s">
+        <v>68</v>
+      </c>
+      <c r="D26" t="s">
+        <v>69</v>
+      </c>
+      <c r="E26" s="2">
+        <v>45731.1875</v>
+      </c>
+      <c r="F26">
+        <v>4</v>
+      </c>
+      <c r="G26" t="s">
+        <v>79</v>
+      </c>
+      <c r="H26" t="s">
+        <v>82</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26" t="s">
+        <v>85</v>
+      </c>
+      <c r="P26" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q26">
+        <v>3</v>
+      </c>
+      <c r="R26">
+        <v>2.2</v>
+      </c>
+      <c r="S26">
+        <v>3.6</v>
+      </c>
+      <c r="T26">
+        <v>1.4</v>
+      </c>
+      <c r="U26">
+        <v>2.75</v>
+      </c>
+      <c r="V26">
+        <v>2.75</v>
+      </c>
+      <c r="W26">
+        <v>1.4</v>
+      </c>
+      <c r="X26">
+        <v>8</v>
+      </c>
+      <c r="Y26">
+        <v>1.08</v>
+      </c>
+      <c r="Z26">
+        <v>2.3</v>
+      </c>
+      <c r="AA26">
+        <v>3.1</v>
+      </c>
+      <c r="AB26">
+        <v>3.2</v>
+      </c>
+      <c r="AC26">
+        <v>1.06</v>
+      </c>
+      <c r="AD26">
+        <v>8</v>
+      </c>
+      <c r="AE26">
+        <v>1.33</v>
+      </c>
+      <c r="AF26">
+        <v>3.2</v>
+      </c>
+      <c r="AG26">
+        <v>1.87</v>
+      </c>
+      <c r="AH26">
+        <v>1.87</v>
+      </c>
+      <c r="AI26">
+        <v>1.67</v>
+      </c>
+      <c r="AJ26">
+        <v>2.1</v>
+      </c>
+      <c r="AK26">
+        <v>1.28</v>
+      </c>
+      <c r="AL26">
+        <v>1.3</v>
+      </c>
+      <c r="AM26">
+        <v>1.75</v>
+      </c>
+      <c r="AN26">
+        <v>0</v>
+      </c>
+      <c r="AO26">
+        <v>0.33</v>
+      </c>
+      <c r="AP26">
+        <v>1</v>
+      </c>
+      <c r="AQ26">
+        <v>0.5</v>
+      </c>
+      <c r="AR26">
+        <v>0</v>
+      </c>
+      <c r="AS26">
+        <v>1.45</v>
+      </c>
+      <c r="AT26">
+        <v>1.45</v>
+      </c>
+      <c r="AU26">
+        <v>2</v>
+      </c>
+      <c r="AV26">
+        <v>3</v>
+      </c>
+      <c r="AW26">
+        <v>4</v>
+      </c>
+      <c r="AX26">
+        <v>5</v>
+      </c>
+      <c r="AY26">
+        <v>6</v>
+      </c>
+      <c r="AZ26">
+        <v>8</v>
+      </c>
+      <c r="BA26">
+        <v>7</v>
+      </c>
+      <c r="BB26">
+        <v>5</v>
+      </c>
+      <c r="BC26">
+        <v>12</v>
+      </c>
+      <c r="BD26">
+        <v>1.63</v>
+      </c>
+      <c r="BE26">
+        <v>7.9</v>
+      </c>
+      <c r="BF26">
+        <v>2.65</v>
+      </c>
+      <c r="BG26">
+        <v>1.45</v>
+      </c>
+      <c r="BH26">
+        <v>2.55</v>
+      </c>
+      <c r="BI26">
+        <v>1.8</v>
+      </c>
+      <c r="BJ26">
+        <v>2</v>
+      </c>
+      <c r="BK26">
+        <v>2.28</v>
+      </c>
+      <c r="BL26">
+        <v>1.58</v>
+      </c>
+      <c r="BM26">
+        <v>2.95</v>
+      </c>
+      <c r="BN26">
+        <v>1.35</v>
+      </c>
+      <c r="BO26">
+        <v>4.05</v>
+      </c>
+      <c r="BP26">
+        <v>1.18</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="122">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -316,6 +316,15 @@
     <t>['66', '77']</t>
   </si>
   <si>
+    <t>['23', '90+1']</t>
+  </si>
+  <si>
+    <t>['56', '76']</t>
+  </si>
+  <si>
+    <t>['3', '55', '78']</t>
+  </si>
+  <si>
     <t>['1', '6']</t>
   </si>
   <si>
@@ -362,6 +371,15 @@
   </si>
   <si>
     <t>['90+5']</t>
+  </si>
+  <si>
+    <t>['44']</t>
+  </si>
+  <si>
+    <t>['3', '71']</t>
+  </si>
+  <si>
+    <t>['12']</t>
   </si>
 </sst>
 </file>
@@ -723,7 +741,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP26"/>
+  <dimension ref="A1:BP29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1185,7 +1203,7 @@
         <v>85</v>
       </c>
       <c r="P3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="Q3">
         <v>3.8</v>
@@ -1266,7 +1284,7 @@
         <v>1</v>
       </c>
       <c r="AQ3">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1469,7 +1487,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ4">
         <v>2</v>
@@ -1597,7 +1615,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="Q5">
         <v>4.5</v>
@@ -2009,7 +2027,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="Q7">
         <v>2.85</v>
@@ -2215,7 +2233,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="Q8">
         <v>2.39</v>
@@ -2293,7 +2311,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AQ8">
         <v>1</v>
@@ -2627,7 +2645,7 @@
         <v>85</v>
       </c>
       <c r="P10" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="Q10">
         <v>4.3</v>
@@ -2833,7 +2851,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="Q11">
         <v>2.8</v>
@@ -2914,7 +2932,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ11">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AR11">
         <v>1.04</v>
@@ -3039,7 +3057,7 @@
         <v>91</v>
       </c>
       <c r="P12" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="Q12">
         <v>3.6</v>
@@ -3245,7 +3263,7 @@
         <v>85</v>
       </c>
       <c r="P13" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="Q13">
         <v>2.43</v>
@@ -3323,7 +3341,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ13">
         <v>1.33</v>
@@ -3451,7 +3469,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="Q14">
         <v>3.9</v>
@@ -3657,7 +3675,7 @@
         <v>93</v>
       </c>
       <c r="P15" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="Q15">
         <v>3.4</v>
@@ -3863,7 +3881,7 @@
         <v>85</v>
       </c>
       <c r="P16" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="Q16">
         <v>3.18</v>
@@ -3941,7 +3959,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AQ16">
         <v>3</v>
@@ -4069,7 +4087,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="Q17">
         <v>3</v>
@@ -4275,7 +4293,7 @@
         <v>85</v>
       </c>
       <c r="P18" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="Q18">
         <v>4.9</v>
@@ -4356,7 +4374,7 @@
         <v>0</v>
       </c>
       <c r="AQ18">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AR18">
         <v>1.29</v>
@@ -4481,7 +4499,7 @@
         <v>95</v>
       </c>
       <c r="P19" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="Q19">
         <v>2.71</v>
@@ -4687,7 +4705,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="Q20">
         <v>3.5</v>
@@ -5099,7 +5117,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="Q22">
         <v>5</v>
@@ -5511,7 +5529,7 @@
         <v>99</v>
       </c>
       <c r="P24" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="Q24">
         <v>3</v>
@@ -6080,6 +6098,624 @@
       </c>
       <c r="BP26">
         <v>1.18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:68">
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>7813846</v>
+      </c>
+      <c r="C27" t="s">
+        <v>68</v>
+      </c>
+      <c r="D27" t="s">
+        <v>69</v>
+      </c>
+      <c r="E27" s="2">
+        <v>45732.08333333334</v>
+      </c>
+      <c r="F27">
+        <v>4</v>
+      </c>
+      <c r="G27" t="s">
+        <v>72</v>
+      </c>
+      <c r="H27" t="s">
+        <v>71</v>
+      </c>
+      <c r="I27">
+        <v>1</v>
+      </c>
+      <c r="J27">
+        <v>1</v>
+      </c>
+      <c r="K27">
+        <v>2</v>
+      </c>
+      <c r="L27">
+        <v>2</v>
+      </c>
+      <c r="M27">
+        <v>1</v>
+      </c>
+      <c r="N27">
+        <v>3</v>
+      </c>
+      <c r="O27" t="s">
+        <v>100</v>
+      </c>
+      <c r="P27" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q27">
+        <v>2.25</v>
+      </c>
+      <c r="R27">
+        <v>2.2</v>
+      </c>
+      <c r="S27">
+        <v>5.5</v>
+      </c>
+      <c r="T27">
+        <v>1.4</v>
+      </c>
+      <c r="U27">
+        <v>2.75</v>
+      </c>
+      <c r="V27">
+        <v>3</v>
+      </c>
+      <c r="W27">
+        <v>1.36</v>
+      </c>
+      <c r="X27">
+        <v>8</v>
+      </c>
+      <c r="Y27">
+        <v>1.08</v>
+      </c>
+      <c r="Z27">
+        <v>1.62</v>
+      </c>
+      <c r="AA27">
+        <v>3.75</v>
+      </c>
+      <c r="AB27">
+        <v>5.3</v>
+      </c>
+      <c r="AC27">
+        <v>1.05</v>
+      </c>
+      <c r="AD27">
+        <v>8.5</v>
+      </c>
+      <c r="AE27">
+        <v>1.3</v>
+      </c>
+      <c r="AF27">
+        <v>3.3</v>
+      </c>
+      <c r="AG27">
+        <v>1.92</v>
+      </c>
+      <c r="AH27">
+        <v>1.82</v>
+      </c>
+      <c r="AI27">
+        <v>1.91</v>
+      </c>
+      <c r="AJ27">
+        <v>1.8</v>
+      </c>
+      <c r="AK27">
+        <v>1.16</v>
+      </c>
+      <c r="AL27">
+        <v>1.25</v>
+      </c>
+      <c r="AM27">
+        <v>2.2</v>
+      </c>
+      <c r="AN27">
+        <v>0.5</v>
+      </c>
+      <c r="AO27">
+        <v>0</v>
+      </c>
+      <c r="AP27">
+        <v>1.33</v>
+      </c>
+      <c r="AQ27">
+        <v>0</v>
+      </c>
+      <c r="AR27">
+        <v>1.42</v>
+      </c>
+      <c r="AS27">
+        <v>0</v>
+      </c>
+      <c r="AT27">
+        <v>1.42</v>
+      </c>
+      <c r="AU27">
+        <v>8</v>
+      </c>
+      <c r="AV27">
+        <v>2</v>
+      </c>
+      <c r="AW27">
+        <v>7</v>
+      </c>
+      <c r="AX27">
+        <v>0</v>
+      </c>
+      <c r="AY27">
+        <v>17</v>
+      </c>
+      <c r="AZ27">
+        <v>2</v>
+      </c>
+      <c r="BA27">
+        <v>6</v>
+      </c>
+      <c r="BB27">
+        <v>0</v>
+      </c>
+      <c r="BC27">
+        <v>6</v>
+      </c>
+      <c r="BD27">
+        <v>1.43</v>
+      </c>
+      <c r="BE27">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BF27">
+        <v>3.3</v>
+      </c>
+      <c r="BG27">
+        <v>1.27</v>
+      </c>
+      <c r="BH27">
+        <v>3.14</v>
+      </c>
+      <c r="BI27">
+        <v>1.51</v>
+      </c>
+      <c r="BJ27">
+        <v>2.26</v>
+      </c>
+      <c r="BK27">
+        <v>1.89</v>
+      </c>
+      <c r="BL27">
+        <v>1.77</v>
+      </c>
+      <c r="BM27">
+        <v>2.46</v>
+      </c>
+      <c r="BN27">
+        <v>1.43</v>
+      </c>
+      <c r="BO27">
+        <v>3.34</v>
+      </c>
+      <c r="BP27">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:68">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>7813847</v>
+      </c>
+      <c r="C28" t="s">
+        <v>68</v>
+      </c>
+      <c r="D28" t="s">
+        <v>69</v>
+      </c>
+      <c r="E28" s="2">
+        <v>45732.08333333334</v>
+      </c>
+      <c r="F28">
+        <v>4</v>
+      </c>
+      <c r="G28" t="s">
+        <v>80</v>
+      </c>
+      <c r="H28" t="s">
+        <v>81</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>1</v>
+      </c>
+      <c r="K28">
+        <v>1</v>
+      </c>
+      <c r="L28">
+        <v>2</v>
+      </c>
+      <c r="M28">
+        <v>2</v>
+      </c>
+      <c r="N28">
+        <v>4</v>
+      </c>
+      <c r="O28" t="s">
+        <v>101</v>
+      </c>
+      <c r="P28" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q28">
+        <v>4</v>
+      </c>
+      <c r="R28">
+        <v>2.2</v>
+      </c>
+      <c r="S28">
+        <v>2.63</v>
+      </c>
+      <c r="T28">
+        <v>1.36</v>
+      </c>
+      <c r="U28">
+        <v>3</v>
+      </c>
+      <c r="V28">
+        <v>2.75</v>
+      </c>
+      <c r="W28">
+        <v>1.4</v>
+      </c>
+      <c r="X28">
+        <v>7</v>
+      </c>
+      <c r="Y28">
+        <v>1.1</v>
+      </c>
+      <c r="Z28">
+        <v>3.45</v>
+      </c>
+      <c r="AA28">
+        <v>3.09</v>
+      </c>
+      <c r="AB28">
+        <v>2.2</v>
+      </c>
+      <c r="AC28">
+        <v>1.05</v>
+      </c>
+      <c r="AD28">
+        <v>8.5</v>
+      </c>
+      <c r="AE28">
+        <v>1.25</v>
+      </c>
+      <c r="AF28">
+        <v>3.6</v>
+      </c>
+      <c r="AG28">
+        <v>1.83</v>
+      </c>
+      <c r="AH28">
+        <v>1.91</v>
+      </c>
+      <c r="AI28">
+        <v>1.67</v>
+      </c>
+      <c r="AJ28">
+        <v>2.1</v>
+      </c>
+      <c r="AK28">
+        <v>1.73</v>
+      </c>
+      <c r="AL28">
+        <v>1.29</v>
+      </c>
+      <c r="AM28">
+        <v>1.3</v>
+      </c>
+      <c r="AN28">
+        <v>0</v>
+      </c>
+      <c r="AO28">
+        <v>2.33</v>
+      </c>
+      <c r="AP28">
+        <v>1</v>
+      </c>
+      <c r="AQ28">
+        <v>2</v>
+      </c>
+      <c r="AR28">
+        <v>0</v>
+      </c>
+      <c r="AS28">
+        <v>1.3</v>
+      </c>
+      <c r="AT28">
+        <v>1.3</v>
+      </c>
+      <c r="AU28">
+        <v>3</v>
+      </c>
+      <c r="AV28">
+        <v>5</v>
+      </c>
+      <c r="AW28">
+        <v>4</v>
+      </c>
+      <c r="AX28">
+        <v>3</v>
+      </c>
+      <c r="AY28">
+        <v>7</v>
+      </c>
+      <c r="AZ28">
+        <v>8</v>
+      </c>
+      <c r="BA28">
+        <v>3</v>
+      </c>
+      <c r="BB28">
+        <v>5</v>
+      </c>
+      <c r="BC28">
+        <v>8</v>
+      </c>
+      <c r="BD28">
+        <v>2.19</v>
+      </c>
+      <c r="BE28">
+        <v>6</v>
+      </c>
+      <c r="BF28">
+        <v>2.02</v>
+      </c>
+      <c r="BG28">
+        <v>1.38</v>
+      </c>
+      <c r="BH28">
+        <v>2.62</v>
+      </c>
+      <c r="BI28">
+        <v>1.71</v>
+      </c>
+      <c r="BJ28">
+        <v>1.97</v>
+      </c>
+      <c r="BK28">
+        <v>2.17</v>
+      </c>
+      <c r="BL28">
+        <v>1.55</v>
+      </c>
+      <c r="BM28">
+        <v>2.92</v>
+      </c>
+      <c r="BN28">
+        <v>1.31</v>
+      </c>
+      <c r="BO28">
+        <v>3.75</v>
+      </c>
+      <c r="BP28">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="29" spans="1:68">
+      <c r="A29" s="1">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>7813848</v>
+      </c>
+      <c r="C29" t="s">
+        <v>68</v>
+      </c>
+      <c r="D29" t="s">
+        <v>69</v>
+      </c>
+      <c r="E29" s="2">
+        <v>45732.1875</v>
+      </c>
+      <c r="F29">
+        <v>4</v>
+      </c>
+      <c r="G29" t="s">
+        <v>76</v>
+      </c>
+      <c r="H29" t="s">
+        <v>73</v>
+      </c>
+      <c r="I29">
+        <v>1</v>
+      </c>
+      <c r="J29">
+        <v>1</v>
+      </c>
+      <c r="K29">
+        <v>2</v>
+      </c>
+      <c r="L29">
+        <v>3</v>
+      </c>
+      <c r="M29">
+        <v>1</v>
+      </c>
+      <c r="N29">
+        <v>4</v>
+      </c>
+      <c r="O29" t="s">
+        <v>102</v>
+      </c>
+      <c r="P29" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q29">
+        <v>2.2</v>
+      </c>
+      <c r="R29">
+        <v>2.2</v>
+      </c>
+      <c r="S29">
+        <v>6</v>
+      </c>
+      <c r="T29">
+        <v>1.44</v>
+      </c>
+      <c r="U29">
+        <v>2.63</v>
+      </c>
+      <c r="V29">
+        <v>3.25</v>
+      </c>
+      <c r="W29">
+        <v>1.33</v>
+      </c>
+      <c r="X29">
+        <v>9</v>
+      </c>
+      <c r="Y29">
+        <v>1.07</v>
+      </c>
+      <c r="Z29">
+        <v>1.64</v>
+      </c>
+      <c r="AA29">
+        <v>3.76</v>
+      </c>
+      <c r="AB29">
+        <v>5.2</v>
+      </c>
+      <c r="AC29">
+        <v>1.05</v>
+      </c>
+      <c r="AD29">
+        <v>8.5</v>
+      </c>
+      <c r="AE29">
+        <v>1.35</v>
+      </c>
+      <c r="AF29">
+        <v>3</v>
+      </c>
+      <c r="AG29">
+        <v>1.95</v>
+      </c>
+      <c r="AH29">
+        <v>1.7</v>
+      </c>
+      <c r="AI29">
+        <v>2.1</v>
+      </c>
+      <c r="AJ29">
+        <v>1.67</v>
+      </c>
+      <c r="AK29">
+        <v>1.16</v>
+      </c>
+      <c r="AL29">
+        <v>1.25</v>
+      </c>
+      <c r="AM29">
+        <v>2.15</v>
+      </c>
+      <c r="AN29">
+        <v>1.5</v>
+      </c>
+      <c r="AO29">
+        <v>0</v>
+      </c>
+      <c r="AP29">
+        <v>2</v>
+      </c>
+      <c r="AQ29">
+        <v>0</v>
+      </c>
+      <c r="AR29">
+        <v>1.22</v>
+      </c>
+      <c r="AS29">
+        <v>0</v>
+      </c>
+      <c r="AT29">
+        <v>1.22</v>
+      </c>
+      <c r="AU29">
+        <v>5</v>
+      </c>
+      <c r="AV29">
+        <v>3</v>
+      </c>
+      <c r="AW29">
+        <v>8</v>
+      </c>
+      <c r="AX29">
+        <v>3</v>
+      </c>
+      <c r="AY29">
+        <v>13</v>
+      </c>
+      <c r="AZ29">
+        <v>6</v>
+      </c>
+      <c r="BA29">
+        <v>8</v>
+      </c>
+      <c r="BB29">
+        <v>4</v>
+      </c>
+      <c r="BC29">
+        <v>12</v>
+      </c>
+      <c r="BD29">
+        <v>1.41</v>
+      </c>
+      <c r="BE29">
+        <v>6.75</v>
+      </c>
+      <c r="BF29">
+        <v>3.84</v>
+      </c>
+      <c r="BG29">
+        <v>1.5</v>
+      </c>
+      <c r="BH29">
+        <v>2.28</v>
+      </c>
+      <c r="BI29">
+        <v>1.92</v>
+      </c>
+      <c r="BJ29">
+        <v>1.75</v>
+      </c>
+      <c r="BK29">
+        <v>2.52</v>
+      </c>
+      <c r="BL29">
+        <v>1.41</v>
+      </c>
+      <c r="BM29">
+        <v>3.5</v>
+      </c>
+      <c r="BN29">
+        <v>1.22</v>
+      </c>
+      <c r="BO29">
+        <v>4.7</v>
+      </c>
+      <c r="BP29">
+        <v>1.14</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="128">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -325,6 +325,15 @@
     <t>['3', '55', '78']</t>
   </si>
   <si>
+    <t>['45+6', '90+1', '90+5']</t>
+  </si>
+  <si>
+    <t>['65', '90+2']</t>
+  </si>
+  <si>
+    <t>['30', '81', '90+1']</t>
+  </si>
+  <si>
     <t>['1', '6']</t>
   </si>
   <si>
@@ -380,6 +389,15 @@
   </si>
   <si>
     <t>['12']</t>
+  </si>
+  <si>
+    <t>['10', '30', '70']</t>
+  </si>
+  <si>
+    <t>['33']</t>
+  </si>
+  <si>
+    <t>['21']</t>
   </si>
 </sst>
 </file>
@@ -741,7 +759,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP29"/>
+  <dimension ref="A1:BP33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1075,7 +1093,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AQ2">
         <v>1.33</v>
@@ -1203,7 +1221,7 @@
         <v>85</v>
       </c>
       <c r="P3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="Q3">
         <v>3.8</v>
@@ -1284,7 +1302,7 @@
         <v>1</v>
       </c>
       <c r="AQ3">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1615,7 +1633,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="Q5">
         <v>4.5</v>
@@ -1693,7 +1711,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AQ5">
         <v>1</v>
@@ -1902,7 +1920,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2027,7 +2045,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="Q7">
         <v>2.85</v>
@@ -2233,7 +2251,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="Q8">
         <v>2.39</v>
@@ -2314,7 +2332,7 @@
         <v>2</v>
       </c>
       <c r="AQ8">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2517,7 +2535,7 @@
         <v>3</v>
       </c>
       <c r="AP9">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AQ9">
         <v>1</v>
@@ -2645,7 +2663,7 @@
         <v>85</v>
       </c>
       <c r="P10" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="Q10">
         <v>4.3</v>
@@ -2723,7 +2741,7 @@
         <v>1</v>
       </c>
       <c r="AP10">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AQ10">
         <v>2</v>
@@ -2851,7 +2869,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="Q11">
         <v>2.8</v>
@@ -2932,7 +2950,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ11">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AR11">
         <v>1.04</v>
@@ -3057,7 +3075,7 @@
         <v>91</v>
       </c>
       <c r="P12" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="Q12">
         <v>3.6</v>
@@ -3263,7 +3281,7 @@
         <v>85</v>
       </c>
       <c r="P13" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="Q13">
         <v>2.43</v>
@@ -3469,7 +3487,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="Q14">
         <v>3.9</v>
@@ -3675,7 +3693,7 @@
         <v>93</v>
       </c>
       <c r="P15" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="Q15">
         <v>3.4</v>
@@ -3756,7 +3774,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ15">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AR15">
         <v>0.82</v>
@@ -3881,7 +3899,7 @@
         <v>85</v>
       </c>
       <c r="P16" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="Q16">
         <v>3.18</v>
@@ -3962,7 +3980,7 @@
         <v>2</v>
       </c>
       <c r="AQ16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR16">
         <v>1.61</v>
@@ -4087,7 +4105,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="Q17">
         <v>3</v>
@@ -4293,7 +4311,7 @@
         <v>85</v>
       </c>
       <c r="P18" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="Q18">
         <v>4.9</v>
@@ -4371,10 +4389,10 @@
         <v>2</v>
       </c>
       <c r="AP18">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AQ18">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AR18">
         <v>1.29</v>
@@ -4499,7 +4517,7 @@
         <v>95</v>
       </c>
       <c r="P19" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="Q19">
         <v>2.71</v>
@@ -4580,7 +4598,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ19">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -4705,7 +4723,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="Q20">
         <v>3.5</v>
@@ -5117,7 +5135,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="Q22">
         <v>5</v>
@@ -5401,7 +5419,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AQ23">
         <v>0</v>
@@ -5529,7 +5547,7 @@
         <v>99</v>
       </c>
       <c r="P24" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="Q24">
         <v>3</v>
@@ -5610,7 +5628,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ24">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AR24">
         <v>1.41</v>
@@ -6019,7 +6037,7 @@
         <v>0.33</v>
       </c>
       <c r="AP26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ26">
         <v>0.5</v>
@@ -6147,7 +6165,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="Q27">
         <v>2.25</v>
@@ -6353,7 +6371,7 @@
         <v>101</v>
       </c>
       <c r="P28" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="Q28">
         <v>4</v>
@@ -6431,10 +6449,10 @@
         <v>2.33</v>
       </c>
       <c r="AP28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ28">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AR28">
         <v>0</v>
@@ -6559,7 +6577,7 @@
         <v>102</v>
       </c>
       <c r="P29" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="Q29">
         <v>2.2</v>
@@ -6716,6 +6734,830 @@
       </c>
       <c r="BP29">
         <v>1.14</v>
+      </c>
+    </row>
+    <row r="30" spans="1:68">
+      <c r="A30" s="1">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>7813849</v>
+      </c>
+      <c r="C30" t="s">
+        <v>68</v>
+      </c>
+      <c r="D30" t="s">
+        <v>69</v>
+      </c>
+      <c r="E30" s="2">
+        <v>45745.08333333334</v>
+      </c>
+      <c r="F30">
+        <v>5</v>
+      </c>
+      <c r="G30" t="s">
+        <v>73</v>
+      </c>
+      <c r="H30" t="s">
+        <v>77</v>
+      </c>
+      <c r="I30">
+        <v>1</v>
+      </c>
+      <c r="J30">
+        <v>2</v>
+      </c>
+      <c r="K30">
+        <v>3</v>
+      </c>
+      <c r="L30">
+        <v>3</v>
+      </c>
+      <c r="M30">
+        <v>3</v>
+      </c>
+      <c r="N30">
+        <v>6</v>
+      </c>
+      <c r="O30" t="s">
+        <v>103</v>
+      </c>
+      <c r="P30" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q30">
+        <v>3.75</v>
+      </c>
+      <c r="R30">
+        <v>2.05</v>
+      </c>
+      <c r="S30">
+        <v>3.1</v>
+      </c>
+      <c r="T30">
+        <v>1.44</v>
+      </c>
+      <c r="U30">
+        <v>2.63</v>
+      </c>
+      <c r="V30">
+        <v>3.4</v>
+      </c>
+      <c r="W30">
+        <v>1.3</v>
+      </c>
+      <c r="X30">
+        <v>10</v>
+      </c>
+      <c r="Y30">
+        <v>1.06</v>
+      </c>
+      <c r="Z30">
+        <v>2.68</v>
+      </c>
+      <c r="AA30">
+        <v>3.28</v>
+      </c>
+      <c r="AB30">
+        <v>2.55</v>
+      </c>
+      <c r="AC30">
+        <v>1.06</v>
+      </c>
+      <c r="AD30">
+        <v>8</v>
+      </c>
+      <c r="AE30">
+        <v>1.38</v>
+      </c>
+      <c r="AF30">
+        <v>2.9</v>
+      </c>
+      <c r="AG30">
+        <v>2.15</v>
+      </c>
+      <c r="AH30">
+        <v>1.63</v>
+      </c>
+      <c r="AI30">
+        <v>1.83</v>
+      </c>
+      <c r="AJ30">
+        <v>1.83</v>
+      </c>
+      <c r="AK30">
+        <v>1.58</v>
+      </c>
+      <c r="AL30">
+        <v>1.31</v>
+      </c>
+      <c r="AM30">
+        <v>1.37</v>
+      </c>
+      <c r="AN30">
+        <v>0</v>
+      </c>
+      <c r="AO30">
+        <v>0</v>
+      </c>
+      <c r="AP30">
+        <v>0.25</v>
+      </c>
+      <c r="AQ30">
+        <v>0.5</v>
+      </c>
+      <c r="AR30">
+        <v>1.22</v>
+      </c>
+      <c r="AS30">
+        <v>0.8</v>
+      </c>
+      <c r="AT30">
+        <v>2.02</v>
+      </c>
+      <c r="AU30">
+        <v>7</v>
+      </c>
+      <c r="AV30">
+        <v>5</v>
+      </c>
+      <c r="AW30">
+        <v>3</v>
+      </c>
+      <c r="AX30">
+        <v>3</v>
+      </c>
+      <c r="AY30">
+        <v>10</v>
+      </c>
+      <c r="AZ30">
+        <v>8</v>
+      </c>
+      <c r="BA30">
+        <v>6</v>
+      </c>
+      <c r="BB30">
+        <v>7</v>
+      </c>
+      <c r="BC30">
+        <v>13</v>
+      </c>
+      <c r="BD30">
+        <v>2.52</v>
+      </c>
+      <c r="BE30">
+        <v>7.7</v>
+      </c>
+      <c r="BF30">
+        <v>1.69</v>
+      </c>
+      <c r="BG30">
+        <v>1.49</v>
+      </c>
+      <c r="BH30">
+        <v>2.44</v>
+      </c>
+      <c r="BI30">
+        <v>1.95</v>
+      </c>
+      <c r="BJ30">
+        <v>1.85</v>
+      </c>
+      <c r="BK30">
+        <v>2.39</v>
+      </c>
+      <c r="BL30">
+        <v>1.54</v>
+      </c>
+      <c r="BM30">
+        <v>3.2</v>
+      </c>
+      <c r="BN30">
+        <v>1.3</v>
+      </c>
+      <c r="BO30">
+        <v>4.3</v>
+      </c>
+      <c r="BP30">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="31" spans="1:68">
+      <c r="A31" s="1">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>7813850</v>
+      </c>
+      <c r="C31" t="s">
+        <v>68</v>
+      </c>
+      <c r="D31" t="s">
+        <v>69</v>
+      </c>
+      <c r="E31" s="2">
+        <v>45745.08333333334</v>
+      </c>
+      <c r="F31">
+        <v>5</v>
+      </c>
+      <c r="G31" t="s">
+        <v>79</v>
+      </c>
+      <c r="H31" t="s">
+        <v>81</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>1</v>
+      </c>
+      <c r="K31">
+        <v>1</v>
+      </c>
+      <c r="L31">
+        <v>2</v>
+      </c>
+      <c r="M31">
+        <v>1</v>
+      </c>
+      <c r="N31">
+        <v>3</v>
+      </c>
+      <c r="O31" t="s">
+        <v>104</v>
+      </c>
+      <c r="P31" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q31">
+        <v>3.25</v>
+      </c>
+      <c r="R31">
+        <v>2.2</v>
+      </c>
+      <c r="S31">
+        <v>3.25</v>
+      </c>
+      <c r="T31">
+        <v>1.4</v>
+      </c>
+      <c r="U31">
+        <v>2.75</v>
+      </c>
+      <c r="V31">
+        <v>2.75</v>
+      </c>
+      <c r="W31">
+        <v>1.4</v>
+      </c>
+      <c r="X31">
+        <v>8</v>
+      </c>
+      <c r="Y31">
+        <v>1.08</v>
+      </c>
+      <c r="Z31">
+        <v>2.69</v>
+      </c>
+      <c r="AA31">
+        <v>3.07</v>
+      </c>
+      <c r="AB31">
+        <v>2.69</v>
+      </c>
+      <c r="AC31">
+        <v>1.06</v>
+      </c>
+      <c r="AD31">
+        <v>8</v>
+      </c>
+      <c r="AE31">
+        <v>1.33</v>
+      </c>
+      <c r="AF31">
+        <v>3.2</v>
+      </c>
+      <c r="AG31">
+        <v>1.85</v>
+      </c>
+      <c r="AH31">
+        <v>1.85</v>
+      </c>
+      <c r="AI31">
+        <v>1.67</v>
+      </c>
+      <c r="AJ31">
+        <v>2.1</v>
+      </c>
+      <c r="AK31">
+        <v>1.36</v>
+      </c>
+      <c r="AL31">
+        <v>1.3</v>
+      </c>
+      <c r="AM31">
+        <v>1.61</v>
+      </c>
+      <c r="AN31">
+        <v>1</v>
+      </c>
+      <c r="AO31">
+        <v>2</v>
+      </c>
+      <c r="AP31">
+        <v>2</v>
+      </c>
+      <c r="AQ31">
+        <v>1.6</v>
+      </c>
+      <c r="AR31">
+        <v>1.17</v>
+      </c>
+      <c r="AS31">
+        <v>1.26</v>
+      </c>
+      <c r="AT31">
+        <v>2.43</v>
+      </c>
+      <c r="AU31">
+        <v>8</v>
+      </c>
+      <c r="AV31">
+        <v>7</v>
+      </c>
+      <c r="AW31">
+        <v>9</v>
+      </c>
+      <c r="AX31">
+        <v>7</v>
+      </c>
+      <c r="AY31">
+        <v>17</v>
+      </c>
+      <c r="AZ31">
+        <v>14</v>
+      </c>
+      <c r="BA31">
+        <v>4</v>
+      </c>
+      <c r="BB31">
+        <v>3</v>
+      </c>
+      <c r="BC31">
+        <v>7</v>
+      </c>
+      <c r="BD31">
+        <v>1.54</v>
+      </c>
+      <c r="BE31">
+        <v>8</v>
+      </c>
+      <c r="BF31">
+        <v>2.91</v>
+      </c>
+      <c r="BG31">
+        <v>1.46</v>
+      </c>
+      <c r="BH31">
+        <v>2.52</v>
+      </c>
+      <c r="BI31">
+        <v>1.82</v>
+      </c>
+      <c r="BJ31">
+        <v>1.98</v>
+      </c>
+      <c r="BK31">
+        <v>2.32</v>
+      </c>
+      <c r="BL31">
+        <v>1.57</v>
+      </c>
+      <c r="BM31">
+        <v>3</v>
+      </c>
+      <c r="BN31">
+        <v>1.34</v>
+      </c>
+      <c r="BO31">
+        <v>4.15</v>
+      </c>
+      <c r="BP31">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:68">
+      <c r="A32" s="1">
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <v>7813851</v>
+      </c>
+      <c r="C32" t="s">
+        <v>68</v>
+      </c>
+      <c r="D32" t="s">
+        <v>69</v>
+      </c>
+      <c r="E32" s="2">
+        <v>45745.1875</v>
+      </c>
+      <c r="F32">
+        <v>5</v>
+      </c>
+      <c r="G32" t="s">
+        <v>80</v>
+      </c>
+      <c r="H32" t="s">
+        <v>83</v>
+      </c>
+      <c r="I32">
+        <v>1</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>1</v>
+      </c>
+      <c r="L32">
+        <v>3</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>3</v>
+      </c>
+      <c r="O32" t="s">
+        <v>105</v>
+      </c>
+      <c r="P32" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q32">
+        <v>3.2</v>
+      </c>
+      <c r="R32">
+        <v>2.05</v>
+      </c>
+      <c r="S32">
+        <v>3.6</v>
+      </c>
+      <c r="T32">
+        <v>1.5</v>
+      </c>
+      <c r="U32">
+        <v>2.5</v>
+      </c>
+      <c r="V32">
+        <v>3.4</v>
+      </c>
+      <c r="W32">
+        <v>1.3</v>
+      </c>
+      <c r="X32">
+        <v>10</v>
+      </c>
+      <c r="Y32">
+        <v>1.06</v>
+      </c>
+      <c r="Z32">
+        <v>2.41</v>
+      </c>
+      <c r="AA32">
+        <v>3.2</v>
+      </c>
+      <c r="AB32">
+        <v>2.92</v>
+      </c>
+      <c r="AC32">
+        <v>1.03</v>
+      </c>
+      <c r="AD32">
+        <v>7.2</v>
+      </c>
+      <c r="AE32">
+        <v>1.35</v>
+      </c>
+      <c r="AF32">
+        <v>2.74</v>
+      </c>
+      <c r="AG32">
+        <v>2.05</v>
+      </c>
+      <c r="AH32">
+        <v>1.61</v>
+      </c>
+      <c r="AI32">
+        <v>1.83</v>
+      </c>
+      <c r="AJ32">
+        <v>1.83</v>
+      </c>
+      <c r="AK32">
+        <v>1.36</v>
+      </c>
+      <c r="AL32">
+        <v>1.36</v>
+      </c>
+      <c r="AM32">
+        <v>1.53</v>
+      </c>
+      <c r="AN32">
+        <v>1</v>
+      </c>
+      <c r="AO32">
+        <v>1</v>
+      </c>
+      <c r="AP32">
+        <v>2</v>
+      </c>
+      <c r="AQ32">
+        <v>0.8</v>
+      </c>
+      <c r="AR32">
+        <v>1.01</v>
+      </c>
+      <c r="AS32">
+        <v>1.11</v>
+      </c>
+      <c r="AT32">
+        <v>2.12</v>
+      </c>
+      <c r="AU32">
+        <v>9</v>
+      </c>
+      <c r="AV32">
+        <v>4</v>
+      </c>
+      <c r="AW32">
+        <v>13</v>
+      </c>
+      <c r="AX32">
+        <v>4</v>
+      </c>
+      <c r="AY32">
+        <v>27</v>
+      </c>
+      <c r="AZ32">
+        <v>8</v>
+      </c>
+      <c r="BA32">
+        <v>5</v>
+      </c>
+      <c r="BB32">
+        <v>2</v>
+      </c>
+      <c r="BC32">
+        <v>7</v>
+      </c>
+      <c r="BD32">
+        <v>1.9</v>
+      </c>
+      <c r="BE32">
+        <v>5.95</v>
+      </c>
+      <c r="BF32">
+        <v>2.36</v>
+      </c>
+      <c r="BG32">
+        <v>1.5</v>
+      </c>
+      <c r="BH32">
+        <v>2.42</v>
+      </c>
+      <c r="BI32">
+        <v>2</v>
+      </c>
+      <c r="BJ32">
+        <v>1.8</v>
+      </c>
+      <c r="BK32">
+        <v>2.41</v>
+      </c>
+      <c r="BL32">
+        <v>1.53</v>
+      </c>
+      <c r="BM32">
+        <v>3.22</v>
+      </c>
+      <c r="BN32">
+        <v>1.3</v>
+      </c>
+      <c r="BO32">
+        <v>4.4</v>
+      </c>
+      <c r="BP32">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="33" spans="1:68">
+      <c r="A33" s="1">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>7813852</v>
+      </c>
+      <c r="C33" t="s">
+        <v>68</v>
+      </c>
+      <c r="D33" t="s">
+        <v>69</v>
+      </c>
+      <c r="E33" s="2">
+        <v>45745.1875</v>
+      </c>
+      <c r="F33">
+        <v>5</v>
+      </c>
+      <c r="G33" t="s">
+        <v>70</v>
+      </c>
+      <c r="H33" t="s">
+        <v>72</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>1</v>
+      </c>
+      <c r="K33">
+        <v>1</v>
+      </c>
+      <c r="L33">
+        <v>1</v>
+      </c>
+      <c r="M33">
+        <v>1</v>
+      </c>
+      <c r="N33">
+        <v>2</v>
+      </c>
+      <c r="O33" t="s">
+        <v>91</v>
+      </c>
+      <c r="P33" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q33">
+        <v>2.63</v>
+      </c>
+      <c r="R33">
+        <v>2.1</v>
+      </c>
+      <c r="S33">
+        <v>4.33</v>
+      </c>
+      <c r="T33">
+        <v>1.4</v>
+      </c>
+      <c r="U33">
+        <v>2.75</v>
+      </c>
+      <c r="V33">
+        <v>3</v>
+      </c>
+      <c r="W33">
+        <v>1.36</v>
+      </c>
+      <c r="X33">
+        <v>8</v>
+      </c>
+      <c r="Y33">
+        <v>1.08</v>
+      </c>
+      <c r="Z33">
+        <v>2.04</v>
+      </c>
+      <c r="AA33">
+        <v>3.08</v>
+      </c>
+      <c r="AB33">
+        <v>3.91</v>
+      </c>
+      <c r="AC33">
+        <v>1.09</v>
+      </c>
+      <c r="AD33">
+        <v>6.5</v>
+      </c>
+      <c r="AE33">
+        <v>1.4</v>
+      </c>
+      <c r="AF33">
+        <v>2.8</v>
+      </c>
+      <c r="AG33">
+        <v>1.98</v>
+      </c>
+      <c r="AH33">
+        <v>1.77</v>
+      </c>
+      <c r="AI33">
+        <v>1.8</v>
+      </c>
+      <c r="AJ33">
+        <v>1.91</v>
+      </c>
+      <c r="AK33">
+        <v>1.31</v>
+      </c>
+      <c r="AL33">
+        <v>1.35</v>
+      </c>
+      <c r="AM33">
+        <v>1.61</v>
+      </c>
+      <c r="AN33">
+        <v>3</v>
+      </c>
+      <c r="AO33">
+        <v>3</v>
+      </c>
+      <c r="AP33">
+        <v>2.5</v>
+      </c>
+      <c r="AQ33">
+        <v>2</v>
+      </c>
+      <c r="AR33">
+        <v>1.69</v>
+      </c>
+      <c r="AS33">
+        <v>0.97</v>
+      </c>
+      <c r="AT33">
+        <v>2.66</v>
+      </c>
+      <c r="AU33">
+        <v>2</v>
+      </c>
+      <c r="AV33">
+        <v>3</v>
+      </c>
+      <c r="AW33">
+        <v>10</v>
+      </c>
+      <c r="AX33">
+        <v>6</v>
+      </c>
+      <c r="AY33">
+        <v>12</v>
+      </c>
+      <c r="AZ33">
+        <v>9</v>
+      </c>
+      <c r="BA33">
+        <v>3</v>
+      </c>
+      <c r="BB33">
+        <v>5</v>
+      </c>
+      <c r="BC33">
+        <v>8</v>
+      </c>
+      <c r="BD33">
+        <v>1.64</v>
+      </c>
+      <c r="BE33">
+        <v>7.9</v>
+      </c>
+      <c r="BF33">
+        <v>2.62</v>
+      </c>
+      <c r="BG33">
+        <v>1.43</v>
+      </c>
+      <c r="BH33">
+        <v>2.6</v>
+      </c>
+      <c r="BI33">
+        <v>1.75</v>
+      </c>
+      <c r="BJ33">
+        <v>2</v>
+      </c>
+      <c r="BK33">
+        <v>2.23</v>
+      </c>
+      <c r="BL33">
+        <v>1.61</v>
+      </c>
+      <c r="BM33">
+        <v>2.88</v>
+      </c>
+      <c r="BN33">
+        <v>1.36</v>
+      </c>
+      <c r="BO33">
+        <v>3.95</v>
+      </c>
+      <c r="BP33">
+        <v>1.19</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="132">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -259,12 +259,12 @@
     <t>Gyeongnam</t>
   </si>
   <si>
+    <t>Asan Mugunghwa</t>
+  </si>
+  <si>
     <t>Jeonnam Dragons</t>
   </si>
   <si>
-    <t>Asan Mugunghwa</t>
-  </si>
-  <si>
     <t>Cheongju</t>
   </si>
   <si>
@@ -334,15 +334,18 @@
     <t>['30', '81', '90+1']</t>
   </si>
   <si>
+    <t>['24', '42', '59']</t>
+  </si>
+  <si>
+    <t>['89']</t>
+  </si>
+  <si>
     <t>['1', '6']</t>
   </si>
   <si>
     <t>['67']</t>
   </si>
   <si>
-    <t>['89']</t>
-  </si>
-  <si>
     <t>['85']</t>
   </si>
   <si>
@@ -398,6 +401,15 @@
   </si>
   <si>
     <t>['21']</t>
+  </si>
+  <si>
+    <t>['45+3', '89']</t>
+  </si>
+  <si>
+    <t>['53', '90+5']</t>
+  </si>
+  <si>
+    <t>['43']</t>
   </si>
 </sst>
 </file>
@@ -759,7 +771,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP33"/>
+  <dimension ref="A1:BP36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1197,7 +1209,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1221,7 +1233,7 @@
         <v>85</v>
       </c>
       <c r="P3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="Q3">
         <v>3.8</v>
@@ -1299,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AQ3">
         <v>1.6</v>
@@ -1508,7 +1520,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ4">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1633,7 +1645,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="Q5">
         <v>4.5</v>
@@ -2021,7 +2033,7 @@
         <v>75</v>
       </c>
       <c r="H7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -2045,7 +2057,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Q7">
         <v>2.85</v>
@@ -2123,7 +2135,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AQ7">
         <v>0.5</v>
@@ -2251,7 +2263,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q8">
         <v>2.39</v>
@@ -2663,7 +2675,7 @@
         <v>85</v>
       </c>
       <c r="P10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q10">
         <v>4.3</v>
@@ -2744,7 +2756,7 @@
         <v>0.25</v>
       </c>
       <c r="AQ10">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AR10">
         <v>0.82</v>
@@ -2845,7 +2857,7 @@
         <v>75</v>
       </c>
       <c r="H11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -2869,7 +2881,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q11">
         <v>2.8</v>
@@ -2947,7 +2959,7 @@
         <v>3</v>
       </c>
       <c r="AP11">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AQ11">
         <v>1.6</v>
@@ -3051,7 +3063,7 @@
         <v>77</v>
       </c>
       <c r="H12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -3075,7 +3087,7 @@
         <v>91</v>
       </c>
       <c r="P12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q12">
         <v>3.6</v>
@@ -3281,7 +3293,7 @@
         <v>85</v>
       </c>
       <c r="P13" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q13">
         <v>2.43</v>
@@ -3487,7 +3499,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Q14">
         <v>3.9</v>
@@ -3565,10 +3577,10 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AQ14">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AR14">
         <v>1.15</v>
@@ -3693,7 +3705,7 @@
         <v>93</v>
       </c>
       <c r="P15" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q15">
         <v>3.4</v>
@@ -3899,7 +3911,7 @@
         <v>85</v>
       </c>
       <c r="P16" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q16">
         <v>3.18</v>
@@ -4105,7 +4117,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q17">
         <v>3</v>
@@ -4287,7 +4299,7 @@
         <v>73</v>
       </c>
       <c r="H18" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -4311,7 +4323,7 @@
         <v>85</v>
       </c>
       <c r="P18" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="Q18">
         <v>4.9</v>
@@ -4517,7 +4529,7 @@
         <v>95</v>
       </c>
       <c r="P19" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q19">
         <v>2.71</v>
@@ -4723,7 +4735,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q20">
         <v>3.5</v>
@@ -4801,7 +4813,7 @@
         <v>1.5</v>
       </c>
       <c r="AP20">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AQ20">
         <v>1</v>
@@ -4905,7 +4917,7 @@
         <v>71</v>
       </c>
       <c r="H21" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -5007,7 +5019,7 @@
         <v>0.5</v>
       </c>
       <c r="AP21">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AQ21">
         <v>0.5</v>
@@ -5135,7 +5147,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q22">
         <v>5</v>
@@ -5547,7 +5559,7 @@
         <v>99</v>
       </c>
       <c r="P24" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q24">
         <v>3</v>
@@ -5935,7 +5947,7 @@
         <v>79</v>
       </c>
       <c r="H26" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -6165,7 +6177,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q27">
         <v>2.25</v>
@@ -6347,7 +6359,7 @@
         <v>80</v>
       </c>
       <c r="H28" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -6371,7 +6383,7 @@
         <v>101</v>
       </c>
       <c r="P28" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q28">
         <v>4</v>
@@ -6577,7 +6589,7 @@
         <v>102</v>
       </c>
       <c r="P29" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q29">
         <v>2.2</v>
@@ -6783,7 +6795,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q30">
         <v>3.75</v>
@@ -6965,7 +6977,7 @@
         <v>79</v>
       </c>
       <c r="H31" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -6989,7 +7001,7 @@
         <v>104</v>
       </c>
       <c r="P31" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q31">
         <v>3.25</v>
@@ -7401,7 +7413,7 @@
         <v>91</v>
       </c>
       <c r="P33" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q33">
         <v>2.63</v>
@@ -7558,6 +7570,624 @@
       </c>
       <c r="BP33">
         <v>1.19</v>
+      </c>
+    </row>
+    <row r="34" spans="1:68">
+      <c r="A34" s="1">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <v>7813854</v>
+      </c>
+      <c r="C34" t="s">
+        <v>68</v>
+      </c>
+      <c r="D34" t="s">
+        <v>69</v>
+      </c>
+      <c r="E34" s="2">
+        <v>45746.08333333334</v>
+      </c>
+      <c r="F34">
+        <v>5</v>
+      </c>
+      <c r="G34" t="s">
+        <v>71</v>
+      </c>
+      <c r="H34" t="s">
+        <v>78</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>1</v>
+      </c>
+      <c r="K34">
+        <v>1</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>2</v>
+      </c>
+      <c r="N34">
+        <v>2</v>
+      </c>
+      <c r="O34" t="s">
+        <v>85</v>
+      </c>
+      <c r="P34" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q34">
+        <v>3.8</v>
+      </c>
+      <c r="R34">
+        <v>2.1</v>
+      </c>
+      <c r="S34">
+        <v>2.75</v>
+      </c>
+      <c r="T34">
+        <v>1.4</v>
+      </c>
+      <c r="U34">
+        <v>2.75</v>
+      </c>
+      <c r="V34">
+        <v>3</v>
+      </c>
+      <c r="W34">
+        <v>1.36</v>
+      </c>
+      <c r="X34">
+        <v>8.5</v>
+      </c>
+      <c r="Y34">
+        <v>1.07</v>
+      </c>
+      <c r="Z34">
+        <v>3.52</v>
+      </c>
+      <c r="AA34">
+        <v>3.31</v>
+      </c>
+      <c r="AB34">
+        <v>2.07</v>
+      </c>
+      <c r="AC34">
+        <v>1.02</v>
+      </c>
+      <c r="AD34">
+        <v>7.9</v>
+      </c>
+      <c r="AE34">
+        <v>1.33</v>
+      </c>
+      <c r="AF34">
+        <v>2.81</v>
+      </c>
+      <c r="AG34">
+        <v>2.05</v>
+      </c>
+      <c r="AH34">
+        <v>1.61</v>
+      </c>
+      <c r="AI34">
+        <v>1.85</v>
+      </c>
+      <c r="AJ34">
+        <v>1.85</v>
+      </c>
+      <c r="AK34">
+        <v>1.7</v>
+      </c>
+      <c r="AL34">
+        <v>1.35</v>
+      </c>
+      <c r="AM34">
+        <v>1.29</v>
+      </c>
+      <c r="AN34">
+        <v>1</v>
+      </c>
+      <c r="AO34">
+        <v>2</v>
+      </c>
+      <c r="AP34">
+        <v>0.75</v>
+      </c>
+      <c r="AQ34">
+        <v>2.33</v>
+      </c>
+      <c r="AR34">
+        <v>0.98</v>
+      </c>
+      <c r="AS34">
+        <v>1.43</v>
+      </c>
+      <c r="AT34">
+        <v>2.41</v>
+      </c>
+      <c r="AU34">
+        <v>3</v>
+      </c>
+      <c r="AV34">
+        <v>4</v>
+      </c>
+      <c r="AW34">
+        <v>4</v>
+      </c>
+      <c r="AX34">
+        <v>8</v>
+      </c>
+      <c r="AY34">
+        <v>7</v>
+      </c>
+      <c r="AZ34">
+        <v>12</v>
+      </c>
+      <c r="BA34">
+        <v>4</v>
+      </c>
+      <c r="BB34">
+        <v>4</v>
+      </c>
+      <c r="BC34">
+        <v>8</v>
+      </c>
+      <c r="BD34">
+        <v>2.72</v>
+      </c>
+      <c r="BE34">
+        <v>6.15</v>
+      </c>
+      <c r="BF34">
+        <v>1.7</v>
+      </c>
+      <c r="BG34">
+        <v>1.44</v>
+      </c>
+      <c r="BH34">
+        <v>2.43</v>
+      </c>
+      <c r="BI34">
+        <v>1.92</v>
+      </c>
+      <c r="BJ34">
+        <v>1.88</v>
+      </c>
+      <c r="BK34">
+        <v>2.35</v>
+      </c>
+      <c r="BL34">
+        <v>1.47</v>
+      </c>
+      <c r="BM34">
+        <v>3.28</v>
+      </c>
+      <c r="BN34">
+        <v>1.25</v>
+      </c>
+      <c r="BO34">
+        <v>4.35</v>
+      </c>
+      <c r="BP34">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="35" spans="1:68">
+      <c r="A35" s="1">
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <v>7813853</v>
+      </c>
+      <c r="C35" t="s">
+        <v>68</v>
+      </c>
+      <c r="D35" t="s">
+        <v>69</v>
+      </c>
+      <c r="E35" s="2">
+        <v>45746.08333333334</v>
+      </c>
+      <c r="F35">
+        <v>5</v>
+      </c>
+      <c r="G35" t="s">
+        <v>75</v>
+      </c>
+      <c r="H35" t="s">
+        <v>76</v>
+      </c>
+      <c r="I35">
+        <v>2</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>2</v>
+      </c>
+      <c r="L35">
+        <v>3</v>
+      </c>
+      <c r="M35">
+        <v>2</v>
+      </c>
+      <c r="N35">
+        <v>5</v>
+      </c>
+      <c r="O35" t="s">
+        <v>106</v>
+      </c>
+      <c r="P35" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q35">
+        <v>2.8</v>
+      </c>
+      <c r="R35">
+        <v>2.15</v>
+      </c>
+      <c r="S35">
+        <v>3.5</v>
+      </c>
+      <c r="T35">
+        <v>1.36</v>
+      </c>
+      <c r="U35">
+        <v>2.9</v>
+      </c>
+      <c r="V35">
+        <v>2.8</v>
+      </c>
+      <c r="W35">
+        <v>1.4</v>
+      </c>
+      <c r="X35">
+        <v>7.5</v>
+      </c>
+      <c r="Y35">
+        <v>1.08</v>
+      </c>
+      <c r="Z35">
+        <v>2.33</v>
+      </c>
+      <c r="AA35">
+        <v>3.21</v>
+      </c>
+      <c r="AB35">
+        <v>3.03</v>
+      </c>
+      <c r="AC35">
+        <v>1</v>
+      </c>
+      <c r="AD35">
+        <v>9.1</v>
+      </c>
+      <c r="AE35">
+        <v>1.26</v>
+      </c>
+      <c r="AF35">
+        <v>3.22</v>
+      </c>
+      <c r="AG35">
+        <v>1.98</v>
+      </c>
+      <c r="AH35">
+        <v>1.77</v>
+      </c>
+      <c r="AI35">
+        <v>1.75</v>
+      </c>
+      <c r="AJ35">
+        <v>2</v>
+      </c>
+      <c r="AK35">
+        <v>1.36</v>
+      </c>
+      <c r="AL35">
+        <v>1.36</v>
+      </c>
+      <c r="AM35">
+        <v>1.57</v>
+      </c>
+      <c r="AN35">
+        <v>2.33</v>
+      </c>
+      <c r="AO35">
+        <v>3</v>
+      </c>
+      <c r="AP35">
+        <v>2.5</v>
+      </c>
+      <c r="AQ35">
+        <v>1.5</v>
+      </c>
+      <c r="AR35">
+        <v>1.05</v>
+      </c>
+      <c r="AS35">
+        <v>1.67</v>
+      </c>
+      <c r="AT35">
+        <v>2.72</v>
+      </c>
+      <c r="AU35">
+        <v>5</v>
+      </c>
+      <c r="AV35">
+        <v>5</v>
+      </c>
+      <c r="AW35">
+        <v>4</v>
+      </c>
+      <c r="AX35">
+        <v>1</v>
+      </c>
+      <c r="AY35">
+        <v>9</v>
+      </c>
+      <c r="AZ35">
+        <v>6</v>
+      </c>
+      <c r="BA35">
+        <v>2</v>
+      </c>
+      <c r="BB35">
+        <v>3</v>
+      </c>
+      <c r="BC35">
+        <v>5</v>
+      </c>
+      <c r="BD35">
+        <v>2.01</v>
+      </c>
+      <c r="BE35">
+        <v>6.05</v>
+      </c>
+      <c r="BF35">
+        <v>2.2</v>
+      </c>
+      <c r="BG35">
+        <v>1.4</v>
+      </c>
+      <c r="BH35">
+        <v>2.56</v>
+      </c>
+      <c r="BI35">
+        <v>1.92</v>
+      </c>
+      <c r="BJ35">
+        <v>1.88</v>
+      </c>
+      <c r="BK35">
+        <v>2.24</v>
+      </c>
+      <c r="BL35">
+        <v>1.52</v>
+      </c>
+      <c r="BM35">
+        <v>3.05</v>
+      </c>
+      <c r="BN35">
+        <v>1.28</v>
+      </c>
+      <c r="BO35">
+        <v>4.05</v>
+      </c>
+      <c r="BP35">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="36" spans="1:68">
+      <c r="A36" s="1">
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <v>7813855</v>
+      </c>
+      <c r="C36" t="s">
+        <v>68</v>
+      </c>
+      <c r="D36" t="s">
+        <v>69</v>
+      </c>
+      <c r="E36" s="2">
+        <v>45746.1875</v>
+      </c>
+      <c r="F36">
+        <v>5</v>
+      </c>
+      <c r="G36" t="s">
+        <v>81</v>
+      </c>
+      <c r="H36" t="s">
+        <v>74</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>1</v>
+      </c>
+      <c r="K36">
+        <v>1</v>
+      </c>
+      <c r="L36">
+        <v>1</v>
+      </c>
+      <c r="M36">
+        <v>1</v>
+      </c>
+      <c r="N36">
+        <v>2</v>
+      </c>
+      <c r="O36" t="s">
+        <v>107</v>
+      </c>
+      <c r="P36" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q36">
+        <v>2.4</v>
+      </c>
+      <c r="R36">
+        <v>2.05</v>
+      </c>
+      <c r="S36">
+        <v>4.7</v>
+      </c>
+      <c r="T36">
+        <v>1.4</v>
+      </c>
+      <c r="U36">
+        <v>2.72</v>
+      </c>
+      <c r="V36">
+        <v>3.04</v>
+      </c>
+      <c r="W36">
+        <v>1.33</v>
+      </c>
+      <c r="X36">
+        <v>8.4</v>
+      </c>
+      <c r="Y36">
+        <v>1.01</v>
+      </c>
+      <c r="Z36">
+        <v>1.88</v>
+      </c>
+      <c r="AA36">
+        <v>3.56</v>
+      </c>
+      <c r="AB36">
+        <v>3.89</v>
+      </c>
+      <c r="AC36">
+        <v>1.02</v>
+      </c>
+      <c r="AD36">
+        <v>7.8</v>
+      </c>
+      <c r="AE36">
+        <v>1.28</v>
+      </c>
+      <c r="AF36">
+        <v>3.08</v>
+      </c>
+      <c r="AG36">
+        <v>2</v>
+      </c>
+      <c r="AH36">
+        <v>1.67</v>
+      </c>
+      <c r="AI36">
+        <v>1.85</v>
+      </c>
+      <c r="AJ36">
+        <v>1.81</v>
+      </c>
+      <c r="AK36">
+        <v>1.18</v>
+      </c>
+      <c r="AL36">
+        <v>1.26</v>
+      </c>
+      <c r="AM36">
+        <v>1.88</v>
+      </c>
+      <c r="AN36">
+        <v>0</v>
+      </c>
+      <c r="AO36">
+        <v>1</v>
+      </c>
+      <c r="AP36">
+        <v>1</v>
+      </c>
+      <c r="AQ36">
+        <v>1</v>
+      </c>
+      <c r="AR36">
+        <v>0</v>
+      </c>
+      <c r="AS36">
+        <v>0.85</v>
+      </c>
+      <c r="AT36">
+        <v>0.85</v>
+      </c>
+      <c r="AU36">
+        <v>8</v>
+      </c>
+      <c r="AV36">
+        <v>3</v>
+      </c>
+      <c r="AW36">
+        <v>4</v>
+      </c>
+      <c r="AX36">
+        <v>3</v>
+      </c>
+      <c r="AY36">
+        <v>12</v>
+      </c>
+      <c r="AZ36">
+        <v>6</v>
+      </c>
+      <c r="BA36">
+        <v>11</v>
+      </c>
+      <c r="BB36">
+        <v>1</v>
+      </c>
+      <c r="BC36">
+        <v>12</v>
+      </c>
+      <c r="BD36">
+        <v>1.54</v>
+      </c>
+      <c r="BE36">
+        <v>8</v>
+      </c>
+      <c r="BF36">
+        <v>2.91</v>
+      </c>
+      <c r="BG36">
+        <v>1.42</v>
+      </c>
+      <c r="BH36">
+        <v>2.49</v>
+      </c>
+      <c r="BI36">
+        <v>1.78</v>
+      </c>
+      <c r="BJ36">
+        <v>1.88</v>
+      </c>
+      <c r="BK36">
+        <v>2.28</v>
+      </c>
+      <c r="BL36">
+        <v>1.5</v>
+      </c>
+      <c r="BM36">
+        <v>3.14</v>
+      </c>
+      <c r="BN36">
+        <v>1.27</v>
+      </c>
+      <c r="BO36">
+        <v>4.2</v>
+      </c>
+      <c r="BP36">
+        <v>1.17</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="135">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -340,6 +340,9 @@
     <t>['89']</t>
   </si>
   <si>
+    <t>['45+5', '48', '81']</t>
+  </si>
+  <si>
     <t>['1', '6']</t>
   </si>
   <si>
@@ -410,6 +413,12 @@
   </si>
   <si>
     <t>['43']</t>
+  </si>
+  <si>
+    <t>['42']</t>
+  </si>
+  <si>
+    <t>['24']</t>
   </si>
 </sst>
 </file>
@@ -771,7 +780,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP36"/>
+  <dimension ref="A1:BP39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1233,7 +1242,7 @@
         <v>85</v>
       </c>
       <c r="P3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q3">
         <v>3.8</v>
@@ -1314,7 +1323,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ3">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1517,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AQ4">
         <v>2.33</v>
@@ -1645,7 +1654,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q5">
         <v>4.5</v>
@@ -2135,7 +2144,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AQ7">
         <v>0.5</v>
@@ -2263,7 +2272,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q8">
         <v>2.39</v>
@@ -2675,7 +2684,7 @@
         <v>85</v>
       </c>
       <c r="P10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q10">
         <v>4.3</v>
@@ -2881,7 +2890,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q11">
         <v>2.8</v>
@@ -2959,10 +2968,10 @@
         <v>3</v>
       </c>
       <c r="AP11">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AQ11">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AR11">
         <v>1.04</v>
@@ -3087,7 +3096,7 @@
         <v>91</v>
       </c>
       <c r="P12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q12">
         <v>3.6</v>
@@ -3165,7 +3174,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AQ12">
         <v>0.5</v>
@@ -3293,7 +3302,7 @@
         <v>85</v>
       </c>
       <c r="P13" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Q13">
         <v>2.43</v>
@@ -3371,7 +3380,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AQ13">
         <v>1.33</v>
@@ -3499,7 +3508,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q14">
         <v>3.9</v>
@@ -3705,7 +3714,7 @@
         <v>93</v>
       </c>
       <c r="P15" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q15">
         <v>3.4</v>
@@ -3911,7 +3920,7 @@
         <v>85</v>
       </c>
       <c r="P16" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q16">
         <v>3.18</v>
@@ -4117,7 +4126,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q17">
         <v>3</v>
@@ -4195,7 +4204,7 @@
         <v>1.5</v>
       </c>
       <c r="AP17">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AQ17">
         <v>1.33</v>
@@ -4323,7 +4332,7 @@
         <v>85</v>
       </c>
       <c r="P18" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q18">
         <v>4.9</v>
@@ -4404,7 +4413,7 @@
         <v>0.25</v>
       </c>
       <c r="AQ18">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AR18">
         <v>1.29</v>
@@ -4529,7 +4538,7 @@
         <v>95</v>
       </c>
       <c r="P19" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q19">
         <v>2.71</v>
@@ -4735,7 +4744,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q20">
         <v>3.5</v>
@@ -4813,7 +4822,7 @@
         <v>1.5</v>
       </c>
       <c r="AP20">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AQ20">
         <v>1</v>
@@ -5147,7 +5156,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q22">
         <v>5</v>
@@ -5228,7 +5237,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ22">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR22">
         <v>0.92</v>
@@ -5559,7 +5568,7 @@
         <v>99</v>
       </c>
       <c r="P24" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q24">
         <v>3</v>
@@ -5637,7 +5646,7 @@
         <v>1.33</v>
       </c>
       <c r="AP24">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AQ24">
         <v>0.8</v>
@@ -6177,7 +6186,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q27">
         <v>2.25</v>
@@ -6255,7 +6264,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AQ27">
         <v>0</v>
@@ -6383,7 +6392,7 @@
         <v>101</v>
       </c>
       <c r="P28" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q28">
         <v>4</v>
@@ -6464,7 +6473,7 @@
         <v>2</v>
       </c>
       <c r="AQ28">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AR28">
         <v>0</v>
@@ -6589,7 +6598,7 @@
         <v>102</v>
       </c>
       <c r="P29" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q29">
         <v>2.2</v>
@@ -6795,7 +6804,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q30">
         <v>3.75</v>
@@ -7001,7 +7010,7 @@
         <v>104</v>
       </c>
       <c r="P31" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q31">
         <v>3.25</v>
@@ -7082,7 +7091,7 @@
         <v>2</v>
       </c>
       <c r="AQ31">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AR31">
         <v>1.17</v>
@@ -7413,7 +7422,7 @@
         <v>91</v>
       </c>
       <c r="P33" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q33">
         <v>2.63</v>
@@ -7619,7 +7628,7 @@
         <v>85</v>
       </c>
       <c r="P34" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q34">
         <v>3.8</v>
@@ -7825,7 +7834,7 @@
         <v>106</v>
       </c>
       <c r="P35" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q35">
         <v>2.8</v>
@@ -7903,7 +7912,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AQ35">
         <v>1.5</v>
@@ -8031,7 +8040,7 @@
         <v>107</v>
       </c>
       <c r="P36" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q36">
         <v>2.4</v>
@@ -8188,6 +8197,624 @@
       </c>
       <c r="BP36">
         <v>1.17</v>
+      </c>
+    </row>
+    <row r="37" spans="1:68">
+      <c r="A37" s="1">
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <v>7813856</v>
+      </c>
+      <c r="C37" t="s">
+        <v>68</v>
+      </c>
+      <c r="D37" t="s">
+        <v>69</v>
+      </c>
+      <c r="E37" s="2">
+        <v>45752.08333333334</v>
+      </c>
+      <c r="F37">
+        <v>6</v>
+      </c>
+      <c r="G37" t="s">
+        <v>75</v>
+      </c>
+      <c r="H37" t="s">
+        <v>71</v>
+      </c>
+      <c r="I37">
+        <v>1</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>1</v>
+      </c>
+      <c r="L37">
+        <v>3</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37">
+        <v>3</v>
+      </c>
+      <c r="O37" t="s">
+        <v>108</v>
+      </c>
+      <c r="P37" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q37">
+        <v>2.25</v>
+      </c>
+      <c r="R37">
+        <v>2.3</v>
+      </c>
+      <c r="S37">
+        <v>5</v>
+      </c>
+      <c r="T37">
+        <v>1.36</v>
+      </c>
+      <c r="U37">
+        <v>3</v>
+      </c>
+      <c r="V37">
+        <v>2.63</v>
+      </c>
+      <c r="W37">
+        <v>1.44</v>
+      </c>
+      <c r="X37">
+        <v>7</v>
+      </c>
+      <c r="Y37">
+        <v>1.1</v>
+      </c>
+      <c r="Z37">
+        <v>1.66</v>
+      </c>
+      <c r="AA37">
+        <v>3.99</v>
+      </c>
+      <c r="AB37">
+        <v>4.6</v>
+      </c>
+      <c r="AC37">
+        <v>0</v>
+      </c>
+      <c r="AD37">
+        <v>0</v>
+      </c>
+      <c r="AE37">
+        <v>0</v>
+      </c>
+      <c r="AF37">
+        <v>0</v>
+      </c>
+      <c r="AG37">
+        <v>1.7</v>
+      </c>
+      <c r="AH37">
+        <v>1.95</v>
+      </c>
+      <c r="AI37">
+        <v>1.8</v>
+      </c>
+      <c r="AJ37">
+        <v>1.91</v>
+      </c>
+      <c r="AK37">
+        <v>0</v>
+      </c>
+      <c r="AL37">
+        <v>0</v>
+      </c>
+      <c r="AM37">
+        <v>0</v>
+      </c>
+      <c r="AN37">
+        <v>2.5</v>
+      </c>
+      <c r="AO37">
+        <v>0</v>
+      </c>
+      <c r="AP37">
+        <v>2.6</v>
+      </c>
+      <c r="AQ37">
+        <v>0</v>
+      </c>
+      <c r="AR37">
+        <v>1.11</v>
+      </c>
+      <c r="AS37">
+        <v>0.52</v>
+      </c>
+      <c r="AT37">
+        <v>1.63</v>
+      </c>
+      <c r="AU37">
+        <v>7</v>
+      </c>
+      <c r="AV37">
+        <v>2</v>
+      </c>
+      <c r="AW37">
+        <v>5</v>
+      </c>
+      <c r="AX37">
+        <v>8</v>
+      </c>
+      <c r="AY37">
+        <v>12</v>
+      </c>
+      <c r="AZ37">
+        <v>10</v>
+      </c>
+      <c r="BA37">
+        <v>4</v>
+      </c>
+      <c r="BB37">
+        <v>4</v>
+      </c>
+      <c r="BC37">
+        <v>8</v>
+      </c>
+      <c r="BD37">
+        <v>0</v>
+      </c>
+      <c r="BE37">
+        <v>0</v>
+      </c>
+      <c r="BF37">
+        <v>0</v>
+      </c>
+      <c r="BG37">
+        <v>0</v>
+      </c>
+      <c r="BH37">
+        <v>0</v>
+      </c>
+      <c r="BI37">
+        <v>0</v>
+      </c>
+      <c r="BJ37">
+        <v>0</v>
+      </c>
+      <c r="BK37">
+        <v>0</v>
+      </c>
+      <c r="BL37">
+        <v>0</v>
+      </c>
+      <c r="BM37">
+        <v>0</v>
+      </c>
+      <c r="BN37">
+        <v>0</v>
+      </c>
+      <c r="BO37">
+        <v>0</v>
+      </c>
+      <c r="BP37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:68">
+      <c r="A38" s="1">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>7813857</v>
+      </c>
+      <c r="C38" t="s">
+        <v>68</v>
+      </c>
+      <c r="D38" t="s">
+        <v>69</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45752.08333333334</v>
+      </c>
+      <c r="F38">
+        <v>6</v>
+      </c>
+      <c r="G38" t="s">
+        <v>77</v>
+      </c>
+      <c r="H38" t="s">
+        <v>70</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>1</v>
+      </c>
+      <c r="K38">
+        <v>1</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38">
+        <v>1</v>
+      </c>
+      <c r="N38">
+        <v>1</v>
+      </c>
+      <c r="O38" t="s">
+        <v>85</v>
+      </c>
+      <c r="P38" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q38">
+        <v>5</v>
+      </c>
+      <c r="R38">
+        <v>2.2</v>
+      </c>
+      <c r="S38">
+        <v>2.38</v>
+      </c>
+      <c r="T38">
+        <v>1.4</v>
+      </c>
+      <c r="U38">
+        <v>2.75</v>
+      </c>
+      <c r="V38">
+        <v>3</v>
+      </c>
+      <c r="W38">
+        <v>1.36</v>
+      </c>
+      <c r="X38">
+        <v>8</v>
+      </c>
+      <c r="Y38">
+        <v>1.08</v>
+      </c>
+      <c r="Z38">
+        <v>3.5</v>
+      </c>
+      <c r="AA38">
+        <v>3.61</v>
+      </c>
+      <c r="AB38">
+        <v>1.98</v>
+      </c>
+      <c r="AC38">
+        <v>0</v>
+      </c>
+      <c r="AD38">
+        <v>0</v>
+      </c>
+      <c r="AE38">
+        <v>2.09</v>
+      </c>
+      <c r="AF38">
+        <v>1.73</v>
+      </c>
+      <c r="AG38">
+        <v>1.98</v>
+      </c>
+      <c r="AH38">
+        <v>1.77</v>
+      </c>
+      <c r="AI38">
+        <v>1.91</v>
+      </c>
+      <c r="AJ38">
+        <v>1.8</v>
+      </c>
+      <c r="AK38">
+        <v>0</v>
+      </c>
+      <c r="AL38">
+        <v>0</v>
+      </c>
+      <c r="AM38">
+        <v>0</v>
+      </c>
+      <c r="AN38">
+        <v>1.67</v>
+      </c>
+      <c r="AO38">
+        <v>0</v>
+      </c>
+      <c r="AP38">
+        <v>1.25</v>
+      </c>
+      <c r="AQ38">
+        <v>1.5</v>
+      </c>
+      <c r="AR38">
+        <v>1.61</v>
+      </c>
+      <c r="AS38">
+        <v>1.24</v>
+      </c>
+      <c r="AT38">
+        <v>2.85</v>
+      </c>
+      <c r="AU38">
+        <v>4</v>
+      </c>
+      <c r="AV38">
+        <v>6</v>
+      </c>
+      <c r="AW38">
+        <v>4</v>
+      </c>
+      <c r="AX38">
+        <v>4</v>
+      </c>
+      <c r="AY38">
+        <v>11</v>
+      </c>
+      <c r="AZ38">
+        <v>11</v>
+      </c>
+      <c r="BA38">
+        <v>4</v>
+      </c>
+      <c r="BB38">
+        <v>3</v>
+      </c>
+      <c r="BC38">
+        <v>7</v>
+      </c>
+      <c r="BD38">
+        <v>0</v>
+      </c>
+      <c r="BE38">
+        <v>0</v>
+      </c>
+      <c r="BF38">
+        <v>0</v>
+      </c>
+      <c r="BG38">
+        <v>0</v>
+      </c>
+      <c r="BH38">
+        <v>0</v>
+      </c>
+      <c r="BI38">
+        <v>0</v>
+      </c>
+      <c r="BJ38">
+        <v>0</v>
+      </c>
+      <c r="BK38">
+        <v>0</v>
+      </c>
+      <c r="BL38">
+        <v>0</v>
+      </c>
+      <c r="BM38">
+        <v>0</v>
+      </c>
+      <c r="BN38">
+        <v>0</v>
+      </c>
+      <c r="BO38">
+        <v>0</v>
+      </c>
+      <c r="BP38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:68">
+      <c r="A39" s="1">
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <v>7813858</v>
+      </c>
+      <c r="C39" t="s">
+        <v>68</v>
+      </c>
+      <c r="D39" t="s">
+        <v>69</v>
+      </c>
+      <c r="E39" s="2">
+        <v>45752.1875</v>
+      </c>
+      <c r="F39">
+        <v>6</v>
+      </c>
+      <c r="G39" t="s">
+        <v>72</v>
+      </c>
+      <c r="H39" t="s">
+        <v>82</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>1</v>
+      </c>
+      <c r="K39">
+        <v>1</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <v>1</v>
+      </c>
+      <c r="N39">
+        <v>1</v>
+      </c>
+      <c r="O39" t="s">
+        <v>85</v>
+      </c>
+      <c r="P39" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q39">
+        <v>3.1</v>
+      </c>
+      <c r="R39">
+        <v>2.05</v>
+      </c>
+      <c r="S39">
+        <v>3.75</v>
+      </c>
+      <c r="T39">
+        <v>1.44</v>
+      </c>
+      <c r="U39">
+        <v>2.63</v>
+      </c>
+      <c r="V39">
+        <v>3.4</v>
+      </c>
+      <c r="W39">
+        <v>1.3</v>
+      </c>
+      <c r="X39">
+        <v>10</v>
+      </c>
+      <c r="Y39">
+        <v>1.06</v>
+      </c>
+      <c r="Z39">
+        <v>2.28</v>
+      </c>
+      <c r="AA39">
+        <v>3.35</v>
+      </c>
+      <c r="AB39">
+        <v>3</v>
+      </c>
+      <c r="AC39">
+        <v>1.02</v>
+      </c>
+      <c r="AD39">
+        <v>8</v>
+      </c>
+      <c r="AE39">
+        <v>2.44</v>
+      </c>
+      <c r="AF39">
+        <v>1.55</v>
+      </c>
+      <c r="AG39">
+        <v>2.05</v>
+      </c>
+      <c r="AH39">
+        <v>1.65</v>
+      </c>
+      <c r="AI39">
+        <v>1.83</v>
+      </c>
+      <c r="AJ39">
+        <v>1.83</v>
+      </c>
+      <c r="AK39">
+        <v>1.36</v>
+      </c>
+      <c r="AL39">
+        <v>1.36</v>
+      </c>
+      <c r="AM39">
+        <v>1.55</v>
+      </c>
+      <c r="AN39">
+        <v>1.33</v>
+      </c>
+      <c r="AO39">
+        <v>1.6</v>
+      </c>
+      <c r="AP39">
+        <v>1</v>
+      </c>
+      <c r="AQ39">
+        <v>1.83</v>
+      </c>
+      <c r="AR39">
+        <v>1.6</v>
+      </c>
+      <c r="AS39">
+        <v>1.35</v>
+      </c>
+      <c r="AT39">
+        <v>2.95</v>
+      </c>
+      <c r="AU39">
+        <v>5</v>
+      </c>
+      <c r="AV39">
+        <v>4</v>
+      </c>
+      <c r="AW39">
+        <v>6</v>
+      </c>
+      <c r="AX39">
+        <v>7</v>
+      </c>
+      <c r="AY39">
+        <v>13</v>
+      </c>
+      <c r="AZ39">
+        <v>13</v>
+      </c>
+      <c r="BA39">
+        <v>7</v>
+      </c>
+      <c r="BB39">
+        <v>3</v>
+      </c>
+      <c r="BC39">
+        <v>10</v>
+      </c>
+      <c r="BD39">
+        <v>1.61</v>
+      </c>
+      <c r="BE39">
+        <v>6.3</v>
+      </c>
+      <c r="BF39">
+        <v>2.96</v>
+      </c>
+      <c r="BG39">
+        <v>1.4</v>
+      </c>
+      <c r="BH39">
+        <v>2.56</v>
+      </c>
+      <c r="BI39">
+        <v>1.74</v>
+      </c>
+      <c r="BJ39">
+        <v>1.93</v>
+      </c>
+      <c r="BK39">
+        <v>2.24</v>
+      </c>
+      <c r="BL39">
+        <v>1.52</v>
+      </c>
+      <c r="BM39">
+        <v>3.05</v>
+      </c>
+      <c r="BN39">
+        <v>1.28</v>
+      </c>
+      <c r="BO39">
+        <v>3.9</v>
+      </c>
+      <c r="BP39">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="139">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -343,6 +343,18 @@
     <t>['45+5', '48', '81']</t>
   </si>
   <si>
+    <t>['11', '23', '36', '44']</t>
+  </si>
+  <si>
+    <t>['45+3']</t>
+  </si>
+  <si>
+    <t>['21', '23', '64']</t>
+  </si>
+  <si>
+    <t>['43']</t>
+  </si>
+  <si>
     <t>['1', '6']</t>
   </si>
   <si>
@@ -358,9 +370,6 @@
     <t>['64']</t>
   </si>
   <si>
-    <t>['45+3']</t>
-  </si>
-  <si>
     <t>['81']</t>
   </si>
   <si>
@@ -412,13 +421,16 @@
     <t>['53', '90+5']</t>
   </si>
   <si>
-    <t>['43']</t>
-  </si>
-  <si>
     <t>['42']</t>
   </si>
   <si>
     <t>['24']</t>
+  </si>
+  <si>
+    <t>['42', '63']</t>
+  </si>
+  <si>
+    <t>['87']</t>
   </si>
 </sst>
 </file>
@@ -780,7 +792,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP39"/>
+  <dimension ref="A1:BP43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1117,7 +1129,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ2">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1242,7 +1254,7 @@
         <v>85</v>
       </c>
       <c r="P3" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="Q3">
         <v>3.8</v>
@@ -1654,7 +1666,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="Q5">
         <v>4.5</v>
@@ -1938,7 +1950,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AQ6">
         <v>0.5</v>
@@ -2272,7 +2284,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="Q8">
         <v>2.39</v>
@@ -2353,7 +2365,7 @@
         <v>2</v>
       </c>
       <c r="AQ8">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2684,7 +2696,7 @@
         <v>85</v>
       </c>
       <c r="P10" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="Q10">
         <v>4.3</v>
@@ -2890,7 +2902,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="Q11">
         <v>2.8</v>
@@ -3096,7 +3108,7 @@
         <v>91</v>
       </c>
       <c r="P12" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="Q12">
         <v>3.6</v>
@@ -3302,7 +3314,7 @@
         <v>85</v>
       </c>
       <c r="P13" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="Q13">
         <v>2.43</v>
@@ -3383,7 +3395,7 @@
         <v>1</v>
       </c>
       <c r="AQ13">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AR13">
         <v>1.4</v>
@@ -3508,7 +3520,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="Q14">
         <v>3.9</v>
@@ -3589,7 +3601,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ14">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AR14">
         <v>1.15</v>
@@ -3714,7 +3726,7 @@
         <v>93</v>
       </c>
       <c r="P15" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="Q15">
         <v>3.4</v>
@@ -3792,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AQ15">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR15">
         <v>0.82</v>
@@ -3920,7 +3932,7 @@
         <v>85</v>
       </c>
       <c r="P16" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="Q16">
         <v>3.18</v>
@@ -4126,7 +4138,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="Q17">
         <v>3</v>
@@ -4207,7 +4219,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ17">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AR17">
         <v>1.52</v>
@@ -4332,7 +4344,7 @@
         <v>85</v>
       </c>
       <c r="P18" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="Q18">
         <v>4.9</v>
@@ -4538,7 +4550,7 @@
         <v>95</v>
       </c>
       <c r="P19" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="Q19">
         <v>2.71</v>
@@ -4616,10 +4628,10 @@
         <v>0.5</v>
       </c>
       <c r="AP19">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AQ19">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -4744,7 +4756,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="Q20">
         <v>3.5</v>
@@ -5156,7 +5168,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="Q22">
         <v>5</v>
@@ -5234,7 +5246,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AQ22">
         <v>1.5</v>
@@ -5568,7 +5580,7 @@
         <v>99</v>
       </c>
       <c r="P24" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="Q24">
         <v>3</v>
@@ -5649,7 +5661,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ24">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR24">
         <v>1.41</v>
@@ -5852,7 +5864,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AQ25">
         <v>1</v>
@@ -6058,7 +6070,7 @@
         <v>0.33</v>
       </c>
       <c r="AP26">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ26">
         <v>0.5</v>
@@ -6186,7 +6198,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="Q27">
         <v>2.25</v>
@@ -6392,7 +6404,7 @@
         <v>101</v>
       </c>
       <c r="P28" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="Q28">
         <v>4</v>
@@ -6598,7 +6610,7 @@
         <v>102</v>
       </c>
       <c r="P29" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="Q29">
         <v>2.2</v>
@@ -6804,7 +6816,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="Q30">
         <v>3.75</v>
@@ -7010,7 +7022,7 @@
         <v>104</v>
       </c>
       <c r="P31" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="Q31">
         <v>3.25</v>
@@ -7088,7 +7100,7 @@
         <v>2</v>
       </c>
       <c r="AP31">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ31">
         <v>1.83</v>
@@ -7297,7 +7309,7 @@
         <v>2</v>
       </c>
       <c r="AQ32">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR32">
         <v>1.01</v>
@@ -7422,7 +7434,7 @@
         <v>91</v>
       </c>
       <c r="P33" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="Q33">
         <v>2.63</v>
@@ -7628,7 +7640,7 @@
         <v>85</v>
       </c>
       <c r="P34" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="Q34">
         <v>3.8</v>
@@ -7834,7 +7846,7 @@
         <v>106</v>
       </c>
       <c r="P35" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="Q35">
         <v>2.8</v>
@@ -7915,7 +7927,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ35">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AR35">
         <v>1.05</v>
@@ -8040,7 +8052,7 @@
         <v>107</v>
       </c>
       <c r="P36" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="Q36">
         <v>2.4</v>
@@ -8118,7 +8130,7 @@
         <v>1</v>
       </c>
       <c r="AP36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ36">
         <v>1</v>
@@ -8452,7 +8464,7 @@
         <v>85</v>
       </c>
       <c r="P38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="Q38">
         <v>5</v>
@@ -8658,7 +8670,7 @@
         <v>85</v>
       </c>
       <c r="P39" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="Q39">
         <v>3.1</v>
@@ -8815,6 +8827,830 @@
       </c>
       <c r="BP39">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:68">
+      <c r="A40" s="1">
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <v>7813859</v>
+      </c>
+      <c r="C40" t="s">
+        <v>68</v>
+      </c>
+      <c r="D40" t="s">
+        <v>69</v>
+      </c>
+      <c r="E40" s="2">
+        <v>45753.08333333334</v>
+      </c>
+      <c r="F40">
+        <v>6</v>
+      </c>
+      <c r="G40" t="s">
+        <v>79</v>
+      </c>
+      <c r="H40" t="s">
+        <v>80</v>
+      </c>
+      <c r="I40">
+        <v>4</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>4</v>
+      </c>
+      <c r="L40">
+        <v>4</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40">
+        <v>4</v>
+      </c>
+      <c r="O40" t="s">
+        <v>109</v>
+      </c>
+      <c r="P40" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q40">
+        <v>2.2</v>
+      </c>
+      <c r="R40">
+        <v>2.2</v>
+      </c>
+      <c r="S40">
+        <v>5</v>
+      </c>
+      <c r="T40">
+        <v>1.36</v>
+      </c>
+      <c r="U40">
+        <v>2.9</v>
+      </c>
+      <c r="V40">
+        <v>2.7</v>
+      </c>
+      <c r="W40">
+        <v>1.4</v>
+      </c>
+      <c r="X40">
+        <v>7.5</v>
+      </c>
+      <c r="Y40">
+        <v>1.08</v>
+      </c>
+      <c r="Z40">
+        <v>1.59</v>
+      </c>
+      <c r="AA40">
+        <v>3.99</v>
+      </c>
+      <c r="AB40">
+        <v>5.2</v>
+      </c>
+      <c r="AC40">
+        <v>1</v>
+      </c>
+      <c r="AD40">
+        <v>9.1</v>
+      </c>
+      <c r="AE40">
+        <v>1.24</v>
+      </c>
+      <c r="AF40">
+        <v>3.34</v>
+      </c>
+      <c r="AG40">
+        <v>1.85</v>
+      </c>
+      <c r="AH40">
+        <v>1.89</v>
+      </c>
+      <c r="AI40">
+        <v>1.85</v>
+      </c>
+      <c r="AJ40">
+        <v>1.85</v>
+      </c>
+      <c r="AK40">
+        <v>1.17</v>
+      </c>
+      <c r="AL40">
+        <v>1.25</v>
+      </c>
+      <c r="AM40">
+        <v>2.2</v>
+      </c>
+      <c r="AN40">
+        <v>2</v>
+      </c>
+      <c r="AO40">
+        <v>1.33</v>
+      </c>
+      <c r="AP40">
+        <v>2.33</v>
+      </c>
+      <c r="AQ40">
+        <v>1</v>
+      </c>
+      <c r="AR40">
+        <v>1.62</v>
+      </c>
+      <c r="AS40">
+        <v>1.05</v>
+      </c>
+      <c r="AT40">
+        <v>2.67</v>
+      </c>
+      <c r="AU40">
+        <v>8</v>
+      </c>
+      <c r="AV40">
+        <v>3</v>
+      </c>
+      <c r="AW40">
+        <v>8</v>
+      </c>
+      <c r="AX40">
+        <v>8</v>
+      </c>
+      <c r="AY40">
+        <v>17</v>
+      </c>
+      <c r="AZ40">
+        <v>18</v>
+      </c>
+      <c r="BA40">
+        <v>6</v>
+      </c>
+      <c r="BB40">
+        <v>4</v>
+      </c>
+      <c r="BC40">
+        <v>10</v>
+      </c>
+      <c r="BD40">
+        <v>1.42</v>
+      </c>
+      <c r="BE40">
+        <v>8.5</v>
+      </c>
+      <c r="BF40">
+        <v>3.38</v>
+      </c>
+      <c r="BG40">
+        <v>1.42</v>
+      </c>
+      <c r="BH40">
+        <v>2.65</v>
+      </c>
+      <c r="BI40">
+        <v>1.74</v>
+      </c>
+      <c r="BJ40">
+        <v>2.03</v>
+      </c>
+      <c r="BK40">
+        <v>2.2</v>
+      </c>
+      <c r="BL40">
+        <v>1.62</v>
+      </c>
+      <c r="BM40">
+        <v>2.83</v>
+      </c>
+      <c r="BN40">
+        <v>1.37</v>
+      </c>
+      <c r="BO40">
+        <v>3.88</v>
+      </c>
+      <c r="BP40">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:68">
+      <c r="A41" s="1">
+        <v>40</v>
+      </c>
+      <c r="B41">
+        <v>7813860</v>
+      </c>
+      <c r="C41" t="s">
+        <v>68</v>
+      </c>
+      <c r="D41" t="s">
+        <v>69</v>
+      </c>
+      <c r="E41" s="2">
+        <v>45753.08333333334</v>
+      </c>
+      <c r="F41">
+        <v>6</v>
+      </c>
+      <c r="G41" t="s">
+        <v>78</v>
+      </c>
+      <c r="H41" t="s">
+        <v>76</v>
+      </c>
+      <c r="I41">
+        <v>1</v>
+      </c>
+      <c r="J41">
+        <v>1</v>
+      </c>
+      <c r="K41">
+        <v>2</v>
+      </c>
+      <c r="L41">
+        <v>1</v>
+      </c>
+      <c r="M41">
+        <v>2</v>
+      </c>
+      <c r="N41">
+        <v>3</v>
+      </c>
+      <c r="O41" t="s">
+        <v>110</v>
+      </c>
+      <c r="P41" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q41">
+        <v>3.25</v>
+      </c>
+      <c r="R41">
+        <v>2.05</v>
+      </c>
+      <c r="S41">
+        <v>3.25</v>
+      </c>
+      <c r="T41">
+        <v>1.44</v>
+      </c>
+      <c r="U41">
+        <v>2.62</v>
+      </c>
+      <c r="V41">
+        <v>3.1</v>
+      </c>
+      <c r="W41">
+        <v>1.33</v>
+      </c>
+      <c r="X41">
+        <v>9</v>
+      </c>
+      <c r="Y41">
+        <v>1.06</v>
+      </c>
+      <c r="Z41">
+        <v>2.84</v>
+      </c>
+      <c r="AA41">
+        <v>3.2</v>
+      </c>
+      <c r="AB41">
+        <v>2.47</v>
+      </c>
+      <c r="AC41">
+        <v>1.03</v>
+      </c>
+      <c r="AD41">
+        <v>7.5</v>
+      </c>
+      <c r="AE41">
+        <v>1.35</v>
+      </c>
+      <c r="AF41">
+        <v>2.74</v>
+      </c>
+      <c r="AG41">
+        <v>2.1</v>
+      </c>
+      <c r="AH41">
+        <v>1.6</v>
+      </c>
+      <c r="AI41">
+        <v>1.85</v>
+      </c>
+      <c r="AJ41">
+        <v>1.85</v>
+      </c>
+      <c r="AK41">
+        <v>1.44</v>
+      </c>
+      <c r="AL41">
+        <v>1.36</v>
+      </c>
+      <c r="AM41">
+        <v>1.44</v>
+      </c>
+      <c r="AN41">
+        <v>0.5</v>
+      </c>
+      <c r="AO41">
+        <v>1.5</v>
+      </c>
+      <c r="AP41">
+        <v>0.33</v>
+      </c>
+      <c r="AQ41">
+        <v>2</v>
+      </c>
+      <c r="AR41">
+        <v>1.52</v>
+      </c>
+      <c r="AS41">
+        <v>1.4</v>
+      </c>
+      <c r="AT41">
+        <v>2.92</v>
+      </c>
+      <c r="AU41">
+        <v>5</v>
+      </c>
+      <c r="AV41">
+        <v>7</v>
+      </c>
+      <c r="AW41">
+        <v>3</v>
+      </c>
+      <c r="AX41">
+        <v>7</v>
+      </c>
+      <c r="AY41">
+        <v>9</v>
+      </c>
+      <c r="AZ41">
+        <v>15</v>
+      </c>
+      <c r="BA41">
+        <v>2</v>
+      </c>
+      <c r="BB41">
+        <v>1</v>
+      </c>
+      <c r="BC41">
+        <v>3</v>
+      </c>
+      <c r="BD41">
+        <v>1.99</v>
+      </c>
+      <c r="BE41">
+        <v>5.85</v>
+      </c>
+      <c r="BF41">
+        <v>2.25</v>
+      </c>
+      <c r="BG41">
+        <v>1.62</v>
+      </c>
+      <c r="BH41">
+        <v>2.28</v>
+      </c>
+      <c r="BI41">
+        <v>2.03</v>
+      </c>
+      <c r="BJ41">
+        <v>1.77</v>
+      </c>
+      <c r="BK41">
+        <v>2.66</v>
+      </c>
+      <c r="BL41">
+        <v>1.37</v>
+      </c>
+      <c r="BM41">
+        <v>3.78</v>
+      </c>
+      <c r="BN41">
+        <v>1.19</v>
+      </c>
+      <c r="BO41">
+        <v>4.95</v>
+      </c>
+      <c r="BP41">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="42" spans="1:68">
+      <c r="A42" s="1">
+        <v>41</v>
+      </c>
+      <c r="B42">
+        <v>7813861</v>
+      </c>
+      <c r="C42" t="s">
+        <v>68</v>
+      </c>
+      <c r="D42" t="s">
+        <v>69</v>
+      </c>
+      <c r="E42" s="2">
+        <v>45753.1875</v>
+      </c>
+      <c r="F42">
+        <v>6</v>
+      </c>
+      <c r="G42" t="s">
+        <v>81</v>
+      </c>
+      <c r="H42" t="s">
+        <v>83</v>
+      </c>
+      <c r="I42">
+        <v>2</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>2</v>
+      </c>
+      <c r="L42">
+        <v>3</v>
+      </c>
+      <c r="M42">
+        <v>1</v>
+      </c>
+      <c r="N42">
+        <v>4</v>
+      </c>
+      <c r="O42" t="s">
+        <v>111</v>
+      </c>
+      <c r="P42" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q42">
+        <v>2.5</v>
+      </c>
+      <c r="R42">
+        <v>2.1</v>
+      </c>
+      <c r="S42">
+        <v>4.5</v>
+      </c>
+      <c r="T42">
+        <v>1.4</v>
+      </c>
+      <c r="U42">
+        <v>2.8</v>
+      </c>
+      <c r="V42">
+        <v>2.9</v>
+      </c>
+      <c r="W42">
+        <v>1.36</v>
+      </c>
+      <c r="X42">
+        <v>8</v>
+      </c>
+      <c r="Y42">
+        <v>1.07</v>
+      </c>
+      <c r="Z42">
+        <v>1.85</v>
+      </c>
+      <c r="AA42">
+        <v>3.35</v>
+      </c>
+      <c r="AB42">
+        <v>3.98</v>
+      </c>
+      <c r="AC42">
+        <v>1.01</v>
+      </c>
+      <c r="AD42">
+        <v>8.5</v>
+      </c>
+      <c r="AE42">
+        <v>1.33</v>
+      </c>
+      <c r="AF42">
+        <v>2.83</v>
+      </c>
+      <c r="AG42">
+        <v>2.13</v>
+      </c>
+      <c r="AH42">
+        <v>1.64</v>
+      </c>
+      <c r="AI42">
+        <v>1.95</v>
+      </c>
+      <c r="AJ42">
+        <v>1.8</v>
+      </c>
+      <c r="AK42">
+        <v>1.22</v>
+      </c>
+      <c r="AL42">
+        <v>1.33</v>
+      </c>
+      <c r="AM42">
+        <v>1.85</v>
+      </c>
+      <c r="AN42">
+        <v>1</v>
+      </c>
+      <c r="AO42">
+        <v>0.8</v>
+      </c>
+      <c r="AP42">
+        <v>2</v>
+      </c>
+      <c r="AQ42">
+        <v>0.67</v>
+      </c>
+      <c r="AR42">
+        <v>1.85</v>
+      </c>
+      <c r="AS42">
+        <v>1.12</v>
+      </c>
+      <c r="AT42">
+        <v>2.97</v>
+      </c>
+      <c r="AU42">
+        <v>7</v>
+      </c>
+      <c r="AV42">
+        <v>5</v>
+      </c>
+      <c r="AW42">
+        <v>5</v>
+      </c>
+      <c r="AX42">
+        <v>6</v>
+      </c>
+      <c r="AY42">
+        <v>12</v>
+      </c>
+      <c r="AZ42">
+        <v>11</v>
+      </c>
+      <c r="BA42">
+        <v>2</v>
+      </c>
+      <c r="BB42">
+        <v>3</v>
+      </c>
+      <c r="BC42">
+        <v>5</v>
+      </c>
+      <c r="BD42">
+        <v>1.42</v>
+      </c>
+      <c r="BE42">
+        <v>6.8</v>
+      </c>
+      <c r="BF42">
+        <v>3.75</v>
+      </c>
+      <c r="BG42">
+        <v>1.48</v>
+      </c>
+      <c r="BH42">
+        <v>2.61</v>
+      </c>
+      <c r="BI42">
+        <v>2</v>
+      </c>
+      <c r="BJ42">
+        <v>1.8</v>
+      </c>
+      <c r="BK42">
+        <v>2.33</v>
+      </c>
+      <c r="BL42">
+        <v>1.58</v>
+      </c>
+      <c r="BM42">
+        <v>3.08</v>
+      </c>
+      <c r="BN42">
+        <v>1.28</v>
+      </c>
+      <c r="BO42">
+        <v>4.25</v>
+      </c>
+      <c r="BP42">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="43" spans="1:68">
+      <c r="A43" s="1">
+        <v>42</v>
+      </c>
+      <c r="B43">
+        <v>7813862</v>
+      </c>
+      <c r="C43" t="s">
+        <v>68</v>
+      </c>
+      <c r="D43" t="s">
+        <v>69</v>
+      </c>
+      <c r="E43" s="2">
+        <v>45753.1875</v>
+      </c>
+      <c r="F43">
+        <v>6</v>
+      </c>
+      <c r="G43" t="s">
+        <v>74</v>
+      </c>
+      <c r="H43" t="s">
+        <v>73</v>
+      </c>
+      <c r="I43">
+        <v>1</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>1</v>
+      </c>
+      <c r="L43">
+        <v>1</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <v>1</v>
+      </c>
+      <c r="O43" t="s">
+        <v>112</v>
+      </c>
+      <c r="P43" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q43">
+        <v>2.8</v>
+      </c>
+      <c r="R43">
+        <v>2</v>
+      </c>
+      <c r="S43">
+        <v>4</v>
+      </c>
+      <c r="T43">
+        <v>1.44</v>
+      </c>
+      <c r="U43">
+        <v>2.5</v>
+      </c>
+      <c r="V43">
+        <v>3.3</v>
+      </c>
+      <c r="W43">
+        <v>1.3</v>
+      </c>
+      <c r="X43">
+        <v>10</v>
+      </c>
+      <c r="Y43">
+        <v>1.05</v>
+      </c>
+      <c r="Z43">
+        <v>2.14</v>
+      </c>
+      <c r="AA43">
+        <v>3.14</v>
+      </c>
+      <c r="AB43">
+        <v>3.53</v>
+      </c>
+      <c r="AC43">
+        <v>1.04</v>
+      </c>
+      <c r="AD43">
+        <v>6.75</v>
+      </c>
+      <c r="AE43">
+        <v>1.4</v>
+      </c>
+      <c r="AF43">
+        <v>2.56</v>
+      </c>
+      <c r="AG43">
+        <v>2.25</v>
+      </c>
+      <c r="AH43">
+        <v>1.53</v>
+      </c>
+      <c r="AI43">
+        <v>2</v>
+      </c>
+      <c r="AJ43">
+        <v>1.75</v>
+      </c>
+      <c r="AK43">
+        <v>1.29</v>
+      </c>
+      <c r="AL43">
+        <v>1.36</v>
+      </c>
+      <c r="AM43">
+        <v>1.67</v>
+      </c>
+      <c r="AN43">
+        <v>2.33</v>
+      </c>
+      <c r="AO43">
+        <v>0</v>
+      </c>
+      <c r="AP43">
+        <v>2.5</v>
+      </c>
+      <c r="AQ43">
+        <v>0</v>
+      </c>
+      <c r="AR43">
+        <v>1.02</v>
+      </c>
+      <c r="AS43">
+        <v>0.83</v>
+      </c>
+      <c r="AT43">
+        <v>1.85</v>
+      </c>
+      <c r="AU43">
+        <v>4</v>
+      </c>
+      <c r="AV43">
+        <v>3</v>
+      </c>
+      <c r="AW43">
+        <v>5</v>
+      </c>
+      <c r="AX43">
+        <v>4</v>
+      </c>
+      <c r="AY43">
+        <v>9</v>
+      </c>
+      <c r="AZ43">
+        <v>7</v>
+      </c>
+      <c r="BA43">
+        <v>2</v>
+      </c>
+      <c r="BB43">
+        <v>3</v>
+      </c>
+      <c r="BC43">
+        <v>5</v>
+      </c>
+      <c r="BD43">
+        <v>1.65</v>
+      </c>
+      <c r="BE43">
+        <v>6.15</v>
+      </c>
+      <c r="BF43">
+        <v>2.86</v>
+      </c>
+      <c r="BG43">
+        <v>1.51</v>
+      </c>
+      <c r="BH43">
+        <v>2.5</v>
+      </c>
+      <c r="BI43">
+        <v>1.92</v>
+      </c>
+      <c r="BJ43">
+        <v>1.88</v>
+      </c>
+      <c r="BK43">
+        <v>2.41</v>
+      </c>
+      <c r="BL43">
+        <v>1.55</v>
+      </c>
+      <c r="BM43">
+        <v>3.2</v>
+      </c>
+      <c r="BN43">
+        <v>1.26</v>
+      </c>
+      <c r="BO43">
+        <v>4.35</v>
+      </c>
+      <c r="BP43">
+        <v>1.16</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="219">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -487,6 +487,9 @@
     <t>['18']</t>
   </si>
   <si>
+    <t>['4502', '65', '73']</t>
+  </si>
+  <si>
     <t>['1', '6']</t>
   </si>
   <si>
@@ -662,6 +665,12 @@
   </si>
   <si>
     <t>['62', '9005']</t>
+  </si>
+  <si>
+    <t>['9003']</t>
+  </si>
+  <si>
+    <t>['17']</t>
   </si>
 </sst>
 </file>
@@ -1023,7 +1032,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP106"/>
+  <dimension ref="A1:BP108"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1485,7 +1494,7 @@
         <v>85</v>
       </c>
       <c r="P3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q3">
         <v>3.8</v>
@@ -1897,7 +1906,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q5">
         <v>4.5</v>
@@ -2515,7 +2524,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q8">
         <v>2.39</v>
@@ -2593,7 +2602,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AQ8">
         <v>1</v>
@@ -2927,7 +2936,7 @@
         <v>85</v>
       </c>
       <c r="P10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q10">
         <v>4.3</v>
@@ -3133,7 +3142,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q11">
         <v>2.8</v>
@@ -3545,7 +3554,7 @@
         <v>85</v>
       </c>
       <c r="P13" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q13">
         <v>2.43</v>
@@ -3751,7 +3760,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q14">
         <v>3.9</v>
@@ -4163,7 +4172,7 @@
         <v>85</v>
       </c>
       <c r="P16" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q16">
         <v>3.18</v>
@@ -4241,7 +4250,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AQ16">
         <v>2.33</v>
@@ -4369,7 +4378,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q17">
         <v>3</v>
@@ -4575,7 +4584,7 @@
         <v>85</v>
       </c>
       <c r="P18" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q18">
         <v>4.9</v>
@@ -4781,7 +4790,7 @@
         <v>95</v>
       </c>
       <c r="P19" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q19">
         <v>2.71</v>
@@ -4987,7 +4996,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q20">
         <v>3.5</v>
@@ -5399,7 +5408,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q22">
         <v>5</v>
@@ -5686,7 +5695,7 @@
         <v>2.78</v>
       </c>
       <c r="AQ23">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AR23">
         <v>1.93</v>
@@ -5811,7 +5820,7 @@
         <v>99</v>
       </c>
       <c r="P24" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q24">
         <v>3</v>
@@ -6429,7 +6438,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q27">
         <v>2.25</v>
@@ -6510,7 +6519,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ27">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="AR27">
         <v>1.42</v>
@@ -6635,7 +6644,7 @@
         <v>101</v>
       </c>
       <c r="P28" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q28">
         <v>4</v>
@@ -6841,7 +6850,7 @@
         <v>102</v>
       </c>
       <c r="P29" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q29">
         <v>2.2</v>
@@ -6919,7 +6928,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AQ29">
         <v>1.14</v>
@@ -7047,7 +7056,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q30">
         <v>3.75</v>
@@ -7253,7 +7262,7 @@
         <v>104</v>
       </c>
       <c r="P31" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q31">
         <v>3.25</v>
@@ -7665,7 +7674,7 @@
         <v>91</v>
       </c>
       <c r="P33" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q33">
         <v>2.63</v>
@@ -7871,7 +7880,7 @@
         <v>85</v>
       </c>
       <c r="P34" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q34">
         <v>3.8</v>
@@ -8077,7 +8086,7 @@
         <v>106</v>
       </c>
       <c r="P35" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q35">
         <v>2.8</v>
@@ -8361,7 +8370,7 @@
         <v>1</v>
       </c>
       <c r="AP36">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AQ36">
         <v>0.86</v>
@@ -8570,7 +8579,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ37">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="AR37">
         <v>1.11</v>
@@ -8695,7 +8704,7 @@
         <v>85</v>
       </c>
       <c r="P38" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q38">
         <v>5</v>
@@ -8901,7 +8910,7 @@
         <v>85</v>
       </c>
       <c r="P39" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q39">
         <v>3.1</v>
@@ -9313,7 +9322,7 @@
         <v>110</v>
       </c>
       <c r="P41" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q41">
         <v>3.25</v>
@@ -9519,7 +9528,7 @@
         <v>111</v>
       </c>
       <c r="P42" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q42">
         <v>2.5</v>
@@ -9597,7 +9606,7 @@
         <v>0.8</v>
       </c>
       <c r="AP42">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AQ42">
         <v>1</v>
@@ -9931,7 +9940,7 @@
         <v>113</v>
       </c>
       <c r="P44" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q44">
         <v>3.4</v>
@@ -10137,7 +10146,7 @@
         <v>113</v>
       </c>
       <c r="P45" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q45">
         <v>3.75</v>
@@ -10343,7 +10352,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q46">
         <v>3.75</v>
@@ -10421,7 +10430,7 @@
         <v>1</v>
       </c>
       <c r="AP46">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AQ46">
         <v>1.57</v>
@@ -10549,7 +10558,7 @@
         <v>85</v>
       </c>
       <c r="P47" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q47">
         <v>3</v>
@@ -10961,7 +10970,7 @@
         <v>116</v>
       </c>
       <c r="P49" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -11042,7 +11051,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ49">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AR49">
         <v>1.58</v>
@@ -11373,7 +11382,7 @@
         <v>85</v>
       </c>
       <c r="P51" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q51">
         <v>2.25</v>
@@ -11660,7 +11669,7 @@
         <v>2.78</v>
       </c>
       <c r="AQ52">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="AR52">
         <v>1.66</v>
@@ -12197,7 +12206,7 @@
         <v>119</v>
       </c>
       <c r="P55" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q55">
         <v>5</v>
@@ -12481,7 +12490,7 @@
         <v>2</v>
       </c>
       <c r="AP56">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AQ56">
         <v>1.73</v>
@@ -12609,7 +12618,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q57">
         <v>3.75</v>
@@ -12815,7 +12824,7 @@
         <v>121</v>
       </c>
       <c r="P58" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q58">
         <v>2.3</v>
@@ -13021,7 +13030,7 @@
         <v>85</v>
       </c>
       <c r="P59" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q59">
         <v>3.2</v>
@@ -13305,7 +13314,7 @@
         <v>1</v>
       </c>
       <c r="AP60">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AQ60">
         <v>1.14</v>
@@ -13433,7 +13442,7 @@
         <v>123</v>
       </c>
       <c r="P61" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q61">
         <v>4</v>
@@ -13511,7 +13520,7 @@
         <v>1.5</v>
       </c>
       <c r="AP61">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AQ61">
         <v>2</v>
@@ -13639,7 +13648,7 @@
         <v>124</v>
       </c>
       <c r="P62" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q62">
         <v>2.3</v>
@@ -13845,7 +13854,7 @@
         <v>85</v>
       </c>
       <c r="P63" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q63">
         <v>3.2</v>
@@ -14051,7 +14060,7 @@
         <v>125</v>
       </c>
       <c r="P64" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q64">
         <v>2.5</v>
@@ -14257,7 +14266,7 @@
         <v>126</v>
       </c>
       <c r="P65" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q65">
         <v>4</v>
@@ -14338,7 +14347,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ65">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AR65">
         <v>1.07</v>
@@ -14463,7 +14472,7 @@
         <v>127</v>
       </c>
       <c r="P66" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q66">
         <v>3</v>
@@ -14541,7 +14550,7 @@
         <v>2</v>
       </c>
       <c r="AP66">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AQ66">
         <v>1.73</v>
@@ -14875,7 +14884,7 @@
         <v>129</v>
       </c>
       <c r="P68" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q68">
         <v>5</v>
@@ -15493,7 +15502,7 @@
         <v>132</v>
       </c>
       <c r="P71" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q71">
         <v>2.63</v>
@@ -15574,7 +15583,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ71">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="AR71">
         <v>1.45</v>
@@ -15905,7 +15914,7 @@
         <v>85</v>
       </c>
       <c r="P73" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q73">
         <v>3.6</v>
@@ -16111,7 +16120,7 @@
         <v>85</v>
       </c>
       <c r="P74" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q74">
         <v>4.33</v>
@@ -16189,7 +16198,7 @@
         <v>2</v>
       </c>
       <c r="AP74">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AQ74">
         <v>2</v>
@@ -16317,7 +16326,7 @@
         <v>134</v>
       </c>
       <c r="P75" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q75">
         <v>1.91</v>
@@ -16523,7 +16532,7 @@
         <v>135</v>
       </c>
       <c r="P76" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q76">
         <v>2.63</v>
@@ -16729,7 +16738,7 @@
         <v>85</v>
       </c>
       <c r="P77" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q77">
         <v>4.5</v>
@@ -17016,7 +17025,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ78">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="AR78">
         <v>1.79</v>
@@ -17141,7 +17150,7 @@
         <v>137</v>
       </c>
       <c r="P79" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q79">
         <v>3.6</v>
@@ -17425,7 +17434,7 @@
         <v>0.2</v>
       </c>
       <c r="AP80">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AQ80">
         <v>0.5</v>
@@ -17759,7 +17768,7 @@
         <v>140</v>
       </c>
       <c r="P82" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q82">
         <v>3.75</v>
@@ -17965,7 +17974,7 @@
         <v>85</v>
       </c>
       <c r="P83" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q83">
         <v>7.5</v>
@@ -18171,7 +18180,7 @@
         <v>141</v>
       </c>
       <c r="P84" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q84">
         <v>2.38</v>
@@ -18377,7 +18386,7 @@
         <v>142</v>
       </c>
       <c r="P85" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q85">
         <v>3.75</v>
@@ -18458,7 +18467,7 @@
         <v>1</v>
       </c>
       <c r="AQ85">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AR85">
         <v>1.63</v>
@@ -18583,7 +18592,7 @@
         <v>85</v>
       </c>
       <c r="P86" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q86">
         <v>4.2</v>
@@ -18664,7 +18673,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ86">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AR86">
         <v>1.42</v>
@@ -19201,7 +19210,7 @@
         <v>143</v>
       </c>
       <c r="P89" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q89">
         <v>2.62</v>
@@ -19282,7 +19291,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ89">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="AR89">
         <v>1.79</v>
@@ -19407,7 +19416,7 @@
         <v>144</v>
       </c>
       <c r="P90" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q90">
         <v>3.1</v>
@@ -19485,7 +19494,7 @@
         <v>2</v>
       </c>
       <c r="AP90">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AQ90">
         <v>1.38</v>
@@ -19819,7 +19828,7 @@
         <v>146</v>
       </c>
       <c r="P92" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20025,7 +20034,7 @@
         <v>147</v>
       </c>
       <c r="P93" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q93">
         <v>2.62</v>
@@ -20231,7 +20240,7 @@
         <v>148</v>
       </c>
       <c r="P94" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q94">
         <v>2.4</v>
@@ -20437,7 +20446,7 @@
         <v>149</v>
       </c>
       <c r="P95" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q95">
         <v>3.1</v>
@@ -20927,7 +20936,7 @@
         <v>1.33</v>
       </c>
       <c r="AP97">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AQ97">
         <v>1.14</v>
@@ -21055,7 +21064,7 @@
         <v>152</v>
       </c>
       <c r="P98" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q98">
         <v>2.3</v>
@@ -21261,7 +21270,7 @@
         <v>153</v>
       </c>
       <c r="P99" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q99">
         <v>6.5</v>
@@ -21467,7 +21476,7 @@
         <v>154</v>
       </c>
       <c r="P100" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q100">
         <v>4.33</v>
@@ -21673,7 +21682,7 @@
         <v>85</v>
       </c>
       <c r="P101" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q101">
         <v>3.88</v>
@@ -21879,7 +21888,7 @@
         <v>85</v>
       </c>
       <c r="P102" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q102">
         <v>2.79</v>
@@ -22085,7 +22094,7 @@
         <v>85</v>
       </c>
       <c r="P103" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q103">
         <v>2.14</v>
@@ -22291,7 +22300,7 @@
         <v>150</v>
       </c>
       <c r="P104" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q104">
         <v>3.4</v>
@@ -22372,7 +22381,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ104">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AR104">
         <v>1.56</v>
@@ -22784,7 +22793,7 @@
         <v>1</v>
       </c>
       <c r="AQ106">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="AR106">
         <v>1.56</v>
@@ -22860,6 +22869,418 @@
       </c>
       <c r="BP106">
         <v>1.18</v>
+      </c>
+    </row>
+    <row r="107" spans="1:68">
+      <c r="A107" s="1">
+        <v>106</v>
+      </c>
+      <c r="B107">
+        <v>7813926</v>
+      </c>
+      <c r="C107" t="s">
+        <v>68</v>
+      </c>
+      <c r="D107" t="s">
+        <v>69</v>
+      </c>
+      <c r="E107" s="2">
+        <v>45822.29166666666</v>
+      </c>
+      <c r="F107">
+        <v>16</v>
+      </c>
+      <c r="G107" t="s">
+        <v>81</v>
+      </c>
+      <c r="H107" t="s">
+        <v>71</v>
+      </c>
+      <c r="I107">
+        <v>0</v>
+      </c>
+      <c r="J107">
+        <v>0</v>
+      </c>
+      <c r="K107">
+        <v>0</v>
+      </c>
+      <c r="L107">
+        <v>0</v>
+      </c>
+      <c r="M107">
+        <v>1</v>
+      </c>
+      <c r="N107">
+        <v>1</v>
+      </c>
+      <c r="O107" t="s">
+        <v>85</v>
+      </c>
+      <c r="P107" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q107">
+        <v>2.13</v>
+      </c>
+      <c r="R107">
+        <v>2.45</v>
+      </c>
+      <c r="S107">
+        <v>5.42</v>
+      </c>
+      <c r="T107">
+        <v>1.32</v>
+      </c>
+      <c r="U107">
+        <v>3.3</v>
+      </c>
+      <c r="V107">
+        <v>2.59</v>
+      </c>
+      <c r="W107">
+        <v>1.49</v>
+      </c>
+      <c r="X107">
+        <v>5.5</v>
+      </c>
+      <c r="Y107">
+        <v>1.11</v>
+      </c>
+      <c r="Z107">
+        <v>1.57</v>
+      </c>
+      <c r="AA107">
+        <v>3.83</v>
+      </c>
+      <c r="AB107">
+        <v>4.5</v>
+      </c>
+      <c r="AC107">
+        <v>1.02</v>
+      </c>
+      <c r="AD107">
+        <v>10</v>
+      </c>
+      <c r="AE107">
+        <v>1.25</v>
+      </c>
+      <c r="AF107">
+        <v>3.6</v>
+      </c>
+      <c r="AG107">
+        <v>1.76</v>
+      </c>
+      <c r="AH107">
+        <v>1.94</v>
+      </c>
+      <c r="AI107">
+        <v>1.75</v>
+      </c>
+      <c r="AJ107">
+        <v>1.95</v>
+      </c>
+      <c r="AK107">
+        <v>1.18</v>
+      </c>
+      <c r="AL107">
+        <v>1.22</v>
+      </c>
+      <c r="AM107">
+        <v>2.3</v>
+      </c>
+      <c r="AN107">
+        <v>1.71</v>
+      </c>
+      <c r="AO107">
+        <v>0</v>
+      </c>
+      <c r="AP107">
+        <v>1.5</v>
+      </c>
+      <c r="AQ107">
+        <v>0.38</v>
+      </c>
+      <c r="AR107">
+        <v>1.82</v>
+      </c>
+      <c r="AS107">
+        <v>1.19</v>
+      </c>
+      <c r="AT107">
+        <v>3.01</v>
+      </c>
+      <c r="AU107">
+        <v>5</v>
+      </c>
+      <c r="AV107">
+        <v>2</v>
+      </c>
+      <c r="AW107">
+        <v>9</v>
+      </c>
+      <c r="AX107">
+        <v>6</v>
+      </c>
+      <c r="AY107">
+        <v>14</v>
+      </c>
+      <c r="AZ107">
+        <v>8</v>
+      </c>
+      <c r="BA107">
+        <v>2</v>
+      </c>
+      <c r="BB107">
+        <v>1</v>
+      </c>
+      <c r="BC107">
+        <v>3</v>
+      </c>
+      <c r="BD107">
+        <v>1.45</v>
+      </c>
+      <c r="BE107">
+        <v>8.5</v>
+      </c>
+      <c r="BF107">
+        <v>3.22</v>
+      </c>
+      <c r="BG107">
+        <v>1.32</v>
+      </c>
+      <c r="BH107">
+        <v>2.88</v>
+      </c>
+      <c r="BI107">
+        <v>1.8</v>
+      </c>
+      <c r="BJ107">
+        <v>2</v>
+      </c>
+      <c r="BK107">
+        <v>2.05</v>
+      </c>
+      <c r="BL107">
+        <v>1.65</v>
+      </c>
+      <c r="BM107">
+        <v>2.7</v>
+      </c>
+      <c r="BN107">
+        <v>1.36</v>
+      </c>
+      <c r="BO107">
+        <v>3.78</v>
+      </c>
+      <c r="BP107">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="108" spans="1:68">
+      <c r="A108" s="1">
+        <v>107</v>
+      </c>
+      <c r="B108">
+        <v>7813927</v>
+      </c>
+      <c r="C108" t="s">
+        <v>68</v>
+      </c>
+      <c r="D108" t="s">
+        <v>69</v>
+      </c>
+      <c r="E108" s="2">
+        <v>45822.29166666666</v>
+      </c>
+      <c r="F108">
+        <v>16</v>
+      </c>
+      <c r="G108" t="s">
+        <v>76</v>
+      </c>
+      <c r="H108" t="s">
+        <v>75</v>
+      </c>
+      <c r="I108">
+        <v>1</v>
+      </c>
+      <c r="J108">
+        <v>1</v>
+      </c>
+      <c r="K108">
+        <v>2</v>
+      </c>
+      <c r="L108">
+        <v>3</v>
+      </c>
+      <c r="M108">
+        <v>1</v>
+      </c>
+      <c r="N108">
+        <v>4</v>
+      </c>
+      <c r="O108" t="s">
+        <v>157</v>
+      </c>
+      <c r="P108" t="s">
+        <v>218</v>
+      </c>
+      <c r="Q108">
+        <v>3.38</v>
+      </c>
+      <c r="R108">
+        <v>2.29</v>
+      </c>
+      <c r="S108">
+        <v>3.05</v>
+      </c>
+      <c r="T108">
+        <v>1.34</v>
+      </c>
+      <c r="U108">
+        <v>3.19</v>
+      </c>
+      <c r="V108">
+        <v>2.71</v>
+      </c>
+      <c r="W108">
+        <v>1.45</v>
+      </c>
+      <c r="X108">
+        <v>6</v>
+      </c>
+      <c r="Y108">
+        <v>1.09</v>
+      </c>
+      <c r="Z108">
+        <v>2.65</v>
+      </c>
+      <c r="AA108">
+        <v>3.17</v>
+      </c>
+      <c r="AB108">
+        <v>2.34</v>
+      </c>
+      <c r="AC108">
+        <v>1.02</v>
+      </c>
+      <c r="AD108">
+        <v>10</v>
+      </c>
+      <c r="AE108">
+        <v>1.29</v>
+      </c>
+      <c r="AF108">
+        <v>3.4</v>
+      </c>
+      <c r="AG108">
+        <v>1.87</v>
+      </c>
+      <c r="AH108">
+        <v>1.83</v>
+      </c>
+      <c r="AI108">
+        <v>1.67</v>
+      </c>
+      <c r="AJ108">
+        <v>2.1</v>
+      </c>
+      <c r="AK108">
+        <v>1.57</v>
+      </c>
+      <c r="AL108">
+        <v>1.3</v>
+      </c>
+      <c r="AM108">
+        <v>1.44</v>
+      </c>
+      <c r="AN108">
+        <v>1.57</v>
+      </c>
+      <c r="AO108">
+        <v>1.83</v>
+      </c>
+      <c r="AP108">
+        <v>1.75</v>
+      </c>
+      <c r="AQ108">
+        <v>1.57</v>
+      </c>
+      <c r="AR108">
+        <v>1.44</v>
+      </c>
+      <c r="AS108">
+        <v>1.23</v>
+      </c>
+      <c r="AT108">
+        <v>2.67</v>
+      </c>
+      <c r="AU108">
+        <v>9</v>
+      </c>
+      <c r="AV108">
+        <v>3</v>
+      </c>
+      <c r="AW108">
+        <v>10</v>
+      </c>
+      <c r="AX108">
+        <v>8</v>
+      </c>
+      <c r="AY108">
+        <v>19</v>
+      </c>
+      <c r="AZ108">
+        <v>11</v>
+      </c>
+      <c r="BA108">
+        <v>5</v>
+      </c>
+      <c r="BB108">
+        <v>5</v>
+      </c>
+      <c r="BC108">
+        <v>10</v>
+      </c>
+      <c r="BD108">
+        <v>1.83</v>
+      </c>
+      <c r="BE108">
+        <v>6.1</v>
+      </c>
+      <c r="BF108">
+        <v>2.45</v>
+      </c>
+      <c r="BG108">
+        <v>1.39</v>
+      </c>
+      <c r="BH108">
+        <v>2.59</v>
+      </c>
+      <c r="BI108">
+        <v>1.85</v>
+      </c>
+      <c r="BJ108">
+        <v>1.95</v>
+      </c>
+      <c r="BK108">
+        <v>2.19</v>
+      </c>
+      <c r="BL108">
+        <v>1.54</v>
+      </c>
+      <c r="BM108">
+        <v>2.97</v>
+      </c>
+      <c r="BN108">
+        <v>1.3</v>
+      </c>
+      <c r="BO108">
+        <v>3.7</v>
+      </c>
+      <c r="BP108">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="221">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -490,10 +490,13 @@
     <t>['4502', '65', '73']</t>
   </si>
   <si>
-    <t>['1', '6']</t>
+    <t>['73', '80', '82']</t>
   </si>
   <si>
     <t>['67']</t>
+  </si>
+  <si>
+    <t>['1', '6']</t>
   </si>
   <si>
     <t>['85']</t>
@@ -671,6 +674,9 @@
   </si>
   <si>
     <t>['17']</t>
+  </si>
+  <si>
+    <t>['15', '49']</t>
   </si>
 </sst>
 </file>
@@ -1032,7 +1038,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP108"/>
+  <dimension ref="A1:BP113"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1369,7 +1375,7 @@
         <v>2.78</v>
       </c>
       <c r="AQ2">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1494,7 +1500,7 @@
         <v>85</v>
       </c>
       <c r="P3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Q3">
         <v>3.8</v>
@@ -2524,7 +2530,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q8">
         <v>2.39</v>
@@ -2936,7 +2942,7 @@
         <v>85</v>
       </c>
       <c r="P10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q10">
         <v>4.3</v>
@@ -3142,7 +3148,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q11">
         <v>2.8</v>
@@ -3426,7 +3432,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ12">
         <v>1.13</v>
@@ -3554,7 +3560,7 @@
         <v>85</v>
       </c>
       <c r="P13" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q13">
         <v>2.43</v>
@@ -3635,7 +3641,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ13">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR13">
         <v>1.4</v>
@@ -3760,7 +3766,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q14">
         <v>3.9</v>
@@ -4172,7 +4178,7 @@
         <v>85</v>
       </c>
       <c r="P16" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q16">
         <v>3.18</v>
@@ -4253,7 +4259,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ16">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AR16">
         <v>1.61</v>
@@ -4378,7 +4384,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q17">
         <v>3</v>
@@ -4456,10 +4462,10 @@
         <v>1.5</v>
       </c>
       <c r="AP17">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ17">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR17">
         <v>1.52</v>
@@ -4790,7 +4796,7 @@
         <v>95</v>
       </c>
       <c r="P19" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q19">
         <v>2.71</v>
@@ -4868,7 +4874,7 @@
         <v>0.5</v>
       </c>
       <c r="AP19">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AQ19">
         <v>1</v>
@@ -4996,7 +5002,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q20">
         <v>3.5</v>
@@ -5408,7 +5414,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q22">
         <v>5</v>
@@ -5489,7 +5495,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ22">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AR22">
         <v>0.92</v>
@@ -5820,7 +5826,7 @@
         <v>99</v>
       </c>
       <c r="P24" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q24">
         <v>3</v>
@@ -5898,7 +5904,7 @@
         <v>1.33</v>
       </c>
       <c r="AP24">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ24">
         <v>1</v>
@@ -6104,10 +6110,10 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AQ25">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="AR25">
         <v>2.07</v>
@@ -6310,7 +6316,7 @@
         <v>0.33</v>
       </c>
       <c r="AP26">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="AQ26">
         <v>1.13</v>
@@ -6438,7 +6444,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q27">
         <v>2.25</v>
@@ -6644,7 +6650,7 @@
         <v>101</v>
       </c>
       <c r="P28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q28">
         <v>4</v>
@@ -6850,7 +6856,7 @@
         <v>102</v>
       </c>
       <c r="P29" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q29">
         <v>2.2</v>
@@ -6931,7 +6937,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ29">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR29">
         <v>1.22</v>
@@ -7056,7 +7062,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q30">
         <v>3.75</v>
@@ -7262,7 +7268,7 @@
         <v>104</v>
       </c>
       <c r="P31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q31">
         <v>3.25</v>
@@ -7340,7 +7346,7 @@
         <v>2</v>
       </c>
       <c r="AP31">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="AQ31">
         <v>1.73</v>
@@ -7674,7 +7680,7 @@
         <v>91</v>
       </c>
       <c r="P33" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q33">
         <v>2.63</v>
@@ -7755,7 +7761,7 @@
         <v>2.78</v>
       </c>
       <c r="AQ33">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AR33">
         <v>1.69</v>
@@ -7880,7 +7886,7 @@
         <v>85</v>
       </c>
       <c r="P34" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q34">
         <v>3.8</v>
@@ -8086,7 +8092,7 @@
         <v>106</v>
       </c>
       <c r="P35" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q35">
         <v>2.8</v>
@@ -8373,7 +8379,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ36">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="AR36">
         <v>0</v>
@@ -8704,7 +8710,7 @@
         <v>85</v>
       </c>
       <c r="P38" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q38">
         <v>5</v>
@@ -8782,10 +8788,10 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ38">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AR38">
         <v>1.61</v>
@@ -8910,7 +8916,7 @@
         <v>85</v>
       </c>
       <c r="P39" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q39">
         <v>3.1</v>
@@ -9194,10 +9200,10 @@
         <v>1.33</v>
       </c>
       <c r="AP40">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="AQ40">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR40">
         <v>1.62</v>
@@ -9322,7 +9328,7 @@
         <v>110</v>
       </c>
       <c r="P41" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q41">
         <v>3.25</v>
@@ -9400,7 +9406,7 @@
         <v>1.5</v>
       </c>
       <c r="AP41">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AQ41">
         <v>1.38</v>
@@ -9528,7 +9534,7 @@
         <v>111</v>
       </c>
       <c r="P42" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q42">
         <v>2.5</v>
@@ -9815,7 +9821,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ43">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR43">
         <v>1.02</v>
@@ -9940,7 +9946,7 @@
         <v>113</v>
       </c>
       <c r="P44" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q44">
         <v>3.4</v>
@@ -10018,7 +10024,7 @@
         <v>0.5</v>
       </c>
       <c r="AP44">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AQ44">
         <v>1.13</v>
@@ -10146,7 +10152,7 @@
         <v>113</v>
       </c>
       <c r="P45" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q45">
         <v>3.75</v>
@@ -10224,7 +10230,7 @@
         <v>1.83</v>
       </c>
       <c r="AP45">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ45">
         <v>1.73</v>
@@ -10352,7 +10358,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q46">
         <v>3.75</v>
@@ -10558,7 +10564,7 @@
         <v>85</v>
       </c>
       <c r="P47" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q47">
         <v>3</v>
@@ -10639,7 +10645,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ47">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="AR47">
         <v>1.74</v>
@@ -10970,7 +10976,7 @@
         <v>116</v>
       </c>
       <c r="P49" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -11257,7 +11263,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ50">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR50">
         <v>1.01</v>
@@ -11382,7 +11388,7 @@
         <v>85</v>
       </c>
       <c r="P51" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q51">
         <v>2.25</v>
@@ -11872,7 +11878,7 @@
         <v>0.5</v>
       </c>
       <c r="AP53">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="AQ53">
         <v>0.5</v>
@@ -12206,7 +12212,7 @@
         <v>119</v>
       </c>
       <c r="P55" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q55">
         <v>5</v>
@@ -12287,7 +12293,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ55">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AR55">
         <v>1.32</v>
@@ -12618,7 +12624,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q57">
         <v>3.75</v>
@@ -12824,7 +12830,7 @@
         <v>121</v>
       </c>
       <c r="P58" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q58">
         <v>2.3</v>
@@ -12905,7 +12911,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ58">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR58">
         <v>1.31</v>
@@ -13030,7 +13036,7 @@
         <v>85</v>
       </c>
       <c r="P59" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q59">
         <v>3.2</v>
@@ -13317,7 +13323,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ60">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR60">
         <v>2.02</v>
@@ -13442,7 +13448,7 @@
         <v>123</v>
       </c>
       <c r="P61" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q61">
         <v>4</v>
@@ -13523,7 +13529,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ61">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AR61">
         <v>1.39</v>
@@ -13648,7 +13654,7 @@
         <v>124</v>
       </c>
       <c r="P62" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q62">
         <v>2.3</v>
@@ -13726,10 +13732,10 @@
         <v>1.67</v>
       </c>
       <c r="AP62">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="AQ62">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="AR62">
         <v>1.79</v>
@@ -13854,7 +13860,7 @@
         <v>85</v>
       </c>
       <c r="P63" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q63">
         <v>3.2</v>
@@ -13932,7 +13938,7 @@
         <v>1.88</v>
       </c>
       <c r="AP63">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AQ63">
         <v>1.73</v>
@@ -14060,7 +14066,7 @@
         <v>125</v>
       </c>
       <c r="P64" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q64">
         <v>2.5</v>
@@ -14266,7 +14272,7 @@
         <v>126</v>
       </c>
       <c r="P65" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q65">
         <v>4</v>
@@ -14472,7 +14478,7 @@
         <v>127</v>
       </c>
       <c r="P66" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q66">
         <v>3</v>
@@ -14759,7 +14765,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ67">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR67">
         <v>1.4</v>
@@ -14884,7 +14890,7 @@
         <v>129</v>
       </c>
       <c r="P68" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q68">
         <v>5</v>
@@ -14962,7 +14968,7 @@
         <v>1</v>
       </c>
       <c r="AP68">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AQ68">
         <v>1.57</v>
@@ -15502,7 +15508,7 @@
         <v>132</v>
       </c>
       <c r="P71" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q71">
         <v>2.63</v>
@@ -15580,7 +15586,7 @@
         <v>0</v>
       </c>
       <c r="AP71">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ71">
         <v>0.38</v>
@@ -15786,7 +15792,7 @@
         <v>0.25</v>
       </c>
       <c r="AP72">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AQ72">
         <v>0.5</v>
@@ -15914,7 +15920,7 @@
         <v>85</v>
       </c>
       <c r="P73" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q73">
         <v>3.6</v>
@@ -16120,7 +16126,7 @@
         <v>85</v>
       </c>
       <c r="P74" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q74">
         <v>4.33</v>
@@ -16201,7 +16207,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ74">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AR74">
         <v>1.98</v>
@@ -16326,7 +16332,7 @@
         <v>134</v>
       </c>
       <c r="P75" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q75">
         <v>1.91</v>
@@ -16407,7 +16413,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ75">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR75">
         <v>1.33</v>
@@ -16532,7 +16538,7 @@
         <v>135</v>
       </c>
       <c r="P76" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q76">
         <v>2.63</v>
@@ -16610,10 +16616,10 @@
         <v>1.25</v>
       </c>
       <c r="AP76">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AQ76">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="AR76">
         <v>0</v>
@@ -16738,7 +16744,7 @@
         <v>85</v>
       </c>
       <c r="P77" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q77">
         <v>4.5</v>
@@ -16816,10 +16822,10 @@
         <v>2.33</v>
       </c>
       <c r="AP77">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AQ77">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AR77">
         <v>1.89</v>
@@ -17022,7 +17028,7 @@
         <v>0</v>
       </c>
       <c r="AP78">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="AQ78">
         <v>0.38</v>
@@ -17150,7 +17156,7 @@
         <v>137</v>
       </c>
       <c r="P79" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q79">
         <v>3.6</v>
@@ -17643,7 +17649,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ81">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="AR81">
         <v>1.17</v>
@@ -17768,7 +17774,7 @@
         <v>140</v>
       </c>
       <c r="P82" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q82">
         <v>3.75</v>
@@ -17974,7 +17980,7 @@
         <v>85</v>
       </c>
       <c r="P83" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q83">
         <v>7.5</v>
@@ -18055,7 +18061,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ83">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AR83">
         <v>1.35</v>
@@ -18180,7 +18186,7 @@
         <v>141</v>
       </c>
       <c r="P84" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q84">
         <v>2.38</v>
@@ -18258,7 +18264,7 @@
         <v>1.11</v>
       </c>
       <c r="AP84">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AQ84">
         <v>1</v>
@@ -18386,7 +18392,7 @@
         <v>142</v>
       </c>
       <c r="P85" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q85">
         <v>3.75</v>
@@ -18464,7 +18470,7 @@
         <v>1.33</v>
       </c>
       <c r="AP85">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AQ85">
         <v>1.57</v>
@@ -18592,7 +18598,7 @@
         <v>85</v>
       </c>
       <c r="P86" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q86">
         <v>4.2</v>
@@ -18670,7 +18676,7 @@
         <v>1.75</v>
       </c>
       <c r="AP86">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ86">
         <v>1.57</v>
@@ -18876,10 +18882,10 @@
         <v>0.8</v>
       </c>
       <c r="AP87">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AQ87">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR87">
         <v>1.66</v>
@@ -19085,7 +19091,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ88">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AR88">
         <v>1.04</v>
@@ -19210,7 +19216,7 @@
         <v>143</v>
       </c>
       <c r="P89" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q89">
         <v>2.62</v>
@@ -19416,7 +19422,7 @@
         <v>144</v>
       </c>
       <c r="P90" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q90">
         <v>3.1</v>
@@ -19828,7 +19834,7 @@
         <v>146</v>
       </c>
       <c r="P92" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -19906,7 +19912,7 @@
         <v>1.4</v>
       </c>
       <c r="AP92">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="AQ92">
         <v>1.14</v>
@@ -20034,7 +20040,7 @@
         <v>147</v>
       </c>
       <c r="P93" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q93">
         <v>2.62</v>
@@ -20115,7 +20121,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ93">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AR93">
         <v>1.35</v>
@@ -20240,7 +20246,7 @@
         <v>148</v>
       </c>
       <c r="P94" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q94">
         <v>2.4</v>
@@ -20318,7 +20324,7 @@
         <v>0.17</v>
       </c>
       <c r="AP94">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AQ94">
         <v>0.5</v>
@@ -20446,7 +20452,7 @@
         <v>149</v>
       </c>
       <c r="P95" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q95">
         <v>3.1</v>
@@ -20524,10 +20530,10 @@
         <v>0.67</v>
       </c>
       <c r="AP95">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AQ95">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR95">
         <v>1.52</v>
@@ -20733,7 +20739,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ96">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="AR96">
         <v>1.3</v>
@@ -21064,7 +21070,7 @@
         <v>152</v>
       </c>
       <c r="P98" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q98">
         <v>2.3</v>
@@ -21142,7 +21148,7 @@
         <v>1.83</v>
       </c>
       <c r="AP98">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="AQ98">
         <v>1.38</v>
@@ -21270,7 +21276,7 @@
         <v>153</v>
       </c>
       <c r="P99" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q99">
         <v>6.5</v>
@@ -21351,7 +21357,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ99">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AR99">
         <v>1.19</v>
@@ -21476,7 +21482,7 @@
         <v>154</v>
       </c>
       <c r="P100" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q100">
         <v>4.33</v>
@@ -21682,7 +21688,7 @@
         <v>85</v>
       </c>
       <c r="P101" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q101">
         <v>3.88</v>
@@ -21760,7 +21766,7 @@
         <v>0.86</v>
       </c>
       <c r="AP101">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AQ101">
         <v>1.13</v>
@@ -21888,7 +21894,7 @@
         <v>85</v>
       </c>
       <c r="P102" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q102">
         <v>2.79</v>
@@ -22094,7 +22100,7 @@
         <v>85</v>
       </c>
       <c r="P103" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q103">
         <v>2.14</v>
@@ -22175,7 +22181,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ103">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR103">
         <v>1.65</v>
@@ -22378,7 +22384,7 @@
         <v>2</v>
       </c>
       <c r="AP104">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AQ104">
         <v>1.57</v>
@@ -22790,7 +22796,7 @@
         <v>0</v>
       </c>
       <c r="AP106">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AQ106">
         <v>0.38</v>
@@ -22918,7 +22924,7 @@
         <v>85</v>
       </c>
       <c r="P107" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q107">
         <v>2.13</v>
@@ -23124,7 +23130,7 @@
         <v>157</v>
       </c>
       <c r="P108" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q108">
         <v>3.38</v>
@@ -23281,6 +23287,1036 @@
       </c>
       <c r="BP108">
         <v>1.22</v>
+      </c>
+    </row>
+    <row r="109" spans="1:68">
+      <c r="A109" s="1">
+        <v>108</v>
+      </c>
+      <c r="B109">
+        <v>7813928</v>
+      </c>
+      <c r="C109" t="s">
+        <v>68</v>
+      </c>
+      <c r="D109" t="s">
+        <v>69</v>
+      </c>
+      <c r="E109" s="2">
+        <v>45822.29166666666</v>
+      </c>
+      <c r="F109">
+        <v>16</v>
+      </c>
+      <c r="G109" t="s">
+        <v>82</v>
+      </c>
+      <c r="H109" t="s">
+        <v>74</v>
+      </c>
+      <c r="I109">
+        <v>0</v>
+      </c>
+      <c r="J109">
+        <v>0</v>
+      </c>
+      <c r="K109">
+        <v>0</v>
+      </c>
+      <c r="L109">
+        <v>0</v>
+      </c>
+      <c r="M109">
+        <v>1</v>
+      </c>
+      <c r="N109">
+        <v>1</v>
+      </c>
+      <c r="O109" t="s">
+        <v>85</v>
+      </c>
+      <c r="P109" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q109">
+        <v>3.32</v>
+      </c>
+      <c r="R109">
+        <v>2.04</v>
+      </c>
+      <c r="S109">
+        <v>3.08</v>
+      </c>
+      <c r="T109">
+        <v>1.41</v>
+      </c>
+      <c r="U109">
+        <v>2.69</v>
+      </c>
+      <c r="V109">
+        <v>2.93</v>
+      </c>
+      <c r="W109">
+        <v>1.35</v>
+      </c>
+      <c r="X109">
+        <v>6.95</v>
+      </c>
+      <c r="Y109">
+        <v>1.04</v>
+      </c>
+      <c r="Z109">
+        <v>2.59</v>
+      </c>
+      <c r="AA109">
+        <v>3.12</v>
+      </c>
+      <c r="AB109">
+        <v>2.42</v>
+      </c>
+      <c r="AC109">
+        <v>1.02</v>
+      </c>
+      <c r="AD109">
+        <v>8.1</v>
+      </c>
+      <c r="AE109">
+        <v>1.3</v>
+      </c>
+      <c r="AF109">
+        <v>2.97</v>
+      </c>
+      <c r="AG109">
+        <v>2</v>
+      </c>
+      <c r="AH109">
+        <v>1.67</v>
+      </c>
+      <c r="AI109">
+        <v>1.76</v>
+      </c>
+      <c r="AJ109">
+        <v>1.91</v>
+      </c>
+      <c r="AK109">
+        <v>1.47</v>
+      </c>
+      <c r="AL109">
+        <v>1.28</v>
+      </c>
+      <c r="AM109">
+        <v>1.41</v>
+      </c>
+      <c r="AN109">
+        <v>0.4</v>
+      </c>
+      <c r="AO109">
+        <v>0.86</v>
+      </c>
+      <c r="AP109">
+        <v>0.33</v>
+      </c>
+      <c r="AQ109">
+        <v>1.13</v>
+      </c>
+      <c r="AR109">
+        <v>1.41</v>
+      </c>
+      <c r="AS109">
+        <v>1.21</v>
+      </c>
+      <c r="AT109">
+        <v>2.62</v>
+      </c>
+      <c r="AU109">
+        <v>4</v>
+      </c>
+      <c r="AV109">
+        <v>6</v>
+      </c>
+      <c r="AW109">
+        <v>6</v>
+      </c>
+      <c r="AX109">
+        <v>7</v>
+      </c>
+      <c r="AY109">
+        <v>10</v>
+      </c>
+      <c r="AZ109">
+        <v>13</v>
+      </c>
+      <c r="BA109">
+        <v>2</v>
+      </c>
+      <c r="BB109">
+        <v>2</v>
+      </c>
+      <c r="BC109">
+        <v>4</v>
+      </c>
+      <c r="BD109">
+        <v>1.98</v>
+      </c>
+      <c r="BE109">
+        <v>5.95</v>
+      </c>
+      <c r="BF109">
+        <v>2.25</v>
+      </c>
+      <c r="BG109">
+        <v>1.47</v>
+      </c>
+      <c r="BH109">
+        <v>2.35</v>
+      </c>
+      <c r="BI109">
+        <v>1.86</v>
+      </c>
+      <c r="BJ109">
+        <v>1.8</v>
+      </c>
+      <c r="BK109">
+        <v>2.43</v>
+      </c>
+      <c r="BL109">
+        <v>1.44</v>
+      </c>
+      <c r="BM109">
+        <v>3.34</v>
+      </c>
+      <c r="BN109">
+        <v>1.24</v>
+      </c>
+      <c r="BO109">
+        <v>4.4</v>
+      </c>
+      <c r="BP109">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="110" spans="1:68">
+      <c r="A110" s="1">
+        <v>109</v>
+      </c>
+      <c r="B110">
+        <v>7813929</v>
+      </c>
+      <c r="C110" t="s">
+        <v>68</v>
+      </c>
+      <c r="D110" t="s">
+        <v>69</v>
+      </c>
+      <c r="E110" s="2">
+        <v>45823.29166666666</v>
+      </c>
+      <c r="F110">
+        <v>16</v>
+      </c>
+      <c r="G110" t="s">
+        <v>83</v>
+      </c>
+      <c r="H110" t="s">
+        <v>72</v>
+      </c>
+      <c r="I110">
+        <v>0</v>
+      </c>
+      <c r="J110">
+        <v>1</v>
+      </c>
+      <c r="K110">
+        <v>1</v>
+      </c>
+      <c r="L110">
+        <v>0</v>
+      </c>
+      <c r="M110">
+        <v>1</v>
+      </c>
+      <c r="N110">
+        <v>1</v>
+      </c>
+      <c r="O110" t="s">
+        <v>85</v>
+      </c>
+      <c r="P110" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q110">
+        <v>3.25</v>
+      </c>
+      <c r="R110">
+        <v>2.2</v>
+      </c>
+      <c r="S110">
+        <v>3.25</v>
+      </c>
+      <c r="T110">
+        <v>1.4</v>
+      </c>
+      <c r="U110">
+        <v>2.75</v>
+      </c>
+      <c r="V110">
+        <v>2.75</v>
+      </c>
+      <c r="W110">
+        <v>1.4</v>
+      </c>
+      <c r="X110">
+        <v>8</v>
+      </c>
+      <c r="Y110">
+        <v>1.08</v>
+      </c>
+      <c r="Z110">
+        <v>2.63</v>
+      </c>
+      <c r="AA110">
+        <v>3.1</v>
+      </c>
+      <c r="AB110">
+        <v>2.4</v>
+      </c>
+      <c r="AC110">
+        <v>1.05</v>
+      </c>
+      <c r="AD110">
+        <v>8.5</v>
+      </c>
+      <c r="AE110">
+        <v>1.3</v>
+      </c>
+      <c r="AF110">
+        <v>3.3</v>
+      </c>
+      <c r="AG110">
+        <v>1.91</v>
+      </c>
+      <c r="AH110">
+        <v>1.79</v>
+      </c>
+      <c r="AI110">
+        <v>1.73</v>
+      </c>
+      <c r="AJ110">
+        <v>2</v>
+      </c>
+      <c r="AK110">
+        <v>1.51</v>
+      </c>
+      <c r="AL110">
+        <v>1.3</v>
+      </c>
+      <c r="AM110">
+        <v>1.44</v>
+      </c>
+      <c r="AN110">
+        <v>2.5</v>
+      </c>
+      <c r="AO110">
+        <v>2.33</v>
+      </c>
+      <c r="AP110">
+        <v>2</v>
+      </c>
+      <c r="AQ110">
+        <v>2.43</v>
+      </c>
+      <c r="AR110">
+        <v>1.42</v>
+      </c>
+      <c r="AS110">
+        <v>1.12</v>
+      </c>
+      <c r="AT110">
+        <v>2.54</v>
+      </c>
+      <c r="AU110">
+        <v>6</v>
+      </c>
+      <c r="AV110">
+        <v>4</v>
+      </c>
+      <c r="AW110">
+        <v>10</v>
+      </c>
+      <c r="AX110">
+        <v>10</v>
+      </c>
+      <c r="AY110">
+        <v>16</v>
+      </c>
+      <c r="AZ110">
+        <v>14</v>
+      </c>
+      <c r="BA110">
+        <v>6</v>
+      </c>
+      <c r="BB110">
+        <v>4</v>
+      </c>
+      <c r="BC110">
+        <v>10</v>
+      </c>
+      <c r="BD110">
+        <v>1.92</v>
+      </c>
+      <c r="BE110">
+        <v>5.95</v>
+      </c>
+      <c r="BF110">
+        <v>2.33</v>
+      </c>
+      <c r="BG110">
+        <v>1.47</v>
+      </c>
+      <c r="BH110">
+        <v>2.35</v>
+      </c>
+      <c r="BI110">
+        <v>1.85</v>
+      </c>
+      <c r="BJ110">
+        <v>1.81</v>
+      </c>
+      <c r="BK110">
+        <v>2.43</v>
+      </c>
+      <c r="BL110">
+        <v>1.44</v>
+      </c>
+      <c r="BM110">
+        <v>3.34</v>
+      </c>
+      <c r="BN110">
+        <v>1.24</v>
+      </c>
+      <c r="BO110">
+        <v>4.2</v>
+      </c>
+      <c r="BP110">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="111" spans="1:68">
+      <c r="A111" s="1">
+        <v>110</v>
+      </c>
+      <c r="B111">
+        <v>7813930</v>
+      </c>
+      <c r="C111" t="s">
+        <v>68</v>
+      </c>
+      <c r="D111" t="s">
+        <v>69</v>
+      </c>
+      <c r="E111" s="2">
+        <v>45823.29166666666</v>
+      </c>
+      <c r="F111">
+        <v>16</v>
+      </c>
+      <c r="G111" t="s">
+        <v>77</v>
+      </c>
+      <c r="H111" t="s">
+        <v>73</v>
+      </c>
+      <c r="I111">
+        <v>0</v>
+      </c>
+      <c r="J111">
+        <v>0</v>
+      </c>
+      <c r="K111">
+        <v>0</v>
+      </c>
+      <c r="L111">
+        <v>0</v>
+      </c>
+      <c r="M111">
+        <v>0</v>
+      </c>
+      <c r="N111">
+        <v>0</v>
+      </c>
+      <c r="O111" t="s">
+        <v>85</v>
+      </c>
+      <c r="P111" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q111">
+        <v>2.75</v>
+      </c>
+      <c r="R111">
+        <v>2.1</v>
+      </c>
+      <c r="S111">
+        <v>4.33</v>
+      </c>
+      <c r="T111">
+        <v>1.44</v>
+      </c>
+      <c r="U111">
+        <v>2.63</v>
+      </c>
+      <c r="V111">
+        <v>3.25</v>
+      </c>
+      <c r="W111">
+        <v>1.33</v>
+      </c>
+      <c r="X111">
+        <v>9</v>
+      </c>
+      <c r="Y111">
+        <v>1.07</v>
+      </c>
+      <c r="Z111">
+        <v>1.97</v>
+      </c>
+      <c r="AA111">
+        <v>3.19</v>
+      </c>
+      <c r="AB111">
+        <v>3.36</v>
+      </c>
+      <c r="AC111">
+        <v>1.06</v>
+      </c>
+      <c r="AD111">
+        <v>8</v>
+      </c>
+      <c r="AE111">
+        <v>1.36</v>
+      </c>
+      <c r="AF111">
+        <v>3</v>
+      </c>
+      <c r="AG111">
+        <v>2</v>
+      </c>
+      <c r="AH111">
+        <v>1.65</v>
+      </c>
+      <c r="AI111">
+        <v>1.91</v>
+      </c>
+      <c r="AJ111">
+        <v>1.8</v>
+      </c>
+      <c r="AK111">
+        <v>1.29</v>
+      </c>
+      <c r="AL111">
+        <v>1.3</v>
+      </c>
+      <c r="AM111">
+        <v>1.73</v>
+      </c>
+      <c r="AN111">
+        <v>1.14</v>
+      </c>
+      <c r="AO111">
+        <v>1.14</v>
+      </c>
+      <c r="AP111">
+        <v>1.13</v>
+      </c>
+      <c r="AQ111">
+        <v>1.13</v>
+      </c>
+      <c r="AR111">
+        <v>1.5</v>
+      </c>
+      <c r="AS111">
+        <v>1.06</v>
+      </c>
+      <c r="AT111">
+        <v>2.56</v>
+      </c>
+      <c r="AU111">
+        <v>2</v>
+      </c>
+      <c r="AV111">
+        <v>2</v>
+      </c>
+      <c r="AW111">
+        <v>0</v>
+      </c>
+      <c r="AX111">
+        <v>4</v>
+      </c>
+      <c r="AY111">
+        <v>2</v>
+      </c>
+      <c r="AZ111">
+        <v>6</v>
+      </c>
+      <c r="BA111">
+        <v>0</v>
+      </c>
+      <c r="BB111">
+        <v>3</v>
+      </c>
+      <c r="BC111">
+        <v>3</v>
+      </c>
+      <c r="BD111">
+        <v>1.54</v>
+      </c>
+      <c r="BE111">
+        <v>7.9</v>
+      </c>
+      <c r="BF111">
+        <v>2.92</v>
+      </c>
+      <c r="BG111">
+        <v>1.43</v>
+      </c>
+      <c r="BH111">
+        <v>2.46</v>
+      </c>
+      <c r="BI111">
+        <v>1.81</v>
+      </c>
+      <c r="BJ111">
+        <v>1.85</v>
+      </c>
+      <c r="BK111">
+        <v>2.33</v>
+      </c>
+      <c r="BL111">
+        <v>1.48</v>
+      </c>
+      <c r="BM111">
+        <v>3.2</v>
+      </c>
+      <c r="BN111">
+        <v>1.26</v>
+      </c>
+      <c r="BO111">
+        <v>4.15</v>
+      </c>
+      <c r="BP111">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="112" spans="1:68">
+      <c r="A112" s="1">
+        <v>111</v>
+      </c>
+      <c r="B112">
+        <v>7813931</v>
+      </c>
+      <c r="C112" t="s">
+        <v>68</v>
+      </c>
+      <c r="D112" t="s">
+        <v>69</v>
+      </c>
+      <c r="E112" s="2">
+        <v>45823.29166666666</v>
+      </c>
+      <c r="F112">
+        <v>16</v>
+      </c>
+      <c r="G112" t="s">
+        <v>78</v>
+      </c>
+      <c r="H112" t="s">
+        <v>80</v>
+      </c>
+      <c r="I112">
+        <v>0</v>
+      </c>
+      <c r="J112">
+        <v>0</v>
+      </c>
+      <c r="K112">
+        <v>0</v>
+      </c>
+      <c r="L112">
+        <v>3</v>
+      </c>
+      <c r="M112">
+        <v>0</v>
+      </c>
+      <c r="N112">
+        <v>3</v>
+      </c>
+      <c r="O112" t="s">
+        <v>158</v>
+      </c>
+      <c r="P112" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q112">
+        <v>2.6</v>
+      </c>
+      <c r="R112">
+        <v>2.2</v>
+      </c>
+      <c r="S112">
+        <v>4.33</v>
+      </c>
+      <c r="T112">
+        <v>1.36</v>
+      </c>
+      <c r="U112">
+        <v>3</v>
+      </c>
+      <c r="V112">
+        <v>2.75</v>
+      </c>
+      <c r="W112">
+        <v>1.4</v>
+      </c>
+      <c r="X112">
+        <v>7</v>
+      </c>
+      <c r="Y112">
+        <v>1.1</v>
+      </c>
+      <c r="Z112">
+        <v>1.94</v>
+      </c>
+      <c r="AA112">
+        <v>3.28</v>
+      </c>
+      <c r="AB112">
+        <v>3.33</v>
+      </c>
+      <c r="AC112">
+        <v>1.05</v>
+      </c>
+      <c r="AD112">
+        <v>8.5</v>
+      </c>
+      <c r="AE112">
+        <v>1.3</v>
+      </c>
+      <c r="AF112">
+        <v>3.3</v>
+      </c>
+      <c r="AG112">
+        <v>1.94</v>
+      </c>
+      <c r="AH112">
+        <v>1.76</v>
+      </c>
+      <c r="AI112">
+        <v>1.8</v>
+      </c>
+      <c r="AJ112">
+        <v>1.91</v>
+      </c>
+      <c r="AK112">
+        <v>1.27</v>
+      </c>
+      <c r="AL112">
+        <v>1.3</v>
+      </c>
+      <c r="AM112">
+        <v>1.77</v>
+      </c>
+      <c r="AN112">
+        <v>1</v>
+      </c>
+      <c r="AO112">
+        <v>1</v>
+      </c>
+      <c r="AP112">
+        <v>1.22</v>
+      </c>
+      <c r="AQ112">
+        <v>0.88</v>
+      </c>
+      <c r="AR112">
+        <v>1.55</v>
+      </c>
+      <c r="AS112">
+        <v>1.16</v>
+      </c>
+      <c r="AT112">
+        <v>2.71</v>
+      </c>
+      <c r="AU112">
+        <v>10</v>
+      </c>
+      <c r="AV112">
+        <v>2</v>
+      </c>
+      <c r="AW112">
+        <v>6</v>
+      </c>
+      <c r="AX112">
+        <v>3</v>
+      </c>
+      <c r="AY112">
+        <v>16</v>
+      </c>
+      <c r="AZ112">
+        <v>5</v>
+      </c>
+      <c r="BA112">
+        <v>9</v>
+      </c>
+      <c r="BB112">
+        <v>2</v>
+      </c>
+      <c r="BC112">
+        <v>11</v>
+      </c>
+      <c r="BD112">
+        <v>1.69</v>
+      </c>
+      <c r="BE112">
+        <v>6.15</v>
+      </c>
+      <c r="BF112">
+        <v>2.75</v>
+      </c>
+      <c r="BG112">
+        <v>1.44</v>
+      </c>
+      <c r="BH112">
+        <v>2.43</v>
+      </c>
+      <c r="BI112">
+        <v>1.82</v>
+      </c>
+      <c r="BJ112">
+        <v>1.84</v>
+      </c>
+      <c r="BK112">
+        <v>2.35</v>
+      </c>
+      <c r="BL112">
+        <v>1.47</v>
+      </c>
+      <c r="BM112">
+        <v>3.28</v>
+      </c>
+      <c r="BN112">
+        <v>1.25</v>
+      </c>
+      <c r="BO112">
+        <v>4.05</v>
+      </c>
+      <c r="BP112">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="113" spans="1:68">
+      <c r="A113" s="1">
+        <v>112</v>
+      </c>
+      <c r="B113">
+        <v>7813932</v>
+      </c>
+      <c r="C113" t="s">
+        <v>68</v>
+      </c>
+      <c r="D113" t="s">
+        <v>69</v>
+      </c>
+      <c r="E113" s="2">
+        <v>45823.29166666666</v>
+      </c>
+      <c r="F113">
+        <v>16</v>
+      </c>
+      <c r="G113" t="s">
+        <v>79</v>
+      </c>
+      <c r="H113" t="s">
+        <v>70</v>
+      </c>
+      <c r="I113">
+        <v>0</v>
+      </c>
+      <c r="J113">
+        <v>1</v>
+      </c>
+      <c r="K113">
+        <v>1</v>
+      </c>
+      <c r="L113">
+        <v>1</v>
+      </c>
+      <c r="M113">
+        <v>2</v>
+      </c>
+      <c r="N113">
+        <v>3</v>
+      </c>
+      <c r="O113" t="s">
+        <v>159</v>
+      </c>
+      <c r="P113" t="s">
+        <v>220</v>
+      </c>
+      <c r="Q113">
+        <v>3.4</v>
+      </c>
+      <c r="R113">
+        <v>2.1</v>
+      </c>
+      <c r="S113">
+        <v>3.2</v>
+      </c>
+      <c r="T113">
+        <v>1.4</v>
+      </c>
+      <c r="U113">
+        <v>2.75</v>
+      </c>
+      <c r="V113">
+        <v>3</v>
+      </c>
+      <c r="W113">
+        <v>1.36</v>
+      </c>
+      <c r="X113">
+        <v>8</v>
+      </c>
+      <c r="Y113">
+        <v>1.08</v>
+      </c>
+      <c r="Z113">
+        <v>2.58</v>
+      </c>
+      <c r="AA113">
+        <v>3.23</v>
+      </c>
+      <c r="AB113">
+        <v>2.36</v>
+      </c>
+      <c r="AC113">
+        <v>1.06</v>
+      </c>
+      <c r="AD113">
+        <v>8</v>
+      </c>
+      <c r="AE113">
+        <v>1.3</v>
+      </c>
+      <c r="AF113">
+        <v>3.25</v>
+      </c>
+      <c r="AG113">
+        <v>1.87</v>
+      </c>
+      <c r="AH113">
+        <v>1.83</v>
+      </c>
+      <c r="AI113">
+        <v>1.8</v>
+      </c>
+      <c r="AJ113">
+        <v>1.91</v>
+      </c>
+      <c r="AK113">
+        <v>1.49</v>
+      </c>
+      <c r="AL113">
+        <v>1.31</v>
+      </c>
+      <c r="AM113">
+        <v>1.46</v>
+      </c>
+      <c r="AN113">
+        <v>2.5</v>
+      </c>
+      <c r="AO113">
+        <v>2</v>
+      </c>
+      <c r="AP113">
+        <v>2.22</v>
+      </c>
+      <c r="AQ113">
+        <v>2.14</v>
+      </c>
+      <c r="AR113">
+        <v>1.85</v>
+      </c>
+      <c r="AS113">
+        <v>1.29</v>
+      </c>
+      <c r="AT113">
+        <v>3.14</v>
+      </c>
+      <c r="AU113">
+        <v>6</v>
+      </c>
+      <c r="AV113">
+        <v>3</v>
+      </c>
+      <c r="AW113">
+        <v>5</v>
+      </c>
+      <c r="AX113">
+        <v>2</v>
+      </c>
+      <c r="AY113">
+        <v>11</v>
+      </c>
+      <c r="AZ113">
+        <v>5</v>
+      </c>
+      <c r="BA113">
+        <v>4</v>
+      </c>
+      <c r="BB113">
+        <v>2</v>
+      </c>
+      <c r="BC113">
+        <v>6</v>
+      </c>
+      <c r="BD113">
+        <v>1.94</v>
+      </c>
+      <c r="BE113">
+        <v>6.05</v>
+      </c>
+      <c r="BF113">
+        <v>2.29</v>
+      </c>
+      <c r="BG113">
+        <v>1.4</v>
+      </c>
+      <c r="BH113">
+        <v>2.56</v>
+      </c>
+      <c r="BI113">
+        <v>1.75</v>
+      </c>
+      <c r="BJ113">
+        <v>1.92</v>
+      </c>
+      <c r="BK113">
+        <v>2.24</v>
+      </c>
+      <c r="BL113">
+        <v>1.52</v>
+      </c>
+      <c r="BM113">
+        <v>3.05</v>
+      </c>
+      <c r="BN113">
+        <v>1.28</v>
+      </c>
+      <c r="BO113">
+        <v>3.95</v>
+      </c>
+      <c r="BP113">
+        <v>1.19</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="225">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -496,6 +496,12 @@
     <t>['67']</t>
   </si>
   <si>
+    <t>['27', '65']</t>
+  </si>
+  <si>
+    <t>['17', '59', '63', '84']</t>
+  </si>
+  <si>
     <t>['1', '6']</t>
   </si>
   <si>
@@ -677,6 +683,12 @@
   </si>
   <si>
     <t>['15', '49']</t>
+  </si>
+  <si>
+    <t>['41', '57']</t>
+  </si>
+  <si>
+    <t>['5', '76']</t>
   </si>
 </sst>
 </file>
@@ -1038,7 +1050,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP113"/>
+  <dimension ref="A1:BP117"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1372,7 +1384,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AQ2">
         <v>0.88</v>
@@ -1500,7 +1512,7 @@
         <v>85</v>
       </c>
       <c r="P3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q3">
         <v>3.8</v>
@@ -1578,7 +1590,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AQ3">
         <v>1.73</v>
@@ -1990,7 +2002,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AQ5">
         <v>1.57</v>
@@ -2196,10 +2208,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ6">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2405,7 +2417,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ7">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2530,7 +2542,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q8">
         <v>2.39</v>
@@ -2814,7 +2826,7 @@
         <v>3</v>
       </c>
       <c r="AP9">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AQ9">
         <v>1.57</v>
@@ -2942,7 +2954,7 @@
         <v>85</v>
       </c>
       <c r="P10" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q10">
         <v>4.3</v>
@@ -3020,7 +3032,7 @@
         <v>1</v>
       </c>
       <c r="AP10">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AQ10">
         <v>1.14</v>
@@ -3148,7 +3160,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q11">
         <v>2.8</v>
@@ -3435,7 +3447,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ12">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3560,7 +3572,7 @@
         <v>85</v>
       </c>
       <c r="P13" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q13">
         <v>2.43</v>
@@ -3766,7 +3778,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q14">
         <v>3.9</v>
@@ -3844,10 +3856,10 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AQ14">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR14">
         <v>1.15</v>
@@ -4050,7 +4062,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ15">
         <v>1</v>
@@ -4178,7 +4190,7 @@
         <v>85</v>
       </c>
       <c r="P16" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q16">
         <v>3.18</v>
@@ -4384,7 +4396,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q17">
         <v>3</v>
@@ -4668,7 +4680,7 @@
         <v>2</v>
       </c>
       <c r="AP18">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AQ18">
         <v>1.73</v>
@@ -4796,7 +4808,7 @@
         <v>95</v>
       </c>
       <c r="P19" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q19">
         <v>2.71</v>
@@ -5002,7 +5014,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q20">
         <v>3.5</v>
@@ -5286,10 +5298,10 @@
         <v>0.5</v>
       </c>
       <c r="AP21">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AQ21">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR21">
         <v>1.02</v>
@@ -5414,7 +5426,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q22">
         <v>5</v>
@@ -5492,7 +5504,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ22">
         <v>2.14</v>
@@ -5698,10 +5710,10 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AQ23">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AR23">
         <v>1.93</v>
@@ -5826,7 +5838,7 @@
         <v>99</v>
       </c>
       <c r="P24" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q24">
         <v>3</v>
@@ -6319,7 +6331,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ26">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR26">
         <v>0</v>
@@ -6444,7 +6456,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q27">
         <v>2.25</v>
@@ -6650,7 +6662,7 @@
         <v>101</v>
       </c>
       <c r="P28" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q28">
         <v>4</v>
@@ -6856,7 +6868,7 @@
         <v>102</v>
       </c>
       <c r="P29" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q29">
         <v>2.2</v>
@@ -7062,7 +7074,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q30">
         <v>3.75</v>
@@ -7140,10 +7152,10 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AQ30">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR30">
         <v>1.22</v>
@@ -7268,7 +7280,7 @@
         <v>104</v>
       </c>
       <c r="P31" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q31">
         <v>3.25</v>
@@ -7680,7 +7692,7 @@
         <v>91</v>
       </c>
       <c r="P33" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q33">
         <v>2.63</v>
@@ -7758,7 +7770,7 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AQ33">
         <v>2.43</v>
@@ -7886,7 +7898,7 @@
         <v>85</v>
       </c>
       <c r="P34" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q34">
         <v>3.8</v>
@@ -7964,7 +7976,7 @@
         <v>2</v>
       </c>
       <c r="AP34">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AQ34">
         <v>1.14</v>
@@ -8092,7 +8104,7 @@
         <v>106</v>
       </c>
       <c r="P35" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q35">
         <v>2.8</v>
@@ -8173,7 +8185,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ35">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR35">
         <v>1.05</v>
@@ -8710,7 +8722,7 @@
         <v>85</v>
       </c>
       <c r="P38" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q38">
         <v>5</v>
@@ -8916,7 +8928,7 @@
         <v>85</v>
       </c>
       <c r="P39" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q39">
         <v>3.1</v>
@@ -9328,7 +9340,7 @@
         <v>110</v>
       </c>
       <c r="P41" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q41">
         <v>3.25</v>
@@ -9409,7 +9421,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ41">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR41">
         <v>1.52</v>
@@ -9534,7 +9546,7 @@
         <v>111</v>
       </c>
       <c r="P42" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q42">
         <v>2.5</v>
@@ -9818,7 +9830,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ43">
         <v>1.13</v>
@@ -9946,7 +9958,7 @@
         <v>113</v>
       </c>
       <c r="P44" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q44">
         <v>3.4</v>
@@ -10027,7 +10039,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ44">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR44">
         <v>1.43</v>
@@ -10152,7 +10164,7 @@
         <v>113</v>
       </c>
       <c r="P45" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q45">
         <v>3.75</v>
@@ -10358,7 +10370,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q46">
         <v>3.75</v>
@@ -10564,7 +10576,7 @@
         <v>85</v>
       </c>
       <c r="P47" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q47">
         <v>3</v>
@@ -10848,7 +10860,7 @@
         <v>0.67</v>
       </c>
       <c r="AP48">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AQ48">
         <v>1</v>
@@ -10976,7 +10988,7 @@
         <v>116</v>
       </c>
       <c r="P49" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -11057,7 +11069,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ49">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AR49">
         <v>1.58</v>
@@ -11260,7 +11272,7 @@
         <v>0</v>
       </c>
       <c r="AP50">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AQ50">
         <v>1.13</v>
@@ -11388,7 +11400,7 @@
         <v>85</v>
       </c>
       <c r="P51" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q51">
         <v>2.25</v>
@@ -11672,7 +11684,7 @@
         <v>0</v>
       </c>
       <c r="AP52">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AQ52">
         <v>0.38</v>
@@ -11881,7 +11893,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ53">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR53">
         <v>1.75</v>
@@ -12084,10 +12096,10 @@
         <v>2</v>
       </c>
       <c r="AP54">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ54">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR54">
         <v>1.1</v>
@@ -12212,7 +12224,7 @@
         <v>119</v>
       </c>
       <c r="P55" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q55">
         <v>5</v>
@@ -12290,7 +12302,7 @@
         <v>2</v>
       </c>
       <c r="AP55">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AQ55">
         <v>2.43</v>
@@ -12624,7 +12636,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q57">
         <v>3.75</v>
@@ -12830,7 +12842,7 @@
         <v>121</v>
       </c>
       <c r="P58" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q58">
         <v>2.3</v>
@@ -13036,7 +13048,7 @@
         <v>85</v>
       </c>
       <c r="P59" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q59">
         <v>3.2</v>
@@ -13114,7 +13126,7 @@
         <v>0.88</v>
       </c>
       <c r="AP59">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AQ59">
         <v>1</v>
@@ -13448,7 +13460,7 @@
         <v>123</v>
       </c>
       <c r="P61" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q61">
         <v>4</v>
@@ -13654,7 +13666,7 @@
         <v>124</v>
       </c>
       <c r="P62" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q62">
         <v>2.3</v>
@@ -13860,7 +13872,7 @@
         <v>85</v>
       </c>
       <c r="P63" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q63">
         <v>3.2</v>
@@ -14066,7 +14078,7 @@
         <v>125</v>
       </c>
       <c r="P64" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q64">
         <v>2.5</v>
@@ -14147,7 +14159,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ64">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR64">
         <v>1.63</v>
@@ -14272,7 +14284,7 @@
         <v>126</v>
       </c>
       <c r="P65" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q65">
         <v>4</v>
@@ -14350,10 +14362,10 @@
         <v>0.5</v>
       </c>
       <c r="AP65">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ65">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AR65">
         <v>1.07</v>
@@ -14478,7 +14490,7 @@
         <v>127</v>
       </c>
       <c r="P66" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q66">
         <v>3</v>
@@ -14762,7 +14774,7 @@
         <v>0.8</v>
       </c>
       <c r="AP67">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AQ67">
         <v>0.88</v>
@@ -14890,7 +14902,7 @@
         <v>129</v>
       </c>
       <c r="P68" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q68">
         <v>5</v>
@@ -15174,7 +15186,7 @@
         <v>1.75</v>
       </c>
       <c r="AP69">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AQ69">
         <v>1.14</v>
@@ -15383,7 +15395,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ70">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR70">
         <v>1.72</v>
@@ -15508,7 +15520,7 @@
         <v>132</v>
       </c>
       <c r="P71" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q71">
         <v>2.63</v>
@@ -15795,7 +15807,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ72">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR72">
         <v>1.67</v>
@@ -15920,7 +15932,7 @@
         <v>85</v>
       </c>
       <c r="P73" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q73">
         <v>3.6</v>
@@ -16001,7 +16013,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ73">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR73">
         <v>1.77</v>
@@ -16126,7 +16138,7 @@
         <v>85</v>
       </c>
       <c r="P74" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q74">
         <v>4.33</v>
@@ -16332,7 +16344,7 @@
         <v>134</v>
       </c>
       <c r="P75" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q75">
         <v>1.91</v>
@@ -16538,7 +16550,7 @@
         <v>135</v>
       </c>
       <c r="P76" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q76">
         <v>2.63</v>
@@ -16744,7 +16756,7 @@
         <v>85</v>
       </c>
       <c r="P77" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q77">
         <v>4.5</v>
@@ -17156,7 +17168,7 @@
         <v>137</v>
       </c>
       <c r="P79" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q79">
         <v>3.6</v>
@@ -17237,7 +17249,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ79">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR79">
         <v>1.7</v>
@@ -17443,7 +17455,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ80">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR80">
         <v>1.42</v>
@@ -17646,7 +17658,7 @@
         <v>1</v>
       </c>
       <c r="AP81">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AQ81">
         <v>1.13</v>
@@ -17774,7 +17786,7 @@
         <v>140</v>
       </c>
       <c r="P82" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q82">
         <v>3.75</v>
@@ -17980,7 +17992,7 @@
         <v>85</v>
       </c>
       <c r="P83" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q83">
         <v>7.5</v>
@@ -18058,7 +18070,7 @@
         <v>2.25</v>
       </c>
       <c r="AP83">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AQ83">
         <v>2.14</v>
@@ -18186,7 +18198,7 @@
         <v>141</v>
       </c>
       <c r="P84" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q84">
         <v>2.38</v>
@@ -18392,7 +18404,7 @@
         <v>142</v>
       </c>
       <c r="P85" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q85">
         <v>3.75</v>
@@ -18473,7 +18485,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ85">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AR85">
         <v>1.63</v>
@@ -18598,7 +18610,7 @@
         <v>85</v>
       </c>
       <c r="P86" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q86">
         <v>4.2</v>
@@ -18679,7 +18691,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ86">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AR86">
         <v>1.42</v>
@@ -19088,7 +19100,7 @@
         <v>2.5</v>
       </c>
       <c r="AP88">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ88">
         <v>2.43</v>
@@ -19216,7 +19228,7 @@
         <v>143</v>
       </c>
       <c r="P89" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q89">
         <v>2.62</v>
@@ -19422,7 +19434,7 @@
         <v>144</v>
       </c>
       <c r="P90" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q90">
         <v>3.1</v>
@@ -19503,7 +19515,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ90">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR90">
         <v>1.82</v>
@@ -19706,7 +19718,7 @@
         <v>1.9</v>
       </c>
       <c r="AP91">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AQ91">
         <v>1.73</v>
@@ -19834,7 +19846,7 @@
         <v>146</v>
       </c>
       <c r="P92" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20040,7 +20052,7 @@
         <v>147</v>
       </c>
       <c r="P93" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q93">
         <v>2.62</v>
@@ -20246,7 +20258,7 @@
         <v>148</v>
       </c>
       <c r="P94" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q94">
         <v>2.4</v>
@@ -20327,7 +20339,7 @@
         <v>2</v>
       </c>
       <c r="AQ94">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR94">
         <v>1.56</v>
@@ -20452,7 +20464,7 @@
         <v>149</v>
       </c>
       <c r="P95" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q95">
         <v>3.1</v>
@@ -20736,7 +20748,7 @@
         <v>1</v>
       </c>
       <c r="AP96">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AQ96">
         <v>1.13</v>
@@ -21070,7 +21082,7 @@
         <v>152</v>
       </c>
       <c r="P98" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q98">
         <v>2.3</v>
@@ -21151,7 +21163,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ98">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR98">
         <v>1.85</v>
@@ -21276,7 +21288,7 @@
         <v>153</v>
       </c>
       <c r="P99" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q99">
         <v>6.5</v>
@@ -21354,7 +21366,7 @@
         <v>2.4</v>
       </c>
       <c r="AP99">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AQ99">
         <v>2.14</v>
@@ -21482,7 +21494,7 @@
         <v>154</v>
       </c>
       <c r="P100" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q100">
         <v>4.33</v>
@@ -21560,7 +21572,7 @@
         <v>1.33</v>
       </c>
       <c r="AP100">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ100">
         <v>1.57</v>
@@ -21688,7 +21700,7 @@
         <v>85</v>
       </c>
       <c r="P101" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q101">
         <v>3.88</v>
@@ -21769,7 +21781,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ101">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR101">
         <v>1.52</v>
@@ -21894,7 +21906,7 @@
         <v>85</v>
       </c>
       <c r="P102" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q102">
         <v>2.79</v>
@@ -21975,7 +21987,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ102">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR102">
         <v>1.78</v>
@@ -22100,7 +22112,7 @@
         <v>85</v>
       </c>
       <c r="P103" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q103">
         <v>2.14</v>
@@ -22387,7 +22399,7 @@
         <v>2</v>
       </c>
       <c r="AQ104">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AR104">
         <v>1.56</v>
@@ -22590,10 +22602,10 @@
         <v>1.57</v>
       </c>
       <c r="AP105">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AQ105">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR105">
         <v>1.75</v>
@@ -22924,7 +22936,7 @@
         <v>85</v>
       </c>
       <c r="P107" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q107">
         <v>2.13</v>
@@ -23130,7 +23142,7 @@
         <v>157</v>
       </c>
       <c r="P108" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q108">
         <v>3.38</v>
@@ -23211,7 +23223,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ108">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AR108">
         <v>1.44</v>
@@ -24160,7 +24172,7 @@
         <v>159</v>
       </c>
       <c r="P113" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q113">
         <v>3.4</v>
@@ -24317,6 +24329,830 @@
       </c>
       <c r="BP113">
         <v>1.19</v>
+      </c>
+    </row>
+    <row r="114" spans="1:68">
+      <c r="A114" s="1">
+        <v>113</v>
+      </c>
+      <c r="B114">
+        <v>7813933</v>
+      </c>
+      <c r="C114" t="s">
+        <v>68</v>
+      </c>
+      <c r="D114" t="s">
+        <v>69</v>
+      </c>
+      <c r="E114" s="2">
+        <v>45829.29166666666</v>
+      </c>
+      <c r="F114">
+        <v>17</v>
+      </c>
+      <c r="G114" t="s">
+        <v>70</v>
+      </c>
+      <c r="H114" t="s">
+        <v>77</v>
+      </c>
+      <c r="I114">
+        <v>1</v>
+      </c>
+      <c r="J114">
+        <v>0</v>
+      </c>
+      <c r="K114">
+        <v>1</v>
+      </c>
+      <c r="L114">
+        <v>2</v>
+      </c>
+      <c r="M114">
+        <v>0</v>
+      </c>
+      <c r="N114">
+        <v>2</v>
+      </c>
+      <c r="O114" t="s">
+        <v>160</v>
+      </c>
+      <c r="P114" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q114">
+        <v>1.79</v>
+      </c>
+      <c r="R114">
+        <v>2.62</v>
+      </c>
+      <c r="S114">
+        <v>7.92</v>
+      </c>
+      <c r="T114">
+        <v>1.32</v>
+      </c>
+      <c r="U114">
+        <v>3.31</v>
+      </c>
+      <c r="V114">
+        <v>2.55</v>
+      </c>
+      <c r="W114">
+        <v>1.5</v>
+      </c>
+      <c r="X114">
+        <v>5.95</v>
+      </c>
+      <c r="Y114">
+        <v>1.07</v>
+      </c>
+      <c r="Z114">
+        <v>1.38</v>
+      </c>
+      <c r="AA114">
+        <v>4.3</v>
+      </c>
+      <c r="AB114">
+        <v>6.2</v>
+      </c>
+      <c r="AC114">
+        <v>1.02</v>
+      </c>
+      <c r="AD114">
+        <v>10</v>
+      </c>
+      <c r="AE114">
+        <v>1.22</v>
+      </c>
+      <c r="AF114">
+        <v>3.8</v>
+      </c>
+      <c r="AG114">
+        <v>1.78</v>
+      </c>
+      <c r="AH114">
+        <v>1.92</v>
+      </c>
+      <c r="AI114">
+        <v>1.95</v>
+      </c>
+      <c r="AJ114">
+        <v>1.81</v>
+      </c>
+      <c r="AK114">
+        <v>1.04</v>
+      </c>
+      <c r="AL114">
+        <v>1.14</v>
+      </c>
+      <c r="AM114">
+        <v>3.02</v>
+      </c>
+      <c r="AN114">
+        <v>2.78</v>
+      </c>
+      <c r="AO114">
+        <v>0.5</v>
+      </c>
+      <c r="AP114">
+        <v>2.8</v>
+      </c>
+      <c r="AQ114">
+        <v>0.44</v>
+      </c>
+      <c r="AR114">
+        <v>1.71</v>
+      </c>
+      <c r="AS114">
+        <v>1.07</v>
+      </c>
+      <c r="AT114">
+        <v>2.78</v>
+      </c>
+      <c r="AU114">
+        <v>5</v>
+      </c>
+      <c r="AV114">
+        <v>0</v>
+      </c>
+      <c r="AW114">
+        <v>5</v>
+      </c>
+      <c r="AX114">
+        <v>8</v>
+      </c>
+      <c r="AY114">
+        <v>10</v>
+      </c>
+      <c r="AZ114">
+        <v>8</v>
+      </c>
+      <c r="BA114">
+        <v>2</v>
+      </c>
+      <c r="BB114">
+        <v>1</v>
+      </c>
+      <c r="BC114">
+        <v>3</v>
+      </c>
+      <c r="BD114">
+        <v>1.35</v>
+      </c>
+      <c r="BE114">
+        <v>8.6</v>
+      </c>
+      <c r="BF114">
+        <v>3.84</v>
+      </c>
+      <c r="BG114">
+        <v>1.48</v>
+      </c>
+      <c r="BH114">
+        <v>2.58</v>
+      </c>
+      <c r="BI114">
+        <v>1.84</v>
+      </c>
+      <c r="BJ114">
+        <v>1.95</v>
+      </c>
+      <c r="BK114">
+        <v>2.36</v>
+      </c>
+      <c r="BL114">
+        <v>1.56</v>
+      </c>
+      <c r="BM114">
+        <v>3.2</v>
+      </c>
+      <c r="BN114">
+        <v>1.3</v>
+      </c>
+      <c r="BO114">
+        <v>4.1</v>
+      </c>
+      <c r="BP114">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="115" spans="1:68">
+      <c r="A115" s="1">
+        <v>114</v>
+      </c>
+      <c r="B115">
+        <v>7813934</v>
+      </c>
+      <c r="C115" t="s">
+        <v>68</v>
+      </c>
+      <c r="D115" t="s">
+        <v>69</v>
+      </c>
+      <c r="E115" s="2">
+        <v>45829.29166666666</v>
+      </c>
+      <c r="F115">
+        <v>17</v>
+      </c>
+      <c r="G115" t="s">
+        <v>71</v>
+      </c>
+      <c r="H115" t="s">
+        <v>75</v>
+      </c>
+      <c r="I115">
+        <v>1</v>
+      </c>
+      <c r="J115">
+        <v>1</v>
+      </c>
+      <c r="K115">
+        <v>2</v>
+      </c>
+      <c r="L115">
+        <v>4</v>
+      </c>
+      <c r="M115">
+        <v>2</v>
+      </c>
+      <c r="N115">
+        <v>6</v>
+      </c>
+      <c r="O115" t="s">
+        <v>161</v>
+      </c>
+      <c r="P115" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q115">
+        <v>4.85</v>
+      </c>
+      <c r="R115">
+        <v>2.2</v>
+      </c>
+      <c r="S115">
+        <v>2.19</v>
+      </c>
+      <c r="T115">
+        <v>1.33</v>
+      </c>
+      <c r="U115">
+        <v>3.04</v>
+      </c>
+      <c r="V115">
+        <v>2.65</v>
+      </c>
+      <c r="W115">
+        <v>1.42</v>
+      </c>
+      <c r="X115">
+        <v>6.5</v>
+      </c>
+      <c r="Y115">
+        <v>1.05</v>
+      </c>
+      <c r="Z115">
+        <v>4.33</v>
+      </c>
+      <c r="AA115">
+        <v>3.72</v>
+      </c>
+      <c r="AB115">
+        <v>1.61</v>
+      </c>
+      <c r="AC115">
+        <v>1.01</v>
+      </c>
+      <c r="AD115">
+        <v>11</v>
+      </c>
+      <c r="AE115">
+        <v>1.21</v>
+      </c>
+      <c r="AF115">
+        <v>3.58</v>
+      </c>
+      <c r="AG115">
+        <v>1.77</v>
+      </c>
+      <c r="AH115">
+        <v>1.93</v>
+      </c>
+      <c r="AI115">
+        <v>1.74</v>
+      </c>
+      <c r="AJ115">
+        <v>1.93</v>
+      </c>
+      <c r="AK115">
+        <v>2.09</v>
+      </c>
+      <c r="AL115">
+        <v>1.22</v>
+      </c>
+      <c r="AM115">
+        <v>1.15</v>
+      </c>
+      <c r="AN115">
+        <v>0.88</v>
+      </c>
+      <c r="AO115">
+        <v>1.57</v>
+      </c>
+      <c r="AP115">
+        <v>1.11</v>
+      </c>
+      <c r="AQ115">
+        <v>1.38</v>
+      </c>
+      <c r="AR115">
+        <v>1.19</v>
+      </c>
+      <c r="AS115">
+        <v>1.24</v>
+      </c>
+      <c r="AT115">
+        <v>2.43</v>
+      </c>
+      <c r="AU115">
+        <v>7</v>
+      </c>
+      <c r="AV115">
+        <v>7</v>
+      </c>
+      <c r="AW115">
+        <v>5</v>
+      </c>
+      <c r="AX115">
+        <v>10</v>
+      </c>
+      <c r="AY115">
+        <v>12</v>
+      </c>
+      <c r="AZ115">
+        <v>17</v>
+      </c>
+      <c r="BA115">
+        <v>3</v>
+      </c>
+      <c r="BB115">
+        <v>5</v>
+      </c>
+      <c r="BC115">
+        <v>8</v>
+      </c>
+      <c r="BD115">
+        <v>2.73</v>
+      </c>
+      <c r="BE115">
+        <v>6.25</v>
+      </c>
+      <c r="BF115">
+        <v>1.69</v>
+      </c>
+      <c r="BG115">
+        <v>1.37</v>
+      </c>
+      <c r="BH115">
+        <v>2.85</v>
+      </c>
+      <c r="BI115">
+        <v>1.72</v>
+      </c>
+      <c r="BJ115">
+        <v>2.09</v>
+      </c>
+      <c r="BK115">
+        <v>2.17</v>
+      </c>
+      <c r="BL115">
+        <v>1.68</v>
+      </c>
+      <c r="BM115">
+        <v>3</v>
+      </c>
+      <c r="BN115">
+        <v>1.34</v>
+      </c>
+      <c r="BO115">
+        <v>3.68</v>
+      </c>
+      <c r="BP115">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="116" spans="1:68">
+      <c r="A116" s="1">
+        <v>115</v>
+      </c>
+      <c r="B116">
+        <v>7813935</v>
+      </c>
+      <c r="C116" t="s">
+        <v>68</v>
+      </c>
+      <c r="D116" t="s">
+        <v>69</v>
+      </c>
+      <c r="E116" s="2">
+        <v>45829.29166666666</v>
+      </c>
+      <c r="F116">
+        <v>17</v>
+      </c>
+      <c r="G116" t="s">
+        <v>73</v>
+      </c>
+      <c r="H116" t="s">
+        <v>76</v>
+      </c>
+      <c r="I116">
+        <v>0</v>
+      </c>
+      <c r="J116">
+        <v>0</v>
+      </c>
+      <c r="K116">
+        <v>0</v>
+      </c>
+      <c r="L116">
+        <v>0</v>
+      </c>
+      <c r="M116">
+        <v>1</v>
+      </c>
+      <c r="N116">
+        <v>1</v>
+      </c>
+      <c r="O116" t="s">
+        <v>85</v>
+      </c>
+      <c r="P116" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q116">
+        <v>4.56</v>
+      </c>
+      <c r="R116">
+        <v>2.18</v>
+      </c>
+      <c r="S116">
+        <v>2.6</v>
+      </c>
+      <c r="T116">
+        <v>1.42</v>
+      </c>
+      <c r="U116">
+        <v>2.83</v>
+      </c>
+      <c r="V116">
+        <v>3.1</v>
+      </c>
+      <c r="W116">
+        <v>1.36</v>
+      </c>
+      <c r="X116">
+        <v>7.4</v>
+      </c>
+      <c r="Y116">
+        <v>1.03</v>
+      </c>
+      <c r="Z116">
+        <v>3.58</v>
+      </c>
+      <c r="AA116">
+        <v>3.29</v>
+      </c>
+      <c r="AB116">
+        <v>1.86</v>
+      </c>
+      <c r="AC116">
+        <v>1.04</v>
+      </c>
+      <c r="AD116">
+        <v>8.5</v>
+      </c>
+      <c r="AE116">
+        <v>1.33</v>
+      </c>
+      <c r="AF116">
+        <v>3</v>
+      </c>
+      <c r="AG116">
+        <v>1.95</v>
+      </c>
+      <c r="AH116">
+        <v>1.75</v>
+      </c>
+      <c r="AI116">
+        <v>1.83</v>
+      </c>
+      <c r="AJ116">
+        <v>1.93</v>
+      </c>
+      <c r="AK116">
+        <v>1.78</v>
+      </c>
+      <c r="AL116">
+        <v>1.26</v>
+      </c>
+      <c r="AM116">
+        <v>1.22</v>
+      </c>
+      <c r="AN116">
+        <v>0.88</v>
+      </c>
+      <c r="AO116">
+        <v>1.38</v>
+      </c>
+      <c r="AP116">
+        <v>0.78</v>
+      </c>
+      <c r="AQ116">
+        <v>1.56</v>
+      </c>
+      <c r="AR116">
+        <v>1.3</v>
+      </c>
+      <c r="AS116">
+        <v>1.47</v>
+      </c>
+      <c r="AT116">
+        <v>2.77</v>
+      </c>
+      <c r="AU116">
+        <v>2</v>
+      </c>
+      <c r="AV116">
+        <v>2</v>
+      </c>
+      <c r="AW116">
+        <v>1</v>
+      </c>
+      <c r="AX116">
+        <v>5</v>
+      </c>
+      <c r="AY116">
+        <v>3</v>
+      </c>
+      <c r="AZ116">
+        <v>7</v>
+      </c>
+      <c r="BA116">
+        <v>3</v>
+      </c>
+      <c r="BB116">
+        <v>5</v>
+      </c>
+      <c r="BC116">
+        <v>8</v>
+      </c>
+      <c r="BD116">
+        <v>2.79</v>
+      </c>
+      <c r="BE116">
+        <v>6.1</v>
+      </c>
+      <c r="BF116">
+        <v>1.68</v>
+      </c>
+      <c r="BG116">
+        <v>1.58</v>
+      </c>
+      <c r="BH116">
+        <v>2.33</v>
+      </c>
+      <c r="BI116">
+        <v>1.98</v>
+      </c>
+      <c r="BJ116">
+        <v>1.82</v>
+      </c>
+      <c r="BK116">
+        <v>2.55</v>
+      </c>
+      <c r="BL116">
+        <v>1.5</v>
+      </c>
+      <c r="BM116">
+        <v>3.58</v>
+      </c>
+      <c r="BN116">
+        <v>1.21</v>
+      </c>
+      <c r="BO116">
+        <v>4.4</v>
+      </c>
+      <c r="BP116">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="117" spans="1:68">
+      <c r="A117" s="1">
+        <v>116</v>
+      </c>
+      <c r="B117">
+        <v>7813936</v>
+      </c>
+      <c r="C117" t="s">
+        <v>68</v>
+      </c>
+      <c r="D117" t="s">
+        <v>69</v>
+      </c>
+      <c r="E117" s="2">
+        <v>45829.29166666666</v>
+      </c>
+      <c r="F117">
+        <v>17</v>
+      </c>
+      <c r="G117" t="s">
+        <v>74</v>
+      </c>
+      <c r="H117" t="s">
+        <v>81</v>
+      </c>
+      <c r="I117">
+        <v>0</v>
+      </c>
+      <c r="J117">
+        <v>1</v>
+      </c>
+      <c r="K117">
+        <v>1</v>
+      </c>
+      <c r="L117">
+        <v>0</v>
+      </c>
+      <c r="M117">
+        <v>2</v>
+      </c>
+      <c r="N117">
+        <v>2</v>
+      </c>
+      <c r="O117" t="s">
+        <v>85</v>
+      </c>
+      <c r="P117" t="s">
+        <v>224</v>
+      </c>
+      <c r="Q117">
+        <v>3.64</v>
+      </c>
+      <c r="R117">
+        <v>2.01</v>
+      </c>
+      <c r="S117">
+        <v>2.9</v>
+      </c>
+      <c r="T117">
+        <v>1.4</v>
+      </c>
+      <c r="U117">
+        <v>2.72</v>
+      </c>
+      <c r="V117">
+        <v>2.98</v>
+      </c>
+      <c r="W117">
+        <v>1.34</v>
+      </c>
+      <c r="X117">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y117">
+        <v>1.02</v>
+      </c>
+      <c r="Z117">
+        <v>3.06</v>
+      </c>
+      <c r="AA117">
+        <v>3.11</v>
+      </c>
+      <c r="AB117">
+        <v>2.12</v>
+      </c>
+      <c r="AC117">
+        <v>1</v>
+      </c>
+      <c r="AD117">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE117">
+        <v>1.27</v>
+      </c>
+      <c r="AF117">
+        <v>3.14</v>
+      </c>
+      <c r="AG117">
+        <v>1.95</v>
+      </c>
+      <c r="AH117">
+        <v>1.7</v>
+      </c>
+      <c r="AI117">
+        <v>1.76</v>
+      </c>
+      <c r="AJ117">
+        <v>1.91</v>
+      </c>
+      <c r="AK117">
+        <v>1.56</v>
+      </c>
+      <c r="AL117">
+        <v>1.28</v>
+      </c>
+      <c r="AM117">
+        <v>1.33</v>
+      </c>
+      <c r="AN117">
+        <v>1.5</v>
+      </c>
+      <c r="AO117">
+        <v>1.13</v>
+      </c>
+      <c r="AP117">
+        <v>1.33</v>
+      </c>
+      <c r="AQ117">
+        <v>1.33</v>
+      </c>
+      <c r="AR117">
+        <v>1.09</v>
+      </c>
+      <c r="AS117">
+        <v>1.39</v>
+      </c>
+      <c r="AT117">
+        <v>2.48</v>
+      </c>
+      <c r="AU117">
+        <v>2</v>
+      </c>
+      <c r="AV117">
+        <v>7</v>
+      </c>
+      <c r="AW117">
+        <v>4</v>
+      </c>
+      <c r="AX117">
+        <v>2</v>
+      </c>
+      <c r="AY117">
+        <v>6</v>
+      </c>
+      <c r="AZ117">
+        <v>9</v>
+      </c>
+      <c r="BA117">
+        <v>7</v>
+      </c>
+      <c r="BB117">
+        <v>6</v>
+      </c>
+      <c r="BC117">
+        <v>13</v>
+      </c>
+      <c r="BD117">
+        <v>2.27</v>
+      </c>
+      <c r="BE117">
+        <v>6</v>
+      </c>
+      <c r="BF117">
+        <v>1.96</v>
+      </c>
+      <c r="BG117">
+        <v>1.49</v>
+      </c>
+      <c r="BH117">
+        <v>2.55</v>
+      </c>
+      <c r="BI117">
+        <v>1.84</v>
+      </c>
+      <c r="BJ117">
+        <v>1.95</v>
+      </c>
+      <c r="BK117">
+        <v>2.34</v>
+      </c>
+      <c r="BL117">
+        <v>1.58</v>
+      </c>
+      <c r="BM117">
+        <v>3.2</v>
+      </c>
+      <c r="BN117">
+        <v>1.3</v>
+      </c>
+      <c r="BO117">
+        <v>4.1</v>
+      </c>
+      <c r="BP117">
+        <v>1.18</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="228">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -502,6 +502,9 @@
     <t>['17', '59', '63', '84']</t>
   </si>
   <si>
+    <t>['6', '72']</t>
+  </si>
+  <si>
     <t>['1', '6']</t>
   </si>
   <si>
@@ -689,6 +692,12 @@
   </si>
   <si>
     <t>['5', '76']</t>
+  </si>
+  <si>
+    <t>['65', '9002']</t>
+  </si>
+  <si>
+    <t>['12', '82']</t>
   </si>
 </sst>
 </file>
@@ -1050,7 +1059,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP117"/>
+  <dimension ref="A1:BP120"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1512,7 +1521,7 @@
         <v>85</v>
       </c>
       <c r="P3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q3">
         <v>3.8</v>
@@ -1796,10 +1805,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ4">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2005,7 +2014,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ5">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2542,7 +2551,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q8">
         <v>2.39</v>
@@ -2829,7 +2838,7 @@
         <v>2.8</v>
       </c>
       <c r="AQ9">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AR9">
         <v>2.58</v>
@@ -2954,7 +2963,7 @@
         <v>85</v>
       </c>
       <c r="P10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q10">
         <v>4.3</v>
@@ -3035,7 +3044,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ10">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR10">
         <v>0.82</v>
@@ -3160,7 +3169,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q11">
         <v>2.8</v>
@@ -3572,7 +3581,7 @@
         <v>85</v>
       </c>
       <c r="P13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q13">
         <v>2.43</v>
@@ -3650,7 +3659,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ13">
         <v>0.88</v>
@@ -3778,7 +3787,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q14">
         <v>3.9</v>
@@ -4190,7 +4199,7 @@
         <v>85</v>
       </c>
       <c r="P16" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q16">
         <v>3.18</v>
@@ -4396,7 +4405,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q17">
         <v>3</v>
@@ -4808,7 +4817,7 @@
         <v>95</v>
       </c>
       <c r="P19" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q19">
         <v>2.71</v>
@@ -5014,7 +5023,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q20">
         <v>3.5</v>
@@ -5095,7 +5104,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ20">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AR20">
         <v>1.06</v>
@@ -5426,7 +5435,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q22">
         <v>5</v>
@@ -5838,7 +5847,7 @@
         <v>99</v>
       </c>
       <c r="P24" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q24">
         <v>3</v>
@@ -6456,7 +6465,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q27">
         <v>2.25</v>
@@ -6534,7 +6543,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ27">
         <v>0.38</v>
@@ -6662,7 +6671,7 @@
         <v>101</v>
       </c>
       <c r="P28" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q28">
         <v>4</v>
@@ -6740,7 +6749,7 @@
         <v>2.33</v>
       </c>
       <c r="AP28">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AQ28">
         <v>1.73</v>
@@ -6868,7 +6877,7 @@
         <v>102</v>
       </c>
       <c r="P29" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q29">
         <v>2.2</v>
@@ -7074,7 +7083,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q30">
         <v>3.75</v>
@@ -7280,7 +7289,7 @@
         <v>104</v>
       </c>
       <c r="P31" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q31">
         <v>3.25</v>
@@ -7564,7 +7573,7 @@
         <v>1</v>
       </c>
       <c r="AP32">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AQ32">
         <v>1</v>
@@ -7692,7 +7701,7 @@
         <v>91</v>
       </c>
       <c r="P33" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q33">
         <v>2.63</v>
@@ -7898,7 +7907,7 @@
         <v>85</v>
       </c>
       <c r="P34" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q34">
         <v>3.8</v>
@@ -7979,7 +7988,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ34">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR34">
         <v>0.98</v>
@@ -8104,7 +8113,7 @@
         <v>106</v>
       </c>
       <c r="P35" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q35">
         <v>2.8</v>
@@ -8722,7 +8731,7 @@
         <v>85</v>
       </c>
       <c r="P38" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q38">
         <v>5</v>
@@ -8928,7 +8937,7 @@
         <v>85</v>
       </c>
       <c r="P39" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q39">
         <v>3.1</v>
@@ -9006,7 +9015,7 @@
         <v>1.6</v>
       </c>
       <c r="AP39">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ39">
         <v>1.73</v>
@@ -9340,7 +9349,7 @@
         <v>110</v>
       </c>
       <c r="P41" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q41">
         <v>3.25</v>
@@ -9546,7 +9555,7 @@
         <v>111</v>
       </c>
       <c r="P42" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q42">
         <v>2.5</v>
@@ -9958,7 +9967,7 @@
         <v>113</v>
       </c>
       <c r="P44" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q44">
         <v>3.4</v>
@@ -10164,7 +10173,7 @@
         <v>113</v>
       </c>
       <c r="P45" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q45">
         <v>3.75</v>
@@ -10370,7 +10379,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q46">
         <v>3.75</v>
@@ -10451,7 +10460,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ46">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AR46">
         <v>1.33</v>
@@ -10576,7 +10585,7 @@
         <v>85</v>
       </c>
       <c r="P47" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q47">
         <v>3</v>
@@ -10654,7 +10663,7 @@
         <v>1</v>
       </c>
       <c r="AP47">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AQ47">
         <v>1.13</v>
@@ -10988,7 +10997,7 @@
         <v>116</v>
       </c>
       <c r="P49" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -11066,7 +11075,7 @@
         <v>0</v>
       </c>
       <c r="AP49">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ49">
         <v>1.38</v>
@@ -11400,7 +11409,7 @@
         <v>85</v>
       </c>
       <c r="P51" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q51">
         <v>2.25</v>
@@ -12224,7 +12233,7 @@
         <v>119</v>
       </c>
       <c r="P55" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q55">
         <v>5</v>
@@ -12636,7 +12645,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q57">
         <v>3.75</v>
@@ -12714,10 +12723,10 @@
         <v>2.33</v>
       </c>
       <c r="AP57">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AQ57">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR57">
         <v>1.79</v>
@@ -12842,7 +12851,7 @@
         <v>121</v>
       </c>
       <c r="P58" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q58">
         <v>2.3</v>
@@ -13048,7 +13057,7 @@
         <v>85</v>
       </c>
       <c r="P59" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q59">
         <v>3.2</v>
@@ -13460,7 +13469,7 @@
         <v>123</v>
       </c>
       <c r="P61" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q61">
         <v>4</v>
@@ -13666,7 +13675,7 @@
         <v>124</v>
       </c>
       <c r="P62" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q62">
         <v>2.3</v>
@@ -13872,7 +13881,7 @@
         <v>85</v>
       </c>
       <c r="P63" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q63">
         <v>3.2</v>
@@ -14078,7 +14087,7 @@
         <v>125</v>
       </c>
       <c r="P64" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q64">
         <v>2.5</v>
@@ -14156,7 +14165,7 @@
         <v>0.33</v>
       </c>
       <c r="AP64">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ64">
         <v>0.44</v>
@@ -14284,7 +14293,7 @@
         <v>126</v>
       </c>
       <c r="P65" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q65">
         <v>4</v>
@@ -14490,7 +14499,7 @@
         <v>127</v>
       </c>
       <c r="P66" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q66">
         <v>3</v>
@@ -14902,7 +14911,7 @@
         <v>129</v>
       </c>
       <c r="P68" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q68">
         <v>5</v>
@@ -14983,7 +14992,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ68">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AR68">
         <v>0</v>
@@ -15189,7 +15198,7 @@
         <v>2.8</v>
       </c>
       <c r="AQ69">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR69">
         <v>1.6</v>
@@ -15392,7 +15401,7 @@
         <v>0.6</v>
       </c>
       <c r="AP70">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ70">
         <v>1.33</v>
@@ -15520,7 +15529,7 @@
         <v>132</v>
       </c>
       <c r="P71" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q71">
         <v>2.63</v>
@@ -15932,7 +15941,7 @@
         <v>85</v>
       </c>
       <c r="P73" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q73">
         <v>3.6</v>
@@ -16010,7 +16019,7 @@
         <v>1.75</v>
       </c>
       <c r="AP73">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AQ73">
         <v>1.56</v>
@@ -16138,7 +16147,7 @@
         <v>85</v>
       </c>
       <c r="P74" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q74">
         <v>4.33</v>
@@ -16344,7 +16353,7 @@
         <v>134</v>
       </c>
       <c r="P75" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q75">
         <v>1.91</v>
@@ -16550,7 +16559,7 @@
         <v>135</v>
       </c>
       <c r="P76" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q76">
         <v>2.63</v>
@@ -16628,7 +16637,7 @@
         <v>1.25</v>
       </c>
       <c r="AP76">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ76">
         <v>1.13</v>
@@ -16756,7 +16765,7 @@
         <v>85</v>
       </c>
       <c r="P77" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q77">
         <v>4.5</v>
@@ -17168,7 +17177,7 @@
         <v>137</v>
       </c>
       <c r="P79" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q79">
         <v>3.6</v>
@@ -17246,7 +17255,7 @@
         <v>0.5</v>
       </c>
       <c r="AP79">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AQ79">
         <v>1.33</v>
@@ -17786,7 +17795,7 @@
         <v>140</v>
       </c>
       <c r="P82" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q82">
         <v>3.75</v>
@@ -17864,10 +17873,10 @@
         <v>1</v>
       </c>
       <c r="AP82">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ82">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AR82">
         <v>1.65</v>
@@ -17992,7 +18001,7 @@
         <v>85</v>
       </c>
       <c r="P83" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q83">
         <v>7.5</v>
@@ -18198,7 +18207,7 @@
         <v>141</v>
       </c>
       <c r="P84" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q84">
         <v>2.38</v>
@@ -18276,7 +18285,7 @@
         <v>1.11</v>
       </c>
       <c r="AP84">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ84">
         <v>1</v>
@@ -18404,7 +18413,7 @@
         <v>142</v>
       </c>
       <c r="P85" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q85">
         <v>3.75</v>
@@ -18610,7 +18619,7 @@
         <v>85</v>
       </c>
       <c r="P86" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q86">
         <v>4.2</v>
@@ -19228,7 +19237,7 @@
         <v>143</v>
       </c>
       <c r="P89" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q89">
         <v>2.62</v>
@@ -19306,7 +19315,7 @@
         <v>0</v>
       </c>
       <c r="AP89">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AQ89">
         <v>0.38</v>
@@ -19434,7 +19443,7 @@
         <v>144</v>
       </c>
       <c r="P90" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q90">
         <v>3.1</v>
@@ -19846,7 +19855,7 @@
         <v>146</v>
       </c>
       <c r="P92" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -19927,7 +19936,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ92">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR92">
         <v>1.86</v>
@@ -20052,7 +20061,7 @@
         <v>147</v>
       </c>
       <c r="P93" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q93">
         <v>2.62</v>
@@ -20258,7 +20267,7 @@
         <v>148</v>
       </c>
       <c r="P94" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q94">
         <v>2.4</v>
@@ -20336,7 +20345,7 @@
         <v>0.17</v>
       </c>
       <c r="AP94">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ94">
         <v>0.44</v>
@@ -20464,7 +20473,7 @@
         <v>149</v>
       </c>
       <c r="P95" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q95">
         <v>3.1</v>
@@ -20957,7 +20966,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ97">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR97">
         <v>1.82</v>
@@ -21082,7 +21091,7 @@
         <v>152</v>
       </c>
       <c r="P98" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q98">
         <v>2.3</v>
@@ -21288,7 +21297,7 @@
         <v>153</v>
       </c>
       <c r="P99" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q99">
         <v>6.5</v>
@@ -21494,7 +21503,7 @@
         <v>154</v>
       </c>
       <c r="P100" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q100">
         <v>4.33</v>
@@ -21575,7 +21584,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ100">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AR100">
         <v>1.06</v>
@@ -21700,7 +21709,7 @@
         <v>85</v>
       </c>
       <c r="P101" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q101">
         <v>3.88</v>
@@ -21906,7 +21915,7 @@
         <v>85</v>
       </c>
       <c r="P102" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q102">
         <v>2.79</v>
@@ -21984,7 +21993,7 @@
         <v>0.14</v>
       </c>
       <c r="AP102">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AQ102">
         <v>0.44</v>
@@ -22112,7 +22121,7 @@
         <v>85</v>
       </c>
       <c r="P103" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q103">
         <v>2.14</v>
@@ -22190,7 +22199,7 @@
         <v>0.83</v>
       </c>
       <c r="AP103">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ103">
         <v>1.13</v>
@@ -22396,7 +22405,7 @@
         <v>2</v>
       </c>
       <c r="AP104">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ104">
         <v>1.38</v>
@@ -22936,7 +22945,7 @@
         <v>85</v>
       </c>
       <c r="P107" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q107">
         <v>2.13</v>
@@ -23142,7 +23151,7 @@
         <v>157</v>
       </c>
       <c r="P108" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q108">
         <v>3.38</v>
@@ -23632,7 +23641,7 @@
         <v>2.33</v>
       </c>
       <c r="AP110">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ110">
         <v>2.43</v>
@@ -24172,7 +24181,7 @@
         <v>159</v>
       </c>
       <c r="P113" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q113">
         <v>3.4</v>
@@ -24584,7 +24593,7 @@
         <v>161</v>
       </c>
       <c r="P115" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q115">
         <v>4.85</v>
@@ -24996,7 +25005,7 @@
         <v>85</v>
       </c>
       <c r="P117" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q117">
         <v>3.64</v>
@@ -25152,6 +25161,624 @@
         <v>4.1</v>
       </c>
       <c r="BP117">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="118" spans="1:68">
+      <c r="A118" s="1">
+        <v>117</v>
+      </c>
+      <c r="B118">
+        <v>7813938</v>
+      </c>
+      <c r="C118" t="s">
+        <v>68</v>
+      </c>
+      <c r="D118" t="s">
+        <v>69</v>
+      </c>
+      <c r="E118" s="2">
+        <v>45830.29166666666</v>
+      </c>
+      <c r="F118">
+        <v>17</v>
+      </c>
+      <c r="G118" t="s">
+        <v>72</v>
+      </c>
+      <c r="H118" t="s">
+        <v>82</v>
+      </c>
+      <c r="I118">
+        <v>1</v>
+      </c>
+      <c r="J118">
+        <v>0</v>
+      </c>
+      <c r="K118">
+        <v>1</v>
+      </c>
+      <c r="L118">
+        <v>2</v>
+      </c>
+      <c r="M118">
+        <v>2</v>
+      </c>
+      <c r="N118">
+        <v>4</v>
+      </c>
+      <c r="O118" t="s">
+        <v>162</v>
+      </c>
+      <c r="P118" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q118">
+        <v>2.15</v>
+      </c>
+      <c r="R118">
+        <v>2.2</v>
+      </c>
+      <c r="S118">
+        <v>5.5</v>
+      </c>
+      <c r="T118">
+        <v>1.4</v>
+      </c>
+      <c r="U118">
+        <v>2.88</v>
+      </c>
+      <c r="V118">
+        <v>2.88</v>
+      </c>
+      <c r="W118">
+        <v>1.4</v>
+      </c>
+      <c r="X118">
+        <v>8</v>
+      </c>
+      <c r="Y118">
+        <v>1.08</v>
+      </c>
+      <c r="Z118">
+        <v>1.57</v>
+      </c>
+      <c r="AA118">
+        <v>3.65</v>
+      </c>
+      <c r="AB118">
+        <v>4.8</v>
+      </c>
+      <c r="AC118">
+        <v>1.01</v>
+      </c>
+      <c r="AD118">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AE118">
+        <v>1.28</v>
+      </c>
+      <c r="AF118">
+        <v>3.08</v>
+      </c>
+      <c r="AG118">
+        <v>1.95</v>
+      </c>
+      <c r="AH118">
+        <v>1.75</v>
+      </c>
+      <c r="AI118">
+        <v>1.95</v>
+      </c>
+      <c r="AJ118">
+        <v>1.8</v>
+      </c>
+      <c r="AK118">
+        <v>1.18</v>
+      </c>
+      <c r="AL118">
+        <v>1.3</v>
+      </c>
+      <c r="AM118">
+        <v>2.1</v>
+      </c>
+      <c r="AN118">
+        <v>1.22</v>
+      </c>
+      <c r="AO118">
+        <v>1</v>
+      </c>
+      <c r="AP118">
+        <v>1.2</v>
+      </c>
+      <c r="AQ118">
+        <v>1</v>
+      </c>
+      <c r="AR118">
+        <v>1.65</v>
+      </c>
+      <c r="AS118">
+        <v>1.25</v>
+      </c>
+      <c r="AT118">
+        <v>2.9</v>
+      </c>
+      <c r="AU118">
+        <v>7</v>
+      </c>
+      <c r="AV118">
+        <v>5</v>
+      </c>
+      <c r="AW118">
+        <v>3</v>
+      </c>
+      <c r="AX118">
+        <v>2</v>
+      </c>
+      <c r="AY118">
+        <v>10</v>
+      </c>
+      <c r="AZ118">
+        <v>7</v>
+      </c>
+      <c r="BA118">
+        <v>6</v>
+      </c>
+      <c r="BB118">
+        <v>3</v>
+      </c>
+      <c r="BC118">
+        <v>9</v>
+      </c>
+      <c r="BD118">
+        <v>1.44</v>
+      </c>
+      <c r="BE118">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF118">
+        <v>3.32</v>
+      </c>
+      <c r="BG118">
+        <v>1.53</v>
+      </c>
+      <c r="BH118">
+        <v>2.45</v>
+      </c>
+      <c r="BI118">
+        <v>1.92</v>
+      </c>
+      <c r="BJ118">
+        <v>1.88</v>
+      </c>
+      <c r="BK118">
+        <v>2.48</v>
+      </c>
+      <c r="BL118">
+        <v>1.52</v>
+      </c>
+      <c r="BM118">
+        <v>3.28</v>
+      </c>
+      <c r="BN118">
+        <v>1.25</v>
+      </c>
+      <c r="BO118">
+        <v>4.3</v>
+      </c>
+      <c r="BP118">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="119" spans="1:68">
+      <c r="A119" s="1">
+        <v>118</v>
+      </c>
+      <c r="B119">
+        <v>7813939</v>
+      </c>
+      <c r="C119" t="s">
+        <v>68</v>
+      </c>
+      <c r="D119" t="s">
+        <v>69</v>
+      </c>
+      <c r="E119" s="2">
+        <v>45830.29166666666</v>
+      </c>
+      <c r="F119">
+        <v>17</v>
+      </c>
+      <c r="G119" t="s">
+        <v>80</v>
+      </c>
+      <c r="H119" t="s">
+        <v>79</v>
+      </c>
+      <c r="I119">
+        <v>0</v>
+      </c>
+      <c r="J119">
+        <v>1</v>
+      </c>
+      <c r="K119">
+        <v>1</v>
+      </c>
+      <c r="L119">
+        <v>0</v>
+      </c>
+      <c r="M119">
+        <v>2</v>
+      </c>
+      <c r="N119">
+        <v>2</v>
+      </c>
+      <c r="O119" t="s">
+        <v>85</v>
+      </c>
+      <c r="P119" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q119">
+        <v>4.4</v>
+      </c>
+      <c r="R119">
+        <v>2.4</v>
+      </c>
+      <c r="S119">
+        <v>2.2</v>
+      </c>
+      <c r="T119">
+        <v>1.29</v>
+      </c>
+      <c r="U119">
+        <v>3.5</v>
+      </c>
+      <c r="V119">
+        <v>2.3</v>
+      </c>
+      <c r="W119">
+        <v>1.55</v>
+      </c>
+      <c r="X119">
+        <v>5.5</v>
+      </c>
+      <c r="Y119">
+        <v>1.14</v>
+      </c>
+      <c r="Z119">
+        <v>3.98</v>
+      </c>
+      <c r="AA119">
+        <v>3.93</v>
+      </c>
+      <c r="AB119">
+        <v>1.63</v>
+      </c>
+      <c r="AC119">
+        <v>1.01</v>
+      </c>
+      <c r="AD119">
+        <v>13</v>
+      </c>
+      <c r="AE119">
+        <v>1.14</v>
+      </c>
+      <c r="AF119">
+        <v>4.4</v>
+      </c>
+      <c r="AG119">
+        <v>1.57</v>
+      </c>
+      <c r="AH119">
+        <v>2.15</v>
+      </c>
+      <c r="AI119">
+        <v>1.62</v>
+      </c>
+      <c r="AJ119">
+        <v>2.25</v>
+      </c>
+      <c r="AK119">
+        <v>2.3</v>
+      </c>
+      <c r="AL119">
+        <v>1.22</v>
+      </c>
+      <c r="AM119">
+        <v>1.17</v>
+      </c>
+      <c r="AN119">
+        <v>1.25</v>
+      </c>
+      <c r="AO119">
+        <v>1.57</v>
+      </c>
+      <c r="AP119">
+        <v>1.11</v>
+      </c>
+      <c r="AQ119">
+        <v>1.75</v>
+      </c>
+      <c r="AR119">
+        <v>1.71</v>
+      </c>
+      <c r="AS119">
+        <v>1.7</v>
+      </c>
+      <c r="AT119">
+        <v>3.41</v>
+      </c>
+      <c r="AU119">
+        <v>5</v>
+      </c>
+      <c r="AV119">
+        <v>8</v>
+      </c>
+      <c r="AW119">
+        <v>6</v>
+      </c>
+      <c r="AX119">
+        <v>6</v>
+      </c>
+      <c r="AY119">
+        <v>11</v>
+      </c>
+      <c r="AZ119">
+        <v>14</v>
+      </c>
+      <c r="BA119">
+        <v>7</v>
+      </c>
+      <c r="BB119">
+        <v>5</v>
+      </c>
+      <c r="BC119">
+        <v>12</v>
+      </c>
+      <c r="BD119">
+        <v>2.76</v>
+      </c>
+      <c r="BE119">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF119">
+        <v>1.58</v>
+      </c>
+      <c r="BG119">
+        <v>1.32</v>
+      </c>
+      <c r="BH119">
+        <v>2.88</v>
+      </c>
+      <c r="BI119">
+        <v>1.6</v>
+      </c>
+      <c r="BJ119">
+        <v>2.26</v>
+      </c>
+      <c r="BK119">
+        <v>1.99</v>
+      </c>
+      <c r="BL119">
+        <v>1.81</v>
+      </c>
+      <c r="BM119">
+        <v>2.53</v>
+      </c>
+      <c r="BN119">
+        <v>1.49</v>
+      </c>
+      <c r="BO119">
+        <v>3.78</v>
+      </c>
+      <c r="BP119">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="120" spans="1:68">
+      <c r="A120" s="1">
+        <v>119</v>
+      </c>
+      <c r="B120">
+        <v>7813937</v>
+      </c>
+      <c r="C120" t="s">
+        <v>68</v>
+      </c>
+      <c r="D120" t="s">
+        <v>69</v>
+      </c>
+      <c r="E120" s="2">
+        <v>45830.29166666666</v>
+      </c>
+      <c r="F120">
+        <v>17</v>
+      </c>
+      <c r="G120" t="s">
+        <v>83</v>
+      </c>
+      <c r="H120" t="s">
+        <v>78</v>
+      </c>
+      <c r="I120">
+        <v>0</v>
+      </c>
+      <c r="J120">
+        <v>0</v>
+      </c>
+      <c r="K120">
+        <v>0</v>
+      </c>
+      <c r="L120">
+        <v>0</v>
+      </c>
+      <c r="M120">
+        <v>0</v>
+      </c>
+      <c r="N120">
+        <v>0</v>
+      </c>
+      <c r="O120" t="s">
+        <v>85</v>
+      </c>
+      <c r="P120" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q120">
+        <v>2.9</v>
+      </c>
+      <c r="R120">
+        <v>2.1</v>
+      </c>
+      <c r="S120">
+        <v>3.6</v>
+      </c>
+      <c r="T120">
+        <v>1.4</v>
+      </c>
+      <c r="U120">
+        <v>2.8</v>
+      </c>
+      <c r="V120">
+        <v>3</v>
+      </c>
+      <c r="W120">
+        <v>1.36</v>
+      </c>
+      <c r="X120">
+        <v>8.5</v>
+      </c>
+      <c r="Y120">
+        <v>1.07</v>
+      </c>
+      <c r="Z120">
+        <v>2.22</v>
+      </c>
+      <c r="AA120">
+        <v>3.1</v>
+      </c>
+      <c r="AB120">
+        <v>2.88</v>
+      </c>
+      <c r="AC120">
+        <v>1.05</v>
+      </c>
+      <c r="AD120">
+        <v>8</v>
+      </c>
+      <c r="AE120">
+        <v>1.3</v>
+      </c>
+      <c r="AF120">
+        <v>2.97</v>
+      </c>
+      <c r="AG120">
+        <v>2</v>
+      </c>
+      <c r="AH120">
+        <v>1.65</v>
+      </c>
+      <c r="AI120">
+        <v>1.83</v>
+      </c>
+      <c r="AJ120">
+        <v>1.91</v>
+      </c>
+      <c r="AK120">
+        <v>1.36</v>
+      </c>
+      <c r="AL120">
+        <v>1.35</v>
+      </c>
+      <c r="AM120">
+        <v>1.57</v>
+      </c>
+      <c r="AN120">
+        <v>2</v>
+      </c>
+      <c r="AO120">
+        <v>1.14</v>
+      </c>
+      <c r="AP120">
+        <v>1.83</v>
+      </c>
+      <c r="AQ120">
+        <v>1.13</v>
+      </c>
+      <c r="AR120">
+        <v>1.62</v>
+      </c>
+      <c r="AS120">
+        <v>1.31</v>
+      </c>
+      <c r="AT120">
+        <v>2.93</v>
+      </c>
+      <c r="AU120">
+        <v>3</v>
+      </c>
+      <c r="AV120">
+        <v>0</v>
+      </c>
+      <c r="AW120">
+        <v>4</v>
+      </c>
+      <c r="AX120">
+        <v>2</v>
+      </c>
+      <c r="AY120">
+        <v>7</v>
+      </c>
+      <c r="AZ120">
+        <v>2</v>
+      </c>
+      <c r="BA120">
+        <v>1</v>
+      </c>
+      <c r="BB120">
+        <v>4</v>
+      </c>
+      <c r="BC120">
+        <v>5</v>
+      </c>
+      <c r="BD120">
+        <v>2.1</v>
+      </c>
+      <c r="BE120">
+        <v>5.95</v>
+      </c>
+      <c r="BF120">
+        <v>2.11</v>
+      </c>
+      <c r="BG120">
+        <v>1.48</v>
+      </c>
+      <c r="BH120">
+        <v>2.58</v>
+      </c>
+      <c r="BI120">
+        <v>1.82</v>
+      </c>
+      <c r="BJ120">
+        <v>1.98</v>
+      </c>
+      <c r="BK120">
+        <v>2.3</v>
+      </c>
+      <c r="BL120">
+        <v>1.58</v>
+      </c>
+      <c r="BM120">
+        <v>3.08</v>
+      </c>
+      <c r="BN120">
+        <v>1.28</v>
+      </c>
+      <c r="BO120">
+        <v>4.1</v>
+      </c>
+      <c r="BP120">
         <v>1.18</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
@@ -673,10 +673,10 @@
     <t>['15', '26']</t>
   </si>
   <si>
-    <t>['41']</t>
+    <t>['62', '9005']</t>
   </si>
   <si>
-    <t>['62', '9005']</t>
+    <t>['66']</t>
   </si>
   <si>
     <t>['9003']</t>
@@ -688,7 +688,7 @@
     <t>['15', '49']</t>
   </si>
   <si>
-    <t>['41', '57']</t>
+    <t>['41', '56']</t>
   </si>
   <si>
     <t>['5', '76']</t>
@@ -21915,7 +21915,7 @@
         <v>85</v>
       </c>
       <c r="P102" t="s">
-        <v>219</v>
+        <v>149</v>
       </c>
       <c r="Q102">
         <v>2.79</v>
@@ -22121,7 +22121,7 @@
         <v>85</v>
       </c>
       <c r="P103" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q103">
         <v>2.14</v>
@@ -22327,7 +22327,7 @@
         <v>150</v>
       </c>
       <c r="P104" t="s">
-        <v>159</v>
+        <v>220</v>
       </c>
       <c r="Q104">
         <v>3.4</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="232">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -505,6 +505,15 @@
     <t>['6', '72']</t>
   </si>
   <si>
+    <t>['27']</t>
+  </si>
+  <si>
+    <t>['35', '45']</t>
+  </si>
+  <si>
+    <t>['9005']</t>
+  </si>
+  <si>
     <t>['1', '6']</t>
   </si>
   <si>
@@ -698,6 +707,9 @@
   </si>
   <si>
     <t>['12', '82']</t>
+  </si>
+  <si>
+    <t>['69']</t>
   </si>
 </sst>
 </file>
@@ -1059,7 +1071,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP120"/>
+  <dimension ref="A1:BP124"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1396,7 +1408,7 @@
         <v>2.8</v>
       </c>
       <c r="AQ2">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1521,7 +1533,7 @@
         <v>85</v>
       </c>
       <c r="P3" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="Q3">
         <v>3.8</v>
@@ -2011,7 +2023,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AQ5">
         <v>1.75</v>
@@ -2551,7 +2563,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="Q8">
         <v>2.39</v>
@@ -2629,7 +2641,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ8">
         <v>1</v>
@@ -2963,7 +2975,7 @@
         <v>85</v>
       </c>
       <c r="P10" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="Q10">
         <v>4.3</v>
@@ -3041,7 +3053,7 @@
         <v>1</v>
       </c>
       <c r="AP10">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AQ10">
         <v>1.13</v>
@@ -3169,7 +3181,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="Q11">
         <v>2.8</v>
@@ -3453,7 +3465,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AQ12">
         <v>1.33</v>
@@ -3581,7 +3593,7 @@
         <v>85</v>
       </c>
       <c r="P13" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="Q13">
         <v>2.43</v>
@@ -3662,7 +3674,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ13">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR13">
         <v>1.4</v>
@@ -3787,7 +3799,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="Q14">
         <v>3.9</v>
@@ -4199,7 +4211,7 @@
         <v>85</v>
       </c>
       <c r="P16" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="Q16">
         <v>3.18</v>
@@ -4277,7 +4289,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ16">
         <v>2.43</v>
@@ -4405,7 +4417,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="Q17">
         <v>3</v>
@@ -4483,10 +4495,10 @@
         <v>1.5</v>
       </c>
       <c r="AP17">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AQ17">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR17">
         <v>1.52</v>
@@ -4689,7 +4701,7 @@
         <v>2</v>
       </c>
       <c r="AP18">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AQ18">
         <v>1.73</v>
@@ -4817,7 +4829,7 @@
         <v>95</v>
       </c>
       <c r="P19" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="Q19">
         <v>2.71</v>
@@ -5023,7 +5035,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="Q20">
         <v>3.5</v>
@@ -5435,7 +5447,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="Q22">
         <v>5</v>
@@ -5722,7 +5734,7 @@
         <v>2.8</v>
       </c>
       <c r="AQ23">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR23">
         <v>1.93</v>
@@ -5847,7 +5859,7 @@
         <v>99</v>
       </c>
       <c r="P24" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="Q24">
         <v>3</v>
@@ -5925,7 +5937,7 @@
         <v>1.33</v>
       </c>
       <c r="AP24">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AQ24">
         <v>1</v>
@@ -6134,7 +6146,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ25">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR25">
         <v>2.07</v>
@@ -6465,7 +6477,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="Q27">
         <v>2.25</v>
@@ -6546,7 +6558,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ27">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="AR27">
         <v>1.42</v>
@@ -6671,7 +6683,7 @@
         <v>101</v>
       </c>
       <c r="P28" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Q28">
         <v>4</v>
@@ -6877,7 +6889,7 @@
         <v>102</v>
       </c>
       <c r="P29" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Q29">
         <v>2.2</v>
@@ -6955,7 +6967,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ29">
         <v>1.13</v>
@@ -7083,7 +7095,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Q30">
         <v>3.75</v>
@@ -7161,7 +7173,7 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AQ30">
         <v>0.44</v>
@@ -7289,7 +7301,7 @@
         <v>104</v>
       </c>
       <c r="P31" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="Q31">
         <v>3.25</v>
@@ -7701,7 +7713,7 @@
         <v>91</v>
       </c>
       <c r="P33" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="Q33">
         <v>2.63</v>
@@ -7907,7 +7919,7 @@
         <v>85</v>
       </c>
       <c r="P34" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="Q34">
         <v>3.8</v>
@@ -8113,7 +8125,7 @@
         <v>106</v>
       </c>
       <c r="P35" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q35">
         <v>2.8</v>
@@ -8397,10 +8409,10 @@
         <v>1</v>
       </c>
       <c r="AP36">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ36">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR36">
         <v>0</v>
@@ -8606,7 +8618,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ37">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="AR37">
         <v>1.11</v>
@@ -8731,7 +8743,7 @@
         <v>85</v>
       </c>
       <c r="P38" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="Q38">
         <v>5</v>
@@ -8809,7 +8821,7 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AQ38">
         <v>2.14</v>
@@ -8937,7 +8949,7 @@
         <v>85</v>
       </c>
       <c r="P39" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="Q39">
         <v>3.1</v>
@@ -9224,7 +9236,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ40">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR40">
         <v>1.62</v>
@@ -9349,7 +9361,7 @@
         <v>110</v>
       </c>
       <c r="P41" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Q41">
         <v>3.25</v>
@@ -9555,7 +9567,7 @@
         <v>111</v>
       </c>
       <c r="P42" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="Q42">
         <v>2.5</v>
@@ -9633,7 +9645,7 @@
         <v>0.8</v>
       </c>
       <c r="AP42">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ42">
         <v>1</v>
@@ -9967,7 +9979,7 @@
         <v>113</v>
       </c>
       <c r="P44" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q44">
         <v>3.4</v>
@@ -10173,7 +10185,7 @@
         <v>113</v>
       </c>
       <c r="P45" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q45">
         <v>3.75</v>
@@ -10251,7 +10263,7 @@
         <v>1.83</v>
       </c>
       <c r="AP45">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AQ45">
         <v>1.73</v>
@@ -10379,7 +10391,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q46">
         <v>3.75</v>
@@ -10457,7 +10469,7 @@
         <v>1</v>
       </c>
       <c r="AP46">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ46">
         <v>1.75</v>
@@ -10585,7 +10597,7 @@
         <v>85</v>
       </c>
       <c r="P47" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q47">
         <v>3</v>
@@ -10666,7 +10678,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ47">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR47">
         <v>1.74</v>
@@ -10997,7 +11009,7 @@
         <v>116</v>
       </c>
       <c r="P49" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -11078,7 +11090,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ49">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR49">
         <v>1.58</v>
@@ -11409,7 +11421,7 @@
         <v>85</v>
       </c>
       <c r="P51" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q51">
         <v>2.25</v>
@@ -11696,7 +11708,7 @@
         <v>2.8</v>
       </c>
       <c r="AQ52">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="AR52">
         <v>1.66</v>
@@ -12233,7 +12245,7 @@
         <v>119</v>
       </c>
       <c r="P55" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q55">
         <v>5</v>
@@ -12311,7 +12323,7 @@
         <v>2</v>
       </c>
       <c r="AP55">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AQ55">
         <v>2.43</v>
@@ -12517,7 +12529,7 @@
         <v>2</v>
       </c>
       <c r="AP56">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ56">
         <v>1.73</v>
@@ -12645,7 +12657,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q57">
         <v>3.75</v>
@@ -12851,7 +12863,7 @@
         <v>121</v>
       </c>
       <c r="P58" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="Q58">
         <v>2.3</v>
@@ -12932,7 +12944,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ58">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR58">
         <v>1.31</v>
@@ -13057,7 +13069,7 @@
         <v>85</v>
       </c>
       <c r="P59" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q59">
         <v>3.2</v>
@@ -13341,7 +13353,7 @@
         <v>1</v>
       </c>
       <c r="AP60">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ60">
         <v>1.13</v>
@@ -13469,7 +13481,7 @@
         <v>123</v>
       </c>
       <c r="P61" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q61">
         <v>4</v>
@@ -13547,7 +13559,7 @@
         <v>1.5</v>
       </c>
       <c r="AP61">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ61">
         <v>2.14</v>
@@ -13675,7 +13687,7 @@
         <v>124</v>
       </c>
       <c r="P62" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q62">
         <v>2.3</v>
@@ -13756,7 +13768,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ62">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR62">
         <v>1.79</v>
@@ -13881,7 +13893,7 @@
         <v>85</v>
       </c>
       <c r="P63" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q63">
         <v>3.2</v>
@@ -14087,7 +14099,7 @@
         <v>125</v>
       </c>
       <c r="P64" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q64">
         <v>2.5</v>
@@ -14293,7 +14305,7 @@
         <v>126</v>
       </c>
       <c r="P65" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q65">
         <v>4</v>
@@ -14374,7 +14386,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ65">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR65">
         <v>1.07</v>
@@ -14499,7 +14511,7 @@
         <v>127</v>
       </c>
       <c r="P66" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q66">
         <v>3</v>
@@ -14577,7 +14589,7 @@
         <v>2</v>
       </c>
       <c r="AP66">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ66">
         <v>1.73</v>
@@ -14783,10 +14795,10 @@
         <v>0.8</v>
       </c>
       <c r="AP67">
+        <v>0.8</v>
+      </c>
+      <c r="AQ67">
         <v>0.78</v>
-      </c>
-      <c r="AQ67">
-        <v>0.88</v>
       </c>
       <c r="AR67">
         <v>1.4</v>
@@ -14911,7 +14923,7 @@
         <v>129</v>
       </c>
       <c r="P68" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q68">
         <v>5</v>
@@ -15529,7 +15541,7 @@
         <v>132</v>
       </c>
       <c r="P71" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q71">
         <v>2.63</v>
@@ -15607,10 +15619,10 @@
         <v>0</v>
       </c>
       <c r="AP71">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AQ71">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="AR71">
         <v>1.45</v>
@@ -15941,7 +15953,7 @@
         <v>85</v>
       </c>
       <c r="P73" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q73">
         <v>3.6</v>
@@ -16147,7 +16159,7 @@
         <v>85</v>
       </c>
       <c r="P74" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q74">
         <v>4.33</v>
@@ -16225,7 +16237,7 @@
         <v>2</v>
       </c>
       <c r="AP74">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ74">
         <v>2.14</v>
@@ -16353,7 +16365,7 @@
         <v>134</v>
       </c>
       <c r="P75" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="Q75">
         <v>1.91</v>
@@ -16559,7 +16571,7 @@
         <v>135</v>
       </c>
       <c r="P76" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q76">
         <v>2.63</v>
@@ -16640,7 +16652,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ76">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR76">
         <v>0</v>
@@ -16765,7 +16777,7 @@
         <v>85</v>
       </c>
       <c r="P77" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q77">
         <v>4.5</v>
@@ -17052,7 +17064,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ78">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="AR78">
         <v>1.79</v>
@@ -17177,7 +17189,7 @@
         <v>137</v>
       </c>
       <c r="P79" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q79">
         <v>3.6</v>
@@ -17461,7 +17473,7 @@
         <v>0.2</v>
       </c>
       <c r="AP80">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ80">
         <v>0.44</v>
@@ -17670,7 +17682,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ81">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR81">
         <v>1.17</v>
@@ -17795,7 +17807,7 @@
         <v>140</v>
       </c>
       <c r="P82" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q82">
         <v>3.75</v>
@@ -18001,7 +18013,7 @@
         <v>85</v>
       </c>
       <c r="P83" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q83">
         <v>7.5</v>
@@ -18079,7 +18091,7 @@
         <v>2.25</v>
       </c>
       <c r="AP83">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AQ83">
         <v>2.14</v>
@@ -18207,7 +18219,7 @@
         <v>141</v>
       </c>
       <c r="P84" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="Q84">
         <v>2.38</v>
@@ -18413,7 +18425,7 @@
         <v>142</v>
       </c>
       <c r="P85" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q85">
         <v>3.75</v>
@@ -18494,7 +18506,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ85">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR85">
         <v>1.63</v>
@@ -18619,7 +18631,7 @@
         <v>85</v>
       </c>
       <c r="P86" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q86">
         <v>4.2</v>
@@ -18697,10 +18709,10 @@
         <v>1.75</v>
       </c>
       <c r="AP86">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AQ86">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR86">
         <v>1.42</v>
@@ -19237,7 +19249,7 @@
         <v>143</v>
       </c>
       <c r="P89" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="Q89">
         <v>2.62</v>
@@ -19318,7 +19330,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ89">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="AR89">
         <v>1.79</v>
@@ -19443,7 +19455,7 @@
         <v>144</v>
       </c>
       <c r="P90" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q90">
         <v>3.1</v>
@@ -19521,7 +19533,7 @@
         <v>2</v>
       </c>
       <c r="AP90">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ90">
         <v>1.56</v>
@@ -19855,7 +19867,7 @@
         <v>146</v>
       </c>
       <c r="P92" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20061,7 +20073,7 @@
         <v>147</v>
       </c>
       <c r="P93" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q93">
         <v>2.62</v>
@@ -20267,7 +20279,7 @@
         <v>148</v>
       </c>
       <c r="P94" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q94">
         <v>2.4</v>
@@ -20473,7 +20485,7 @@
         <v>149</v>
       </c>
       <c r="P95" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q95">
         <v>3.1</v>
@@ -20554,7 +20566,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ95">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR95">
         <v>1.52</v>
@@ -20757,10 +20769,10 @@
         <v>1</v>
       </c>
       <c r="AP96">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AQ96">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR96">
         <v>1.3</v>
@@ -20963,7 +20975,7 @@
         <v>1.33</v>
       </c>
       <c r="AP97">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ97">
         <v>1.13</v>
@@ -21091,7 +21103,7 @@
         <v>152</v>
       </c>
       <c r="P98" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q98">
         <v>2.3</v>
@@ -21297,7 +21309,7 @@
         <v>153</v>
       </c>
       <c r="P99" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q99">
         <v>6.5</v>
@@ -21503,7 +21515,7 @@
         <v>154</v>
       </c>
       <c r="P100" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q100">
         <v>4.33</v>
@@ -21709,7 +21721,7 @@
         <v>85</v>
       </c>
       <c r="P101" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q101">
         <v>3.88</v>
@@ -22121,7 +22133,7 @@
         <v>85</v>
       </c>
       <c r="P103" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q103">
         <v>2.14</v>
@@ -22327,7 +22339,7 @@
         <v>150</v>
       </c>
       <c r="P104" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q104">
         <v>3.4</v>
@@ -22408,7 +22420,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ104">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR104">
         <v>1.56</v>
@@ -22820,7 +22832,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ106">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="AR106">
         <v>1.56</v>
@@ -22945,7 +22957,7 @@
         <v>85</v>
       </c>
       <c r="P107" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q107">
         <v>2.13</v>
@@ -23023,10 +23035,10 @@
         <v>0</v>
       </c>
       <c r="AP107">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ107">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="AR107">
         <v>1.82</v>
@@ -23151,7 +23163,7 @@
         <v>157</v>
       </c>
       <c r="P108" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q108">
         <v>3.38</v>
@@ -23229,10 +23241,10 @@
         <v>1.83</v>
       </c>
       <c r="AP108">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ108">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR108">
         <v>1.44</v>
@@ -23438,7 +23450,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ109">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR109">
         <v>1.41</v>
@@ -23847,7 +23859,7 @@
         <v>1.14</v>
       </c>
       <c r="AP111">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AQ111">
         <v>1.13</v>
@@ -24056,7 +24068,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ112">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR112">
         <v>1.55</v>
@@ -24181,7 +24193,7 @@
         <v>159</v>
       </c>
       <c r="P113" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q113">
         <v>3.4</v>
@@ -24593,7 +24605,7 @@
         <v>161</v>
       </c>
       <c r="P115" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q115">
         <v>4.85</v>
@@ -24674,7 +24686,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ115">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR115">
         <v>1.19</v>
@@ -24877,7 +24889,7 @@
         <v>1.38</v>
       </c>
       <c r="AP116">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AQ116">
         <v>1.56</v>
@@ -25005,7 +25017,7 @@
         <v>85</v>
       </c>
       <c r="P117" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q117">
         <v>3.64</v>
@@ -25211,7 +25223,7 @@
         <v>162</v>
       </c>
       <c r="P118" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q118">
         <v>2.15</v>
@@ -25417,7 +25429,7 @@
         <v>85</v>
       </c>
       <c r="P119" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q119">
         <v>4.4</v>
@@ -25779,6 +25791,830 @@
         <v>4.1</v>
       </c>
       <c r="BP120">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="121" spans="1:68">
+      <c r="A121" s="1">
+        <v>120</v>
+      </c>
+      <c r="B121">
+        <v>7813940</v>
+      </c>
+      <c r="C121" t="s">
+        <v>68</v>
+      </c>
+      <c r="D121" t="s">
+        <v>69</v>
+      </c>
+      <c r="E121" s="2">
+        <v>45836.29166666666</v>
+      </c>
+      <c r="F121">
+        <v>18</v>
+      </c>
+      <c r="G121" t="s">
+        <v>81</v>
+      </c>
+      <c r="H121" t="s">
+        <v>75</v>
+      </c>
+      <c r="I121">
+        <v>1</v>
+      </c>
+      <c r="J121">
+        <v>0</v>
+      </c>
+      <c r="K121">
+        <v>1</v>
+      </c>
+      <c r="L121">
+        <v>1</v>
+      </c>
+      <c r="M121">
+        <v>1</v>
+      </c>
+      <c r="N121">
+        <v>2</v>
+      </c>
+      <c r="O121" t="s">
+        <v>163</v>
+      </c>
+      <c r="P121" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q121">
+        <v>2.93</v>
+      </c>
+      <c r="R121">
+        <v>2.15</v>
+      </c>
+      <c r="S121">
+        <v>3.22</v>
+      </c>
+      <c r="T121">
+        <v>1.31</v>
+      </c>
+      <c r="U121">
+        <v>3.14</v>
+      </c>
+      <c r="V121">
+        <v>2.58</v>
+      </c>
+      <c r="W121">
+        <v>1.44</v>
+      </c>
+      <c r="X121">
+        <v>6.65</v>
+      </c>
+      <c r="Y121">
+        <v>1.05</v>
+      </c>
+      <c r="Z121">
+        <v>2.35</v>
+      </c>
+      <c r="AA121">
+        <v>3.2</v>
+      </c>
+      <c r="AB121">
+        <v>2.62</v>
+      </c>
+      <c r="AC121">
+        <v>1.01</v>
+      </c>
+      <c r="AD121">
+        <v>11</v>
+      </c>
+      <c r="AE121">
+        <v>1.18</v>
+      </c>
+      <c r="AF121">
+        <v>3.86</v>
+      </c>
+      <c r="AG121">
+        <v>1.81</v>
+      </c>
+      <c r="AH121">
+        <v>1.89</v>
+      </c>
+      <c r="AI121">
+        <v>1.59</v>
+      </c>
+      <c r="AJ121">
+        <v>2.15</v>
+      </c>
+      <c r="AK121">
+        <v>1.41</v>
+      </c>
+      <c r="AL121">
+        <v>1.26</v>
+      </c>
+      <c r="AM121">
+        <v>1.5</v>
+      </c>
+      <c r="AN121">
+        <v>1.5</v>
+      </c>
+      <c r="AO121">
+        <v>1.38</v>
+      </c>
+      <c r="AP121">
+        <v>1.44</v>
+      </c>
+      <c r="AQ121">
+        <v>1.33</v>
+      </c>
+      <c r="AR121">
+        <v>1.8</v>
+      </c>
+      <c r="AS121">
+        <v>1.35</v>
+      </c>
+      <c r="AT121">
+        <v>3.15</v>
+      </c>
+      <c r="AU121">
+        <v>5</v>
+      </c>
+      <c r="AV121">
+        <v>4</v>
+      </c>
+      <c r="AW121">
+        <v>4</v>
+      </c>
+      <c r="AX121">
+        <v>7</v>
+      </c>
+      <c r="AY121">
+        <v>9</v>
+      </c>
+      <c r="AZ121">
+        <v>11</v>
+      </c>
+      <c r="BA121">
+        <v>1</v>
+      </c>
+      <c r="BB121">
+        <v>0</v>
+      </c>
+      <c r="BC121">
+        <v>1</v>
+      </c>
+      <c r="BD121">
+        <v>1.92</v>
+      </c>
+      <c r="BE121">
+        <v>6</v>
+      </c>
+      <c r="BF121">
+        <v>2.32</v>
+      </c>
+      <c r="BG121">
+        <v>1.4</v>
+      </c>
+      <c r="BH121">
+        <v>2.56</v>
+      </c>
+      <c r="BI121">
+        <v>1.95</v>
+      </c>
+      <c r="BJ121">
+        <v>1.85</v>
+      </c>
+      <c r="BK121">
+        <v>2.26</v>
+      </c>
+      <c r="BL121">
+        <v>1.51</v>
+      </c>
+      <c r="BM121">
+        <v>3.08</v>
+      </c>
+      <c r="BN121">
+        <v>1.28</v>
+      </c>
+      <c r="BO121">
+        <v>3.95</v>
+      </c>
+      <c r="BP121">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="122" spans="1:68">
+      <c r="A122" s="1">
+        <v>121</v>
+      </c>
+      <c r="B122">
+        <v>7813941</v>
+      </c>
+      <c r="C122" t="s">
+        <v>68</v>
+      </c>
+      <c r="D122" t="s">
+        <v>69</v>
+      </c>
+      <c r="E122" s="2">
+        <v>45836.29166666666</v>
+      </c>
+      <c r="F122">
+        <v>18</v>
+      </c>
+      <c r="G122" t="s">
+        <v>76</v>
+      </c>
+      <c r="H122" t="s">
+        <v>80</v>
+      </c>
+      <c r="I122">
+        <v>2</v>
+      </c>
+      <c r="J122">
+        <v>0</v>
+      </c>
+      <c r="K122">
+        <v>2</v>
+      </c>
+      <c r="L122">
+        <v>2</v>
+      </c>
+      <c r="M122">
+        <v>0</v>
+      </c>
+      <c r="N122">
+        <v>2</v>
+      </c>
+      <c r="O122" t="s">
+        <v>164</v>
+      </c>
+      <c r="P122" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q122">
+        <v>2.24</v>
+      </c>
+      <c r="R122">
+        <v>2.23</v>
+      </c>
+      <c r="S122">
+        <v>4.78</v>
+      </c>
+      <c r="T122">
+        <v>1.3</v>
+      </c>
+      <c r="U122">
+        <v>3.2</v>
+      </c>
+      <c r="V122">
+        <v>2.55</v>
+      </c>
+      <c r="W122">
+        <v>1.45</v>
+      </c>
+      <c r="X122">
+        <v>6.4</v>
+      </c>
+      <c r="Y122">
+        <v>1.05</v>
+      </c>
+      <c r="Z122">
+        <v>1.75</v>
+      </c>
+      <c r="AA122">
+        <v>3.59</v>
+      </c>
+      <c r="AB122">
+        <v>3.71</v>
+      </c>
+      <c r="AC122">
+        <v>1.02</v>
+      </c>
+      <c r="AD122">
+        <v>10</v>
+      </c>
+      <c r="AE122">
+        <v>1.22</v>
+      </c>
+      <c r="AF122">
+        <v>3.8</v>
+      </c>
+      <c r="AG122">
+        <v>1.73</v>
+      </c>
+      <c r="AH122">
+        <v>1.95</v>
+      </c>
+      <c r="AI122">
+        <v>1.67</v>
+      </c>
+      <c r="AJ122">
+        <v>2.15</v>
+      </c>
+      <c r="AK122">
+        <v>1.16</v>
+      </c>
+      <c r="AL122">
+        <v>1.21</v>
+      </c>
+      <c r="AM122">
+        <v>2.04</v>
+      </c>
+      <c r="AN122">
+        <v>1.75</v>
+      </c>
+      <c r="AO122">
+        <v>0.88</v>
+      </c>
+      <c r="AP122">
+        <v>1.89</v>
+      </c>
+      <c r="AQ122">
+        <v>0.78</v>
+      </c>
+      <c r="AR122">
+        <v>1.52</v>
+      </c>
+      <c r="AS122">
+        <v>1.1</v>
+      </c>
+      <c r="AT122">
+        <v>2.62</v>
+      </c>
+      <c r="AU122">
+        <v>9</v>
+      </c>
+      <c r="AV122">
+        <v>0</v>
+      </c>
+      <c r="AW122">
+        <v>15</v>
+      </c>
+      <c r="AX122">
+        <v>7</v>
+      </c>
+      <c r="AY122">
+        <v>24</v>
+      </c>
+      <c r="AZ122">
+        <v>7</v>
+      </c>
+      <c r="BA122">
+        <v>6</v>
+      </c>
+      <c r="BB122">
+        <v>6</v>
+      </c>
+      <c r="BC122">
+        <v>12</v>
+      </c>
+      <c r="BD122">
+        <v>1.51</v>
+      </c>
+      <c r="BE122">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF122">
+        <v>3</v>
+      </c>
+      <c r="BG122">
+        <v>1.37</v>
+      </c>
+      <c r="BH122">
+        <v>2.66</v>
+      </c>
+      <c r="BI122">
+        <v>1.8</v>
+      </c>
+      <c r="BJ122">
+        <v>2</v>
+      </c>
+      <c r="BK122">
+        <v>2.15</v>
+      </c>
+      <c r="BL122">
+        <v>1.56</v>
+      </c>
+      <c r="BM122">
+        <v>2.88</v>
+      </c>
+      <c r="BN122">
+        <v>1.32</v>
+      </c>
+      <c r="BO122">
+        <v>3.8</v>
+      </c>
+      <c r="BP122">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="123" spans="1:68">
+      <c r="A123" s="1">
+        <v>122</v>
+      </c>
+      <c r="B123">
+        <v>7813942</v>
+      </c>
+      <c r="C123" t="s">
+        <v>68</v>
+      </c>
+      <c r="D123" t="s">
+        <v>69</v>
+      </c>
+      <c r="E123" s="2">
+        <v>45836.29166666666</v>
+      </c>
+      <c r="F123">
+        <v>18</v>
+      </c>
+      <c r="G123" t="s">
+        <v>73</v>
+      </c>
+      <c r="H123" t="s">
+        <v>71</v>
+      </c>
+      <c r="I123">
+        <v>0</v>
+      </c>
+      <c r="J123">
+        <v>0</v>
+      </c>
+      <c r="K123">
+        <v>0</v>
+      </c>
+      <c r="L123">
+        <v>0</v>
+      </c>
+      <c r="M123">
+        <v>0</v>
+      </c>
+      <c r="N123">
+        <v>0</v>
+      </c>
+      <c r="O123" t="s">
+        <v>85</v>
+      </c>
+      <c r="P123" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q123">
+        <v>3</v>
+      </c>
+      <c r="R123">
+        <v>1.97</v>
+      </c>
+      <c r="S123">
+        <v>3.62</v>
+      </c>
+      <c r="T123">
+        <v>1.42</v>
+      </c>
+      <c r="U123">
+        <v>2.65</v>
+      </c>
+      <c r="V123">
+        <v>3.04</v>
+      </c>
+      <c r="W123">
+        <v>1.33</v>
+      </c>
+      <c r="X123">
+        <v>8.5</v>
+      </c>
+      <c r="Y123">
+        <v>1.01</v>
+      </c>
+      <c r="Z123">
+        <v>2.38</v>
+      </c>
+      <c r="AA123">
+        <v>3.05</v>
+      </c>
+      <c r="AB123">
+        <v>2.69</v>
+      </c>
+      <c r="AC123">
+        <v>1.03</v>
+      </c>
+      <c r="AD123">
+        <v>9</v>
+      </c>
+      <c r="AE123">
+        <v>1.28</v>
+      </c>
+      <c r="AF123">
+        <v>3.05</v>
+      </c>
+      <c r="AG123">
+        <v>2</v>
+      </c>
+      <c r="AH123">
+        <v>1.72</v>
+      </c>
+      <c r="AI123">
+        <v>1.78</v>
+      </c>
+      <c r="AJ123">
+        <v>1.88</v>
+      </c>
+      <c r="AK123">
+        <v>1.34</v>
+      </c>
+      <c r="AL123">
+        <v>1.3</v>
+      </c>
+      <c r="AM123">
+        <v>1.52</v>
+      </c>
+      <c r="AN123">
+        <v>0.78</v>
+      </c>
+      <c r="AO123">
+        <v>0.38</v>
+      </c>
+      <c r="AP123">
+        <v>0.8</v>
+      </c>
+      <c r="AQ123">
+        <v>0.44</v>
+      </c>
+      <c r="AR123">
+        <v>1.21</v>
+      </c>
+      <c r="AS123">
+        <v>1.16</v>
+      </c>
+      <c r="AT123">
+        <v>2.37</v>
+      </c>
+      <c r="AU123">
+        <v>2</v>
+      </c>
+      <c r="AV123">
+        <v>4</v>
+      </c>
+      <c r="AW123">
+        <v>2</v>
+      </c>
+      <c r="AX123">
+        <v>5</v>
+      </c>
+      <c r="AY123">
+        <v>4</v>
+      </c>
+      <c r="AZ123">
+        <v>9</v>
+      </c>
+      <c r="BA123">
+        <v>1</v>
+      </c>
+      <c r="BB123">
+        <v>6</v>
+      </c>
+      <c r="BC123">
+        <v>7</v>
+      </c>
+      <c r="BD123">
+        <v>2.01</v>
+      </c>
+      <c r="BE123">
+        <v>5.9</v>
+      </c>
+      <c r="BF123">
+        <v>2.22</v>
+      </c>
+      <c r="BG123">
+        <v>1.51</v>
+      </c>
+      <c r="BH123">
+        <v>2.26</v>
+      </c>
+      <c r="BI123">
+        <v>1.9</v>
+      </c>
+      <c r="BJ123">
+        <v>1.9</v>
+      </c>
+      <c r="BK123">
+        <v>2.56</v>
+      </c>
+      <c r="BL123">
+        <v>1.4</v>
+      </c>
+      <c r="BM123">
+        <v>3.58</v>
+      </c>
+      <c r="BN123">
+        <v>1.21</v>
+      </c>
+      <c r="BO123">
+        <v>4.9</v>
+      </c>
+      <c r="BP123">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="124" spans="1:68">
+      <c r="A124" s="1">
+        <v>123</v>
+      </c>
+      <c r="B124">
+        <v>7813943</v>
+      </c>
+      <c r="C124" t="s">
+        <v>68</v>
+      </c>
+      <c r="D124" t="s">
+        <v>69</v>
+      </c>
+      <c r="E124" s="2">
+        <v>45836.29166666666</v>
+      </c>
+      <c r="F124">
+        <v>18</v>
+      </c>
+      <c r="G124" t="s">
+        <v>77</v>
+      </c>
+      <c r="H124" t="s">
+        <v>74</v>
+      </c>
+      <c r="I124">
+        <v>0</v>
+      </c>
+      <c r="J124">
+        <v>0</v>
+      </c>
+      <c r="K124">
+        <v>0</v>
+      </c>
+      <c r="L124">
+        <v>1</v>
+      </c>
+      <c r="M124">
+        <v>0</v>
+      </c>
+      <c r="N124">
+        <v>1</v>
+      </c>
+      <c r="O124" t="s">
+        <v>165</v>
+      </c>
+      <c r="P124" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q124">
+        <v>3.22</v>
+      </c>
+      <c r="R124">
+        <v>1.97</v>
+      </c>
+      <c r="S124">
+        <v>3.34</v>
+      </c>
+      <c r="T124">
+        <v>1.44</v>
+      </c>
+      <c r="U124">
+        <v>2.57</v>
+      </c>
+      <c r="V124">
+        <v>3.14</v>
+      </c>
+      <c r="W124">
+        <v>1.31</v>
+      </c>
+      <c r="X124">
+        <v>8.1</v>
+      </c>
+      <c r="Y124">
+        <v>1.02</v>
+      </c>
+      <c r="Z124">
+        <v>2.58</v>
+      </c>
+      <c r="AA124">
+        <v>3.09</v>
+      </c>
+      <c r="AB124">
+        <v>2.45</v>
+      </c>
+      <c r="AC124">
+        <v>1.02</v>
+      </c>
+      <c r="AD124">
+        <v>7.8</v>
+      </c>
+      <c r="AE124">
+        <v>1.34</v>
+      </c>
+      <c r="AF124">
+        <v>2.78</v>
+      </c>
+      <c r="AG124">
+        <v>1.97</v>
+      </c>
+      <c r="AH124">
+        <v>1.73</v>
+      </c>
+      <c r="AI124">
+        <v>1.85</v>
+      </c>
+      <c r="AJ124">
+        <v>1.81</v>
+      </c>
+      <c r="AK124">
+        <v>1.42</v>
+      </c>
+      <c r="AL124">
+        <v>1.3</v>
+      </c>
+      <c r="AM124">
+        <v>1.43</v>
+      </c>
+      <c r="AN124">
+        <v>1.13</v>
+      </c>
+      <c r="AO124">
+        <v>1.13</v>
+      </c>
+      <c r="AP124">
+        <v>1.33</v>
+      </c>
+      <c r="AQ124">
+        <v>1</v>
+      </c>
+      <c r="AR124">
+        <v>1.38</v>
+      </c>
+      <c r="AS124">
+        <v>1.28</v>
+      </c>
+      <c r="AT124">
+        <v>2.66</v>
+      </c>
+      <c r="AU124">
+        <v>2</v>
+      </c>
+      <c r="AV124">
+        <v>5</v>
+      </c>
+      <c r="AW124">
+        <v>4</v>
+      </c>
+      <c r="AX124">
+        <v>4</v>
+      </c>
+      <c r="AY124">
+        <v>6</v>
+      </c>
+      <c r="AZ124">
+        <v>9</v>
+      </c>
+      <c r="BA124">
+        <v>3</v>
+      </c>
+      <c r="BB124">
+        <v>3</v>
+      </c>
+      <c r="BC124">
+        <v>6</v>
+      </c>
+      <c r="BD124">
+        <v>1.84</v>
+      </c>
+      <c r="BE124">
+        <v>6.1</v>
+      </c>
+      <c r="BF124">
+        <v>2.44</v>
+      </c>
+      <c r="BG124">
+        <v>1.42</v>
+      </c>
+      <c r="BH124">
+        <v>2.49</v>
+      </c>
+      <c r="BI124">
+        <v>1.85</v>
+      </c>
+      <c r="BJ124">
+        <v>1.95</v>
+      </c>
+      <c r="BK124">
+        <v>2.28</v>
+      </c>
+      <c r="BL124">
+        <v>1.5</v>
+      </c>
+      <c r="BM124">
+        <v>3.14</v>
+      </c>
+      <c r="BN124">
+        <v>1.27</v>
+      </c>
+      <c r="BO124">
+        <v>4.1</v>
+      </c>
+      <c r="BP124">
         <v>1.18</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
@@ -1405,10 +1405,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.8</v>
+        <v>2.53</v>
       </c>
       <c r="AQ2">
-        <v>0.78</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.11</v>
+        <v>0.78</v>
       </c>
       <c r="AQ3">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1817,10 +1817,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.2</v>
+        <v>1.71</v>
       </c>
       <c r="AQ4">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2023,10 +2023,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ5">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2229,10 +2229,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AQ6">
-        <v>0.44</v>
+        <v>0.89</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2435,10 +2435,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.89</v>
+        <v>1.61</v>
       </c>
       <c r="AQ7">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2641,10 +2641,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.89</v>
+        <v>1.72</v>
       </c>
       <c r="AQ8">
-        <v>1</v>
+        <v>0.76</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2847,10 +2847,10 @@
         <v>3</v>
       </c>
       <c r="AP9">
-        <v>2.8</v>
+        <v>2.53</v>
       </c>
       <c r="AQ9">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AR9">
         <v>2.58</v>
@@ -3053,10 +3053,10 @@
         <v>1</v>
       </c>
       <c r="AP10">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ10">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AR10">
         <v>0.82</v>
@@ -3259,10 +3259,10 @@
         <v>3</v>
       </c>
       <c r="AP11">
-        <v>1.89</v>
+        <v>1.61</v>
       </c>
       <c r="AQ11">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AR11">
         <v>1.04</v>
@@ -3465,19 +3465,19 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.33</v>
+        <v>0.89</v>
       </c>
       <c r="AQ12">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="AS12">
         <v>0.92</v>
       </c>
       <c r="AT12">
-        <v>0.92</v>
+        <v>1.72</v>
       </c>
       <c r="AU12">
         <v>6</v>
@@ -3671,10 +3671,10 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.2</v>
+        <v>1.71</v>
       </c>
       <c r="AQ13">
-        <v>0.78</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR13">
         <v>1.4</v>
@@ -3874,22 +3874,22 @@
         <v>0</v>
       </c>
       <c r="AO14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP14">
-        <v>1.11</v>
+        <v>0.78</v>
       </c>
       <c r="AQ14">
-        <v>1.56</v>
+        <v>1.72</v>
       </c>
       <c r="AR14">
         <v>1.15</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AT14">
-        <v>1.15</v>
+        <v>2.76</v>
       </c>
       <c r="AU14">
         <v>3</v>
@@ -4083,10 +4083,10 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AQ15">
-        <v>1</v>
+        <v>0.76</v>
       </c>
       <c r="AR15">
         <v>0.82</v>
@@ -4286,22 +4286,22 @@
         <v>3</v>
       </c>
       <c r="AO16">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AP16">
-        <v>1.89</v>
+        <v>1.72</v>
       </c>
       <c r="AQ16">
-        <v>2.43</v>
+        <v>1.71</v>
       </c>
       <c r="AR16">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AT16">
-        <v>1.61</v>
+        <v>3.06</v>
       </c>
       <c r="AU16">
         <v>2</v>
@@ -4489,25 +4489,25 @@
         <v>1.57</v>
       </c>
       <c r="AN17">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AO17">
         <v>1.5</v>
       </c>
       <c r="AP17">
-        <v>1.33</v>
+        <v>0.89</v>
       </c>
       <c r="AQ17">
-        <v>0.78</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR17">
-        <v>1.52</v>
+        <v>1.16</v>
       </c>
       <c r="AS17">
         <v>0.89</v>
       </c>
       <c r="AT17">
-        <v>2.41</v>
+        <v>2.05</v>
       </c>
       <c r="AU17">
         <v>4</v>
@@ -4701,10 +4701,10 @@
         <v>2</v>
       </c>
       <c r="AP18">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ18">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AR18">
         <v>1.29</v>
@@ -4901,25 +4901,25 @@
         <v>1.71</v>
       </c>
       <c r="AN19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO19">
         <v>0.5</v>
       </c>
       <c r="AP19">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AQ19">
-        <v>1</v>
+        <v>0.76</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AS19">
         <v>0.73</v>
       </c>
       <c r="AT19">
-        <v>0.73</v>
+        <v>2.16</v>
       </c>
       <c r="AU19">
         <v>9</v>
@@ -5113,10 +5113,10 @@
         <v>1.5</v>
       </c>
       <c r="AP20">
-        <v>1.89</v>
+        <v>1.61</v>
       </c>
       <c r="AQ20">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AR20">
         <v>1.06</v>
@@ -5319,10 +5319,10 @@
         <v>0.5</v>
       </c>
       <c r="AP21">
-        <v>1.11</v>
+        <v>0.78</v>
       </c>
       <c r="AQ21">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AR21">
         <v>1.02</v>
@@ -5522,22 +5522,22 @@
         <v>2</v>
       </c>
       <c r="AO22">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP22">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AQ22">
-        <v>2.14</v>
+        <v>2.53</v>
       </c>
       <c r="AR22">
         <v>0.92</v>
       </c>
       <c r="AS22">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AT22">
-        <v>0.92</v>
+        <v>2.85</v>
       </c>
       <c r="AU22">
         <v>5</v>
@@ -5725,25 +5725,25 @@
         <v>1.7</v>
       </c>
       <c r="AN23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO23">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AP23">
-        <v>2.8</v>
+        <v>2.53</v>
       </c>
       <c r="AQ23">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="AR23">
-        <v>1.93</v>
+        <v>1.7</v>
       </c>
       <c r="AS23">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AT23">
-        <v>1.93</v>
+        <v>2.75</v>
       </c>
       <c r="AU23">
         <v>2</v>
@@ -5931,25 +5931,25 @@
         <v>1.61</v>
       </c>
       <c r="AN24">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AO24">
         <v>1.33</v>
       </c>
       <c r="AP24">
-        <v>1.33</v>
+        <v>0.89</v>
       </c>
       <c r="AQ24">
-        <v>1</v>
+        <v>0.76</v>
       </c>
       <c r="AR24">
-        <v>1.41</v>
+        <v>1.21</v>
       </c>
       <c r="AS24">
         <v>0.87</v>
       </c>
       <c r="AT24">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="AU24">
         <v>9</v>
@@ -6137,25 +6137,25 @@
         <v>1.8</v>
       </c>
       <c r="AN25">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AO25">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AP25">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AQ25">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR25">
-        <v>2.07</v>
+        <v>1.64</v>
       </c>
       <c r="AS25">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AT25">
-        <v>2.07</v>
+        <v>2.66</v>
       </c>
       <c r="AU25">
         <v>3</v>
@@ -6343,25 +6343,25 @@
         <v>1.75</v>
       </c>
       <c r="AN26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO26">
         <v>0.33</v>
       </c>
       <c r="AP26">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AQ26">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AR26">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AS26">
         <v>1.45</v>
       </c>
       <c r="AT26">
-        <v>1.45</v>
+        <v>3.14</v>
       </c>
       <c r="AU26">
         <v>2</v>
@@ -6549,25 +6549,25 @@
         <v>2.2</v>
       </c>
       <c r="AN27">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AO27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP27">
-        <v>1.2</v>
+        <v>1.71</v>
       </c>
       <c r="AQ27">
-        <v>0.44</v>
+        <v>0.78</v>
       </c>
       <c r="AR27">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="AS27">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="AT27">
-        <v>1.42</v>
+        <v>2.25</v>
       </c>
       <c r="AU27">
         <v>8</v>
@@ -6755,25 +6755,25 @@
         <v>1.3</v>
       </c>
       <c r="AN28">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AO28">
         <v>2.33</v>
       </c>
       <c r="AP28">
-        <v>1.11</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ28">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AR28">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AS28">
         <v>1.3</v>
       </c>
       <c r="AT28">
-        <v>1.3</v>
+        <v>2.35</v>
       </c>
       <c r="AU28">
         <v>3</v>
@@ -6961,25 +6961,25 @@
         <v>2.15</v>
       </c>
       <c r="AN29">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AO29">
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.89</v>
+        <v>1.72</v>
       </c>
       <c r="AQ29">
-        <v>1.13</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR29">
+        <v>1.37</v>
+      </c>
+      <c r="AS29">
         <v>1.22</v>
       </c>
-      <c r="AS29">
-        <v>0</v>
-      </c>
       <c r="AT29">
-        <v>1.22</v>
+        <v>2.59</v>
       </c>
       <c r="AU29">
         <v>5</v>
@@ -7170,22 +7170,22 @@
         <v>0</v>
       </c>
       <c r="AO30">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AP30">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ30">
-        <v>0.44</v>
+        <v>0.89</v>
       </c>
       <c r="AR30">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AS30">
-        <v>0.8</v>
+        <v>1.41</v>
       </c>
       <c r="AT30">
-        <v>2.02</v>
+        <v>2.54</v>
       </c>
       <c r="AU30">
         <v>7</v>
@@ -7379,19 +7379,19 @@
         <v>2</v>
       </c>
       <c r="AP31">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AQ31">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AR31">
-        <v>1.17</v>
+        <v>1.56</v>
       </c>
       <c r="AS31">
         <v>1.26</v>
       </c>
       <c r="AT31">
-        <v>2.43</v>
+        <v>2.82</v>
       </c>
       <c r="AU31">
         <v>8</v>
@@ -7579,25 +7579,25 @@
         <v>1.53</v>
       </c>
       <c r="AN32">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AO32">
         <v>1</v>
       </c>
       <c r="AP32">
-        <v>1.11</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ32">
-        <v>1</v>
+        <v>0.76</v>
       </c>
       <c r="AR32">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AS32">
         <v>1.11</v>
       </c>
       <c r="AT32">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AU32">
         <v>9</v>
@@ -7785,25 +7785,25 @@
         <v>1.61</v>
       </c>
       <c r="AN33">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="AO33">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="AP33">
-        <v>2.8</v>
+        <v>2.53</v>
       </c>
       <c r="AQ33">
-        <v>2.43</v>
+        <v>1.71</v>
       </c>
       <c r="AR33">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AS33">
-        <v>0.97</v>
+        <v>1.44</v>
       </c>
       <c r="AT33">
-        <v>2.66</v>
+        <v>3.01</v>
       </c>
       <c r="AU33">
         <v>2</v>
@@ -7991,25 +7991,25 @@
         <v>1.29</v>
       </c>
       <c r="AN34">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AO34">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="AP34">
-        <v>1.11</v>
+        <v>0.78</v>
       </c>
       <c r="AQ34">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AR34">
-        <v>0.98</v>
+        <v>0.87</v>
       </c>
       <c r="AS34">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AT34">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
       <c r="AU34">
         <v>3</v>
@@ -8197,25 +8197,25 @@
         <v>1.57</v>
       </c>
       <c r="AN35">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="AO35">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="AP35">
-        <v>1.89</v>
+        <v>1.61</v>
       </c>
       <c r="AQ35">
-        <v>1.56</v>
+        <v>1.72</v>
       </c>
       <c r="AR35">
-        <v>1.05</v>
+        <v>0.9</v>
       </c>
       <c r="AS35">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="AT35">
-        <v>2.72</v>
+        <v>2.32</v>
       </c>
       <c r="AU35">
         <v>5</v>
@@ -8403,25 +8403,25 @@
         <v>1.88</v>
       </c>
       <c r="AN36">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AO36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP36">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AQ36">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR36">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AS36">
-        <v>0.85</v>
+        <v>0.98</v>
       </c>
       <c r="AT36">
-        <v>0.85</v>
+        <v>2.32</v>
       </c>
       <c r="AU36">
         <v>8</v>
@@ -8609,25 +8609,25 @@
         <v>0</v>
       </c>
       <c r="AN37">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AO37">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AP37">
+        <v>1.61</v>
+      </c>
+      <c r="AQ37">
+        <v>0.78</v>
+      </c>
+      <c r="AR37">
+        <v>0.98</v>
+      </c>
+      <c r="AS37">
+        <v>0.91</v>
+      </c>
+      <c r="AT37">
         <v>1.89</v>
-      </c>
-      <c r="AQ37">
-        <v>0.44</v>
-      </c>
-      <c r="AR37">
-        <v>1.11</v>
-      </c>
-      <c r="AS37">
-        <v>0.52</v>
-      </c>
-      <c r="AT37">
-        <v>1.63</v>
       </c>
       <c r="AU37">
         <v>7</v>
@@ -8815,25 +8815,25 @@
         <v>0</v>
       </c>
       <c r="AN38">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="AO38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AP38">
-        <v>1.33</v>
+        <v>0.89</v>
       </c>
       <c r="AQ38">
-        <v>2.14</v>
+        <v>2.53</v>
       </c>
       <c r="AR38">
-        <v>1.61</v>
+        <v>1.37</v>
       </c>
       <c r="AS38">
-        <v>1.24</v>
+        <v>1.55</v>
       </c>
       <c r="AT38">
-        <v>2.85</v>
+        <v>2.92</v>
       </c>
       <c r="AU38">
         <v>4</v>
@@ -9021,25 +9021,25 @@
         <v>1.55</v>
       </c>
       <c r="AN39">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="AO39">
         <v>1.6</v>
       </c>
       <c r="AP39">
-        <v>1.2</v>
+        <v>1.71</v>
       </c>
       <c r="AQ39">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AR39">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="AS39">
         <v>1.35</v>
       </c>
       <c r="AT39">
-        <v>2.95</v>
+        <v>2.73</v>
       </c>
       <c r="AU39">
         <v>5</v>
@@ -9227,25 +9227,25 @@
         <v>2.2</v>
       </c>
       <c r="AN40">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AO40">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="AP40">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AQ40">
-        <v>0.78</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR40">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AS40">
-        <v>1.05</v>
+        <v>1.32</v>
       </c>
       <c r="AT40">
-        <v>2.67</v>
+        <v>2.98</v>
       </c>
       <c r="AU40">
         <v>8</v>
@@ -9433,25 +9433,25 @@
         <v>1.44</v>
       </c>
       <c r="AN41">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="AO41">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AP41">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AQ41">
-        <v>1.56</v>
+        <v>1.72</v>
       </c>
       <c r="AR41">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="AS41">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AT41">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="AU41">
         <v>5</v>
@@ -9639,25 +9639,25 @@
         <v>1.85</v>
       </c>
       <c r="AN42">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="AO42">
         <v>0.8</v>
       </c>
       <c r="AP42">
+        <v>1.39</v>
+      </c>
+      <c r="AQ42">
+        <v>0.76</v>
+      </c>
+      <c r="AR42">
         <v>1.44</v>
-      </c>
-      <c r="AQ42">
-        <v>1</v>
-      </c>
-      <c r="AR42">
-        <v>1.85</v>
       </c>
       <c r="AS42">
         <v>1.12</v>
       </c>
       <c r="AT42">
-        <v>2.97</v>
+        <v>2.56</v>
       </c>
       <c r="AU42">
         <v>7</v>
@@ -9845,25 +9845,25 @@
         <v>1.67</v>
       </c>
       <c r="AN43">
-        <v>2.33</v>
+        <v>1.8</v>
       </c>
       <c r="AO43">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AP43">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AQ43">
-        <v>1.13</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR43">
-        <v>1.02</v>
+        <v>0.96</v>
       </c>
       <c r="AS43">
-        <v>0.83</v>
+        <v>1.22</v>
       </c>
       <c r="AT43">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="AU43">
         <v>4</v>
@@ -10051,25 +10051,25 @@
         <v>1.44</v>
       </c>
       <c r="AN44">
-        <v>0.33</v>
+        <v>1.33</v>
       </c>
       <c r="AO44">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AP44">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AQ44">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AR44">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AS44">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="AT44">
-        <v>2.77</v>
+        <v>2.94</v>
       </c>
       <c r="AU44">
         <v>6</v>
@@ -10257,25 +10257,25 @@
         <v>1.36</v>
       </c>
       <c r="AN45">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AO45">
         <v>1.83</v>
       </c>
       <c r="AP45">
-        <v>1.33</v>
+        <v>0.89</v>
       </c>
       <c r="AQ45">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AR45">
-        <v>1.49</v>
+        <v>1.34</v>
       </c>
       <c r="AS45">
         <v>1.33</v>
       </c>
       <c r="AT45">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="AU45">
         <v>5</v>
@@ -10466,22 +10466,22 @@
         <v>2</v>
       </c>
       <c r="AO46">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AP46">
-        <v>1.89</v>
+        <v>1.72</v>
       </c>
       <c r="AQ46">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AR46">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AS46">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AT46">
-        <v>3.02</v>
+        <v>3.14</v>
       </c>
       <c r="AU46">
         <v>6</v>
@@ -10669,25 +10669,25 @@
         <v>1.65</v>
       </c>
       <c r="AN47">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AO47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP47">
-        <v>1.11</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ47">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR47">
-        <v>1.74</v>
+        <v>1.33</v>
       </c>
       <c r="AS47">
-        <v>0.86</v>
+        <v>1.02</v>
       </c>
       <c r="AT47">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="AU47">
         <v>4</v>
@@ -10875,25 +10875,25 @@
         <v>2.38</v>
       </c>
       <c r="AN48">
-        <v>2.5</v>
+        <v>2.17</v>
       </c>
       <c r="AO48">
         <v>0.67</v>
       </c>
       <c r="AP48">
-        <v>2.8</v>
+        <v>2.53</v>
       </c>
       <c r="AQ48">
-        <v>1</v>
+        <v>0.76</v>
       </c>
       <c r="AR48">
-        <v>1.63</v>
+        <v>1.54</v>
       </c>
       <c r="AS48">
         <v>1.19</v>
       </c>
       <c r="AT48">
-        <v>2.82</v>
+        <v>2.73</v>
       </c>
       <c r="AU48">
         <v>6</v>
@@ -11081,25 +11081,25 @@
         <v>1.55</v>
       </c>
       <c r="AN49">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AO49">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AP49">
-        <v>1.2</v>
+        <v>1.71</v>
       </c>
       <c r="AQ49">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="AR49">
-        <v>1.58</v>
+        <v>1.4</v>
       </c>
       <c r="AS49">
-        <v>0.43</v>
+        <v>1.07</v>
       </c>
       <c r="AT49">
-        <v>2.01</v>
+        <v>2.47</v>
       </c>
       <c r="AU49">
         <v>9</v>
@@ -11287,25 +11287,25 @@
         <v>1.67</v>
       </c>
       <c r="AN50">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="AO50">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AP50">
-        <v>1.11</v>
+        <v>0.78</v>
       </c>
       <c r="AQ50">
-        <v>1.13</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR50">
-        <v>1.01</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AS50">
-        <v>0.96</v>
+        <v>1.2</v>
       </c>
       <c r="AT50">
-        <v>1.97</v>
+        <v>2.14</v>
       </c>
       <c r="AU50">
         <v>3</v>
@@ -11493,25 +11493,25 @@
         <v>2.2</v>
       </c>
       <c r="AN51">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="AO51">
         <v>0.57</v>
       </c>
       <c r="AP51">
-        <v>1.89</v>
+        <v>1.61</v>
       </c>
       <c r="AQ51">
-        <v>1</v>
+        <v>0.76</v>
       </c>
       <c r="AR51">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AS51">
         <v>1.24</v>
       </c>
       <c r="AT51">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="AU51">
         <v>4</v>
@@ -11699,25 +11699,25 @@
         <v>2.7</v>
       </c>
       <c r="AN52">
-        <v>2.6</v>
+        <v>2.29</v>
       </c>
       <c r="AO52">
-        <v>0</v>
+        <v>0.43</v>
       </c>
       <c r="AP52">
-        <v>2.8</v>
+        <v>2.53</v>
       </c>
       <c r="AQ52">
-        <v>0.44</v>
+        <v>0.78</v>
       </c>
       <c r="AR52">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AS52">
-        <v>0.8</v>
+        <v>1.01</v>
       </c>
       <c r="AT52">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="AU52">
         <v>6</v>
@@ -11905,25 +11905,25 @@
         <v>2.3</v>
       </c>
       <c r="AN53">
-        <v>2.33</v>
+        <v>1.57</v>
       </c>
       <c r="AO53">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="AP53">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AQ53">
-        <v>0.44</v>
+        <v>0.89</v>
       </c>
       <c r="AR53">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AS53">
-        <v>1.02</v>
+        <v>1.32</v>
       </c>
       <c r="AT53">
-        <v>2.77</v>
+        <v>3.02</v>
       </c>
       <c r="AU53">
         <v>7</v>
@@ -12111,25 +12111,25 @@
         <v>1.3</v>
       </c>
       <c r="AN54">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="AO54">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AP54">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AQ54">
-        <v>1.56</v>
+        <v>1.72</v>
       </c>
       <c r="AR54">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="AS54">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AT54">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="AU54">
         <v>2</v>
@@ -12317,25 +12317,25 @@
         <v>1.22</v>
       </c>
       <c r="AN55">
-        <v>0.25</v>
+        <v>0.57</v>
       </c>
       <c r="AO55">
-        <v>2</v>
+        <v>1.29</v>
       </c>
       <c r="AP55">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ55">
-        <v>2.43</v>
+        <v>1.71</v>
       </c>
       <c r="AR55">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="AS55">
-        <v>1.04</v>
+        <v>1.46</v>
       </c>
       <c r="AT55">
-        <v>2.36</v>
+        <v>2.64</v>
       </c>
       <c r="AU55">
         <v>5</v>
@@ -12523,25 +12523,25 @@
         <v>1.53</v>
       </c>
       <c r="AN56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO56">
         <v>2</v>
       </c>
       <c r="AP56">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AQ56">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AR56">
-        <v>1.83</v>
+        <v>1.46</v>
       </c>
       <c r="AS56">
         <v>1.29</v>
       </c>
       <c r="AT56">
-        <v>3.12</v>
+        <v>2.75</v>
       </c>
       <c r="AU56">
         <v>7</v>
@@ -12729,25 +12729,25 @@
         <v>1.36</v>
       </c>
       <c r="AN57">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AO57">
-        <v>2.33</v>
+        <v>1.29</v>
       </c>
       <c r="AP57">
-        <v>1.11</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ57">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AR57">
-        <v>1.79</v>
+        <v>1.41</v>
       </c>
       <c r="AS57">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AT57">
-        <v>3.24</v>
+        <v>2.91</v>
       </c>
       <c r="AU57">
         <v>9</v>
@@ -12935,25 +12935,25 @@
         <v>2.1</v>
       </c>
       <c r="AN58">
-        <v>2.17</v>
+        <v>1.75</v>
       </c>
       <c r="AO58">
-        <v>1</v>
+        <v>1.38</v>
       </c>
       <c r="AP58">
-        <v>1.89</v>
+        <v>1.61</v>
       </c>
       <c r="AQ58">
-        <v>0.78</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR58">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AS58">
-        <v>1.13</v>
+        <v>1.45</v>
       </c>
       <c r="AT58">
-        <v>2.44</v>
+        <v>2.73</v>
       </c>
       <c r="AU58">
         <v>4</v>
@@ -13141,25 +13141,25 @@
         <v>1.53</v>
       </c>
       <c r="AN59">
-        <v>0.6</v>
+        <v>0.38</v>
       </c>
       <c r="AO59">
         <v>0.88</v>
       </c>
       <c r="AP59">
-        <v>1.11</v>
+        <v>0.78</v>
       </c>
       <c r="AQ59">
-        <v>1</v>
+        <v>0.76</v>
       </c>
       <c r="AR59">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AS59">
         <v>1.26</v>
       </c>
       <c r="AT59">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="AU59">
         <v>2</v>
@@ -13347,25 +13347,25 @@
         <v>2.15</v>
       </c>
       <c r="AN60">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="AO60">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AP60">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AQ60">
-        <v>1.13</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR60">
-        <v>2.02</v>
+        <v>1.58</v>
       </c>
       <c r="AS60">
-        <v>0.99</v>
+        <v>1.24</v>
       </c>
       <c r="AT60">
-        <v>3.01</v>
+        <v>2.82</v>
       </c>
       <c r="AU60">
         <v>7</v>
@@ -13556,22 +13556,22 @@
         <v>1.75</v>
       </c>
       <c r="AO61">
-        <v>1.5</v>
+        <v>2.38</v>
       </c>
       <c r="AP61">
-        <v>1.89</v>
+        <v>1.72</v>
       </c>
       <c r="AQ61">
-        <v>2.14</v>
+        <v>2.53</v>
       </c>
       <c r="AR61">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="AS61">
-        <v>1.35</v>
+        <v>1.54</v>
       </c>
       <c r="AT61">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="AU61">
         <v>6</v>
@@ -13759,25 +13759,25 @@
         <v>2.2</v>
       </c>
       <c r="AN62">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="AO62">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AP62">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AQ62">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR62">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="AS62">
-        <v>0.92</v>
+        <v>1.01</v>
       </c>
       <c r="AT62">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="AU62">
         <v>7</v>
@@ -13965,25 +13965,25 @@
         <v>1.5</v>
       </c>
       <c r="AN63">
-        <v>0.5</v>
+        <v>1.13</v>
       </c>
       <c r="AO63">
         <v>1.88</v>
       </c>
       <c r="AP63">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AQ63">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AR63">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AS63">
         <v>1.28</v>
       </c>
       <c r="AT63">
-        <v>2.82</v>
+        <v>2.71</v>
       </c>
       <c r="AU63">
         <v>8</v>
@@ -14171,22 +14171,22 @@
         <v>1.95</v>
       </c>
       <c r="AN64">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AO64">
-        <v>0.33</v>
+        <v>0.75</v>
       </c>
       <c r="AP64">
-        <v>1.2</v>
+        <v>1.71</v>
       </c>
       <c r="AQ64">
-        <v>0.44</v>
+        <v>0.89</v>
       </c>
       <c r="AR64">
-        <v>1.63</v>
+        <v>1.41</v>
       </c>
       <c r="AS64">
-        <v>1.09</v>
+        <v>1.31</v>
       </c>
       <c r="AT64">
         <v>2.72</v>
@@ -14377,25 +14377,25 @@
         <v>0</v>
       </c>
       <c r="AN65">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="AO65">
-        <v>0.5</v>
+        <v>1.89</v>
       </c>
       <c r="AP65">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AQ65">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="AR65">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AS65">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AT65">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="AU65">
         <v>3</v>
@@ -14583,25 +14583,25 @@
         <v>0</v>
       </c>
       <c r="AN66">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="AO66">
         <v>2</v>
       </c>
       <c r="AP66">
-        <v>1.89</v>
+        <v>1.72</v>
       </c>
       <c r="AQ66">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AR66">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AS66">
         <v>1.25</v>
       </c>
       <c r="AT66">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="AU66">
         <v>4</v>
@@ -14789,25 +14789,25 @@
         <v>0</v>
       </c>
       <c r="AN67">
-        <v>0.2</v>
+        <v>0.44</v>
       </c>
       <c r="AO67">
-        <v>0.8</v>
+        <v>1.22</v>
       </c>
       <c r="AP67">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ67">
-        <v>0.78</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR67">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AS67">
-        <v>1.16</v>
+        <v>1.43</v>
       </c>
       <c r="AT67">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="AU67">
         <v>3</v>
@@ -14995,25 +14995,25 @@
         <v>0</v>
       </c>
       <c r="AN68">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AO68">
-        <v>1</v>
+        <v>1.89</v>
       </c>
       <c r="AP68">
-        <v>0.33</v>
+        <v>0.76</v>
       </c>
       <c r="AQ68">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AR68">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AS68">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AT68">
-        <v>1.66</v>
+        <v>2.98</v>
       </c>
       <c r="AU68">
         <v>6</v>
@@ -15201,25 +15201,25 @@
         <v>0</v>
       </c>
       <c r="AN69">
-        <v>2.67</v>
+        <v>2.44</v>
       </c>
       <c r="AO69">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="AP69">
-        <v>2.8</v>
+        <v>2.53</v>
       </c>
       <c r="AQ69">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AR69">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="AS69">
-        <v>1.31</v>
+        <v>1.51</v>
       </c>
       <c r="AT69">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="AU69">
         <v>6</v>
@@ -15407,25 +15407,25 @@
         <v>0</v>
       </c>
       <c r="AN70">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="AO70">
-        <v>0.6</v>
+        <v>1.22</v>
       </c>
       <c r="AP70">
-        <v>1.2</v>
+        <v>1.71</v>
       </c>
       <c r="AQ70">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AR70">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="AS70">
-        <v>1.32</v>
+        <v>1.61</v>
       </c>
       <c r="AT70">
-        <v>3.04</v>
+        <v>3.11</v>
       </c>
       <c r="AU70">
         <v>6</v>
@@ -15613,25 +15613,25 @@
         <v>0</v>
       </c>
       <c r="AN71">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AO71">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AP71">
-        <v>1.33</v>
+        <v>0.89</v>
       </c>
       <c r="AQ71">
-        <v>0.44</v>
+        <v>0.78</v>
       </c>
       <c r="AR71">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AS71">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="AT71">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="AU71">
         <v>5</v>
@@ -15819,25 +15819,25 @@
         <v>0</v>
       </c>
       <c r="AN72">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="AO72">
-        <v>0.25</v>
+        <v>0.9</v>
       </c>
       <c r="AP72">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AQ72">
-        <v>0.44</v>
+        <v>0.89</v>
       </c>
       <c r="AR72">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AS72">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AT72">
-        <v>2.92</v>
+        <v>2.79</v>
       </c>
       <c r="AU72">
         <v>2</v>
@@ -16025,25 +16025,25 @@
         <v>0</v>
       </c>
       <c r="AN73">
-        <v>1.75</v>
+        <v>1.1</v>
       </c>
       <c r="AO73">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AP73">
-        <v>1.11</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ73">
-        <v>1.56</v>
+        <v>1.72</v>
       </c>
       <c r="AR73">
-        <v>1.77</v>
+        <v>1.4</v>
       </c>
       <c r="AS73">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="AT73">
-        <v>3.29</v>
+        <v>2.86</v>
       </c>
       <c r="AU73">
         <v>5</v>
@@ -16231,25 +16231,25 @@
         <v>0</v>
       </c>
       <c r="AN74">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="AO74">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AP74">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AQ74">
-        <v>2.14</v>
+        <v>2.53</v>
       </c>
       <c r="AR74">
-        <v>1.98</v>
+        <v>1.57</v>
       </c>
       <c r="AS74">
-        <v>1.27</v>
+        <v>1.53</v>
       </c>
       <c r="AT74">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AU74">
         <v>3</v>
@@ -16437,25 +16437,25 @@
         <v>0</v>
       </c>
       <c r="AN75">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AO75">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="AP75">
-        <v>1.89</v>
+        <v>1.61</v>
       </c>
       <c r="AQ75">
-        <v>1.13</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR75">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AS75">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AT75">
-        <v>2.44</v>
+        <v>2.59</v>
       </c>
       <c r="AU75">
         <v>5</v>
@@ -16643,25 +16643,25 @@
         <v>0</v>
       </c>
       <c r="AN76">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AO76">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AP76">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AQ76">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR76">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AS76">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AT76">
-        <v>1.02</v>
+        <v>2.32</v>
       </c>
       <c r="AU76">
         <v>4</v>
@@ -16849,25 +16849,25 @@
         <v>0</v>
       </c>
       <c r="AN77">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AO77">
-        <v>2.33</v>
+        <v>1.8</v>
       </c>
       <c r="AP77">
-        <v>0.33</v>
+        <v>0.76</v>
       </c>
       <c r="AQ77">
-        <v>2.43</v>
+        <v>1.71</v>
       </c>
       <c r="AR77">
-        <v>1.89</v>
+        <v>1.32</v>
       </c>
       <c r="AS77">
-        <v>1.05</v>
+        <v>1.47</v>
       </c>
       <c r="AT77">
-        <v>2.94</v>
+        <v>2.79</v>
       </c>
       <c r="AU77">
         <v>5</v>
@@ -17055,25 +17055,25 @@
         <v>0</v>
       </c>
       <c r="AN78">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="AO78">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="AP78">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AQ78">
-        <v>0.44</v>
+        <v>0.78</v>
       </c>
       <c r="AR78">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="AS78">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AT78">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="AU78">
         <v>8</v>
@@ -17261,25 +17261,25 @@
         <v>1.38</v>
       </c>
       <c r="AN79">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AO79">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AP79">
-        <v>1.11</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ79">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AR79">
-        <v>1.7</v>
+        <v>1.41</v>
       </c>
       <c r="AS79">
-        <v>1.29</v>
+        <v>1.53</v>
       </c>
       <c r="AT79">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="AU79">
         <v>5</v>
@@ -17467,25 +17467,25 @@
         <v>1.83</v>
       </c>
       <c r="AN80">
-        <v>1.33</v>
+        <v>1.64</v>
       </c>
       <c r="AO80">
-        <v>0.2</v>
+        <v>0.82</v>
       </c>
       <c r="AP80">
-        <v>1.89</v>
+        <v>1.72</v>
       </c>
       <c r="AQ80">
-        <v>0.44</v>
+        <v>0.89</v>
       </c>
       <c r="AR80">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AS80">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AT80">
-        <v>2.58</v>
+        <v>2.76</v>
       </c>
       <c r="AU80">
         <v>3</v>
@@ -17673,25 +17673,25 @@
         <v>1.4</v>
       </c>
       <c r="AN81">
-        <v>0.5</v>
+        <v>0.27</v>
       </c>
       <c r="AO81">
-        <v>1</v>
+        <v>1.45</v>
       </c>
       <c r="AP81">
-        <v>1.11</v>
+        <v>0.78</v>
       </c>
       <c r="AQ81">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR81">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AS81">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AT81">
-        <v>2.31</v>
+        <v>2.24</v>
       </c>
       <c r="AU81">
         <v>4</v>
@@ -17879,25 +17879,25 @@
         <v>1.36</v>
       </c>
       <c r="AN82">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AO82">
-        <v>1</v>
+        <v>1.91</v>
       </c>
       <c r="AP82">
-        <v>1.2</v>
+        <v>1.71</v>
       </c>
       <c r="AQ82">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AR82">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="AS82">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="AT82">
-        <v>3.33</v>
+        <v>3.25</v>
       </c>
       <c r="AU82">
         <v>9</v>
@@ -18085,25 +18085,25 @@
         <v>1.1</v>
       </c>
       <c r="AN83">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="AO83">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="AP83">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ83">
-        <v>2.14</v>
+        <v>2.53</v>
       </c>
       <c r="AR83">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AS83">
-        <v>1.23</v>
+        <v>1.49</v>
       </c>
       <c r="AT83">
-        <v>2.58</v>
+        <v>2.74</v>
       </c>
       <c r="AU83">
         <v>0</v>
@@ -18291,25 +18291,25 @@
         <v>2</v>
       </c>
       <c r="AN84">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO84">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AP84">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AQ84">
-        <v>1</v>
+        <v>0.76</v>
       </c>
       <c r="AR84">
-        <v>1.02</v>
+        <v>1.26</v>
       </c>
       <c r="AS84">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AT84">
-        <v>2.27</v>
+        <v>2.59</v>
       </c>
       <c r="AU84">
         <v>8</v>
@@ -18497,25 +18497,25 @@
         <v>1.36</v>
       </c>
       <c r="AN85">
-        <v>0.83</v>
+        <v>1.09</v>
       </c>
       <c r="AO85">
-        <v>1.33</v>
+        <v>1.91</v>
       </c>
       <c r="AP85">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AQ85">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="AR85">
-        <v>1.63</v>
+        <v>1.45</v>
       </c>
       <c r="AS85">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AT85">
-        <v>2.99</v>
+        <v>2.8</v>
       </c>
       <c r="AU85">
         <v>4</v>
@@ -18703,25 +18703,25 @@
         <v>1.25</v>
       </c>
       <c r="AN86">
-        <v>1.33</v>
+        <v>0.75</v>
       </c>
       <c r="AO86">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AP86">
-        <v>1.33</v>
+        <v>0.89</v>
       </c>
       <c r="AQ86">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="AR86">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="AS86">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AT86">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="AU86">
         <v>7</v>
@@ -18909,25 +18909,25 @@
         <v>1.75</v>
       </c>
       <c r="AN87">
-        <v>0.5</v>
+        <v>0.92</v>
       </c>
       <c r="AO87">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AP87">
-        <v>0.33</v>
+        <v>0.76</v>
       </c>
       <c r="AQ87">
-        <v>1.13</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR87">
-        <v>1.66</v>
+        <v>1.32</v>
       </c>
       <c r="AS87">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AT87">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="AU87">
         <v>2</v>
@@ -19115,25 +19115,25 @@
         <v>1.3</v>
       </c>
       <c r="AN88">
-        <v>1.83</v>
+        <v>1.42</v>
       </c>
       <c r="AO88">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="AP88">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AQ88">
-        <v>2.43</v>
+        <v>1.71</v>
       </c>
       <c r="AR88">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AS88">
-        <v>1.16</v>
+        <v>1.49</v>
       </c>
       <c r="AT88">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="AU88">
         <v>2</v>
@@ -19321,25 +19321,25 @@
         <v>1.73</v>
       </c>
       <c r="AN89">
+        <v>0.92</v>
+      </c>
+      <c r="AO89">
+        <v>0.33</v>
+      </c>
+      <c r="AP89">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AQ89">
+        <v>0.78</v>
+      </c>
+      <c r="AR89">
+        <v>1.48</v>
+      </c>
+      <c r="AS89">
         <v>1.17</v>
       </c>
-      <c r="AO89">
-        <v>0</v>
-      </c>
-      <c r="AP89">
-        <v>1.11</v>
-      </c>
-      <c r="AQ89">
-        <v>0.44</v>
-      </c>
-      <c r="AR89">
-        <v>1.79</v>
-      </c>
-      <c r="AS89">
-        <v>1.14</v>
-      </c>
       <c r="AT89">
-        <v>2.93</v>
+        <v>2.65</v>
       </c>
       <c r="AU89">
         <v>7</v>
@@ -19527,25 +19527,25 @@
         <v>1.53</v>
       </c>
       <c r="AN90">
-        <v>1.6</v>
+        <v>1.17</v>
       </c>
       <c r="AO90">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AP90">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AQ90">
-        <v>1.56</v>
+        <v>1.72</v>
       </c>
       <c r="AR90">
-        <v>1.82</v>
+        <v>1.58</v>
       </c>
       <c r="AS90">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="AT90">
-        <v>3.33</v>
+        <v>3.05</v>
       </c>
       <c r="AU90">
         <v>4</v>
@@ -19733,25 +19733,25 @@
         <v>2</v>
       </c>
       <c r="AN91">
-        <v>2.71</v>
+        <v>2.58</v>
       </c>
       <c r="AO91">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="AP91">
-        <v>2.8</v>
+        <v>2.53</v>
       </c>
       <c r="AQ91">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AR91">
-        <v>1.64</v>
+        <v>1.49</v>
       </c>
       <c r="AS91">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AT91">
-        <v>2.93</v>
+        <v>2.82</v>
       </c>
       <c r="AU91">
         <v>8</v>
@@ -19939,25 +19939,25 @@
         <v>1.95</v>
       </c>
       <c r="AN92">
-        <v>2.67</v>
+        <v>2</v>
       </c>
       <c r="AO92">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AP92">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AQ92">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AR92">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="AS92">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="AT92">
-        <v>3.08</v>
+        <v>3.21</v>
       </c>
       <c r="AU92">
         <v>6</v>
@@ -20145,25 +20145,25 @@
         <v>1.62</v>
       </c>
       <c r="AN93">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="AO93">
-        <v>2.2</v>
+        <v>1.69</v>
       </c>
       <c r="AP93">
-        <v>1.89</v>
+        <v>1.61</v>
       </c>
       <c r="AQ93">
-        <v>2.43</v>
+        <v>1.71</v>
       </c>
       <c r="AR93">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AS93">
-        <v>1.12</v>
+        <v>1.45</v>
       </c>
       <c r="AT93">
-        <v>2.47</v>
+        <v>2.73</v>
       </c>
       <c r="AU93">
         <v>5</v>
@@ -20351,25 +20351,25 @@
         <v>1.95</v>
       </c>
       <c r="AN94">
-        <v>3</v>
+        <v>1.92</v>
       </c>
       <c r="AO94">
-        <v>0.17</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AP94">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AQ94">
-        <v>0.44</v>
+        <v>0.89</v>
       </c>
       <c r="AR94">
-        <v>1.56</v>
+        <v>1.27</v>
       </c>
       <c r="AS94">
-        <v>1.09</v>
+        <v>1.31</v>
       </c>
       <c r="AT94">
-        <v>2.65</v>
+        <v>2.58</v>
       </c>
       <c r="AU94">
         <v>7</v>
@@ -20557,25 +20557,25 @@
         <v>1.5</v>
       </c>
       <c r="AN95">
-        <v>0.67</v>
+        <v>0.92</v>
       </c>
       <c r="AO95">
-        <v>0.67</v>
+        <v>1.08</v>
       </c>
       <c r="AP95">
-        <v>0.33</v>
+        <v>0.76</v>
       </c>
       <c r="AQ95">
-        <v>0.78</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR95">
-        <v>1.52</v>
+        <v>1.31</v>
       </c>
       <c r="AS95">
-        <v>1.16</v>
+        <v>1.5</v>
       </c>
       <c r="AT95">
-        <v>2.68</v>
+        <v>2.81</v>
       </c>
       <c r="AU95">
         <v>5</v>
@@ -20763,25 +20763,25 @@
         <v>1.35</v>
       </c>
       <c r="AN96">
-        <v>0.57</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AO96">
-        <v>1</v>
+        <v>1.38</v>
       </c>
       <c r="AP96">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ96">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR96">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AS96">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AT96">
-        <v>2.51</v>
+        <v>2.36</v>
       </c>
       <c r="AU96">
         <v>5</v>
@@ -20969,25 +20969,25 @@
         <v>1.65</v>
       </c>
       <c r="AN97">
-        <v>1.5</v>
+        <v>1.15</v>
       </c>
       <c r="AO97">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AP97">
+        <v>1.39</v>
+      </c>
+      <c r="AQ97">
+        <v>1.18</v>
+      </c>
+      <c r="AR97">
+        <v>1.59</v>
+      </c>
+      <c r="AS97">
         <v>1.44</v>
       </c>
-      <c r="AQ97">
-        <v>1.13</v>
-      </c>
-      <c r="AR97">
-        <v>1.82</v>
-      </c>
-      <c r="AS97">
-        <v>1.31</v>
-      </c>
       <c r="AT97">
-        <v>3.13</v>
+        <v>3.03</v>
       </c>
       <c r="AU97">
         <v>5</v>
@@ -21175,25 +21175,25 @@
         <v>2</v>
       </c>
       <c r="AN98">
-        <v>2.43</v>
+        <v>1.92</v>
       </c>
       <c r="AO98">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AP98">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AQ98">
-        <v>1.56</v>
+        <v>1.72</v>
       </c>
       <c r="AR98">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AS98">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AT98">
-        <v>3.49</v>
+        <v>3.31</v>
       </c>
       <c r="AU98">
         <v>8</v>
@@ -21381,25 +21381,25 @@
         <v>1.08</v>
       </c>
       <c r="AN99">
-        <v>0.57</v>
+        <v>0.31</v>
       </c>
       <c r="AO99">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="AP99">
-        <v>1.11</v>
+        <v>0.78</v>
       </c>
       <c r="AQ99">
-        <v>2.14</v>
+        <v>2.53</v>
       </c>
       <c r="AR99">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AS99">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="AT99">
-        <v>2.48</v>
+        <v>2.8</v>
       </c>
       <c r="AU99">
         <v>6</v>
@@ -21587,25 +21587,25 @@
         <v>1.17</v>
       </c>
       <c r="AN100">
-        <v>1.71</v>
+        <v>1.29</v>
       </c>
       <c r="AO100">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="AP100">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AQ100">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AR100">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AS100">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AT100">
-        <v>2.77</v>
+        <v>2.91</v>
       </c>
       <c r="AU100">
         <v>5</v>
@@ -21793,25 +21793,25 @@
         <v>1.28</v>
       </c>
       <c r="AN101">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="AO101">
-        <v>0.86</v>
+        <v>1.29</v>
       </c>
       <c r="AP101">
-        <v>0.33</v>
+        <v>0.76</v>
       </c>
       <c r="AQ101">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AR101">
-        <v>1.52</v>
+        <v>1.31</v>
       </c>
       <c r="AS101">
-        <v>1.4</v>
+        <v>1.59</v>
       </c>
       <c r="AT101">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="AU101">
         <v>0</v>
@@ -21999,25 +21999,25 @@
         <v>1.57</v>
       </c>
       <c r="AN102">
-        <v>1.43</v>
+        <v>1.21</v>
       </c>
       <c r="AO102">
-        <v>0.14</v>
+        <v>0.64</v>
       </c>
       <c r="AP102">
-        <v>1.11</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ102">
-        <v>0.44</v>
+        <v>0.89</v>
       </c>
       <c r="AR102">
-        <v>1.78</v>
+        <v>1.5</v>
       </c>
       <c r="AS102">
-        <v>1.09</v>
+        <v>1.31</v>
       </c>
       <c r="AT102">
-        <v>2.87</v>
+        <v>2.81</v>
       </c>
       <c r="AU102">
         <v>6</v>
@@ -22205,25 +22205,25 @@
         <v>2.22</v>
       </c>
       <c r="AN103">
-        <v>1.38</v>
+        <v>1.79</v>
       </c>
       <c r="AO103">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AP103">
-        <v>1.2</v>
+        <v>1.71</v>
       </c>
       <c r="AQ103">
-        <v>1.13</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR103">
-        <v>1.65</v>
+        <v>1.45</v>
       </c>
       <c r="AS103">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AT103">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="AU103">
         <v>4</v>
@@ -22411,25 +22411,25 @@
         <v>1.42</v>
       </c>
       <c r="AN104">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO104">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AP104">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AQ104">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="AR104">
-        <v>1.56</v>
+        <v>1.27</v>
       </c>
       <c r="AS104">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AT104">
-        <v>2.74</v>
+        <v>2.55</v>
       </c>
       <c r="AU104">
         <v>4</v>
@@ -22617,25 +22617,25 @@
         <v>2.05</v>
       </c>
       <c r="AN105">
-        <v>2.75</v>
+        <v>2.43</v>
       </c>
       <c r="AO105">
         <v>1.57</v>
       </c>
       <c r="AP105">
-        <v>2.8</v>
+        <v>2.53</v>
       </c>
       <c r="AQ105">
-        <v>1.56</v>
+        <v>1.72</v>
       </c>
       <c r="AR105">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AS105">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AT105">
-        <v>3.39</v>
+        <v>3.1</v>
       </c>
       <c r="AU105">
         <v>6</v>
@@ -22823,25 +22823,25 @@
         <v>1.85</v>
       </c>
       <c r="AN106">
-        <v>0.71</v>
+        <v>0.93</v>
       </c>
       <c r="AO106">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AP106">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AQ106">
-        <v>0.44</v>
+        <v>0.78</v>
       </c>
       <c r="AR106">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AS106">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AT106">
-        <v>2.83</v>
+        <v>2.67</v>
       </c>
       <c r="AU106">
         <v>3</v>
@@ -23029,25 +23029,25 @@
         <v>2.3</v>
       </c>
       <c r="AN107">
-        <v>1.71</v>
+        <v>1.4</v>
       </c>
       <c r="AO107">
-        <v>0</v>
+        <v>0.47</v>
       </c>
       <c r="AP107">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AQ107">
-        <v>0.44</v>
+        <v>0.78</v>
       </c>
       <c r="AR107">
-        <v>1.82</v>
+        <v>1.57</v>
       </c>
       <c r="AS107">
         <v>1.19</v>
       </c>
       <c r="AT107">
-        <v>3.01</v>
+        <v>2.76</v>
       </c>
       <c r="AU107">
         <v>5</v>
@@ -23235,25 +23235,25 @@
         <v>1.44</v>
       </c>
       <c r="AN108">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AO108">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AP108">
-        <v>1.89</v>
+        <v>1.72</v>
       </c>
       <c r="AQ108">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="AR108">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AS108">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AT108">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="AU108">
         <v>9</v>
@@ -23441,25 +23441,25 @@
         <v>1.41</v>
       </c>
       <c r="AN109">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="AO109">
-        <v>0.86</v>
+        <v>1.2</v>
       </c>
       <c r="AP109">
-        <v>0.33</v>
+        <v>0.76</v>
       </c>
       <c r="AQ109">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR109">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="AS109">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="AT109">
-        <v>2.62</v>
+        <v>2.43</v>
       </c>
       <c r="AU109">
         <v>4</v>
@@ -23647,25 +23647,25 @@
         <v>1.44</v>
       </c>
       <c r="AN110">
-        <v>2.5</v>
+        <v>1.93</v>
       </c>
       <c r="AO110">
-        <v>2.33</v>
+        <v>1.67</v>
       </c>
       <c r="AP110">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AQ110">
-        <v>2.43</v>
+        <v>1.71</v>
       </c>
       <c r="AR110">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="AS110">
-        <v>1.12</v>
+        <v>1.46</v>
       </c>
       <c r="AT110">
-        <v>2.54</v>
+        <v>2.72</v>
       </c>
       <c r="AU110">
         <v>6</v>
@@ -23853,25 +23853,25 @@
         <v>1.73</v>
       </c>
       <c r="AN111">
-        <v>1.14</v>
+        <v>0.8</v>
       </c>
       <c r="AO111">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AP111">
-        <v>1.33</v>
+        <v>0.89</v>
       </c>
       <c r="AQ111">
-        <v>1.13</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR111">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AS111">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AT111">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="AU111">
         <v>2</v>
@@ -24059,25 +24059,25 @@
         <v>1.77</v>
       </c>
       <c r="AN112">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="AO112">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AP112">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AQ112">
-        <v>0.78</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR112">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="AS112">
-        <v>1.16</v>
+        <v>1.47</v>
       </c>
       <c r="AT112">
-        <v>2.71</v>
+        <v>2.92</v>
       </c>
       <c r="AU112">
         <v>10</v>
@@ -24265,25 +24265,25 @@
         <v>1.46</v>
       </c>
       <c r="AN113">
-        <v>2.5</v>
+        <v>2.07</v>
       </c>
       <c r="AO113">
-        <v>2</v>
+        <v>2.47</v>
       </c>
       <c r="AP113">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AQ113">
-        <v>2.14</v>
+        <v>2.53</v>
       </c>
       <c r="AR113">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AS113">
-        <v>1.29</v>
+        <v>1.56</v>
       </c>
       <c r="AT113">
-        <v>3.14</v>
+        <v>3.34</v>
       </c>
       <c r="AU113">
         <v>6</v>
@@ -24471,25 +24471,25 @@
         <v>3.02</v>
       </c>
       <c r="AN114">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="AO114">
-        <v>0.5</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AP114">
-        <v>2.8</v>
+        <v>2.53</v>
       </c>
       <c r="AQ114">
-        <v>0.44</v>
+        <v>0.89</v>
       </c>
       <c r="AR114">
-        <v>1.71</v>
+        <v>1.51</v>
       </c>
       <c r="AS114">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="AT114">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="AU114">
         <v>5</v>
@@ -24677,25 +24677,25 @@
         <v>1.15</v>
       </c>
       <c r="AN115">
-        <v>0.88</v>
+        <v>0.63</v>
       </c>
       <c r="AO115">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AP115">
-        <v>1.11</v>
+        <v>0.78</v>
       </c>
       <c r="AQ115">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="AR115">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AS115">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AT115">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="AU115">
         <v>7</v>
@@ -24883,25 +24883,25 @@
         <v>1.22</v>
       </c>
       <c r="AN116">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AO116">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AP116">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ116">
-        <v>1.56</v>
+        <v>1.72</v>
       </c>
       <c r="AR116">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AS116">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AT116">
-        <v>2.77</v>
+        <v>2.66</v>
       </c>
       <c r="AU116">
         <v>2</v>
@@ -25089,25 +25089,25 @@
         <v>1.33</v>
       </c>
       <c r="AN117">
-        <v>1.5</v>
+        <v>1.31</v>
       </c>
       <c r="AO117">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="AP117">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AQ117">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AR117">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="AS117">
-        <v>1.39</v>
+        <v>1.58</v>
       </c>
       <c r="AT117">
-        <v>2.48</v>
+        <v>2.76</v>
       </c>
       <c r="AU117">
         <v>2</v>
@@ -25295,25 +25295,25 @@
         <v>2.1</v>
       </c>
       <c r="AN118">
-        <v>1.22</v>
+        <v>1.75</v>
       </c>
       <c r="AO118">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AP118">
-        <v>1.2</v>
+        <v>1.71</v>
       </c>
       <c r="AQ118">
-        <v>1</v>
+        <v>0.76</v>
       </c>
       <c r="AR118">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="AS118">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AT118">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="AU118">
         <v>7</v>
@@ -25501,25 +25501,25 @@
         <v>1.17</v>
       </c>
       <c r="AN119">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AO119">
-        <v>1.57</v>
+        <v>1.94</v>
       </c>
       <c r="AP119">
-        <v>1.11</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ119">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AR119">
-        <v>1.71</v>
+        <v>1.42</v>
       </c>
       <c r="AS119">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AT119">
-        <v>3.41</v>
+        <v>3.18</v>
       </c>
       <c r="AU119">
         <v>5</v>
@@ -25707,25 +25707,25 @@
         <v>1.57</v>
       </c>
       <c r="AN120">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="AO120">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AP120">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AQ120">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AR120">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="AS120">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="AT120">
-        <v>2.93</v>
+        <v>2.83</v>
       </c>
       <c r="AU120">
         <v>3</v>
@@ -25913,25 +25913,25 @@
         <v>1.5</v>
       </c>
       <c r="AN121">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AO121">
-        <v>1.38</v>
+        <v>1.65</v>
       </c>
       <c r="AP121">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AQ121">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="AR121">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="AS121">
         <v>1.35</v>
       </c>
       <c r="AT121">
-        <v>3.15</v>
+        <v>2.93</v>
       </c>
       <c r="AU121">
         <v>5</v>
@@ -26119,25 +26119,25 @@
         <v>2.04</v>
       </c>
       <c r="AN122">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AO122">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AP122">
-        <v>1.89</v>
+        <v>1.72</v>
       </c>
       <c r="AQ122">
-        <v>0.78</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR122">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="AS122">
-        <v>1.1</v>
+        <v>1.42</v>
       </c>
       <c r="AT122">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AU122">
         <v>9</v>
@@ -26325,25 +26325,25 @@
         <v>1.52</v>
       </c>
       <c r="AN123">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AO123">
+        <v>0.76</v>
+      </c>
+      <c r="AP123">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AQ123">
         <v>0.78</v>
       </c>
-      <c r="AO123">
-        <v>0.38</v>
-      </c>
-      <c r="AP123">
-        <v>0.8</v>
-      </c>
-      <c r="AQ123">
-        <v>0.44</v>
-      </c>
       <c r="AR123">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="AS123">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AT123">
-        <v>2.37</v>
+        <v>2.32</v>
       </c>
       <c r="AU123">
         <v>2</v>
@@ -26531,25 +26531,25 @@
         <v>1.43</v>
       </c>
       <c r="AN124">
-        <v>1.13</v>
+        <v>0.76</v>
       </c>
       <c r="AO124">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AP124">
-        <v>1.33</v>
+        <v>0.89</v>
       </c>
       <c r="AQ124">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR124">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="AS124">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AT124">
-        <v>2.66</v>
+        <v>2.39</v>
       </c>
       <c r="AU124">
         <v>2</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="238">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -514,6 +514,15 @@
     <t>['9005']</t>
   </si>
   <si>
+    <t>['19']</t>
+  </si>
+  <si>
+    <t>['15', '60']</t>
+  </si>
+  <si>
+    <t>['37']</t>
+  </si>
+  <si>
     <t>['1', '6']</t>
   </si>
   <si>
@@ -710,6 +719,15 @@
   </si>
   <si>
     <t>['69']</t>
+  </si>
+  <si>
+    <t>['9001']</t>
+  </si>
+  <si>
+    <t>['71', '9006']</t>
+  </si>
+  <si>
+    <t>['9007']</t>
   </si>
 </sst>
 </file>
@@ -1071,7 +1089,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP124"/>
+  <dimension ref="A1:BP127"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1405,7 +1423,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="AQ2">
         <v>0.9399999999999999</v>
@@ -1533,7 +1551,7 @@
         <v>85</v>
       </c>
       <c r="P3" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="Q3">
         <v>3.8</v>
@@ -1614,7 +1632,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ3">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1817,10 +1835,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ4">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2026,7 +2044,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AQ5">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2563,7 +2581,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="Q8">
         <v>2.39</v>
@@ -2644,7 +2662,7 @@
         <v>1.72</v>
       </c>
       <c r="AQ8">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2847,10 +2865,10 @@
         <v>3</v>
       </c>
       <c r="AP9">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="AQ9">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AR9">
         <v>2.58</v>
@@ -2975,7 +2993,7 @@
         <v>85</v>
       </c>
       <c r="P10" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="Q10">
         <v>4.3</v>
@@ -3056,7 +3074,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AQ10">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR10">
         <v>0.82</v>
@@ -3181,7 +3199,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="Q11">
         <v>2.8</v>
@@ -3262,7 +3280,7 @@
         <v>1.61</v>
       </c>
       <c r="AQ11">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AR11">
         <v>1.04</v>
@@ -3593,7 +3611,7 @@
         <v>85</v>
       </c>
       <c r="P13" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="Q13">
         <v>2.43</v>
@@ -3671,7 +3689,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ13">
         <v>0.9399999999999999</v>
@@ -3799,7 +3817,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="Q14">
         <v>3.9</v>
@@ -4086,7 +4104,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ15">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="AR15">
         <v>0.82</v>
@@ -4211,7 +4229,7 @@
         <v>85</v>
       </c>
       <c r="P16" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="Q16">
         <v>3.18</v>
@@ -4292,7 +4310,7 @@
         <v>1.72</v>
       </c>
       <c r="AQ16">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AR16">
         <v>1.64</v>
@@ -4417,7 +4435,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="Q17">
         <v>3</v>
@@ -4704,7 +4722,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AQ18">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AR18">
         <v>1.29</v>
@@ -4829,7 +4847,7 @@
         <v>95</v>
       </c>
       <c r="P19" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="Q19">
         <v>2.71</v>
@@ -4907,10 +4925,10 @@
         <v>0.5</v>
       </c>
       <c r="AP19">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ19">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="AR19">
         <v>1.43</v>
@@ -5035,7 +5053,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="Q20">
         <v>3.5</v>
@@ -5116,7 +5134,7 @@
         <v>1.61</v>
       </c>
       <c r="AQ20">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AR20">
         <v>1.06</v>
@@ -5447,7 +5465,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Q22">
         <v>5</v>
@@ -5528,7 +5546,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ22">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="AR22">
         <v>0.92</v>
@@ -5731,7 +5749,7 @@
         <v>2.33</v>
       </c>
       <c r="AP23">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="AQ23">
         <v>1.61</v>
@@ -5859,7 +5877,7 @@
         <v>99</v>
       </c>
       <c r="P24" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Q24">
         <v>3</v>
@@ -5940,7 +5958,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ24">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="AR24">
         <v>1.21</v>
@@ -6143,7 +6161,7 @@
         <v>2.33</v>
       </c>
       <c r="AP25">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ25">
         <v>1.17</v>
@@ -6349,7 +6367,7 @@
         <v>0.33</v>
       </c>
       <c r="AP26">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AQ26">
         <v>1.39</v>
@@ -6477,7 +6495,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Q27">
         <v>2.25</v>
@@ -6555,7 +6573,7 @@
         <v>1</v>
       </c>
       <c r="AP27">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ27">
         <v>0.78</v>
@@ -6683,7 +6701,7 @@
         <v>101</v>
       </c>
       <c r="P28" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="Q28">
         <v>4</v>
@@ -6764,7 +6782,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AQ28">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AR28">
         <v>1.05</v>
@@ -6889,7 +6907,7 @@
         <v>102</v>
       </c>
       <c r="P29" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="Q29">
         <v>2.2</v>
@@ -7095,7 +7113,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="Q30">
         <v>3.75</v>
@@ -7301,7 +7319,7 @@
         <v>104</v>
       </c>
       <c r="P31" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q31">
         <v>3.25</v>
@@ -7379,10 +7397,10 @@
         <v>2</v>
       </c>
       <c r="AP31">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AQ31">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AR31">
         <v>1.56</v>
@@ -7588,7 +7606,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AQ32">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="AR32">
         <v>1.04</v>
@@ -7713,7 +7731,7 @@
         <v>91</v>
       </c>
       <c r="P33" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="Q33">
         <v>2.63</v>
@@ -7791,10 +7809,10 @@
         <v>1.75</v>
       </c>
       <c r="AP33">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="AQ33">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AR33">
         <v>1.57</v>
@@ -7919,7 +7937,7 @@
         <v>85</v>
       </c>
       <c r="P34" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="Q34">
         <v>3.8</v>
@@ -8000,7 +8018,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ34">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR34">
         <v>0.87</v>
@@ -8125,7 +8143,7 @@
         <v>106</v>
       </c>
       <c r="P35" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Q35">
         <v>2.8</v>
@@ -8743,7 +8761,7 @@
         <v>85</v>
       </c>
       <c r="P38" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="Q38">
         <v>5</v>
@@ -8824,7 +8842,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ38">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="AR38">
         <v>1.37</v>
@@ -8949,7 +8967,7 @@
         <v>85</v>
       </c>
       <c r="P39" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q39">
         <v>3.1</v>
@@ -9027,10 +9045,10 @@
         <v>1.6</v>
       </c>
       <c r="AP39">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ39">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AR39">
         <v>1.38</v>
@@ -9233,7 +9251,7 @@
         <v>1.6</v>
       </c>
       <c r="AP40">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AQ40">
         <v>0.9399999999999999</v>
@@ -9361,7 +9379,7 @@
         <v>110</v>
       </c>
       <c r="P41" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q41">
         <v>3.25</v>
@@ -9439,7 +9457,7 @@
         <v>1.8</v>
       </c>
       <c r="AP41">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ41">
         <v>1.72</v>
@@ -9567,7 +9585,7 @@
         <v>111</v>
       </c>
       <c r="P42" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q42">
         <v>2.5</v>
@@ -9648,7 +9666,7 @@
         <v>1.39</v>
       </c>
       <c r="AQ42">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="AR42">
         <v>1.44</v>
@@ -9979,7 +9997,7 @@
         <v>113</v>
       </c>
       <c r="P44" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q44">
         <v>3.4</v>
@@ -10057,7 +10075,7 @@
         <v>1</v>
       </c>
       <c r="AP44">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ44">
         <v>1.39</v>
@@ -10185,7 +10203,7 @@
         <v>113</v>
       </c>
       <c r="P45" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q45">
         <v>3.75</v>
@@ -10266,7 +10284,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ45">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AR45">
         <v>1.34</v>
@@ -10391,7 +10409,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q46">
         <v>3.75</v>
@@ -10472,7 +10490,7 @@
         <v>1.72</v>
       </c>
       <c r="AQ46">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AR46">
         <v>1.42</v>
@@ -10597,7 +10615,7 @@
         <v>85</v>
       </c>
       <c r="P47" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q47">
         <v>3</v>
@@ -10881,10 +10899,10 @@
         <v>0.67</v>
       </c>
       <c r="AP48">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="AQ48">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="AR48">
         <v>1.54</v>
@@ -11009,7 +11027,7 @@
         <v>116</v>
       </c>
       <c r="P49" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -11087,7 +11105,7 @@
         <v>2.17</v>
       </c>
       <c r="AP49">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ49">
         <v>1.61</v>
@@ -11421,7 +11439,7 @@
         <v>85</v>
       </c>
       <c r="P51" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q51">
         <v>2.25</v>
@@ -11502,7 +11520,7 @@
         <v>1.61</v>
       </c>
       <c r="AQ51">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="AR51">
         <v>1.19</v>
@@ -11705,7 +11723,7 @@
         <v>0.43</v>
       </c>
       <c r="AP52">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="AQ52">
         <v>0.78</v>
@@ -11911,7 +11929,7 @@
         <v>0.86</v>
       </c>
       <c r="AP53">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AQ53">
         <v>0.89</v>
@@ -12245,7 +12263,7 @@
         <v>119</v>
       </c>
       <c r="P55" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q55">
         <v>5</v>
@@ -12326,7 +12344,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AQ55">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AR55">
         <v>1.18</v>
@@ -12532,7 +12550,7 @@
         <v>1.39</v>
       </c>
       <c r="AQ56">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AR56">
         <v>1.46</v>
@@ -12657,7 +12675,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q57">
         <v>3.75</v>
@@ -12738,7 +12756,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AQ57">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR57">
         <v>1.41</v>
@@ -12863,7 +12881,7 @@
         <v>121</v>
       </c>
       <c r="P58" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Q58">
         <v>2.3</v>
@@ -13069,7 +13087,7 @@
         <v>85</v>
       </c>
       <c r="P59" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q59">
         <v>3.2</v>
@@ -13150,7 +13168,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ59">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="AR59">
         <v>1.07</v>
@@ -13481,7 +13499,7 @@
         <v>123</v>
       </c>
       <c r="P61" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q61">
         <v>4</v>
@@ -13562,7 +13580,7 @@
         <v>1.72</v>
       </c>
       <c r="AQ61">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="AR61">
         <v>1.46</v>
@@ -13687,7 +13705,7 @@
         <v>124</v>
       </c>
       <c r="P62" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q62">
         <v>2.3</v>
@@ -13765,7 +13783,7 @@
         <v>2</v>
       </c>
       <c r="AP62">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AQ62">
         <v>1.17</v>
@@ -13893,7 +13911,7 @@
         <v>85</v>
       </c>
       <c r="P63" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q63">
         <v>3.2</v>
@@ -13971,10 +13989,10 @@
         <v>1.88</v>
       </c>
       <c r="AP63">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ63">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AR63">
         <v>1.43</v>
@@ -14099,7 +14117,7 @@
         <v>125</v>
       </c>
       <c r="P64" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q64">
         <v>2.5</v>
@@ -14177,7 +14195,7 @@
         <v>0.75</v>
       </c>
       <c r="AP64">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ64">
         <v>0.89</v>
@@ -14305,7 +14323,7 @@
         <v>126</v>
       </c>
       <c r="P65" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q65">
         <v>4</v>
@@ -14511,7 +14529,7 @@
         <v>127</v>
       </c>
       <c r="P66" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q66">
         <v>3</v>
@@ -14592,7 +14610,7 @@
         <v>1.72</v>
       </c>
       <c r="AQ66">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AR66">
         <v>1.5</v>
@@ -14923,7 +14941,7 @@
         <v>129</v>
       </c>
       <c r="P68" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q68">
         <v>5</v>
@@ -15001,10 +15019,10 @@
         <v>1.89</v>
       </c>
       <c r="AP68">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="AQ68">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AR68">
         <v>1.25</v>
@@ -15207,10 +15225,10 @@
         <v>1</v>
       </c>
       <c r="AP69">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="AQ69">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR69">
         <v>1.49</v>
@@ -15413,7 +15431,7 @@
         <v>1.22</v>
       </c>
       <c r="AP70">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ70">
         <v>1.39</v>
@@ -15541,7 +15559,7 @@
         <v>132</v>
       </c>
       <c r="P71" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q71">
         <v>2.63</v>
@@ -15825,7 +15843,7 @@
         <v>0.9</v>
       </c>
       <c r="AP72">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ72">
         <v>0.89</v>
@@ -15953,7 +15971,7 @@
         <v>85</v>
       </c>
       <c r="P73" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q73">
         <v>3.6</v>
@@ -16159,7 +16177,7 @@
         <v>85</v>
       </c>
       <c r="P74" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q74">
         <v>4.33</v>
@@ -16240,7 +16258,7 @@
         <v>1.39</v>
       </c>
       <c r="AQ74">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="AR74">
         <v>1.57</v>
@@ -16365,7 +16383,7 @@
         <v>134</v>
       </c>
       <c r="P75" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="Q75">
         <v>1.91</v>
@@ -16571,7 +16589,7 @@
         <v>135</v>
       </c>
       <c r="P76" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q76">
         <v>2.63</v>
@@ -16649,7 +16667,7 @@
         <v>1.6</v>
       </c>
       <c r="AP76">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AQ76">
         <v>1.17</v>
@@ -16777,7 +16795,7 @@
         <v>85</v>
       </c>
       <c r="P77" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q77">
         <v>4.5</v>
@@ -16855,10 +16873,10 @@
         <v>1.8</v>
       </c>
       <c r="AP77">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="AQ77">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AR77">
         <v>1.32</v>
@@ -17061,7 +17079,7 @@
         <v>0.3</v>
       </c>
       <c r="AP78">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AQ78">
         <v>0.78</v>
@@ -17189,7 +17207,7 @@
         <v>137</v>
       </c>
       <c r="P79" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q79">
         <v>3.6</v>
@@ -17807,7 +17825,7 @@
         <v>140</v>
       </c>
       <c r="P82" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q82">
         <v>3.75</v>
@@ -17885,10 +17903,10 @@
         <v>1.91</v>
       </c>
       <c r="AP82">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ82">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AR82">
         <v>1.47</v>
@@ -18013,7 +18031,7 @@
         <v>85</v>
       </c>
       <c r="P83" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q83">
         <v>7.5</v>
@@ -18094,7 +18112,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AQ83">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="AR83">
         <v>1.25</v>
@@ -18219,7 +18237,7 @@
         <v>141</v>
       </c>
       <c r="P84" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Q84">
         <v>2.38</v>
@@ -18297,10 +18315,10 @@
         <v>1</v>
       </c>
       <c r="AP84">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AQ84">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="AR84">
         <v>1.26</v>
@@ -18425,7 +18443,7 @@
         <v>142</v>
       </c>
       <c r="P85" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q85">
         <v>3.75</v>
@@ -18503,7 +18521,7 @@
         <v>1.91</v>
       </c>
       <c r="AP85">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ85">
         <v>1.61</v>
@@ -18631,7 +18649,7 @@
         <v>85</v>
       </c>
       <c r="P86" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q86">
         <v>4.2</v>
@@ -18915,7 +18933,7 @@
         <v>0.67</v>
       </c>
       <c r="AP87">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="AQ87">
         <v>0.9399999999999999</v>
@@ -19124,7 +19142,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ88">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AR88">
         <v>1.13</v>
@@ -19249,7 +19267,7 @@
         <v>143</v>
       </c>
       <c r="P89" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="Q89">
         <v>2.62</v>
@@ -19455,7 +19473,7 @@
         <v>144</v>
       </c>
       <c r="P90" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q90">
         <v>3.1</v>
@@ -19739,10 +19757,10 @@
         <v>2.08</v>
       </c>
       <c r="AP91">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="AQ91">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AR91">
         <v>1.49</v>
@@ -19867,7 +19885,7 @@
         <v>146</v>
       </c>
       <c r="P92" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -19945,10 +19963,10 @@
         <v>1</v>
       </c>
       <c r="AP92">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AQ92">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR92">
         <v>1.79</v>
@@ -20073,7 +20091,7 @@
         <v>147</v>
       </c>
       <c r="P93" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q93">
         <v>2.62</v>
@@ -20154,7 +20172,7 @@
         <v>1.61</v>
       </c>
       <c r="AQ93">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AR93">
         <v>1.28</v>
@@ -20279,7 +20297,7 @@
         <v>148</v>
       </c>
       <c r="P94" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q94">
         <v>2.4</v>
@@ -20357,7 +20375,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AP94">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AQ94">
         <v>0.89</v>
@@ -20485,7 +20503,7 @@
         <v>149</v>
       </c>
       <c r="P95" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q95">
         <v>3.1</v>
@@ -20563,7 +20581,7 @@
         <v>1.08</v>
       </c>
       <c r="AP95">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="AQ95">
         <v>0.9399999999999999</v>
@@ -20978,7 +20996,7 @@
         <v>1.39</v>
       </c>
       <c r="AQ97">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR97">
         <v>1.59</v>
@@ -21103,7 +21121,7 @@
         <v>152</v>
       </c>
       <c r="P98" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q98">
         <v>2.3</v>
@@ -21181,7 +21199,7 @@
         <v>1.69</v>
       </c>
       <c r="AP98">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AQ98">
         <v>1.72</v>
@@ -21309,7 +21327,7 @@
         <v>153</v>
       </c>
       <c r="P99" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q99">
         <v>6.5</v>
@@ -21390,7 +21408,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ99">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="AR99">
         <v>1.23</v>
@@ -21515,7 +21533,7 @@
         <v>154</v>
       </c>
       <c r="P100" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q100">
         <v>4.33</v>
@@ -21596,7 +21614,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ100">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AR100">
         <v>1.13</v>
@@ -21721,7 +21739,7 @@
         <v>85</v>
       </c>
       <c r="P101" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q101">
         <v>3.88</v>
@@ -21799,7 +21817,7 @@
         <v>1.29</v>
       </c>
       <c r="AP101">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="AQ101">
         <v>1.39</v>
@@ -22133,7 +22151,7 @@
         <v>85</v>
       </c>
       <c r="P103" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q103">
         <v>2.14</v>
@@ -22211,7 +22229,7 @@
         <v>0.86</v>
       </c>
       <c r="AP103">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ103">
         <v>0.9399999999999999</v>
@@ -22339,7 +22357,7 @@
         <v>150</v>
       </c>
       <c r="P104" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q104">
         <v>3.4</v>
@@ -22417,7 +22435,7 @@
         <v>1.93</v>
       </c>
       <c r="AP104">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AQ104">
         <v>1.61</v>
@@ -22623,7 +22641,7 @@
         <v>1.57</v>
       </c>
       <c r="AP105">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="AQ105">
         <v>1.72</v>
@@ -22829,7 +22847,7 @@
         <v>0.5</v>
       </c>
       <c r="AP106">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ106">
         <v>0.78</v>
@@ -22957,7 +22975,7 @@
         <v>85</v>
       </c>
       <c r="P107" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q107">
         <v>2.13</v>
@@ -23163,7 +23181,7 @@
         <v>157</v>
       </c>
       <c r="P108" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q108">
         <v>3.38</v>
@@ -23447,7 +23465,7 @@
         <v>1.2</v>
       </c>
       <c r="AP109">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="AQ109">
         <v>1.17</v>
@@ -23653,10 +23671,10 @@
         <v>1.67</v>
       </c>
       <c r="AP110">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AQ110">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AR110">
         <v>1.26</v>
@@ -24065,7 +24083,7 @@
         <v>1.13</v>
       </c>
       <c r="AP112">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ112">
         <v>0.9399999999999999</v>
@@ -24193,7 +24211,7 @@
         <v>159</v>
       </c>
       <c r="P113" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q113">
         <v>3.4</v>
@@ -24271,10 +24289,10 @@
         <v>2.47</v>
       </c>
       <c r="AP113">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AQ113">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="AR113">
         <v>1.78</v>
@@ -24477,7 +24495,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="AP114">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="AQ114">
         <v>0.89</v>
@@ -24605,7 +24623,7 @@
         <v>161</v>
       </c>
       <c r="P115" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q115">
         <v>4.85</v>
@@ -25017,7 +25035,7 @@
         <v>85</v>
       </c>
       <c r="P117" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q117">
         <v>3.64</v>
@@ -25223,7 +25241,7 @@
         <v>162</v>
       </c>
       <c r="P118" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q118">
         <v>2.15</v>
@@ -25301,10 +25319,10 @@
         <v>0.75</v>
       </c>
       <c r="AP118">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ118">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="AR118">
         <v>1.48</v>
@@ -25429,7 +25447,7 @@
         <v>85</v>
       </c>
       <c r="P119" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q119">
         <v>4.4</v>
@@ -25510,7 +25528,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AQ119">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AR119">
         <v>1.42</v>
@@ -25713,10 +25731,10 @@
         <v>1.19</v>
       </c>
       <c r="AP120">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AQ120">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR120">
         <v>1.33</v>
@@ -25841,7 +25859,7 @@
         <v>163</v>
       </c>
       <c r="P121" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q121">
         <v>2.93</v>
@@ -26616,6 +26634,624 @@
       </c>
       <c r="BP124">
         <v>1.18</v>
+      </c>
+    </row>
+    <row r="125" spans="1:68">
+      <c r="A125" s="1">
+        <v>124</v>
+      </c>
+      <c r="B125">
+        <v>7813944</v>
+      </c>
+      <c r="C125" t="s">
+        <v>68</v>
+      </c>
+      <c r="D125" t="s">
+        <v>69</v>
+      </c>
+      <c r="E125" s="2">
+        <v>45837.29166666666</v>
+      </c>
+      <c r="F125">
+        <v>18</v>
+      </c>
+      <c r="G125" t="s">
+        <v>79</v>
+      </c>
+      <c r="H125" t="s">
+        <v>72</v>
+      </c>
+      <c r="I125">
+        <v>1</v>
+      </c>
+      <c r="J125">
+        <v>0</v>
+      </c>
+      <c r="K125">
+        <v>1</v>
+      </c>
+      <c r="L125">
+        <v>1</v>
+      </c>
+      <c r="M125">
+        <v>1</v>
+      </c>
+      <c r="N125">
+        <v>2</v>
+      </c>
+      <c r="O125" t="s">
+        <v>166</v>
+      </c>
+      <c r="P125" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q125">
+        <v>2.5</v>
+      </c>
+      <c r="R125">
+        <v>2.3</v>
+      </c>
+      <c r="S125">
+        <v>3.8</v>
+      </c>
+      <c r="T125">
+        <v>1.3</v>
+      </c>
+      <c r="U125">
+        <v>3.2</v>
+      </c>
+      <c r="V125">
+        <v>2.5</v>
+      </c>
+      <c r="W125">
+        <v>1.44</v>
+      </c>
+      <c r="X125">
+        <v>6</v>
+      </c>
+      <c r="Y125">
+        <v>1.11</v>
+      </c>
+      <c r="Z125">
+        <v>1.9</v>
+      </c>
+      <c r="AA125">
+        <v>3.45</v>
+      </c>
+      <c r="AB125">
+        <v>3.31</v>
+      </c>
+      <c r="AC125">
+        <v>1.01</v>
+      </c>
+      <c r="AD125">
+        <v>11</v>
+      </c>
+      <c r="AE125">
+        <v>1.21</v>
+      </c>
+      <c r="AF125">
+        <v>3.58</v>
+      </c>
+      <c r="AG125">
+        <v>1.81</v>
+      </c>
+      <c r="AH125">
+        <v>1.89</v>
+      </c>
+      <c r="AI125">
+        <v>1.67</v>
+      </c>
+      <c r="AJ125">
+        <v>2.1</v>
+      </c>
+      <c r="AK125">
+        <v>1.29</v>
+      </c>
+      <c r="AL125">
+        <v>1.3</v>
+      </c>
+      <c r="AM125">
+        <v>1.8</v>
+      </c>
+      <c r="AN125">
+        <v>2</v>
+      </c>
+      <c r="AO125">
+        <v>1.71</v>
+      </c>
+      <c r="AP125">
+        <v>1.94</v>
+      </c>
+      <c r="AQ125">
+        <v>1.67</v>
+      </c>
+      <c r="AR125">
+        <v>1.76</v>
+      </c>
+      <c r="AS125">
+        <v>1.47</v>
+      </c>
+      <c r="AT125">
+        <v>3.23</v>
+      </c>
+      <c r="AU125">
+        <v>2</v>
+      </c>
+      <c r="AV125">
+        <v>2</v>
+      </c>
+      <c r="AW125">
+        <v>10</v>
+      </c>
+      <c r="AX125">
+        <v>6</v>
+      </c>
+      <c r="AY125">
+        <v>12</v>
+      </c>
+      <c r="AZ125">
+        <v>8</v>
+      </c>
+      <c r="BA125">
+        <v>2</v>
+      </c>
+      <c r="BB125">
+        <v>7</v>
+      </c>
+      <c r="BC125">
+        <v>9</v>
+      </c>
+      <c r="BD125">
+        <v>1.67</v>
+      </c>
+      <c r="BE125">
+        <v>8</v>
+      </c>
+      <c r="BF125">
+        <v>2.54</v>
+      </c>
+      <c r="BG125">
+        <v>1.35</v>
+      </c>
+      <c r="BH125">
+        <v>2.74</v>
+      </c>
+      <c r="BI125">
+        <v>1.66</v>
+      </c>
+      <c r="BJ125">
+        <v>2.04</v>
+      </c>
+      <c r="BK125">
+        <v>2.08</v>
+      </c>
+      <c r="BL125">
+        <v>1.6</v>
+      </c>
+      <c r="BM125">
+        <v>2.81</v>
+      </c>
+      <c r="BN125">
+        <v>1.33</v>
+      </c>
+      <c r="BO125">
+        <v>3.58</v>
+      </c>
+      <c r="BP125">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="126" spans="1:68">
+      <c r="A126" s="1">
+        <v>125</v>
+      </c>
+      <c r="B126">
+        <v>7813945</v>
+      </c>
+      <c r="C126" t="s">
+        <v>68</v>
+      </c>
+      <c r="D126" t="s">
+        <v>69</v>
+      </c>
+      <c r="E126" s="2">
+        <v>45837.29166666666</v>
+      </c>
+      <c r="F126">
+        <v>18</v>
+      </c>
+      <c r="G126" t="s">
+        <v>82</v>
+      </c>
+      <c r="H126" t="s">
+        <v>83</v>
+      </c>
+      <c r="I126">
+        <v>1</v>
+      </c>
+      <c r="J126">
+        <v>0</v>
+      </c>
+      <c r="K126">
+        <v>1</v>
+      </c>
+      <c r="L126">
+        <v>2</v>
+      </c>
+      <c r="M126">
+        <v>2</v>
+      </c>
+      <c r="N126">
+        <v>4</v>
+      </c>
+      <c r="O126" t="s">
+        <v>167</v>
+      </c>
+      <c r="P126" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q126">
+        <v>3.6</v>
+      </c>
+      <c r="R126">
+        <v>2.2</v>
+      </c>
+      <c r="S126">
+        <v>2.7</v>
+      </c>
+      <c r="T126">
+        <v>1.36</v>
+      </c>
+      <c r="U126">
+        <v>2.9</v>
+      </c>
+      <c r="V126">
+        <v>2.8</v>
+      </c>
+      <c r="W126">
+        <v>1.4</v>
+      </c>
+      <c r="X126">
+        <v>7</v>
+      </c>
+      <c r="Y126">
+        <v>1.08</v>
+      </c>
+      <c r="Z126">
+        <v>2.88</v>
+      </c>
+      <c r="AA126">
+        <v>3.41</v>
+      </c>
+      <c r="AB126">
+        <v>2.08</v>
+      </c>
+      <c r="AC126">
+        <v>1.01</v>
+      </c>
+      <c r="AD126">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AE126">
+        <v>1.24</v>
+      </c>
+      <c r="AF126">
+        <v>3.34</v>
+      </c>
+      <c r="AG126">
+        <v>1.87</v>
+      </c>
+      <c r="AH126">
+        <v>1.83</v>
+      </c>
+      <c r="AI126">
+        <v>1.73</v>
+      </c>
+      <c r="AJ126">
+        <v>2.05</v>
+      </c>
+      <c r="AK126">
+        <v>1.65</v>
+      </c>
+      <c r="AL126">
+        <v>1.3</v>
+      </c>
+      <c r="AM126">
+        <v>1.36</v>
+      </c>
+      <c r="AN126">
+        <v>0.76</v>
+      </c>
+      <c r="AO126">
+        <v>1.76</v>
+      </c>
+      <c r="AP126">
+        <v>0.78</v>
+      </c>
+      <c r="AQ126">
+        <v>1.72</v>
+      </c>
+      <c r="AR126">
+        <v>1.3</v>
+      </c>
+      <c r="AS126">
+        <v>1.32</v>
+      </c>
+      <c r="AT126">
+        <v>2.62</v>
+      </c>
+      <c r="AU126">
+        <v>3</v>
+      </c>
+      <c r="AV126">
+        <v>3</v>
+      </c>
+      <c r="AW126">
+        <v>4</v>
+      </c>
+      <c r="AX126">
+        <v>3</v>
+      </c>
+      <c r="AY126">
+        <v>7</v>
+      </c>
+      <c r="AZ126">
+        <v>6</v>
+      </c>
+      <c r="BA126">
+        <v>5</v>
+      </c>
+      <c r="BB126">
+        <v>3</v>
+      </c>
+      <c r="BC126">
+        <v>8</v>
+      </c>
+      <c r="BD126">
+        <v>2.26</v>
+      </c>
+      <c r="BE126">
+        <v>5.85</v>
+      </c>
+      <c r="BF126">
+        <v>1.98</v>
+      </c>
+      <c r="BG126">
+        <v>1.49</v>
+      </c>
+      <c r="BH126">
+        <v>2.3</v>
+      </c>
+      <c r="BI126">
+        <v>1.89</v>
+      </c>
+      <c r="BJ126">
+        <v>1.77</v>
+      </c>
+      <c r="BK126">
+        <v>2.49</v>
+      </c>
+      <c r="BL126">
+        <v>1.42</v>
+      </c>
+      <c r="BM126">
+        <v>3.5</v>
+      </c>
+      <c r="BN126">
+        <v>1.22</v>
+      </c>
+      <c r="BO126">
+        <v>4.5</v>
+      </c>
+      <c r="BP126">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="127" spans="1:68">
+      <c r="A127" s="1">
+        <v>126</v>
+      </c>
+      <c r="B127">
+        <v>7813946</v>
+      </c>
+      <c r="C127" t="s">
+        <v>68</v>
+      </c>
+      <c r="D127" t="s">
+        <v>69</v>
+      </c>
+      <c r="E127" s="2">
+        <v>45837.29166666666</v>
+      </c>
+      <c r="F127">
+        <v>18</v>
+      </c>
+      <c r="G127" t="s">
+        <v>78</v>
+      </c>
+      <c r="H127" t="s">
+        <v>70</v>
+      </c>
+      <c r="I127">
+        <v>1</v>
+      </c>
+      <c r="J127">
+        <v>0</v>
+      </c>
+      <c r="K127">
+        <v>1</v>
+      </c>
+      <c r="L127">
+        <v>1</v>
+      </c>
+      <c r="M127">
+        <v>1</v>
+      </c>
+      <c r="N127">
+        <v>2</v>
+      </c>
+      <c r="O127" t="s">
+        <v>168</v>
+      </c>
+      <c r="P127" t="s">
+        <v>237</v>
+      </c>
+      <c r="Q127">
+        <v>4.33</v>
+      </c>
+      <c r="R127">
+        <v>2.1</v>
+      </c>
+      <c r="S127">
+        <v>2.5</v>
+      </c>
+      <c r="T127">
+        <v>1.4</v>
+      </c>
+      <c r="U127">
+        <v>2.75</v>
+      </c>
+      <c r="V127">
+        <v>3</v>
+      </c>
+      <c r="W127">
+        <v>1.36</v>
+      </c>
+      <c r="X127">
+        <v>8.5</v>
+      </c>
+      <c r="Y127">
+        <v>1.07</v>
+      </c>
+      <c r="Z127">
+        <v>3.69</v>
+      </c>
+      <c r="AA127">
+        <v>3.21</v>
+      </c>
+      <c r="AB127">
+        <v>1.86</v>
+      </c>
+      <c r="AC127">
+        <v>1.01</v>
+      </c>
+      <c r="AD127">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AE127">
+        <v>1.34</v>
+      </c>
+      <c r="AF127">
+        <v>2.78</v>
+      </c>
+      <c r="AG127">
+        <v>2</v>
+      </c>
+      <c r="AH127">
+        <v>1.65</v>
+      </c>
+      <c r="AI127">
+        <v>1.91</v>
+      </c>
+      <c r="AJ127">
+        <v>1.83</v>
+      </c>
+      <c r="AK127">
+        <v>1.85</v>
+      </c>
+      <c r="AL127">
+        <v>1.33</v>
+      </c>
+      <c r="AM127">
+        <v>1.22</v>
+      </c>
+      <c r="AN127">
+        <v>1.18</v>
+      </c>
+      <c r="AO127">
+        <v>2.53</v>
+      </c>
+      <c r="AP127">
+        <v>1.17</v>
+      </c>
+      <c r="AQ127">
+        <v>2.44</v>
+      </c>
+      <c r="AR127">
+        <v>1.46</v>
+      </c>
+      <c r="AS127">
+        <v>1.5</v>
+      </c>
+      <c r="AT127">
+        <v>2.96</v>
+      </c>
+      <c r="AU127">
+        <v>2</v>
+      </c>
+      <c r="AV127">
+        <v>2</v>
+      </c>
+      <c r="AW127">
+        <v>2</v>
+      </c>
+      <c r="AX127">
+        <v>5</v>
+      </c>
+      <c r="AY127">
+        <v>4</v>
+      </c>
+      <c r="AZ127">
+        <v>7</v>
+      </c>
+      <c r="BA127">
+        <v>0</v>
+      </c>
+      <c r="BB127">
+        <v>4</v>
+      </c>
+      <c r="BC127">
+        <v>4</v>
+      </c>
+      <c r="BD127">
+        <v>2.26</v>
+      </c>
+      <c r="BE127">
+        <v>5.8</v>
+      </c>
+      <c r="BF127">
+        <v>1.99</v>
+      </c>
+      <c r="BG127">
+        <v>1.57</v>
+      </c>
+      <c r="BH127">
+        <v>2.14</v>
+      </c>
+      <c r="BI127">
+        <v>2.03</v>
+      </c>
+      <c r="BJ127">
+        <v>1.67</v>
+      </c>
+      <c r="BK127">
+        <v>2.7</v>
+      </c>
+      <c r="BL127">
+        <v>1.36</v>
+      </c>
+      <c r="BM127">
+        <v>3.86</v>
+      </c>
+      <c r="BN127">
+        <v>1.18</v>
+      </c>
+      <c r="BO127">
+        <v>4.95</v>
+      </c>
+      <c r="BP127">
+        <v>1.12</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
@@ -26776,31 +26776,31 @@
         <v>3.23</v>
       </c>
       <c r="AU125">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV125">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AW125">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX125">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY125">
         <v>12</v>
       </c>
       <c r="AZ125">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="BA125">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB125">
         <v>7</v>
       </c>
       <c r="BC125">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD125">
         <v>1.67</v>
@@ -26982,22 +26982,22 @@
         <v>2.62</v>
       </c>
       <c r="AU126">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AV126">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW126">
+        <v>5</v>
+      </c>
+      <c r="AX126">
         <v>4</v>
       </c>
-      <c r="AX126">
-        <v>3</v>
-      </c>
       <c r="AY126">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AZ126">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BA126">
         <v>5</v>
@@ -27188,7 +27188,7 @@
         <v>2.96</v>
       </c>
       <c r="AU127">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AV127">
         <v>2</v>
@@ -27197,13 +27197,13 @@
         <v>2</v>
       </c>
       <c r="AX127">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AY127">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AZ127">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BA127">
         <v>0</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
@@ -1423,10 +1423,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.44</v>
+        <v>2.8</v>
       </c>
       <c r="AQ2">
-        <v>0.9399999999999999</v>
+        <v>0.78</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1629,10 +1629,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.78</v>
+        <v>1.11</v>
       </c>
       <c r="AQ3">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1835,10 +1835,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="AQ4">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2041,10 +2041,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>0.9399999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="AQ5">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2247,10 +2247,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AQ6">
-        <v>0.89</v>
+        <v>0.44</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2453,10 +2453,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.61</v>
+        <v>1.89</v>
       </c>
       <c r="AQ7">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2659,10 +2659,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.72</v>
+        <v>1.89</v>
       </c>
       <c r="AQ8">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2865,10 +2865,10 @@
         <v>3</v>
       </c>
       <c r="AP9">
-        <v>2.44</v>
+        <v>2.8</v>
       </c>
       <c r="AQ9">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="AR9">
         <v>2.58</v>
@@ -3071,10 +3071,10 @@
         <v>1</v>
       </c>
       <c r="AP10">
-        <v>0.9399999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="AQ10">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AR10">
         <v>0.82</v>
@@ -3277,10 +3277,10 @@
         <v>3</v>
       </c>
       <c r="AP11">
-        <v>1.61</v>
+        <v>1.89</v>
       </c>
       <c r="AQ11">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AR11">
         <v>1.04</v>
@@ -3483,19 +3483,19 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>0.89</v>
+        <v>1.33</v>
       </c>
       <c r="AQ12">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AR12">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AS12">
         <v>0.92</v>
       </c>
       <c r="AT12">
-        <v>1.72</v>
+        <v>0.92</v>
       </c>
       <c r="AU12">
         <v>6</v>
@@ -3689,10 +3689,10 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="AQ13">
-        <v>0.9399999999999999</v>
+        <v>0.78</v>
       </c>
       <c r="AR13">
         <v>1.4</v>
@@ -3892,22 +3892,22 @@
         <v>0</v>
       </c>
       <c r="AO14">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP14">
-        <v>0.78</v>
+        <v>1.11</v>
       </c>
       <c r="AQ14">
-        <v>1.72</v>
+        <v>1.56</v>
       </c>
       <c r="AR14">
         <v>1.15</v>
       </c>
       <c r="AS14">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AT14">
-        <v>2.76</v>
+        <v>1.15</v>
       </c>
       <c r="AU14">
         <v>3</v>
@@ -4101,10 +4101,10 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AQ15">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR15">
         <v>0.82</v>
@@ -4304,22 +4304,22 @@
         <v>3</v>
       </c>
       <c r="AO16">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.72</v>
+        <v>1.89</v>
       </c>
       <c r="AQ16">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="AR16">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AS16">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AT16">
-        <v>3.06</v>
+        <v>1.61</v>
       </c>
       <c r="AU16">
         <v>2</v>
@@ -4507,25 +4507,25 @@
         <v>1.57</v>
       </c>
       <c r="AN17">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AO17">
         <v>1.5</v>
       </c>
       <c r="AP17">
-        <v>0.89</v>
+        <v>1.33</v>
       </c>
       <c r="AQ17">
-        <v>0.9399999999999999</v>
+        <v>0.78</v>
       </c>
       <c r="AR17">
-        <v>1.16</v>
+        <v>1.52</v>
       </c>
       <c r="AS17">
         <v>0.89</v>
       </c>
       <c r="AT17">
-        <v>2.05</v>
+        <v>2.41</v>
       </c>
       <c r="AU17">
         <v>4</v>
@@ -4719,10 +4719,10 @@
         <v>2</v>
       </c>
       <c r="AP18">
-        <v>0.9399999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="AQ18">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AR18">
         <v>1.29</v>
@@ -4919,25 +4919,25 @@
         <v>1.71</v>
       </c>
       <c r="AN19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO19">
         <v>0.5</v>
       </c>
       <c r="AP19">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AQ19">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR19">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AS19">
         <v>0.73</v>
       </c>
       <c r="AT19">
-        <v>2.16</v>
+        <v>0.73</v>
       </c>
       <c r="AU19">
         <v>9</v>
@@ -5131,10 +5131,10 @@
         <v>1.5</v>
       </c>
       <c r="AP20">
-        <v>1.61</v>
+        <v>1.89</v>
       </c>
       <c r="AQ20">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="AR20">
         <v>1.06</v>
@@ -5337,10 +5337,10 @@
         <v>0.5</v>
       </c>
       <c r="AP21">
-        <v>0.78</v>
+        <v>1.11</v>
       </c>
       <c r="AQ21">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AR21">
         <v>1.02</v>
@@ -5540,22 +5540,22 @@
         <v>2</v>
       </c>
       <c r="AO22">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AQ22">
-        <v>2.44</v>
+        <v>2</v>
       </c>
       <c r="AR22">
         <v>0.92</v>
       </c>
       <c r="AS22">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AT22">
-        <v>2.85</v>
+        <v>0.92</v>
       </c>
       <c r="AU22">
         <v>5</v>
@@ -5743,25 +5743,25 @@
         <v>1.7</v>
       </c>
       <c r="AN23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO23">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AP23">
-        <v>2.44</v>
+        <v>2.8</v>
       </c>
       <c r="AQ23">
-        <v>1.61</v>
+        <v>1.33</v>
       </c>
       <c r="AR23">
-        <v>1.7</v>
+        <v>1.93</v>
       </c>
       <c r="AS23">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AT23">
-        <v>2.75</v>
+        <v>1.93</v>
       </c>
       <c r="AU23">
         <v>2</v>
@@ -5949,25 +5949,25 @@
         <v>1.61</v>
       </c>
       <c r="AN24">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AO24">
         <v>1.33</v>
       </c>
       <c r="AP24">
-        <v>0.89</v>
+        <v>1.33</v>
       </c>
       <c r="AQ24">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR24">
-        <v>1.21</v>
+        <v>1.41</v>
       </c>
       <c r="AS24">
         <v>0.87</v>
       </c>
       <c r="AT24">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="AU24">
         <v>9</v>
@@ -6155,25 +6155,25 @@
         <v>1.8</v>
       </c>
       <c r="AN25">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AO25">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AQ25">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR25">
-        <v>1.64</v>
+        <v>2.07</v>
       </c>
       <c r="AS25">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AT25">
-        <v>2.66</v>
+        <v>2.07</v>
       </c>
       <c r="AU25">
         <v>3</v>
@@ -6361,25 +6361,25 @@
         <v>1.75</v>
       </c>
       <c r="AN26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO26">
         <v>0.33</v>
       </c>
       <c r="AP26">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AQ26">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AR26">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AS26">
         <v>1.45</v>
       </c>
       <c r="AT26">
-        <v>3.14</v>
+        <v>1.45</v>
       </c>
       <c r="AU26">
         <v>2</v>
@@ -6567,25 +6567,25 @@
         <v>2.2</v>
       </c>
       <c r="AN27">
-        <v>1.33</v>
+        <v>0.5</v>
       </c>
       <c r="AO27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="AQ27">
-        <v>0.78</v>
+        <v>0.44</v>
       </c>
       <c r="AR27">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AS27">
-        <v>0.98</v>
+        <v>0</v>
       </c>
       <c r="AT27">
-        <v>2.25</v>
+        <v>1.42</v>
       </c>
       <c r="AU27">
         <v>8</v>
@@ -6773,25 +6773,25 @@
         <v>1.3</v>
       </c>
       <c r="AN28">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AO28">
         <v>2.33</v>
       </c>
       <c r="AP28">
-        <v>0.9399999999999999</v>
+        <v>1.11</v>
       </c>
       <c r="AQ28">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AR28">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AS28">
         <v>1.3</v>
       </c>
       <c r="AT28">
-        <v>2.35</v>
+        <v>1.3</v>
       </c>
       <c r="AU28">
         <v>3</v>
@@ -6979,25 +6979,25 @@
         <v>2.15</v>
       </c>
       <c r="AN29">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AO29">
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.72</v>
+        <v>1.89</v>
       </c>
       <c r="AQ29">
-        <v>0.9399999999999999</v>
+        <v>1.13</v>
       </c>
       <c r="AR29">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="AS29">
+        <v>0</v>
+      </c>
+      <c r="AT29">
         <v>1.22</v>
-      </c>
-      <c r="AT29">
-        <v>2.59</v>
       </c>
       <c r="AU29">
         <v>5</v>
@@ -7188,22 +7188,22 @@
         <v>0</v>
       </c>
       <c r="AO30">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AP30">
-        <v>0.9399999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="AQ30">
-        <v>0.89</v>
+        <v>0.44</v>
       </c>
       <c r="AR30">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AS30">
-        <v>1.41</v>
+        <v>0.8</v>
       </c>
       <c r="AT30">
-        <v>2.54</v>
+        <v>2.02</v>
       </c>
       <c r="AU30">
         <v>7</v>
@@ -7397,19 +7397,19 @@
         <v>2</v>
       </c>
       <c r="AP31">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AQ31">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AR31">
-        <v>1.56</v>
+        <v>1.17</v>
       </c>
       <c r="AS31">
         <v>1.26</v>
       </c>
       <c r="AT31">
-        <v>2.82</v>
+        <v>2.43</v>
       </c>
       <c r="AU31">
         <v>8</v>
@@ -7597,25 +7597,25 @@
         <v>1.53</v>
       </c>
       <c r="AN32">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AO32">
         <v>1</v>
       </c>
       <c r="AP32">
-        <v>0.9399999999999999</v>
+        <v>1.11</v>
       </c>
       <c r="AQ32">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR32">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AS32">
         <v>1.11</v>
       </c>
       <c r="AT32">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AU32">
         <v>9</v>
@@ -7803,25 +7803,25 @@
         <v>1.61</v>
       </c>
       <c r="AN33">
+        <v>3</v>
+      </c>
+      <c r="AO33">
+        <v>3</v>
+      </c>
+      <c r="AP33">
+        <v>2.8</v>
+      </c>
+      <c r="AQ33">
         <v>2.25</v>
       </c>
-      <c r="AO33">
-        <v>1.75</v>
-      </c>
-      <c r="AP33">
-        <v>2.44</v>
-      </c>
-      <c r="AQ33">
-        <v>1.67</v>
-      </c>
       <c r="AR33">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="AS33">
-        <v>1.44</v>
+        <v>0.97</v>
       </c>
       <c r="AT33">
-        <v>3.01</v>
+        <v>2.66</v>
       </c>
       <c r="AU33">
         <v>2</v>
@@ -8009,25 +8009,25 @@
         <v>1.29</v>
       </c>
       <c r="AN34">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AO34">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="AP34">
-        <v>0.78</v>
+        <v>1.11</v>
       </c>
       <c r="AQ34">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AR34">
-        <v>0.87</v>
+        <v>0.98</v>
       </c>
       <c r="AS34">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AT34">
-        <v>2.35</v>
+        <v>2.41</v>
       </c>
       <c r="AU34">
         <v>3</v>
@@ -8215,25 +8215,25 @@
         <v>1.57</v>
       </c>
       <c r="AN35">
-        <v>1.75</v>
+        <v>2.33</v>
       </c>
       <c r="AO35">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="AP35">
-        <v>1.61</v>
+        <v>1.89</v>
       </c>
       <c r="AQ35">
-        <v>1.72</v>
+        <v>1.56</v>
       </c>
       <c r="AR35">
-        <v>0.9</v>
+        <v>1.05</v>
       </c>
       <c r="AS35">
-        <v>1.42</v>
+        <v>1.67</v>
       </c>
       <c r="AT35">
-        <v>2.32</v>
+        <v>2.72</v>
       </c>
       <c r="AU35">
         <v>5</v>
@@ -8421,25 +8421,25 @@
         <v>1.88</v>
       </c>
       <c r="AN36">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AO36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP36">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AQ36">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR36">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AS36">
-        <v>0.98</v>
+        <v>0.85</v>
       </c>
       <c r="AT36">
-        <v>2.32</v>
+        <v>0.85</v>
       </c>
       <c r="AU36">
         <v>8</v>
@@ -8627,25 +8627,25 @@
         <v>0</v>
       </c>
       <c r="AN37">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AO37">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="AP37">
-        <v>1.61</v>
+        <v>1.89</v>
       </c>
       <c r="AQ37">
-        <v>0.78</v>
+        <v>0.44</v>
       </c>
       <c r="AR37">
-        <v>0.98</v>
+        <v>1.11</v>
       </c>
       <c r="AS37">
-        <v>0.91</v>
+        <v>0.52</v>
       </c>
       <c r="AT37">
-        <v>1.89</v>
+        <v>1.63</v>
       </c>
       <c r="AU37">
         <v>7</v>
@@ -8833,25 +8833,25 @@
         <v>0</v>
       </c>
       <c r="AN38">
-        <v>1.2</v>
+        <v>1.67</v>
       </c>
       <c r="AO38">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AP38">
-        <v>0.89</v>
+        <v>1.33</v>
       </c>
       <c r="AQ38">
-        <v>2.44</v>
+        <v>2</v>
       </c>
       <c r="AR38">
-        <v>1.37</v>
+        <v>1.61</v>
       </c>
       <c r="AS38">
-        <v>1.55</v>
+        <v>1.24</v>
       </c>
       <c r="AT38">
-        <v>2.92</v>
+        <v>2.85</v>
       </c>
       <c r="AU38">
         <v>4</v>
@@ -9039,25 +9039,25 @@
         <v>1.55</v>
       </c>
       <c r="AN39">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AO39">
         <v>1.6</v>
       </c>
       <c r="AP39">
+        <v>1.2</v>
+      </c>
+      <c r="AQ39">
         <v>1.67</v>
       </c>
-      <c r="AQ39">
-        <v>1.72</v>
-      </c>
       <c r="AR39">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="AS39">
         <v>1.35</v>
       </c>
       <c r="AT39">
-        <v>2.73</v>
+        <v>2.95</v>
       </c>
       <c r="AU39">
         <v>5</v>
@@ -9245,25 +9245,25 @@
         <v>2.2</v>
       </c>
       <c r="AN40">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="AO40">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AP40">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AQ40">
-        <v>0.9399999999999999</v>
+        <v>0.78</v>
       </c>
       <c r="AR40">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AS40">
-        <v>1.32</v>
+        <v>1.05</v>
       </c>
       <c r="AT40">
-        <v>2.98</v>
+        <v>2.67</v>
       </c>
       <c r="AU40">
         <v>8</v>
@@ -9451,25 +9451,25 @@
         <v>1.44</v>
       </c>
       <c r="AN41">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="AO41">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AP41">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AQ41">
-        <v>1.72</v>
+        <v>1.56</v>
       </c>
       <c r="AR41">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="AS41">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AT41">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="AU41">
         <v>5</v>
@@ -9657,25 +9657,25 @@
         <v>1.85</v>
       </c>
       <c r="AN42">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AO42">
         <v>0.8</v>
       </c>
       <c r="AP42">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AQ42">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR42">
-        <v>1.44</v>
+        <v>1.85</v>
       </c>
       <c r="AS42">
         <v>1.12</v>
       </c>
       <c r="AT42">
-        <v>2.56</v>
+        <v>2.97</v>
       </c>
       <c r="AU42">
         <v>7</v>
@@ -9863,25 +9863,25 @@
         <v>1.67</v>
       </c>
       <c r="AN43">
-        <v>1.8</v>
+        <v>2.33</v>
       </c>
       <c r="AO43">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AP43">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AQ43">
-        <v>0.9399999999999999</v>
+        <v>1.13</v>
       </c>
       <c r="AR43">
-        <v>0.96</v>
+        <v>1.02</v>
       </c>
       <c r="AS43">
-        <v>1.22</v>
+        <v>0.83</v>
       </c>
       <c r="AT43">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="AU43">
         <v>4</v>
@@ -10069,25 +10069,25 @@
         <v>1.44</v>
       </c>
       <c r="AN44">
+        <v>0.33</v>
+      </c>
+      <c r="AO44">
+        <v>0.5</v>
+      </c>
+      <c r="AP44">
+        <v>1.2</v>
+      </c>
+      <c r="AQ44">
         <v>1.33</v>
       </c>
-      <c r="AO44">
-        <v>1</v>
-      </c>
-      <c r="AP44">
-        <v>1.17</v>
-      </c>
-      <c r="AQ44">
-        <v>1.39</v>
-      </c>
       <c r="AR44">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AS44">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="AT44">
-        <v>2.94</v>
+        <v>2.77</v>
       </c>
       <c r="AU44">
         <v>6</v>
@@ -10275,25 +10275,25 @@
         <v>1.36</v>
       </c>
       <c r="AN45">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AO45">
         <v>1.83</v>
       </c>
       <c r="AP45">
-        <v>0.89</v>
+        <v>1.33</v>
       </c>
       <c r="AQ45">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AR45">
-        <v>1.34</v>
+        <v>1.49</v>
       </c>
       <c r="AS45">
         <v>1.33</v>
       </c>
       <c r="AT45">
-        <v>2.67</v>
+        <v>2.82</v>
       </c>
       <c r="AU45">
         <v>5</v>
@@ -10484,22 +10484,22 @@
         <v>2</v>
       </c>
       <c r="AO46">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="AP46">
-        <v>1.72</v>
+        <v>1.89</v>
       </c>
       <c r="AQ46">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="AR46">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AS46">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AT46">
-        <v>3.14</v>
+        <v>3.02</v>
       </c>
       <c r="AU46">
         <v>6</v>
@@ -10687,25 +10687,25 @@
         <v>1.65</v>
       </c>
       <c r="AN47">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="AO47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP47">
-        <v>0.9399999999999999</v>
+        <v>1.11</v>
       </c>
       <c r="AQ47">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR47">
-        <v>1.33</v>
+        <v>1.74</v>
       </c>
       <c r="AS47">
-        <v>1.02</v>
+        <v>0.86</v>
       </c>
       <c r="AT47">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="AU47">
         <v>4</v>
@@ -10893,25 +10893,25 @@
         <v>2.38</v>
       </c>
       <c r="AN48">
-        <v>2.17</v>
+        <v>2.5</v>
       </c>
       <c r="AO48">
         <v>0.67</v>
       </c>
       <c r="AP48">
-        <v>2.44</v>
+        <v>2.8</v>
       </c>
       <c r="AQ48">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR48">
-        <v>1.54</v>
+        <v>1.63</v>
       </c>
       <c r="AS48">
         <v>1.19</v>
       </c>
       <c r="AT48">
-        <v>2.73</v>
+        <v>2.82</v>
       </c>
       <c r="AU48">
         <v>6</v>
@@ -11099,25 +11099,25 @@
         <v>1.55</v>
       </c>
       <c r="AN49">
+        <v>1</v>
+      </c>
+      <c r="AO49">
+        <v>0</v>
+      </c>
+      <c r="AP49">
+        <v>1.2</v>
+      </c>
+      <c r="AQ49">
         <v>1.33</v>
       </c>
-      <c r="AO49">
-        <v>2.17</v>
-      </c>
-      <c r="AP49">
-        <v>1.67</v>
-      </c>
-      <c r="AQ49">
-        <v>1.61</v>
-      </c>
       <c r="AR49">
-        <v>1.4</v>
+        <v>1.58</v>
       </c>
       <c r="AS49">
-        <v>1.07</v>
+        <v>0.43</v>
       </c>
       <c r="AT49">
-        <v>2.47</v>
+        <v>2.01</v>
       </c>
       <c r="AU49">
         <v>9</v>
@@ -11305,25 +11305,25 @@
         <v>1.67</v>
       </c>
       <c r="AN50">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="AO50">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="AP50">
-        <v>0.78</v>
+        <v>1.11</v>
       </c>
       <c r="AQ50">
-        <v>0.9399999999999999</v>
+        <v>1.13</v>
       </c>
       <c r="AR50">
-        <v>0.9399999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AS50">
-        <v>1.2</v>
+        <v>0.96</v>
       </c>
       <c r="AT50">
-        <v>2.14</v>
+        <v>1.97</v>
       </c>
       <c r="AU50">
         <v>3</v>
@@ -11511,25 +11511,25 @@
         <v>2.2</v>
       </c>
       <c r="AN51">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="AO51">
         <v>0.57</v>
       </c>
       <c r="AP51">
-        <v>1.61</v>
+        <v>1.89</v>
       </c>
       <c r="AQ51">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR51">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AS51">
         <v>1.24</v>
       </c>
       <c r="AT51">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="AU51">
         <v>4</v>
@@ -11717,25 +11717,25 @@
         <v>2.7</v>
       </c>
       <c r="AN52">
-        <v>2.29</v>
+        <v>2.6</v>
       </c>
       <c r="AO52">
-        <v>0.43</v>
+        <v>0</v>
       </c>
       <c r="AP52">
-        <v>2.44</v>
+        <v>2.8</v>
       </c>
       <c r="AQ52">
-        <v>0.78</v>
+        <v>0.44</v>
       </c>
       <c r="AR52">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AS52">
-        <v>1.01</v>
+        <v>0.8</v>
       </c>
       <c r="AT52">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="AU52">
         <v>6</v>
@@ -11923,25 +11923,25 @@
         <v>2.3</v>
       </c>
       <c r="AN53">
-        <v>1.57</v>
+        <v>2.33</v>
       </c>
       <c r="AO53">
-        <v>0.86</v>
+        <v>0.5</v>
       </c>
       <c r="AP53">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AQ53">
-        <v>0.89</v>
+        <v>0.44</v>
       </c>
       <c r="AR53">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AS53">
-        <v>1.32</v>
+        <v>1.02</v>
       </c>
       <c r="AT53">
-        <v>3.02</v>
+        <v>2.77</v>
       </c>
       <c r="AU53">
         <v>7</v>
@@ -12129,25 +12129,25 @@
         <v>1.3</v>
       </c>
       <c r="AN54">
-        <v>2.14</v>
+        <v>2.5</v>
       </c>
       <c r="AO54">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AP54">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AQ54">
-        <v>1.72</v>
+        <v>1.56</v>
       </c>
       <c r="AR54">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="AS54">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AT54">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="AU54">
         <v>2</v>
@@ -12335,25 +12335,25 @@
         <v>1.22</v>
       </c>
       <c r="AN55">
-        <v>0.57</v>
+        <v>0.25</v>
       </c>
       <c r="AO55">
-        <v>1.29</v>
+        <v>2</v>
       </c>
       <c r="AP55">
-        <v>0.9399999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="AQ55">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="AR55">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="AS55">
-        <v>1.46</v>
+        <v>1.04</v>
       </c>
       <c r="AT55">
-        <v>2.64</v>
+        <v>2.36</v>
       </c>
       <c r="AU55">
         <v>5</v>
@@ -12541,25 +12541,25 @@
         <v>1.53</v>
       </c>
       <c r="AN56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO56">
         <v>2</v>
       </c>
       <c r="AP56">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AQ56">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AR56">
-        <v>1.46</v>
+        <v>1.83</v>
       </c>
       <c r="AS56">
         <v>1.29</v>
       </c>
       <c r="AT56">
-        <v>2.75</v>
+        <v>3.12</v>
       </c>
       <c r="AU56">
         <v>7</v>
@@ -12747,25 +12747,25 @@
         <v>1.36</v>
       </c>
       <c r="AN57">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AO57">
-        <v>1.29</v>
+        <v>2.33</v>
       </c>
       <c r="AP57">
-        <v>0.9399999999999999</v>
+        <v>1.11</v>
       </c>
       <c r="AQ57">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AR57">
-        <v>1.41</v>
+        <v>1.79</v>
       </c>
       <c r="AS57">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AT57">
-        <v>2.91</v>
+        <v>3.24</v>
       </c>
       <c r="AU57">
         <v>9</v>
@@ -12953,25 +12953,25 @@
         <v>2.1</v>
       </c>
       <c r="AN58">
-        <v>1.75</v>
+        <v>2.17</v>
       </c>
       <c r="AO58">
-        <v>1.38</v>
+        <v>1</v>
       </c>
       <c r="AP58">
-        <v>1.61</v>
+        <v>1.89</v>
       </c>
       <c r="AQ58">
-        <v>0.9399999999999999</v>
+        <v>0.78</v>
       </c>
       <c r="AR58">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AS58">
-        <v>1.45</v>
+        <v>1.13</v>
       </c>
       <c r="AT58">
-        <v>2.73</v>
+        <v>2.44</v>
       </c>
       <c r="AU58">
         <v>4</v>
@@ -13159,25 +13159,25 @@
         <v>1.53</v>
       </c>
       <c r="AN59">
-        <v>0.38</v>
+        <v>0.6</v>
       </c>
       <c r="AO59">
         <v>0.88</v>
       </c>
       <c r="AP59">
-        <v>0.78</v>
+        <v>1.11</v>
       </c>
       <c r="AQ59">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR59">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AS59">
         <v>1.26</v>
       </c>
       <c r="AT59">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="AU59">
         <v>2</v>
@@ -13365,25 +13365,25 @@
         <v>2.15</v>
       </c>
       <c r="AN60">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AO60">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AP60">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AQ60">
-        <v>0.9399999999999999</v>
+        <v>1.13</v>
       </c>
       <c r="AR60">
-        <v>1.58</v>
+        <v>2.02</v>
       </c>
       <c r="AS60">
-        <v>1.24</v>
+        <v>0.99</v>
       </c>
       <c r="AT60">
-        <v>2.82</v>
+        <v>3.01</v>
       </c>
       <c r="AU60">
         <v>7</v>
@@ -13574,22 +13574,22 @@
         <v>1.75</v>
       </c>
       <c r="AO61">
-        <v>2.38</v>
+        <v>1.5</v>
       </c>
       <c r="AP61">
-        <v>1.72</v>
+        <v>1.89</v>
       </c>
       <c r="AQ61">
-        <v>2.44</v>
+        <v>2</v>
       </c>
       <c r="AR61">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="AS61">
-        <v>1.54</v>
+        <v>1.35</v>
       </c>
       <c r="AT61">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="AU61">
         <v>6</v>
@@ -13777,25 +13777,25 @@
         <v>2.2</v>
       </c>
       <c r="AN62">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="AO62">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AP62">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AQ62">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR62">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="AS62">
-        <v>1.01</v>
+        <v>0.92</v>
       </c>
       <c r="AT62">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="AU62">
         <v>7</v>
@@ -13983,25 +13983,25 @@
         <v>1.5</v>
       </c>
       <c r="AN63">
-        <v>1.13</v>
+        <v>0.5</v>
       </c>
       <c r="AO63">
         <v>1.88</v>
       </c>
       <c r="AP63">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AQ63">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AR63">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="AS63">
         <v>1.28</v>
       </c>
       <c r="AT63">
-        <v>2.71</v>
+        <v>2.82</v>
       </c>
       <c r="AU63">
         <v>8</v>
@@ -14189,22 +14189,22 @@
         <v>1.95</v>
       </c>
       <c r="AN64">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AO64">
-        <v>0.75</v>
+        <v>0.33</v>
       </c>
       <c r="AP64">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="AQ64">
-        <v>0.89</v>
+        <v>0.44</v>
       </c>
       <c r="AR64">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="AS64">
-        <v>1.31</v>
+        <v>1.09</v>
       </c>
       <c r="AT64">
         <v>2.72</v>
@@ -14395,25 +14395,25 @@
         <v>0</v>
       </c>
       <c r="AN65">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
       <c r="AO65">
-        <v>1.89</v>
+        <v>0.5</v>
       </c>
       <c r="AP65">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AQ65">
-        <v>1.61</v>
+        <v>1.33</v>
       </c>
       <c r="AR65">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AS65">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AT65">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="AU65">
         <v>3</v>
@@ -14601,25 +14601,25 @@
         <v>0</v>
       </c>
       <c r="AN66">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AO66">
         <v>2</v>
       </c>
       <c r="AP66">
-        <v>1.72</v>
+        <v>1.89</v>
       </c>
       <c r="AQ66">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AR66">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AS66">
         <v>1.25</v>
       </c>
       <c r="AT66">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="AU66">
         <v>4</v>
@@ -14807,25 +14807,25 @@
         <v>0</v>
       </c>
       <c r="AN67">
-        <v>0.44</v>
+        <v>0.2</v>
       </c>
       <c r="AO67">
-        <v>1.22</v>
+        <v>0.8</v>
       </c>
       <c r="AP67">
-        <v>0.9399999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="AQ67">
-        <v>0.9399999999999999</v>
+        <v>0.78</v>
       </c>
       <c r="AR67">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AS67">
-        <v>1.43</v>
+        <v>1.16</v>
       </c>
       <c r="AT67">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="AU67">
         <v>3</v>
@@ -15013,25 +15013,25 @@
         <v>0</v>
       </c>
       <c r="AN68">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AO68">
-        <v>1.89</v>
+        <v>1</v>
       </c>
       <c r="AP68">
-        <v>0.78</v>
+        <v>0.43</v>
       </c>
       <c r="AQ68">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="AR68">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AS68">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AT68">
-        <v>2.98</v>
+        <v>1.66</v>
       </c>
       <c r="AU68">
         <v>6</v>
@@ -15219,25 +15219,25 @@
         <v>0</v>
       </c>
       <c r="AN69">
-        <v>2.44</v>
+        <v>2.67</v>
       </c>
       <c r="AO69">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="AP69">
-        <v>2.44</v>
+        <v>2.8</v>
       </c>
       <c r="AQ69">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AR69">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="AS69">
-        <v>1.51</v>
+        <v>1.31</v>
       </c>
       <c r="AT69">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="AU69">
         <v>6</v>
@@ -15425,25 +15425,25 @@
         <v>0</v>
       </c>
       <c r="AN70">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="AO70">
-        <v>1.22</v>
+        <v>0.6</v>
       </c>
       <c r="AP70">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="AQ70">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AR70">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="AS70">
-        <v>1.61</v>
+        <v>1.32</v>
       </c>
       <c r="AT70">
-        <v>3.11</v>
+        <v>3.04</v>
       </c>
       <c r="AU70">
         <v>6</v>
@@ -15631,25 +15631,25 @@
         <v>0</v>
       </c>
       <c r="AN71">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AO71">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AP71">
-        <v>0.89</v>
+        <v>1.33</v>
       </c>
       <c r="AQ71">
-        <v>0.78</v>
+        <v>0.44</v>
       </c>
       <c r="AR71">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AS71">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="AT71">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="AU71">
         <v>5</v>
@@ -15837,25 +15837,25 @@
         <v>0</v>
       </c>
       <c r="AN72">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="AO72">
-        <v>0.9</v>
+        <v>0.25</v>
       </c>
       <c r="AP72">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AQ72">
-        <v>0.89</v>
+        <v>0.44</v>
       </c>
       <c r="AR72">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AS72">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AT72">
-        <v>2.79</v>
+        <v>2.92</v>
       </c>
       <c r="AU72">
         <v>2</v>
@@ -16043,25 +16043,25 @@
         <v>0</v>
       </c>
       <c r="AN73">
-        <v>1.1</v>
+        <v>1.75</v>
       </c>
       <c r="AO73">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AP73">
-        <v>0.9399999999999999</v>
+        <v>1.11</v>
       </c>
       <c r="AQ73">
-        <v>1.72</v>
+        <v>1.56</v>
       </c>
       <c r="AR73">
-        <v>1.4</v>
+        <v>1.77</v>
       </c>
       <c r="AS73">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AT73">
-        <v>2.86</v>
+        <v>3.29</v>
       </c>
       <c r="AU73">
         <v>5</v>
@@ -16249,25 +16249,25 @@
         <v>0</v>
       </c>
       <c r="AN74">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="AO74">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AP74">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AQ74">
-        <v>2.44</v>
+        <v>2</v>
       </c>
       <c r="AR74">
-        <v>1.57</v>
+        <v>1.98</v>
       </c>
       <c r="AS74">
-        <v>1.53</v>
+        <v>1.27</v>
       </c>
       <c r="AT74">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AU74">
         <v>3</v>
@@ -16455,25 +16455,25 @@
         <v>0</v>
       </c>
       <c r="AN75">
-        <v>2</v>
+        <v>2.29</v>
       </c>
       <c r="AO75">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="AP75">
-        <v>1.61</v>
+        <v>1.89</v>
       </c>
       <c r="AQ75">
-        <v>0.9399999999999999</v>
+        <v>1.13</v>
       </c>
       <c r="AR75">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AS75">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AT75">
-        <v>2.59</v>
+        <v>2.44</v>
       </c>
       <c r="AU75">
         <v>5</v>
@@ -16661,25 +16661,25 @@
         <v>0</v>
       </c>
       <c r="AN76">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AO76">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="AP76">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AQ76">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR76">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AS76">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AT76">
-        <v>2.32</v>
+        <v>1.02</v>
       </c>
       <c r="AU76">
         <v>4</v>
@@ -16867,25 +16867,25 @@
         <v>0</v>
       </c>
       <c r="AN77">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AO77">
-        <v>1.8</v>
+        <v>2.33</v>
       </c>
       <c r="AP77">
-        <v>0.78</v>
+        <v>0.43</v>
       </c>
       <c r="AQ77">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="AR77">
-        <v>1.32</v>
+        <v>1.89</v>
       </c>
       <c r="AS77">
-        <v>1.47</v>
+        <v>1.05</v>
       </c>
       <c r="AT77">
-        <v>2.79</v>
+        <v>2.94</v>
       </c>
       <c r="AU77">
         <v>5</v>
@@ -17073,25 +17073,25 @@
         <v>0</v>
       </c>
       <c r="AN78">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="AO78">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="AP78">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AQ78">
-        <v>0.78</v>
+        <v>0.44</v>
       </c>
       <c r="AR78">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="AS78">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AT78">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="AU78">
         <v>8</v>
@@ -17279,25 +17279,25 @@
         <v>1.38</v>
       </c>
       <c r="AN79">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AO79">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AP79">
-        <v>0.9399999999999999</v>
+        <v>1.11</v>
       </c>
       <c r="AQ79">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AR79">
-        <v>1.41</v>
+        <v>1.7</v>
       </c>
       <c r="AS79">
-        <v>1.53</v>
+        <v>1.29</v>
       </c>
       <c r="AT79">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="AU79">
         <v>5</v>
@@ -17485,25 +17485,25 @@
         <v>1.83</v>
       </c>
       <c r="AN80">
-        <v>1.64</v>
+        <v>1.33</v>
       </c>
       <c r="AO80">
-        <v>0.82</v>
+        <v>0.2</v>
       </c>
       <c r="AP80">
-        <v>1.72</v>
+        <v>1.89</v>
       </c>
       <c r="AQ80">
-        <v>0.89</v>
+        <v>0.44</v>
       </c>
       <c r="AR80">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AS80">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AT80">
-        <v>2.76</v>
+        <v>2.58</v>
       </c>
       <c r="AU80">
         <v>3</v>
@@ -17691,25 +17691,25 @@
         <v>1.4</v>
       </c>
       <c r="AN81">
-        <v>0.27</v>
+        <v>0.5</v>
       </c>
       <c r="AO81">
-        <v>1.45</v>
+        <v>1</v>
       </c>
       <c r="AP81">
-        <v>0.78</v>
+        <v>1.11</v>
       </c>
       <c r="AQ81">
+        <v>1</v>
+      </c>
+      <c r="AR81">
         <v>1.17</v>
       </c>
-      <c r="AR81">
-        <v>1.16</v>
-      </c>
       <c r="AS81">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AT81">
-        <v>2.24</v>
+        <v>2.31</v>
       </c>
       <c r="AU81">
         <v>4</v>
@@ -17897,25 +17897,25 @@
         <v>1.36</v>
       </c>
       <c r="AN82">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AO82">
-        <v>1.91</v>
+        <v>1</v>
       </c>
       <c r="AP82">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="AQ82">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="AR82">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="AS82">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="AT82">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="AU82">
         <v>9</v>
@@ -18103,25 +18103,25 @@
         <v>1.1</v>
       </c>
       <c r="AN83">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AO83">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="AP83">
-        <v>0.9399999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="AQ83">
-        <v>2.44</v>
+        <v>2</v>
       </c>
       <c r="AR83">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AS83">
-        <v>1.49</v>
+        <v>1.23</v>
       </c>
       <c r="AT83">
-        <v>2.74</v>
+        <v>2.58</v>
       </c>
       <c r="AU83">
         <v>0</v>
@@ -18309,25 +18309,25 @@
         <v>2</v>
       </c>
       <c r="AN84">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO84">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AP84">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AQ84">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR84">
-        <v>1.26</v>
+        <v>1.02</v>
       </c>
       <c r="AS84">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AT84">
-        <v>2.59</v>
+        <v>2.27</v>
       </c>
       <c r="AU84">
         <v>8</v>
@@ -18515,25 +18515,25 @@
         <v>1.36</v>
       </c>
       <c r="AN85">
-        <v>1.09</v>
+        <v>0.83</v>
       </c>
       <c r="AO85">
-        <v>1.91</v>
+        <v>1.33</v>
       </c>
       <c r="AP85">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AQ85">
-        <v>1.61</v>
+        <v>1.33</v>
       </c>
       <c r="AR85">
-        <v>1.45</v>
+        <v>1.63</v>
       </c>
       <c r="AS85">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AT85">
-        <v>2.8</v>
+        <v>2.99</v>
       </c>
       <c r="AU85">
         <v>4</v>
@@ -18721,25 +18721,25 @@
         <v>1.25</v>
       </c>
       <c r="AN86">
-        <v>0.75</v>
+        <v>1.33</v>
       </c>
       <c r="AO86">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AP86">
-        <v>0.89</v>
+        <v>1.33</v>
       </c>
       <c r="AQ86">
-        <v>1.61</v>
+        <v>1.33</v>
       </c>
       <c r="AR86">
+        <v>1.42</v>
+      </c>
+      <c r="AS86">
         <v>1.26</v>
       </c>
-      <c r="AS86">
-        <v>1.32</v>
-      </c>
       <c r="AT86">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="AU86">
         <v>7</v>
@@ -18927,25 +18927,25 @@
         <v>1.75</v>
       </c>
       <c r="AN87">
-        <v>0.92</v>
+        <v>0.5</v>
       </c>
       <c r="AO87">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="AP87">
-        <v>0.78</v>
+        <v>0.43</v>
       </c>
       <c r="AQ87">
-        <v>0.9399999999999999</v>
+        <v>1.13</v>
       </c>
       <c r="AR87">
-        <v>1.32</v>
+        <v>1.66</v>
       </c>
       <c r="AS87">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AT87">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="AU87">
         <v>2</v>
@@ -19133,25 +19133,25 @@
         <v>1.3</v>
       </c>
       <c r="AN88">
-        <v>1.42</v>
+        <v>1.83</v>
       </c>
       <c r="AO88">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="AP88">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AQ88">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="AR88">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AS88">
-        <v>1.49</v>
+        <v>1.16</v>
       </c>
       <c r="AT88">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="AU88">
         <v>2</v>
@@ -19339,25 +19339,25 @@
         <v>1.73</v>
       </c>
       <c r="AN89">
-        <v>0.92</v>
+        <v>1.17</v>
       </c>
       <c r="AO89">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AP89">
-        <v>0.9399999999999999</v>
+        <v>1.11</v>
       </c>
       <c r="AQ89">
-        <v>0.78</v>
+        <v>0.44</v>
       </c>
       <c r="AR89">
-        <v>1.48</v>
+        <v>1.79</v>
       </c>
       <c r="AS89">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AT89">
-        <v>2.65</v>
+        <v>2.93</v>
       </c>
       <c r="AU89">
         <v>7</v>
@@ -19545,25 +19545,25 @@
         <v>1.53</v>
       </c>
       <c r="AN90">
-        <v>1.17</v>
+        <v>1.6</v>
       </c>
       <c r="AO90">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AP90">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AQ90">
-        <v>1.72</v>
+        <v>1.56</v>
       </c>
       <c r="AR90">
-        <v>1.58</v>
+        <v>1.82</v>
       </c>
       <c r="AS90">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="AT90">
-        <v>3.05</v>
+        <v>3.33</v>
       </c>
       <c r="AU90">
         <v>4</v>
@@ -19751,25 +19751,25 @@
         <v>2</v>
       </c>
       <c r="AN91">
-        <v>2.58</v>
+        <v>2.71</v>
       </c>
       <c r="AO91">
-        <v>2.08</v>
+        <v>1.9</v>
       </c>
       <c r="AP91">
-        <v>2.44</v>
+        <v>2.8</v>
       </c>
       <c r="AQ91">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AR91">
-        <v>1.49</v>
+        <v>1.64</v>
       </c>
       <c r="AS91">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AT91">
-        <v>2.82</v>
+        <v>2.93</v>
       </c>
       <c r="AU91">
         <v>8</v>
@@ -19957,25 +19957,25 @@
         <v>1.95</v>
       </c>
       <c r="AN92">
-        <v>2</v>
+        <v>2.67</v>
       </c>
       <c r="AO92">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AP92">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AQ92">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AR92">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="AS92">
-        <v>1.42</v>
+        <v>1.22</v>
       </c>
       <c r="AT92">
-        <v>3.21</v>
+        <v>3.08</v>
       </c>
       <c r="AU92">
         <v>6</v>
@@ -20163,25 +20163,25 @@
         <v>1.62</v>
       </c>
       <c r="AN93">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="AO93">
-        <v>1.69</v>
+        <v>2.2</v>
       </c>
       <c r="AP93">
-        <v>1.61</v>
+        <v>1.89</v>
       </c>
       <c r="AQ93">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="AR93">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AS93">
-        <v>1.45</v>
+        <v>1.12</v>
       </c>
       <c r="AT93">
-        <v>2.73</v>
+        <v>2.47</v>
       </c>
       <c r="AU93">
         <v>5</v>
@@ -20369,25 +20369,25 @@
         <v>1.95</v>
       </c>
       <c r="AN94">
-        <v>1.92</v>
+        <v>3</v>
       </c>
       <c r="AO94">
-        <v>0.6899999999999999</v>
+        <v>0.17</v>
       </c>
       <c r="AP94">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AQ94">
-        <v>0.89</v>
+        <v>0.44</v>
       </c>
       <c r="AR94">
-        <v>1.27</v>
+        <v>1.56</v>
       </c>
       <c r="AS94">
-        <v>1.31</v>
+        <v>1.09</v>
       </c>
       <c r="AT94">
-        <v>2.58</v>
+        <v>2.65</v>
       </c>
       <c r="AU94">
         <v>7</v>
@@ -20575,25 +20575,25 @@
         <v>1.5</v>
       </c>
       <c r="AN95">
-        <v>0.92</v>
+        <v>0.67</v>
       </c>
       <c r="AO95">
-        <v>1.08</v>
+        <v>0.67</v>
       </c>
       <c r="AP95">
+        <v>0.43</v>
+      </c>
+      <c r="AQ95">
         <v>0.78</v>
       </c>
-      <c r="AQ95">
-        <v>0.9399999999999999</v>
-      </c>
       <c r="AR95">
-        <v>1.31</v>
+        <v>1.52</v>
       </c>
       <c r="AS95">
-        <v>1.5</v>
+        <v>1.16</v>
       </c>
       <c r="AT95">
-        <v>2.81</v>
+        <v>2.68</v>
       </c>
       <c r="AU95">
         <v>5</v>
@@ -20781,25 +20781,25 @@
         <v>1.35</v>
       </c>
       <c r="AN96">
-        <v>0.6899999999999999</v>
+        <v>0.57</v>
       </c>
       <c r="AO96">
-        <v>1.38</v>
+        <v>1</v>
       </c>
       <c r="AP96">
-        <v>0.9399999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="AQ96">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR96">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AS96">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="AT96">
-        <v>2.36</v>
+        <v>2.51</v>
       </c>
       <c r="AU96">
         <v>5</v>
@@ -20987,25 +20987,25 @@
         <v>1.65</v>
       </c>
       <c r="AN97">
-        <v>1.15</v>
+        <v>1.5</v>
       </c>
       <c r="AO97">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AP97">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AQ97">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AR97">
-        <v>1.59</v>
+        <v>1.82</v>
       </c>
       <c r="AS97">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AT97">
-        <v>3.03</v>
+        <v>3.13</v>
       </c>
       <c r="AU97">
         <v>5</v>
@@ -21193,25 +21193,25 @@
         <v>2</v>
       </c>
       <c r="AN98">
-        <v>1.92</v>
+        <v>2.43</v>
       </c>
       <c r="AO98">
-        <v>1.69</v>
+        <v>1.83</v>
       </c>
       <c r="AP98">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AQ98">
-        <v>1.72</v>
+        <v>1.56</v>
       </c>
       <c r="AR98">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AS98">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="AT98">
-        <v>3.31</v>
+        <v>3.49</v>
       </c>
       <c r="AU98">
         <v>8</v>
@@ -21399,25 +21399,25 @@
         <v>1.08</v>
       </c>
       <c r="AN99">
-        <v>0.31</v>
+        <v>0.57</v>
       </c>
       <c r="AO99">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="AP99">
-        <v>0.78</v>
+        <v>1.11</v>
       </c>
       <c r="AQ99">
-        <v>2.44</v>
+        <v>2</v>
       </c>
       <c r="AR99">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AS99">
-        <v>1.57</v>
+        <v>1.29</v>
       </c>
       <c r="AT99">
-        <v>2.8</v>
+        <v>2.48</v>
       </c>
       <c r="AU99">
         <v>6</v>
@@ -21605,25 +21605,25 @@
         <v>1.17</v>
       </c>
       <c r="AN100">
-        <v>1.29</v>
+        <v>1.71</v>
       </c>
       <c r="AO100">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AP100">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AQ100">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="AR100">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AS100">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="AT100">
-        <v>2.91</v>
+        <v>2.77</v>
       </c>
       <c r="AU100">
         <v>5</v>
@@ -21811,25 +21811,25 @@
         <v>1.28</v>
       </c>
       <c r="AN101">
+        <v>0.5</v>
+      </c>
+      <c r="AO101">
         <v>0.86</v>
       </c>
-      <c r="AO101">
-        <v>1.29</v>
-      </c>
       <c r="AP101">
-        <v>0.78</v>
+        <v>0.43</v>
       </c>
       <c r="AQ101">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AR101">
-        <v>1.31</v>
+        <v>1.52</v>
       </c>
       <c r="AS101">
-        <v>1.59</v>
+        <v>1.4</v>
       </c>
       <c r="AT101">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="AU101">
         <v>0</v>
@@ -22017,25 +22017,25 @@
         <v>1.57</v>
       </c>
       <c r="AN102">
-        <v>1.21</v>
+        <v>1.43</v>
       </c>
       <c r="AO102">
-        <v>0.64</v>
+        <v>0.14</v>
       </c>
       <c r="AP102">
-        <v>0.9399999999999999</v>
+        <v>1.11</v>
       </c>
       <c r="AQ102">
-        <v>0.89</v>
+        <v>0.44</v>
       </c>
       <c r="AR102">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="AS102">
-        <v>1.31</v>
+        <v>1.09</v>
       </c>
       <c r="AT102">
-        <v>2.81</v>
+        <v>2.87</v>
       </c>
       <c r="AU102">
         <v>6</v>
@@ -22223,25 +22223,25 @@
         <v>2.22</v>
       </c>
       <c r="AN103">
-        <v>1.79</v>
+        <v>1.38</v>
       </c>
       <c r="AO103">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="AP103">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="AQ103">
-        <v>0.9399999999999999</v>
+        <v>1.13</v>
       </c>
       <c r="AR103">
-        <v>1.45</v>
+        <v>1.65</v>
       </c>
       <c r="AS103">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="AT103">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="AU103">
         <v>4</v>
@@ -22429,25 +22429,25 @@
         <v>1.42</v>
       </c>
       <c r="AN104">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO104">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AP104">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AQ104">
-        <v>1.61</v>
+        <v>1.33</v>
       </c>
       <c r="AR104">
-        <v>1.27</v>
+        <v>1.56</v>
       </c>
       <c r="AS104">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AT104">
-        <v>2.55</v>
+        <v>2.74</v>
       </c>
       <c r="AU104">
         <v>4</v>
@@ -22635,25 +22635,25 @@
         <v>2.05</v>
       </c>
       <c r="AN105">
-        <v>2.43</v>
+        <v>2.75</v>
       </c>
       <c r="AO105">
         <v>1.57</v>
       </c>
       <c r="AP105">
-        <v>2.44</v>
+        <v>2.8</v>
       </c>
       <c r="AQ105">
-        <v>1.72</v>
+        <v>1.56</v>
       </c>
       <c r="AR105">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AS105">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="AT105">
-        <v>3.1</v>
+        <v>3.39</v>
       </c>
       <c r="AU105">
         <v>6</v>
@@ -22841,25 +22841,25 @@
         <v>1.85</v>
       </c>
       <c r="AN106">
-        <v>0.93</v>
+        <v>0.71</v>
       </c>
       <c r="AO106">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AP106">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AQ106">
-        <v>0.78</v>
+        <v>0.44</v>
       </c>
       <c r="AR106">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AS106">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AT106">
-        <v>2.67</v>
+        <v>2.83</v>
       </c>
       <c r="AU106">
         <v>3</v>
@@ -23047,25 +23047,25 @@
         <v>2.3</v>
       </c>
       <c r="AN107">
-        <v>1.4</v>
+        <v>1.71</v>
       </c>
       <c r="AO107">
-        <v>0.47</v>
+        <v>0</v>
       </c>
       <c r="AP107">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AQ107">
-        <v>0.78</v>
+        <v>0.44</v>
       </c>
       <c r="AR107">
-        <v>1.57</v>
+        <v>1.82</v>
       </c>
       <c r="AS107">
         <v>1.19</v>
       </c>
       <c r="AT107">
-        <v>2.76</v>
+        <v>3.01</v>
       </c>
       <c r="AU107">
         <v>5</v>
@@ -23253,25 +23253,25 @@
         <v>1.44</v>
       </c>
       <c r="AN108">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AO108">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AP108">
-        <v>1.72</v>
+        <v>1.89</v>
       </c>
       <c r="AQ108">
-        <v>1.61</v>
+        <v>1.33</v>
       </c>
       <c r="AR108">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AS108">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AT108">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="AU108">
         <v>9</v>
@@ -23459,25 +23459,25 @@
         <v>1.41</v>
       </c>
       <c r="AN109">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="AO109">
-        <v>1.2</v>
+        <v>0.86</v>
       </c>
       <c r="AP109">
-        <v>0.78</v>
+        <v>0.43</v>
       </c>
       <c r="AQ109">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR109">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AS109">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AT109">
-        <v>2.43</v>
+        <v>2.62</v>
       </c>
       <c r="AU109">
         <v>4</v>
@@ -23665,25 +23665,25 @@
         <v>1.44</v>
       </c>
       <c r="AN110">
-        <v>1.93</v>
+        <v>2.5</v>
       </c>
       <c r="AO110">
-        <v>1.67</v>
+        <v>2.33</v>
       </c>
       <c r="AP110">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AQ110">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="AR110">
-        <v>1.26</v>
+        <v>1.42</v>
       </c>
       <c r="AS110">
-        <v>1.46</v>
+        <v>1.12</v>
       </c>
       <c r="AT110">
-        <v>2.72</v>
+        <v>2.54</v>
       </c>
       <c r="AU110">
         <v>6</v>
@@ -23871,25 +23871,25 @@
         <v>1.73</v>
       </c>
       <c r="AN111">
-        <v>0.8</v>
+        <v>1.14</v>
       </c>
       <c r="AO111">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AP111">
-        <v>0.89</v>
+        <v>1.33</v>
       </c>
       <c r="AQ111">
-        <v>0.9399999999999999</v>
+        <v>1.13</v>
       </c>
       <c r="AR111">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AS111">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="AT111">
-        <v>2.47</v>
+        <v>2.56</v>
       </c>
       <c r="AU111">
         <v>2</v>
@@ -24077,25 +24077,25 @@
         <v>1.77</v>
       </c>
       <c r="AN112">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AO112">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AP112">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AQ112">
-        <v>0.9399999999999999</v>
+        <v>0.78</v>
       </c>
       <c r="AR112">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="AS112">
-        <v>1.47</v>
+        <v>1.16</v>
       </c>
       <c r="AT112">
-        <v>2.92</v>
+        <v>2.71</v>
       </c>
       <c r="AU112">
         <v>10</v>
@@ -24283,25 +24283,25 @@
         <v>1.46</v>
       </c>
       <c r="AN113">
-        <v>2.07</v>
+        <v>2.5</v>
       </c>
       <c r="AO113">
-        <v>2.47</v>
+        <v>2</v>
       </c>
       <c r="AP113">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AQ113">
-        <v>2.44</v>
+        <v>2</v>
       </c>
       <c r="AR113">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AS113">
-        <v>1.56</v>
+        <v>1.29</v>
       </c>
       <c r="AT113">
-        <v>3.34</v>
+        <v>3.14</v>
       </c>
       <c r="AU113">
         <v>6</v>
@@ -24489,25 +24489,25 @@
         <v>3.02</v>
       </c>
       <c r="AN114">
-        <v>2.5</v>
+        <v>2.78</v>
       </c>
       <c r="AO114">
-        <v>0.8100000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AP114">
-        <v>2.44</v>
+        <v>2.8</v>
       </c>
       <c r="AQ114">
-        <v>0.89</v>
+        <v>0.44</v>
       </c>
       <c r="AR114">
-        <v>1.51</v>
+        <v>1.71</v>
       </c>
       <c r="AS114">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="AT114">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AU114">
         <v>5</v>
@@ -24695,25 +24695,25 @@
         <v>1.15</v>
       </c>
       <c r="AN115">
-        <v>0.63</v>
+        <v>0.88</v>
       </c>
       <c r="AO115">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AP115">
-        <v>0.78</v>
+        <v>1.11</v>
       </c>
       <c r="AQ115">
-        <v>1.61</v>
+        <v>1.33</v>
       </c>
       <c r="AR115">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AS115">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AT115">
-        <v>2.47</v>
+        <v>2.43</v>
       </c>
       <c r="AU115">
         <v>7</v>
@@ -24901,25 +24901,25 @@
         <v>1.22</v>
       </c>
       <c r="AN116">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AO116">
+        <v>1.38</v>
+      </c>
+      <c r="AP116">
+        <v>0.8</v>
+      </c>
+      <c r="AQ116">
         <v>1.56</v>
       </c>
-      <c r="AP116">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="AQ116">
-        <v>1.72</v>
-      </c>
       <c r="AR116">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AS116">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AT116">
-        <v>2.66</v>
+        <v>2.77</v>
       </c>
       <c r="AU116">
         <v>2</v>
@@ -25107,25 +25107,25 @@
         <v>1.33</v>
       </c>
       <c r="AN117">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="AO117">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="AP117">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AQ117">
+        <v>1.33</v>
+      </c>
+      <c r="AR117">
+        <v>1.09</v>
+      </c>
+      <c r="AS117">
         <v>1.39</v>
       </c>
-      <c r="AR117">
-        <v>1.18</v>
-      </c>
-      <c r="AS117">
-        <v>1.58</v>
-      </c>
       <c r="AT117">
-        <v>2.76</v>
+        <v>2.48</v>
       </c>
       <c r="AU117">
         <v>2</v>
@@ -25313,25 +25313,25 @@
         <v>2.1</v>
       </c>
       <c r="AN118">
-        <v>1.75</v>
+        <v>1.22</v>
       </c>
       <c r="AO118">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AP118">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="AQ118">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR118">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="AS118">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AT118">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="AU118">
         <v>7</v>
@@ -25519,25 +25519,25 @@
         <v>1.17</v>
       </c>
       <c r="AN119">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="AO119">
-        <v>1.94</v>
+        <v>1.57</v>
       </c>
       <c r="AP119">
-        <v>0.9399999999999999</v>
+        <v>1.11</v>
       </c>
       <c r="AQ119">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="AR119">
-        <v>1.42</v>
+        <v>1.71</v>
       </c>
       <c r="AS119">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AT119">
-        <v>3.18</v>
+        <v>3.41</v>
       </c>
       <c r="AU119">
         <v>5</v>
@@ -25725,25 +25725,25 @@
         <v>1.57</v>
       </c>
       <c r="AN120">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="AO120">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AP120">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AQ120">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AR120">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="AS120">
-        <v>1.5</v>
+        <v>1.31</v>
       </c>
       <c r="AT120">
-        <v>2.83</v>
+        <v>2.93</v>
       </c>
       <c r="AU120">
         <v>3</v>
@@ -25931,25 +25931,25 @@
         <v>1.5</v>
       </c>
       <c r="AN121">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AO121">
-        <v>1.65</v>
+        <v>1.38</v>
       </c>
       <c r="AP121">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AQ121">
-        <v>1.61</v>
+        <v>1.33</v>
       </c>
       <c r="AR121">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="AS121">
         <v>1.35</v>
       </c>
       <c r="AT121">
-        <v>2.93</v>
+        <v>3.15</v>
       </c>
       <c r="AU121">
         <v>5</v>
@@ -26137,25 +26137,25 @@
         <v>2.04</v>
       </c>
       <c r="AN122">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AO122">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AP122">
-        <v>1.72</v>
+        <v>1.89</v>
       </c>
       <c r="AQ122">
-        <v>0.9399999999999999</v>
+        <v>0.78</v>
       </c>
       <c r="AR122">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AS122">
-        <v>1.42</v>
+        <v>1.1</v>
       </c>
       <c r="AT122">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="AU122">
         <v>9</v>
@@ -26343,25 +26343,25 @@
         <v>1.52</v>
       </c>
       <c r="AN123">
-        <v>0.9399999999999999</v>
+        <v>0.78</v>
       </c>
       <c r="AO123">
-        <v>0.76</v>
+        <v>0.38</v>
       </c>
       <c r="AP123">
-        <v>0.9399999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="AQ123">
-        <v>0.78</v>
+        <v>0.44</v>
       </c>
       <c r="AR123">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="AS123">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AT123">
-        <v>2.32</v>
+        <v>2.37</v>
       </c>
       <c r="AU123">
         <v>2</v>
@@ -26549,25 +26549,25 @@
         <v>1.43</v>
       </c>
       <c r="AN124">
-        <v>0.76</v>
+        <v>1.13</v>
       </c>
       <c r="AO124">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="AP124">
-        <v>0.89</v>
+        <v>1.33</v>
       </c>
       <c r="AQ124">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR124">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="AS124">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AT124">
-        <v>2.39</v>
+        <v>2.66</v>
       </c>
       <c r="AU124">
         <v>2</v>
@@ -26755,25 +26755,25 @@
         <v>1.8</v>
       </c>
       <c r="AN125">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="AO125">
-        <v>1.71</v>
+        <v>2.43</v>
       </c>
       <c r="AP125">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AQ125">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="AR125">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="AS125">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="AT125">
-        <v>3.23</v>
+        <v>3.04</v>
       </c>
       <c r="AU125">
         <v>3</v>
@@ -26961,22 +26961,22 @@
         <v>1.36</v>
       </c>
       <c r="AN126">
-        <v>0.76</v>
+        <v>0.33</v>
       </c>
       <c r="AO126">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AP126">
-        <v>0.78</v>
+        <v>0.43</v>
       </c>
       <c r="AQ126">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AR126">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AS126">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AT126">
         <v>2.62</v>
@@ -27167,25 +27167,25 @@
         <v>1.22</v>
       </c>
       <c r="AN127">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AO127">
-        <v>2.53</v>
+        <v>2.14</v>
       </c>
       <c r="AP127">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AQ127">
-        <v>2.44</v>
+        <v>2</v>
       </c>
       <c r="AR127">
-        <v>1.46</v>
+        <v>1.63</v>
       </c>
       <c r="AS127">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AT127">
-        <v>2.96</v>
+        <v>2.83</v>
       </c>
       <c r="AU127">
         <v>8</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="243">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -472,10 +472,10 @@
     <t>['31', '88']</t>
   </si>
   <si>
-    <t>['52', '60', '88']</t>
+    <t>['52', '60', '69', '88']</t>
   </si>
   <si>
-    <t>['20', '69', '9005']</t>
+    <t>['20', '69', '90+5']</t>
   </si>
   <si>
     <t>['38']</t>
@@ -487,7 +487,7 @@
     <t>['18']</t>
   </si>
   <si>
-    <t>['4502', '65', '73']</t>
+    <t>['45+2', '65', '73']</t>
   </si>
   <si>
     <t>['73', '80', '82']</t>
@@ -511,7 +511,7 @@
     <t>['35', '45']</t>
   </si>
   <si>
-    <t>['9005']</t>
+    <t>['90+5']</t>
   </si>
   <si>
     <t>['19']</t>
@@ -521,6 +521,18 @@
   </si>
   <si>
     <t>['37']</t>
+  </si>
+  <si>
+    <t>['48', '68']</t>
+  </si>
+  <si>
+    <t>['19', '87']</t>
+  </si>
+  <si>
+    <t>['56', '78']</t>
+  </si>
+  <si>
+    <t>['45+5']</t>
   </si>
   <si>
     <t>['1', '6']</t>
@@ -554,9 +566,6 @@
   </si>
   <si>
     <t>['71']</t>
-  </si>
-  <si>
-    <t>['90+5']</t>
   </si>
   <si>
     <t>['44']</t>
@@ -682,22 +691,22 @@
     <t>['29']</t>
   </si>
   <si>
-    <t>['44', '57']</t>
+    <t>['23', '44', '57']</t>
   </si>
   <si>
-    <t>['9', '9006']</t>
+    <t>['9', '90+6']</t>
   </si>
   <si>
     <t>['15', '26']</t>
   </si>
   <si>
-    <t>['62', '9005']</t>
+    <t>['62', '90+5']</t>
   </si>
   <si>
     <t>['66']</t>
   </si>
   <si>
-    <t>['9003']</t>
+    <t>['90+3']</t>
   </si>
   <si>
     <t>['17']</t>
@@ -712,22 +721,28 @@
     <t>['5', '76']</t>
   </si>
   <si>
-    <t>['65', '9002']</t>
-  </si>
-  <si>
-    <t>['12', '82']</t>
+    <t>['12', '56', '82']</t>
   </si>
   <si>
     <t>['69']</t>
   </si>
   <si>
-    <t>['9001']</t>
+    <t>['71', '90+6']</t>
   </si>
   <si>
-    <t>['71', '9006']</t>
+    <t>['90+7']</t>
   </si>
   <si>
-    <t>['9007']</t>
+    <t>['34', '44', '81']</t>
+  </si>
+  <si>
+    <t>['41']</t>
+  </si>
+  <si>
+    <t>['9']</t>
+  </si>
+  <si>
+    <t>['14']</t>
   </si>
 </sst>
 </file>
@@ -1089,7 +1104,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP127"/>
+  <dimension ref="A1:BP131"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1551,7 +1566,7 @@
         <v>85</v>
       </c>
       <c r="P3" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="Q3">
         <v>3.8</v>
@@ -1629,7 +1644,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.11</v>
+        <v>0.89</v>
       </c>
       <c r="AQ3">
         <v>1.67</v>
@@ -2044,7 +2059,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ5">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2581,7 +2596,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="Q8">
         <v>2.39</v>
@@ -2868,7 +2883,7 @@
         <v>2.8</v>
       </c>
       <c r="AQ9">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AR9">
         <v>2.58</v>
@@ -2993,7 +3008,7 @@
         <v>85</v>
       </c>
       <c r="P10" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="Q10">
         <v>4.3</v>
@@ -3199,7 +3214,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="Q11">
         <v>2.8</v>
@@ -3611,7 +3626,7 @@
         <v>85</v>
       </c>
       <c r="P13" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="Q13">
         <v>2.43</v>
@@ -3817,7 +3832,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="Q14">
         <v>3.9</v>
@@ -3895,7 +3910,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.11</v>
+        <v>0.89</v>
       </c>
       <c r="AQ14">
         <v>1.56</v>
@@ -4229,7 +4244,7 @@
         <v>85</v>
       </c>
       <c r="P16" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="Q16">
         <v>3.18</v>
@@ -4435,7 +4450,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="Q17">
         <v>3</v>
@@ -4847,7 +4862,7 @@
         <v>95</v>
       </c>
       <c r="P19" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="Q19">
         <v>2.71</v>
@@ -5053,7 +5068,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="Q20">
         <v>3.5</v>
@@ -5134,7 +5149,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ20">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AR20">
         <v>1.06</v>
@@ -5337,7 +5352,7 @@
         <v>0.5</v>
       </c>
       <c r="AP21">
-        <v>1.11</v>
+        <v>0.89</v>
       </c>
       <c r="AQ21">
         <v>1.33</v>
@@ -5465,7 +5480,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="Q22">
         <v>5</v>
@@ -5546,7 +5561,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ22">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AR22">
         <v>0.92</v>
@@ -5752,7 +5767,7 @@
         <v>2.8</v>
       </c>
       <c r="AQ23">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR23">
         <v>1.93</v>
@@ -5877,7 +5892,7 @@
         <v>99</v>
       </c>
       <c r="P24" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="Q24">
         <v>3</v>
@@ -6495,7 +6510,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="Q27">
         <v>2.25</v>
@@ -6701,7 +6716,7 @@
         <v>101</v>
       </c>
       <c r="P28" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q28">
         <v>4</v>
@@ -6779,7 +6794,7 @@
         <v>2.33</v>
       </c>
       <c r="AP28">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ28">
         <v>1.67</v>
@@ -6907,7 +6922,7 @@
         <v>102</v>
       </c>
       <c r="P29" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="Q29">
         <v>2.2</v>
@@ -6988,7 +7003,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ29">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AR29">
         <v>1.22</v>
@@ -7113,7 +7128,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="Q30">
         <v>3.75</v>
@@ -7319,7 +7334,7 @@
         <v>104</v>
       </c>
       <c r="P31" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Q31">
         <v>3.25</v>
@@ -7603,7 +7618,7 @@
         <v>1</v>
       </c>
       <c r="AP32">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ32">
         <v>1</v>
@@ -7731,7 +7746,7 @@
         <v>91</v>
       </c>
       <c r="P33" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="Q33">
         <v>2.63</v>
@@ -7937,7 +7952,7 @@
         <v>85</v>
       </c>
       <c r="P34" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q34">
         <v>3.8</v>
@@ -8015,7 +8030,7 @@
         <v>2</v>
       </c>
       <c r="AP34">
-        <v>1.11</v>
+        <v>0.89</v>
       </c>
       <c r="AQ34">
         <v>1.13</v>
@@ -8143,7 +8158,7 @@
         <v>106</v>
       </c>
       <c r="P35" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q35">
         <v>2.8</v>
@@ -8427,7 +8442,7 @@
         <v>1</v>
       </c>
       <c r="AP36">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ36">
         <v>1</v>
@@ -8761,7 +8776,7 @@
         <v>85</v>
       </c>
       <c r="P38" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q38">
         <v>5</v>
@@ -8842,7 +8857,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ38">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AR38">
         <v>1.61</v>
@@ -8967,7 +8982,7 @@
         <v>85</v>
       </c>
       <c r="P39" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q39">
         <v>3.1</v>
@@ -9379,7 +9394,7 @@
         <v>110</v>
       </c>
       <c r="P41" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q41">
         <v>3.25</v>
@@ -9585,7 +9600,7 @@
         <v>111</v>
       </c>
       <c r="P42" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q42">
         <v>2.5</v>
@@ -9663,7 +9678,7 @@
         <v>0.8</v>
       </c>
       <c r="AP42">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ42">
         <v>1</v>
@@ -9872,7 +9887,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ43">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AR43">
         <v>1.02</v>
@@ -9997,7 +10012,7 @@
         <v>113</v>
       </c>
       <c r="P44" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q44">
         <v>3.4</v>
@@ -10203,7 +10218,7 @@
         <v>113</v>
       </c>
       <c r="P45" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q45">
         <v>3.75</v>
@@ -10409,7 +10424,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q46">
         <v>3.75</v>
@@ -10490,7 +10505,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ46">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AR46">
         <v>1.33</v>
@@ -10615,7 +10630,7 @@
         <v>85</v>
       </c>
       <c r="P47" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q47">
         <v>3</v>
@@ -10693,7 +10708,7 @@
         <v>1</v>
       </c>
       <c r="AP47">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ47">
         <v>1</v>
@@ -11027,7 +11042,7 @@
         <v>116</v>
       </c>
       <c r="P49" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -11108,7 +11123,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ49">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR49">
         <v>1.58</v>
@@ -11311,10 +11326,10 @@
         <v>0</v>
       </c>
       <c r="AP50">
+        <v>0.89</v>
+      </c>
+      <c r="AQ50">
         <v>1.11</v>
-      </c>
-      <c r="AQ50">
-        <v>1.13</v>
       </c>
       <c r="AR50">
         <v>1.01</v>
@@ -11439,7 +11454,7 @@
         <v>85</v>
       </c>
       <c r="P51" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q51">
         <v>2.25</v>
@@ -12263,7 +12278,7 @@
         <v>119</v>
       </c>
       <c r="P55" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q55">
         <v>5</v>
@@ -12547,7 +12562,7 @@
         <v>2</v>
       </c>
       <c r="AP56">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ56">
         <v>1.67</v>
@@ -12675,7 +12690,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q57">
         <v>3.75</v>
@@ -12753,7 +12768,7 @@
         <v>2.33</v>
       </c>
       <c r="AP57">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ57">
         <v>1.13</v>
@@ -12881,7 +12896,7 @@
         <v>121</v>
       </c>
       <c r="P58" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="Q58">
         <v>2.3</v>
@@ -13087,7 +13102,7 @@
         <v>85</v>
       </c>
       <c r="P59" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q59">
         <v>3.2</v>
@@ -13165,7 +13180,7 @@
         <v>0.88</v>
       </c>
       <c r="AP59">
-        <v>1.11</v>
+        <v>0.89</v>
       </c>
       <c r="AQ59">
         <v>1</v>
@@ -13371,10 +13386,10 @@
         <v>1</v>
       </c>
       <c r="AP60">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ60">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AR60">
         <v>2.02</v>
@@ -13499,7 +13514,7 @@
         <v>123</v>
       </c>
       <c r="P61" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q61">
         <v>4</v>
@@ -13580,7 +13595,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ61">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AR61">
         <v>1.39</v>
@@ -13705,7 +13720,7 @@
         <v>124</v>
       </c>
       <c r="P62" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q62">
         <v>2.3</v>
@@ -13911,7 +13926,7 @@
         <v>85</v>
       </c>
       <c r="P63" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q63">
         <v>3.2</v>
@@ -14117,7 +14132,7 @@
         <v>125</v>
       </c>
       <c r="P64" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q64">
         <v>2.5</v>
@@ -14323,7 +14338,7 @@
         <v>126</v>
       </c>
       <c r="P65" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q65">
         <v>4</v>
@@ -14404,7 +14419,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ65">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR65">
         <v>1.07</v>
@@ -14529,7 +14544,7 @@
         <v>127</v>
       </c>
       <c r="P66" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q66">
         <v>3</v>
@@ -14941,7 +14956,7 @@
         <v>129</v>
       </c>
       <c r="P68" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q68">
         <v>5</v>
@@ -15019,10 +15034,10 @@
         <v>1</v>
       </c>
       <c r="AP68">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="AQ68">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AR68">
         <v>0</v>
@@ -15559,7 +15574,7 @@
         <v>132</v>
       </c>
       <c r="P71" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q71">
         <v>2.63</v>
@@ -15971,7 +15986,7 @@
         <v>85</v>
       </c>
       <c r="P73" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q73">
         <v>3.6</v>
@@ -16049,7 +16064,7 @@
         <v>1.75</v>
       </c>
       <c r="AP73">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ73">
         <v>1.56</v>
@@ -16177,7 +16192,7 @@
         <v>85</v>
       </c>
       <c r="P74" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q74">
         <v>4.33</v>
@@ -16255,10 +16270,10 @@
         <v>2</v>
       </c>
       <c r="AP74">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ74">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AR74">
         <v>1.98</v>
@@ -16383,7 +16398,7 @@
         <v>134</v>
       </c>
       <c r="P75" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="Q75">
         <v>1.91</v>
@@ -16464,7 +16479,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ75">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AR75">
         <v>1.33</v>
@@ -16589,7 +16604,7 @@
         <v>135</v>
       </c>
       <c r="P76" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q76">
         <v>2.63</v>
@@ -16667,7 +16682,7 @@
         <v>1.25</v>
       </c>
       <c r="AP76">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ76">
         <v>1</v>
@@ -16795,7 +16810,7 @@
         <v>85</v>
       </c>
       <c r="P77" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q77">
         <v>4.5</v>
@@ -16873,7 +16888,7 @@
         <v>2.33</v>
       </c>
       <c r="AP77">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="AQ77">
         <v>2.25</v>
@@ -17207,7 +17222,7 @@
         <v>137</v>
       </c>
       <c r="P79" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q79">
         <v>3.6</v>
@@ -17285,7 +17300,7 @@
         <v>0.5</v>
       </c>
       <c r="AP79">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ79">
         <v>1.33</v>
@@ -17697,7 +17712,7 @@
         <v>1</v>
       </c>
       <c r="AP81">
-        <v>1.11</v>
+        <v>0.89</v>
       </c>
       <c r="AQ81">
         <v>1</v>
@@ -17825,7 +17840,7 @@
         <v>140</v>
       </c>
       <c r="P82" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q82">
         <v>3.75</v>
@@ -17906,7 +17921,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ82">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AR82">
         <v>1.65</v>
@@ -18031,7 +18046,7 @@
         <v>85</v>
       </c>
       <c r="P83" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q83">
         <v>7.5</v>
@@ -18112,7 +18127,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ83">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AR83">
         <v>1.35</v>
@@ -18237,7 +18252,7 @@
         <v>141</v>
       </c>
       <c r="P84" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="Q84">
         <v>2.38</v>
@@ -18315,7 +18330,7 @@
         <v>1.11</v>
       </c>
       <c r="AP84">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ84">
         <v>1</v>
@@ -18443,7 +18458,7 @@
         <v>142</v>
       </c>
       <c r="P85" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q85">
         <v>3.75</v>
@@ -18524,7 +18539,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ85">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR85">
         <v>1.63</v>
@@ -18649,7 +18664,7 @@
         <v>85</v>
       </c>
       <c r="P86" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q86">
         <v>4.2</v>
@@ -18730,7 +18745,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ86">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR86">
         <v>1.42</v>
@@ -18933,10 +18948,10 @@
         <v>0.8</v>
       </c>
       <c r="AP87">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="AQ87">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AR87">
         <v>1.66</v>
@@ -19267,7 +19282,7 @@
         <v>143</v>
       </c>
       <c r="P89" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q89">
         <v>2.62</v>
@@ -19345,7 +19360,7 @@
         <v>0</v>
       </c>
       <c r="AP89">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ89">
         <v>0.44</v>
@@ -19473,7 +19488,7 @@
         <v>144</v>
       </c>
       <c r="P90" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q90">
         <v>3.1</v>
@@ -19551,7 +19566,7 @@
         <v>2</v>
       </c>
       <c r="AP90">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ90">
         <v>1.56</v>
@@ -19885,7 +19900,7 @@
         <v>146</v>
       </c>
       <c r="P92" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20091,7 +20106,7 @@
         <v>147</v>
       </c>
       <c r="P93" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q93">
         <v>2.62</v>
@@ -20297,7 +20312,7 @@
         <v>148</v>
       </c>
       <c r="P94" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q94">
         <v>2.4</v>
@@ -20375,7 +20390,7 @@
         <v>0.17</v>
       </c>
       <c r="AP94">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ94">
         <v>0.44</v>
@@ -20503,7 +20518,7 @@
         <v>149</v>
       </c>
       <c r="P95" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q95">
         <v>3.1</v>
@@ -20581,7 +20596,7 @@
         <v>0.67</v>
       </c>
       <c r="AP95">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="AQ95">
         <v>0.78</v>
@@ -20993,7 +21008,7 @@
         <v>1.33</v>
       </c>
       <c r="AP97">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ97">
         <v>1.13</v>
@@ -21109,19 +21124,19 @@
         <v>1</v>
       </c>
       <c r="L98">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M98">
         <v>1</v>
       </c>
       <c r="N98">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O98" t="s">
         <v>152</v>
       </c>
       <c r="P98" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q98">
         <v>2.3</v>
@@ -21309,25 +21324,25 @@
         <v>1</v>
       </c>
       <c r="J99">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K99">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L99">
         <v>3</v>
       </c>
       <c r="M99">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N99">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O99" t="s">
         <v>153</v>
       </c>
       <c r="P99" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q99">
         <v>6.5</v>
@@ -21405,10 +21420,10 @@
         <v>2.4</v>
       </c>
       <c r="AP99">
-        <v>1.11</v>
+        <v>0.89</v>
       </c>
       <c r="AQ99">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AR99">
         <v>1.19</v>
@@ -21533,7 +21548,7 @@
         <v>154</v>
       </c>
       <c r="P100" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q100">
         <v>4.33</v>
@@ -21614,7 +21629,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ100">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AR100">
         <v>1.06</v>
@@ -21739,7 +21754,7 @@
         <v>85</v>
       </c>
       <c r="P101" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q101">
         <v>3.88</v>
@@ -21817,7 +21832,7 @@
         <v>0.86</v>
       </c>
       <c r="AP101">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="AQ101">
         <v>1.33</v>
@@ -22023,7 +22038,7 @@
         <v>0.14</v>
       </c>
       <c r="AP102">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ102">
         <v>0.44</v>
@@ -22151,7 +22166,7 @@
         <v>85</v>
       </c>
       <c r="P103" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q103">
         <v>2.14</v>
@@ -22232,7 +22247,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ103">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AR103">
         <v>1.65</v>
@@ -22357,7 +22372,7 @@
         <v>150</v>
       </c>
       <c r="P104" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q104">
         <v>3.4</v>
@@ -22435,10 +22450,10 @@
         <v>2</v>
       </c>
       <c r="AP104">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ104">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR104">
         <v>1.56</v>
@@ -22975,7 +22990,7 @@
         <v>85</v>
       </c>
       <c r="P107" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q107">
         <v>2.13</v>
@@ -23053,7 +23068,7 @@
         <v>0</v>
       </c>
       <c r="AP107">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ107">
         <v>0.44</v>
@@ -23181,7 +23196,7 @@
         <v>157</v>
       </c>
       <c r="P108" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q108">
         <v>3.38</v>
@@ -23262,7 +23277,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ108">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR108">
         <v>1.44</v>
@@ -23465,7 +23480,7 @@
         <v>0.86</v>
       </c>
       <c r="AP109">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="AQ109">
         <v>1</v>
@@ -23671,7 +23686,7 @@
         <v>2.33</v>
       </c>
       <c r="AP110">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ110">
         <v>2.25</v>
@@ -23880,7 +23895,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ111">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AR111">
         <v>1.5</v>
@@ -24211,7 +24226,7 @@
         <v>159</v>
       </c>
       <c r="P113" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q113">
         <v>3.4</v>
@@ -24286,13 +24301,13 @@
         <v>2.5</v>
       </c>
       <c r="AO113">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AP113">
         <v>2.1</v>
       </c>
       <c r="AQ113">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AR113">
         <v>1.85</v>
@@ -24623,7 +24638,7 @@
         <v>161</v>
       </c>
       <c r="P115" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q115">
         <v>4.85</v>
@@ -24695,16 +24710,16 @@
         <v>1.15</v>
       </c>
       <c r="AN115">
-        <v>0.88</v>
+        <v>0.63</v>
       </c>
       <c r="AO115">
         <v>1.57</v>
       </c>
       <c r="AP115">
-        <v>1.11</v>
+        <v>0.89</v>
       </c>
       <c r="AQ115">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR115">
         <v>1.19</v>
@@ -25035,7 +25050,7 @@
         <v>85</v>
       </c>
       <c r="P117" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q117">
         <v>3.64</v>
@@ -25241,7 +25256,7 @@
         <v>162</v>
       </c>
       <c r="P118" t="s">
-        <v>232</v>
+        <v>104</v>
       </c>
       <c r="Q118">
         <v>2.15</v>
@@ -25435,19 +25450,19 @@
         <v>1</v>
       </c>
       <c r="L119">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M119">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N119">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O119" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="P119" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q119">
         <v>4.4</v>
@@ -25525,10 +25540,10 @@
         <v>1.57</v>
       </c>
       <c r="AP119">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ119">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AR119">
         <v>1.71</v>
@@ -25731,7 +25746,7 @@
         <v>1.14</v>
       </c>
       <c r="AP120">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ120">
         <v>1.13</v>
@@ -25859,7 +25874,7 @@
         <v>163</v>
       </c>
       <c r="P121" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q121">
         <v>2.93</v>
@@ -25937,10 +25952,10 @@
         <v>1.38</v>
       </c>
       <c r="AP121">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ121">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR121">
         <v>1.8</v>
@@ -26683,7 +26698,7 @@
         <v>166</v>
       </c>
       <c r="P125" t="s">
-        <v>235</v>
+        <v>213</v>
       </c>
       <c r="Q125">
         <v>2.5</v>
@@ -26889,7 +26904,7 @@
         <v>167</v>
       </c>
       <c r="P126" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q126">
         <v>3.6</v>
@@ -26967,7 +26982,7 @@
         <v>1.73</v>
       </c>
       <c r="AP126">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="AQ126">
         <v>1.67</v>
@@ -27095,7 +27110,7 @@
         <v>168</v>
       </c>
       <c r="P127" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q127">
         <v>4.33</v>
@@ -27170,13 +27185,13 @@
         <v>1.22</v>
       </c>
       <c r="AO127">
-        <v>2.14</v>
+        <v>2.29</v>
       </c>
       <c r="AP127">
         <v>1.2</v>
       </c>
       <c r="AQ127">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AR127">
         <v>1.63</v>
@@ -27252,6 +27267,830 @@
       </c>
       <c r="BP127">
         <v>1.12</v>
+      </c>
+    </row>
+    <row r="128" spans="1:68">
+      <c r="A128" s="1">
+        <v>127</v>
+      </c>
+      <c r="B128">
+        <v>7813947</v>
+      </c>
+      <c r="C128" t="s">
+        <v>68</v>
+      </c>
+      <c r="D128" t="s">
+        <v>69</v>
+      </c>
+      <c r="E128" s="2">
+        <v>45843.29166666666</v>
+      </c>
+      <c r="F128">
+        <v>19</v>
+      </c>
+      <c r="G128" t="s">
+        <v>81</v>
+      </c>
+      <c r="H128" t="s">
+        <v>79</v>
+      </c>
+      <c r="I128">
+        <v>0</v>
+      </c>
+      <c r="J128">
+        <v>2</v>
+      </c>
+      <c r="K128">
+        <v>2</v>
+      </c>
+      <c r="L128">
+        <v>2</v>
+      </c>
+      <c r="M128">
+        <v>3</v>
+      </c>
+      <c r="N128">
+        <v>5</v>
+      </c>
+      <c r="O128" t="s">
+        <v>169</v>
+      </c>
+      <c r="P128" t="s">
+        <v>239</v>
+      </c>
+      <c r="Q128">
+        <v>3.5</v>
+      </c>
+      <c r="R128">
+        <v>2.25</v>
+      </c>
+      <c r="S128">
+        <v>2.7</v>
+      </c>
+      <c r="T128">
+        <v>1.33</v>
+      </c>
+      <c r="U128">
+        <v>3.1</v>
+      </c>
+      <c r="V128">
+        <v>2.6</v>
+      </c>
+      <c r="W128">
+        <v>1.44</v>
+      </c>
+      <c r="X128">
+        <v>6.5</v>
+      </c>
+      <c r="Y128">
+        <v>1.11</v>
+      </c>
+      <c r="Z128">
+        <v>2.95</v>
+      </c>
+      <c r="AA128">
+        <v>3.31</v>
+      </c>
+      <c r="AB128">
+        <v>2.09</v>
+      </c>
+      <c r="AC128">
+        <v>1.01</v>
+      </c>
+      <c r="AD128">
+        <v>11</v>
+      </c>
+      <c r="AE128">
+        <v>1.17</v>
+      </c>
+      <c r="AF128">
+        <v>4.05</v>
+      </c>
+      <c r="AG128">
+        <v>1.82</v>
+      </c>
+      <c r="AH128">
+        <v>1.88</v>
+      </c>
+      <c r="AI128">
+        <v>1.65</v>
+      </c>
+      <c r="AJ128">
+        <v>2.15</v>
+      </c>
+      <c r="AK128">
+        <v>1.62</v>
+      </c>
+      <c r="AL128">
+        <v>1.3</v>
+      </c>
+      <c r="AM128">
+        <v>1.36</v>
+      </c>
+      <c r="AN128">
+        <v>1.44</v>
+      </c>
+      <c r="AO128">
+        <v>1.75</v>
+      </c>
+      <c r="AP128">
+        <v>1.3</v>
+      </c>
+      <c r="AQ128">
+        <v>1.89</v>
+      </c>
+      <c r="AR128">
+        <v>1.71</v>
+      </c>
+      <c r="AS128">
+        <v>1.71</v>
+      </c>
+      <c r="AT128">
+        <v>3.42</v>
+      </c>
+      <c r="AU128">
+        <v>9</v>
+      </c>
+      <c r="AV128">
+        <v>9</v>
+      </c>
+      <c r="AW128">
+        <v>11</v>
+      </c>
+      <c r="AX128">
+        <v>12</v>
+      </c>
+      <c r="AY128">
+        <v>20</v>
+      </c>
+      <c r="AZ128">
+        <v>21</v>
+      </c>
+      <c r="BA128">
+        <v>7</v>
+      </c>
+      <c r="BB128">
+        <v>6</v>
+      </c>
+      <c r="BC128">
+        <v>13</v>
+      </c>
+      <c r="BD128">
+        <v>2.31</v>
+      </c>
+      <c r="BE128">
+        <v>6.59</v>
+      </c>
+      <c r="BF128">
+        <v>2.01</v>
+      </c>
+      <c r="BG128">
+        <v>1.59</v>
+      </c>
+      <c r="BH128">
+        <v>2.19</v>
+      </c>
+      <c r="BI128">
+        <v>2.01</v>
+      </c>
+      <c r="BJ128">
+        <v>1.71</v>
+      </c>
+      <c r="BK128">
+        <v>2.66</v>
+      </c>
+      <c r="BL128">
+        <v>1.39</v>
+      </c>
+      <c r="BM128">
+        <v>3.79</v>
+      </c>
+      <c r="BN128">
+        <v>1.18</v>
+      </c>
+      <c r="BO128">
+        <v>5.82</v>
+      </c>
+      <c r="BP128">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="129" spans="1:68">
+      <c r="A129" s="1">
+        <v>128</v>
+      </c>
+      <c r="B129">
+        <v>7813948</v>
+      </c>
+      <c r="C129" t="s">
+        <v>68</v>
+      </c>
+      <c r="D129" t="s">
+        <v>69</v>
+      </c>
+      <c r="E129" s="2">
+        <v>45843.29166666666</v>
+      </c>
+      <c r="F129">
+        <v>19</v>
+      </c>
+      <c r="G129" t="s">
+        <v>83</v>
+      </c>
+      <c r="H129" t="s">
+        <v>70</v>
+      </c>
+      <c r="I129">
+        <v>1</v>
+      </c>
+      <c r="J129">
+        <v>1</v>
+      </c>
+      <c r="K129">
+        <v>2</v>
+      </c>
+      <c r="L129">
+        <v>2</v>
+      </c>
+      <c r="M129">
+        <v>1</v>
+      </c>
+      <c r="N129">
+        <v>3</v>
+      </c>
+      <c r="O129" t="s">
+        <v>170</v>
+      </c>
+      <c r="P129" t="s">
+        <v>240</v>
+      </c>
+      <c r="Q129">
+        <v>4.33</v>
+      </c>
+      <c r="R129">
+        <v>2.15</v>
+      </c>
+      <c r="S129">
+        <v>2.45</v>
+      </c>
+      <c r="T129">
+        <v>1.4</v>
+      </c>
+      <c r="U129">
+        <v>2.88</v>
+      </c>
+      <c r="V129">
+        <v>2.9</v>
+      </c>
+      <c r="W129">
+        <v>1.36</v>
+      </c>
+      <c r="X129">
+        <v>8</v>
+      </c>
+      <c r="Y129">
+        <v>1.08</v>
+      </c>
+      <c r="Z129">
+        <v>3.71</v>
+      </c>
+      <c r="AA129">
+        <v>3.21</v>
+      </c>
+      <c r="AB129">
+        <v>1.86</v>
+      </c>
+      <c r="AC129">
+        <v>1</v>
+      </c>
+      <c r="AD129">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE129">
+        <v>1.24</v>
+      </c>
+      <c r="AF129">
+        <v>3.34</v>
+      </c>
+      <c r="AG129">
+        <v>1.93</v>
+      </c>
+      <c r="AH129">
+        <v>1.77</v>
+      </c>
+      <c r="AI129">
+        <v>1.83</v>
+      </c>
+      <c r="AJ129">
+        <v>1.91</v>
+      </c>
+      <c r="AK129">
+        <v>1.95</v>
+      </c>
+      <c r="AL129">
+        <v>1.3</v>
+      </c>
+      <c r="AM129">
+        <v>1.2</v>
+      </c>
+      <c r="AN129">
+        <v>1.83</v>
+      </c>
+      <c r="AO129">
+        <v>2.13</v>
+      </c>
+      <c r="AP129">
+        <v>2</v>
+      </c>
+      <c r="AQ129">
+        <v>1.89</v>
+      </c>
+      <c r="AR129">
+        <v>1.53</v>
+      </c>
+      <c r="AS129">
+        <v>1.18</v>
+      </c>
+      <c r="AT129">
+        <v>2.71</v>
+      </c>
+      <c r="AU129">
+        <v>4</v>
+      </c>
+      <c r="AV129">
+        <v>4</v>
+      </c>
+      <c r="AW129">
+        <v>3</v>
+      </c>
+      <c r="AX129">
+        <v>7</v>
+      </c>
+      <c r="AY129">
+        <v>7</v>
+      </c>
+      <c r="AZ129">
+        <v>11</v>
+      </c>
+      <c r="BA129">
+        <v>2</v>
+      </c>
+      <c r="BB129">
+        <v>9</v>
+      </c>
+      <c r="BC129">
+        <v>11</v>
+      </c>
+      <c r="BD129">
+        <v>3.16</v>
+      </c>
+      <c r="BE129">
+        <v>7.06</v>
+      </c>
+      <c r="BF129">
+        <v>1.62</v>
+      </c>
+      <c r="BG129">
+        <v>1.56</v>
+      </c>
+      <c r="BH129">
+        <v>2.25</v>
+      </c>
+      <c r="BI129">
+        <v>1.96</v>
+      </c>
+      <c r="BJ129">
+        <v>1.75</v>
+      </c>
+      <c r="BK129">
+        <v>2.57</v>
+      </c>
+      <c r="BL129">
+        <v>1.42</v>
+      </c>
+      <c r="BM129">
+        <v>3.62</v>
+      </c>
+      <c r="BN129">
+        <v>1.2</v>
+      </c>
+      <c r="BO129">
+        <v>5.5</v>
+      </c>
+      <c r="BP129">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="130" spans="1:68">
+      <c r="A130" s="1">
+        <v>129</v>
+      </c>
+      <c r="B130">
+        <v>7813949</v>
+      </c>
+      <c r="C130" t="s">
+        <v>68</v>
+      </c>
+      <c r="D130" t="s">
+        <v>69</v>
+      </c>
+      <c r="E130" s="2">
+        <v>45843.29166666666</v>
+      </c>
+      <c r="F130">
+        <v>19</v>
+      </c>
+      <c r="G130" t="s">
+        <v>82</v>
+      </c>
+      <c r="H130" t="s">
+        <v>75</v>
+      </c>
+      <c r="I130">
+        <v>0</v>
+      </c>
+      <c r="J130">
+        <v>1</v>
+      </c>
+      <c r="K130">
+        <v>1</v>
+      </c>
+      <c r="L130">
+        <v>2</v>
+      </c>
+      <c r="M130">
+        <v>1</v>
+      </c>
+      <c r="N130">
+        <v>3</v>
+      </c>
+      <c r="O130" t="s">
+        <v>171</v>
+      </c>
+      <c r="P130" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q130">
+        <v>4.2</v>
+      </c>
+      <c r="R130">
+        <v>2.2</v>
+      </c>
+      <c r="S130">
+        <v>2.45</v>
+      </c>
+      <c r="T130">
+        <v>1.35</v>
+      </c>
+      <c r="U130">
+        <v>3</v>
+      </c>
+      <c r="V130">
+        <v>2.7</v>
+      </c>
+      <c r="W130">
+        <v>1.44</v>
+      </c>
+      <c r="X130">
+        <v>7</v>
+      </c>
+      <c r="Y130">
+        <v>1.1</v>
+      </c>
+      <c r="Z130">
+        <v>3.89</v>
+      </c>
+      <c r="AA130">
+        <v>3.57</v>
+      </c>
+      <c r="AB130">
+        <v>1.72</v>
+      </c>
+      <c r="AC130">
+        <v>1.01</v>
+      </c>
+      <c r="AD130">
+        <v>11</v>
+      </c>
+      <c r="AE130">
+        <v>1.22</v>
+      </c>
+      <c r="AF130">
+        <v>3.5</v>
+      </c>
+      <c r="AG130">
+        <v>1.8</v>
+      </c>
+      <c r="AH130">
+        <v>1.9</v>
+      </c>
+      <c r="AI130">
+        <v>1.75</v>
+      </c>
+      <c r="AJ130">
+        <v>2</v>
+      </c>
+      <c r="AK130">
+        <v>1.85</v>
+      </c>
+      <c r="AL130">
+        <v>1.3</v>
+      </c>
+      <c r="AM130">
+        <v>1.25</v>
+      </c>
+      <c r="AN130">
+        <v>0.43</v>
+      </c>
+      <c r="AO130">
+        <v>1.33</v>
+      </c>
+      <c r="AP130">
+        <v>0.75</v>
+      </c>
+      <c r="AQ130">
+        <v>1.2</v>
+      </c>
+      <c r="AR130">
+        <v>1.45</v>
+      </c>
+      <c r="AS130">
+        <v>1.33</v>
+      </c>
+      <c r="AT130">
+        <v>2.78</v>
+      </c>
+      <c r="AU130">
+        <v>6</v>
+      </c>
+      <c r="AV130">
+        <v>3</v>
+      </c>
+      <c r="AW130">
+        <v>7</v>
+      </c>
+      <c r="AX130">
+        <v>8</v>
+      </c>
+      <c r="AY130">
+        <v>13</v>
+      </c>
+      <c r="AZ130">
+        <v>11</v>
+      </c>
+      <c r="BA130">
+        <v>1</v>
+      </c>
+      <c r="BB130">
+        <v>1</v>
+      </c>
+      <c r="BC130">
+        <v>2</v>
+      </c>
+      <c r="BD130">
+        <v>3.07</v>
+      </c>
+      <c r="BE130">
+        <v>6.9</v>
+      </c>
+      <c r="BF130">
+        <v>1.65</v>
+      </c>
+      <c r="BG130">
+        <v>1.64</v>
+      </c>
+      <c r="BH130">
+        <v>2.12</v>
+      </c>
+      <c r="BI130">
+        <v>2.08</v>
+      </c>
+      <c r="BJ130">
+        <v>1.66</v>
+      </c>
+      <c r="BK130">
+        <v>2.78</v>
+      </c>
+      <c r="BL130">
+        <v>1.36</v>
+      </c>
+      <c r="BM130">
+        <v>4.01</v>
+      </c>
+      <c r="BN130">
+        <v>1.16</v>
+      </c>
+      <c r="BO130">
+        <v>6.25</v>
+      </c>
+      <c r="BP130">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="131" spans="1:68">
+      <c r="A131" s="1">
+        <v>130</v>
+      </c>
+      <c r="B131">
+        <v>7813950</v>
+      </c>
+      <c r="C131" t="s">
+        <v>68</v>
+      </c>
+      <c r="D131" t="s">
+        <v>69</v>
+      </c>
+      <c r="E131" s="2">
+        <v>45843.29166666666</v>
+      </c>
+      <c r="F131">
+        <v>19</v>
+      </c>
+      <c r="G131" t="s">
+        <v>80</v>
+      </c>
+      <c r="H131" t="s">
+        <v>73</v>
+      </c>
+      <c r="I131">
+        <v>1</v>
+      </c>
+      <c r="J131">
+        <v>1</v>
+      </c>
+      <c r="K131">
+        <v>2</v>
+      </c>
+      <c r="L131">
+        <v>1</v>
+      </c>
+      <c r="M131">
+        <v>1</v>
+      </c>
+      <c r="N131">
+        <v>2</v>
+      </c>
+      <c r="O131" t="s">
+        <v>172</v>
+      </c>
+      <c r="P131" t="s">
+        <v>242</v>
+      </c>
+      <c r="Q131">
+        <v>2.8</v>
+      </c>
+      <c r="R131">
+        <v>2.1</v>
+      </c>
+      <c r="S131">
+        <v>3.6</v>
+      </c>
+      <c r="T131">
+        <v>1.4</v>
+      </c>
+      <c r="U131">
+        <v>2.8</v>
+      </c>
+      <c r="V131">
+        <v>2.9</v>
+      </c>
+      <c r="W131">
+        <v>1.36</v>
+      </c>
+      <c r="X131">
+        <v>7.5</v>
+      </c>
+      <c r="Y131">
+        <v>1.08</v>
+      </c>
+      <c r="Z131">
+        <v>2.2</v>
+      </c>
+      <c r="AA131">
+        <v>3.17</v>
+      </c>
+      <c r="AB131">
+        <v>2.86</v>
+      </c>
+      <c r="AC131">
+        <v>1.01</v>
+      </c>
+      <c r="AD131">
+        <v>8.4</v>
+      </c>
+      <c r="AE131">
+        <v>1.28</v>
+      </c>
+      <c r="AF131">
+        <v>3.08</v>
+      </c>
+      <c r="AG131">
+        <v>1.95</v>
+      </c>
+      <c r="AH131">
+        <v>1.75</v>
+      </c>
+      <c r="AI131">
+        <v>1.75</v>
+      </c>
+      <c r="AJ131">
+        <v>2</v>
+      </c>
+      <c r="AK131">
+        <v>1.36</v>
+      </c>
+      <c r="AL131">
+        <v>1.35</v>
+      </c>
+      <c r="AM131">
+        <v>1.6</v>
+      </c>
+      <c r="AN131">
+        <v>1.11</v>
+      </c>
+      <c r="AO131">
+        <v>1.13</v>
+      </c>
+      <c r="AP131">
+        <v>1.1</v>
+      </c>
+      <c r="AQ131">
+        <v>1.11</v>
+      </c>
+      <c r="AR131">
+        <v>1.67</v>
+      </c>
+      <c r="AS131">
+        <v>1.03</v>
+      </c>
+      <c r="AT131">
+        <v>2.7</v>
+      </c>
+      <c r="AU131">
+        <v>6</v>
+      </c>
+      <c r="AV131">
+        <v>6</v>
+      </c>
+      <c r="AW131">
+        <v>4</v>
+      </c>
+      <c r="AX131">
+        <v>1</v>
+      </c>
+      <c r="AY131">
+        <v>10</v>
+      </c>
+      <c r="AZ131">
+        <v>7</v>
+      </c>
+      <c r="BA131">
+        <v>2</v>
+      </c>
+      <c r="BB131">
+        <v>2</v>
+      </c>
+      <c r="BC131">
+        <v>4</v>
+      </c>
+      <c r="BD131">
+        <v>1.68</v>
+      </c>
+      <c r="BE131">
+        <v>6.88</v>
+      </c>
+      <c r="BF131">
+        <v>2.98</v>
+      </c>
+      <c r="BG131">
+        <v>1.61</v>
+      </c>
+      <c r="BH131">
+        <v>2.15</v>
+      </c>
+      <c r="BI131">
+        <v>2.04</v>
+      </c>
+      <c r="BJ131">
+        <v>1.69</v>
+      </c>
+      <c r="BK131">
+        <v>2.71</v>
+      </c>
+      <c r="BL131">
+        <v>1.37</v>
+      </c>
+      <c r="BM131">
+        <v>3.88</v>
+      </c>
+      <c r="BN131">
+        <v>1.17</v>
+      </c>
+      <c r="BO131">
+        <v>6.01</v>
+      </c>
+      <c r="BP131">
+        <v>1.04</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="212">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -469,60 +469,6 @@
     <t>['6']</t>
   </si>
   <si>
-    <t>['31', '88']</t>
-  </si>
-  <si>
-    <t>['52', '60', '69', '88']</t>
-  </si>
-  <si>
-    <t>['20', '69', '90+5']</t>
-  </si>
-  <si>
-    <t>['38']</t>
-  </si>
-  <si>
-    <t>['52']</t>
-  </si>
-  <si>
-    <t>['18']</t>
-  </si>
-  <si>
-    <t>['45+2', '65', '73']</t>
-  </si>
-  <si>
-    <t>['73', '80', '82']</t>
-  </si>
-  <si>
-    <t>['67']</t>
-  </si>
-  <si>
-    <t>['27', '65']</t>
-  </si>
-  <si>
-    <t>['17', '59', '63', '84']</t>
-  </si>
-  <si>
-    <t>['6', '72']</t>
-  </si>
-  <si>
-    <t>['27']</t>
-  </si>
-  <si>
-    <t>['35', '45']</t>
-  </si>
-  <si>
-    <t>['90+5']</t>
-  </si>
-  <si>
-    <t>['19']</t>
-  </si>
-  <si>
-    <t>['15', '60']</t>
-  </si>
-  <si>
-    <t>['37']</t>
-  </si>
-  <si>
     <t>['48', '68']</t>
   </si>
   <si>
@@ -536,6 +482,9 @@
   </si>
   <si>
     <t>['1', '6']</t>
+  </si>
+  <si>
+    <t>['67']</t>
   </si>
   <si>
     <t>['85']</t>
@@ -566,6 +515,9 @@
   </si>
   <si>
     <t>['71']</t>
+  </si>
+  <si>
+    <t>['90+5']</t>
   </si>
   <si>
     <t>['44']</t>
@@ -686,51 +638,6 @@
   </si>
   <si>
     <t>['65', '75']</t>
-  </si>
-  <si>
-    <t>['29']</t>
-  </si>
-  <si>
-    <t>['23', '44', '57']</t>
-  </si>
-  <si>
-    <t>['9', '90+6']</t>
-  </si>
-  <si>
-    <t>['15', '26']</t>
-  </si>
-  <si>
-    <t>['62', '90+5']</t>
-  </si>
-  <si>
-    <t>['66']</t>
-  </si>
-  <si>
-    <t>['90+3']</t>
-  </si>
-  <si>
-    <t>['17']</t>
-  </si>
-  <si>
-    <t>['15', '49']</t>
-  </si>
-  <si>
-    <t>['41', '56']</t>
-  </si>
-  <si>
-    <t>['5', '76']</t>
-  </si>
-  <si>
-    <t>['12', '56', '82']</t>
-  </si>
-  <si>
-    <t>['69']</t>
-  </si>
-  <si>
-    <t>['71', '90+6']</t>
-  </si>
-  <si>
-    <t>['90+7']</t>
   </si>
   <si>
     <t>['34', '44', '81']</t>
@@ -1104,7 +1011,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP131"/>
+  <dimension ref="A1:BP100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1438,10 +1345,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AQ2">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1566,7 +1473,7 @@
         <v>85</v>
       </c>
       <c r="P3" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="Q3">
         <v>3.8</v>
@@ -1644,10 +1551,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.89</v>
+        <v>0.57</v>
       </c>
       <c r="AQ3">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1850,10 +1757,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="AQ4">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1978,7 +1885,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="Q5">
         <v>4.5</v>
@@ -2056,10 +1963,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="AQ5">
-        <v>1.89</v>
+        <v>1.57</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2262,10 +2169,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.33</v>
+        <v>1.71</v>
       </c>
       <c r="AQ6">
-        <v>0.44</v>
+        <v>0.14</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2471,7 +2378,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ7">
-        <v>1.33</v>
+        <v>0.86</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2596,7 +2503,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="Q8">
         <v>2.39</v>
@@ -2674,7 +2581,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.89</v>
+        <v>1.57</v>
       </c>
       <c r="AQ8">
         <v>1</v>
@@ -2880,10 +2787,10 @@
         <v>3</v>
       </c>
       <c r="AP9">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AQ9">
-        <v>1.89</v>
+        <v>1.57</v>
       </c>
       <c r="AR9">
         <v>2.58</v>
@@ -3008,7 +2915,7 @@
         <v>85</v>
       </c>
       <c r="P10" t="s">
-        <v>175</v>
+        <v>158</v>
       </c>
       <c r="Q10">
         <v>4.3</v>
@@ -3086,10 +2993,10 @@
         <v>1</v>
       </c>
       <c r="AP10">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="AQ10">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR10">
         <v>0.82</v>
@@ -3214,7 +3121,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>176</v>
+        <v>159</v>
       </c>
       <c r="Q11">
         <v>2.8</v>
@@ -3295,7 +3202,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ11">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AR11">
         <v>1.04</v>
@@ -3498,10 +3405,10 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AQ12">
-        <v>1.33</v>
+        <v>0.86</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3626,7 +3533,7 @@
         <v>85</v>
       </c>
       <c r="P13" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="Q13">
         <v>2.43</v>
@@ -3704,10 +3611,10 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="AQ13">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR13">
         <v>1.4</v>
@@ -3832,7 +3739,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>178</v>
+        <v>161</v>
       </c>
       <c r="Q14">
         <v>3.9</v>
@@ -3910,10 +3817,10 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>0.89</v>
+        <v>0.57</v>
       </c>
       <c r="AQ14">
-        <v>1.56</v>
+        <v>1.83</v>
       </c>
       <c r="AR14">
         <v>1.15</v>
@@ -4116,7 +4023,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.33</v>
+        <v>1.71</v>
       </c>
       <c r="AQ15">
         <v>1</v>
@@ -4244,7 +4151,7 @@
         <v>85</v>
       </c>
       <c r="P16" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="Q16">
         <v>3.18</v>
@@ -4322,10 +4229,10 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.89</v>
+        <v>1.57</v>
       </c>
       <c r="AQ16">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AR16">
         <v>1.61</v>
@@ -4450,7 +4357,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="Q17">
         <v>3</v>
@@ -4528,10 +4435,10 @@
         <v>1.5</v>
       </c>
       <c r="AP17">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AQ17">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR17">
         <v>1.52</v>
@@ -4656,7 +4563,7 @@
         <v>85</v>
       </c>
       <c r="P18" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="Q18">
         <v>4.9</v>
@@ -4734,10 +4641,10 @@
         <v>2</v>
       </c>
       <c r="AP18">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="AQ18">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AR18">
         <v>1.29</v>
@@ -4862,7 +4769,7 @@
         <v>95</v>
       </c>
       <c r="P19" t="s">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="Q19">
         <v>2.71</v>
@@ -4940,7 +4847,7 @@
         <v>0.5</v>
       </c>
       <c r="AP19">
-        <v>1.2</v>
+        <v>0.71</v>
       </c>
       <c r="AQ19">
         <v>1</v>
@@ -5068,7 +4975,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="Q20">
         <v>3.5</v>
@@ -5149,7 +5056,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ20">
-        <v>1.89</v>
+        <v>1.57</v>
       </c>
       <c r="AR20">
         <v>1.06</v>
@@ -5352,10 +5259,10 @@
         <v>0.5</v>
       </c>
       <c r="AP21">
-        <v>0.89</v>
+        <v>0.57</v>
       </c>
       <c r="AQ21">
-        <v>1.33</v>
+        <v>0.86</v>
       </c>
       <c r="AR21">
         <v>1.02</v>
@@ -5480,7 +5387,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="Q22">
         <v>5</v>
@@ -5558,10 +5465,10 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.33</v>
+        <v>1.71</v>
       </c>
       <c r="AQ22">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AR22">
         <v>0.92</v>
@@ -5764,10 +5671,10 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AQ23">
-        <v>1.2</v>
+        <v>1.67</v>
       </c>
       <c r="AR23">
         <v>1.93</v>
@@ -5892,7 +5799,7 @@
         <v>99</v>
       </c>
       <c r="P24" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q24">
         <v>3</v>
@@ -5970,7 +5877,7 @@
         <v>1.33</v>
       </c>
       <c r="AP24">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AQ24">
         <v>1</v>
@@ -6176,10 +6083,10 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.2</v>
+        <v>0.71</v>
       </c>
       <c r="AQ25">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AR25">
         <v>2.07</v>
@@ -6382,10 +6289,10 @@
         <v>0.33</v>
       </c>
       <c r="AP26">
-        <v>2.1</v>
+        <v>2.43</v>
       </c>
       <c r="AQ26">
-        <v>1.33</v>
+        <v>0.86</v>
       </c>
       <c r="AR26">
         <v>0</v>
@@ -6510,7 +6417,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="Q27">
         <v>2.25</v>
@@ -6588,10 +6495,10 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="AQ27">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="AR27">
         <v>1.42</v>
@@ -6716,7 +6623,7 @@
         <v>101</v>
       </c>
       <c r="P28" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="Q28">
         <v>4</v>
@@ -6794,10 +6701,10 @@
         <v>2.33</v>
       </c>
       <c r="AP28">
-        <v>1.1</v>
+        <v>1.38</v>
       </c>
       <c r="AQ28">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AR28">
         <v>0</v>
@@ -6922,7 +6829,7 @@
         <v>102</v>
       </c>
       <c r="P29" t="s">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="Q29">
         <v>2.2</v>
@@ -7000,10 +6907,10 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.89</v>
+        <v>1.57</v>
       </c>
       <c r="AQ29">
-        <v>1.11</v>
+        <v>0.86</v>
       </c>
       <c r="AR29">
         <v>1.22</v>
@@ -7128,7 +7035,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="Q30">
         <v>3.75</v>
@@ -7206,10 +7113,10 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="AQ30">
-        <v>0.44</v>
+        <v>0.14</v>
       </c>
       <c r="AR30">
         <v>1.22</v>
@@ -7334,7 +7241,7 @@
         <v>104</v>
       </c>
       <c r="P31" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="Q31">
         <v>3.25</v>
@@ -7412,10 +7319,10 @@
         <v>2</v>
       </c>
       <c r="AP31">
-        <v>2.1</v>
+        <v>2.43</v>
       </c>
       <c r="AQ31">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AR31">
         <v>1.17</v>
@@ -7618,7 +7525,7 @@
         <v>1</v>
       </c>
       <c r="AP32">
-        <v>1.1</v>
+        <v>1.38</v>
       </c>
       <c r="AQ32">
         <v>1</v>
@@ -7746,7 +7653,7 @@
         <v>91</v>
       </c>
       <c r="P33" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="Q33">
         <v>2.63</v>
@@ -7824,10 +7731,10 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AQ33">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AR33">
         <v>1.69</v>
@@ -7952,7 +7859,7 @@
         <v>85</v>
       </c>
       <c r="P34" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="Q34">
         <v>3.8</v>
@@ -8030,10 +7937,10 @@
         <v>2</v>
       </c>
       <c r="AP34">
-        <v>0.89</v>
+        <v>0.57</v>
       </c>
       <c r="AQ34">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR34">
         <v>0.98</v>
@@ -8158,7 +8065,7 @@
         <v>106</v>
       </c>
       <c r="P35" t="s">
-        <v>191</v>
+        <v>175</v>
       </c>
       <c r="Q35">
         <v>2.8</v>
@@ -8239,7 +8146,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ35">
-        <v>1.56</v>
+        <v>1.83</v>
       </c>
       <c r="AR35">
         <v>1.05</v>
@@ -8442,10 +8349,10 @@
         <v>1</v>
       </c>
       <c r="AP36">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AQ36">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AR36">
         <v>0</v>
@@ -8651,7 +8558,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ37">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="AR37">
         <v>1.11</v>
@@ -8776,7 +8683,7 @@
         <v>85</v>
       </c>
       <c r="P38" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="Q38">
         <v>5</v>
@@ -8854,10 +8761,10 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AQ38">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AR38">
         <v>1.61</v>
@@ -8982,7 +8889,7 @@
         <v>85</v>
       </c>
       <c r="P39" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="Q39">
         <v>3.1</v>
@@ -9060,10 +8967,10 @@
         <v>1.6</v>
       </c>
       <c r="AP39">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="AQ39">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AR39">
         <v>1.6</v>
@@ -9266,10 +9173,10 @@
         <v>1.33</v>
       </c>
       <c r="AP40">
-        <v>2.1</v>
+        <v>2.43</v>
       </c>
       <c r="AQ40">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR40">
         <v>1.62</v>
@@ -9394,7 +9301,7 @@
         <v>110</v>
       </c>
       <c r="P41" t="s">
-        <v>194</v>
+        <v>178</v>
       </c>
       <c r="Q41">
         <v>3.25</v>
@@ -9472,10 +9379,10 @@
         <v>1.5</v>
       </c>
       <c r="AP41">
-        <v>1.2</v>
+        <v>0.71</v>
       </c>
       <c r="AQ41">
-        <v>1.56</v>
+        <v>1.83</v>
       </c>
       <c r="AR41">
         <v>1.52</v>
@@ -9600,7 +9507,7 @@
         <v>111</v>
       </c>
       <c r="P42" t="s">
-        <v>195</v>
+        <v>179</v>
       </c>
       <c r="Q42">
         <v>2.5</v>
@@ -9678,7 +9585,7 @@
         <v>0.8</v>
       </c>
       <c r="AP42">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AQ42">
         <v>1</v>
@@ -9884,10 +9791,10 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>1.33</v>
+        <v>1.71</v>
       </c>
       <c r="AQ43">
-        <v>1.11</v>
+        <v>0.86</v>
       </c>
       <c r="AR43">
         <v>1.02</v>
@@ -10012,7 +9919,7 @@
         <v>113</v>
       </c>
       <c r="P44" t="s">
-        <v>196</v>
+        <v>180</v>
       </c>
       <c r="Q44">
         <v>3.4</v>
@@ -10090,10 +9997,10 @@
         <v>0.5</v>
       </c>
       <c r="AP44">
-        <v>1.2</v>
+        <v>0.71</v>
       </c>
       <c r="AQ44">
-        <v>1.33</v>
+        <v>0.86</v>
       </c>
       <c r="AR44">
         <v>1.43</v>
@@ -10218,7 +10125,7 @@
         <v>113</v>
       </c>
       <c r="P45" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="Q45">
         <v>3.75</v>
@@ -10296,10 +10203,10 @@
         <v>1.83</v>
       </c>
       <c r="AP45">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AQ45">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AR45">
         <v>1.49</v>
@@ -10424,7 +10331,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="Q46">
         <v>3.75</v>
@@ -10502,10 +10409,10 @@
         <v>1</v>
       </c>
       <c r="AP46">
-        <v>1.89</v>
+        <v>1.57</v>
       </c>
       <c r="AQ46">
-        <v>1.89</v>
+        <v>1.57</v>
       </c>
       <c r="AR46">
         <v>1.33</v>
@@ -10630,7 +10537,7 @@
         <v>85</v>
       </c>
       <c r="P47" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="Q47">
         <v>3</v>
@@ -10708,10 +10615,10 @@
         <v>1</v>
       </c>
       <c r="AP47">
-        <v>1.1</v>
+        <v>1.38</v>
       </c>
       <c r="AQ47">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AR47">
         <v>1.74</v>
@@ -10914,7 +10821,7 @@
         <v>0.67</v>
       </c>
       <c r="AP48">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AQ48">
         <v>1</v>
@@ -11042,7 +10949,7 @@
         <v>116</v>
       </c>
       <c r="P49" t="s">
-        <v>199</v>
+        <v>183</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -11120,10 +11027,10 @@
         <v>0</v>
       </c>
       <c r="AP49">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="AQ49">
-        <v>1.2</v>
+        <v>1.67</v>
       </c>
       <c r="AR49">
         <v>1.58</v>
@@ -11326,10 +11233,10 @@
         <v>0</v>
       </c>
       <c r="AP50">
-        <v>0.89</v>
+        <v>0.57</v>
       </c>
       <c r="AQ50">
-        <v>1.11</v>
+        <v>0.86</v>
       </c>
       <c r="AR50">
         <v>1.01</v>
@@ -11454,7 +11361,7 @@
         <v>85</v>
       </c>
       <c r="P51" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="Q51">
         <v>2.25</v>
@@ -11738,10 +11645,10 @@
         <v>0</v>
       </c>
       <c r="AP52">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AQ52">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="AR52">
         <v>1.66</v>
@@ -11944,10 +11851,10 @@
         <v>0.5</v>
       </c>
       <c r="AP53">
-        <v>2.1</v>
+        <v>2.43</v>
       </c>
       <c r="AQ53">
-        <v>0.44</v>
+        <v>0.14</v>
       </c>
       <c r="AR53">
         <v>1.75</v>
@@ -12150,10 +12057,10 @@
         <v>2</v>
       </c>
       <c r="AP54">
-        <v>1.33</v>
+        <v>1.71</v>
       </c>
       <c r="AQ54">
-        <v>1.56</v>
+        <v>1.83</v>
       </c>
       <c r="AR54">
         <v>1.1</v>
@@ -12278,7 +12185,7 @@
         <v>119</v>
       </c>
       <c r="P55" t="s">
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="Q55">
         <v>5</v>
@@ -12356,10 +12263,10 @@
         <v>2</v>
       </c>
       <c r="AP55">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="AQ55">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AR55">
         <v>1.32</v>
@@ -12562,10 +12469,10 @@
         <v>2</v>
       </c>
       <c r="AP56">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AQ56">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AR56">
         <v>1.83</v>
@@ -12690,7 +12597,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="Q57">
         <v>3.75</v>
@@ -12768,10 +12675,10 @@
         <v>2.33</v>
       </c>
       <c r="AP57">
-        <v>1.1</v>
+        <v>1.38</v>
       </c>
       <c r="AQ57">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR57">
         <v>1.79</v>
@@ -12896,7 +12803,7 @@
         <v>121</v>
       </c>
       <c r="P58" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="Q58">
         <v>2.3</v>
@@ -12977,7 +12884,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ58">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR58">
         <v>1.31</v>
@@ -13102,7 +13009,7 @@
         <v>85</v>
       </c>
       <c r="P59" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="Q59">
         <v>3.2</v>
@@ -13180,7 +13087,7 @@
         <v>0.88</v>
       </c>
       <c r="AP59">
-        <v>0.89</v>
+        <v>0.57</v>
       </c>
       <c r="AQ59">
         <v>1</v>
@@ -13386,10 +13293,10 @@
         <v>1</v>
       </c>
       <c r="AP60">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AQ60">
-        <v>1.11</v>
+        <v>0.86</v>
       </c>
       <c r="AR60">
         <v>2.02</v>
@@ -13514,7 +13421,7 @@
         <v>123</v>
       </c>
       <c r="P61" t="s">
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="Q61">
         <v>4</v>
@@ -13592,10 +13499,10 @@
         <v>1.5</v>
       </c>
       <c r="AP61">
-        <v>1.89</v>
+        <v>1.57</v>
       </c>
       <c r="AQ61">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AR61">
         <v>1.39</v>
@@ -13720,7 +13627,7 @@
         <v>124</v>
       </c>
       <c r="P62" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="Q62">
         <v>2.3</v>
@@ -13798,10 +13705,10 @@
         <v>1.67</v>
       </c>
       <c r="AP62">
-        <v>2.1</v>
+        <v>2.43</v>
       </c>
       <c r="AQ62">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AR62">
         <v>1.79</v>
@@ -13926,7 +13833,7 @@
         <v>85</v>
       </c>
       <c r="P63" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="Q63">
         <v>3.2</v>
@@ -14004,10 +13911,10 @@
         <v>1.88</v>
       </c>
       <c r="AP63">
-        <v>1.2</v>
+        <v>0.71</v>
       </c>
       <c r="AQ63">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AR63">
         <v>1.54</v>
@@ -14132,7 +14039,7 @@
         <v>125</v>
       </c>
       <c r="P64" t="s">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="Q64">
         <v>2.5</v>
@@ -14210,10 +14117,10 @@
         <v>0.33</v>
       </c>
       <c r="AP64">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="AQ64">
-        <v>0.44</v>
+        <v>0.14</v>
       </c>
       <c r="AR64">
         <v>1.63</v>
@@ -14338,7 +14245,7 @@
         <v>126</v>
       </c>
       <c r="P65" t="s">
-        <v>207</v>
+        <v>191</v>
       </c>
       <c r="Q65">
         <v>4</v>
@@ -14416,10 +14323,10 @@
         <v>0.5</v>
       </c>
       <c r="AP65">
-        <v>1.33</v>
+        <v>1.71</v>
       </c>
       <c r="AQ65">
-        <v>1.2</v>
+        <v>1.67</v>
       </c>
       <c r="AR65">
         <v>1.07</v>
@@ -14544,7 +14451,7 @@
         <v>127</v>
       </c>
       <c r="P66" t="s">
-        <v>208</v>
+        <v>192</v>
       </c>
       <c r="Q66">
         <v>3</v>
@@ -14622,10 +14529,10 @@
         <v>2</v>
       </c>
       <c r="AP66">
-        <v>1.89</v>
+        <v>1.57</v>
       </c>
       <c r="AQ66">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AR66">
         <v>1.49</v>
@@ -14828,10 +14735,10 @@
         <v>0.8</v>
       </c>
       <c r="AP67">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="AQ67">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR67">
         <v>1.4</v>
@@ -14956,7 +14863,7 @@
         <v>129</v>
       </c>
       <c r="P68" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="Q68">
         <v>5</v>
@@ -15034,10 +14941,10 @@
         <v>1</v>
       </c>
       <c r="AP68">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ68">
-        <v>1.89</v>
+        <v>1.57</v>
       </c>
       <c r="AR68">
         <v>0</v>
@@ -15240,10 +15147,10 @@
         <v>1.75</v>
       </c>
       <c r="AP69">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AQ69">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR69">
         <v>1.6</v>
@@ -15446,10 +15353,10 @@
         <v>0.6</v>
       </c>
       <c r="AP70">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="AQ70">
-        <v>1.33</v>
+        <v>0.86</v>
       </c>
       <c r="AR70">
         <v>1.72</v>
@@ -15574,7 +15481,7 @@
         <v>132</v>
       </c>
       <c r="P71" t="s">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="Q71">
         <v>2.63</v>
@@ -15652,10 +15559,10 @@
         <v>0</v>
       </c>
       <c r="AP71">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AQ71">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="AR71">
         <v>1.45</v>
@@ -15858,10 +15765,10 @@
         <v>0.25</v>
       </c>
       <c r="AP72">
-        <v>1.2</v>
+        <v>0.71</v>
       </c>
       <c r="AQ72">
-        <v>0.44</v>
+        <v>0.14</v>
       </c>
       <c r="AR72">
         <v>1.67</v>
@@ -15986,7 +15893,7 @@
         <v>85</v>
       </c>
       <c r="P73" t="s">
-        <v>211</v>
+        <v>195</v>
       </c>
       <c r="Q73">
         <v>3.6</v>
@@ -16064,10 +15971,10 @@
         <v>1.75</v>
       </c>
       <c r="AP73">
-        <v>1.1</v>
+        <v>1.38</v>
       </c>
       <c r="AQ73">
-        <v>1.56</v>
+        <v>1.83</v>
       </c>
       <c r="AR73">
         <v>1.77</v>
@@ -16192,7 +16099,7 @@
         <v>85</v>
       </c>
       <c r="P74" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="Q74">
         <v>4.33</v>
@@ -16270,10 +16177,10 @@
         <v>2</v>
       </c>
       <c r="AP74">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AQ74">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AR74">
         <v>1.98</v>
@@ -16398,7 +16305,7 @@
         <v>134</v>
       </c>
       <c r="P75" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="Q75">
         <v>1.91</v>
@@ -16479,7 +16386,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ75">
-        <v>1.11</v>
+        <v>0.86</v>
       </c>
       <c r="AR75">
         <v>1.33</v>
@@ -16604,7 +16511,7 @@
         <v>135</v>
       </c>
       <c r="P76" t="s">
-        <v>213</v>
+        <v>197</v>
       </c>
       <c r="Q76">
         <v>2.63</v>
@@ -16682,10 +16589,10 @@
         <v>1.25</v>
       </c>
       <c r="AP76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ76">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AR76">
         <v>0</v>
@@ -16810,7 +16717,7 @@
         <v>85</v>
       </c>
       <c r="P77" t="s">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="Q77">
         <v>4.5</v>
@@ -16888,10 +16795,10 @@
         <v>2.33</v>
       </c>
       <c r="AP77">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ77">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AR77">
         <v>1.89</v>
@@ -17094,10 +17001,10 @@
         <v>0</v>
       </c>
       <c r="AP78">
-        <v>2.1</v>
+        <v>2.43</v>
       </c>
       <c r="AQ78">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="AR78">
         <v>1.79</v>
@@ -17222,7 +17129,7 @@
         <v>137</v>
       </c>
       <c r="P79" t="s">
-        <v>215</v>
+        <v>199</v>
       </c>
       <c r="Q79">
         <v>3.6</v>
@@ -17300,10 +17207,10 @@
         <v>0.5</v>
       </c>
       <c r="AP79">
-        <v>1.1</v>
+        <v>1.38</v>
       </c>
       <c r="AQ79">
-        <v>1.33</v>
+        <v>0.86</v>
       </c>
       <c r="AR79">
         <v>1.7</v>
@@ -17506,10 +17413,10 @@
         <v>0.2</v>
       </c>
       <c r="AP80">
-        <v>1.89</v>
+        <v>1.57</v>
       </c>
       <c r="AQ80">
-        <v>0.44</v>
+        <v>0.14</v>
       </c>
       <c r="AR80">
         <v>1.42</v>
@@ -17712,10 +17619,10 @@
         <v>1</v>
       </c>
       <c r="AP81">
-        <v>0.89</v>
+        <v>0.57</v>
       </c>
       <c r="AQ81">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AR81">
         <v>1.17</v>
@@ -17840,7 +17747,7 @@
         <v>140</v>
       </c>
       <c r="P82" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="Q82">
         <v>3.75</v>
@@ -17918,10 +17825,10 @@
         <v>1</v>
       </c>
       <c r="AP82">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="AQ82">
-        <v>1.89</v>
+        <v>1.57</v>
       </c>
       <c r="AR82">
         <v>1.65</v>
@@ -18046,7 +17953,7 @@
         <v>85</v>
       </c>
       <c r="P83" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="Q83">
         <v>7.5</v>
@@ -18124,10 +18031,10 @@
         <v>2.25</v>
       </c>
       <c r="AP83">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="AQ83">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AR83">
         <v>1.35</v>
@@ -18252,7 +18159,7 @@
         <v>141</v>
       </c>
       <c r="P84" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q84">
         <v>2.38</v>
@@ -18330,7 +18237,7 @@
         <v>1.11</v>
       </c>
       <c r="AP84">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ84">
         <v>1</v>
@@ -18458,7 +18365,7 @@
         <v>142</v>
       </c>
       <c r="P85" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="Q85">
         <v>3.75</v>
@@ -18536,10 +18443,10 @@
         <v>1.33</v>
       </c>
       <c r="AP85">
-        <v>1.2</v>
+        <v>0.71</v>
       </c>
       <c r="AQ85">
-        <v>1.2</v>
+        <v>1.67</v>
       </c>
       <c r="AR85">
         <v>1.63</v>
@@ -18664,7 +18571,7 @@
         <v>85</v>
       </c>
       <c r="P86" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="Q86">
         <v>4.2</v>
@@ -18742,10 +18649,10 @@
         <v>1.75</v>
       </c>
       <c r="AP86">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AQ86">
-        <v>1.2</v>
+        <v>1.67</v>
       </c>
       <c r="AR86">
         <v>1.42</v>
@@ -18948,10 +18855,10 @@
         <v>0.8</v>
       </c>
       <c r="AP87">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ87">
-        <v>1.11</v>
+        <v>0.86</v>
       </c>
       <c r="AR87">
         <v>1.66</v>
@@ -19154,10 +19061,10 @@
         <v>2.5</v>
       </c>
       <c r="AP88">
-        <v>1.33</v>
+        <v>1.71</v>
       </c>
       <c r="AQ88">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AR88">
         <v>1.04</v>
@@ -19282,7 +19189,7 @@
         <v>143</v>
       </c>
       <c r="P89" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="Q89">
         <v>2.62</v>
@@ -19360,10 +19267,10 @@
         <v>0</v>
       </c>
       <c r="AP89">
-        <v>1.1</v>
+        <v>1.38</v>
       </c>
       <c r="AQ89">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="AR89">
         <v>1.79</v>
@@ -19488,7 +19395,7 @@
         <v>144</v>
       </c>
       <c r="P90" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="Q90">
         <v>3.1</v>
@@ -19566,10 +19473,10 @@
         <v>2</v>
       </c>
       <c r="AP90">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AQ90">
-        <v>1.56</v>
+        <v>1.83</v>
       </c>
       <c r="AR90">
         <v>1.82</v>
@@ -19772,10 +19679,10 @@
         <v>1.9</v>
       </c>
       <c r="AP91">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AQ91">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AR91">
         <v>1.64</v>
@@ -19900,7 +19807,7 @@
         <v>146</v>
       </c>
       <c r="P92" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -19978,10 +19885,10 @@
         <v>1.4</v>
       </c>
       <c r="AP92">
-        <v>2.1</v>
+        <v>2.43</v>
       </c>
       <c r="AQ92">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR92">
         <v>1.86</v>
@@ -20106,7 +20013,7 @@
         <v>147</v>
       </c>
       <c r="P93" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="Q93">
         <v>2.62</v>
@@ -20187,7 +20094,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ93">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AR93">
         <v>1.35</v>
@@ -20312,7 +20219,7 @@
         <v>148</v>
       </c>
       <c r="P94" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="Q94">
         <v>2.4</v>
@@ -20390,10 +20297,10 @@
         <v>0.17</v>
       </c>
       <c r="AP94">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ94">
-        <v>0.44</v>
+        <v>0.14</v>
       </c>
       <c r="AR94">
         <v>1.56</v>
@@ -20518,7 +20425,7 @@
         <v>149</v>
       </c>
       <c r="P95" t="s">
-        <v>223</v>
+        <v>207</v>
       </c>
       <c r="Q95">
         <v>3.1</v>
@@ -20596,10 +20503,10 @@
         <v>0.67</v>
       </c>
       <c r="AP95">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ95">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR95">
         <v>1.52</v>
@@ -20802,10 +20709,10 @@
         <v>1</v>
       </c>
       <c r="AP96">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="AQ96">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AR96">
         <v>1.3</v>
@@ -20888,7 +20795,7 @@
         <v>96</v>
       </c>
       <c r="B97">
-        <v>7813916</v>
+        <v>7813947</v>
       </c>
       <c r="C97" t="s">
         <v>68</v>
@@ -20897,109 +20804,109 @@
         <v>69</v>
       </c>
       <c r="E97" s="2">
-        <v>45809.1875</v>
+        <v>45843.29166666666</v>
       </c>
       <c r="F97">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G97" t="s">
         <v>81</v>
       </c>
       <c r="H97" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I97">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J97">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K97">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L97">
         <v>2</v>
       </c>
       <c r="M97">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N97">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O97" t="s">
         <v>151</v>
       </c>
       <c r="P97" t="s">
-        <v>85</v>
+        <v>208</v>
       </c>
       <c r="Q97">
+        <v>3.5</v>
+      </c>
+      <c r="R97">
+        <v>2.25</v>
+      </c>
+      <c r="S97">
         <v>2.7</v>
       </c>
-      <c r="R97">
-        <v>2.1</v>
-      </c>
-      <c r="S97">
-        <v>4</v>
-      </c>
       <c r="T97">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="U97">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="V97">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="W97">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="X97">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="Y97">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Z97">
-        <v>2.11</v>
+        <v>2.95</v>
       </c>
       <c r="AA97">
-        <v>3.24</v>
+        <v>3.31</v>
       </c>
       <c r="AB97">
-        <v>3.25</v>
+        <v>2.09</v>
       </c>
       <c r="AC97">
         <v>1.01</v>
       </c>
       <c r="AD97">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="AE97">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AF97">
-        <v>2.83</v>
+        <v>4.05</v>
       </c>
       <c r="AG97">
-        <v>2.17</v>
+        <v>1.82</v>
       </c>
       <c r="AH97">
+        <v>1.88</v>
+      </c>
+      <c r="AI97">
+        <v>1.65</v>
+      </c>
+      <c r="AJ97">
+        <v>2.15</v>
+      </c>
+      <c r="AK97">
         <v>1.62</v>
       </c>
-      <c r="AI97">
-        <v>1.85</v>
-      </c>
-      <c r="AJ97">
-        <v>1.85</v>
-      </c>
-      <c r="AK97">
+      <c r="AL97">
         <v>1.3</v>
       </c>
-      <c r="AL97">
+      <c r="AM97">
         <v>1.36</v>
-      </c>
-      <c r="AM97">
-        <v>1.65</v>
       </c>
       <c r="AN97">
         <v>1.5</v>
@@ -21008,85 +20915,85 @@
         <v>1.33</v>
       </c>
       <c r="AP97">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AQ97">
-        <v>1.13</v>
+        <v>1.57</v>
       </c>
       <c r="AR97">
         <v>1.82</v>
       </c>
       <c r="AS97">
-        <v>1.31</v>
+        <v>1.71</v>
       </c>
       <c r="AT97">
-        <v>3.13</v>
+        <v>3.53</v>
       </c>
       <c r="AU97">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AV97">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AW97">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AX97">
+        <v>12</v>
+      </c>
+      <c r="AY97">
+        <v>20</v>
+      </c>
+      <c r="AZ97">
+        <v>21</v>
+      </c>
+      <c r="BA97">
+        <v>7</v>
+      </c>
+      <c r="BB97">
         <v>6</v>
       </c>
-      <c r="AY97">
-        <v>10</v>
-      </c>
-      <c r="AZ97">
-        <v>9</v>
-      </c>
-      <c r="BA97">
-        <v>4</v>
-      </c>
-      <c r="BB97">
-        <v>1</v>
-      </c>
       <c r="BC97">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="BD97">
-        <v>1.69</v>
+        <v>2.31</v>
       </c>
       <c r="BE97">
-        <v>7.6</v>
+        <v>6.59</v>
       </c>
       <c r="BF97">
-        <v>2.53</v>
+        <v>2.01</v>
       </c>
       <c r="BG97">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="BH97">
-        <v>2.44</v>
+        <v>2.19</v>
       </c>
       <c r="BI97">
-        <v>1.92</v>
+        <v>2.01</v>
       </c>
       <c r="BJ97">
-        <v>1.88</v>
+        <v>1.71</v>
       </c>
       <c r="BK97">
-        <v>2.42</v>
+        <v>2.66</v>
       </c>
       <c r="BL97">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="BM97">
-        <v>3.34</v>
+        <v>3.79</v>
       </c>
       <c r="BN97">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="BO97">
-        <v>4.25</v>
+        <v>5.82</v>
       </c>
       <c r="BP97">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="98" spans="1:68">
@@ -21094,7 +21001,7 @@
         <v>97</v>
       </c>
       <c r="B98">
-        <v>7813917</v>
+        <v>7813948</v>
       </c>
       <c r="C98" t="s">
         <v>68</v>
@@ -21103,82 +21010,82 @@
         <v>69</v>
       </c>
       <c r="E98" s="2">
-        <v>45809.29166666666</v>
+        <v>45843.29166666666</v>
       </c>
       <c r="F98">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G98" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H98" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="I98">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J98">
         <v>1</v>
       </c>
       <c r="K98">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L98">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M98">
         <v>1</v>
       </c>
       <c r="N98">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O98" t="s">
         <v>152</v>
       </c>
       <c r="P98" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="Q98">
-        <v>2.3</v>
+        <v>4.33</v>
       </c>
       <c r="R98">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="S98">
-        <v>4.4</v>
+        <v>2.45</v>
       </c>
       <c r="T98">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="U98">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="V98">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="W98">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="X98">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="Y98">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z98">
-        <v>1.69</v>
+        <v>3.71</v>
       </c>
       <c r="AA98">
-        <v>3.62</v>
+        <v>3.21</v>
       </c>
       <c r="AB98">
-        <v>3.95</v>
+        <v>1.86</v>
       </c>
       <c r="AC98">
         <v>1</v>
       </c>
       <c r="AD98">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE98">
         <v>1.24</v>
@@ -21187,112 +21094,112 @@
         <v>3.34</v>
       </c>
       <c r="AG98">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AH98">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="AI98">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AJ98">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AK98">
+        <v>1.95</v>
+      </c>
+      <c r="AL98">
+        <v>1.3</v>
+      </c>
+      <c r="AM98">
         <v>1.2</v>
       </c>
-      <c r="AL98">
+      <c r="AN98">
+        <v>3</v>
+      </c>
+      <c r="AO98">
+        <v>2.4</v>
+      </c>
+      <c r="AP98">
+        <v>3</v>
+      </c>
+      <c r="AQ98">
+        <v>2</v>
+      </c>
+      <c r="AR98">
+        <v>1.56</v>
+      </c>
+      <c r="AS98">
         <v>1.29</v>
       </c>
-      <c r="AM98">
-        <v>2</v>
-      </c>
-      <c r="AN98">
-        <v>2.43</v>
-      </c>
-      <c r="AO98">
-        <v>1.83</v>
-      </c>
-      <c r="AP98">
-        <v>2.1</v>
-      </c>
-      <c r="AQ98">
-        <v>1.56</v>
-      </c>
-      <c r="AR98">
-        <v>1.85</v>
-      </c>
-      <c r="AS98">
-        <v>1.64</v>
-      </c>
       <c r="AT98">
-        <v>3.49</v>
+        <v>2.85</v>
       </c>
       <c r="AU98">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AV98">
         <v>4</v>
       </c>
       <c r="AW98">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AX98">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY98">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="AZ98">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA98">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB98">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BC98">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BD98">
-        <v>1.63</v>
+        <v>3.16</v>
       </c>
       <c r="BE98">
-        <v>8.1</v>
+        <v>7.06</v>
       </c>
       <c r="BF98">
-        <v>2.62</v>
+        <v>1.62</v>
       </c>
       <c r="BG98">
-        <v>1.32</v>
+        <v>1.56</v>
       </c>
       <c r="BH98">
-        <v>2.88</v>
+        <v>2.25</v>
       </c>
       <c r="BI98">
-        <v>1.66</v>
+        <v>1.96</v>
       </c>
       <c r="BJ98">
-        <v>2.18</v>
+        <v>1.75</v>
       </c>
       <c r="BK98">
-        <v>2.1</v>
+        <v>2.57</v>
       </c>
       <c r="BL98">
-        <v>1.71</v>
+        <v>1.42</v>
       </c>
       <c r="BM98">
-        <v>2.69</v>
+        <v>3.62</v>
       </c>
       <c r="BN98">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="BO98">
-        <v>3.75</v>
+        <v>5.5</v>
       </c>
       <c r="BP98">
-        <v>1.19</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="99" spans="1:68">
@@ -21300,7 +21207,7 @@
         <v>98</v>
       </c>
       <c r="B99">
-        <v>7813918</v>
+        <v>7813949</v>
       </c>
       <c r="C99" t="s">
         <v>68</v>
@@ -21309,76 +21216,76 @@
         <v>69</v>
       </c>
       <c r="E99" s="2">
-        <v>45809.29166666666</v>
+        <v>45843.29166666666</v>
       </c>
       <c r="F99">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G99" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="H99" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="I99">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J99">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K99">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L99">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M99">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N99">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O99" t="s">
         <v>153</v>
       </c>
       <c r="P99" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="Q99">
-        <v>6.5</v>
+        <v>4.2</v>
       </c>
       <c r="R99">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="S99">
-        <v>1.85</v>
+        <v>2.45</v>
       </c>
       <c r="T99">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="U99">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="V99">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="W99">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="X99">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y99">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z99">
-        <v>6.9</v>
+        <v>3.89</v>
       </c>
       <c r="AA99">
-        <v>4.4</v>
+        <v>3.57</v>
       </c>
       <c r="AB99">
-        <v>1.34</v>
+        <v>1.72</v>
       </c>
       <c r="AC99">
         <v>1.01</v>
@@ -21387,118 +21294,118 @@
         <v>11</v>
       </c>
       <c r="AE99">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AF99">
-        <v>4.15</v>
+        <v>3.5</v>
       </c>
       <c r="AG99">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AH99">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AI99">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AJ99">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AK99">
-        <v>3</v>
+        <v>1.85</v>
       </c>
       <c r="AL99">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AM99">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="AN99">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AO99">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AP99">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="AQ99">
-        <v>1.89</v>
+        <v>1.67</v>
       </c>
       <c r="AR99">
-        <v>1.19</v>
+        <v>1.52</v>
       </c>
       <c r="AS99">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AT99">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="AU99">
         <v>6</v>
       </c>
       <c r="AV99">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AW99">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AX99">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AY99">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AZ99">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BA99">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BB99">
         <v>1</v>
       </c>
       <c r="BC99">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BD99">
-        <v>2.83</v>
+        <v>3.07</v>
       </c>
       <c r="BE99">
-        <v>8.1</v>
+        <v>6.9</v>
       </c>
       <c r="BF99">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="BG99">
-        <v>1.34</v>
+        <v>1.64</v>
       </c>
       <c r="BH99">
+        <v>2.12</v>
+      </c>
+      <c r="BI99">
+        <v>2.08</v>
+      </c>
+      <c r="BJ99">
+        <v>1.66</v>
+      </c>
+      <c r="BK99">
         <v>2.78</v>
       </c>
-      <c r="BI99">
-        <v>1.71</v>
-      </c>
-      <c r="BJ99">
-        <v>2.09</v>
-      </c>
-      <c r="BK99">
-        <v>2.15</v>
-      </c>
       <c r="BL99">
-        <v>1.68</v>
+        <v>1.36</v>
       </c>
       <c r="BM99">
-        <v>2.78</v>
+        <v>4.01</v>
       </c>
       <c r="BN99">
-        <v>1.34</v>
+        <v>1.16</v>
       </c>
       <c r="BO99">
-        <v>3.62</v>
+        <v>6.25</v>
       </c>
       <c r="BP99">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="100" spans="1:68">
@@ -21506,7 +21413,7 @@
         <v>99</v>
       </c>
       <c r="B100">
-        <v>7813920</v>
+        <v>7813950</v>
       </c>
       <c r="C100" t="s">
         <v>68</v>
@@ -21515,16 +21422,16 @@
         <v>69</v>
       </c>
       <c r="E100" s="2">
-        <v>45814.29166666666</v>
+        <v>45843.29166666666</v>
       </c>
       <c r="F100">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G100" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H100" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="I100">
         <v>1</v>
@@ -21539,6557 +21446,171 @@
         <v>1</v>
       </c>
       <c r="M100">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N100">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O100" t="s">
         <v>154</v>
       </c>
       <c r="P100" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="Q100">
-        <v>4.33</v>
+        <v>2.8</v>
       </c>
       <c r="R100">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S100">
-        <v>2.35</v>
+        <v>3.6</v>
       </c>
       <c r="T100">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="U100">
         <v>2.8</v>
       </c>
       <c r="V100">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="W100">
+        <v>1.36</v>
+      </c>
+      <c r="X100">
+        <v>7.5</v>
+      </c>
+      <c r="Y100">
+        <v>1.08</v>
+      </c>
+      <c r="Z100">
+        <v>2.2</v>
+      </c>
+      <c r="AA100">
+        <v>3.17</v>
+      </c>
+      <c r="AB100">
+        <v>2.86</v>
+      </c>
+      <c r="AC100">
+        <v>1.01</v>
+      </c>
+      <c r="AD100">
+        <v>8.4</v>
+      </c>
+      <c r="AE100">
+        <v>1.28</v>
+      </c>
+      <c r="AF100">
+        <v>3.08</v>
+      </c>
+      <c r="AG100">
+        <v>1.95</v>
+      </c>
+      <c r="AH100">
+        <v>1.75</v>
+      </c>
+      <c r="AI100">
+        <v>1.75</v>
+      </c>
+      <c r="AJ100">
+        <v>2</v>
+      </c>
+      <c r="AK100">
+        <v>1.36</v>
+      </c>
+      <c r="AL100">
+        <v>1.35</v>
+      </c>
+      <c r="AM100">
+        <v>1.6</v>
+      </c>
+      <c r="AN100">
+        <v>1.43</v>
+      </c>
+      <c r="AO100">
+        <v>0.83</v>
+      </c>
+      <c r="AP100">
         <v>1.38</v>
       </c>
-      <c r="X100">
-        <v>6.4</v>
-      </c>
-      <c r="Y100">
-        <v>1.05</v>
-      </c>
-      <c r="Z100">
+      <c r="AQ100">
+        <v>0.86</v>
+      </c>
+      <c r="AR100">
+        <v>1.78</v>
+      </c>
+      <c r="AS100">
+        <v>1.15</v>
+      </c>
+      <c r="AT100">
+        <v>2.93</v>
+      </c>
+      <c r="AU100">
+        <v>6</v>
+      </c>
+      <c r="AV100">
+        <v>6</v>
+      </c>
+      <c r="AW100">
         <v>4</v>
       </c>
-      <c r="AA100">
-        <v>3.52</v>
-      </c>
-      <c r="AB100">
-        <v>1.7</v>
-      </c>
-      <c r="AC100">
-        <v>1.05</v>
-      </c>
-      <c r="AD100">
-        <v>8.5</v>
-      </c>
-      <c r="AE100">
-        <v>1.3</v>
-      </c>
-      <c r="AF100">
-        <v>3.35</v>
-      </c>
-      <c r="AG100">
-        <v>1.89</v>
-      </c>
-      <c r="AH100">
-        <v>1.81</v>
-      </c>
-      <c r="AI100">
-        <v>1.8</v>
-      </c>
-      <c r="AJ100">
-        <v>1.83</v>
-      </c>
-      <c r="AK100">
-        <v>2</v>
-      </c>
-      <c r="AL100">
-        <v>1.22</v>
-      </c>
-      <c r="AM100">
-        <v>1.17</v>
-      </c>
-      <c r="AN100">
-        <v>1.71</v>
-      </c>
-      <c r="AO100">
-        <v>1.33</v>
-      </c>
-      <c r="AP100">
-        <v>1.33</v>
-      </c>
-      <c r="AQ100">
-        <v>1.89</v>
-      </c>
-      <c r="AR100">
-        <v>1.06</v>
-      </c>
-      <c r="AS100">
-        <v>1.71</v>
-      </c>
-      <c r="AT100">
-        <v>2.77</v>
-      </c>
-      <c r="AU100">
-        <v>5</v>
-      </c>
-      <c r="AV100">
-        <v>7</v>
-      </c>
-      <c r="AW100">
-        <v>5</v>
-      </c>
       <c r="AX100">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AY100">
         <v>10</v>
       </c>
       <c r="AZ100">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="BA100">
+        <v>2</v>
+      </c>
+      <c r="BB100">
+        <v>2</v>
+      </c>
+      <c r="BC100">
         <v>4</v>
       </c>
-      <c r="BB100">
-        <v>1</v>
-      </c>
-      <c r="BC100">
-        <v>5</v>
-      </c>
       <c r="BD100">
-        <v>3.12</v>
+        <v>1.68</v>
       </c>
       <c r="BE100">
-        <v>8.199999999999999</v>
+        <v>6.88</v>
       </c>
       <c r="BF100">
-        <v>1.48</v>
+        <v>2.98</v>
       </c>
       <c r="BG100">
-        <v>1.34</v>
+        <v>1.61</v>
       </c>
       <c r="BH100">
-        <v>2.78</v>
+        <v>2.15</v>
       </c>
       <c r="BI100">
-        <v>1.65</v>
+        <v>2.04</v>
       </c>
       <c r="BJ100">
-        <v>2.05</v>
+        <v>1.69</v>
       </c>
       <c r="BK100">
-        <v>2.08</v>
+        <v>2.71</v>
       </c>
       <c r="BL100">
-        <v>1.6</v>
+        <v>1.37</v>
       </c>
       <c r="BM100">
-        <v>2.78</v>
+        <v>3.88</v>
       </c>
       <c r="BN100">
-        <v>1.34</v>
+        <v>1.17</v>
       </c>
       <c r="BO100">
-        <v>3.55</v>
+        <v>6.01</v>
       </c>
       <c r="BP100">
-        <v>1.23</v>
-      </c>
-    </row>
-    <row r="101" spans="1:68">
-      <c r="A101" s="1">
-        <v>100</v>
-      </c>
-      <c r="B101">
-        <v>7813919</v>
-      </c>
-      <c r="C101" t="s">
-        <v>68</v>
-      </c>
-      <c r="D101" t="s">
-        <v>69</v>
-      </c>
-      <c r="E101" s="2">
-        <v>45814.29166666666</v>
-      </c>
-      <c r="F101">
-        <v>15</v>
-      </c>
-      <c r="G101" t="s">
-        <v>82</v>
-      </c>
-      <c r="H101" t="s">
-        <v>81</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>2</v>
-      </c>
-      <c r="K101">
-        <v>2</v>
-      </c>
-      <c r="L101">
-        <v>0</v>
-      </c>
-      <c r="M101">
-        <v>2</v>
-      </c>
-      <c r="N101">
-        <v>2</v>
-      </c>
-      <c r="O101" t="s">
-        <v>85</v>
-      </c>
-      <c r="P101" t="s">
-        <v>227</v>
-      </c>
-      <c r="Q101">
-        <v>3.88</v>
-      </c>
-      <c r="R101">
-        <v>2.04</v>
-      </c>
-      <c r="S101">
-        <v>2.7</v>
-      </c>
-      <c r="T101">
-        <v>1.4</v>
-      </c>
-      <c r="U101">
-        <v>2.72</v>
-      </c>
-      <c r="V101">
-        <v>2.93</v>
-      </c>
-      <c r="W101">
-        <v>1.35</v>
-      </c>
-      <c r="X101">
-        <v>7.3</v>
-      </c>
-      <c r="Y101">
-        <v>1.03</v>
-      </c>
-      <c r="Z101">
-        <v>3.24</v>
-      </c>
-      <c r="AA101">
-        <v>3.28</v>
-      </c>
-      <c r="AB101">
-        <v>2.1</v>
-      </c>
-      <c r="AC101">
-        <v>1.01</v>
-      </c>
-      <c r="AD101">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="AE101">
-        <v>1.29</v>
-      </c>
-      <c r="AF101">
-        <v>3.04</v>
-      </c>
-      <c r="AG101">
-        <v>2</v>
-      </c>
-      <c r="AH101">
-        <v>1.73</v>
-      </c>
-      <c r="AI101">
-        <v>1.79</v>
-      </c>
-      <c r="AJ101">
-        <v>1.87</v>
-      </c>
-      <c r="AK101">
-        <v>1.64</v>
-      </c>
-      <c r="AL101">
-        <v>1.28</v>
-      </c>
-      <c r="AM101">
-        <v>1.28</v>
-      </c>
-      <c r="AN101">
-        <v>0.5</v>
-      </c>
-      <c r="AO101">
-        <v>0.86</v>
-      </c>
-      <c r="AP101">
-        <v>0.75</v>
-      </c>
-      <c r="AQ101">
-        <v>1.33</v>
-      </c>
-      <c r="AR101">
-        <v>1.52</v>
-      </c>
-      <c r="AS101">
-        <v>1.4</v>
-      </c>
-      <c r="AT101">
-        <v>2.92</v>
-      </c>
-      <c r="AU101">
-        <v>0</v>
-      </c>
-      <c r="AV101">
-        <v>3</v>
-      </c>
-      <c r="AW101">
-        <v>7</v>
-      </c>
-      <c r="AX101">
-        <v>5</v>
-      </c>
-      <c r="AY101">
-        <v>7</v>
-      </c>
-      <c r="AZ101">
-        <v>8</v>
-      </c>
-      <c r="BA101">
-        <v>6</v>
-      </c>
-      <c r="BB101">
-        <v>10</v>
-      </c>
-      <c r="BC101">
-        <v>16</v>
-      </c>
-      <c r="BD101">
-        <v>2.6</v>
-      </c>
-      <c r="BE101">
-        <v>6.05</v>
-      </c>
-      <c r="BF101">
-        <v>1.76</v>
-      </c>
-      <c r="BG101">
-        <v>1.46</v>
-      </c>
-      <c r="BH101">
-        <v>2.38</v>
-      </c>
-      <c r="BI101">
-        <v>1.85</v>
-      </c>
-      <c r="BJ101">
-        <v>1.81</v>
-      </c>
-      <c r="BK101">
-        <v>2.42</v>
-      </c>
-      <c r="BL101">
-        <v>1.44</v>
-      </c>
-      <c r="BM101">
-        <v>3.34</v>
-      </c>
-      <c r="BN101">
-        <v>1.24</v>
-      </c>
-      <c r="BO101">
-        <v>4.25</v>
-      </c>
-      <c r="BP101">
-        <v>1.16</v>
-      </c>
-    </row>
-    <row r="102" spans="1:68">
-      <c r="A102" s="1">
-        <v>101</v>
-      </c>
-      <c r="B102">
-        <v>7813923</v>
-      </c>
-      <c r="C102" t="s">
-        <v>68</v>
-      </c>
-      <c r="D102" t="s">
-        <v>69</v>
-      </c>
-      <c r="E102" s="2">
-        <v>45815.29166666666</v>
-      </c>
-      <c r="F102">
-        <v>15</v>
-      </c>
-      <c r="G102" t="s">
-        <v>80</v>
-      </c>
-      <c r="H102" t="s">
-        <v>77</v>
-      </c>
-      <c r="I102">
-        <v>0</v>
-      </c>
-      <c r="J102">
-        <v>1</v>
-      </c>
-      <c r="K102">
-        <v>1</v>
-      </c>
-      <c r="L102">
-        <v>0</v>
-      </c>
-      <c r="M102">
-        <v>1</v>
-      </c>
-      <c r="N102">
-        <v>1</v>
-      </c>
-      <c r="O102" t="s">
-        <v>85</v>
-      </c>
-      <c r="P102" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q102">
-        <v>2.79</v>
-      </c>
-      <c r="R102">
-        <v>2.12</v>
-      </c>
-      <c r="S102">
-        <v>3.48</v>
-      </c>
-      <c r="T102">
-        <v>1.35</v>
-      </c>
-      <c r="U102">
-        <v>2.93</v>
-      </c>
-      <c r="V102">
-        <v>2.69</v>
-      </c>
-      <c r="W102">
-        <v>1.41</v>
-      </c>
-      <c r="X102">
-        <v>6.4</v>
-      </c>
-      <c r="Y102">
-        <v>1.05</v>
-      </c>
-      <c r="Z102">
-        <v>2.16</v>
-      </c>
-      <c r="AA102">
-        <v>3.38</v>
-      </c>
-      <c r="AB102">
-        <v>2.76</v>
-      </c>
-      <c r="AC102">
-        <v>1</v>
-      </c>
-      <c r="AD102">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AE102">
-        <v>1.22</v>
-      </c>
-      <c r="AF102">
-        <v>3.48</v>
-      </c>
-      <c r="AG102">
-        <v>1.82</v>
-      </c>
-      <c r="AH102">
-        <v>1.88</v>
-      </c>
-      <c r="AI102">
-        <v>1.65</v>
-      </c>
-      <c r="AJ102">
-        <v>2.05</v>
-      </c>
-      <c r="AK102">
-        <v>1.35</v>
-      </c>
-      <c r="AL102">
-        <v>1.26</v>
-      </c>
-      <c r="AM102">
-        <v>1.57</v>
-      </c>
-      <c r="AN102">
-        <v>1.43</v>
-      </c>
-      <c r="AO102">
-        <v>0.14</v>
-      </c>
-      <c r="AP102">
-        <v>1.1</v>
-      </c>
-      <c r="AQ102">
-        <v>0.44</v>
-      </c>
-      <c r="AR102">
-        <v>1.78</v>
-      </c>
-      <c r="AS102">
-        <v>1.09</v>
-      </c>
-      <c r="AT102">
-        <v>2.87</v>
-      </c>
-      <c r="AU102">
-        <v>6</v>
-      </c>
-      <c r="AV102">
-        <v>4</v>
-      </c>
-      <c r="AW102">
-        <v>1</v>
-      </c>
-      <c r="AX102">
-        <v>2</v>
-      </c>
-      <c r="AY102">
-        <v>7</v>
-      </c>
-      <c r="AZ102">
-        <v>6</v>
-      </c>
-      <c r="BA102">
-        <v>4</v>
-      </c>
-      <c r="BB102">
-        <v>3</v>
-      </c>
-      <c r="BC102">
-        <v>7</v>
-      </c>
-      <c r="BD102">
-        <v>2</v>
-      </c>
-      <c r="BE102">
-        <v>6.05</v>
-      </c>
-      <c r="BF102">
-        <v>2.21</v>
-      </c>
-      <c r="BG102">
-        <v>1.37</v>
-      </c>
-      <c r="BH102">
-        <v>2.66</v>
-      </c>
-      <c r="BI102">
-        <v>1.7</v>
-      </c>
-      <c r="BJ102">
-        <v>1.98</v>
-      </c>
-      <c r="BK102">
-        <v>2.15</v>
-      </c>
-      <c r="BL102">
-        <v>1.56</v>
-      </c>
-      <c r="BM102">
-        <v>2.92</v>
-      </c>
-      <c r="BN102">
-        <v>1.31</v>
-      </c>
-      <c r="BO102">
-        <v>3.48</v>
-      </c>
-      <c r="BP102">
-        <v>1.24</v>
-      </c>
-    </row>
-    <row r="103" spans="1:68">
-      <c r="A103" s="1">
-        <v>102</v>
-      </c>
-      <c r="B103">
-        <v>7813921</v>
-      </c>
-      <c r="C103" t="s">
-        <v>68</v>
-      </c>
-      <c r="D103" t="s">
-        <v>69</v>
-      </c>
-      <c r="E103" s="2">
-        <v>45815.29166666666</v>
-      </c>
-      <c r="F103">
-        <v>15</v>
-      </c>
-      <c r="G103" t="s">
-        <v>72</v>
-      </c>
-      <c r="H103" t="s">
-        <v>73</v>
-      </c>
-      <c r="I103">
-        <v>0</v>
-      </c>
-      <c r="J103">
-        <v>0</v>
-      </c>
-      <c r="K103">
-        <v>0</v>
-      </c>
-      <c r="L103">
-        <v>0</v>
-      </c>
-      <c r="M103">
-        <v>2</v>
-      </c>
-      <c r="N103">
-        <v>2</v>
-      </c>
-      <c r="O103" t="s">
-        <v>85</v>
-      </c>
-      <c r="P103" t="s">
-        <v>228</v>
-      </c>
-      <c r="Q103">
-        <v>2.14</v>
-      </c>
-      <c r="R103">
-        <v>2.16</v>
-      </c>
-      <c r="S103">
-        <v>5.35</v>
-      </c>
-      <c r="T103">
-        <v>1.37</v>
-      </c>
-      <c r="U103">
-        <v>2.84</v>
-      </c>
-      <c r="V103">
-        <v>2.8</v>
-      </c>
-      <c r="W103">
-        <v>1.38</v>
-      </c>
-      <c r="X103">
-        <v>6.85</v>
-      </c>
-      <c r="Y103">
-        <v>1.04</v>
-      </c>
-      <c r="Z103">
-        <v>1.55</v>
-      </c>
-      <c r="AA103">
-        <v>3.72</v>
-      </c>
-      <c r="AB103">
-        <v>4.8</v>
-      </c>
-      <c r="AC103">
-        <v>1</v>
-      </c>
-      <c r="AD103">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AE103">
-        <v>1.26</v>
-      </c>
-      <c r="AF103">
-        <v>3.22</v>
-      </c>
-      <c r="AG103">
-        <v>1.9</v>
-      </c>
-      <c r="AH103">
-        <v>1.8</v>
-      </c>
-      <c r="AI103">
-        <v>1.9</v>
-      </c>
-      <c r="AJ103">
-        <v>1.77</v>
-      </c>
-      <c r="AK103">
-        <v>1.11</v>
-      </c>
-      <c r="AL103">
-        <v>1.22</v>
-      </c>
-      <c r="AM103">
-        <v>2.22</v>
-      </c>
-      <c r="AN103">
-        <v>1.38</v>
-      </c>
-      <c r="AO103">
-        <v>0.83</v>
-      </c>
-      <c r="AP103">
-        <v>1.2</v>
-      </c>
-      <c r="AQ103">
-        <v>1.11</v>
-      </c>
-      <c r="AR103">
-        <v>1.65</v>
-      </c>
-      <c r="AS103">
-        <v>1.15</v>
-      </c>
-      <c r="AT103">
-        <v>2.8</v>
-      </c>
-      <c r="AU103">
-        <v>4</v>
-      </c>
-      <c r="AV103">
-        <v>3</v>
-      </c>
-      <c r="AW103">
-        <v>9</v>
-      </c>
-      <c r="AX103">
-        <v>0</v>
-      </c>
-      <c r="AY103">
-        <v>13</v>
-      </c>
-      <c r="AZ103">
-        <v>3</v>
-      </c>
-      <c r="BA103">
-        <v>9</v>
-      </c>
-      <c r="BB103">
-        <v>1</v>
-      </c>
-      <c r="BC103">
-        <v>10</v>
-      </c>
-      <c r="BD103">
-        <v>1.34</v>
-      </c>
-      <c r="BE103">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="BF103">
-        <v>3.9</v>
-      </c>
-      <c r="BG103">
-        <v>1.48</v>
-      </c>
-      <c r="BH103">
-        <v>2.33</v>
-      </c>
-      <c r="BI103">
-        <v>1.87</v>
-      </c>
-      <c r="BJ103">
-        <v>1.79</v>
-      </c>
-      <c r="BK103">
-        <v>2.46</v>
-      </c>
-      <c r="BL103">
-        <v>1.43</v>
-      </c>
-      <c r="BM103">
-        <v>3.42</v>
-      </c>
-      <c r="BN103">
-        <v>1.23</v>
-      </c>
-      <c r="BO103">
-        <v>4.9</v>
-      </c>
-      <c r="BP103">
-        <v>1.13</v>
-      </c>
-    </row>
-    <row r="104" spans="1:68">
-      <c r="A104" s="1">
-        <v>103</v>
-      </c>
-      <c r="B104">
-        <v>7813922</v>
-      </c>
-      <c r="C104" t="s">
-        <v>68</v>
-      </c>
-      <c r="D104" t="s">
-        <v>69</v>
-      </c>
-      <c r="E104" s="2">
-        <v>45815.29166666666</v>
-      </c>
-      <c r="F104">
-        <v>15</v>
-      </c>
-      <c r="G104" t="s">
-        <v>83</v>
-      </c>
-      <c r="H104" t="s">
-        <v>75</v>
-      </c>
-      <c r="I104">
-        <v>1</v>
-      </c>
-      <c r="J104">
-        <v>0</v>
-      </c>
-      <c r="K104">
-        <v>1</v>
-      </c>
-      <c r="L104">
-        <v>1</v>
-      </c>
-      <c r="M104">
-        <v>1</v>
-      </c>
-      <c r="N104">
-        <v>2</v>
-      </c>
-      <c r="O104" t="s">
-        <v>150</v>
-      </c>
-      <c r="P104" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q104">
-        <v>3.4</v>
-      </c>
-      <c r="R104">
-        <v>2.2</v>
-      </c>
-      <c r="S104">
-        <v>3</v>
-      </c>
-      <c r="T104">
-        <v>1.36</v>
-      </c>
-      <c r="U104">
-        <v>3</v>
-      </c>
-      <c r="V104">
-        <v>2.63</v>
-      </c>
-      <c r="W104">
-        <v>1.44</v>
-      </c>
-      <c r="X104">
-        <v>7</v>
-      </c>
-      <c r="Y104">
-        <v>1.1</v>
-      </c>
-      <c r="Z104">
-        <v>2.63</v>
-      </c>
-      <c r="AA104">
-        <v>3.29</v>
-      </c>
-      <c r="AB104">
-        <v>2.3</v>
-      </c>
-      <c r="AC104">
-        <v>1.05</v>
-      </c>
-      <c r="AD104">
-        <v>8.5</v>
-      </c>
-      <c r="AE104">
-        <v>1.25</v>
-      </c>
-      <c r="AF104">
-        <v>3.7</v>
-      </c>
-      <c r="AG104">
-        <v>1.8</v>
-      </c>
-      <c r="AH104">
-        <v>1.9</v>
-      </c>
-      <c r="AI104">
-        <v>1.67</v>
-      </c>
-      <c r="AJ104">
-        <v>2.1</v>
-      </c>
-      <c r="AK104">
-        <v>1.55</v>
-      </c>
-      <c r="AL104">
-        <v>1.29</v>
-      </c>
-      <c r="AM104">
-        <v>1.42</v>
-      </c>
-      <c r="AN104">
-        <v>3</v>
-      </c>
-      <c r="AO104">
-        <v>2</v>
-      </c>
-      <c r="AP104">
-        <v>2</v>
-      </c>
-      <c r="AQ104">
-        <v>1.2</v>
-      </c>
-      <c r="AR104">
-        <v>1.56</v>
-      </c>
-      <c r="AS104">
-        <v>1.18</v>
-      </c>
-      <c r="AT104">
-        <v>2.74</v>
-      </c>
-      <c r="AU104">
-        <v>4</v>
-      </c>
-      <c r="AV104">
-        <v>4</v>
-      </c>
-      <c r="AW104">
-        <v>3</v>
-      </c>
-      <c r="AX104">
-        <v>4</v>
-      </c>
-      <c r="AY104">
-        <v>7</v>
-      </c>
-      <c r="AZ104">
-        <v>8</v>
-      </c>
-      <c r="BA104">
-        <v>4</v>
-      </c>
-      <c r="BB104">
-        <v>8</v>
-      </c>
-      <c r="BC104">
-        <v>12</v>
-      </c>
-      <c r="BD104">
-        <v>2.05</v>
-      </c>
-      <c r="BE104">
-        <v>6</v>
-      </c>
-      <c r="BF104">
-        <v>2.16</v>
-      </c>
-      <c r="BG104">
-        <v>1.44</v>
-      </c>
-      <c r="BH104">
-        <v>2.43</v>
-      </c>
-      <c r="BI104">
-        <v>1.91</v>
-      </c>
-      <c r="BJ104">
-        <v>1.8</v>
-      </c>
-      <c r="BK104">
-        <v>2.35</v>
-      </c>
-      <c r="BL104">
-        <v>1.47</v>
-      </c>
-      <c r="BM104">
-        <v>3.2</v>
-      </c>
-      <c r="BN104">
-        <v>1.26</v>
-      </c>
-      <c r="BO104">
-        <v>4.2</v>
-      </c>
-      <c r="BP104">
-        <v>1.17</v>
-      </c>
-    </row>
-    <row r="105" spans="1:68">
-      <c r="A105" s="1">
-        <v>104</v>
-      </c>
-      <c r="B105">
-        <v>7813924</v>
-      </c>
-      <c r="C105" t="s">
-        <v>68</v>
-      </c>
-      <c r="D105" t="s">
-        <v>69</v>
-      </c>
-      <c r="E105" s="2">
-        <v>45816.29166666666</v>
-      </c>
-      <c r="F105">
-        <v>15</v>
-      </c>
-      <c r="G105" t="s">
-        <v>70</v>
-      </c>
-      <c r="H105" t="s">
-        <v>76</v>
-      </c>
-      <c r="I105">
-        <v>0</v>
-      </c>
-      <c r="J105">
-        <v>0</v>
-      </c>
-      <c r="K105">
-        <v>0</v>
-      </c>
-      <c r="L105">
-        <v>1</v>
-      </c>
-      <c r="M105">
-        <v>0</v>
-      </c>
-      <c r="N105">
-        <v>1</v>
-      </c>
-      <c r="O105" t="s">
-        <v>155</v>
-      </c>
-      <c r="P105" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q105">
-        <v>2.25</v>
-      </c>
-      <c r="R105">
-        <v>2.2</v>
-      </c>
-      <c r="S105">
-        <v>5.5</v>
-      </c>
-      <c r="T105">
-        <v>1.4</v>
-      </c>
-      <c r="U105">
-        <v>2.75</v>
-      </c>
-      <c r="V105">
-        <v>3</v>
-      </c>
-      <c r="W105">
-        <v>1.36</v>
-      </c>
-      <c r="X105">
-        <v>8</v>
-      </c>
-      <c r="Y105">
-        <v>1.08</v>
-      </c>
-      <c r="Z105">
-        <v>1.62</v>
-      </c>
-      <c r="AA105">
-        <v>3.56</v>
-      </c>
-      <c r="AB105">
-        <v>4.6</v>
-      </c>
-      <c r="AC105">
-        <v>1</v>
-      </c>
-      <c r="AD105">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AE105">
-        <v>1.26</v>
-      </c>
-      <c r="AF105">
-        <v>3.22</v>
-      </c>
-      <c r="AG105">
-        <v>1.94</v>
-      </c>
-      <c r="AH105">
-        <v>1.76</v>
-      </c>
-      <c r="AI105">
-        <v>2</v>
-      </c>
-      <c r="AJ105">
-        <v>1.73</v>
-      </c>
-      <c r="AK105">
-        <v>1.18</v>
-      </c>
-      <c r="AL105">
-        <v>1.3</v>
-      </c>
-      <c r="AM105">
-        <v>2.05</v>
-      </c>
-      <c r="AN105">
-        <v>2.75</v>
-      </c>
-      <c r="AO105">
-        <v>1.57</v>
-      </c>
-      <c r="AP105">
-        <v>2.8</v>
-      </c>
-      <c r="AQ105">
-        <v>1.56</v>
-      </c>
-      <c r="AR105">
-        <v>1.75</v>
-      </c>
-      <c r="AS105">
-        <v>1.64</v>
-      </c>
-      <c r="AT105">
-        <v>3.39</v>
-      </c>
-      <c r="AU105">
-        <v>6</v>
-      </c>
-      <c r="AV105">
-        <v>0</v>
-      </c>
-      <c r="AW105">
-        <v>6</v>
-      </c>
-      <c r="AX105">
-        <v>4</v>
-      </c>
-      <c r="AY105">
-        <v>12</v>
-      </c>
-      <c r="AZ105">
-        <v>4</v>
-      </c>
-      <c r="BA105">
-        <v>3</v>
-      </c>
-      <c r="BB105">
-        <v>2</v>
-      </c>
-      <c r="BC105">
-        <v>5</v>
-      </c>
-      <c r="BD105">
-        <v>1.55</v>
-      </c>
-      <c r="BE105">
-        <v>7.8</v>
-      </c>
-      <c r="BF105">
-        <v>2.9</v>
-      </c>
-      <c r="BG105">
-        <v>1.46</v>
-      </c>
-      <c r="BH105">
-        <v>2.38</v>
-      </c>
-      <c r="BI105">
-        <v>1.85</v>
-      </c>
-      <c r="BJ105">
-        <v>1.81</v>
-      </c>
-      <c r="BK105">
-        <v>2.42</v>
-      </c>
-      <c r="BL105">
-        <v>1.44</v>
-      </c>
-      <c r="BM105">
-        <v>3.34</v>
-      </c>
-      <c r="BN105">
-        <v>1.24</v>
-      </c>
-      <c r="BO105">
-        <v>4</v>
-      </c>
-      <c r="BP105">
-        <v>1.19</v>
-      </c>
-    </row>
-    <row r="106" spans="1:68">
-      <c r="A106" s="1">
-        <v>105</v>
-      </c>
-      <c r="B106">
-        <v>7813925</v>
-      </c>
-      <c r="C106" t="s">
-        <v>68</v>
-      </c>
-      <c r="D106" t="s">
-        <v>69</v>
-      </c>
-      <c r="E106" s="2">
-        <v>45816.29166666666</v>
-      </c>
-      <c r="F106">
-        <v>15</v>
-      </c>
-      <c r="G106" t="s">
-        <v>78</v>
-      </c>
-      <c r="H106" t="s">
-        <v>71</v>
-      </c>
-      <c r="I106">
-        <v>1</v>
-      </c>
-      <c r="J106">
-        <v>0</v>
-      </c>
-      <c r="K106">
-        <v>1</v>
-      </c>
-      <c r="L106">
-        <v>1</v>
-      </c>
-      <c r="M106">
-        <v>0</v>
-      </c>
-      <c r="N106">
-        <v>1</v>
-      </c>
-      <c r="O106" t="s">
-        <v>156</v>
-      </c>
-      <c r="P106" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q106">
-        <v>2.5</v>
-      </c>
-      <c r="R106">
-        <v>2.2</v>
-      </c>
-      <c r="S106">
-        <v>4.5</v>
-      </c>
-      <c r="T106">
-        <v>1.4</v>
-      </c>
-      <c r="U106">
-        <v>2.75</v>
-      </c>
-      <c r="V106">
-        <v>3</v>
-      </c>
-      <c r="W106">
-        <v>1.36</v>
-      </c>
-      <c r="X106">
-        <v>8</v>
-      </c>
-      <c r="Y106">
-        <v>1.08</v>
-      </c>
-      <c r="Z106">
-        <v>1.82</v>
-      </c>
-      <c r="AA106">
-        <v>3.31</v>
-      </c>
-      <c r="AB106">
-        <v>3.71</v>
-      </c>
-      <c r="AC106">
-        <v>1.01</v>
-      </c>
-      <c r="AD106">
-        <v>8.5</v>
-      </c>
-      <c r="AE106">
-        <v>1.27</v>
-      </c>
-      <c r="AF106">
-        <v>3.14</v>
-      </c>
-      <c r="AG106">
-        <v>1.95</v>
-      </c>
-      <c r="AH106">
-        <v>1.75</v>
-      </c>
-      <c r="AI106">
-        <v>1.83</v>
-      </c>
-      <c r="AJ106">
-        <v>1.83</v>
-      </c>
-      <c r="AK106">
-        <v>1.22</v>
-      </c>
-      <c r="AL106">
-        <v>1.3</v>
-      </c>
-      <c r="AM106">
-        <v>1.85</v>
-      </c>
-      <c r="AN106">
-        <v>0.71</v>
-      </c>
-      <c r="AO106">
-        <v>0</v>
-      </c>
-      <c r="AP106">
-        <v>1.2</v>
-      </c>
-      <c r="AQ106">
-        <v>0.44</v>
-      </c>
-      <c r="AR106">
-        <v>1.56</v>
-      </c>
-      <c r="AS106">
-        <v>1.27</v>
-      </c>
-      <c r="AT106">
-        <v>2.83</v>
-      </c>
-      <c r="AU106">
-        <v>3</v>
-      </c>
-      <c r="AV106">
-        <v>2</v>
-      </c>
-      <c r="AW106">
-        <v>11</v>
-      </c>
-      <c r="AX106">
-        <v>4</v>
-      </c>
-      <c r="AY106">
-        <v>14</v>
-      </c>
-      <c r="AZ106">
-        <v>6</v>
-      </c>
-      <c r="BA106">
-        <v>11</v>
-      </c>
-      <c r="BB106">
-        <v>2</v>
-      </c>
-      <c r="BC106">
-        <v>13</v>
-      </c>
-      <c r="BD106">
-        <v>1.65</v>
-      </c>
-      <c r="BE106">
-        <v>6.2</v>
-      </c>
-      <c r="BF106">
-        <v>2.85</v>
-      </c>
-      <c r="BG106">
-        <v>1.44</v>
-      </c>
-      <c r="BH106">
-        <v>2.43</v>
-      </c>
-      <c r="BI106">
-        <v>1.81</v>
-      </c>
-      <c r="BJ106">
-        <v>1.85</v>
-      </c>
-      <c r="BK106">
-        <v>2.33</v>
-      </c>
-      <c r="BL106">
-        <v>1.48</v>
-      </c>
-      <c r="BM106">
-        <v>3.2</v>
-      </c>
-      <c r="BN106">
-        <v>1.26</v>
-      </c>
-      <c r="BO106">
-        <v>4.05</v>
-      </c>
-      <c r="BP106">
-        <v>1.18</v>
-      </c>
-    </row>
-    <row r="107" spans="1:68">
-      <c r="A107" s="1">
-        <v>106</v>
-      </c>
-      <c r="B107">
-        <v>7813926</v>
-      </c>
-      <c r="C107" t="s">
-        <v>68</v>
-      </c>
-      <c r="D107" t="s">
-        <v>69</v>
-      </c>
-      <c r="E107" s="2">
-        <v>45822.29166666666</v>
-      </c>
-      <c r="F107">
-        <v>16</v>
-      </c>
-      <c r="G107" t="s">
-        <v>81</v>
-      </c>
-      <c r="H107" t="s">
-        <v>71</v>
-      </c>
-      <c r="I107">
-        <v>0</v>
-      </c>
-      <c r="J107">
-        <v>0</v>
-      </c>
-      <c r="K107">
-        <v>0</v>
-      </c>
-      <c r="L107">
-        <v>0</v>
-      </c>
-      <c r="M107">
-        <v>1</v>
-      </c>
-      <c r="N107">
-        <v>1</v>
-      </c>
-      <c r="O107" t="s">
-        <v>85</v>
-      </c>
-      <c r="P107" t="s">
-        <v>230</v>
-      </c>
-      <c r="Q107">
-        <v>2.13</v>
-      </c>
-      <c r="R107">
-        <v>2.45</v>
-      </c>
-      <c r="S107">
-        <v>5.42</v>
-      </c>
-      <c r="T107">
-        <v>1.32</v>
-      </c>
-      <c r="U107">
-        <v>3.3</v>
-      </c>
-      <c r="V107">
-        <v>2.59</v>
-      </c>
-      <c r="W107">
-        <v>1.49</v>
-      </c>
-      <c r="X107">
-        <v>5.5</v>
-      </c>
-      <c r="Y107">
-        <v>1.11</v>
-      </c>
-      <c r="Z107">
-        <v>1.57</v>
-      </c>
-      <c r="AA107">
-        <v>3.83</v>
-      </c>
-      <c r="AB107">
-        <v>4.5</v>
-      </c>
-      <c r="AC107">
-        <v>1.02</v>
-      </c>
-      <c r="AD107">
-        <v>10</v>
-      </c>
-      <c r="AE107">
-        <v>1.25</v>
-      </c>
-      <c r="AF107">
-        <v>3.6</v>
-      </c>
-      <c r="AG107">
-        <v>1.76</v>
-      </c>
-      <c r="AH107">
-        <v>1.94</v>
-      </c>
-      <c r="AI107">
-        <v>1.75</v>
-      </c>
-      <c r="AJ107">
-        <v>1.95</v>
-      </c>
-      <c r="AK107">
-        <v>1.18</v>
-      </c>
-      <c r="AL107">
-        <v>1.22</v>
-      </c>
-      <c r="AM107">
-        <v>2.3</v>
-      </c>
-      <c r="AN107">
-        <v>1.71</v>
-      </c>
-      <c r="AO107">
-        <v>0</v>
-      </c>
-      <c r="AP107">
-        <v>1.3</v>
-      </c>
-      <c r="AQ107">
-        <v>0.44</v>
-      </c>
-      <c r="AR107">
-        <v>1.82</v>
-      </c>
-      <c r="AS107">
-        <v>1.19</v>
-      </c>
-      <c r="AT107">
-        <v>3.01</v>
-      </c>
-      <c r="AU107">
-        <v>5</v>
-      </c>
-      <c r="AV107">
-        <v>2</v>
-      </c>
-      <c r="AW107">
-        <v>9</v>
-      </c>
-      <c r="AX107">
-        <v>6</v>
-      </c>
-      <c r="AY107">
-        <v>14</v>
-      </c>
-      <c r="AZ107">
-        <v>8</v>
-      </c>
-      <c r="BA107">
-        <v>2</v>
-      </c>
-      <c r="BB107">
-        <v>1</v>
-      </c>
-      <c r="BC107">
-        <v>3</v>
-      </c>
-      <c r="BD107">
-        <v>1.45</v>
-      </c>
-      <c r="BE107">
-        <v>8.5</v>
-      </c>
-      <c r="BF107">
-        <v>3.22</v>
-      </c>
-      <c r="BG107">
-        <v>1.32</v>
-      </c>
-      <c r="BH107">
-        <v>2.88</v>
-      </c>
-      <c r="BI107">
-        <v>1.8</v>
-      </c>
-      <c r="BJ107">
-        <v>2</v>
-      </c>
-      <c r="BK107">
-        <v>2.05</v>
-      </c>
-      <c r="BL107">
-        <v>1.65</v>
-      </c>
-      <c r="BM107">
-        <v>2.7</v>
-      </c>
-      <c r="BN107">
-        <v>1.36</v>
-      </c>
-      <c r="BO107">
-        <v>3.78</v>
-      </c>
-      <c r="BP107">
-        <v>1.19</v>
-      </c>
-    </row>
-    <row r="108" spans="1:68">
-      <c r="A108" s="1">
-        <v>107</v>
-      </c>
-      <c r="B108">
-        <v>7813927</v>
-      </c>
-      <c r="C108" t="s">
-        <v>68</v>
-      </c>
-      <c r="D108" t="s">
-        <v>69</v>
-      </c>
-      <c r="E108" s="2">
-        <v>45822.29166666666</v>
-      </c>
-      <c r="F108">
-        <v>16</v>
-      </c>
-      <c r="G108" t="s">
-        <v>76</v>
-      </c>
-      <c r="H108" t="s">
-        <v>75</v>
-      </c>
-      <c r="I108">
-        <v>1</v>
-      </c>
-      <c r="J108">
-        <v>1</v>
-      </c>
-      <c r="K108">
-        <v>2</v>
-      </c>
-      <c r="L108">
-        <v>3</v>
-      </c>
-      <c r="M108">
-        <v>1</v>
-      </c>
-      <c r="N108">
-        <v>4</v>
-      </c>
-      <c r="O108" t="s">
-        <v>157</v>
-      </c>
-      <c r="P108" t="s">
-        <v>231</v>
-      </c>
-      <c r="Q108">
-        <v>3.38</v>
-      </c>
-      <c r="R108">
-        <v>2.29</v>
-      </c>
-      <c r="S108">
-        <v>3.05</v>
-      </c>
-      <c r="T108">
-        <v>1.34</v>
-      </c>
-      <c r="U108">
-        <v>3.19</v>
-      </c>
-      <c r="V108">
-        <v>2.71</v>
-      </c>
-      <c r="W108">
-        <v>1.45</v>
-      </c>
-      <c r="X108">
-        <v>6</v>
-      </c>
-      <c r="Y108">
-        <v>1.09</v>
-      </c>
-      <c r="Z108">
-        <v>2.65</v>
-      </c>
-      <c r="AA108">
-        <v>3.17</v>
-      </c>
-      <c r="AB108">
-        <v>2.34</v>
-      </c>
-      <c r="AC108">
-        <v>1.02</v>
-      </c>
-      <c r="AD108">
-        <v>10</v>
-      </c>
-      <c r="AE108">
-        <v>1.29</v>
-      </c>
-      <c r="AF108">
-        <v>3.4</v>
-      </c>
-      <c r="AG108">
-        <v>1.87</v>
-      </c>
-      <c r="AH108">
-        <v>1.83</v>
-      </c>
-      <c r="AI108">
-        <v>1.67</v>
-      </c>
-      <c r="AJ108">
-        <v>2.1</v>
-      </c>
-      <c r="AK108">
-        <v>1.57</v>
-      </c>
-      <c r="AL108">
-        <v>1.3</v>
-      </c>
-      <c r="AM108">
-        <v>1.44</v>
-      </c>
-      <c r="AN108">
-        <v>1.57</v>
-      </c>
-      <c r="AO108">
-        <v>1.83</v>
-      </c>
-      <c r="AP108">
-        <v>1.89</v>
-      </c>
-      <c r="AQ108">
-        <v>1.2</v>
-      </c>
-      <c r="AR108">
-        <v>1.44</v>
-      </c>
-      <c r="AS108">
-        <v>1.23</v>
-      </c>
-      <c r="AT108">
-        <v>2.67</v>
-      </c>
-      <c r="AU108">
-        <v>9</v>
-      </c>
-      <c r="AV108">
-        <v>3</v>
-      </c>
-      <c r="AW108">
-        <v>10</v>
-      </c>
-      <c r="AX108">
-        <v>8</v>
-      </c>
-      <c r="AY108">
-        <v>19</v>
-      </c>
-      <c r="AZ108">
-        <v>11</v>
-      </c>
-      <c r="BA108">
-        <v>5</v>
-      </c>
-      <c r="BB108">
-        <v>5</v>
-      </c>
-      <c r="BC108">
-        <v>10</v>
-      </c>
-      <c r="BD108">
-        <v>1.83</v>
-      </c>
-      <c r="BE108">
-        <v>6.1</v>
-      </c>
-      <c r="BF108">
-        <v>2.45</v>
-      </c>
-      <c r="BG108">
-        <v>1.39</v>
-      </c>
-      <c r="BH108">
-        <v>2.59</v>
-      </c>
-      <c r="BI108">
-        <v>1.85</v>
-      </c>
-      <c r="BJ108">
-        <v>1.95</v>
-      </c>
-      <c r="BK108">
-        <v>2.19</v>
-      </c>
-      <c r="BL108">
-        <v>1.54</v>
-      </c>
-      <c r="BM108">
-        <v>2.97</v>
-      </c>
-      <c r="BN108">
-        <v>1.3</v>
-      </c>
-      <c r="BO108">
-        <v>3.7</v>
-      </c>
-      <c r="BP108">
-        <v>1.22</v>
-      </c>
-    </row>
-    <row r="109" spans="1:68">
-      <c r="A109" s="1">
-        <v>108</v>
-      </c>
-      <c r="B109">
-        <v>7813928</v>
-      </c>
-      <c r="C109" t="s">
-        <v>68</v>
-      </c>
-      <c r="D109" t="s">
-        <v>69</v>
-      </c>
-      <c r="E109" s="2">
-        <v>45822.29166666666</v>
-      </c>
-      <c r="F109">
-        <v>16</v>
-      </c>
-      <c r="G109" t="s">
-        <v>82</v>
-      </c>
-      <c r="H109" t="s">
-        <v>74</v>
-      </c>
-      <c r="I109">
-        <v>0</v>
-      </c>
-      <c r="J109">
-        <v>0</v>
-      </c>
-      <c r="K109">
-        <v>0</v>
-      </c>
-      <c r="L109">
-        <v>0</v>
-      </c>
-      <c r="M109">
-        <v>1</v>
-      </c>
-      <c r="N109">
-        <v>1</v>
-      </c>
-      <c r="O109" t="s">
-        <v>85</v>
-      </c>
-      <c r="P109" t="s">
-        <v>91</v>
-      </c>
-      <c r="Q109">
-        <v>3.32</v>
-      </c>
-      <c r="R109">
-        <v>2.04</v>
-      </c>
-      <c r="S109">
-        <v>3.08</v>
-      </c>
-      <c r="T109">
-        <v>1.41</v>
-      </c>
-      <c r="U109">
-        <v>2.69</v>
-      </c>
-      <c r="V109">
-        <v>2.93</v>
-      </c>
-      <c r="W109">
-        <v>1.35</v>
-      </c>
-      <c r="X109">
-        <v>6.95</v>
-      </c>
-      <c r="Y109">
-        <v>1.04</v>
-      </c>
-      <c r="Z109">
-        <v>2.59</v>
-      </c>
-      <c r="AA109">
-        <v>3.12</v>
-      </c>
-      <c r="AB109">
-        <v>2.42</v>
-      </c>
-      <c r="AC109">
-        <v>1.02</v>
-      </c>
-      <c r="AD109">
-        <v>8.1</v>
-      </c>
-      <c r="AE109">
-        <v>1.3</v>
-      </c>
-      <c r="AF109">
-        <v>2.97</v>
-      </c>
-      <c r="AG109">
-        <v>2</v>
-      </c>
-      <c r="AH109">
-        <v>1.67</v>
-      </c>
-      <c r="AI109">
-        <v>1.76</v>
-      </c>
-      <c r="AJ109">
-        <v>1.91</v>
-      </c>
-      <c r="AK109">
-        <v>1.47</v>
-      </c>
-      <c r="AL109">
-        <v>1.28</v>
-      </c>
-      <c r="AM109">
-        <v>1.41</v>
-      </c>
-      <c r="AN109">
-        <v>0.4</v>
-      </c>
-      <c r="AO109">
-        <v>0.86</v>
-      </c>
-      <c r="AP109">
-        <v>0.75</v>
-      </c>
-      <c r="AQ109">
-        <v>1</v>
-      </c>
-      <c r="AR109">
-        <v>1.41</v>
-      </c>
-      <c r="AS109">
-        <v>1.21</v>
-      </c>
-      <c r="AT109">
-        <v>2.62</v>
-      </c>
-      <c r="AU109">
-        <v>4</v>
-      </c>
-      <c r="AV109">
-        <v>6</v>
-      </c>
-      <c r="AW109">
-        <v>6</v>
-      </c>
-      <c r="AX109">
-        <v>7</v>
-      </c>
-      <c r="AY109">
-        <v>10</v>
-      </c>
-      <c r="AZ109">
-        <v>13</v>
-      </c>
-      <c r="BA109">
-        <v>2</v>
-      </c>
-      <c r="BB109">
-        <v>2</v>
-      </c>
-      <c r="BC109">
-        <v>4</v>
-      </c>
-      <c r="BD109">
-        <v>1.98</v>
-      </c>
-      <c r="BE109">
-        <v>5.95</v>
-      </c>
-      <c r="BF109">
-        <v>2.25</v>
-      </c>
-      <c r="BG109">
-        <v>1.47</v>
-      </c>
-      <c r="BH109">
-        <v>2.35</v>
-      </c>
-      <c r="BI109">
-        <v>1.86</v>
-      </c>
-      <c r="BJ109">
-        <v>1.8</v>
-      </c>
-      <c r="BK109">
-        <v>2.43</v>
-      </c>
-      <c r="BL109">
-        <v>1.44</v>
-      </c>
-      <c r="BM109">
-        <v>3.34</v>
-      </c>
-      <c r="BN109">
-        <v>1.24</v>
-      </c>
-      <c r="BO109">
-        <v>4.4</v>
-      </c>
-      <c r="BP109">
-        <v>1.15</v>
-      </c>
-    </row>
-    <row r="110" spans="1:68">
-      <c r="A110" s="1">
-        <v>109</v>
-      </c>
-      <c r="B110">
-        <v>7813929</v>
-      </c>
-      <c r="C110" t="s">
-        <v>68</v>
-      </c>
-      <c r="D110" t="s">
-        <v>69</v>
-      </c>
-      <c r="E110" s="2">
-        <v>45823.29166666666</v>
-      </c>
-      <c r="F110">
-        <v>16</v>
-      </c>
-      <c r="G110" t="s">
-        <v>83</v>
-      </c>
-      <c r="H110" t="s">
-        <v>72</v>
-      </c>
-      <c r="I110">
-        <v>0</v>
-      </c>
-      <c r="J110">
-        <v>1</v>
-      </c>
-      <c r="K110">
-        <v>1</v>
-      </c>
-      <c r="L110">
-        <v>0</v>
-      </c>
-      <c r="M110">
-        <v>1</v>
-      </c>
-      <c r="N110">
-        <v>1</v>
-      </c>
-      <c r="O110" t="s">
-        <v>85</v>
-      </c>
-      <c r="P110" t="s">
-        <v>154</v>
-      </c>
-      <c r="Q110">
-        <v>3.25</v>
-      </c>
-      <c r="R110">
-        <v>2.2</v>
-      </c>
-      <c r="S110">
-        <v>3.25</v>
-      </c>
-      <c r="T110">
-        <v>1.4</v>
-      </c>
-      <c r="U110">
-        <v>2.75</v>
-      </c>
-      <c r="V110">
-        <v>2.75</v>
-      </c>
-      <c r="W110">
-        <v>1.4</v>
-      </c>
-      <c r="X110">
-        <v>8</v>
-      </c>
-      <c r="Y110">
-        <v>1.08</v>
-      </c>
-      <c r="Z110">
-        <v>2.63</v>
-      </c>
-      <c r="AA110">
-        <v>3.1</v>
-      </c>
-      <c r="AB110">
-        <v>2.4</v>
-      </c>
-      <c r="AC110">
-        <v>1.05</v>
-      </c>
-      <c r="AD110">
-        <v>8.5</v>
-      </c>
-      <c r="AE110">
-        <v>1.3</v>
-      </c>
-      <c r="AF110">
-        <v>3.3</v>
-      </c>
-      <c r="AG110">
-        <v>1.91</v>
-      </c>
-      <c r="AH110">
-        <v>1.79</v>
-      </c>
-      <c r="AI110">
-        <v>1.73</v>
-      </c>
-      <c r="AJ110">
-        <v>2</v>
-      </c>
-      <c r="AK110">
-        <v>1.51</v>
-      </c>
-      <c r="AL110">
-        <v>1.3</v>
-      </c>
-      <c r="AM110">
-        <v>1.44</v>
-      </c>
-      <c r="AN110">
-        <v>2.5</v>
-      </c>
-      <c r="AO110">
-        <v>2.33</v>
-      </c>
-      <c r="AP110">
-        <v>2</v>
-      </c>
-      <c r="AQ110">
-        <v>2.25</v>
-      </c>
-      <c r="AR110">
-        <v>1.42</v>
-      </c>
-      <c r="AS110">
-        <v>1.12</v>
-      </c>
-      <c r="AT110">
-        <v>2.54</v>
-      </c>
-      <c r="AU110">
-        <v>6</v>
-      </c>
-      <c r="AV110">
-        <v>4</v>
-      </c>
-      <c r="AW110">
-        <v>10</v>
-      </c>
-      <c r="AX110">
-        <v>10</v>
-      </c>
-      <c r="AY110">
-        <v>16</v>
-      </c>
-      <c r="AZ110">
-        <v>14</v>
-      </c>
-      <c r="BA110">
-        <v>6</v>
-      </c>
-      <c r="BB110">
-        <v>4</v>
-      </c>
-      <c r="BC110">
-        <v>10</v>
-      </c>
-      <c r="BD110">
-        <v>1.92</v>
-      </c>
-      <c r="BE110">
-        <v>5.95</v>
-      </c>
-      <c r="BF110">
-        <v>2.33</v>
-      </c>
-      <c r="BG110">
-        <v>1.47</v>
-      </c>
-      <c r="BH110">
-        <v>2.35</v>
-      </c>
-      <c r="BI110">
-        <v>1.85</v>
-      </c>
-      <c r="BJ110">
-        <v>1.81</v>
-      </c>
-      <c r="BK110">
-        <v>2.43</v>
-      </c>
-      <c r="BL110">
-        <v>1.44</v>
-      </c>
-      <c r="BM110">
-        <v>3.34</v>
-      </c>
-      <c r="BN110">
-        <v>1.24</v>
-      </c>
-      <c r="BO110">
-        <v>4.2</v>
-      </c>
-      <c r="BP110">
-        <v>1.17</v>
-      </c>
-    </row>
-    <row r="111" spans="1:68">
-      <c r="A111" s="1">
-        <v>110</v>
-      </c>
-      <c r="B111">
-        <v>7813930</v>
-      </c>
-      <c r="C111" t="s">
-        <v>68</v>
-      </c>
-      <c r="D111" t="s">
-        <v>69</v>
-      </c>
-      <c r="E111" s="2">
-        <v>45823.29166666666</v>
-      </c>
-      <c r="F111">
-        <v>16</v>
-      </c>
-      <c r="G111" t="s">
-        <v>77</v>
-      </c>
-      <c r="H111" t="s">
-        <v>73</v>
-      </c>
-      <c r="I111">
-        <v>0</v>
-      </c>
-      <c r="J111">
-        <v>0</v>
-      </c>
-      <c r="K111">
-        <v>0</v>
-      </c>
-      <c r="L111">
-        <v>0</v>
-      </c>
-      <c r="M111">
-        <v>0</v>
-      </c>
-      <c r="N111">
-        <v>0</v>
-      </c>
-      <c r="O111" t="s">
-        <v>85</v>
-      </c>
-      <c r="P111" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q111">
-        <v>2.75</v>
-      </c>
-      <c r="R111">
-        <v>2.1</v>
-      </c>
-      <c r="S111">
-        <v>4.33</v>
-      </c>
-      <c r="T111">
-        <v>1.44</v>
-      </c>
-      <c r="U111">
-        <v>2.63</v>
-      </c>
-      <c r="V111">
-        <v>3.25</v>
-      </c>
-      <c r="W111">
-        <v>1.33</v>
-      </c>
-      <c r="X111">
-        <v>9</v>
-      </c>
-      <c r="Y111">
-        <v>1.07</v>
-      </c>
-      <c r="Z111">
-        <v>1.97</v>
-      </c>
-      <c r="AA111">
-        <v>3.19</v>
-      </c>
-      <c r="AB111">
-        <v>3.36</v>
-      </c>
-      <c r="AC111">
-        <v>1.06</v>
-      </c>
-      <c r="AD111">
-        <v>8</v>
-      </c>
-      <c r="AE111">
-        <v>1.36</v>
-      </c>
-      <c r="AF111">
-        <v>3</v>
-      </c>
-      <c r="AG111">
-        <v>2</v>
-      </c>
-      <c r="AH111">
-        <v>1.65</v>
-      </c>
-      <c r="AI111">
-        <v>1.91</v>
-      </c>
-      <c r="AJ111">
-        <v>1.8</v>
-      </c>
-      <c r="AK111">
-        <v>1.29</v>
-      </c>
-      <c r="AL111">
-        <v>1.3</v>
-      </c>
-      <c r="AM111">
-        <v>1.73</v>
-      </c>
-      <c r="AN111">
-        <v>1.14</v>
-      </c>
-      <c r="AO111">
-        <v>1.14</v>
-      </c>
-      <c r="AP111">
-        <v>1.33</v>
-      </c>
-      <c r="AQ111">
-        <v>1.11</v>
-      </c>
-      <c r="AR111">
-        <v>1.5</v>
-      </c>
-      <c r="AS111">
-        <v>1.06</v>
-      </c>
-      <c r="AT111">
-        <v>2.56</v>
-      </c>
-      <c r="AU111">
-        <v>2</v>
-      </c>
-      <c r="AV111">
-        <v>2</v>
-      </c>
-      <c r="AW111">
-        <v>0</v>
-      </c>
-      <c r="AX111">
-        <v>4</v>
-      </c>
-      <c r="AY111">
-        <v>2</v>
-      </c>
-      <c r="AZ111">
-        <v>6</v>
-      </c>
-      <c r="BA111">
-        <v>0</v>
-      </c>
-      <c r="BB111">
-        <v>3</v>
-      </c>
-      <c r="BC111">
-        <v>3</v>
-      </c>
-      <c r="BD111">
-        <v>1.54</v>
-      </c>
-      <c r="BE111">
-        <v>7.9</v>
-      </c>
-      <c r="BF111">
-        <v>2.92</v>
-      </c>
-      <c r="BG111">
-        <v>1.43</v>
-      </c>
-      <c r="BH111">
-        <v>2.46</v>
-      </c>
-      <c r="BI111">
-        <v>1.81</v>
-      </c>
-      <c r="BJ111">
-        <v>1.85</v>
-      </c>
-      <c r="BK111">
-        <v>2.33</v>
-      </c>
-      <c r="BL111">
-        <v>1.48</v>
-      </c>
-      <c r="BM111">
-        <v>3.2</v>
-      </c>
-      <c r="BN111">
-        <v>1.26</v>
-      </c>
-      <c r="BO111">
-        <v>4.15</v>
-      </c>
-      <c r="BP111">
-        <v>1.17</v>
-      </c>
-    </row>
-    <row r="112" spans="1:68">
-      <c r="A112" s="1">
-        <v>111</v>
-      </c>
-      <c r="B112">
-        <v>7813931</v>
-      </c>
-      <c r="C112" t="s">
-        <v>68</v>
-      </c>
-      <c r="D112" t="s">
-        <v>69</v>
-      </c>
-      <c r="E112" s="2">
-        <v>45823.29166666666</v>
-      </c>
-      <c r="F112">
-        <v>16</v>
-      </c>
-      <c r="G112" t="s">
-        <v>78</v>
-      </c>
-      <c r="H112" t="s">
-        <v>80</v>
-      </c>
-      <c r="I112">
-        <v>0</v>
-      </c>
-      <c r="J112">
-        <v>0</v>
-      </c>
-      <c r="K112">
-        <v>0</v>
-      </c>
-      <c r="L112">
-        <v>3</v>
-      </c>
-      <c r="M112">
-        <v>0</v>
-      </c>
-      <c r="N112">
-        <v>3</v>
-      </c>
-      <c r="O112" t="s">
-        <v>158</v>
-      </c>
-      <c r="P112" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q112">
-        <v>2.6</v>
-      </c>
-      <c r="R112">
-        <v>2.2</v>
-      </c>
-      <c r="S112">
-        <v>4.33</v>
-      </c>
-      <c r="T112">
-        <v>1.36</v>
-      </c>
-      <c r="U112">
-        <v>3</v>
-      </c>
-      <c r="V112">
-        <v>2.75</v>
-      </c>
-      <c r="W112">
-        <v>1.4</v>
-      </c>
-      <c r="X112">
-        <v>7</v>
-      </c>
-      <c r="Y112">
-        <v>1.1</v>
-      </c>
-      <c r="Z112">
-        <v>1.94</v>
-      </c>
-      <c r="AA112">
-        <v>3.28</v>
-      </c>
-      <c r="AB112">
-        <v>3.33</v>
-      </c>
-      <c r="AC112">
-        <v>1.05</v>
-      </c>
-      <c r="AD112">
-        <v>8.5</v>
-      </c>
-      <c r="AE112">
-        <v>1.3</v>
-      </c>
-      <c r="AF112">
-        <v>3.3</v>
-      </c>
-      <c r="AG112">
-        <v>1.94</v>
-      </c>
-      <c r="AH112">
-        <v>1.76</v>
-      </c>
-      <c r="AI112">
-        <v>1.8</v>
-      </c>
-      <c r="AJ112">
-        <v>1.91</v>
-      </c>
-      <c r="AK112">
-        <v>1.27</v>
-      </c>
-      <c r="AL112">
-        <v>1.3</v>
-      </c>
-      <c r="AM112">
-        <v>1.77</v>
-      </c>
-      <c r="AN112">
-        <v>1</v>
-      </c>
-      <c r="AO112">
-        <v>1</v>
-      </c>
-      <c r="AP112">
-        <v>1.2</v>
-      </c>
-      <c r="AQ112">
-        <v>0.78</v>
-      </c>
-      <c r="AR112">
-        <v>1.55</v>
-      </c>
-      <c r="AS112">
-        <v>1.16</v>
-      </c>
-      <c r="AT112">
-        <v>2.71</v>
-      </c>
-      <c r="AU112">
-        <v>10</v>
-      </c>
-      <c r="AV112">
-        <v>2</v>
-      </c>
-      <c r="AW112">
-        <v>6</v>
-      </c>
-      <c r="AX112">
-        <v>3</v>
-      </c>
-      <c r="AY112">
-        <v>16</v>
-      </c>
-      <c r="AZ112">
-        <v>5</v>
-      </c>
-      <c r="BA112">
-        <v>9</v>
-      </c>
-      <c r="BB112">
-        <v>2</v>
-      </c>
-      <c r="BC112">
-        <v>11</v>
-      </c>
-      <c r="BD112">
-        <v>1.69</v>
-      </c>
-      <c r="BE112">
-        <v>6.15</v>
-      </c>
-      <c r="BF112">
-        <v>2.75</v>
-      </c>
-      <c r="BG112">
-        <v>1.44</v>
-      </c>
-      <c r="BH112">
-        <v>2.43</v>
-      </c>
-      <c r="BI112">
-        <v>1.82</v>
-      </c>
-      <c r="BJ112">
-        <v>1.84</v>
-      </c>
-      <c r="BK112">
-        <v>2.35</v>
-      </c>
-      <c r="BL112">
-        <v>1.47</v>
-      </c>
-      <c r="BM112">
-        <v>3.28</v>
-      </c>
-      <c r="BN112">
-        <v>1.25</v>
-      </c>
-      <c r="BO112">
-        <v>4.05</v>
-      </c>
-      <c r="BP112">
-        <v>1.18</v>
-      </c>
-    </row>
-    <row r="113" spans="1:68">
-      <c r="A113" s="1">
-        <v>112</v>
-      </c>
-      <c r="B113">
-        <v>7813932</v>
-      </c>
-      <c r="C113" t="s">
-        <v>68</v>
-      </c>
-      <c r="D113" t="s">
-        <v>69</v>
-      </c>
-      <c r="E113" s="2">
-        <v>45823.29166666666</v>
-      </c>
-      <c r="F113">
-        <v>16</v>
-      </c>
-      <c r="G113" t="s">
-        <v>79</v>
-      </c>
-      <c r="H113" t="s">
-        <v>70</v>
-      </c>
-      <c r="I113">
-        <v>0</v>
-      </c>
-      <c r="J113">
-        <v>1</v>
-      </c>
-      <c r="K113">
-        <v>1</v>
-      </c>
-      <c r="L113">
-        <v>1</v>
-      </c>
-      <c r="M113">
-        <v>2</v>
-      </c>
-      <c r="N113">
-        <v>3</v>
-      </c>
-      <c r="O113" t="s">
-        <v>159</v>
-      </c>
-      <c r="P113" t="s">
-        <v>232</v>
-      </c>
-      <c r="Q113">
-        <v>3.4</v>
-      </c>
-      <c r="R113">
-        <v>2.1</v>
-      </c>
-      <c r="S113">
-        <v>3.2</v>
-      </c>
-      <c r="T113">
-        <v>1.4</v>
-      </c>
-      <c r="U113">
-        <v>2.75</v>
-      </c>
-      <c r="V113">
-        <v>3</v>
-      </c>
-      <c r="W113">
-        <v>1.36</v>
-      </c>
-      <c r="X113">
-        <v>8</v>
-      </c>
-      <c r="Y113">
-        <v>1.08</v>
-      </c>
-      <c r="Z113">
-        <v>2.58</v>
-      </c>
-      <c r="AA113">
-        <v>3.23</v>
-      </c>
-      <c r="AB113">
-        <v>2.36</v>
-      </c>
-      <c r="AC113">
-        <v>1.06</v>
-      </c>
-      <c r="AD113">
-        <v>8</v>
-      </c>
-      <c r="AE113">
-        <v>1.3</v>
-      </c>
-      <c r="AF113">
-        <v>3.25</v>
-      </c>
-      <c r="AG113">
-        <v>1.87</v>
-      </c>
-      <c r="AH113">
-        <v>1.83</v>
-      </c>
-      <c r="AI113">
-        <v>1.8</v>
-      </c>
-      <c r="AJ113">
-        <v>1.91</v>
-      </c>
-      <c r="AK113">
-        <v>1.49</v>
-      </c>
-      <c r="AL113">
-        <v>1.31</v>
-      </c>
-      <c r="AM113">
-        <v>1.46</v>
-      </c>
-      <c r="AN113">
-        <v>2.5</v>
-      </c>
-      <c r="AO113">
-        <v>2.17</v>
-      </c>
-      <c r="AP113">
-        <v>2.1</v>
-      </c>
-      <c r="AQ113">
-        <v>1.89</v>
-      </c>
-      <c r="AR113">
-        <v>1.85</v>
-      </c>
-      <c r="AS113">
-        <v>1.29</v>
-      </c>
-      <c r="AT113">
-        <v>3.14</v>
-      </c>
-      <c r="AU113">
-        <v>6</v>
-      </c>
-      <c r="AV113">
-        <v>3</v>
-      </c>
-      <c r="AW113">
-        <v>5</v>
-      </c>
-      <c r="AX113">
-        <v>2</v>
-      </c>
-      <c r="AY113">
-        <v>11</v>
-      </c>
-      <c r="AZ113">
-        <v>5</v>
-      </c>
-      <c r="BA113">
-        <v>4</v>
-      </c>
-      <c r="BB113">
-        <v>2</v>
-      </c>
-      <c r="BC113">
-        <v>6</v>
-      </c>
-      <c r="BD113">
-        <v>1.94</v>
-      </c>
-      <c r="BE113">
-        <v>6.05</v>
-      </c>
-      <c r="BF113">
-        <v>2.29</v>
-      </c>
-      <c r="BG113">
-        <v>1.4</v>
-      </c>
-      <c r="BH113">
-        <v>2.56</v>
-      </c>
-      <c r="BI113">
-        <v>1.75</v>
-      </c>
-      <c r="BJ113">
-        <v>1.92</v>
-      </c>
-      <c r="BK113">
-        <v>2.24</v>
-      </c>
-      <c r="BL113">
-        <v>1.52</v>
-      </c>
-      <c r="BM113">
-        <v>3.05</v>
-      </c>
-      <c r="BN113">
-        <v>1.28</v>
-      </c>
-      <c r="BO113">
-        <v>3.95</v>
-      </c>
-      <c r="BP113">
-        <v>1.19</v>
-      </c>
-    </row>
-    <row r="114" spans="1:68">
-      <c r="A114" s="1">
-        <v>113</v>
-      </c>
-      <c r="B114">
-        <v>7813933</v>
-      </c>
-      <c r="C114" t="s">
-        <v>68</v>
-      </c>
-      <c r="D114" t="s">
-        <v>69</v>
-      </c>
-      <c r="E114" s="2">
-        <v>45829.29166666666</v>
-      </c>
-      <c r="F114">
-        <v>17</v>
-      </c>
-      <c r="G114" t="s">
-        <v>70</v>
-      </c>
-      <c r="H114" t="s">
-        <v>77</v>
-      </c>
-      <c r="I114">
-        <v>1</v>
-      </c>
-      <c r="J114">
-        <v>0</v>
-      </c>
-      <c r="K114">
-        <v>1</v>
-      </c>
-      <c r="L114">
-        <v>2</v>
-      </c>
-      <c r="M114">
-        <v>0</v>
-      </c>
-      <c r="N114">
-        <v>2</v>
-      </c>
-      <c r="O114" t="s">
-        <v>160</v>
-      </c>
-      <c r="P114" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q114">
-        <v>1.79</v>
-      </c>
-      <c r="R114">
-        <v>2.62</v>
-      </c>
-      <c r="S114">
-        <v>7.92</v>
-      </c>
-      <c r="T114">
-        <v>1.32</v>
-      </c>
-      <c r="U114">
-        <v>3.31</v>
-      </c>
-      <c r="V114">
-        <v>2.55</v>
-      </c>
-      <c r="W114">
-        <v>1.5</v>
-      </c>
-      <c r="X114">
-        <v>5.95</v>
-      </c>
-      <c r="Y114">
-        <v>1.07</v>
-      </c>
-      <c r="Z114">
-        <v>1.38</v>
-      </c>
-      <c r="AA114">
-        <v>4.3</v>
-      </c>
-      <c r="AB114">
-        <v>6.2</v>
-      </c>
-      <c r="AC114">
-        <v>1.02</v>
-      </c>
-      <c r="AD114">
-        <v>10</v>
-      </c>
-      <c r="AE114">
-        <v>1.22</v>
-      </c>
-      <c r="AF114">
-        <v>3.8</v>
-      </c>
-      <c r="AG114">
-        <v>1.78</v>
-      </c>
-      <c r="AH114">
-        <v>1.92</v>
-      </c>
-      <c r="AI114">
-        <v>1.95</v>
-      </c>
-      <c r="AJ114">
-        <v>1.81</v>
-      </c>
-      <c r="AK114">
-        <v>1.04</v>
-      </c>
-      <c r="AL114">
-        <v>1.14</v>
-      </c>
-      <c r="AM114">
-        <v>3.02</v>
-      </c>
-      <c r="AN114">
-        <v>2.78</v>
-      </c>
-      <c r="AO114">
-        <v>0.5</v>
-      </c>
-      <c r="AP114">
-        <v>2.8</v>
-      </c>
-      <c r="AQ114">
-        <v>0.44</v>
-      </c>
-      <c r="AR114">
-        <v>1.71</v>
-      </c>
-      <c r="AS114">
-        <v>1.07</v>
-      </c>
-      <c r="AT114">
-        <v>2.78</v>
-      </c>
-      <c r="AU114">
-        <v>5</v>
-      </c>
-      <c r="AV114">
-        <v>0</v>
-      </c>
-      <c r="AW114">
-        <v>5</v>
-      </c>
-      <c r="AX114">
-        <v>8</v>
-      </c>
-      <c r="AY114">
-        <v>10</v>
-      </c>
-      <c r="AZ114">
-        <v>8</v>
-      </c>
-      <c r="BA114">
-        <v>2</v>
-      </c>
-      <c r="BB114">
-        <v>1</v>
-      </c>
-      <c r="BC114">
-        <v>3</v>
-      </c>
-      <c r="BD114">
-        <v>1.35</v>
-      </c>
-      <c r="BE114">
-        <v>8.6</v>
-      </c>
-      <c r="BF114">
-        <v>3.84</v>
-      </c>
-      <c r="BG114">
-        <v>1.48</v>
-      </c>
-      <c r="BH114">
-        <v>2.58</v>
-      </c>
-      <c r="BI114">
-        <v>1.84</v>
-      </c>
-      <c r="BJ114">
-        <v>1.95</v>
-      </c>
-      <c r="BK114">
-        <v>2.36</v>
-      </c>
-      <c r="BL114">
-        <v>1.56</v>
-      </c>
-      <c r="BM114">
-        <v>3.2</v>
-      </c>
-      <c r="BN114">
-        <v>1.3</v>
-      </c>
-      <c r="BO114">
-        <v>4.1</v>
-      </c>
-      <c r="BP114">
-        <v>1.18</v>
-      </c>
-    </row>
-    <row r="115" spans="1:68">
-      <c r="A115" s="1">
-        <v>114</v>
-      </c>
-      <c r="B115">
-        <v>7813934</v>
-      </c>
-      <c r="C115" t="s">
-        <v>68</v>
-      </c>
-      <c r="D115" t="s">
-        <v>69</v>
-      </c>
-      <c r="E115" s="2">
-        <v>45829.29166666666</v>
-      </c>
-      <c r="F115">
-        <v>17</v>
-      </c>
-      <c r="G115" t="s">
-        <v>71</v>
-      </c>
-      <c r="H115" t="s">
-        <v>75</v>
-      </c>
-      <c r="I115">
-        <v>1</v>
-      </c>
-      <c r="J115">
-        <v>1</v>
-      </c>
-      <c r="K115">
-        <v>2</v>
-      </c>
-      <c r="L115">
-        <v>4</v>
-      </c>
-      <c r="M115">
-        <v>2</v>
-      </c>
-      <c r="N115">
-        <v>6</v>
-      </c>
-      <c r="O115" t="s">
-        <v>161</v>
-      </c>
-      <c r="P115" t="s">
-        <v>233</v>
-      </c>
-      <c r="Q115">
-        <v>4.85</v>
-      </c>
-      <c r="R115">
-        <v>2.2</v>
-      </c>
-      <c r="S115">
-        <v>2.19</v>
-      </c>
-      <c r="T115">
-        <v>1.33</v>
-      </c>
-      <c r="U115">
-        <v>3.04</v>
-      </c>
-      <c r="V115">
-        <v>2.65</v>
-      </c>
-      <c r="W115">
-        <v>1.42</v>
-      </c>
-      <c r="X115">
-        <v>6.5</v>
-      </c>
-      <c r="Y115">
-        <v>1.05</v>
-      </c>
-      <c r="Z115">
-        <v>4.33</v>
-      </c>
-      <c r="AA115">
-        <v>3.72</v>
-      </c>
-      <c r="AB115">
-        <v>1.61</v>
-      </c>
-      <c r="AC115">
-        <v>1.01</v>
-      </c>
-      <c r="AD115">
-        <v>11</v>
-      </c>
-      <c r="AE115">
-        <v>1.21</v>
-      </c>
-      <c r="AF115">
-        <v>3.58</v>
-      </c>
-      <c r="AG115">
-        <v>1.77</v>
-      </c>
-      <c r="AH115">
-        <v>1.93</v>
-      </c>
-      <c r="AI115">
-        <v>1.74</v>
-      </c>
-      <c r="AJ115">
-        <v>1.93</v>
-      </c>
-      <c r="AK115">
-        <v>2.09</v>
-      </c>
-      <c r="AL115">
-        <v>1.22</v>
-      </c>
-      <c r="AM115">
-        <v>1.15</v>
-      </c>
-      <c r="AN115">
-        <v>0.63</v>
-      </c>
-      <c r="AO115">
-        <v>1.57</v>
-      </c>
-      <c r="AP115">
-        <v>0.89</v>
-      </c>
-      <c r="AQ115">
-        <v>1.2</v>
-      </c>
-      <c r="AR115">
-        <v>1.19</v>
-      </c>
-      <c r="AS115">
-        <v>1.24</v>
-      </c>
-      <c r="AT115">
-        <v>2.43</v>
-      </c>
-      <c r="AU115">
-        <v>7</v>
-      </c>
-      <c r="AV115">
-        <v>7</v>
-      </c>
-      <c r="AW115">
-        <v>5</v>
-      </c>
-      <c r="AX115">
-        <v>10</v>
-      </c>
-      <c r="AY115">
-        <v>12</v>
-      </c>
-      <c r="AZ115">
-        <v>17</v>
-      </c>
-      <c r="BA115">
-        <v>3</v>
-      </c>
-      <c r="BB115">
-        <v>5</v>
-      </c>
-      <c r="BC115">
-        <v>8</v>
-      </c>
-      <c r="BD115">
-        <v>2.73</v>
-      </c>
-      <c r="BE115">
-        <v>6.25</v>
-      </c>
-      <c r="BF115">
-        <v>1.69</v>
-      </c>
-      <c r="BG115">
-        <v>1.37</v>
-      </c>
-      <c r="BH115">
-        <v>2.85</v>
-      </c>
-      <c r="BI115">
-        <v>1.72</v>
-      </c>
-      <c r="BJ115">
-        <v>2.09</v>
-      </c>
-      <c r="BK115">
-        <v>2.17</v>
-      </c>
-      <c r="BL115">
-        <v>1.68</v>
-      </c>
-      <c r="BM115">
-        <v>3</v>
-      </c>
-      <c r="BN115">
-        <v>1.34</v>
-      </c>
-      <c r="BO115">
-        <v>3.68</v>
-      </c>
-      <c r="BP115">
-        <v>1.22</v>
-      </c>
-    </row>
-    <row r="116" spans="1:68">
-      <c r="A116" s="1">
-        <v>115</v>
-      </c>
-      <c r="B116">
-        <v>7813935</v>
-      </c>
-      <c r="C116" t="s">
-        <v>68</v>
-      </c>
-      <c r="D116" t="s">
-        <v>69</v>
-      </c>
-      <c r="E116" s="2">
-        <v>45829.29166666666</v>
-      </c>
-      <c r="F116">
-        <v>17</v>
-      </c>
-      <c r="G116" t="s">
-        <v>73</v>
-      </c>
-      <c r="H116" t="s">
-        <v>76</v>
-      </c>
-      <c r="I116">
-        <v>0</v>
-      </c>
-      <c r="J116">
-        <v>0</v>
-      </c>
-      <c r="K116">
-        <v>0</v>
-      </c>
-      <c r="L116">
-        <v>0</v>
-      </c>
-      <c r="M116">
-        <v>1</v>
-      </c>
-      <c r="N116">
-        <v>1</v>
-      </c>
-      <c r="O116" t="s">
-        <v>85</v>
-      </c>
-      <c r="P116" t="s">
-        <v>91</v>
-      </c>
-      <c r="Q116">
-        <v>4.56</v>
-      </c>
-      <c r="R116">
-        <v>2.18</v>
-      </c>
-      <c r="S116">
-        <v>2.6</v>
-      </c>
-      <c r="T116">
-        <v>1.42</v>
-      </c>
-      <c r="U116">
-        <v>2.83</v>
-      </c>
-      <c r="V116">
-        <v>3.1</v>
-      </c>
-      <c r="W116">
-        <v>1.36</v>
-      </c>
-      <c r="X116">
-        <v>7.4</v>
-      </c>
-      <c r="Y116">
-        <v>1.03</v>
-      </c>
-      <c r="Z116">
-        <v>3.58</v>
-      </c>
-      <c r="AA116">
-        <v>3.29</v>
-      </c>
-      <c r="AB116">
-        <v>1.86</v>
-      </c>
-      <c r="AC116">
-        <v>1.04</v>
-      </c>
-      <c r="AD116">
-        <v>8.5</v>
-      </c>
-      <c r="AE116">
-        <v>1.33</v>
-      </c>
-      <c r="AF116">
-        <v>3</v>
-      </c>
-      <c r="AG116">
-        <v>1.95</v>
-      </c>
-      <c r="AH116">
-        <v>1.75</v>
-      </c>
-      <c r="AI116">
-        <v>1.83</v>
-      </c>
-      <c r="AJ116">
-        <v>1.93</v>
-      </c>
-      <c r="AK116">
-        <v>1.78</v>
-      </c>
-      <c r="AL116">
-        <v>1.26</v>
-      </c>
-      <c r="AM116">
-        <v>1.22</v>
-      </c>
-      <c r="AN116">
-        <v>0.88</v>
-      </c>
-      <c r="AO116">
-        <v>1.38</v>
-      </c>
-      <c r="AP116">
-        <v>0.8</v>
-      </c>
-      <c r="AQ116">
-        <v>1.56</v>
-      </c>
-      <c r="AR116">
-        <v>1.3</v>
-      </c>
-      <c r="AS116">
-        <v>1.47</v>
-      </c>
-      <c r="AT116">
-        <v>2.77</v>
-      </c>
-      <c r="AU116">
-        <v>2</v>
-      </c>
-      <c r="AV116">
-        <v>2</v>
-      </c>
-      <c r="AW116">
-        <v>1</v>
-      </c>
-      <c r="AX116">
-        <v>5</v>
-      </c>
-      <c r="AY116">
-        <v>3</v>
-      </c>
-      <c r="AZ116">
-        <v>7</v>
-      </c>
-      <c r="BA116">
-        <v>3</v>
-      </c>
-      <c r="BB116">
-        <v>5</v>
-      </c>
-      <c r="BC116">
-        <v>8</v>
-      </c>
-      <c r="BD116">
-        <v>2.79</v>
-      </c>
-      <c r="BE116">
-        <v>6.1</v>
-      </c>
-      <c r="BF116">
-        <v>1.68</v>
-      </c>
-      <c r="BG116">
-        <v>1.58</v>
-      </c>
-      <c r="BH116">
-        <v>2.33</v>
-      </c>
-      <c r="BI116">
-        <v>1.98</v>
-      </c>
-      <c r="BJ116">
-        <v>1.82</v>
-      </c>
-      <c r="BK116">
-        <v>2.55</v>
-      </c>
-      <c r="BL116">
-        <v>1.5</v>
-      </c>
-      <c r="BM116">
-        <v>3.58</v>
-      </c>
-      <c r="BN116">
-        <v>1.21</v>
-      </c>
-      <c r="BO116">
-        <v>4.4</v>
-      </c>
-      <c r="BP116">
-        <v>1.15</v>
-      </c>
-    </row>
-    <row r="117" spans="1:68">
-      <c r="A117" s="1">
-        <v>116</v>
-      </c>
-      <c r="B117">
-        <v>7813936</v>
-      </c>
-      <c r="C117" t="s">
-        <v>68</v>
-      </c>
-      <c r="D117" t="s">
-        <v>69</v>
-      </c>
-      <c r="E117" s="2">
-        <v>45829.29166666666</v>
-      </c>
-      <c r="F117">
-        <v>17</v>
-      </c>
-      <c r="G117" t="s">
-        <v>74</v>
-      </c>
-      <c r="H117" t="s">
-        <v>81</v>
-      </c>
-      <c r="I117">
-        <v>0</v>
-      </c>
-      <c r="J117">
-        <v>1</v>
-      </c>
-      <c r="K117">
-        <v>1</v>
-      </c>
-      <c r="L117">
-        <v>0</v>
-      </c>
-      <c r="M117">
-        <v>2</v>
-      </c>
-      <c r="N117">
-        <v>2</v>
-      </c>
-      <c r="O117" t="s">
-        <v>85</v>
-      </c>
-      <c r="P117" t="s">
-        <v>234</v>
-      </c>
-      <c r="Q117">
-        <v>3.64</v>
-      </c>
-      <c r="R117">
-        <v>2.01</v>
-      </c>
-      <c r="S117">
-        <v>2.9</v>
-      </c>
-      <c r="T117">
-        <v>1.4</v>
-      </c>
-      <c r="U117">
-        <v>2.72</v>
-      </c>
-      <c r="V117">
-        <v>2.98</v>
-      </c>
-      <c r="W117">
-        <v>1.34</v>
-      </c>
-      <c r="X117">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Y117">
-        <v>1.02</v>
-      </c>
-      <c r="Z117">
-        <v>3.06</v>
-      </c>
-      <c r="AA117">
-        <v>3.11</v>
-      </c>
-      <c r="AB117">
-        <v>2.12</v>
-      </c>
-      <c r="AC117">
-        <v>1</v>
-      </c>
-      <c r="AD117">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AE117">
-        <v>1.27</v>
-      </c>
-      <c r="AF117">
-        <v>3.14</v>
-      </c>
-      <c r="AG117">
-        <v>1.95</v>
-      </c>
-      <c r="AH117">
-        <v>1.7</v>
-      </c>
-      <c r="AI117">
-        <v>1.76</v>
-      </c>
-      <c r="AJ117">
-        <v>1.91</v>
-      </c>
-      <c r="AK117">
-        <v>1.56</v>
-      </c>
-      <c r="AL117">
-        <v>1.28</v>
-      </c>
-      <c r="AM117">
-        <v>1.33</v>
-      </c>
-      <c r="AN117">
-        <v>1.5</v>
-      </c>
-      <c r="AO117">
-        <v>1.13</v>
-      </c>
-      <c r="AP117">
-        <v>1.33</v>
-      </c>
-      <c r="AQ117">
-        <v>1.33</v>
-      </c>
-      <c r="AR117">
-        <v>1.09</v>
-      </c>
-      <c r="AS117">
-        <v>1.39</v>
-      </c>
-      <c r="AT117">
-        <v>2.48</v>
-      </c>
-      <c r="AU117">
-        <v>2</v>
-      </c>
-      <c r="AV117">
-        <v>7</v>
-      </c>
-      <c r="AW117">
-        <v>4</v>
-      </c>
-      <c r="AX117">
-        <v>2</v>
-      </c>
-      <c r="AY117">
-        <v>6</v>
-      </c>
-      <c r="AZ117">
-        <v>9</v>
-      </c>
-      <c r="BA117">
-        <v>7</v>
-      </c>
-      <c r="BB117">
-        <v>6</v>
-      </c>
-      <c r="BC117">
-        <v>13</v>
-      </c>
-      <c r="BD117">
-        <v>2.27</v>
-      </c>
-      <c r="BE117">
-        <v>6</v>
-      </c>
-      <c r="BF117">
-        <v>1.96</v>
-      </c>
-      <c r="BG117">
-        <v>1.49</v>
-      </c>
-      <c r="BH117">
-        <v>2.55</v>
-      </c>
-      <c r="BI117">
-        <v>1.84</v>
-      </c>
-      <c r="BJ117">
-        <v>1.95</v>
-      </c>
-      <c r="BK117">
-        <v>2.34</v>
-      </c>
-      <c r="BL117">
-        <v>1.58</v>
-      </c>
-      <c r="BM117">
-        <v>3.2</v>
-      </c>
-      <c r="BN117">
-        <v>1.3</v>
-      </c>
-      <c r="BO117">
-        <v>4.1</v>
-      </c>
-      <c r="BP117">
-        <v>1.18</v>
-      </c>
-    </row>
-    <row r="118" spans="1:68">
-      <c r="A118" s="1">
-        <v>117</v>
-      </c>
-      <c r="B118">
-        <v>7813938</v>
-      </c>
-      <c r="C118" t="s">
-        <v>68</v>
-      </c>
-      <c r="D118" t="s">
-        <v>69</v>
-      </c>
-      <c r="E118" s="2">
-        <v>45830.29166666666</v>
-      </c>
-      <c r="F118">
-        <v>17</v>
-      </c>
-      <c r="G118" t="s">
-        <v>72</v>
-      </c>
-      <c r="H118" t="s">
-        <v>82</v>
-      </c>
-      <c r="I118">
-        <v>1</v>
-      </c>
-      <c r="J118">
-        <v>0</v>
-      </c>
-      <c r="K118">
-        <v>1</v>
-      </c>
-      <c r="L118">
-        <v>2</v>
-      </c>
-      <c r="M118">
-        <v>2</v>
-      </c>
-      <c r="N118">
-        <v>4</v>
-      </c>
-      <c r="O118" t="s">
-        <v>162</v>
-      </c>
-      <c r="P118" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q118">
-        <v>2.15</v>
-      </c>
-      <c r="R118">
-        <v>2.2</v>
-      </c>
-      <c r="S118">
-        <v>5.5</v>
-      </c>
-      <c r="T118">
-        <v>1.4</v>
-      </c>
-      <c r="U118">
-        <v>2.88</v>
-      </c>
-      <c r="V118">
-        <v>2.88</v>
-      </c>
-      <c r="W118">
-        <v>1.4</v>
-      </c>
-      <c r="X118">
-        <v>8</v>
-      </c>
-      <c r="Y118">
-        <v>1.08</v>
-      </c>
-      <c r="Z118">
-        <v>1.57</v>
-      </c>
-      <c r="AA118">
-        <v>3.65</v>
-      </c>
-      <c r="AB118">
-        <v>4.8</v>
-      </c>
-      <c r="AC118">
-        <v>1.01</v>
-      </c>
-      <c r="AD118">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="AE118">
-        <v>1.28</v>
-      </c>
-      <c r="AF118">
-        <v>3.08</v>
-      </c>
-      <c r="AG118">
-        <v>1.95</v>
-      </c>
-      <c r="AH118">
-        <v>1.75</v>
-      </c>
-      <c r="AI118">
-        <v>1.95</v>
-      </c>
-      <c r="AJ118">
-        <v>1.8</v>
-      </c>
-      <c r="AK118">
-        <v>1.18</v>
-      </c>
-      <c r="AL118">
-        <v>1.3</v>
-      </c>
-      <c r="AM118">
-        <v>2.1</v>
-      </c>
-      <c r="AN118">
-        <v>1.22</v>
-      </c>
-      <c r="AO118">
-        <v>1</v>
-      </c>
-      <c r="AP118">
-        <v>1.2</v>
-      </c>
-      <c r="AQ118">
-        <v>1</v>
-      </c>
-      <c r="AR118">
-        <v>1.65</v>
-      </c>
-      <c r="AS118">
-        <v>1.25</v>
-      </c>
-      <c r="AT118">
-        <v>2.9</v>
-      </c>
-      <c r="AU118">
-        <v>7</v>
-      </c>
-      <c r="AV118">
-        <v>5</v>
-      </c>
-      <c r="AW118">
-        <v>3</v>
-      </c>
-      <c r="AX118">
-        <v>2</v>
-      </c>
-      <c r="AY118">
-        <v>10</v>
-      </c>
-      <c r="AZ118">
-        <v>7</v>
-      </c>
-      <c r="BA118">
-        <v>6</v>
-      </c>
-      <c r="BB118">
-        <v>3</v>
-      </c>
-      <c r="BC118">
-        <v>9</v>
-      </c>
-      <c r="BD118">
-        <v>1.44</v>
-      </c>
-      <c r="BE118">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF118">
-        <v>3.32</v>
-      </c>
-      <c r="BG118">
-        <v>1.53</v>
-      </c>
-      <c r="BH118">
-        <v>2.45</v>
-      </c>
-      <c r="BI118">
-        <v>1.92</v>
-      </c>
-      <c r="BJ118">
-        <v>1.88</v>
-      </c>
-      <c r="BK118">
-        <v>2.48</v>
-      </c>
-      <c r="BL118">
-        <v>1.52</v>
-      </c>
-      <c r="BM118">
-        <v>3.28</v>
-      </c>
-      <c r="BN118">
-        <v>1.25</v>
-      </c>
-      <c r="BO118">
-        <v>4.3</v>
-      </c>
-      <c r="BP118">
-        <v>1.16</v>
-      </c>
-    </row>
-    <row r="119" spans="1:68">
-      <c r="A119" s="1">
-        <v>118</v>
-      </c>
-      <c r="B119">
-        <v>7813939</v>
-      </c>
-      <c r="C119" t="s">
-        <v>68</v>
-      </c>
-      <c r="D119" t="s">
-        <v>69</v>
-      </c>
-      <c r="E119" s="2">
-        <v>45830.29166666666</v>
-      </c>
-      <c r="F119">
-        <v>17</v>
-      </c>
-      <c r="G119" t="s">
-        <v>80</v>
-      </c>
-      <c r="H119" t="s">
-        <v>79</v>
-      </c>
-      <c r="I119">
-        <v>0</v>
-      </c>
-      <c r="J119">
-        <v>1</v>
-      </c>
-      <c r="K119">
-        <v>1</v>
-      </c>
-      <c r="L119">
-        <v>1</v>
-      </c>
-      <c r="M119">
-        <v>3</v>
-      </c>
-      <c r="N119">
-        <v>4</v>
-      </c>
-      <c r="O119" t="s">
-        <v>92</v>
-      </c>
-      <c r="P119" t="s">
-        <v>235</v>
-      </c>
-      <c r="Q119">
-        <v>4.4</v>
-      </c>
-      <c r="R119">
-        <v>2.4</v>
-      </c>
-      <c r="S119">
-        <v>2.2</v>
-      </c>
-      <c r="T119">
-        <v>1.29</v>
-      </c>
-      <c r="U119">
-        <v>3.5</v>
-      </c>
-      <c r="V119">
-        <v>2.3</v>
-      </c>
-      <c r="W119">
-        <v>1.55</v>
-      </c>
-      <c r="X119">
-        <v>5.5</v>
-      </c>
-      <c r="Y119">
-        <v>1.14</v>
-      </c>
-      <c r="Z119">
-        <v>3.98</v>
-      </c>
-      <c r="AA119">
-        <v>3.93</v>
-      </c>
-      <c r="AB119">
-        <v>1.63</v>
-      </c>
-      <c r="AC119">
-        <v>1.01</v>
-      </c>
-      <c r="AD119">
-        <v>13</v>
-      </c>
-      <c r="AE119">
-        <v>1.14</v>
-      </c>
-      <c r="AF119">
-        <v>4.4</v>
-      </c>
-      <c r="AG119">
-        <v>1.57</v>
-      </c>
-      <c r="AH119">
-        <v>2.15</v>
-      </c>
-      <c r="AI119">
-        <v>1.62</v>
-      </c>
-      <c r="AJ119">
-        <v>2.25</v>
-      </c>
-      <c r="AK119">
-        <v>2.3</v>
-      </c>
-      <c r="AL119">
-        <v>1.22</v>
-      </c>
-      <c r="AM119">
-        <v>1.17</v>
-      </c>
-      <c r="AN119">
-        <v>1.25</v>
-      </c>
-      <c r="AO119">
-        <v>1.57</v>
-      </c>
-      <c r="AP119">
-        <v>1.1</v>
-      </c>
-      <c r="AQ119">
-        <v>1.89</v>
-      </c>
-      <c r="AR119">
-        <v>1.71</v>
-      </c>
-      <c r="AS119">
-        <v>1.7</v>
-      </c>
-      <c r="AT119">
-        <v>3.41</v>
-      </c>
-      <c r="AU119">
-        <v>5</v>
-      </c>
-      <c r="AV119">
-        <v>8</v>
-      </c>
-      <c r="AW119">
-        <v>6</v>
-      </c>
-      <c r="AX119">
-        <v>6</v>
-      </c>
-      <c r="AY119">
-        <v>11</v>
-      </c>
-      <c r="AZ119">
-        <v>14</v>
-      </c>
-      <c r="BA119">
-        <v>7</v>
-      </c>
-      <c r="BB119">
-        <v>5</v>
-      </c>
-      <c r="BC119">
-        <v>12</v>
-      </c>
-      <c r="BD119">
-        <v>2.76</v>
-      </c>
-      <c r="BE119">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF119">
-        <v>1.58</v>
-      </c>
-      <c r="BG119">
-        <v>1.32</v>
-      </c>
-      <c r="BH119">
-        <v>2.88</v>
-      </c>
-      <c r="BI119">
-        <v>1.6</v>
-      </c>
-      <c r="BJ119">
-        <v>2.26</v>
-      </c>
-      <c r="BK119">
-        <v>1.99</v>
-      </c>
-      <c r="BL119">
-        <v>1.81</v>
-      </c>
-      <c r="BM119">
-        <v>2.53</v>
-      </c>
-      <c r="BN119">
-        <v>1.49</v>
-      </c>
-      <c r="BO119">
-        <v>3.78</v>
-      </c>
-      <c r="BP119">
-        <v>1.19</v>
-      </c>
-    </row>
-    <row r="120" spans="1:68">
-      <c r="A120" s="1">
-        <v>119</v>
-      </c>
-      <c r="B120">
-        <v>7813937</v>
-      </c>
-      <c r="C120" t="s">
-        <v>68</v>
-      </c>
-      <c r="D120" t="s">
-        <v>69</v>
-      </c>
-      <c r="E120" s="2">
-        <v>45830.29166666666</v>
-      </c>
-      <c r="F120">
-        <v>17</v>
-      </c>
-      <c r="G120" t="s">
-        <v>83</v>
-      </c>
-      <c r="H120" t="s">
-        <v>78</v>
-      </c>
-      <c r="I120">
-        <v>0</v>
-      </c>
-      <c r="J120">
-        <v>0</v>
-      </c>
-      <c r="K120">
-        <v>0</v>
-      </c>
-      <c r="L120">
-        <v>0</v>
-      </c>
-      <c r="M120">
-        <v>0</v>
-      </c>
-      <c r="N120">
-        <v>0</v>
-      </c>
-      <c r="O120" t="s">
-        <v>85</v>
-      </c>
-      <c r="P120" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q120">
-        <v>2.9</v>
-      </c>
-      <c r="R120">
-        <v>2.1</v>
-      </c>
-      <c r="S120">
-        <v>3.6</v>
-      </c>
-      <c r="T120">
-        <v>1.4</v>
-      </c>
-      <c r="U120">
-        <v>2.8</v>
-      </c>
-      <c r="V120">
-        <v>3</v>
-      </c>
-      <c r="W120">
-        <v>1.36</v>
-      </c>
-      <c r="X120">
-        <v>8.5</v>
-      </c>
-      <c r="Y120">
-        <v>1.07</v>
-      </c>
-      <c r="Z120">
-        <v>2.22</v>
-      </c>
-      <c r="AA120">
-        <v>3.1</v>
-      </c>
-      <c r="AB120">
-        <v>2.88</v>
-      </c>
-      <c r="AC120">
-        <v>1.05</v>
-      </c>
-      <c r="AD120">
-        <v>8</v>
-      </c>
-      <c r="AE120">
-        <v>1.3</v>
-      </c>
-      <c r="AF120">
-        <v>2.97</v>
-      </c>
-      <c r="AG120">
-        <v>2</v>
-      </c>
-      <c r="AH120">
-        <v>1.65</v>
-      </c>
-      <c r="AI120">
-        <v>1.83</v>
-      </c>
-      <c r="AJ120">
-        <v>1.91</v>
-      </c>
-      <c r="AK120">
-        <v>1.36</v>
-      </c>
-      <c r="AL120">
-        <v>1.35</v>
-      </c>
-      <c r="AM120">
-        <v>1.57</v>
-      </c>
-      <c r="AN120">
-        <v>2</v>
-      </c>
-      <c r="AO120">
-        <v>1.14</v>
-      </c>
-      <c r="AP120">
-        <v>2</v>
-      </c>
-      <c r="AQ120">
-        <v>1.13</v>
-      </c>
-      <c r="AR120">
-        <v>1.62</v>
-      </c>
-      <c r="AS120">
-        <v>1.31</v>
-      </c>
-      <c r="AT120">
-        <v>2.93</v>
-      </c>
-      <c r="AU120">
-        <v>3</v>
-      </c>
-      <c r="AV120">
-        <v>0</v>
-      </c>
-      <c r="AW120">
-        <v>4</v>
-      </c>
-      <c r="AX120">
-        <v>2</v>
-      </c>
-      <c r="AY120">
-        <v>7</v>
-      </c>
-      <c r="AZ120">
-        <v>2</v>
-      </c>
-      <c r="BA120">
-        <v>1</v>
-      </c>
-      <c r="BB120">
-        <v>4</v>
-      </c>
-      <c r="BC120">
-        <v>5</v>
-      </c>
-      <c r="BD120">
-        <v>2.1</v>
-      </c>
-      <c r="BE120">
-        <v>5.95</v>
-      </c>
-      <c r="BF120">
-        <v>2.11</v>
-      </c>
-      <c r="BG120">
-        <v>1.48</v>
-      </c>
-      <c r="BH120">
-        <v>2.58</v>
-      </c>
-      <c r="BI120">
-        <v>1.82</v>
-      </c>
-      <c r="BJ120">
-        <v>1.98</v>
-      </c>
-      <c r="BK120">
-        <v>2.3</v>
-      </c>
-      <c r="BL120">
-        <v>1.58</v>
-      </c>
-      <c r="BM120">
-        <v>3.08</v>
-      </c>
-      <c r="BN120">
-        <v>1.28</v>
-      </c>
-      <c r="BO120">
-        <v>4.1</v>
-      </c>
-      <c r="BP120">
-        <v>1.18</v>
-      </c>
-    </row>
-    <row r="121" spans="1:68">
-      <c r="A121" s="1">
-        <v>120</v>
-      </c>
-      <c r="B121">
-        <v>7813940</v>
-      </c>
-      <c r="C121" t="s">
-        <v>68</v>
-      </c>
-      <c r="D121" t="s">
-        <v>69</v>
-      </c>
-      <c r="E121" s="2">
-        <v>45836.29166666666</v>
-      </c>
-      <c r="F121">
-        <v>18</v>
-      </c>
-      <c r="G121" t="s">
-        <v>81</v>
-      </c>
-      <c r="H121" t="s">
-        <v>75</v>
-      </c>
-      <c r="I121">
-        <v>1</v>
-      </c>
-      <c r="J121">
-        <v>0</v>
-      </c>
-      <c r="K121">
-        <v>1</v>
-      </c>
-      <c r="L121">
-        <v>1</v>
-      </c>
-      <c r="M121">
-        <v>1</v>
-      </c>
-      <c r="N121">
-        <v>2</v>
-      </c>
-      <c r="O121" t="s">
-        <v>163</v>
-      </c>
-      <c r="P121" t="s">
-        <v>236</v>
-      </c>
-      <c r="Q121">
-        <v>2.93</v>
-      </c>
-      <c r="R121">
-        <v>2.15</v>
-      </c>
-      <c r="S121">
-        <v>3.22</v>
-      </c>
-      <c r="T121">
-        <v>1.31</v>
-      </c>
-      <c r="U121">
-        <v>3.14</v>
-      </c>
-      <c r="V121">
-        <v>2.58</v>
-      </c>
-      <c r="W121">
-        <v>1.44</v>
-      </c>
-      <c r="X121">
-        <v>6.65</v>
-      </c>
-      <c r="Y121">
-        <v>1.05</v>
-      </c>
-      <c r="Z121">
-        <v>2.35</v>
-      </c>
-      <c r="AA121">
-        <v>3.2</v>
-      </c>
-      <c r="AB121">
-        <v>2.62</v>
-      </c>
-      <c r="AC121">
-        <v>1.01</v>
-      </c>
-      <c r="AD121">
-        <v>11</v>
-      </c>
-      <c r="AE121">
-        <v>1.18</v>
-      </c>
-      <c r="AF121">
-        <v>3.86</v>
-      </c>
-      <c r="AG121">
-        <v>1.81</v>
-      </c>
-      <c r="AH121">
-        <v>1.89</v>
-      </c>
-      <c r="AI121">
-        <v>1.59</v>
-      </c>
-      <c r="AJ121">
-        <v>2.15</v>
-      </c>
-      <c r="AK121">
-        <v>1.41</v>
-      </c>
-      <c r="AL121">
-        <v>1.26</v>
-      </c>
-      <c r="AM121">
-        <v>1.5</v>
-      </c>
-      <c r="AN121">
-        <v>1.5</v>
-      </c>
-      <c r="AO121">
-        <v>1.38</v>
-      </c>
-      <c r="AP121">
-        <v>1.3</v>
-      </c>
-      <c r="AQ121">
-        <v>1.2</v>
-      </c>
-      <c r="AR121">
-        <v>1.8</v>
-      </c>
-      <c r="AS121">
-        <v>1.35</v>
-      </c>
-      <c r="AT121">
-        <v>3.15</v>
-      </c>
-      <c r="AU121">
-        <v>5</v>
-      </c>
-      <c r="AV121">
-        <v>4</v>
-      </c>
-      <c r="AW121">
-        <v>4</v>
-      </c>
-      <c r="AX121">
-        <v>7</v>
-      </c>
-      <c r="AY121">
-        <v>9</v>
-      </c>
-      <c r="AZ121">
-        <v>11</v>
-      </c>
-      <c r="BA121">
-        <v>1</v>
-      </c>
-      <c r="BB121">
-        <v>0</v>
-      </c>
-      <c r="BC121">
-        <v>1</v>
-      </c>
-      <c r="BD121">
-        <v>1.92</v>
-      </c>
-      <c r="BE121">
-        <v>6</v>
-      </c>
-      <c r="BF121">
-        <v>2.32</v>
-      </c>
-      <c r="BG121">
-        <v>1.4</v>
-      </c>
-      <c r="BH121">
-        <v>2.56</v>
-      </c>
-      <c r="BI121">
-        <v>1.95</v>
-      </c>
-      <c r="BJ121">
-        <v>1.85</v>
-      </c>
-      <c r="BK121">
-        <v>2.26</v>
-      </c>
-      <c r="BL121">
-        <v>1.51</v>
-      </c>
-      <c r="BM121">
-        <v>3.08</v>
-      </c>
-      <c r="BN121">
-        <v>1.28</v>
-      </c>
-      <c r="BO121">
-        <v>3.95</v>
-      </c>
-      <c r="BP121">
-        <v>1.19</v>
-      </c>
-    </row>
-    <row r="122" spans="1:68">
-      <c r="A122" s="1">
-        <v>121</v>
-      </c>
-      <c r="B122">
-        <v>7813941</v>
-      </c>
-      <c r="C122" t="s">
-        <v>68</v>
-      </c>
-      <c r="D122" t="s">
-        <v>69</v>
-      </c>
-      <c r="E122" s="2">
-        <v>45836.29166666666</v>
-      </c>
-      <c r="F122">
-        <v>18</v>
-      </c>
-      <c r="G122" t="s">
-        <v>76</v>
-      </c>
-      <c r="H122" t="s">
-        <v>80</v>
-      </c>
-      <c r="I122">
-        <v>2</v>
-      </c>
-      <c r="J122">
-        <v>0</v>
-      </c>
-      <c r="K122">
-        <v>2</v>
-      </c>
-      <c r="L122">
-        <v>2</v>
-      </c>
-      <c r="M122">
-        <v>0</v>
-      </c>
-      <c r="N122">
-        <v>2</v>
-      </c>
-      <c r="O122" t="s">
-        <v>164</v>
-      </c>
-      <c r="P122" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q122">
-        <v>2.24</v>
-      </c>
-      <c r="R122">
-        <v>2.23</v>
-      </c>
-      <c r="S122">
-        <v>4.78</v>
-      </c>
-      <c r="T122">
-        <v>1.3</v>
-      </c>
-      <c r="U122">
-        <v>3.2</v>
-      </c>
-      <c r="V122">
-        <v>2.55</v>
-      </c>
-      <c r="W122">
-        <v>1.45</v>
-      </c>
-      <c r="X122">
-        <v>6.4</v>
-      </c>
-      <c r="Y122">
-        <v>1.05</v>
-      </c>
-      <c r="Z122">
-        <v>1.75</v>
-      </c>
-      <c r="AA122">
-        <v>3.59</v>
-      </c>
-      <c r="AB122">
-        <v>3.71</v>
-      </c>
-      <c r="AC122">
-        <v>1.02</v>
-      </c>
-      <c r="AD122">
-        <v>10</v>
-      </c>
-      <c r="AE122">
-        <v>1.22</v>
-      </c>
-      <c r="AF122">
-        <v>3.8</v>
-      </c>
-      <c r="AG122">
-        <v>1.73</v>
-      </c>
-      <c r="AH122">
-        <v>1.95</v>
-      </c>
-      <c r="AI122">
-        <v>1.67</v>
-      </c>
-      <c r="AJ122">
-        <v>2.15</v>
-      </c>
-      <c r="AK122">
-        <v>1.16</v>
-      </c>
-      <c r="AL122">
-        <v>1.21</v>
-      </c>
-      <c r="AM122">
-        <v>2.04</v>
-      </c>
-      <c r="AN122">
-        <v>1.75</v>
-      </c>
-      <c r="AO122">
-        <v>0.88</v>
-      </c>
-      <c r="AP122">
-        <v>1.89</v>
-      </c>
-      <c r="AQ122">
-        <v>0.78</v>
-      </c>
-      <c r="AR122">
-        <v>1.52</v>
-      </c>
-      <c r="AS122">
-        <v>1.1</v>
-      </c>
-      <c r="AT122">
-        <v>2.62</v>
-      </c>
-      <c r="AU122">
-        <v>9</v>
-      </c>
-      <c r="AV122">
-        <v>0</v>
-      </c>
-      <c r="AW122">
-        <v>15</v>
-      </c>
-      <c r="AX122">
-        <v>7</v>
-      </c>
-      <c r="AY122">
-        <v>24</v>
-      </c>
-      <c r="AZ122">
-        <v>7</v>
-      </c>
-      <c r="BA122">
-        <v>6</v>
-      </c>
-      <c r="BB122">
-        <v>6</v>
-      </c>
-      <c r="BC122">
-        <v>12</v>
-      </c>
-      <c r="BD122">
-        <v>1.51</v>
-      </c>
-      <c r="BE122">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF122">
-        <v>3</v>
-      </c>
-      <c r="BG122">
-        <v>1.37</v>
-      </c>
-      <c r="BH122">
-        <v>2.66</v>
-      </c>
-      <c r="BI122">
-        <v>1.8</v>
-      </c>
-      <c r="BJ122">
-        <v>2</v>
-      </c>
-      <c r="BK122">
-        <v>2.15</v>
-      </c>
-      <c r="BL122">
-        <v>1.56</v>
-      </c>
-      <c r="BM122">
-        <v>2.88</v>
-      </c>
-      <c r="BN122">
-        <v>1.32</v>
-      </c>
-      <c r="BO122">
-        <v>3.8</v>
-      </c>
-      <c r="BP122">
-        <v>1.21</v>
-      </c>
-    </row>
-    <row r="123" spans="1:68">
-      <c r="A123" s="1">
-        <v>122</v>
-      </c>
-      <c r="B123">
-        <v>7813942</v>
-      </c>
-      <c r="C123" t="s">
-        <v>68</v>
-      </c>
-      <c r="D123" t="s">
-        <v>69</v>
-      </c>
-      <c r="E123" s="2">
-        <v>45836.29166666666</v>
-      </c>
-      <c r="F123">
-        <v>18</v>
-      </c>
-      <c r="G123" t="s">
-        <v>73</v>
-      </c>
-      <c r="H123" t="s">
-        <v>71</v>
-      </c>
-      <c r="I123">
-        <v>0</v>
-      </c>
-      <c r="J123">
-        <v>0</v>
-      </c>
-      <c r="K123">
-        <v>0</v>
-      </c>
-      <c r="L123">
-        <v>0</v>
-      </c>
-      <c r="M123">
-        <v>0</v>
-      </c>
-      <c r="N123">
-        <v>0</v>
-      </c>
-      <c r="O123" t="s">
-        <v>85</v>
-      </c>
-      <c r="P123" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q123">
-        <v>3</v>
-      </c>
-      <c r="R123">
-        <v>1.97</v>
-      </c>
-      <c r="S123">
-        <v>3.62</v>
-      </c>
-      <c r="T123">
-        <v>1.42</v>
-      </c>
-      <c r="U123">
-        <v>2.65</v>
-      </c>
-      <c r="V123">
-        <v>3.04</v>
-      </c>
-      <c r="W123">
-        <v>1.33</v>
-      </c>
-      <c r="X123">
-        <v>8.5</v>
-      </c>
-      <c r="Y123">
-        <v>1.01</v>
-      </c>
-      <c r="Z123">
-        <v>2.38</v>
-      </c>
-      <c r="AA123">
-        <v>3.05</v>
-      </c>
-      <c r="AB123">
-        <v>2.69</v>
-      </c>
-      <c r="AC123">
-        <v>1.03</v>
-      </c>
-      <c r="AD123">
-        <v>9</v>
-      </c>
-      <c r="AE123">
-        <v>1.28</v>
-      </c>
-      <c r="AF123">
-        <v>3.05</v>
-      </c>
-      <c r="AG123">
-        <v>2</v>
-      </c>
-      <c r="AH123">
-        <v>1.72</v>
-      </c>
-      <c r="AI123">
-        <v>1.78</v>
-      </c>
-      <c r="AJ123">
-        <v>1.88</v>
-      </c>
-      <c r="AK123">
-        <v>1.34</v>
-      </c>
-      <c r="AL123">
-        <v>1.3</v>
-      </c>
-      <c r="AM123">
-        <v>1.52</v>
-      </c>
-      <c r="AN123">
-        <v>0.78</v>
-      </c>
-      <c r="AO123">
-        <v>0.38</v>
-      </c>
-      <c r="AP123">
-        <v>0.8</v>
-      </c>
-      <c r="AQ123">
-        <v>0.44</v>
-      </c>
-      <c r="AR123">
-        <v>1.21</v>
-      </c>
-      <c r="AS123">
-        <v>1.16</v>
-      </c>
-      <c r="AT123">
-        <v>2.37</v>
-      </c>
-      <c r="AU123">
-        <v>2</v>
-      </c>
-      <c r="AV123">
-        <v>4</v>
-      </c>
-      <c r="AW123">
-        <v>2</v>
-      </c>
-      <c r="AX123">
-        <v>5</v>
-      </c>
-      <c r="AY123">
-        <v>4</v>
-      </c>
-      <c r="AZ123">
-        <v>9</v>
-      </c>
-      <c r="BA123">
-        <v>1</v>
-      </c>
-      <c r="BB123">
-        <v>6</v>
-      </c>
-      <c r="BC123">
-        <v>7</v>
-      </c>
-      <c r="BD123">
-        <v>2.01</v>
-      </c>
-      <c r="BE123">
-        <v>5.9</v>
-      </c>
-      <c r="BF123">
-        <v>2.22</v>
-      </c>
-      <c r="BG123">
-        <v>1.51</v>
-      </c>
-      <c r="BH123">
-        <v>2.26</v>
-      </c>
-      <c r="BI123">
-        <v>1.9</v>
-      </c>
-      <c r="BJ123">
-        <v>1.9</v>
-      </c>
-      <c r="BK123">
-        <v>2.56</v>
-      </c>
-      <c r="BL123">
-        <v>1.4</v>
-      </c>
-      <c r="BM123">
-        <v>3.58</v>
-      </c>
-      <c r="BN123">
-        <v>1.21</v>
-      </c>
-      <c r="BO123">
-        <v>4.9</v>
-      </c>
-      <c r="BP123">
-        <v>1.12</v>
-      </c>
-    </row>
-    <row r="124" spans="1:68">
-      <c r="A124" s="1">
-        <v>123</v>
-      </c>
-      <c r="B124">
-        <v>7813943</v>
-      </c>
-      <c r="C124" t="s">
-        <v>68</v>
-      </c>
-      <c r="D124" t="s">
-        <v>69</v>
-      </c>
-      <c r="E124" s="2">
-        <v>45836.29166666666</v>
-      </c>
-      <c r="F124">
-        <v>18</v>
-      </c>
-      <c r="G124" t="s">
-        <v>77</v>
-      </c>
-      <c r="H124" t="s">
-        <v>74</v>
-      </c>
-      <c r="I124">
-        <v>0</v>
-      </c>
-      <c r="J124">
-        <v>0</v>
-      </c>
-      <c r="K124">
-        <v>0</v>
-      </c>
-      <c r="L124">
-        <v>1</v>
-      </c>
-      <c r="M124">
-        <v>0</v>
-      </c>
-      <c r="N124">
-        <v>1</v>
-      </c>
-      <c r="O124" t="s">
-        <v>165</v>
-      </c>
-      <c r="P124" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q124">
-        <v>3.22</v>
-      </c>
-      <c r="R124">
-        <v>1.97</v>
-      </c>
-      <c r="S124">
-        <v>3.34</v>
-      </c>
-      <c r="T124">
-        <v>1.44</v>
-      </c>
-      <c r="U124">
-        <v>2.57</v>
-      </c>
-      <c r="V124">
-        <v>3.14</v>
-      </c>
-      <c r="W124">
-        <v>1.31</v>
-      </c>
-      <c r="X124">
-        <v>8.1</v>
-      </c>
-      <c r="Y124">
-        <v>1.02</v>
-      </c>
-      <c r="Z124">
-        <v>2.58</v>
-      </c>
-      <c r="AA124">
-        <v>3.09</v>
-      </c>
-      <c r="AB124">
-        <v>2.45</v>
-      </c>
-      <c r="AC124">
-        <v>1.02</v>
-      </c>
-      <c r="AD124">
-        <v>7.8</v>
-      </c>
-      <c r="AE124">
-        <v>1.34</v>
-      </c>
-      <c r="AF124">
-        <v>2.78</v>
-      </c>
-      <c r="AG124">
-        <v>1.97</v>
-      </c>
-      <c r="AH124">
-        <v>1.73</v>
-      </c>
-      <c r="AI124">
-        <v>1.85</v>
-      </c>
-      <c r="AJ124">
-        <v>1.81</v>
-      </c>
-      <c r="AK124">
-        <v>1.42</v>
-      </c>
-      <c r="AL124">
-        <v>1.3</v>
-      </c>
-      <c r="AM124">
-        <v>1.43</v>
-      </c>
-      <c r="AN124">
-        <v>1.13</v>
-      </c>
-      <c r="AO124">
-        <v>1.13</v>
-      </c>
-      <c r="AP124">
-        <v>1.33</v>
-      </c>
-      <c r="AQ124">
-        <v>1</v>
-      </c>
-      <c r="AR124">
-        <v>1.38</v>
-      </c>
-      <c r="AS124">
-        <v>1.28</v>
-      </c>
-      <c r="AT124">
-        <v>2.66</v>
-      </c>
-      <c r="AU124">
-        <v>2</v>
-      </c>
-      <c r="AV124">
-        <v>5</v>
-      </c>
-      <c r="AW124">
-        <v>4</v>
-      </c>
-      <c r="AX124">
-        <v>4</v>
-      </c>
-      <c r="AY124">
-        <v>6</v>
-      </c>
-      <c r="AZ124">
-        <v>9</v>
-      </c>
-      <c r="BA124">
-        <v>3</v>
-      </c>
-      <c r="BB124">
-        <v>3</v>
-      </c>
-      <c r="BC124">
-        <v>6</v>
-      </c>
-      <c r="BD124">
-        <v>1.84</v>
-      </c>
-      <c r="BE124">
-        <v>6.1</v>
-      </c>
-      <c r="BF124">
-        <v>2.44</v>
-      </c>
-      <c r="BG124">
-        <v>1.42</v>
-      </c>
-      <c r="BH124">
-        <v>2.49</v>
-      </c>
-      <c r="BI124">
-        <v>1.85</v>
-      </c>
-      <c r="BJ124">
-        <v>1.95</v>
-      </c>
-      <c r="BK124">
-        <v>2.28</v>
-      </c>
-      <c r="BL124">
-        <v>1.5</v>
-      </c>
-      <c r="BM124">
-        <v>3.14</v>
-      </c>
-      <c r="BN124">
-        <v>1.27</v>
-      </c>
-      <c r="BO124">
-        <v>4.1</v>
-      </c>
-      <c r="BP124">
-        <v>1.18</v>
-      </c>
-    </row>
-    <row r="125" spans="1:68">
-      <c r="A125" s="1">
-        <v>124</v>
-      </c>
-      <c r="B125">
-        <v>7813944</v>
-      </c>
-      <c r="C125" t="s">
-        <v>68</v>
-      </c>
-      <c r="D125" t="s">
-        <v>69</v>
-      </c>
-      <c r="E125" s="2">
-        <v>45837.29166666666</v>
-      </c>
-      <c r="F125">
-        <v>18</v>
-      </c>
-      <c r="G125" t="s">
-        <v>79</v>
-      </c>
-      <c r="H125" t="s">
-        <v>72</v>
-      </c>
-      <c r="I125">
-        <v>1</v>
-      </c>
-      <c r="J125">
-        <v>0</v>
-      </c>
-      <c r="K125">
-        <v>1</v>
-      </c>
-      <c r="L125">
-        <v>1</v>
-      </c>
-      <c r="M125">
-        <v>1</v>
-      </c>
-      <c r="N125">
-        <v>2</v>
-      </c>
-      <c r="O125" t="s">
-        <v>166</v>
-      </c>
-      <c r="P125" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q125">
-        <v>2.5</v>
-      </c>
-      <c r="R125">
-        <v>2.3</v>
-      </c>
-      <c r="S125">
-        <v>3.8</v>
-      </c>
-      <c r="T125">
-        <v>1.3</v>
-      </c>
-      <c r="U125">
-        <v>3.2</v>
-      </c>
-      <c r="V125">
-        <v>2.5</v>
-      </c>
-      <c r="W125">
-        <v>1.44</v>
-      </c>
-      <c r="X125">
-        <v>6</v>
-      </c>
-      <c r="Y125">
-        <v>1.11</v>
-      </c>
-      <c r="Z125">
-        <v>1.9</v>
-      </c>
-      <c r="AA125">
-        <v>3.45</v>
-      </c>
-      <c r="AB125">
-        <v>3.31</v>
-      </c>
-      <c r="AC125">
-        <v>1.01</v>
-      </c>
-      <c r="AD125">
-        <v>11</v>
-      </c>
-      <c r="AE125">
-        <v>1.21</v>
-      </c>
-      <c r="AF125">
-        <v>3.58</v>
-      </c>
-      <c r="AG125">
-        <v>1.81</v>
-      </c>
-      <c r="AH125">
-        <v>1.89</v>
-      </c>
-      <c r="AI125">
-        <v>1.67</v>
-      </c>
-      <c r="AJ125">
-        <v>2.1</v>
-      </c>
-      <c r="AK125">
-        <v>1.29</v>
-      </c>
-      <c r="AL125">
-        <v>1.3</v>
-      </c>
-      <c r="AM125">
-        <v>1.8</v>
-      </c>
-      <c r="AN125">
-        <v>2.22</v>
-      </c>
-      <c r="AO125">
-        <v>2.43</v>
-      </c>
-      <c r="AP125">
-        <v>2.1</v>
-      </c>
-      <c r="AQ125">
-        <v>2.25</v>
-      </c>
-      <c r="AR125">
-        <v>1.82</v>
-      </c>
-      <c r="AS125">
-        <v>1.22</v>
-      </c>
-      <c r="AT125">
-        <v>3.04</v>
-      </c>
-      <c r="AU125">
-        <v>3</v>
-      </c>
-      <c r="AV125">
-        <v>7</v>
-      </c>
-      <c r="AW125">
-        <v>9</v>
-      </c>
-      <c r="AX125">
-        <v>5</v>
-      </c>
-      <c r="AY125">
-        <v>12</v>
-      </c>
-      <c r="AZ125">
-        <v>12</v>
-      </c>
-      <c r="BA125">
-        <v>3</v>
-      </c>
-      <c r="BB125">
-        <v>7</v>
-      </c>
-      <c r="BC125">
-        <v>10</v>
-      </c>
-      <c r="BD125">
-        <v>1.67</v>
-      </c>
-      <c r="BE125">
-        <v>8</v>
-      </c>
-      <c r="BF125">
-        <v>2.54</v>
-      </c>
-      <c r="BG125">
-        <v>1.35</v>
-      </c>
-      <c r="BH125">
-        <v>2.74</v>
-      </c>
-      <c r="BI125">
-        <v>1.66</v>
-      </c>
-      <c r="BJ125">
-        <v>2.04</v>
-      </c>
-      <c r="BK125">
-        <v>2.08</v>
-      </c>
-      <c r="BL125">
-        <v>1.6</v>
-      </c>
-      <c r="BM125">
-        <v>2.81</v>
-      </c>
-      <c r="BN125">
-        <v>1.33</v>
-      </c>
-      <c r="BO125">
-        <v>3.58</v>
-      </c>
-      <c r="BP125">
-        <v>1.23</v>
-      </c>
-    </row>
-    <row r="126" spans="1:68">
-      <c r="A126" s="1">
-        <v>125</v>
-      </c>
-      <c r="B126">
-        <v>7813945</v>
-      </c>
-      <c r="C126" t="s">
-        <v>68</v>
-      </c>
-      <c r="D126" t="s">
-        <v>69</v>
-      </c>
-      <c r="E126" s="2">
-        <v>45837.29166666666</v>
-      </c>
-      <c r="F126">
-        <v>18</v>
-      </c>
-      <c r="G126" t="s">
-        <v>82</v>
-      </c>
-      <c r="H126" t="s">
-        <v>83</v>
-      </c>
-      <c r="I126">
-        <v>1</v>
-      </c>
-      <c r="J126">
-        <v>0</v>
-      </c>
-      <c r="K126">
-        <v>1</v>
-      </c>
-      <c r="L126">
-        <v>2</v>
-      </c>
-      <c r="M126">
-        <v>2</v>
-      </c>
-      <c r="N126">
-        <v>4</v>
-      </c>
-      <c r="O126" t="s">
-        <v>167</v>
-      </c>
-      <c r="P126" t="s">
-        <v>237</v>
-      </c>
-      <c r="Q126">
-        <v>3.6</v>
-      </c>
-      <c r="R126">
-        <v>2.2</v>
-      </c>
-      <c r="S126">
-        <v>2.7</v>
-      </c>
-      <c r="T126">
-        <v>1.36</v>
-      </c>
-      <c r="U126">
-        <v>2.9</v>
-      </c>
-      <c r="V126">
-        <v>2.8</v>
-      </c>
-      <c r="W126">
-        <v>1.4</v>
-      </c>
-      <c r="X126">
-        <v>7</v>
-      </c>
-      <c r="Y126">
-        <v>1.08</v>
-      </c>
-      <c r="Z126">
-        <v>2.88</v>
-      </c>
-      <c r="AA126">
-        <v>3.41</v>
-      </c>
-      <c r="AB126">
-        <v>2.08</v>
-      </c>
-      <c r="AC126">
-        <v>1.01</v>
-      </c>
-      <c r="AD126">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AE126">
-        <v>1.24</v>
-      </c>
-      <c r="AF126">
-        <v>3.34</v>
-      </c>
-      <c r="AG126">
-        <v>1.87</v>
-      </c>
-      <c r="AH126">
-        <v>1.83</v>
-      </c>
-      <c r="AI126">
-        <v>1.73</v>
-      </c>
-      <c r="AJ126">
-        <v>2.05</v>
-      </c>
-      <c r="AK126">
-        <v>1.65</v>
-      </c>
-      <c r="AL126">
-        <v>1.3</v>
-      </c>
-      <c r="AM126">
-        <v>1.36</v>
-      </c>
-      <c r="AN126">
-        <v>0.33</v>
-      </c>
-      <c r="AO126">
-        <v>1.73</v>
-      </c>
-      <c r="AP126">
-        <v>0.75</v>
-      </c>
-      <c r="AQ126">
-        <v>1.67</v>
-      </c>
-      <c r="AR126">
-        <v>1.4</v>
-      </c>
-      <c r="AS126">
-        <v>1.22</v>
-      </c>
-      <c r="AT126">
-        <v>2.62</v>
-      </c>
-      <c r="AU126">
-        <v>7</v>
-      </c>
-      <c r="AV126">
-        <v>4</v>
-      </c>
-      <c r="AW126">
-        <v>5</v>
-      </c>
-      <c r="AX126">
-        <v>4</v>
-      </c>
-      <c r="AY126">
-        <v>12</v>
-      </c>
-      <c r="AZ126">
-        <v>8</v>
-      </c>
-      <c r="BA126">
-        <v>5</v>
-      </c>
-      <c r="BB126">
-        <v>3</v>
-      </c>
-      <c r="BC126">
-        <v>8</v>
-      </c>
-      <c r="BD126">
-        <v>2.26</v>
-      </c>
-      <c r="BE126">
-        <v>5.85</v>
-      </c>
-      <c r="BF126">
-        <v>1.98</v>
-      </c>
-      <c r="BG126">
-        <v>1.49</v>
-      </c>
-      <c r="BH126">
-        <v>2.3</v>
-      </c>
-      <c r="BI126">
-        <v>1.89</v>
-      </c>
-      <c r="BJ126">
-        <v>1.77</v>
-      </c>
-      <c r="BK126">
-        <v>2.49</v>
-      </c>
-      <c r="BL126">
-        <v>1.42</v>
-      </c>
-      <c r="BM126">
-        <v>3.5</v>
-      </c>
-      <c r="BN126">
-        <v>1.22</v>
-      </c>
-      <c r="BO126">
-        <v>4.5</v>
-      </c>
-      <c r="BP126">
-        <v>1.15</v>
-      </c>
-    </row>
-    <row r="127" spans="1:68">
-      <c r="A127" s="1">
-        <v>126</v>
-      </c>
-      <c r="B127">
-        <v>7813946</v>
-      </c>
-      <c r="C127" t="s">
-        <v>68</v>
-      </c>
-      <c r="D127" t="s">
-        <v>69</v>
-      </c>
-      <c r="E127" s="2">
-        <v>45837.29166666666</v>
-      </c>
-      <c r="F127">
-        <v>18</v>
-      </c>
-      <c r="G127" t="s">
-        <v>78</v>
-      </c>
-      <c r="H127" t="s">
-        <v>70</v>
-      </c>
-      <c r="I127">
-        <v>1</v>
-      </c>
-      <c r="J127">
-        <v>0</v>
-      </c>
-      <c r="K127">
-        <v>1</v>
-      </c>
-      <c r="L127">
-        <v>1</v>
-      </c>
-      <c r="M127">
-        <v>1</v>
-      </c>
-      <c r="N127">
-        <v>2</v>
-      </c>
-      <c r="O127" t="s">
-        <v>168</v>
-      </c>
-      <c r="P127" t="s">
-        <v>238</v>
-      </c>
-      <c r="Q127">
-        <v>4.33</v>
-      </c>
-      <c r="R127">
-        <v>2.1</v>
-      </c>
-      <c r="S127">
-        <v>2.5</v>
-      </c>
-      <c r="T127">
-        <v>1.4</v>
-      </c>
-      <c r="U127">
-        <v>2.75</v>
-      </c>
-      <c r="V127">
-        <v>3</v>
-      </c>
-      <c r="W127">
-        <v>1.36</v>
-      </c>
-      <c r="X127">
-        <v>8.5</v>
-      </c>
-      <c r="Y127">
-        <v>1.07</v>
-      </c>
-      <c r="Z127">
-        <v>3.69</v>
-      </c>
-      <c r="AA127">
-        <v>3.21</v>
-      </c>
-      <c r="AB127">
-        <v>1.86</v>
-      </c>
-      <c r="AC127">
-        <v>1.01</v>
-      </c>
-      <c r="AD127">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AE127">
-        <v>1.34</v>
-      </c>
-      <c r="AF127">
-        <v>2.78</v>
-      </c>
-      <c r="AG127">
-        <v>2</v>
-      </c>
-      <c r="AH127">
-        <v>1.65</v>
-      </c>
-      <c r="AI127">
-        <v>1.91</v>
-      </c>
-      <c r="AJ127">
-        <v>1.83</v>
-      </c>
-      <c r="AK127">
-        <v>1.85</v>
-      </c>
-      <c r="AL127">
-        <v>1.33</v>
-      </c>
-      <c r="AM127">
-        <v>1.22</v>
-      </c>
-      <c r="AN127">
-        <v>1.22</v>
-      </c>
-      <c r="AO127">
-        <v>2.29</v>
-      </c>
-      <c r="AP127">
-        <v>1.2</v>
-      </c>
-      <c r="AQ127">
-        <v>1.89</v>
-      </c>
-      <c r="AR127">
-        <v>1.63</v>
-      </c>
-      <c r="AS127">
-        <v>1.2</v>
-      </c>
-      <c r="AT127">
-        <v>2.83</v>
-      </c>
-      <c r="AU127">
-        <v>8</v>
-      </c>
-      <c r="AV127">
-        <v>2</v>
-      </c>
-      <c r="AW127">
-        <v>2</v>
-      </c>
-      <c r="AX127">
-        <v>8</v>
-      </c>
-      <c r="AY127">
-        <v>10</v>
-      </c>
-      <c r="AZ127">
-        <v>10</v>
-      </c>
-      <c r="BA127">
-        <v>0</v>
-      </c>
-      <c r="BB127">
-        <v>4</v>
-      </c>
-      <c r="BC127">
-        <v>4</v>
-      </c>
-      <c r="BD127">
-        <v>2.26</v>
-      </c>
-      <c r="BE127">
-        <v>5.8</v>
-      </c>
-      <c r="BF127">
-        <v>1.99</v>
-      </c>
-      <c r="BG127">
-        <v>1.57</v>
-      </c>
-      <c r="BH127">
-        <v>2.14</v>
-      </c>
-      <c r="BI127">
-        <v>2.03</v>
-      </c>
-      <c r="BJ127">
-        <v>1.67</v>
-      </c>
-      <c r="BK127">
-        <v>2.7</v>
-      </c>
-      <c r="BL127">
-        <v>1.36</v>
-      </c>
-      <c r="BM127">
-        <v>3.86</v>
-      </c>
-      <c r="BN127">
-        <v>1.18</v>
-      </c>
-      <c r="BO127">
-        <v>4.95</v>
-      </c>
-      <c r="BP127">
-        <v>1.12</v>
-      </c>
-    </row>
-    <row r="128" spans="1:68">
-      <c r="A128" s="1">
-        <v>127</v>
-      </c>
-      <c r="B128">
-        <v>7813947</v>
-      </c>
-      <c r="C128" t="s">
-        <v>68</v>
-      </c>
-      <c r="D128" t="s">
-        <v>69</v>
-      </c>
-      <c r="E128" s="2">
-        <v>45843.29166666666</v>
-      </c>
-      <c r="F128">
-        <v>19</v>
-      </c>
-      <c r="G128" t="s">
-        <v>81</v>
-      </c>
-      <c r="H128" t="s">
-        <v>79</v>
-      </c>
-      <c r="I128">
-        <v>0</v>
-      </c>
-      <c r="J128">
-        <v>2</v>
-      </c>
-      <c r="K128">
-        <v>2</v>
-      </c>
-      <c r="L128">
-        <v>2</v>
-      </c>
-      <c r="M128">
-        <v>3</v>
-      </c>
-      <c r="N128">
-        <v>5</v>
-      </c>
-      <c r="O128" t="s">
-        <v>169</v>
-      </c>
-      <c r="P128" t="s">
-        <v>239</v>
-      </c>
-      <c r="Q128">
-        <v>3.5</v>
-      </c>
-      <c r="R128">
-        <v>2.25</v>
-      </c>
-      <c r="S128">
-        <v>2.7</v>
-      </c>
-      <c r="T128">
-        <v>1.33</v>
-      </c>
-      <c r="U128">
-        <v>3.1</v>
-      </c>
-      <c r="V128">
-        <v>2.6</v>
-      </c>
-      <c r="W128">
-        <v>1.44</v>
-      </c>
-      <c r="X128">
-        <v>6.5</v>
-      </c>
-      <c r="Y128">
-        <v>1.11</v>
-      </c>
-      <c r="Z128">
-        <v>2.95</v>
-      </c>
-      <c r="AA128">
-        <v>3.31</v>
-      </c>
-      <c r="AB128">
-        <v>2.09</v>
-      </c>
-      <c r="AC128">
-        <v>1.01</v>
-      </c>
-      <c r="AD128">
-        <v>11</v>
-      </c>
-      <c r="AE128">
-        <v>1.17</v>
-      </c>
-      <c r="AF128">
-        <v>4.05</v>
-      </c>
-      <c r="AG128">
-        <v>1.82</v>
-      </c>
-      <c r="AH128">
-        <v>1.88</v>
-      </c>
-      <c r="AI128">
-        <v>1.65</v>
-      </c>
-      <c r="AJ128">
-        <v>2.15</v>
-      </c>
-      <c r="AK128">
-        <v>1.62</v>
-      </c>
-      <c r="AL128">
-        <v>1.3</v>
-      </c>
-      <c r="AM128">
-        <v>1.36</v>
-      </c>
-      <c r="AN128">
-        <v>1.44</v>
-      </c>
-      <c r="AO128">
-        <v>1.75</v>
-      </c>
-      <c r="AP128">
-        <v>1.3</v>
-      </c>
-      <c r="AQ128">
-        <v>1.89</v>
-      </c>
-      <c r="AR128">
-        <v>1.71</v>
-      </c>
-      <c r="AS128">
-        <v>1.71</v>
-      </c>
-      <c r="AT128">
-        <v>3.42</v>
-      </c>
-      <c r="AU128">
-        <v>9</v>
-      </c>
-      <c r="AV128">
-        <v>9</v>
-      </c>
-      <c r="AW128">
-        <v>11</v>
-      </c>
-      <c r="AX128">
-        <v>12</v>
-      </c>
-      <c r="AY128">
-        <v>20</v>
-      </c>
-      <c r="AZ128">
-        <v>21</v>
-      </c>
-      <c r="BA128">
-        <v>7</v>
-      </c>
-      <c r="BB128">
-        <v>6</v>
-      </c>
-      <c r="BC128">
-        <v>13</v>
-      </c>
-      <c r="BD128">
-        <v>2.31</v>
-      </c>
-      <c r="BE128">
-        <v>6.59</v>
-      </c>
-      <c r="BF128">
-        <v>2.01</v>
-      </c>
-      <c r="BG128">
-        <v>1.59</v>
-      </c>
-      <c r="BH128">
-        <v>2.19</v>
-      </c>
-      <c r="BI128">
-        <v>2.01</v>
-      </c>
-      <c r="BJ128">
-        <v>1.71</v>
-      </c>
-      <c r="BK128">
-        <v>2.66</v>
-      </c>
-      <c r="BL128">
-        <v>1.39</v>
-      </c>
-      <c r="BM128">
-        <v>3.79</v>
-      </c>
-      <c r="BN128">
-        <v>1.18</v>
-      </c>
-      <c r="BO128">
-        <v>5.82</v>
-      </c>
-      <c r="BP128">
-        <v>1.05</v>
-      </c>
-    </row>
-    <row r="129" spans="1:68">
-      <c r="A129" s="1">
-        <v>128</v>
-      </c>
-      <c r="B129">
-        <v>7813948</v>
-      </c>
-      <c r="C129" t="s">
-        <v>68</v>
-      </c>
-      <c r="D129" t="s">
-        <v>69</v>
-      </c>
-      <c r="E129" s="2">
-        <v>45843.29166666666</v>
-      </c>
-      <c r="F129">
-        <v>19</v>
-      </c>
-      <c r="G129" t="s">
-        <v>83</v>
-      </c>
-      <c r="H129" t="s">
-        <v>70</v>
-      </c>
-      <c r="I129">
-        <v>1</v>
-      </c>
-      <c r="J129">
-        <v>1</v>
-      </c>
-      <c r="K129">
-        <v>2</v>
-      </c>
-      <c r="L129">
-        <v>2</v>
-      </c>
-      <c r="M129">
-        <v>1</v>
-      </c>
-      <c r="N129">
-        <v>3</v>
-      </c>
-      <c r="O129" t="s">
-        <v>170</v>
-      </c>
-      <c r="P129" t="s">
-        <v>240</v>
-      </c>
-      <c r="Q129">
-        <v>4.33</v>
-      </c>
-      <c r="R129">
-        <v>2.15</v>
-      </c>
-      <c r="S129">
-        <v>2.45</v>
-      </c>
-      <c r="T129">
-        <v>1.4</v>
-      </c>
-      <c r="U129">
-        <v>2.88</v>
-      </c>
-      <c r="V129">
-        <v>2.9</v>
-      </c>
-      <c r="W129">
-        <v>1.36</v>
-      </c>
-      <c r="X129">
-        <v>8</v>
-      </c>
-      <c r="Y129">
-        <v>1.08</v>
-      </c>
-      <c r="Z129">
-        <v>3.71</v>
-      </c>
-      <c r="AA129">
-        <v>3.21</v>
-      </c>
-      <c r="AB129">
-        <v>1.86</v>
-      </c>
-      <c r="AC129">
-        <v>1</v>
-      </c>
-      <c r="AD129">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AE129">
-        <v>1.24</v>
-      </c>
-      <c r="AF129">
-        <v>3.34</v>
-      </c>
-      <c r="AG129">
-        <v>1.93</v>
-      </c>
-      <c r="AH129">
-        <v>1.77</v>
-      </c>
-      <c r="AI129">
-        <v>1.83</v>
-      </c>
-      <c r="AJ129">
-        <v>1.91</v>
-      </c>
-      <c r="AK129">
-        <v>1.95</v>
-      </c>
-      <c r="AL129">
-        <v>1.3</v>
-      </c>
-      <c r="AM129">
-        <v>1.2</v>
-      </c>
-      <c r="AN129">
-        <v>1.83</v>
-      </c>
-      <c r="AO129">
-        <v>2.13</v>
-      </c>
-      <c r="AP129">
-        <v>2</v>
-      </c>
-      <c r="AQ129">
-        <v>1.89</v>
-      </c>
-      <c r="AR129">
-        <v>1.53</v>
-      </c>
-      <c r="AS129">
-        <v>1.18</v>
-      </c>
-      <c r="AT129">
-        <v>2.71</v>
-      </c>
-      <c r="AU129">
-        <v>4</v>
-      </c>
-      <c r="AV129">
-        <v>4</v>
-      </c>
-      <c r="AW129">
-        <v>3</v>
-      </c>
-      <c r="AX129">
-        <v>7</v>
-      </c>
-      <c r="AY129">
-        <v>7</v>
-      </c>
-      <c r="AZ129">
-        <v>11</v>
-      </c>
-      <c r="BA129">
-        <v>2</v>
-      </c>
-      <c r="BB129">
-        <v>9</v>
-      </c>
-      <c r="BC129">
-        <v>11</v>
-      </c>
-      <c r="BD129">
-        <v>3.16</v>
-      </c>
-      <c r="BE129">
-        <v>7.06</v>
-      </c>
-      <c r="BF129">
-        <v>1.62</v>
-      </c>
-      <c r="BG129">
-        <v>1.56</v>
-      </c>
-      <c r="BH129">
-        <v>2.25</v>
-      </c>
-      <c r="BI129">
-        <v>1.96</v>
-      </c>
-      <c r="BJ129">
-        <v>1.75</v>
-      </c>
-      <c r="BK129">
-        <v>2.57</v>
-      </c>
-      <c r="BL129">
-        <v>1.42</v>
-      </c>
-      <c r="BM129">
-        <v>3.62</v>
-      </c>
-      <c r="BN129">
-        <v>1.2</v>
-      </c>
-      <c r="BO129">
-        <v>5.5</v>
-      </c>
-      <c r="BP129">
-        <v>1.06</v>
-      </c>
-    </row>
-    <row r="130" spans="1:68">
-      <c r="A130" s="1">
-        <v>129</v>
-      </c>
-      <c r="B130">
-        <v>7813949</v>
-      </c>
-      <c r="C130" t="s">
-        <v>68</v>
-      </c>
-      <c r="D130" t="s">
-        <v>69</v>
-      </c>
-      <c r="E130" s="2">
-        <v>45843.29166666666</v>
-      </c>
-      <c r="F130">
-        <v>19</v>
-      </c>
-      <c r="G130" t="s">
-        <v>82</v>
-      </c>
-      <c r="H130" t="s">
-        <v>75</v>
-      </c>
-      <c r="I130">
-        <v>0</v>
-      </c>
-      <c r="J130">
-        <v>1</v>
-      </c>
-      <c r="K130">
-        <v>1</v>
-      </c>
-      <c r="L130">
-        <v>2</v>
-      </c>
-      <c r="M130">
-        <v>1</v>
-      </c>
-      <c r="N130">
-        <v>3</v>
-      </c>
-      <c r="O130" t="s">
-        <v>171</v>
-      </c>
-      <c r="P130" t="s">
-        <v>241</v>
-      </c>
-      <c r="Q130">
-        <v>4.2</v>
-      </c>
-      <c r="R130">
-        <v>2.2</v>
-      </c>
-      <c r="S130">
-        <v>2.45</v>
-      </c>
-      <c r="T130">
-        <v>1.35</v>
-      </c>
-      <c r="U130">
-        <v>3</v>
-      </c>
-      <c r="V130">
-        <v>2.7</v>
-      </c>
-      <c r="W130">
-        <v>1.44</v>
-      </c>
-      <c r="X130">
-        <v>7</v>
-      </c>
-      <c r="Y130">
-        <v>1.1</v>
-      </c>
-      <c r="Z130">
-        <v>3.89</v>
-      </c>
-      <c r="AA130">
-        <v>3.57</v>
-      </c>
-      <c r="AB130">
-        <v>1.72</v>
-      </c>
-      <c r="AC130">
-        <v>1.01</v>
-      </c>
-      <c r="AD130">
-        <v>11</v>
-      </c>
-      <c r="AE130">
-        <v>1.22</v>
-      </c>
-      <c r="AF130">
-        <v>3.5</v>
-      </c>
-      <c r="AG130">
-        <v>1.8</v>
-      </c>
-      <c r="AH130">
-        <v>1.9</v>
-      </c>
-      <c r="AI130">
-        <v>1.75</v>
-      </c>
-      <c r="AJ130">
-        <v>2</v>
-      </c>
-      <c r="AK130">
-        <v>1.85</v>
-      </c>
-      <c r="AL130">
-        <v>1.3</v>
-      </c>
-      <c r="AM130">
-        <v>1.25</v>
-      </c>
-      <c r="AN130">
-        <v>0.43</v>
-      </c>
-      <c r="AO130">
-        <v>1.33</v>
-      </c>
-      <c r="AP130">
-        <v>0.75</v>
-      </c>
-      <c r="AQ130">
-        <v>1.2</v>
-      </c>
-      <c r="AR130">
-        <v>1.45</v>
-      </c>
-      <c r="AS130">
-        <v>1.33</v>
-      </c>
-      <c r="AT130">
-        <v>2.78</v>
-      </c>
-      <c r="AU130">
-        <v>6</v>
-      </c>
-      <c r="AV130">
-        <v>3</v>
-      </c>
-      <c r="AW130">
-        <v>7</v>
-      </c>
-      <c r="AX130">
-        <v>8</v>
-      </c>
-      <c r="AY130">
-        <v>13</v>
-      </c>
-      <c r="AZ130">
-        <v>11</v>
-      </c>
-      <c r="BA130">
-        <v>1</v>
-      </c>
-      <c r="BB130">
-        <v>1</v>
-      </c>
-      <c r="BC130">
-        <v>2</v>
-      </c>
-      <c r="BD130">
-        <v>3.07</v>
-      </c>
-      <c r="BE130">
-        <v>6.9</v>
-      </c>
-      <c r="BF130">
-        <v>1.65</v>
-      </c>
-      <c r="BG130">
-        <v>1.64</v>
-      </c>
-      <c r="BH130">
-        <v>2.12</v>
-      </c>
-      <c r="BI130">
-        <v>2.08</v>
-      </c>
-      <c r="BJ130">
-        <v>1.66</v>
-      </c>
-      <c r="BK130">
-        <v>2.78</v>
-      </c>
-      <c r="BL130">
-        <v>1.36</v>
-      </c>
-      <c r="BM130">
-        <v>4.01</v>
-      </c>
-      <c r="BN130">
-        <v>1.16</v>
-      </c>
-      <c r="BO130">
-        <v>6.25</v>
-      </c>
-      <c r="BP130">
-        <v>1.04</v>
-      </c>
-    </row>
-    <row r="131" spans="1:68">
-      <c r="A131" s="1">
-        <v>130</v>
-      </c>
-      <c r="B131">
-        <v>7813950</v>
-      </c>
-      <c r="C131" t="s">
-        <v>68</v>
-      </c>
-      <c r="D131" t="s">
-        <v>69</v>
-      </c>
-      <c r="E131" s="2">
-        <v>45843.29166666666</v>
-      </c>
-      <c r="F131">
-        <v>19</v>
-      </c>
-      <c r="G131" t="s">
-        <v>80</v>
-      </c>
-      <c r="H131" t="s">
-        <v>73</v>
-      </c>
-      <c r="I131">
-        <v>1</v>
-      </c>
-      <c r="J131">
-        <v>1</v>
-      </c>
-      <c r="K131">
-        <v>2</v>
-      </c>
-      <c r="L131">
-        <v>1</v>
-      </c>
-      <c r="M131">
-        <v>1</v>
-      </c>
-      <c r="N131">
-        <v>2</v>
-      </c>
-      <c r="O131" t="s">
-        <v>172</v>
-      </c>
-      <c r="P131" t="s">
-        <v>242</v>
-      </c>
-      <c r="Q131">
-        <v>2.8</v>
-      </c>
-      <c r="R131">
-        <v>2.1</v>
-      </c>
-      <c r="S131">
-        <v>3.6</v>
-      </c>
-      <c r="T131">
-        <v>1.4</v>
-      </c>
-      <c r="U131">
-        <v>2.8</v>
-      </c>
-      <c r="V131">
-        <v>2.9</v>
-      </c>
-      <c r="W131">
-        <v>1.36</v>
-      </c>
-      <c r="X131">
-        <v>7.5</v>
-      </c>
-      <c r="Y131">
-        <v>1.08</v>
-      </c>
-      <c r="Z131">
-        <v>2.2</v>
-      </c>
-      <c r="AA131">
-        <v>3.17</v>
-      </c>
-      <c r="AB131">
-        <v>2.86</v>
-      </c>
-      <c r="AC131">
-        <v>1.01</v>
-      </c>
-      <c r="AD131">
-        <v>8.4</v>
-      </c>
-      <c r="AE131">
-        <v>1.28</v>
-      </c>
-      <c r="AF131">
-        <v>3.08</v>
-      </c>
-      <c r="AG131">
-        <v>1.95</v>
-      </c>
-      <c r="AH131">
-        <v>1.75</v>
-      </c>
-      <c r="AI131">
-        <v>1.75</v>
-      </c>
-      <c r="AJ131">
-        <v>2</v>
-      </c>
-      <c r="AK131">
-        <v>1.36</v>
-      </c>
-      <c r="AL131">
-        <v>1.35</v>
-      </c>
-      <c r="AM131">
-        <v>1.6</v>
-      </c>
-      <c r="AN131">
-        <v>1.11</v>
-      </c>
-      <c r="AO131">
-        <v>1.13</v>
-      </c>
-      <c r="AP131">
-        <v>1.1</v>
-      </c>
-      <c r="AQ131">
-        <v>1.11</v>
-      </c>
-      <c r="AR131">
-        <v>1.67</v>
-      </c>
-      <c r="AS131">
-        <v>1.03</v>
-      </c>
-      <c r="AT131">
-        <v>2.7</v>
-      </c>
-      <c r="AU131">
-        <v>6</v>
-      </c>
-      <c r="AV131">
-        <v>6</v>
-      </c>
-      <c r="AW131">
-        <v>4</v>
-      </c>
-      <c r="AX131">
-        <v>1</v>
-      </c>
-      <c r="AY131">
-        <v>10</v>
-      </c>
-      <c r="AZ131">
-        <v>7</v>
-      </c>
-      <c r="BA131">
-        <v>2</v>
-      </c>
-      <c r="BB131">
-        <v>2</v>
-      </c>
-      <c r="BC131">
-        <v>4</v>
-      </c>
-      <c r="BD131">
-        <v>1.68</v>
-      </c>
-      <c r="BE131">
-        <v>6.88</v>
-      </c>
-      <c r="BF131">
-        <v>2.98</v>
-      </c>
-      <c r="BG131">
-        <v>1.61</v>
-      </c>
-      <c r="BH131">
-        <v>2.15</v>
-      </c>
-      <c r="BI131">
-        <v>2.04</v>
-      </c>
-      <c r="BJ131">
-        <v>1.69</v>
-      </c>
-      <c r="BK131">
-        <v>2.71</v>
-      </c>
-      <c r="BL131">
-        <v>1.37</v>
-      </c>
-      <c r="BM131">
-        <v>3.88</v>
-      </c>
-      <c r="BN131">
-        <v>1.17</v>
-      </c>
-      <c r="BO131">
-        <v>6.01</v>
-      </c>
-      <c r="BP131">
         <v>1.04</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="243">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -469,6 +469,60 @@
     <t>['6']</t>
   </si>
   <si>
+    <t>['31', '88']</t>
+  </si>
+  <si>
+    <t>['52', '60', '69', '88']</t>
+  </si>
+  <si>
+    <t>['20', '69', '90+5']</t>
+  </si>
+  <si>
+    <t>['38']</t>
+  </si>
+  <si>
+    <t>['52']</t>
+  </si>
+  <si>
+    <t>['18']</t>
+  </si>
+  <si>
+    <t>['45+2', '65', '73']</t>
+  </si>
+  <si>
+    <t>['73', '80', '82']</t>
+  </si>
+  <si>
+    <t>['67']</t>
+  </si>
+  <si>
+    <t>['27', '65']</t>
+  </si>
+  <si>
+    <t>['17', '59', '63', '84']</t>
+  </si>
+  <si>
+    <t>['6', '72']</t>
+  </si>
+  <si>
+    <t>['27']</t>
+  </si>
+  <si>
+    <t>['35', '45']</t>
+  </si>
+  <si>
+    <t>['90+5']</t>
+  </si>
+  <si>
+    <t>['19']</t>
+  </si>
+  <si>
+    <t>['15', '60']</t>
+  </si>
+  <si>
+    <t>['37']</t>
+  </si>
+  <si>
     <t>['48', '68']</t>
   </si>
   <si>
@@ -482,9 +536,6 @@
   </si>
   <si>
     <t>['1', '6']</t>
-  </si>
-  <si>
-    <t>['67']</t>
   </si>
   <si>
     <t>['85']</t>
@@ -515,9 +566,6 @@
   </si>
   <si>
     <t>['71']</t>
-  </si>
-  <si>
-    <t>['90+5']</t>
   </si>
   <si>
     <t>['44']</t>
@@ -638,6 +686,51 @@
   </si>
   <si>
     <t>['65', '75']</t>
+  </si>
+  <si>
+    <t>['29']</t>
+  </si>
+  <si>
+    <t>['23', '44', '57']</t>
+  </si>
+  <si>
+    <t>['9', '90+6']</t>
+  </si>
+  <si>
+    <t>['15', '26']</t>
+  </si>
+  <si>
+    <t>['62', '90+5']</t>
+  </si>
+  <si>
+    <t>['66']</t>
+  </si>
+  <si>
+    <t>['90+3']</t>
+  </si>
+  <si>
+    <t>['17']</t>
+  </si>
+  <si>
+    <t>['15', '49']</t>
+  </si>
+  <si>
+    <t>['41', '56']</t>
+  </si>
+  <si>
+    <t>['5', '76']</t>
+  </si>
+  <si>
+    <t>['12', '56', '82']</t>
+  </si>
+  <si>
+    <t>['69']</t>
+  </si>
+  <si>
+    <t>['71', '90+6']</t>
+  </si>
+  <si>
+    <t>['90+7']</t>
   </si>
   <si>
     <t>['34', '44', '81']</t>
@@ -1011,7 +1104,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP100"/>
+  <dimension ref="A1:BP131"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1345,10 +1438,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AQ2">
-        <v>1</v>
+        <v>0.78</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1473,7 +1566,7 @@
         <v>85</v>
       </c>
       <c r="P3" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="Q3">
         <v>3.8</v>
@@ -1551,10 +1644,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.57</v>
+        <v>0.89</v>
       </c>
       <c r="AQ3">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1757,10 +1850,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="AQ4">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1885,7 +1978,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="Q5">
         <v>4.5</v>
@@ -1963,10 +2056,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>0.88</v>
+        <v>0.8</v>
       </c>
       <c r="AQ5">
-        <v>1.57</v>
+        <v>1.89</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2169,10 +2262,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.71</v>
+        <v>1.33</v>
       </c>
       <c r="AQ6">
-        <v>0.14</v>
+        <v>0.44</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2378,7 +2471,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ7">
-        <v>0.86</v>
+        <v>1.33</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2503,7 +2596,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="Q8">
         <v>2.39</v>
@@ -2581,7 +2674,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.57</v>
+        <v>1.89</v>
       </c>
       <c r="AQ8">
         <v>1</v>
@@ -2787,10 +2880,10 @@
         <v>3</v>
       </c>
       <c r="AP9">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AQ9">
-        <v>1.57</v>
+        <v>1.89</v>
       </c>
       <c r="AR9">
         <v>2.58</v>
@@ -2915,7 +3008,7 @@
         <v>85</v>
       </c>
       <c r="P10" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="Q10">
         <v>4.3</v>
@@ -2993,10 +3086,10 @@
         <v>1</v>
       </c>
       <c r="AP10">
-        <v>0.88</v>
+        <v>0.8</v>
       </c>
       <c r="AQ10">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="AR10">
         <v>0.82</v>
@@ -3121,7 +3214,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="Q11">
         <v>2.8</v>
@@ -3202,7 +3295,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ11">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR11">
         <v>1.04</v>
@@ -3405,10 +3498,10 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AQ12">
-        <v>0.86</v>
+        <v>1.33</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3533,7 +3626,7 @@
         <v>85</v>
       </c>
       <c r="P13" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="Q13">
         <v>2.43</v>
@@ -3611,10 +3704,10 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="AQ13">
-        <v>1</v>
+        <v>0.78</v>
       </c>
       <c r="AR13">
         <v>1.4</v>
@@ -3739,7 +3832,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="Q14">
         <v>3.9</v>
@@ -3817,10 +3910,10 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>0.57</v>
+        <v>0.89</v>
       </c>
       <c r="AQ14">
-        <v>1.83</v>
+        <v>1.56</v>
       </c>
       <c r="AR14">
         <v>1.15</v>
@@ -4023,7 +4116,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.71</v>
+        <v>1.33</v>
       </c>
       <c r="AQ15">
         <v>1</v>
@@ -4151,7 +4244,7 @@
         <v>85</v>
       </c>
       <c r="P16" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="Q16">
         <v>3.18</v>
@@ -4229,10 +4322,10 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.57</v>
+        <v>1.89</v>
       </c>
       <c r="AQ16">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="AR16">
         <v>1.61</v>
@@ -4357,7 +4450,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>163</v>
+        <v>180</v>
       </c>
       <c r="Q17">
         <v>3</v>
@@ -4435,10 +4528,10 @@
         <v>1.5</v>
       </c>
       <c r="AP17">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AQ17">
-        <v>1</v>
+        <v>0.78</v>
       </c>
       <c r="AR17">
         <v>1.52</v>
@@ -4563,7 +4656,7 @@
         <v>85</v>
       </c>
       <c r="P18" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="Q18">
         <v>4.9</v>
@@ -4641,10 +4734,10 @@
         <v>2</v>
       </c>
       <c r="AP18">
-        <v>0.88</v>
+        <v>0.8</v>
       </c>
       <c r="AQ18">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR18">
         <v>1.29</v>
@@ -4769,7 +4862,7 @@
         <v>95</v>
       </c>
       <c r="P19" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="Q19">
         <v>2.71</v>
@@ -4847,7 +4940,7 @@
         <v>0.5</v>
       </c>
       <c r="AP19">
-        <v>0.71</v>
+        <v>1.2</v>
       </c>
       <c r="AQ19">
         <v>1</v>
@@ -4975,7 +5068,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="Q20">
         <v>3.5</v>
@@ -5056,7 +5149,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ20">
-        <v>1.57</v>
+        <v>1.89</v>
       </c>
       <c r="AR20">
         <v>1.06</v>
@@ -5259,10 +5352,10 @@
         <v>0.5</v>
       </c>
       <c r="AP21">
-        <v>0.57</v>
+        <v>0.89</v>
       </c>
       <c r="AQ21">
-        <v>0.86</v>
+        <v>1.33</v>
       </c>
       <c r="AR21">
         <v>1.02</v>
@@ -5387,7 +5480,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="Q22">
         <v>5</v>
@@ -5465,10 +5558,10 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.71</v>
+        <v>1.33</v>
       </c>
       <c r="AQ22">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AR22">
         <v>0.92</v>
@@ -5671,10 +5764,10 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AQ23">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="AR23">
         <v>1.93</v>
@@ -5799,7 +5892,7 @@
         <v>99</v>
       </c>
       <c r="P24" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="Q24">
         <v>3</v>
@@ -5877,7 +5970,7 @@
         <v>1.33</v>
       </c>
       <c r="AP24">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AQ24">
         <v>1</v>
@@ -6083,10 +6176,10 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>0.71</v>
+        <v>1.2</v>
       </c>
       <c r="AQ25">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR25">
         <v>2.07</v>
@@ -6289,10 +6382,10 @@
         <v>0.33</v>
       </c>
       <c r="AP26">
-        <v>2.43</v>
+        <v>2.1</v>
       </c>
       <c r="AQ26">
-        <v>0.86</v>
+        <v>1.33</v>
       </c>
       <c r="AR26">
         <v>0</v>
@@ -6417,7 +6510,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="Q27">
         <v>2.25</v>
@@ -6495,10 +6588,10 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="AQ27">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="AR27">
         <v>1.42</v>
@@ -6623,7 +6716,7 @@
         <v>101</v>
       </c>
       <c r="P28" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="Q28">
         <v>4</v>
@@ -6701,10 +6794,10 @@
         <v>2.33</v>
       </c>
       <c r="AP28">
-        <v>1.38</v>
+        <v>1.1</v>
       </c>
       <c r="AQ28">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR28">
         <v>0</v>
@@ -6829,7 +6922,7 @@
         <v>102</v>
       </c>
       <c r="P29" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="Q29">
         <v>2.2</v>
@@ -6907,10 +7000,10 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.57</v>
+        <v>1.89</v>
       </c>
       <c r="AQ29">
-        <v>0.86</v>
+        <v>1.11</v>
       </c>
       <c r="AR29">
         <v>1.22</v>
@@ -7035,7 +7128,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="Q30">
         <v>3.75</v>
@@ -7113,10 +7206,10 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>0.88</v>
+        <v>0.8</v>
       </c>
       <c r="AQ30">
-        <v>0.14</v>
+        <v>0.44</v>
       </c>
       <c r="AR30">
         <v>1.22</v>
@@ -7241,7 +7334,7 @@
         <v>104</v>
       </c>
       <c r="P31" t="s">
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="Q31">
         <v>3.25</v>
@@ -7319,10 +7412,10 @@
         <v>2</v>
       </c>
       <c r="AP31">
-        <v>2.43</v>
+        <v>2.1</v>
       </c>
       <c r="AQ31">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR31">
         <v>1.17</v>
@@ -7525,7 +7618,7 @@
         <v>1</v>
       </c>
       <c r="AP32">
-        <v>1.38</v>
+        <v>1.1</v>
       </c>
       <c r="AQ32">
         <v>1</v>
@@ -7653,7 +7746,7 @@
         <v>91</v>
       </c>
       <c r="P33" t="s">
-        <v>173</v>
+        <v>189</v>
       </c>
       <c r="Q33">
         <v>2.63</v>
@@ -7731,10 +7824,10 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AQ33">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="AR33">
         <v>1.69</v>
@@ -7859,7 +7952,7 @@
         <v>85</v>
       </c>
       <c r="P34" t="s">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="Q34">
         <v>3.8</v>
@@ -7937,10 +8030,10 @@
         <v>2</v>
       </c>
       <c r="AP34">
-        <v>0.57</v>
+        <v>0.89</v>
       </c>
       <c r="AQ34">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="AR34">
         <v>0.98</v>
@@ -8065,7 +8158,7 @@
         <v>106</v>
       </c>
       <c r="P35" t="s">
-        <v>175</v>
+        <v>191</v>
       </c>
       <c r="Q35">
         <v>2.8</v>
@@ -8146,7 +8239,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ35">
-        <v>1.83</v>
+        <v>1.56</v>
       </c>
       <c r="AR35">
         <v>1.05</v>
@@ -8349,10 +8442,10 @@
         <v>1</v>
       </c>
       <c r="AP36">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AQ36">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR36">
         <v>0</v>
@@ -8558,7 +8651,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ37">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="AR37">
         <v>1.11</v>
@@ -8683,7 +8776,7 @@
         <v>85</v>
       </c>
       <c r="P38" t="s">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="Q38">
         <v>5</v>
@@ -8761,10 +8854,10 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AQ38">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AR38">
         <v>1.61</v>
@@ -8889,7 +8982,7 @@
         <v>85</v>
       </c>
       <c r="P39" t="s">
-        <v>177</v>
+        <v>193</v>
       </c>
       <c r="Q39">
         <v>3.1</v>
@@ -8967,10 +9060,10 @@
         <v>1.6</v>
       </c>
       <c r="AP39">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="AQ39">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR39">
         <v>1.6</v>
@@ -9173,10 +9266,10 @@
         <v>1.33</v>
       </c>
       <c r="AP40">
-        <v>2.43</v>
+        <v>2.1</v>
       </c>
       <c r="AQ40">
-        <v>1</v>
+        <v>0.78</v>
       </c>
       <c r="AR40">
         <v>1.62</v>
@@ -9301,7 +9394,7 @@
         <v>110</v>
       </c>
       <c r="P41" t="s">
-        <v>178</v>
+        <v>194</v>
       </c>
       <c r="Q41">
         <v>3.25</v>
@@ -9379,10 +9472,10 @@
         <v>1.5</v>
       </c>
       <c r="AP41">
-        <v>0.71</v>
+        <v>1.2</v>
       </c>
       <c r="AQ41">
-        <v>1.83</v>
+        <v>1.56</v>
       </c>
       <c r="AR41">
         <v>1.52</v>
@@ -9507,7 +9600,7 @@
         <v>111</v>
       </c>
       <c r="P42" t="s">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="Q42">
         <v>2.5</v>
@@ -9585,7 +9678,7 @@
         <v>0.8</v>
       </c>
       <c r="AP42">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AQ42">
         <v>1</v>
@@ -9791,10 +9884,10 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>1.71</v>
+        <v>1.33</v>
       </c>
       <c r="AQ43">
-        <v>0.86</v>
+        <v>1.11</v>
       </c>
       <c r="AR43">
         <v>1.02</v>
@@ -9919,7 +10012,7 @@
         <v>113</v>
       </c>
       <c r="P44" t="s">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="Q44">
         <v>3.4</v>
@@ -9997,10 +10090,10 @@
         <v>0.5</v>
       </c>
       <c r="AP44">
-        <v>0.71</v>
+        <v>1.2</v>
       </c>
       <c r="AQ44">
-        <v>0.86</v>
+        <v>1.33</v>
       </c>
       <c r="AR44">
         <v>1.43</v>
@@ -10125,7 +10218,7 @@
         <v>113</v>
       </c>
       <c r="P45" t="s">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="Q45">
         <v>3.75</v>
@@ -10203,10 +10296,10 @@
         <v>1.83</v>
       </c>
       <c r="AP45">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AQ45">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR45">
         <v>1.49</v>
@@ -10331,7 +10424,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="Q46">
         <v>3.75</v>
@@ -10409,10 +10502,10 @@
         <v>1</v>
       </c>
       <c r="AP46">
-        <v>1.57</v>
+        <v>1.89</v>
       </c>
       <c r="AQ46">
-        <v>1.57</v>
+        <v>1.89</v>
       </c>
       <c r="AR46">
         <v>1.33</v>
@@ -10537,7 +10630,7 @@
         <v>85</v>
       </c>
       <c r="P47" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="Q47">
         <v>3</v>
@@ -10615,10 +10708,10 @@
         <v>1</v>
       </c>
       <c r="AP47">
-        <v>1.38</v>
+        <v>1.1</v>
       </c>
       <c r="AQ47">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR47">
         <v>1.74</v>
@@ -10821,7 +10914,7 @@
         <v>0.67</v>
       </c>
       <c r="AP48">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AQ48">
         <v>1</v>
@@ -10949,7 +11042,7 @@
         <v>116</v>
       </c>
       <c r="P49" t="s">
-        <v>183</v>
+        <v>199</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -11027,10 +11120,10 @@
         <v>0</v>
       </c>
       <c r="AP49">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="AQ49">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="AR49">
         <v>1.58</v>
@@ -11233,10 +11326,10 @@
         <v>0</v>
       </c>
       <c r="AP50">
-        <v>0.57</v>
+        <v>0.89</v>
       </c>
       <c r="AQ50">
-        <v>0.86</v>
+        <v>1.11</v>
       </c>
       <c r="AR50">
         <v>1.01</v>
@@ -11361,7 +11454,7 @@
         <v>85</v>
       </c>
       <c r="P51" t="s">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="Q51">
         <v>2.25</v>
@@ -11645,10 +11738,10 @@
         <v>0</v>
       </c>
       <c r="AP52">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AQ52">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="AR52">
         <v>1.66</v>
@@ -11851,10 +11944,10 @@
         <v>0.5</v>
       </c>
       <c r="AP53">
-        <v>2.43</v>
+        <v>2.1</v>
       </c>
       <c r="AQ53">
-        <v>0.14</v>
+        <v>0.44</v>
       </c>
       <c r="AR53">
         <v>1.75</v>
@@ -12057,10 +12150,10 @@
         <v>2</v>
       </c>
       <c r="AP54">
-        <v>1.71</v>
+        <v>1.33</v>
       </c>
       <c r="AQ54">
-        <v>1.83</v>
+        <v>1.56</v>
       </c>
       <c r="AR54">
         <v>1.1</v>
@@ -12185,7 +12278,7 @@
         <v>119</v>
       </c>
       <c r="P55" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="Q55">
         <v>5</v>
@@ -12263,10 +12356,10 @@
         <v>2</v>
       </c>
       <c r="AP55">
-        <v>0.88</v>
+        <v>0.8</v>
       </c>
       <c r="AQ55">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="AR55">
         <v>1.32</v>
@@ -12469,10 +12562,10 @@
         <v>2</v>
       </c>
       <c r="AP56">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AQ56">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR56">
         <v>1.83</v>
@@ -12597,7 +12690,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>186</v>
+        <v>202</v>
       </c>
       <c r="Q57">
         <v>3.75</v>
@@ -12675,10 +12768,10 @@
         <v>2.33</v>
       </c>
       <c r="AP57">
-        <v>1.38</v>
+        <v>1.1</v>
       </c>
       <c r="AQ57">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="AR57">
         <v>1.79</v>
@@ -12803,7 +12896,7 @@
         <v>121</v>
       </c>
       <c r="P58" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="Q58">
         <v>2.3</v>
@@ -12884,7 +12977,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ58">
-        <v>1</v>
+        <v>0.78</v>
       </c>
       <c r="AR58">
         <v>1.31</v>
@@ -13009,7 +13102,7 @@
         <v>85</v>
       </c>
       <c r="P59" t="s">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="Q59">
         <v>3.2</v>
@@ -13087,7 +13180,7 @@
         <v>0.88</v>
       </c>
       <c r="AP59">
-        <v>0.57</v>
+        <v>0.89</v>
       </c>
       <c r="AQ59">
         <v>1</v>
@@ -13293,10 +13386,10 @@
         <v>1</v>
       </c>
       <c r="AP60">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AQ60">
-        <v>0.86</v>
+        <v>1.11</v>
       </c>
       <c r="AR60">
         <v>2.02</v>
@@ -13421,7 +13514,7 @@
         <v>123</v>
       </c>
       <c r="P61" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="Q61">
         <v>4</v>
@@ -13499,10 +13592,10 @@
         <v>1.5</v>
       </c>
       <c r="AP61">
-        <v>1.57</v>
+        <v>1.89</v>
       </c>
       <c r="AQ61">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AR61">
         <v>1.39</v>
@@ -13627,7 +13720,7 @@
         <v>124</v>
       </c>
       <c r="P62" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="Q62">
         <v>2.3</v>
@@ -13705,10 +13798,10 @@
         <v>1.67</v>
       </c>
       <c r="AP62">
-        <v>2.43</v>
+        <v>2.1</v>
       </c>
       <c r="AQ62">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR62">
         <v>1.79</v>
@@ -13833,7 +13926,7 @@
         <v>85</v>
       </c>
       <c r="P63" t="s">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="Q63">
         <v>3.2</v>
@@ -13911,10 +14004,10 @@
         <v>1.88</v>
       </c>
       <c r="AP63">
-        <v>0.71</v>
+        <v>1.2</v>
       </c>
       <c r="AQ63">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR63">
         <v>1.54</v>
@@ -14039,7 +14132,7 @@
         <v>125</v>
       </c>
       <c r="P64" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="Q64">
         <v>2.5</v>
@@ -14117,10 +14210,10 @@
         <v>0.33</v>
       </c>
       <c r="AP64">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="AQ64">
-        <v>0.14</v>
+        <v>0.44</v>
       </c>
       <c r="AR64">
         <v>1.63</v>
@@ -14245,7 +14338,7 @@
         <v>126</v>
       </c>
       <c r="P65" t="s">
-        <v>191</v>
+        <v>207</v>
       </c>
       <c r="Q65">
         <v>4</v>
@@ -14323,10 +14416,10 @@
         <v>0.5</v>
       </c>
       <c r="AP65">
-        <v>1.71</v>
+        <v>1.33</v>
       </c>
       <c r="AQ65">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="AR65">
         <v>1.07</v>
@@ -14451,7 +14544,7 @@
         <v>127</v>
       </c>
       <c r="P66" t="s">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="Q66">
         <v>3</v>
@@ -14529,10 +14622,10 @@
         <v>2</v>
       </c>
       <c r="AP66">
-        <v>1.57</v>
+        <v>1.89</v>
       </c>
       <c r="AQ66">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR66">
         <v>1.49</v>
@@ -14735,10 +14828,10 @@
         <v>0.8</v>
       </c>
       <c r="AP67">
-        <v>0.88</v>
+        <v>0.8</v>
       </c>
       <c r="AQ67">
-        <v>1</v>
+        <v>0.78</v>
       </c>
       <c r="AR67">
         <v>1.4</v>
@@ -14863,7 +14956,7 @@
         <v>129</v>
       </c>
       <c r="P68" t="s">
-        <v>193</v>
+        <v>209</v>
       </c>
       <c r="Q68">
         <v>5</v>
@@ -14941,10 +15034,10 @@
         <v>1</v>
       </c>
       <c r="AP68">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AQ68">
-        <v>1.57</v>
+        <v>1.89</v>
       </c>
       <c r="AR68">
         <v>0</v>
@@ -15147,10 +15240,10 @@
         <v>1.75</v>
       </c>
       <c r="AP69">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AQ69">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="AR69">
         <v>1.6</v>
@@ -15353,10 +15446,10 @@
         <v>0.6</v>
       </c>
       <c r="AP70">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="AQ70">
-        <v>0.86</v>
+        <v>1.33</v>
       </c>
       <c r="AR70">
         <v>1.72</v>
@@ -15481,7 +15574,7 @@
         <v>132</v>
       </c>
       <c r="P71" t="s">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="Q71">
         <v>2.63</v>
@@ -15559,10 +15652,10 @@
         <v>0</v>
       </c>
       <c r="AP71">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AQ71">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="AR71">
         <v>1.45</v>
@@ -15765,10 +15858,10 @@
         <v>0.25</v>
       </c>
       <c r="AP72">
-        <v>0.71</v>
+        <v>1.2</v>
       </c>
       <c r="AQ72">
-        <v>0.14</v>
+        <v>0.44</v>
       </c>
       <c r="AR72">
         <v>1.67</v>
@@ -15893,7 +15986,7 @@
         <v>85</v>
       </c>
       <c r="P73" t="s">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="Q73">
         <v>3.6</v>
@@ -15971,10 +16064,10 @@
         <v>1.75</v>
       </c>
       <c r="AP73">
-        <v>1.38</v>
+        <v>1.1</v>
       </c>
       <c r="AQ73">
-        <v>1.83</v>
+        <v>1.56</v>
       </c>
       <c r="AR73">
         <v>1.77</v>
@@ -16099,7 +16192,7 @@
         <v>85</v>
       </c>
       <c r="P74" t="s">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="Q74">
         <v>4.33</v>
@@ -16177,10 +16270,10 @@
         <v>2</v>
       </c>
       <c r="AP74">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AQ74">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AR74">
         <v>1.98</v>
@@ -16305,7 +16398,7 @@
         <v>134</v>
       </c>
       <c r="P75" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="Q75">
         <v>1.91</v>
@@ -16386,7 +16479,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ75">
-        <v>0.86</v>
+        <v>1.11</v>
       </c>
       <c r="AR75">
         <v>1.33</v>
@@ -16511,7 +16604,7 @@
         <v>135</v>
       </c>
       <c r="P76" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="Q76">
         <v>2.63</v>
@@ -16589,10 +16682,10 @@
         <v>1.25</v>
       </c>
       <c r="AP76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ76">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR76">
         <v>0</v>
@@ -16717,7 +16810,7 @@
         <v>85</v>
       </c>
       <c r="P77" t="s">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="Q77">
         <v>4.5</v>
@@ -16795,10 +16888,10 @@
         <v>2.33</v>
       </c>
       <c r="AP77">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AQ77">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="AR77">
         <v>1.89</v>
@@ -17001,10 +17094,10 @@
         <v>0</v>
       </c>
       <c r="AP78">
-        <v>2.43</v>
+        <v>2.1</v>
       </c>
       <c r="AQ78">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="AR78">
         <v>1.79</v>
@@ -17129,7 +17222,7 @@
         <v>137</v>
       </c>
       <c r="P79" t="s">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="Q79">
         <v>3.6</v>
@@ -17207,10 +17300,10 @@
         <v>0.5</v>
       </c>
       <c r="AP79">
-        <v>1.38</v>
+        <v>1.1</v>
       </c>
       <c r="AQ79">
-        <v>0.86</v>
+        <v>1.33</v>
       </c>
       <c r="AR79">
         <v>1.7</v>
@@ -17413,10 +17506,10 @@
         <v>0.2</v>
       </c>
       <c r="AP80">
-        <v>1.57</v>
+        <v>1.89</v>
       </c>
       <c r="AQ80">
-        <v>0.14</v>
+        <v>0.44</v>
       </c>
       <c r="AR80">
         <v>1.42</v>
@@ -17619,10 +17712,10 @@
         <v>1</v>
       </c>
       <c r="AP81">
-        <v>0.57</v>
+        <v>0.89</v>
       </c>
       <c r="AQ81">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR81">
         <v>1.17</v>
@@ -17747,7 +17840,7 @@
         <v>140</v>
       </c>
       <c r="P82" t="s">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="Q82">
         <v>3.75</v>
@@ -17825,10 +17918,10 @@
         <v>1</v>
       </c>
       <c r="AP82">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="AQ82">
-        <v>1.57</v>
+        <v>1.89</v>
       </c>
       <c r="AR82">
         <v>1.65</v>
@@ -17953,7 +18046,7 @@
         <v>85</v>
       </c>
       <c r="P83" t="s">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="Q83">
         <v>7.5</v>
@@ -18031,10 +18124,10 @@
         <v>2.25</v>
       </c>
       <c r="AP83">
-        <v>0.88</v>
+        <v>0.8</v>
       </c>
       <c r="AQ83">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AR83">
         <v>1.35</v>
@@ -18159,7 +18252,7 @@
         <v>141</v>
       </c>
       <c r="P84" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="Q84">
         <v>2.38</v>
@@ -18237,7 +18330,7 @@
         <v>1.11</v>
       </c>
       <c r="AP84">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ84">
         <v>1</v>
@@ -18365,7 +18458,7 @@
         <v>142</v>
       </c>
       <c r="P85" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="Q85">
         <v>3.75</v>
@@ -18443,10 +18536,10 @@
         <v>1.33</v>
       </c>
       <c r="AP85">
-        <v>0.71</v>
+        <v>1.2</v>
       </c>
       <c r="AQ85">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="AR85">
         <v>1.63</v>
@@ -18571,7 +18664,7 @@
         <v>85</v>
       </c>
       <c r="P86" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="Q86">
         <v>4.2</v>
@@ -18649,10 +18742,10 @@
         <v>1.75</v>
       </c>
       <c r="AP86">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AQ86">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="AR86">
         <v>1.42</v>
@@ -18855,10 +18948,10 @@
         <v>0.8</v>
       </c>
       <c r="AP87">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AQ87">
-        <v>0.86</v>
+        <v>1.11</v>
       </c>
       <c r="AR87">
         <v>1.66</v>
@@ -19061,10 +19154,10 @@
         <v>2.5</v>
       </c>
       <c r="AP88">
-        <v>1.71</v>
+        <v>1.33</v>
       </c>
       <c r="AQ88">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="AR88">
         <v>1.04</v>
@@ -19189,7 +19282,7 @@
         <v>143</v>
       </c>
       <c r="P89" t="s">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="Q89">
         <v>2.62</v>
@@ -19267,10 +19360,10 @@
         <v>0</v>
       </c>
       <c r="AP89">
-        <v>1.38</v>
+        <v>1.1</v>
       </c>
       <c r="AQ89">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="AR89">
         <v>1.79</v>
@@ -19395,7 +19488,7 @@
         <v>144</v>
       </c>
       <c r="P90" t="s">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="Q90">
         <v>3.1</v>
@@ -19473,10 +19566,10 @@
         <v>2</v>
       </c>
       <c r="AP90">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AQ90">
-        <v>1.83</v>
+        <v>1.56</v>
       </c>
       <c r="AR90">
         <v>1.82</v>
@@ -19679,10 +19772,10 @@
         <v>1.9</v>
       </c>
       <c r="AP91">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AQ91">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR91">
         <v>1.64</v>
@@ -19807,7 +19900,7 @@
         <v>146</v>
       </c>
       <c r="P92" t="s">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -19885,10 +19978,10 @@
         <v>1.4</v>
       </c>
       <c r="AP92">
-        <v>2.43</v>
+        <v>2.1</v>
       </c>
       <c r="AQ92">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="AR92">
         <v>1.86</v>
@@ -20013,7 +20106,7 @@
         <v>147</v>
       </c>
       <c r="P93" t="s">
-        <v>205</v>
+        <v>221</v>
       </c>
       <c r="Q93">
         <v>2.62</v>
@@ -20094,7 +20187,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ93">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="AR93">
         <v>1.35</v>
@@ -20219,7 +20312,7 @@
         <v>148</v>
       </c>
       <c r="P94" t="s">
-        <v>206</v>
+        <v>222</v>
       </c>
       <c r="Q94">
         <v>2.4</v>
@@ -20297,10 +20390,10 @@
         <v>0.17</v>
       </c>
       <c r="AP94">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ94">
-        <v>0.14</v>
+        <v>0.44</v>
       </c>
       <c r="AR94">
         <v>1.56</v>
@@ -20425,7 +20518,7 @@
         <v>149</v>
       </c>
       <c r="P95" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="Q95">
         <v>3.1</v>
@@ -20503,10 +20596,10 @@
         <v>0.67</v>
       </c>
       <c r="AP95">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AQ95">
-        <v>1</v>
+        <v>0.78</v>
       </c>
       <c r="AR95">
         <v>1.52</v>
@@ -20709,10 +20802,10 @@
         <v>1</v>
       </c>
       <c r="AP96">
-        <v>0.88</v>
+        <v>0.8</v>
       </c>
       <c r="AQ96">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR96">
         <v>1.3</v>
@@ -20795,7 +20888,7 @@
         <v>96</v>
       </c>
       <c r="B97">
-        <v>7813947</v>
+        <v>7813916</v>
       </c>
       <c r="C97" t="s">
         <v>68</v>
@@ -20804,109 +20897,109 @@
         <v>69</v>
       </c>
       <c r="E97" s="2">
-        <v>45843.29166666666</v>
+        <v>45809.1875</v>
       </c>
       <c r="F97">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G97" t="s">
         <v>81</v>
       </c>
       <c r="H97" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I97">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J97">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K97">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L97">
         <v>2</v>
       </c>
       <c r="M97">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N97">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O97" t="s">
         <v>151</v>
       </c>
       <c r="P97" t="s">
-        <v>208</v>
+        <v>85</v>
       </c>
       <c r="Q97">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="R97">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S97">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="T97">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="U97">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="V97">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="W97">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="X97">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="Y97">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Z97">
-        <v>2.95</v>
+        <v>2.11</v>
       </c>
       <c r="AA97">
-        <v>3.31</v>
+        <v>3.24</v>
       </c>
       <c r="AB97">
-        <v>2.09</v>
+        <v>3.25</v>
       </c>
       <c r="AC97">
         <v>1.01</v>
       </c>
       <c r="AD97">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="AE97">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AF97">
-        <v>4.05</v>
+        <v>2.83</v>
       </c>
       <c r="AG97">
-        <v>1.82</v>
+        <v>2.17</v>
       </c>
       <c r="AH97">
-        <v>1.88</v>
+        <v>1.62</v>
       </c>
       <c r="AI97">
+        <v>1.85</v>
+      </c>
+      <c r="AJ97">
+        <v>1.85</v>
+      </c>
+      <c r="AK97">
+        <v>1.3</v>
+      </c>
+      <c r="AL97">
+        <v>1.36</v>
+      </c>
+      <c r="AM97">
         <v>1.65</v>
-      </c>
-      <c r="AJ97">
-        <v>2.15</v>
-      </c>
-      <c r="AK97">
-        <v>1.62</v>
-      </c>
-      <c r="AL97">
-        <v>1.3</v>
-      </c>
-      <c r="AM97">
-        <v>1.36</v>
       </c>
       <c r="AN97">
         <v>1.5</v>
@@ -20915,85 +21008,85 @@
         <v>1.33</v>
       </c>
       <c r="AP97">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AQ97">
-        <v>1.57</v>
+        <v>1.13</v>
       </c>
       <c r="AR97">
         <v>1.82</v>
       </c>
       <c r="AS97">
-        <v>1.71</v>
+        <v>1.31</v>
       </c>
       <c r="AT97">
-        <v>3.53</v>
+        <v>3.13</v>
       </c>
       <c r="AU97">
+        <v>5</v>
+      </c>
+      <c r="AV97">
+        <v>3</v>
+      </c>
+      <c r="AW97">
+        <v>5</v>
+      </c>
+      <c r="AX97">
+        <v>6</v>
+      </c>
+      <c r="AY97">
+        <v>10</v>
+      </c>
+      <c r="AZ97">
         <v>9</v>
       </c>
-      <c r="AV97">
-        <v>9</v>
-      </c>
-      <c r="AW97">
-        <v>11</v>
-      </c>
-      <c r="AX97">
-        <v>12</v>
-      </c>
-      <c r="AY97">
-        <v>20</v>
-      </c>
-      <c r="AZ97">
-        <v>21</v>
-      </c>
       <c r="BA97">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="BB97">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BC97">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="BD97">
-        <v>2.31</v>
+        <v>1.69</v>
       </c>
       <c r="BE97">
-        <v>6.59</v>
+        <v>7.6</v>
       </c>
       <c r="BF97">
-        <v>2.01</v>
+        <v>2.53</v>
       </c>
       <c r="BG97">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="BH97">
-        <v>2.19</v>
+        <v>2.44</v>
       </c>
       <c r="BI97">
-        <v>2.01</v>
+        <v>1.92</v>
       </c>
       <c r="BJ97">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="BK97">
-        <v>2.66</v>
+        <v>2.42</v>
       </c>
       <c r="BL97">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="BM97">
-        <v>3.79</v>
+        <v>3.34</v>
       </c>
       <c r="BN97">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="BO97">
-        <v>5.82</v>
+        <v>4.25</v>
       </c>
       <c r="BP97">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="98" spans="1:68">
@@ -21001,7 +21094,7 @@
         <v>97</v>
       </c>
       <c r="B98">
-        <v>7813948</v>
+        <v>7813917</v>
       </c>
       <c r="C98" t="s">
         <v>68</v>
@@ -21010,82 +21103,82 @@
         <v>69</v>
       </c>
       <c r="E98" s="2">
-        <v>45843.29166666666</v>
+        <v>45809.29166666666</v>
       </c>
       <c r="F98">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G98" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="H98" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="I98">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J98">
         <v>1</v>
       </c>
       <c r="K98">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L98">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M98">
         <v>1</v>
       </c>
       <c r="N98">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O98" t="s">
         <v>152</v>
       </c>
       <c r="P98" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="Q98">
-        <v>4.33</v>
+        <v>2.3</v>
       </c>
       <c r="R98">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="S98">
-        <v>2.45</v>
+        <v>4.4</v>
       </c>
       <c r="T98">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="U98">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="V98">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="W98">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="X98">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="Y98">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z98">
-        <v>3.71</v>
+        <v>1.69</v>
       </c>
       <c r="AA98">
-        <v>3.21</v>
+        <v>3.62</v>
       </c>
       <c r="AB98">
-        <v>1.86</v>
+        <v>3.95</v>
       </c>
       <c r="AC98">
         <v>1</v>
       </c>
       <c r="AD98">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="AE98">
         <v>1.24</v>
@@ -21094,112 +21187,112 @@
         <v>3.34</v>
       </c>
       <c r="AG98">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AH98">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="AI98">
+        <v>1.73</v>
+      </c>
+      <c r="AJ98">
+        <v>2.05</v>
+      </c>
+      <c r="AK98">
+        <v>1.2</v>
+      </c>
+      <c r="AL98">
+        <v>1.29</v>
+      </c>
+      <c r="AM98">
+        <v>2</v>
+      </c>
+      <c r="AN98">
+        <v>2.43</v>
+      </c>
+      <c r="AO98">
         <v>1.83</v>
       </c>
-      <c r="AJ98">
-        <v>1.91</v>
-      </c>
-      <c r="AK98">
-        <v>1.95</v>
-      </c>
-      <c r="AL98">
-        <v>1.3</v>
-      </c>
-      <c r="AM98">
-        <v>1.2</v>
-      </c>
-      <c r="AN98">
-        <v>3</v>
-      </c>
-      <c r="AO98">
-        <v>2.4</v>
-      </c>
       <c r="AP98">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="AQ98">
-        <v>2</v>
+        <v>1.56</v>
       </c>
       <c r="AR98">
-        <v>1.56</v>
+        <v>1.85</v>
       </c>
       <c r="AS98">
-        <v>1.29</v>
+        <v>1.64</v>
       </c>
       <c r="AT98">
-        <v>2.85</v>
+        <v>3.49</v>
       </c>
       <c r="AU98">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AV98">
         <v>4</v>
       </c>
       <c r="AW98">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AX98">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY98">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AZ98">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA98">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB98">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC98">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BD98">
-        <v>3.16</v>
+        <v>1.63</v>
       </c>
       <c r="BE98">
-        <v>7.06</v>
+        <v>8.1</v>
       </c>
       <c r="BF98">
-        <v>1.62</v>
+        <v>2.62</v>
       </c>
       <c r="BG98">
-        <v>1.56</v>
+        <v>1.32</v>
       </c>
       <c r="BH98">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="BI98">
-        <v>1.96</v>
+        <v>1.66</v>
       </c>
       <c r="BJ98">
-        <v>1.75</v>
+        <v>2.18</v>
       </c>
       <c r="BK98">
-        <v>2.57</v>
+        <v>2.1</v>
       </c>
       <c r="BL98">
-        <v>1.42</v>
+        <v>1.71</v>
       </c>
       <c r="BM98">
-        <v>3.62</v>
+        <v>2.69</v>
       </c>
       <c r="BN98">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="BO98">
-        <v>5.5</v>
+        <v>3.75</v>
       </c>
       <c r="BP98">
-        <v>1.06</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="99" spans="1:68">
@@ -21207,7 +21300,7 @@
         <v>98</v>
       </c>
       <c r="B99">
-        <v>7813949</v>
+        <v>7813918</v>
       </c>
       <c r="C99" t="s">
         <v>68</v>
@@ -21216,76 +21309,76 @@
         <v>69</v>
       </c>
       <c r="E99" s="2">
-        <v>45843.29166666666</v>
+        <v>45809.29166666666</v>
       </c>
       <c r="F99">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G99" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="H99" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="I99">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J99">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K99">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L99">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M99">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N99">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O99" t="s">
         <v>153</v>
       </c>
       <c r="P99" t="s">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="Q99">
-        <v>4.2</v>
+        <v>6.5</v>
       </c>
       <c r="R99">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="S99">
-        <v>2.45</v>
+        <v>1.85</v>
       </c>
       <c r="T99">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="U99">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="V99">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="W99">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="X99">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y99">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z99">
-        <v>3.89</v>
+        <v>6.9</v>
       </c>
       <c r="AA99">
-        <v>3.57</v>
+        <v>4.4</v>
       </c>
       <c r="AB99">
-        <v>1.72</v>
+        <v>1.34</v>
       </c>
       <c r="AC99">
         <v>1.01</v>
@@ -21294,118 +21387,118 @@
         <v>11</v>
       </c>
       <c r="AE99">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AF99">
-        <v>3.5</v>
+        <v>4.15</v>
       </c>
       <c r="AG99">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AH99">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AI99">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AJ99">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AK99">
-        <v>1.85</v>
+        <v>3</v>
       </c>
       <c r="AL99">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AM99">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="AN99">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AO99">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AP99">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AQ99">
-        <v>1.67</v>
+        <v>1.89</v>
       </c>
       <c r="AR99">
-        <v>1.52</v>
+        <v>1.19</v>
       </c>
       <c r="AS99">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AT99">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="AU99">
         <v>6</v>
       </c>
       <c r="AV99">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AW99">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AX99">
+        <v>4</v>
+      </c>
+      <c r="AY99">
         <v>8</v>
       </c>
-      <c r="AY99">
-        <v>13</v>
-      </c>
       <c r="AZ99">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA99">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BB99">
         <v>1</v>
       </c>
       <c r="BC99">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BD99">
-        <v>3.07</v>
+        <v>2.83</v>
       </c>
       <c r="BE99">
-        <v>6.9</v>
+        <v>8.1</v>
       </c>
       <c r="BF99">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="BG99">
-        <v>1.64</v>
+        <v>1.34</v>
       </c>
       <c r="BH99">
-        <v>2.12</v>
+        <v>2.78</v>
       </c>
       <c r="BI99">
-        <v>2.08</v>
+        <v>1.71</v>
       </c>
       <c r="BJ99">
-        <v>1.66</v>
+        <v>2.09</v>
       </c>
       <c r="BK99">
+        <v>2.15</v>
+      </c>
+      <c r="BL99">
+        <v>1.68</v>
+      </c>
+      <c r="BM99">
         <v>2.78</v>
       </c>
-      <c r="BL99">
-        <v>1.36</v>
-      </c>
-      <c r="BM99">
-        <v>4.01</v>
-      </c>
       <c r="BN99">
-        <v>1.16</v>
+        <v>1.34</v>
       </c>
       <c r="BO99">
-        <v>6.25</v>
+        <v>3.62</v>
       </c>
       <c r="BP99">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="100" spans="1:68">
@@ -21413,7 +21506,7 @@
         <v>99</v>
       </c>
       <c r="B100">
-        <v>7813950</v>
+        <v>7813920</v>
       </c>
       <c r="C100" t="s">
         <v>68</v>
@@ -21422,16 +21515,16 @@
         <v>69</v>
       </c>
       <c r="E100" s="2">
-        <v>45843.29166666666</v>
+        <v>45814.29166666666</v>
       </c>
       <c r="F100">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G100" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="H100" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="I100">
         <v>1</v>
@@ -21446,171 +21539,6557 @@
         <v>1</v>
       </c>
       <c r="M100">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N100">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O100" t="s">
         <v>154</v>
       </c>
       <c r="P100" t="s">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="Q100">
-        <v>2.8</v>
+        <v>4.33</v>
       </c>
       <c r="R100">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S100">
-        <v>3.6</v>
+        <v>2.35</v>
       </c>
       <c r="T100">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="U100">
         <v>2.8</v>
       </c>
       <c r="V100">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="W100">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="X100">
-        <v>7.5</v>
+        <v>6.4</v>
       </c>
       <c r="Y100">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Z100">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="AA100">
-        <v>3.17</v>
+        <v>3.52</v>
       </c>
       <c r="AB100">
-        <v>2.86</v>
+        <v>1.7</v>
       </c>
       <c r="AC100">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AD100">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="AE100">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AF100">
-        <v>3.08</v>
+        <v>3.35</v>
       </c>
       <c r="AG100">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AH100">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AI100">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AJ100">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AK100">
-        <v>1.36</v>
+        <v>2</v>
       </c>
       <c r="AL100">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AM100">
-        <v>1.6</v>
+        <v>1.17</v>
       </c>
       <c r="AN100">
-        <v>1.43</v>
+        <v>1.71</v>
       </c>
       <c r="AO100">
-        <v>0.83</v>
+        <v>1.33</v>
       </c>
       <c r="AP100">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ100">
-        <v>0.86</v>
+        <v>1.89</v>
       </c>
       <c r="AR100">
-        <v>1.78</v>
+        <v>1.06</v>
       </c>
       <c r="AS100">
-        <v>1.15</v>
+        <v>1.71</v>
       </c>
       <c r="AT100">
-        <v>2.93</v>
+        <v>2.77</v>
       </c>
       <c r="AU100">
+        <v>5</v>
+      </c>
+      <c r="AV100">
+        <v>7</v>
+      </c>
+      <c r="AW100">
+        <v>5</v>
+      </c>
+      <c r="AX100">
         <v>6</v>
-      </c>
-      <c r="AV100">
-        <v>6</v>
-      </c>
-      <c r="AW100">
-        <v>4</v>
-      </c>
-      <c r="AX100">
-        <v>1</v>
       </c>
       <c r="AY100">
         <v>10</v>
       </c>
       <c r="AZ100">
+        <v>13</v>
+      </c>
+      <c r="BA100">
+        <v>4</v>
+      </c>
+      <c r="BB100">
+        <v>1</v>
+      </c>
+      <c r="BC100">
+        <v>5</v>
+      </c>
+      <c r="BD100">
+        <v>3.12</v>
+      </c>
+      <c r="BE100">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF100">
+        <v>1.48</v>
+      </c>
+      <c r="BG100">
+        <v>1.34</v>
+      </c>
+      <c r="BH100">
+        <v>2.78</v>
+      </c>
+      <c r="BI100">
+        <v>1.65</v>
+      </c>
+      <c r="BJ100">
+        <v>2.05</v>
+      </c>
+      <c r="BK100">
+        <v>2.08</v>
+      </c>
+      <c r="BL100">
+        <v>1.6</v>
+      </c>
+      <c r="BM100">
+        <v>2.78</v>
+      </c>
+      <c r="BN100">
+        <v>1.34</v>
+      </c>
+      <c r="BO100">
+        <v>3.55</v>
+      </c>
+      <c r="BP100">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="101" spans="1:68">
+      <c r="A101" s="1">
+        <v>100</v>
+      </c>
+      <c r="B101">
+        <v>7813919</v>
+      </c>
+      <c r="C101" t="s">
+        <v>68</v>
+      </c>
+      <c r="D101" t="s">
+        <v>69</v>
+      </c>
+      <c r="E101" s="2">
+        <v>45814.29166666666</v>
+      </c>
+      <c r="F101">
+        <v>15</v>
+      </c>
+      <c r="G101" t="s">
+        <v>82</v>
+      </c>
+      <c r="H101" t="s">
+        <v>81</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>2</v>
+      </c>
+      <c r="K101">
+        <v>2</v>
+      </c>
+      <c r="L101">
+        <v>0</v>
+      </c>
+      <c r="M101">
+        <v>2</v>
+      </c>
+      <c r="N101">
+        <v>2</v>
+      </c>
+      <c r="O101" t="s">
+        <v>85</v>
+      </c>
+      <c r="P101" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q101">
+        <v>3.88</v>
+      </c>
+      <c r="R101">
+        <v>2.04</v>
+      </c>
+      <c r="S101">
+        <v>2.7</v>
+      </c>
+      <c r="T101">
+        <v>1.4</v>
+      </c>
+      <c r="U101">
+        <v>2.72</v>
+      </c>
+      <c r="V101">
+        <v>2.93</v>
+      </c>
+      <c r="W101">
+        <v>1.35</v>
+      </c>
+      <c r="X101">
+        <v>7.3</v>
+      </c>
+      <c r="Y101">
+        <v>1.03</v>
+      </c>
+      <c r="Z101">
+        <v>3.24</v>
+      </c>
+      <c r="AA101">
+        <v>3.28</v>
+      </c>
+      <c r="AB101">
+        <v>2.1</v>
+      </c>
+      <c r="AC101">
+        <v>1.01</v>
+      </c>
+      <c r="AD101">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AE101">
+        <v>1.29</v>
+      </c>
+      <c r="AF101">
+        <v>3.04</v>
+      </c>
+      <c r="AG101">
+        <v>2</v>
+      </c>
+      <c r="AH101">
+        <v>1.73</v>
+      </c>
+      <c r="AI101">
+        <v>1.79</v>
+      </c>
+      <c r="AJ101">
+        <v>1.87</v>
+      </c>
+      <c r="AK101">
+        <v>1.64</v>
+      </c>
+      <c r="AL101">
+        <v>1.28</v>
+      </c>
+      <c r="AM101">
+        <v>1.28</v>
+      </c>
+      <c r="AN101">
+        <v>0.5</v>
+      </c>
+      <c r="AO101">
+        <v>0.86</v>
+      </c>
+      <c r="AP101">
+        <v>0.75</v>
+      </c>
+      <c r="AQ101">
+        <v>1.33</v>
+      </c>
+      <c r="AR101">
+        <v>1.52</v>
+      </c>
+      <c r="AS101">
+        <v>1.4</v>
+      </c>
+      <c r="AT101">
+        <v>2.92</v>
+      </c>
+      <c r="AU101">
+        <v>0</v>
+      </c>
+      <c r="AV101">
+        <v>3</v>
+      </c>
+      <c r="AW101">
         <v>7</v>
       </c>
-      <c r="BA100">
-        <v>2</v>
-      </c>
-      <c r="BB100">
-        <v>2</v>
-      </c>
-      <c r="BC100">
+      <c r="AX101">
+        <v>5</v>
+      </c>
+      <c r="AY101">
+        <v>7</v>
+      </c>
+      <c r="AZ101">
+        <v>8</v>
+      </c>
+      <c r="BA101">
+        <v>6</v>
+      </c>
+      <c r="BB101">
+        <v>10</v>
+      </c>
+      <c r="BC101">
+        <v>16</v>
+      </c>
+      <c r="BD101">
+        <v>2.6</v>
+      </c>
+      <c r="BE101">
+        <v>6.05</v>
+      </c>
+      <c r="BF101">
+        <v>1.76</v>
+      </c>
+      <c r="BG101">
+        <v>1.46</v>
+      </c>
+      <c r="BH101">
+        <v>2.38</v>
+      </c>
+      <c r="BI101">
+        <v>1.85</v>
+      </c>
+      <c r="BJ101">
+        <v>1.81</v>
+      </c>
+      <c r="BK101">
+        <v>2.42</v>
+      </c>
+      <c r="BL101">
+        <v>1.44</v>
+      </c>
+      <c r="BM101">
+        <v>3.34</v>
+      </c>
+      <c r="BN101">
+        <v>1.24</v>
+      </c>
+      <c r="BO101">
+        <v>4.25</v>
+      </c>
+      <c r="BP101">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="102" spans="1:68">
+      <c r="A102" s="1">
+        <v>101</v>
+      </c>
+      <c r="B102">
+        <v>7813923</v>
+      </c>
+      <c r="C102" t="s">
+        <v>68</v>
+      </c>
+      <c r="D102" t="s">
+        <v>69</v>
+      </c>
+      <c r="E102" s="2">
+        <v>45815.29166666666</v>
+      </c>
+      <c r="F102">
+        <v>15</v>
+      </c>
+      <c r="G102" t="s">
+        <v>80</v>
+      </c>
+      <c r="H102" t="s">
+        <v>77</v>
+      </c>
+      <c r="I102">
+        <v>0</v>
+      </c>
+      <c r="J102">
+        <v>1</v>
+      </c>
+      <c r="K102">
+        <v>1</v>
+      </c>
+      <c r="L102">
+        <v>0</v>
+      </c>
+      <c r="M102">
+        <v>1</v>
+      </c>
+      <c r="N102">
+        <v>1</v>
+      </c>
+      <c r="O102" t="s">
+        <v>85</v>
+      </c>
+      <c r="P102" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q102">
+        <v>2.79</v>
+      </c>
+      <c r="R102">
+        <v>2.12</v>
+      </c>
+      <c r="S102">
+        <v>3.48</v>
+      </c>
+      <c r="T102">
+        <v>1.35</v>
+      </c>
+      <c r="U102">
+        <v>2.93</v>
+      </c>
+      <c r="V102">
+        <v>2.69</v>
+      </c>
+      <c r="W102">
+        <v>1.41</v>
+      </c>
+      <c r="X102">
+        <v>6.4</v>
+      </c>
+      <c r="Y102">
+        <v>1.05</v>
+      </c>
+      <c r="Z102">
+        <v>2.16</v>
+      </c>
+      <c r="AA102">
+        <v>3.38</v>
+      </c>
+      <c r="AB102">
+        <v>2.76</v>
+      </c>
+      <c r="AC102">
+        <v>1</v>
+      </c>
+      <c r="AD102">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AE102">
+        <v>1.22</v>
+      </c>
+      <c r="AF102">
+        <v>3.48</v>
+      </c>
+      <c r="AG102">
+        <v>1.82</v>
+      </c>
+      <c r="AH102">
+        <v>1.88</v>
+      </c>
+      <c r="AI102">
+        <v>1.65</v>
+      </c>
+      <c r="AJ102">
+        <v>2.05</v>
+      </c>
+      <c r="AK102">
+        <v>1.35</v>
+      </c>
+      <c r="AL102">
+        <v>1.26</v>
+      </c>
+      <c r="AM102">
+        <v>1.57</v>
+      </c>
+      <c r="AN102">
+        <v>1.43</v>
+      </c>
+      <c r="AO102">
+        <v>0.14</v>
+      </c>
+      <c r="AP102">
+        <v>1.1</v>
+      </c>
+      <c r="AQ102">
+        <v>0.44</v>
+      </c>
+      <c r="AR102">
+        <v>1.78</v>
+      </c>
+      <c r="AS102">
+        <v>1.09</v>
+      </c>
+      <c r="AT102">
+        <v>2.87</v>
+      </c>
+      <c r="AU102">
+        <v>6</v>
+      </c>
+      <c r="AV102">
         <v>4</v>
       </c>
-      <c r="BD100">
+      <c r="AW102">
+        <v>1</v>
+      </c>
+      <c r="AX102">
+        <v>2</v>
+      </c>
+      <c r="AY102">
+        <v>7</v>
+      </c>
+      <c r="AZ102">
+        <v>6</v>
+      </c>
+      <c r="BA102">
+        <v>4</v>
+      </c>
+      <c r="BB102">
+        <v>3</v>
+      </c>
+      <c r="BC102">
+        <v>7</v>
+      </c>
+      <c r="BD102">
+        <v>2</v>
+      </c>
+      <c r="BE102">
+        <v>6.05</v>
+      </c>
+      <c r="BF102">
+        <v>2.21</v>
+      </c>
+      <c r="BG102">
+        <v>1.37</v>
+      </c>
+      <c r="BH102">
+        <v>2.66</v>
+      </c>
+      <c r="BI102">
+        <v>1.7</v>
+      </c>
+      <c r="BJ102">
+        <v>1.98</v>
+      </c>
+      <c r="BK102">
+        <v>2.15</v>
+      </c>
+      <c r="BL102">
+        <v>1.56</v>
+      </c>
+      <c r="BM102">
+        <v>2.92</v>
+      </c>
+      <c r="BN102">
+        <v>1.31</v>
+      </c>
+      <c r="BO102">
+        <v>3.48</v>
+      </c>
+      <c r="BP102">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="103" spans="1:68">
+      <c r="A103" s="1">
+        <v>102</v>
+      </c>
+      <c r="B103">
+        <v>7813921</v>
+      </c>
+      <c r="C103" t="s">
+        <v>68</v>
+      </c>
+      <c r="D103" t="s">
+        <v>69</v>
+      </c>
+      <c r="E103" s="2">
+        <v>45815.29166666666</v>
+      </c>
+      <c r="F103">
+        <v>15</v>
+      </c>
+      <c r="G103" t="s">
+        <v>72</v>
+      </c>
+      <c r="H103" t="s">
+        <v>73</v>
+      </c>
+      <c r="I103">
+        <v>0</v>
+      </c>
+      <c r="J103">
+        <v>0</v>
+      </c>
+      <c r="K103">
+        <v>0</v>
+      </c>
+      <c r="L103">
+        <v>0</v>
+      </c>
+      <c r="M103">
+        <v>2</v>
+      </c>
+      <c r="N103">
+        <v>2</v>
+      </c>
+      <c r="O103" t="s">
+        <v>85</v>
+      </c>
+      <c r="P103" t="s">
+        <v>228</v>
+      </c>
+      <c r="Q103">
+        <v>2.14</v>
+      </c>
+      <c r="R103">
+        <v>2.16</v>
+      </c>
+      <c r="S103">
+        <v>5.35</v>
+      </c>
+      <c r="T103">
+        <v>1.37</v>
+      </c>
+      <c r="U103">
+        <v>2.84</v>
+      </c>
+      <c r="V103">
+        <v>2.8</v>
+      </c>
+      <c r="W103">
+        <v>1.38</v>
+      </c>
+      <c r="X103">
+        <v>6.85</v>
+      </c>
+      <c r="Y103">
+        <v>1.04</v>
+      </c>
+      <c r="Z103">
+        <v>1.55</v>
+      </c>
+      <c r="AA103">
+        <v>3.72</v>
+      </c>
+      <c r="AB103">
+        <v>4.8</v>
+      </c>
+      <c r="AC103">
+        <v>1</v>
+      </c>
+      <c r="AD103">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE103">
+        <v>1.26</v>
+      </c>
+      <c r="AF103">
+        <v>3.22</v>
+      </c>
+      <c r="AG103">
+        <v>1.9</v>
+      </c>
+      <c r="AH103">
+        <v>1.8</v>
+      </c>
+      <c r="AI103">
+        <v>1.9</v>
+      </c>
+      <c r="AJ103">
+        <v>1.77</v>
+      </c>
+      <c r="AK103">
+        <v>1.11</v>
+      </c>
+      <c r="AL103">
+        <v>1.22</v>
+      </c>
+      <c r="AM103">
+        <v>2.22</v>
+      </c>
+      <c r="AN103">
+        <v>1.38</v>
+      </c>
+      <c r="AO103">
+        <v>0.83</v>
+      </c>
+      <c r="AP103">
+        <v>1.2</v>
+      </c>
+      <c r="AQ103">
+        <v>1.11</v>
+      </c>
+      <c r="AR103">
+        <v>1.65</v>
+      </c>
+      <c r="AS103">
+        <v>1.15</v>
+      </c>
+      <c r="AT103">
+        <v>2.8</v>
+      </c>
+      <c r="AU103">
+        <v>4</v>
+      </c>
+      <c r="AV103">
+        <v>3</v>
+      </c>
+      <c r="AW103">
+        <v>9</v>
+      </c>
+      <c r="AX103">
+        <v>0</v>
+      </c>
+      <c r="AY103">
+        <v>13</v>
+      </c>
+      <c r="AZ103">
+        <v>3</v>
+      </c>
+      <c r="BA103">
+        <v>9</v>
+      </c>
+      <c r="BB103">
+        <v>1</v>
+      </c>
+      <c r="BC103">
+        <v>10</v>
+      </c>
+      <c r="BD103">
+        <v>1.34</v>
+      </c>
+      <c r="BE103">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BF103">
+        <v>3.9</v>
+      </c>
+      <c r="BG103">
+        <v>1.48</v>
+      </c>
+      <c r="BH103">
+        <v>2.33</v>
+      </c>
+      <c r="BI103">
+        <v>1.87</v>
+      </c>
+      <c r="BJ103">
+        <v>1.79</v>
+      </c>
+      <c r="BK103">
+        <v>2.46</v>
+      </c>
+      <c r="BL103">
+        <v>1.43</v>
+      </c>
+      <c r="BM103">
+        <v>3.42</v>
+      </c>
+      <c r="BN103">
+        <v>1.23</v>
+      </c>
+      <c r="BO103">
+        <v>4.9</v>
+      </c>
+      <c r="BP103">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="104" spans="1:68">
+      <c r="A104" s="1">
+        <v>103</v>
+      </c>
+      <c r="B104">
+        <v>7813922</v>
+      </c>
+      <c r="C104" t="s">
+        <v>68</v>
+      </c>
+      <c r="D104" t="s">
+        <v>69</v>
+      </c>
+      <c r="E104" s="2">
+        <v>45815.29166666666</v>
+      </c>
+      <c r="F104">
+        <v>15</v>
+      </c>
+      <c r="G104" t="s">
+        <v>83</v>
+      </c>
+      <c r="H104" t="s">
+        <v>75</v>
+      </c>
+      <c r="I104">
+        <v>1</v>
+      </c>
+      <c r="J104">
+        <v>0</v>
+      </c>
+      <c r="K104">
+        <v>1</v>
+      </c>
+      <c r="L104">
+        <v>1</v>
+      </c>
+      <c r="M104">
+        <v>1</v>
+      </c>
+      <c r="N104">
+        <v>2</v>
+      </c>
+      <c r="O104" t="s">
+        <v>150</v>
+      </c>
+      <c r="P104" t="s">
+        <v>229</v>
+      </c>
+      <c r="Q104">
+        <v>3.4</v>
+      </c>
+      <c r="R104">
+        <v>2.2</v>
+      </c>
+      <c r="S104">
+        <v>3</v>
+      </c>
+      <c r="T104">
+        <v>1.36</v>
+      </c>
+      <c r="U104">
+        <v>3</v>
+      </c>
+      <c r="V104">
+        <v>2.63</v>
+      </c>
+      <c r="W104">
+        <v>1.44</v>
+      </c>
+      <c r="X104">
+        <v>7</v>
+      </c>
+      <c r="Y104">
+        <v>1.1</v>
+      </c>
+      <c r="Z104">
+        <v>2.63</v>
+      </c>
+      <c r="AA104">
+        <v>3.29</v>
+      </c>
+      <c r="AB104">
+        <v>2.3</v>
+      </c>
+      <c r="AC104">
+        <v>1.05</v>
+      </c>
+      <c r="AD104">
+        <v>8.5</v>
+      </c>
+      <c r="AE104">
+        <v>1.25</v>
+      </c>
+      <c r="AF104">
+        <v>3.7</v>
+      </c>
+      <c r="AG104">
+        <v>1.8</v>
+      </c>
+      <c r="AH104">
+        <v>1.9</v>
+      </c>
+      <c r="AI104">
+        <v>1.67</v>
+      </c>
+      <c r="AJ104">
+        <v>2.1</v>
+      </c>
+      <c r="AK104">
+        <v>1.55</v>
+      </c>
+      <c r="AL104">
+        <v>1.29</v>
+      </c>
+      <c r="AM104">
+        <v>1.42</v>
+      </c>
+      <c r="AN104">
+        <v>3</v>
+      </c>
+      <c r="AO104">
+        <v>2</v>
+      </c>
+      <c r="AP104">
+        <v>2</v>
+      </c>
+      <c r="AQ104">
+        <v>1.2</v>
+      </c>
+      <c r="AR104">
+        <v>1.56</v>
+      </c>
+      <c r="AS104">
+        <v>1.18</v>
+      </c>
+      <c r="AT104">
+        <v>2.74</v>
+      </c>
+      <c r="AU104">
+        <v>4</v>
+      </c>
+      <c r="AV104">
+        <v>4</v>
+      </c>
+      <c r="AW104">
+        <v>3</v>
+      </c>
+      <c r="AX104">
+        <v>4</v>
+      </c>
+      <c r="AY104">
+        <v>7</v>
+      </c>
+      <c r="AZ104">
+        <v>8</v>
+      </c>
+      <c r="BA104">
+        <v>4</v>
+      </c>
+      <c r="BB104">
+        <v>8</v>
+      </c>
+      <c r="BC104">
+        <v>12</v>
+      </c>
+      <c r="BD104">
+        <v>2.05</v>
+      </c>
+      <c r="BE104">
+        <v>6</v>
+      </c>
+      <c r="BF104">
+        <v>2.16</v>
+      </c>
+      <c r="BG104">
+        <v>1.44</v>
+      </c>
+      <c r="BH104">
+        <v>2.43</v>
+      </c>
+      <c r="BI104">
+        <v>1.91</v>
+      </c>
+      <c r="BJ104">
+        <v>1.8</v>
+      </c>
+      <c r="BK104">
+        <v>2.35</v>
+      </c>
+      <c r="BL104">
+        <v>1.47</v>
+      </c>
+      <c r="BM104">
+        <v>3.2</v>
+      </c>
+      <c r="BN104">
+        <v>1.26</v>
+      </c>
+      <c r="BO104">
+        <v>4.2</v>
+      </c>
+      <c r="BP104">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="105" spans="1:68">
+      <c r="A105" s="1">
+        <v>104</v>
+      </c>
+      <c r="B105">
+        <v>7813924</v>
+      </c>
+      <c r="C105" t="s">
+        <v>68</v>
+      </c>
+      <c r="D105" t="s">
+        <v>69</v>
+      </c>
+      <c r="E105" s="2">
+        <v>45816.29166666666</v>
+      </c>
+      <c r="F105">
+        <v>15</v>
+      </c>
+      <c r="G105" t="s">
+        <v>70</v>
+      </c>
+      <c r="H105" t="s">
+        <v>76</v>
+      </c>
+      <c r="I105">
+        <v>0</v>
+      </c>
+      <c r="J105">
+        <v>0</v>
+      </c>
+      <c r="K105">
+        <v>0</v>
+      </c>
+      <c r="L105">
+        <v>1</v>
+      </c>
+      <c r="M105">
+        <v>0</v>
+      </c>
+      <c r="N105">
+        <v>1</v>
+      </c>
+      <c r="O105" t="s">
+        <v>155</v>
+      </c>
+      <c r="P105" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q105">
+        <v>2.25</v>
+      </c>
+      <c r="R105">
+        <v>2.2</v>
+      </c>
+      <c r="S105">
+        <v>5.5</v>
+      </c>
+      <c r="T105">
+        <v>1.4</v>
+      </c>
+      <c r="U105">
+        <v>2.75</v>
+      </c>
+      <c r="V105">
+        <v>3</v>
+      </c>
+      <c r="W105">
+        <v>1.36</v>
+      </c>
+      <c r="X105">
+        <v>8</v>
+      </c>
+      <c r="Y105">
+        <v>1.08</v>
+      </c>
+      <c r="Z105">
+        <v>1.62</v>
+      </c>
+      <c r="AA105">
+        <v>3.56</v>
+      </c>
+      <c r="AB105">
+        <v>4.6</v>
+      </c>
+      <c r="AC105">
+        <v>1</v>
+      </c>
+      <c r="AD105">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AE105">
+        <v>1.26</v>
+      </c>
+      <c r="AF105">
+        <v>3.22</v>
+      </c>
+      <c r="AG105">
+        <v>1.94</v>
+      </c>
+      <c r="AH105">
+        <v>1.76</v>
+      </c>
+      <c r="AI105">
+        <v>2</v>
+      </c>
+      <c r="AJ105">
+        <v>1.73</v>
+      </c>
+      <c r="AK105">
+        <v>1.18</v>
+      </c>
+      <c r="AL105">
+        <v>1.3</v>
+      </c>
+      <c r="AM105">
+        <v>2.05</v>
+      </c>
+      <c r="AN105">
+        <v>2.75</v>
+      </c>
+      <c r="AO105">
+        <v>1.57</v>
+      </c>
+      <c r="AP105">
+        <v>2.8</v>
+      </c>
+      <c r="AQ105">
+        <v>1.56</v>
+      </c>
+      <c r="AR105">
+        <v>1.75</v>
+      </c>
+      <c r="AS105">
+        <v>1.64</v>
+      </c>
+      <c r="AT105">
+        <v>3.39</v>
+      </c>
+      <c r="AU105">
+        <v>6</v>
+      </c>
+      <c r="AV105">
+        <v>0</v>
+      </c>
+      <c r="AW105">
+        <v>6</v>
+      </c>
+      <c r="AX105">
+        <v>4</v>
+      </c>
+      <c r="AY105">
+        <v>12</v>
+      </c>
+      <c r="AZ105">
+        <v>4</v>
+      </c>
+      <c r="BA105">
+        <v>3</v>
+      </c>
+      <c r="BB105">
+        <v>2</v>
+      </c>
+      <c r="BC105">
+        <v>5</v>
+      </c>
+      <c r="BD105">
+        <v>1.55</v>
+      </c>
+      <c r="BE105">
+        <v>7.8</v>
+      </c>
+      <c r="BF105">
+        <v>2.9</v>
+      </c>
+      <c r="BG105">
+        <v>1.46</v>
+      </c>
+      <c r="BH105">
+        <v>2.38</v>
+      </c>
+      <c r="BI105">
+        <v>1.85</v>
+      </c>
+      <c r="BJ105">
+        <v>1.81</v>
+      </c>
+      <c r="BK105">
+        <v>2.42</v>
+      </c>
+      <c r="BL105">
+        <v>1.44</v>
+      </c>
+      <c r="BM105">
+        <v>3.34</v>
+      </c>
+      <c r="BN105">
+        <v>1.24</v>
+      </c>
+      <c r="BO105">
+        <v>4</v>
+      </c>
+      <c r="BP105">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="106" spans="1:68">
+      <c r="A106" s="1">
+        <v>105</v>
+      </c>
+      <c r="B106">
+        <v>7813925</v>
+      </c>
+      <c r="C106" t="s">
+        <v>68</v>
+      </c>
+      <c r="D106" t="s">
+        <v>69</v>
+      </c>
+      <c r="E106" s="2">
+        <v>45816.29166666666</v>
+      </c>
+      <c r="F106">
+        <v>15</v>
+      </c>
+      <c r="G106" t="s">
+        <v>78</v>
+      </c>
+      <c r="H106" t="s">
+        <v>71</v>
+      </c>
+      <c r="I106">
+        <v>1</v>
+      </c>
+      <c r="J106">
+        <v>0</v>
+      </c>
+      <c r="K106">
+        <v>1</v>
+      </c>
+      <c r="L106">
+        <v>1</v>
+      </c>
+      <c r="M106">
+        <v>0</v>
+      </c>
+      <c r="N106">
+        <v>1</v>
+      </c>
+      <c r="O106" t="s">
+        <v>156</v>
+      </c>
+      <c r="P106" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q106">
+        <v>2.5</v>
+      </c>
+      <c r="R106">
+        <v>2.2</v>
+      </c>
+      <c r="S106">
+        <v>4.5</v>
+      </c>
+      <c r="T106">
+        <v>1.4</v>
+      </c>
+      <c r="U106">
+        <v>2.75</v>
+      </c>
+      <c r="V106">
+        <v>3</v>
+      </c>
+      <c r="W106">
+        <v>1.36</v>
+      </c>
+      <c r="X106">
+        <v>8</v>
+      </c>
+      <c r="Y106">
+        <v>1.08</v>
+      </c>
+      <c r="Z106">
+        <v>1.82</v>
+      </c>
+      <c r="AA106">
+        <v>3.31</v>
+      </c>
+      <c r="AB106">
+        <v>3.71</v>
+      </c>
+      <c r="AC106">
+        <v>1.01</v>
+      </c>
+      <c r="AD106">
+        <v>8.5</v>
+      </c>
+      <c r="AE106">
+        <v>1.27</v>
+      </c>
+      <c r="AF106">
+        <v>3.14</v>
+      </c>
+      <c r="AG106">
+        <v>1.95</v>
+      </c>
+      <c r="AH106">
+        <v>1.75</v>
+      </c>
+      <c r="AI106">
+        <v>1.83</v>
+      </c>
+      <c r="AJ106">
+        <v>1.83</v>
+      </c>
+      <c r="AK106">
+        <v>1.22</v>
+      </c>
+      <c r="AL106">
+        <v>1.3</v>
+      </c>
+      <c r="AM106">
+        <v>1.85</v>
+      </c>
+      <c r="AN106">
+        <v>0.71</v>
+      </c>
+      <c r="AO106">
+        <v>0</v>
+      </c>
+      <c r="AP106">
+        <v>1.2</v>
+      </c>
+      <c r="AQ106">
+        <v>0.44</v>
+      </c>
+      <c r="AR106">
+        <v>1.56</v>
+      </c>
+      <c r="AS106">
+        <v>1.27</v>
+      </c>
+      <c r="AT106">
+        <v>2.83</v>
+      </c>
+      <c r="AU106">
+        <v>3</v>
+      </c>
+      <c r="AV106">
+        <v>2</v>
+      </c>
+      <c r="AW106">
+        <v>11</v>
+      </c>
+      <c r="AX106">
+        <v>4</v>
+      </c>
+      <c r="AY106">
+        <v>14</v>
+      </c>
+      <c r="AZ106">
+        <v>6</v>
+      </c>
+      <c r="BA106">
+        <v>11</v>
+      </c>
+      <c r="BB106">
+        <v>2</v>
+      </c>
+      <c r="BC106">
+        <v>13</v>
+      </c>
+      <c r="BD106">
+        <v>1.65</v>
+      </c>
+      <c r="BE106">
+        <v>6.2</v>
+      </c>
+      <c r="BF106">
+        <v>2.85</v>
+      </c>
+      <c r="BG106">
+        <v>1.44</v>
+      </c>
+      <c r="BH106">
+        <v>2.43</v>
+      </c>
+      <c r="BI106">
+        <v>1.81</v>
+      </c>
+      <c r="BJ106">
+        <v>1.85</v>
+      </c>
+      <c r="BK106">
+        <v>2.33</v>
+      </c>
+      <c r="BL106">
+        <v>1.48</v>
+      </c>
+      <c r="BM106">
+        <v>3.2</v>
+      </c>
+      <c r="BN106">
+        <v>1.26</v>
+      </c>
+      <c r="BO106">
+        <v>4.05</v>
+      </c>
+      <c r="BP106">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="107" spans="1:68">
+      <c r="A107" s="1">
+        <v>106</v>
+      </c>
+      <c r="B107">
+        <v>7813926</v>
+      </c>
+      <c r="C107" t="s">
+        <v>68</v>
+      </c>
+      <c r="D107" t="s">
+        <v>69</v>
+      </c>
+      <c r="E107" s="2">
+        <v>45822.29166666666</v>
+      </c>
+      <c r="F107">
+        <v>16</v>
+      </c>
+      <c r="G107" t="s">
+        <v>81</v>
+      </c>
+      <c r="H107" t="s">
+        <v>71</v>
+      </c>
+      <c r="I107">
+        <v>0</v>
+      </c>
+      <c r="J107">
+        <v>0</v>
+      </c>
+      <c r="K107">
+        <v>0</v>
+      </c>
+      <c r="L107">
+        <v>0</v>
+      </c>
+      <c r="M107">
+        <v>1</v>
+      </c>
+      <c r="N107">
+        <v>1</v>
+      </c>
+      <c r="O107" t="s">
+        <v>85</v>
+      </c>
+      <c r="P107" t="s">
+        <v>230</v>
+      </c>
+      <c r="Q107">
+        <v>2.13</v>
+      </c>
+      <c r="R107">
+        <v>2.45</v>
+      </c>
+      <c r="S107">
+        <v>5.42</v>
+      </c>
+      <c r="T107">
+        <v>1.32</v>
+      </c>
+      <c r="U107">
+        <v>3.3</v>
+      </c>
+      <c r="V107">
+        <v>2.59</v>
+      </c>
+      <c r="W107">
+        <v>1.49</v>
+      </c>
+      <c r="X107">
+        <v>5.5</v>
+      </c>
+      <c r="Y107">
+        <v>1.11</v>
+      </c>
+      <c r="Z107">
+        <v>1.57</v>
+      </c>
+      <c r="AA107">
+        <v>3.83</v>
+      </c>
+      <c r="AB107">
+        <v>4.5</v>
+      </c>
+      <c r="AC107">
+        <v>1.02</v>
+      </c>
+      <c r="AD107">
+        <v>10</v>
+      </c>
+      <c r="AE107">
+        <v>1.25</v>
+      </c>
+      <c r="AF107">
+        <v>3.6</v>
+      </c>
+      <c r="AG107">
+        <v>1.76</v>
+      </c>
+      <c r="AH107">
+        <v>1.94</v>
+      </c>
+      <c r="AI107">
+        <v>1.75</v>
+      </c>
+      <c r="AJ107">
+        <v>1.95</v>
+      </c>
+      <c r="AK107">
+        <v>1.18</v>
+      </c>
+      <c r="AL107">
+        <v>1.22</v>
+      </c>
+      <c r="AM107">
+        <v>2.3</v>
+      </c>
+      <c r="AN107">
+        <v>1.71</v>
+      </c>
+      <c r="AO107">
+        <v>0</v>
+      </c>
+      <c r="AP107">
+        <v>1.3</v>
+      </c>
+      <c r="AQ107">
+        <v>0.44</v>
+      </c>
+      <c r="AR107">
+        <v>1.82</v>
+      </c>
+      <c r="AS107">
+        <v>1.19</v>
+      </c>
+      <c r="AT107">
+        <v>3.01</v>
+      </c>
+      <c r="AU107">
+        <v>5</v>
+      </c>
+      <c r="AV107">
+        <v>2</v>
+      </c>
+      <c r="AW107">
+        <v>9</v>
+      </c>
+      <c r="AX107">
+        <v>6</v>
+      </c>
+      <c r="AY107">
+        <v>14</v>
+      </c>
+      <c r="AZ107">
+        <v>8</v>
+      </c>
+      <c r="BA107">
+        <v>2</v>
+      </c>
+      <c r="BB107">
+        <v>1</v>
+      </c>
+      <c r="BC107">
+        <v>3</v>
+      </c>
+      <c r="BD107">
+        <v>1.45</v>
+      </c>
+      <c r="BE107">
+        <v>8.5</v>
+      </c>
+      <c r="BF107">
+        <v>3.22</v>
+      </c>
+      <c r="BG107">
+        <v>1.32</v>
+      </c>
+      <c r="BH107">
+        <v>2.88</v>
+      </c>
+      <c r="BI107">
+        <v>1.8</v>
+      </c>
+      <c r="BJ107">
+        <v>2</v>
+      </c>
+      <c r="BK107">
+        <v>2.05</v>
+      </c>
+      <c r="BL107">
+        <v>1.65</v>
+      </c>
+      <c r="BM107">
+        <v>2.7</v>
+      </c>
+      <c r="BN107">
+        <v>1.36</v>
+      </c>
+      <c r="BO107">
+        <v>3.78</v>
+      </c>
+      <c r="BP107">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="108" spans="1:68">
+      <c r="A108" s="1">
+        <v>107</v>
+      </c>
+      <c r="B108">
+        <v>7813927</v>
+      </c>
+      <c r="C108" t="s">
+        <v>68</v>
+      </c>
+      <c r="D108" t="s">
+        <v>69</v>
+      </c>
+      <c r="E108" s="2">
+        <v>45822.29166666666</v>
+      </c>
+      <c r="F108">
+        <v>16</v>
+      </c>
+      <c r="G108" t="s">
+        <v>76</v>
+      </c>
+      <c r="H108" t="s">
+        <v>75</v>
+      </c>
+      <c r="I108">
+        <v>1</v>
+      </c>
+      <c r="J108">
+        <v>1</v>
+      </c>
+      <c r="K108">
+        <v>2</v>
+      </c>
+      <c r="L108">
+        <v>3</v>
+      </c>
+      <c r="M108">
+        <v>1</v>
+      </c>
+      <c r="N108">
+        <v>4</v>
+      </c>
+      <c r="O108" t="s">
+        <v>157</v>
+      </c>
+      <c r="P108" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q108">
+        <v>3.38</v>
+      </c>
+      <c r="R108">
+        <v>2.29</v>
+      </c>
+      <c r="S108">
+        <v>3.05</v>
+      </c>
+      <c r="T108">
+        <v>1.34</v>
+      </c>
+      <c r="U108">
+        <v>3.19</v>
+      </c>
+      <c r="V108">
+        <v>2.71</v>
+      </c>
+      <c r="W108">
+        <v>1.45</v>
+      </c>
+      <c r="X108">
+        <v>6</v>
+      </c>
+      <c r="Y108">
+        <v>1.09</v>
+      </c>
+      <c r="Z108">
+        <v>2.65</v>
+      </c>
+      <c r="AA108">
+        <v>3.17</v>
+      </c>
+      <c r="AB108">
+        <v>2.34</v>
+      </c>
+      <c r="AC108">
+        <v>1.02</v>
+      </c>
+      <c r="AD108">
+        <v>10</v>
+      </c>
+      <c r="AE108">
+        <v>1.29</v>
+      </c>
+      <c r="AF108">
+        <v>3.4</v>
+      </c>
+      <c r="AG108">
+        <v>1.87</v>
+      </c>
+      <c r="AH108">
+        <v>1.83</v>
+      </c>
+      <c r="AI108">
+        <v>1.67</v>
+      </c>
+      <c r="AJ108">
+        <v>2.1</v>
+      </c>
+      <c r="AK108">
+        <v>1.57</v>
+      </c>
+      <c r="AL108">
+        <v>1.3</v>
+      </c>
+      <c r="AM108">
+        <v>1.44</v>
+      </c>
+      <c r="AN108">
+        <v>1.57</v>
+      </c>
+      <c r="AO108">
+        <v>1.83</v>
+      </c>
+      <c r="AP108">
+        <v>1.89</v>
+      </c>
+      <c r="AQ108">
+        <v>1.2</v>
+      </c>
+      <c r="AR108">
+        <v>1.44</v>
+      </c>
+      <c r="AS108">
+        <v>1.23</v>
+      </c>
+      <c r="AT108">
+        <v>2.67</v>
+      </c>
+      <c r="AU108">
+        <v>9</v>
+      </c>
+      <c r="AV108">
+        <v>3</v>
+      </c>
+      <c r="AW108">
+        <v>10</v>
+      </c>
+      <c r="AX108">
+        <v>8</v>
+      </c>
+      <c r="AY108">
+        <v>19</v>
+      </c>
+      <c r="AZ108">
+        <v>11</v>
+      </c>
+      <c r="BA108">
+        <v>5</v>
+      </c>
+      <c r="BB108">
+        <v>5</v>
+      </c>
+      <c r="BC108">
+        <v>10</v>
+      </c>
+      <c r="BD108">
+        <v>1.83</v>
+      </c>
+      <c r="BE108">
+        <v>6.1</v>
+      </c>
+      <c r="BF108">
+        <v>2.45</v>
+      </c>
+      <c r="BG108">
+        <v>1.39</v>
+      </c>
+      <c r="BH108">
+        <v>2.59</v>
+      </c>
+      <c r="BI108">
+        <v>1.85</v>
+      </c>
+      <c r="BJ108">
+        <v>1.95</v>
+      </c>
+      <c r="BK108">
+        <v>2.19</v>
+      </c>
+      <c r="BL108">
+        <v>1.54</v>
+      </c>
+      <c r="BM108">
+        <v>2.97</v>
+      </c>
+      <c r="BN108">
+        <v>1.3</v>
+      </c>
+      <c r="BO108">
+        <v>3.7</v>
+      </c>
+      <c r="BP108">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="109" spans="1:68">
+      <c r="A109" s="1">
+        <v>108</v>
+      </c>
+      <c r="B109">
+        <v>7813928</v>
+      </c>
+      <c r="C109" t="s">
+        <v>68</v>
+      </c>
+      <c r="D109" t="s">
+        <v>69</v>
+      </c>
+      <c r="E109" s="2">
+        <v>45822.29166666666</v>
+      </c>
+      <c r="F109">
+        <v>16</v>
+      </c>
+      <c r="G109" t="s">
+        <v>82</v>
+      </c>
+      <c r="H109" t="s">
+        <v>74</v>
+      </c>
+      <c r="I109">
+        <v>0</v>
+      </c>
+      <c r="J109">
+        <v>0</v>
+      </c>
+      <c r="K109">
+        <v>0</v>
+      </c>
+      <c r="L109">
+        <v>0</v>
+      </c>
+      <c r="M109">
+        <v>1</v>
+      </c>
+      <c r="N109">
+        <v>1</v>
+      </c>
+      <c r="O109" t="s">
+        <v>85</v>
+      </c>
+      <c r="P109" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q109">
+        <v>3.32</v>
+      </c>
+      <c r="R109">
+        <v>2.04</v>
+      </c>
+      <c r="S109">
+        <v>3.08</v>
+      </c>
+      <c r="T109">
+        <v>1.41</v>
+      </c>
+      <c r="U109">
+        <v>2.69</v>
+      </c>
+      <c r="V109">
+        <v>2.93</v>
+      </c>
+      <c r="W109">
+        <v>1.35</v>
+      </c>
+      <c r="X109">
+        <v>6.95</v>
+      </c>
+      <c r="Y109">
+        <v>1.04</v>
+      </c>
+      <c r="Z109">
+        <v>2.59</v>
+      </c>
+      <c r="AA109">
+        <v>3.12</v>
+      </c>
+      <c r="AB109">
+        <v>2.42</v>
+      </c>
+      <c r="AC109">
+        <v>1.02</v>
+      </c>
+      <c r="AD109">
+        <v>8.1</v>
+      </c>
+      <c r="AE109">
+        <v>1.3</v>
+      </c>
+      <c r="AF109">
+        <v>2.97</v>
+      </c>
+      <c r="AG109">
+        <v>2</v>
+      </c>
+      <c r="AH109">
+        <v>1.67</v>
+      </c>
+      <c r="AI109">
+        <v>1.76</v>
+      </c>
+      <c r="AJ109">
+        <v>1.91</v>
+      </c>
+      <c r="AK109">
+        <v>1.47</v>
+      </c>
+      <c r="AL109">
+        <v>1.28</v>
+      </c>
+      <c r="AM109">
+        <v>1.41</v>
+      </c>
+      <c r="AN109">
+        <v>0.4</v>
+      </c>
+      <c r="AO109">
+        <v>0.86</v>
+      </c>
+      <c r="AP109">
+        <v>0.75</v>
+      </c>
+      <c r="AQ109">
+        <v>1</v>
+      </c>
+      <c r="AR109">
+        <v>1.41</v>
+      </c>
+      <c r="AS109">
+        <v>1.21</v>
+      </c>
+      <c r="AT109">
+        <v>2.62</v>
+      </c>
+      <c r="AU109">
+        <v>4</v>
+      </c>
+      <c r="AV109">
+        <v>6</v>
+      </c>
+      <c r="AW109">
+        <v>6</v>
+      </c>
+      <c r="AX109">
+        <v>7</v>
+      </c>
+      <c r="AY109">
+        <v>10</v>
+      </c>
+      <c r="AZ109">
+        <v>13</v>
+      </c>
+      <c r="BA109">
+        <v>2</v>
+      </c>
+      <c r="BB109">
+        <v>2</v>
+      </c>
+      <c r="BC109">
+        <v>4</v>
+      </c>
+      <c r="BD109">
+        <v>1.98</v>
+      </c>
+      <c r="BE109">
+        <v>5.95</v>
+      </c>
+      <c r="BF109">
+        <v>2.25</v>
+      </c>
+      <c r="BG109">
+        <v>1.47</v>
+      </c>
+      <c r="BH109">
+        <v>2.35</v>
+      </c>
+      <c r="BI109">
+        <v>1.86</v>
+      </c>
+      <c r="BJ109">
+        <v>1.8</v>
+      </c>
+      <c r="BK109">
+        <v>2.43</v>
+      </c>
+      <c r="BL109">
+        <v>1.44</v>
+      </c>
+      <c r="BM109">
+        <v>3.34</v>
+      </c>
+      <c r="BN109">
+        <v>1.24</v>
+      </c>
+      <c r="BO109">
+        <v>4.4</v>
+      </c>
+      <c r="BP109">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="110" spans="1:68">
+      <c r="A110" s="1">
+        <v>109</v>
+      </c>
+      <c r="B110">
+        <v>7813929</v>
+      </c>
+      <c r="C110" t="s">
+        <v>68</v>
+      </c>
+      <c r="D110" t="s">
+        <v>69</v>
+      </c>
+      <c r="E110" s="2">
+        <v>45823.29166666666</v>
+      </c>
+      <c r="F110">
+        <v>16</v>
+      </c>
+      <c r="G110" t="s">
+        <v>83</v>
+      </c>
+      <c r="H110" t="s">
+        <v>72</v>
+      </c>
+      <c r="I110">
+        <v>0</v>
+      </c>
+      <c r="J110">
+        <v>1</v>
+      </c>
+      <c r="K110">
+        <v>1</v>
+      </c>
+      <c r="L110">
+        <v>0</v>
+      </c>
+      <c r="M110">
+        <v>1</v>
+      </c>
+      <c r="N110">
+        <v>1</v>
+      </c>
+      <c r="O110" t="s">
+        <v>85</v>
+      </c>
+      <c r="P110" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q110">
+        <v>3.25</v>
+      </c>
+      <c r="R110">
+        <v>2.2</v>
+      </c>
+      <c r="S110">
+        <v>3.25</v>
+      </c>
+      <c r="T110">
+        <v>1.4</v>
+      </c>
+      <c r="U110">
+        <v>2.75</v>
+      </c>
+      <c r="V110">
+        <v>2.75</v>
+      </c>
+      <c r="W110">
+        <v>1.4</v>
+      </c>
+      <c r="X110">
+        <v>8</v>
+      </c>
+      <c r="Y110">
+        <v>1.08</v>
+      </c>
+      <c r="Z110">
+        <v>2.63</v>
+      </c>
+      <c r="AA110">
+        <v>3.1</v>
+      </c>
+      <c r="AB110">
+        <v>2.4</v>
+      </c>
+      <c r="AC110">
+        <v>1.05</v>
+      </c>
+      <c r="AD110">
+        <v>8.5</v>
+      </c>
+      <c r="AE110">
+        <v>1.3</v>
+      </c>
+      <c r="AF110">
+        <v>3.3</v>
+      </c>
+      <c r="AG110">
+        <v>1.91</v>
+      </c>
+      <c r="AH110">
+        <v>1.79</v>
+      </c>
+      <c r="AI110">
+        <v>1.73</v>
+      </c>
+      <c r="AJ110">
+        <v>2</v>
+      </c>
+      <c r="AK110">
+        <v>1.51</v>
+      </c>
+      <c r="AL110">
+        <v>1.3</v>
+      </c>
+      <c r="AM110">
+        <v>1.44</v>
+      </c>
+      <c r="AN110">
+        <v>2.5</v>
+      </c>
+      <c r="AO110">
+        <v>2.33</v>
+      </c>
+      <c r="AP110">
+        <v>2</v>
+      </c>
+      <c r="AQ110">
+        <v>2.25</v>
+      </c>
+      <c r="AR110">
+        <v>1.42</v>
+      </c>
+      <c r="AS110">
+        <v>1.12</v>
+      </c>
+      <c r="AT110">
+        <v>2.54</v>
+      </c>
+      <c r="AU110">
+        <v>6</v>
+      </c>
+      <c r="AV110">
+        <v>4</v>
+      </c>
+      <c r="AW110">
+        <v>10</v>
+      </c>
+      <c r="AX110">
+        <v>10</v>
+      </c>
+      <c r="AY110">
+        <v>16</v>
+      </c>
+      <c r="AZ110">
+        <v>14</v>
+      </c>
+      <c r="BA110">
+        <v>6</v>
+      </c>
+      <c r="BB110">
+        <v>4</v>
+      </c>
+      <c r="BC110">
+        <v>10</v>
+      </c>
+      <c r="BD110">
+        <v>1.92</v>
+      </c>
+      <c r="BE110">
+        <v>5.95</v>
+      </c>
+      <c r="BF110">
+        <v>2.33</v>
+      </c>
+      <c r="BG110">
+        <v>1.47</v>
+      </c>
+      <c r="BH110">
+        <v>2.35</v>
+      </c>
+      <c r="BI110">
+        <v>1.85</v>
+      </c>
+      <c r="BJ110">
+        <v>1.81</v>
+      </c>
+      <c r="BK110">
+        <v>2.43</v>
+      </c>
+      <c r="BL110">
+        <v>1.44</v>
+      </c>
+      <c r="BM110">
+        <v>3.34</v>
+      </c>
+      <c r="BN110">
+        <v>1.24</v>
+      </c>
+      <c r="BO110">
+        <v>4.2</v>
+      </c>
+      <c r="BP110">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="111" spans="1:68">
+      <c r="A111" s="1">
+        <v>110</v>
+      </c>
+      <c r="B111">
+        <v>7813930</v>
+      </c>
+      <c r="C111" t="s">
+        <v>68</v>
+      </c>
+      <c r="D111" t="s">
+        <v>69</v>
+      </c>
+      <c r="E111" s="2">
+        <v>45823.29166666666</v>
+      </c>
+      <c r="F111">
+        <v>16</v>
+      </c>
+      <c r="G111" t="s">
+        <v>77</v>
+      </c>
+      <c r="H111" t="s">
+        <v>73</v>
+      </c>
+      <c r="I111">
+        <v>0</v>
+      </c>
+      <c r="J111">
+        <v>0</v>
+      </c>
+      <c r="K111">
+        <v>0</v>
+      </c>
+      <c r="L111">
+        <v>0</v>
+      </c>
+      <c r="M111">
+        <v>0</v>
+      </c>
+      <c r="N111">
+        <v>0</v>
+      </c>
+      <c r="O111" t="s">
+        <v>85</v>
+      </c>
+      <c r="P111" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q111">
+        <v>2.75</v>
+      </c>
+      <c r="R111">
+        <v>2.1</v>
+      </c>
+      <c r="S111">
+        <v>4.33</v>
+      </c>
+      <c r="T111">
+        <v>1.44</v>
+      </c>
+      <c r="U111">
+        <v>2.63</v>
+      </c>
+      <c r="V111">
+        <v>3.25</v>
+      </c>
+      <c r="W111">
+        <v>1.33</v>
+      </c>
+      <c r="X111">
+        <v>9</v>
+      </c>
+      <c r="Y111">
+        <v>1.07</v>
+      </c>
+      <c r="Z111">
+        <v>1.97</v>
+      </c>
+      <c r="AA111">
+        <v>3.19</v>
+      </c>
+      <c r="AB111">
+        <v>3.36</v>
+      </c>
+      <c r="AC111">
+        <v>1.06</v>
+      </c>
+      <c r="AD111">
+        <v>8</v>
+      </c>
+      <c r="AE111">
+        <v>1.36</v>
+      </c>
+      <c r="AF111">
+        <v>3</v>
+      </c>
+      <c r="AG111">
+        <v>2</v>
+      </c>
+      <c r="AH111">
+        <v>1.65</v>
+      </c>
+      <c r="AI111">
+        <v>1.91</v>
+      </c>
+      <c r="AJ111">
+        <v>1.8</v>
+      </c>
+      <c r="AK111">
+        <v>1.29</v>
+      </c>
+      <c r="AL111">
+        <v>1.3</v>
+      </c>
+      <c r="AM111">
+        <v>1.73</v>
+      </c>
+      <c r="AN111">
+        <v>1.14</v>
+      </c>
+      <c r="AO111">
+        <v>1.14</v>
+      </c>
+      <c r="AP111">
+        <v>1.33</v>
+      </c>
+      <c r="AQ111">
+        <v>1.11</v>
+      </c>
+      <c r="AR111">
+        <v>1.5</v>
+      </c>
+      <c r="AS111">
+        <v>1.06</v>
+      </c>
+      <c r="AT111">
+        <v>2.56</v>
+      </c>
+      <c r="AU111">
+        <v>2</v>
+      </c>
+      <c r="AV111">
+        <v>2</v>
+      </c>
+      <c r="AW111">
+        <v>0</v>
+      </c>
+      <c r="AX111">
+        <v>4</v>
+      </c>
+      <c r="AY111">
+        <v>2</v>
+      </c>
+      <c r="AZ111">
+        <v>6</v>
+      </c>
+      <c r="BA111">
+        <v>0</v>
+      </c>
+      <c r="BB111">
+        <v>3</v>
+      </c>
+      <c r="BC111">
+        <v>3</v>
+      </c>
+      <c r="BD111">
+        <v>1.54</v>
+      </c>
+      <c r="BE111">
+        <v>7.9</v>
+      </c>
+      <c r="BF111">
+        <v>2.92</v>
+      </c>
+      <c r="BG111">
+        <v>1.43</v>
+      </c>
+      <c r="BH111">
+        <v>2.46</v>
+      </c>
+      <c r="BI111">
+        <v>1.81</v>
+      </c>
+      <c r="BJ111">
+        <v>1.85</v>
+      </c>
+      <c r="BK111">
+        <v>2.33</v>
+      </c>
+      <c r="BL111">
+        <v>1.48</v>
+      </c>
+      <c r="BM111">
+        <v>3.2</v>
+      </c>
+      <c r="BN111">
+        <v>1.26</v>
+      </c>
+      <c r="BO111">
+        <v>4.15</v>
+      </c>
+      <c r="BP111">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="112" spans="1:68">
+      <c r="A112" s="1">
+        <v>111</v>
+      </c>
+      <c r="B112">
+        <v>7813931</v>
+      </c>
+      <c r="C112" t="s">
+        <v>68</v>
+      </c>
+      <c r="D112" t="s">
+        <v>69</v>
+      </c>
+      <c r="E112" s="2">
+        <v>45823.29166666666</v>
+      </c>
+      <c r="F112">
+        <v>16</v>
+      </c>
+      <c r="G112" t="s">
+        <v>78</v>
+      </c>
+      <c r="H112" t="s">
+        <v>80</v>
+      </c>
+      <c r="I112">
+        <v>0</v>
+      </c>
+      <c r="J112">
+        <v>0</v>
+      </c>
+      <c r="K112">
+        <v>0</v>
+      </c>
+      <c r="L112">
+        <v>3</v>
+      </c>
+      <c r="M112">
+        <v>0</v>
+      </c>
+      <c r="N112">
+        <v>3</v>
+      </c>
+      <c r="O112" t="s">
+        <v>158</v>
+      </c>
+      <c r="P112" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q112">
+        <v>2.6</v>
+      </c>
+      <c r="R112">
+        <v>2.2</v>
+      </c>
+      <c r="S112">
+        <v>4.33</v>
+      </c>
+      <c r="T112">
+        <v>1.36</v>
+      </c>
+      <c r="U112">
+        <v>3</v>
+      </c>
+      <c r="V112">
+        <v>2.75</v>
+      </c>
+      <c r="W112">
+        <v>1.4</v>
+      </c>
+      <c r="X112">
+        <v>7</v>
+      </c>
+      <c r="Y112">
+        <v>1.1</v>
+      </c>
+      <c r="Z112">
+        <v>1.94</v>
+      </c>
+      <c r="AA112">
+        <v>3.28</v>
+      </c>
+      <c r="AB112">
+        <v>3.33</v>
+      </c>
+      <c r="AC112">
+        <v>1.05</v>
+      </c>
+      <c r="AD112">
+        <v>8.5</v>
+      </c>
+      <c r="AE112">
+        <v>1.3</v>
+      </c>
+      <c r="AF112">
+        <v>3.3</v>
+      </c>
+      <c r="AG112">
+        <v>1.94</v>
+      </c>
+      <c r="AH112">
+        <v>1.76</v>
+      </c>
+      <c r="AI112">
+        <v>1.8</v>
+      </c>
+      <c r="AJ112">
+        <v>1.91</v>
+      </c>
+      <c r="AK112">
+        <v>1.27</v>
+      </c>
+      <c r="AL112">
+        <v>1.3</v>
+      </c>
+      <c r="AM112">
+        <v>1.77</v>
+      </c>
+      <c r="AN112">
+        <v>1</v>
+      </c>
+      <c r="AO112">
+        <v>1</v>
+      </c>
+      <c r="AP112">
+        <v>1.2</v>
+      </c>
+      <c r="AQ112">
+        <v>0.78</v>
+      </c>
+      <c r="AR112">
+        <v>1.55</v>
+      </c>
+      <c r="AS112">
+        <v>1.16</v>
+      </c>
+      <c r="AT112">
+        <v>2.71</v>
+      </c>
+      <c r="AU112">
+        <v>10</v>
+      </c>
+      <c r="AV112">
+        <v>2</v>
+      </c>
+      <c r="AW112">
+        <v>6</v>
+      </c>
+      <c r="AX112">
+        <v>3</v>
+      </c>
+      <c r="AY112">
+        <v>16</v>
+      </c>
+      <c r="AZ112">
+        <v>5</v>
+      </c>
+      <c r="BA112">
+        <v>9</v>
+      </c>
+      <c r="BB112">
+        <v>2</v>
+      </c>
+      <c r="BC112">
+        <v>11</v>
+      </c>
+      <c r="BD112">
+        <v>1.69</v>
+      </c>
+      <c r="BE112">
+        <v>6.15</v>
+      </c>
+      <c r="BF112">
+        <v>2.75</v>
+      </c>
+      <c r="BG112">
+        <v>1.44</v>
+      </c>
+      <c r="BH112">
+        <v>2.43</v>
+      </c>
+      <c r="BI112">
+        <v>1.82</v>
+      </c>
+      <c r="BJ112">
+        <v>1.84</v>
+      </c>
+      <c r="BK112">
+        <v>2.35</v>
+      </c>
+      <c r="BL112">
+        <v>1.47</v>
+      </c>
+      <c r="BM112">
+        <v>3.28</v>
+      </c>
+      <c r="BN112">
+        <v>1.25</v>
+      </c>
+      <c r="BO112">
+        <v>4.05</v>
+      </c>
+      <c r="BP112">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="113" spans="1:68">
+      <c r="A113" s="1">
+        <v>112</v>
+      </c>
+      <c r="B113">
+        <v>7813932</v>
+      </c>
+      <c r="C113" t="s">
+        <v>68</v>
+      </c>
+      <c r="D113" t="s">
+        <v>69</v>
+      </c>
+      <c r="E113" s="2">
+        <v>45823.29166666666</v>
+      </c>
+      <c r="F113">
+        <v>16</v>
+      </c>
+      <c r="G113" t="s">
+        <v>79</v>
+      </c>
+      <c r="H113" t="s">
+        <v>70</v>
+      </c>
+      <c r="I113">
+        <v>0</v>
+      </c>
+      <c r="J113">
+        <v>1</v>
+      </c>
+      <c r="K113">
+        <v>1</v>
+      </c>
+      <c r="L113">
+        <v>1</v>
+      </c>
+      <c r="M113">
+        <v>2</v>
+      </c>
+      <c r="N113">
+        <v>3</v>
+      </c>
+      <c r="O113" t="s">
+        <v>159</v>
+      </c>
+      <c r="P113" t="s">
+        <v>232</v>
+      </c>
+      <c r="Q113">
+        <v>3.4</v>
+      </c>
+      <c r="R113">
+        <v>2.1</v>
+      </c>
+      <c r="S113">
+        <v>3.2</v>
+      </c>
+      <c r="T113">
+        <v>1.4</v>
+      </c>
+      <c r="U113">
+        <v>2.75</v>
+      </c>
+      <c r="V113">
+        <v>3</v>
+      </c>
+      <c r="W113">
+        <v>1.36</v>
+      </c>
+      <c r="X113">
+        <v>8</v>
+      </c>
+      <c r="Y113">
+        <v>1.08</v>
+      </c>
+      <c r="Z113">
+        <v>2.58</v>
+      </c>
+      <c r="AA113">
+        <v>3.23</v>
+      </c>
+      <c r="AB113">
+        <v>2.36</v>
+      </c>
+      <c r="AC113">
+        <v>1.06</v>
+      </c>
+      <c r="AD113">
+        <v>8</v>
+      </c>
+      <c r="AE113">
+        <v>1.3</v>
+      </c>
+      <c r="AF113">
+        <v>3.25</v>
+      </c>
+      <c r="AG113">
+        <v>1.87</v>
+      </c>
+      <c r="AH113">
+        <v>1.83</v>
+      </c>
+      <c r="AI113">
+        <v>1.8</v>
+      </c>
+      <c r="AJ113">
+        <v>1.91</v>
+      </c>
+      <c r="AK113">
+        <v>1.49</v>
+      </c>
+      <c r="AL113">
+        <v>1.31</v>
+      </c>
+      <c r="AM113">
+        <v>1.46</v>
+      </c>
+      <c r="AN113">
+        <v>2.5</v>
+      </c>
+      <c r="AO113">
+        <v>2.17</v>
+      </c>
+      <c r="AP113">
+        <v>2.1</v>
+      </c>
+      <c r="AQ113">
+        <v>1.89</v>
+      </c>
+      <c r="AR113">
+        <v>1.85</v>
+      </c>
+      <c r="AS113">
+        <v>1.29</v>
+      </c>
+      <c r="AT113">
+        <v>3.14</v>
+      </c>
+      <c r="AU113">
+        <v>6</v>
+      </c>
+      <c r="AV113">
+        <v>3</v>
+      </c>
+      <c r="AW113">
+        <v>5</v>
+      </c>
+      <c r="AX113">
+        <v>2</v>
+      </c>
+      <c r="AY113">
+        <v>11</v>
+      </c>
+      <c r="AZ113">
+        <v>5</v>
+      </c>
+      <c r="BA113">
+        <v>4</v>
+      </c>
+      <c r="BB113">
+        <v>2</v>
+      </c>
+      <c r="BC113">
+        <v>6</v>
+      </c>
+      <c r="BD113">
+        <v>1.94</v>
+      </c>
+      <c r="BE113">
+        <v>6.05</v>
+      </c>
+      <c r="BF113">
+        <v>2.29</v>
+      </c>
+      <c r="BG113">
+        <v>1.4</v>
+      </c>
+      <c r="BH113">
+        <v>2.56</v>
+      </c>
+      <c r="BI113">
+        <v>1.75</v>
+      </c>
+      <c r="BJ113">
+        <v>1.92</v>
+      </c>
+      <c r="BK113">
+        <v>2.24</v>
+      </c>
+      <c r="BL113">
+        <v>1.52</v>
+      </c>
+      <c r="BM113">
+        <v>3.05</v>
+      </c>
+      <c r="BN113">
+        <v>1.28</v>
+      </c>
+      <c r="BO113">
+        <v>3.95</v>
+      </c>
+      <c r="BP113">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="114" spans="1:68">
+      <c r="A114" s="1">
+        <v>113</v>
+      </c>
+      <c r="B114">
+        <v>7813933</v>
+      </c>
+      <c r="C114" t="s">
+        <v>68</v>
+      </c>
+      <c r="D114" t="s">
+        <v>69</v>
+      </c>
+      <c r="E114" s="2">
+        <v>45829.29166666666</v>
+      </c>
+      <c r="F114">
+        <v>17</v>
+      </c>
+      <c r="G114" t="s">
+        <v>70</v>
+      </c>
+      <c r="H114" t="s">
+        <v>77</v>
+      </c>
+      <c r="I114">
+        <v>1</v>
+      </c>
+      <c r="J114">
+        <v>0</v>
+      </c>
+      <c r="K114">
+        <v>1</v>
+      </c>
+      <c r="L114">
+        <v>2</v>
+      </c>
+      <c r="M114">
+        <v>0</v>
+      </c>
+      <c r="N114">
+        <v>2</v>
+      </c>
+      <c r="O114" t="s">
+        <v>160</v>
+      </c>
+      <c r="P114" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q114">
+        <v>1.79</v>
+      </c>
+      <c r="R114">
+        <v>2.62</v>
+      </c>
+      <c r="S114">
+        <v>7.92</v>
+      </c>
+      <c r="T114">
+        <v>1.32</v>
+      </c>
+      <c r="U114">
+        <v>3.31</v>
+      </c>
+      <c r="V114">
+        <v>2.55</v>
+      </c>
+      <c r="W114">
+        <v>1.5</v>
+      </c>
+      <c r="X114">
+        <v>5.95</v>
+      </c>
+      <c r="Y114">
+        <v>1.07</v>
+      </c>
+      <c r="Z114">
+        <v>1.38</v>
+      </c>
+      <c r="AA114">
+        <v>4.3</v>
+      </c>
+      <c r="AB114">
+        <v>6.2</v>
+      </c>
+      <c r="AC114">
+        <v>1.02</v>
+      </c>
+      <c r="AD114">
+        <v>10</v>
+      </c>
+      <c r="AE114">
+        <v>1.22</v>
+      </c>
+      <c r="AF114">
+        <v>3.8</v>
+      </c>
+      <c r="AG114">
+        <v>1.78</v>
+      </c>
+      <c r="AH114">
+        <v>1.92</v>
+      </c>
+      <c r="AI114">
+        <v>1.95</v>
+      </c>
+      <c r="AJ114">
+        <v>1.81</v>
+      </c>
+      <c r="AK114">
+        <v>1.04</v>
+      </c>
+      <c r="AL114">
+        <v>1.14</v>
+      </c>
+      <c r="AM114">
+        <v>3.02</v>
+      </c>
+      <c r="AN114">
+        <v>2.78</v>
+      </c>
+      <c r="AO114">
+        <v>0.5</v>
+      </c>
+      <c r="AP114">
+        <v>2.8</v>
+      </c>
+      <c r="AQ114">
+        <v>0.44</v>
+      </c>
+      <c r="AR114">
+        <v>1.71</v>
+      </c>
+      <c r="AS114">
+        <v>1.07</v>
+      </c>
+      <c r="AT114">
+        <v>2.78</v>
+      </c>
+      <c r="AU114">
+        <v>5</v>
+      </c>
+      <c r="AV114">
+        <v>0</v>
+      </c>
+      <c r="AW114">
+        <v>5</v>
+      </c>
+      <c r="AX114">
+        <v>8</v>
+      </c>
+      <c r="AY114">
+        <v>10</v>
+      </c>
+      <c r="AZ114">
+        <v>8</v>
+      </c>
+      <c r="BA114">
+        <v>2</v>
+      </c>
+      <c r="BB114">
+        <v>1</v>
+      </c>
+      <c r="BC114">
+        <v>3</v>
+      </c>
+      <c r="BD114">
+        <v>1.35</v>
+      </c>
+      <c r="BE114">
+        <v>8.6</v>
+      </c>
+      <c r="BF114">
+        <v>3.84</v>
+      </c>
+      <c r="BG114">
+        <v>1.48</v>
+      </c>
+      <c r="BH114">
+        <v>2.58</v>
+      </c>
+      <c r="BI114">
+        <v>1.84</v>
+      </c>
+      <c r="BJ114">
+        <v>1.95</v>
+      </c>
+      <c r="BK114">
+        <v>2.36</v>
+      </c>
+      <c r="BL114">
+        <v>1.56</v>
+      </c>
+      <c r="BM114">
+        <v>3.2</v>
+      </c>
+      <c r="BN114">
+        <v>1.3</v>
+      </c>
+      <c r="BO114">
+        <v>4.1</v>
+      </c>
+      <c r="BP114">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="115" spans="1:68">
+      <c r="A115" s="1">
+        <v>114</v>
+      </c>
+      <c r="B115">
+        <v>7813934</v>
+      </c>
+      <c r="C115" t="s">
+        <v>68</v>
+      </c>
+      <c r="D115" t="s">
+        <v>69</v>
+      </c>
+      <c r="E115" s="2">
+        <v>45829.29166666666</v>
+      </c>
+      <c r="F115">
+        <v>17</v>
+      </c>
+      <c r="G115" t="s">
+        <v>71</v>
+      </c>
+      <c r="H115" t="s">
+        <v>75</v>
+      </c>
+      <c r="I115">
+        <v>1</v>
+      </c>
+      <c r="J115">
+        <v>1</v>
+      </c>
+      <c r="K115">
+        <v>2</v>
+      </c>
+      <c r="L115">
+        <v>4</v>
+      </c>
+      <c r="M115">
+        <v>2</v>
+      </c>
+      <c r="N115">
+        <v>6</v>
+      </c>
+      <c r="O115" t="s">
+        <v>161</v>
+      </c>
+      <c r="P115" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q115">
+        <v>4.85</v>
+      </c>
+      <c r="R115">
+        <v>2.2</v>
+      </c>
+      <c r="S115">
+        <v>2.19</v>
+      </c>
+      <c r="T115">
+        <v>1.33</v>
+      </c>
+      <c r="U115">
+        <v>3.04</v>
+      </c>
+      <c r="V115">
+        <v>2.65</v>
+      </c>
+      <c r="W115">
+        <v>1.42</v>
+      </c>
+      <c r="X115">
+        <v>6.5</v>
+      </c>
+      <c r="Y115">
+        <v>1.05</v>
+      </c>
+      <c r="Z115">
+        <v>4.33</v>
+      </c>
+      <c r="AA115">
+        <v>3.72</v>
+      </c>
+      <c r="AB115">
+        <v>1.61</v>
+      </c>
+      <c r="AC115">
+        <v>1.01</v>
+      </c>
+      <c r="AD115">
+        <v>11</v>
+      </c>
+      <c r="AE115">
+        <v>1.21</v>
+      </c>
+      <c r="AF115">
+        <v>3.58</v>
+      </c>
+      <c r="AG115">
+        <v>1.77</v>
+      </c>
+      <c r="AH115">
+        <v>1.93</v>
+      </c>
+      <c r="AI115">
+        <v>1.74</v>
+      </c>
+      <c r="AJ115">
+        <v>1.93</v>
+      </c>
+      <c r="AK115">
+        <v>2.09</v>
+      </c>
+      <c r="AL115">
+        <v>1.22</v>
+      </c>
+      <c r="AM115">
+        <v>1.15</v>
+      </c>
+      <c r="AN115">
+        <v>0.63</v>
+      </c>
+      <c r="AO115">
+        <v>1.57</v>
+      </c>
+      <c r="AP115">
+        <v>0.89</v>
+      </c>
+      <c r="AQ115">
+        <v>1.2</v>
+      </c>
+      <c r="AR115">
+        <v>1.19</v>
+      </c>
+      <c r="AS115">
+        <v>1.24</v>
+      </c>
+      <c r="AT115">
+        <v>2.43</v>
+      </c>
+      <c r="AU115">
+        <v>7</v>
+      </c>
+      <c r="AV115">
+        <v>7</v>
+      </c>
+      <c r="AW115">
+        <v>5</v>
+      </c>
+      <c r="AX115">
+        <v>10</v>
+      </c>
+      <c r="AY115">
+        <v>12</v>
+      </c>
+      <c r="AZ115">
+        <v>17</v>
+      </c>
+      <c r="BA115">
+        <v>3</v>
+      </c>
+      <c r="BB115">
+        <v>5</v>
+      </c>
+      <c r="BC115">
+        <v>8</v>
+      </c>
+      <c r="BD115">
+        <v>2.73</v>
+      </c>
+      <c r="BE115">
+        <v>6.25</v>
+      </c>
+      <c r="BF115">
+        <v>1.69</v>
+      </c>
+      <c r="BG115">
+        <v>1.37</v>
+      </c>
+      <c r="BH115">
+        <v>2.85</v>
+      </c>
+      <c r="BI115">
+        <v>1.72</v>
+      </c>
+      <c r="BJ115">
+        <v>2.09</v>
+      </c>
+      <c r="BK115">
+        <v>2.17</v>
+      </c>
+      <c r="BL115">
         <v>1.68</v>
       </c>
-      <c r="BE100">
+      <c r="BM115">
+        <v>3</v>
+      </c>
+      <c r="BN115">
+        <v>1.34</v>
+      </c>
+      <c r="BO115">
+        <v>3.68</v>
+      </c>
+      <c r="BP115">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="116" spans="1:68">
+      <c r="A116" s="1">
+        <v>115</v>
+      </c>
+      <c r="B116">
+        <v>7813935</v>
+      </c>
+      <c r="C116" t="s">
+        <v>68</v>
+      </c>
+      <c r="D116" t="s">
+        <v>69</v>
+      </c>
+      <c r="E116" s="2">
+        <v>45829.29166666666</v>
+      </c>
+      <c r="F116">
+        <v>17</v>
+      </c>
+      <c r="G116" t="s">
+        <v>73</v>
+      </c>
+      <c r="H116" t="s">
+        <v>76</v>
+      </c>
+      <c r="I116">
+        <v>0</v>
+      </c>
+      <c r="J116">
+        <v>0</v>
+      </c>
+      <c r="K116">
+        <v>0</v>
+      </c>
+      <c r="L116">
+        <v>0</v>
+      </c>
+      <c r="M116">
+        <v>1</v>
+      </c>
+      <c r="N116">
+        <v>1</v>
+      </c>
+      <c r="O116" t="s">
+        <v>85</v>
+      </c>
+      <c r="P116" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q116">
+        <v>4.56</v>
+      </c>
+      <c r="R116">
+        <v>2.18</v>
+      </c>
+      <c r="S116">
+        <v>2.6</v>
+      </c>
+      <c r="T116">
+        <v>1.42</v>
+      </c>
+      <c r="U116">
+        <v>2.83</v>
+      </c>
+      <c r="V116">
+        <v>3.1</v>
+      </c>
+      <c r="W116">
+        <v>1.36</v>
+      </c>
+      <c r="X116">
+        <v>7.4</v>
+      </c>
+      <c r="Y116">
+        <v>1.03</v>
+      </c>
+      <c r="Z116">
+        <v>3.58</v>
+      </c>
+      <c r="AA116">
+        <v>3.29</v>
+      </c>
+      <c r="AB116">
+        <v>1.86</v>
+      </c>
+      <c r="AC116">
+        <v>1.04</v>
+      </c>
+      <c r="AD116">
+        <v>8.5</v>
+      </c>
+      <c r="AE116">
+        <v>1.33</v>
+      </c>
+      <c r="AF116">
+        <v>3</v>
+      </c>
+      <c r="AG116">
+        <v>1.95</v>
+      </c>
+      <c r="AH116">
+        <v>1.75</v>
+      </c>
+      <c r="AI116">
+        <v>1.83</v>
+      </c>
+      <c r="AJ116">
+        <v>1.93</v>
+      </c>
+      <c r="AK116">
+        <v>1.78</v>
+      </c>
+      <c r="AL116">
+        <v>1.26</v>
+      </c>
+      <c r="AM116">
+        <v>1.22</v>
+      </c>
+      <c r="AN116">
+        <v>0.88</v>
+      </c>
+      <c r="AO116">
+        <v>1.38</v>
+      </c>
+      <c r="AP116">
+        <v>0.8</v>
+      </c>
+      <c r="AQ116">
+        <v>1.56</v>
+      </c>
+      <c r="AR116">
+        <v>1.3</v>
+      </c>
+      <c r="AS116">
+        <v>1.47</v>
+      </c>
+      <c r="AT116">
+        <v>2.77</v>
+      </c>
+      <c r="AU116">
+        <v>2</v>
+      </c>
+      <c r="AV116">
+        <v>2</v>
+      </c>
+      <c r="AW116">
+        <v>1</v>
+      </c>
+      <c r="AX116">
+        <v>5</v>
+      </c>
+      <c r="AY116">
+        <v>3</v>
+      </c>
+      <c r="AZ116">
+        <v>7</v>
+      </c>
+      <c r="BA116">
+        <v>3</v>
+      </c>
+      <c r="BB116">
+        <v>5</v>
+      </c>
+      <c r="BC116">
+        <v>8</v>
+      </c>
+      <c r="BD116">
+        <v>2.79</v>
+      </c>
+      <c r="BE116">
+        <v>6.1</v>
+      </c>
+      <c r="BF116">
+        <v>1.68</v>
+      </c>
+      <c r="BG116">
+        <v>1.58</v>
+      </c>
+      <c r="BH116">
+        <v>2.33</v>
+      </c>
+      <c r="BI116">
+        <v>1.98</v>
+      </c>
+      <c r="BJ116">
+        <v>1.82</v>
+      </c>
+      <c r="BK116">
+        <v>2.55</v>
+      </c>
+      <c r="BL116">
+        <v>1.5</v>
+      </c>
+      <c r="BM116">
+        <v>3.58</v>
+      </c>
+      <c r="BN116">
+        <v>1.21</v>
+      </c>
+      <c r="BO116">
+        <v>4.4</v>
+      </c>
+      <c r="BP116">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="117" spans="1:68">
+      <c r="A117" s="1">
+        <v>116</v>
+      </c>
+      <c r="B117">
+        <v>7813936</v>
+      </c>
+      <c r="C117" t="s">
+        <v>68</v>
+      </c>
+      <c r="D117" t="s">
+        <v>69</v>
+      </c>
+      <c r="E117" s="2">
+        <v>45829.29166666666</v>
+      </c>
+      <c r="F117">
+        <v>17</v>
+      </c>
+      <c r="G117" t="s">
+        <v>74</v>
+      </c>
+      <c r="H117" t="s">
+        <v>81</v>
+      </c>
+      <c r="I117">
+        <v>0</v>
+      </c>
+      <c r="J117">
+        <v>1</v>
+      </c>
+      <c r="K117">
+        <v>1</v>
+      </c>
+      <c r="L117">
+        <v>0</v>
+      </c>
+      <c r="M117">
+        <v>2</v>
+      </c>
+      <c r="N117">
+        <v>2</v>
+      </c>
+      <c r="O117" t="s">
+        <v>85</v>
+      </c>
+      <c r="P117" t="s">
+        <v>234</v>
+      </c>
+      <c r="Q117">
+        <v>3.64</v>
+      </c>
+      <c r="R117">
+        <v>2.01</v>
+      </c>
+      <c r="S117">
+        <v>2.9</v>
+      </c>
+      <c r="T117">
+        <v>1.4</v>
+      </c>
+      <c r="U117">
+        <v>2.72</v>
+      </c>
+      <c r="V117">
+        <v>2.98</v>
+      </c>
+      <c r="W117">
+        <v>1.34</v>
+      </c>
+      <c r="X117">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y117">
+        <v>1.02</v>
+      </c>
+      <c r="Z117">
+        <v>3.06</v>
+      </c>
+      <c r="AA117">
+        <v>3.11</v>
+      </c>
+      <c r="AB117">
+        <v>2.12</v>
+      </c>
+      <c r="AC117">
+        <v>1</v>
+      </c>
+      <c r="AD117">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE117">
+        <v>1.27</v>
+      </c>
+      <c r="AF117">
+        <v>3.14</v>
+      </c>
+      <c r="AG117">
+        <v>1.95</v>
+      </c>
+      <c r="AH117">
+        <v>1.7</v>
+      </c>
+      <c r="AI117">
+        <v>1.76</v>
+      </c>
+      <c r="AJ117">
+        <v>1.91</v>
+      </c>
+      <c r="AK117">
+        <v>1.56</v>
+      </c>
+      <c r="AL117">
+        <v>1.28</v>
+      </c>
+      <c r="AM117">
+        <v>1.33</v>
+      </c>
+      <c r="AN117">
+        <v>1.5</v>
+      </c>
+      <c r="AO117">
+        <v>1.13</v>
+      </c>
+      <c r="AP117">
+        <v>1.33</v>
+      </c>
+      <c r="AQ117">
+        <v>1.33</v>
+      </c>
+      <c r="AR117">
+        <v>1.09</v>
+      </c>
+      <c r="AS117">
+        <v>1.39</v>
+      </c>
+      <c r="AT117">
+        <v>2.48</v>
+      </c>
+      <c r="AU117">
+        <v>2</v>
+      </c>
+      <c r="AV117">
+        <v>7</v>
+      </c>
+      <c r="AW117">
+        <v>4</v>
+      </c>
+      <c r="AX117">
+        <v>2</v>
+      </c>
+      <c r="AY117">
+        <v>6</v>
+      </c>
+      <c r="AZ117">
+        <v>9</v>
+      </c>
+      <c r="BA117">
+        <v>7</v>
+      </c>
+      <c r="BB117">
+        <v>6</v>
+      </c>
+      <c r="BC117">
+        <v>13</v>
+      </c>
+      <c r="BD117">
+        <v>2.27</v>
+      </c>
+      <c r="BE117">
+        <v>6</v>
+      </c>
+      <c r="BF117">
+        <v>1.96</v>
+      </c>
+      <c r="BG117">
+        <v>1.49</v>
+      </c>
+      <c r="BH117">
+        <v>2.55</v>
+      </c>
+      <c r="BI117">
+        <v>1.84</v>
+      </c>
+      <c r="BJ117">
+        <v>1.95</v>
+      </c>
+      <c r="BK117">
+        <v>2.34</v>
+      </c>
+      <c r="BL117">
+        <v>1.58</v>
+      </c>
+      <c r="BM117">
+        <v>3.2</v>
+      </c>
+      <c r="BN117">
+        <v>1.3</v>
+      </c>
+      <c r="BO117">
+        <v>4.1</v>
+      </c>
+      <c r="BP117">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="118" spans="1:68">
+      <c r="A118" s="1">
+        <v>117</v>
+      </c>
+      <c r="B118">
+        <v>7813938</v>
+      </c>
+      <c r="C118" t="s">
+        <v>68</v>
+      </c>
+      <c r="D118" t="s">
+        <v>69</v>
+      </c>
+      <c r="E118" s="2">
+        <v>45830.29166666666</v>
+      </c>
+      <c r="F118">
+        <v>17</v>
+      </c>
+      <c r="G118" t="s">
+        <v>72</v>
+      </c>
+      <c r="H118" t="s">
+        <v>82</v>
+      </c>
+      <c r="I118">
+        <v>1</v>
+      </c>
+      <c r="J118">
+        <v>0</v>
+      </c>
+      <c r="K118">
+        <v>1</v>
+      </c>
+      <c r="L118">
+        <v>2</v>
+      </c>
+      <c r="M118">
+        <v>2</v>
+      </c>
+      <c r="N118">
+        <v>4</v>
+      </c>
+      <c r="O118" t="s">
+        <v>162</v>
+      </c>
+      <c r="P118" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q118">
+        <v>2.15</v>
+      </c>
+      <c r="R118">
+        <v>2.2</v>
+      </c>
+      <c r="S118">
+        <v>5.5</v>
+      </c>
+      <c r="T118">
+        <v>1.4</v>
+      </c>
+      <c r="U118">
+        <v>2.88</v>
+      </c>
+      <c r="V118">
+        <v>2.88</v>
+      </c>
+      <c r="W118">
+        <v>1.4</v>
+      </c>
+      <c r="X118">
+        <v>8</v>
+      </c>
+      <c r="Y118">
+        <v>1.08</v>
+      </c>
+      <c r="Z118">
+        <v>1.57</v>
+      </c>
+      <c r="AA118">
+        <v>3.65</v>
+      </c>
+      <c r="AB118">
+        <v>4.8</v>
+      </c>
+      <c r="AC118">
+        <v>1.01</v>
+      </c>
+      <c r="AD118">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AE118">
+        <v>1.28</v>
+      </c>
+      <c r="AF118">
+        <v>3.08</v>
+      </c>
+      <c r="AG118">
+        <v>1.95</v>
+      </c>
+      <c r="AH118">
+        <v>1.75</v>
+      </c>
+      <c r="AI118">
+        <v>1.95</v>
+      </c>
+      <c r="AJ118">
+        <v>1.8</v>
+      </c>
+      <c r="AK118">
+        <v>1.18</v>
+      </c>
+      <c r="AL118">
+        <v>1.3</v>
+      </c>
+      <c r="AM118">
+        <v>2.1</v>
+      </c>
+      <c r="AN118">
+        <v>1.22</v>
+      </c>
+      <c r="AO118">
+        <v>1</v>
+      </c>
+      <c r="AP118">
+        <v>1.2</v>
+      </c>
+      <c r="AQ118">
+        <v>1</v>
+      </c>
+      <c r="AR118">
+        <v>1.65</v>
+      </c>
+      <c r="AS118">
+        <v>1.25</v>
+      </c>
+      <c r="AT118">
+        <v>2.9</v>
+      </c>
+      <c r="AU118">
+        <v>7</v>
+      </c>
+      <c r="AV118">
+        <v>5</v>
+      </c>
+      <c r="AW118">
+        <v>3</v>
+      </c>
+      <c r="AX118">
+        <v>2</v>
+      </c>
+      <c r="AY118">
+        <v>10</v>
+      </c>
+      <c r="AZ118">
+        <v>7</v>
+      </c>
+      <c r="BA118">
+        <v>6</v>
+      </c>
+      <c r="BB118">
+        <v>3</v>
+      </c>
+      <c r="BC118">
+        <v>9</v>
+      </c>
+      <c r="BD118">
+        <v>1.44</v>
+      </c>
+      <c r="BE118">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF118">
+        <v>3.32</v>
+      </c>
+      <c r="BG118">
+        <v>1.53</v>
+      </c>
+      <c r="BH118">
+        <v>2.45</v>
+      </c>
+      <c r="BI118">
+        <v>1.92</v>
+      </c>
+      <c r="BJ118">
+        <v>1.88</v>
+      </c>
+      <c r="BK118">
+        <v>2.48</v>
+      </c>
+      <c r="BL118">
+        <v>1.52</v>
+      </c>
+      <c r="BM118">
+        <v>3.28</v>
+      </c>
+      <c r="BN118">
+        <v>1.25</v>
+      </c>
+      <c r="BO118">
+        <v>4.3</v>
+      </c>
+      <c r="BP118">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="119" spans="1:68">
+      <c r="A119" s="1">
+        <v>118</v>
+      </c>
+      <c r="B119">
+        <v>7813939</v>
+      </c>
+      <c r="C119" t="s">
+        <v>68</v>
+      </c>
+      <c r="D119" t="s">
+        <v>69</v>
+      </c>
+      <c r="E119" s="2">
+        <v>45830.29166666666</v>
+      </c>
+      <c r="F119">
+        <v>17</v>
+      </c>
+      <c r="G119" t="s">
+        <v>80</v>
+      </c>
+      <c r="H119" t="s">
+        <v>79</v>
+      </c>
+      <c r="I119">
+        <v>0</v>
+      </c>
+      <c r="J119">
+        <v>1</v>
+      </c>
+      <c r="K119">
+        <v>1</v>
+      </c>
+      <c r="L119">
+        <v>1</v>
+      </c>
+      <c r="M119">
+        <v>3</v>
+      </c>
+      <c r="N119">
+        <v>4</v>
+      </c>
+      <c r="O119" t="s">
+        <v>92</v>
+      </c>
+      <c r="P119" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q119">
+        <v>4.4</v>
+      </c>
+      <c r="R119">
+        <v>2.4</v>
+      </c>
+      <c r="S119">
+        <v>2.2</v>
+      </c>
+      <c r="T119">
+        <v>1.29</v>
+      </c>
+      <c r="U119">
+        <v>3.5</v>
+      </c>
+      <c r="V119">
+        <v>2.3</v>
+      </c>
+      <c r="W119">
+        <v>1.55</v>
+      </c>
+      <c r="X119">
+        <v>5.5</v>
+      </c>
+      <c r="Y119">
+        <v>1.14</v>
+      </c>
+      <c r="Z119">
+        <v>3.98</v>
+      </c>
+      <c r="AA119">
+        <v>3.93</v>
+      </c>
+      <c r="AB119">
+        <v>1.63</v>
+      </c>
+      <c r="AC119">
+        <v>1.01</v>
+      </c>
+      <c r="AD119">
+        <v>13</v>
+      </c>
+      <c r="AE119">
+        <v>1.14</v>
+      </c>
+      <c r="AF119">
+        <v>4.4</v>
+      </c>
+      <c r="AG119">
+        <v>1.57</v>
+      </c>
+      <c r="AH119">
+        <v>2.15</v>
+      </c>
+      <c r="AI119">
+        <v>1.62</v>
+      </c>
+      <c r="AJ119">
+        <v>2.25</v>
+      </c>
+      <c r="AK119">
+        <v>2.3</v>
+      </c>
+      <c r="AL119">
+        <v>1.22</v>
+      </c>
+      <c r="AM119">
+        <v>1.17</v>
+      </c>
+      <c r="AN119">
+        <v>1.25</v>
+      </c>
+      <c r="AO119">
+        <v>1.57</v>
+      </c>
+      <c r="AP119">
+        <v>1.1</v>
+      </c>
+      <c r="AQ119">
+        <v>1.89</v>
+      </c>
+      <c r="AR119">
+        <v>1.71</v>
+      </c>
+      <c r="AS119">
+        <v>1.7</v>
+      </c>
+      <c r="AT119">
+        <v>3.41</v>
+      </c>
+      <c r="AU119">
+        <v>5</v>
+      </c>
+      <c r="AV119">
+        <v>8</v>
+      </c>
+      <c r="AW119">
+        <v>6</v>
+      </c>
+      <c r="AX119">
+        <v>6</v>
+      </c>
+      <c r="AY119">
+        <v>11</v>
+      </c>
+      <c r="AZ119">
+        <v>14</v>
+      </c>
+      <c r="BA119">
+        <v>7</v>
+      </c>
+      <c r="BB119">
+        <v>5</v>
+      </c>
+      <c r="BC119">
+        <v>12</v>
+      </c>
+      <c r="BD119">
+        <v>2.76</v>
+      </c>
+      <c r="BE119">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF119">
+        <v>1.58</v>
+      </c>
+      <c r="BG119">
+        <v>1.32</v>
+      </c>
+      <c r="BH119">
+        <v>2.88</v>
+      </c>
+      <c r="BI119">
+        <v>1.6</v>
+      </c>
+      <c r="BJ119">
+        <v>2.26</v>
+      </c>
+      <c r="BK119">
+        <v>1.99</v>
+      </c>
+      <c r="BL119">
+        <v>1.81</v>
+      </c>
+      <c r="BM119">
+        <v>2.53</v>
+      </c>
+      <c r="BN119">
+        <v>1.49</v>
+      </c>
+      <c r="BO119">
+        <v>3.78</v>
+      </c>
+      <c r="BP119">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="120" spans="1:68">
+      <c r="A120" s="1">
+        <v>119</v>
+      </c>
+      <c r="B120">
+        <v>7813937</v>
+      </c>
+      <c r="C120" t="s">
+        <v>68</v>
+      </c>
+      <c r="D120" t="s">
+        <v>69</v>
+      </c>
+      <c r="E120" s="2">
+        <v>45830.29166666666</v>
+      </c>
+      <c r="F120">
+        <v>17</v>
+      </c>
+      <c r="G120" t="s">
+        <v>83</v>
+      </c>
+      <c r="H120" t="s">
+        <v>78</v>
+      </c>
+      <c r="I120">
+        <v>0</v>
+      </c>
+      <c r="J120">
+        <v>0</v>
+      </c>
+      <c r="K120">
+        <v>0</v>
+      </c>
+      <c r="L120">
+        <v>0</v>
+      </c>
+      <c r="M120">
+        <v>0</v>
+      </c>
+      <c r="N120">
+        <v>0</v>
+      </c>
+      <c r="O120" t="s">
+        <v>85</v>
+      </c>
+      <c r="P120" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q120">
+        <v>2.9</v>
+      </c>
+      <c r="R120">
+        <v>2.1</v>
+      </c>
+      <c r="S120">
+        <v>3.6</v>
+      </c>
+      <c r="T120">
+        <v>1.4</v>
+      </c>
+      <c r="U120">
+        <v>2.8</v>
+      </c>
+      <c r="V120">
+        <v>3</v>
+      </c>
+      <c r="W120">
+        <v>1.36</v>
+      </c>
+      <c r="X120">
+        <v>8.5</v>
+      </c>
+      <c r="Y120">
+        <v>1.07</v>
+      </c>
+      <c r="Z120">
+        <v>2.22</v>
+      </c>
+      <c r="AA120">
+        <v>3.1</v>
+      </c>
+      <c r="AB120">
+        <v>2.88</v>
+      </c>
+      <c r="AC120">
+        <v>1.05</v>
+      </c>
+      <c r="AD120">
+        <v>8</v>
+      </c>
+      <c r="AE120">
+        <v>1.3</v>
+      </c>
+      <c r="AF120">
+        <v>2.97</v>
+      </c>
+      <c r="AG120">
+        <v>2</v>
+      </c>
+      <c r="AH120">
+        <v>1.65</v>
+      </c>
+      <c r="AI120">
+        <v>1.83</v>
+      </c>
+      <c r="AJ120">
+        <v>1.91</v>
+      </c>
+      <c r="AK120">
+        <v>1.36</v>
+      </c>
+      <c r="AL120">
+        <v>1.35</v>
+      </c>
+      <c r="AM120">
+        <v>1.57</v>
+      </c>
+      <c r="AN120">
+        <v>2</v>
+      </c>
+      <c r="AO120">
+        <v>1.14</v>
+      </c>
+      <c r="AP120">
+        <v>2</v>
+      </c>
+      <c r="AQ120">
+        <v>1.13</v>
+      </c>
+      <c r="AR120">
+        <v>1.62</v>
+      </c>
+      <c r="AS120">
+        <v>1.31</v>
+      </c>
+      <c r="AT120">
+        <v>2.93</v>
+      </c>
+      <c r="AU120">
+        <v>3</v>
+      </c>
+      <c r="AV120">
+        <v>0</v>
+      </c>
+      <c r="AW120">
+        <v>4</v>
+      </c>
+      <c r="AX120">
+        <v>2</v>
+      </c>
+      <c r="AY120">
+        <v>7</v>
+      </c>
+      <c r="AZ120">
+        <v>2</v>
+      </c>
+      <c r="BA120">
+        <v>1</v>
+      </c>
+      <c r="BB120">
+        <v>4</v>
+      </c>
+      <c r="BC120">
+        <v>5</v>
+      </c>
+      <c r="BD120">
+        <v>2.1</v>
+      </c>
+      <c r="BE120">
+        <v>5.95</v>
+      </c>
+      <c r="BF120">
+        <v>2.11</v>
+      </c>
+      <c r="BG120">
+        <v>1.48</v>
+      </c>
+      <c r="BH120">
+        <v>2.58</v>
+      </c>
+      <c r="BI120">
+        <v>1.82</v>
+      </c>
+      <c r="BJ120">
+        <v>1.98</v>
+      </c>
+      <c r="BK120">
+        <v>2.3</v>
+      </c>
+      <c r="BL120">
+        <v>1.58</v>
+      </c>
+      <c r="BM120">
+        <v>3.08</v>
+      </c>
+      <c r="BN120">
+        <v>1.28</v>
+      </c>
+      <c r="BO120">
+        <v>4.1</v>
+      </c>
+      <c r="BP120">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="121" spans="1:68">
+      <c r="A121" s="1">
+        <v>120</v>
+      </c>
+      <c r="B121">
+        <v>7813940</v>
+      </c>
+      <c r="C121" t="s">
+        <v>68</v>
+      </c>
+      <c r="D121" t="s">
+        <v>69</v>
+      </c>
+      <c r="E121" s="2">
+        <v>45836.29166666666</v>
+      </c>
+      <c r="F121">
+        <v>18</v>
+      </c>
+      <c r="G121" t="s">
+        <v>81</v>
+      </c>
+      <c r="H121" t="s">
+        <v>75</v>
+      </c>
+      <c r="I121">
+        <v>1</v>
+      </c>
+      <c r="J121">
+        <v>0</v>
+      </c>
+      <c r="K121">
+        <v>1</v>
+      </c>
+      <c r="L121">
+        <v>1</v>
+      </c>
+      <c r="M121">
+        <v>1</v>
+      </c>
+      <c r="N121">
+        <v>2</v>
+      </c>
+      <c r="O121" t="s">
+        <v>163</v>
+      </c>
+      <c r="P121" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q121">
+        <v>2.93</v>
+      </c>
+      <c r="R121">
+        <v>2.15</v>
+      </c>
+      <c r="S121">
+        <v>3.22</v>
+      </c>
+      <c r="T121">
+        <v>1.31</v>
+      </c>
+      <c r="U121">
+        <v>3.14</v>
+      </c>
+      <c r="V121">
+        <v>2.58</v>
+      </c>
+      <c r="W121">
+        <v>1.44</v>
+      </c>
+      <c r="X121">
+        <v>6.65</v>
+      </c>
+      <c r="Y121">
+        <v>1.05</v>
+      </c>
+      <c r="Z121">
+        <v>2.35</v>
+      </c>
+      <c r="AA121">
+        <v>3.2</v>
+      </c>
+      <c r="AB121">
+        <v>2.62</v>
+      </c>
+      <c r="AC121">
+        <v>1.01</v>
+      </c>
+      <c r="AD121">
+        <v>11</v>
+      </c>
+      <c r="AE121">
+        <v>1.18</v>
+      </c>
+      <c r="AF121">
+        <v>3.86</v>
+      </c>
+      <c r="AG121">
+        <v>1.81</v>
+      </c>
+      <c r="AH121">
+        <v>1.89</v>
+      </c>
+      <c r="AI121">
+        <v>1.59</v>
+      </c>
+      <c r="AJ121">
+        <v>2.15</v>
+      </c>
+      <c r="AK121">
+        <v>1.41</v>
+      </c>
+      <c r="AL121">
+        <v>1.26</v>
+      </c>
+      <c r="AM121">
+        <v>1.5</v>
+      </c>
+      <c r="AN121">
+        <v>1.5</v>
+      </c>
+      <c r="AO121">
+        <v>1.38</v>
+      </c>
+      <c r="AP121">
+        <v>1.3</v>
+      </c>
+      <c r="AQ121">
+        <v>1.2</v>
+      </c>
+      <c r="AR121">
+        <v>1.8</v>
+      </c>
+      <c r="AS121">
+        <v>1.35</v>
+      </c>
+      <c r="AT121">
+        <v>3.15</v>
+      </c>
+      <c r="AU121">
+        <v>5</v>
+      </c>
+      <c r="AV121">
+        <v>4</v>
+      </c>
+      <c r="AW121">
+        <v>4</v>
+      </c>
+      <c r="AX121">
+        <v>7</v>
+      </c>
+      <c r="AY121">
+        <v>9</v>
+      </c>
+      <c r="AZ121">
+        <v>11</v>
+      </c>
+      <c r="BA121">
+        <v>1</v>
+      </c>
+      <c r="BB121">
+        <v>0</v>
+      </c>
+      <c r="BC121">
+        <v>1</v>
+      </c>
+      <c r="BD121">
+        <v>1.92</v>
+      </c>
+      <c r="BE121">
+        <v>6</v>
+      </c>
+      <c r="BF121">
+        <v>2.32</v>
+      </c>
+      <c r="BG121">
+        <v>1.4</v>
+      </c>
+      <c r="BH121">
+        <v>2.56</v>
+      </c>
+      <c r="BI121">
+        <v>1.95</v>
+      </c>
+      <c r="BJ121">
+        <v>1.85</v>
+      </c>
+      <c r="BK121">
+        <v>2.26</v>
+      </c>
+      <c r="BL121">
+        <v>1.51</v>
+      </c>
+      <c r="BM121">
+        <v>3.08</v>
+      </c>
+      <c r="BN121">
+        <v>1.28</v>
+      </c>
+      <c r="BO121">
+        <v>3.95</v>
+      </c>
+      <c r="BP121">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="122" spans="1:68">
+      <c r="A122" s="1">
+        <v>121</v>
+      </c>
+      <c r="B122">
+        <v>7813941</v>
+      </c>
+      <c r="C122" t="s">
+        <v>68</v>
+      </c>
+      <c r="D122" t="s">
+        <v>69</v>
+      </c>
+      <c r="E122" s="2">
+        <v>45836.29166666666</v>
+      </c>
+      <c r="F122">
+        <v>18</v>
+      </c>
+      <c r="G122" t="s">
+        <v>76</v>
+      </c>
+      <c r="H122" t="s">
+        <v>80</v>
+      </c>
+      <c r="I122">
+        <v>2</v>
+      </c>
+      <c r="J122">
+        <v>0</v>
+      </c>
+      <c r="K122">
+        <v>2</v>
+      </c>
+      <c r="L122">
+        <v>2</v>
+      </c>
+      <c r="M122">
+        <v>0</v>
+      </c>
+      <c r="N122">
+        <v>2</v>
+      </c>
+      <c r="O122" t="s">
+        <v>164</v>
+      </c>
+      <c r="P122" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q122">
+        <v>2.24</v>
+      </c>
+      <c r="R122">
+        <v>2.23</v>
+      </c>
+      <c r="S122">
+        <v>4.78</v>
+      </c>
+      <c r="T122">
+        <v>1.3</v>
+      </c>
+      <c r="U122">
+        <v>3.2</v>
+      </c>
+      <c r="V122">
+        <v>2.55</v>
+      </c>
+      <c r="W122">
+        <v>1.45</v>
+      </c>
+      <c r="X122">
+        <v>6.4</v>
+      </c>
+      <c r="Y122">
+        <v>1.05</v>
+      </c>
+      <c r="Z122">
+        <v>1.75</v>
+      </c>
+      <c r="AA122">
+        <v>3.59</v>
+      </c>
+      <c r="AB122">
+        <v>3.71</v>
+      </c>
+      <c r="AC122">
+        <v>1.02</v>
+      </c>
+      <c r="AD122">
+        <v>10</v>
+      </c>
+      <c r="AE122">
+        <v>1.22</v>
+      </c>
+      <c r="AF122">
+        <v>3.8</v>
+      </c>
+      <c r="AG122">
+        <v>1.73</v>
+      </c>
+      <c r="AH122">
+        <v>1.95</v>
+      </c>
+      <c r="AI122">
+        <v>1.67</v>
+      </c>
+      <c r="AJ122">
+        <v>2.15</v>
+      </c>
+      <c r="AK122">
+        <v>1.16</v>
+      </c>
+      <c r="AL122">
+        <v>1.21</v>
+      </c>
+      <c r="AM122">
+        <v>2.04</v>
+      </c>
+      <c r="AN122">
+        <v>1.75</v>
+      </c>
+      <c r="AO122">
+        <v>0.88</v>
+      </c>
+      <c r="AP122">
+        <v>1.89</v>
+      </c>
+      <c r="AQ122">
+        <v>0.78</v>
+      </c>
+      <c r="AR122">
+        <v>1.52</v>
+      </c>
+      <c r="AS122">
+        <v>1.1</v>
+      </c>
+      <c r="AT122">
+        <v>2.62</v>
+      </c>
+      <c r="AU122">
+        <v>9</v>
+      </c>
+      <c r="AV122">
+        <v>0</v>
+      </c>
+      <c r="AW122">
+        <v>15</v>
+      </c>
+      <c r="AX122">
+        <v>7</v>
+      </c>
+      <c r="AY122">
+        <v>24</v>
+      </c>
+      <c r="AZ122">
+        <v>7</v>
+      </c>
+      <c r="BA122">
+        <v>6</v>
+      </c>
+      <c r="BB122">
+        <v>6</v>
+      </c>
+      <c r="BC122">
+        <v>12</v>
+      </c>
+      <c r="BD122">
+        <v>1.51</v>
+      </c>
+      <c r="BE122">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF122">
+        <v>3</v>
+      </c>
+      <c r="BG122">
+        <v>1.37</v>
+      </c>
+      <c r="BH122">
+        <v>2.66</v>
+      </c>
+      <c r="BI122">
+        <v>1.8</v>
+      </c>
+      <c r="BJ122">
+        <v>2</v>
+      </c>
+      <c r="BK122">
+        <v>2.15</v>
+      </c>
+      <c r="BL122">
+        <v>1.56</v>
+      </c>
+      <c r="BM122">
+        <v>2.88</v>
+      </c>
+      <c r="BN122">
+        <v>1.32</v>
+      </c>
+      <c r="BO122">
+        <v>3.8</v>
+      </c>
+      <c r="BP122">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="123" spans="1:68">
+      <c r="A123" s="1">
+        <v>122</v>
+      </c>
+      <c r="B123">
+        <v>7813942</v>
+      </c>
+      <c r="C123" t="s">
+        <v>68</v>
+      </c>
+      <c r="D123" t="s">
+        <v>69</v>
+      </c>
+      <c r="E123" s="2">
+        <v>45836.29166666666</v>
+      </c>
+      <c r="F123">
+        <v>18</v>
+      </c>
+      <c r="G123" t="s">
+        <v>73</v>
+      </c>
+      <c r="H123" t="s">
+        <v>71</v>
+      </c>
+      <c r="I123">
+        <v>0</v>
+      </c>
+      <c r="J123">
+        <v>0</v>
+      </c>
+      <c r="K123">
+        <v>0</v>
+      </c>
+      <c r="L123">
+        <v>0</v>
+      </c>
+      <c r="M123">
+        <v>0</v>
+      </c>
+      <c r="N123">
+        <v>0</v>
+      </c>
+      <c r="O123" t="s">
+        <v>85</v>
+      </c>
+      <c r="P123" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q123">
+        <v>3</v>
+      </c>
+      <c r="R123">
+        <v>1.97</v>
+      </c>
+      <c r="S123">
+        <v>3.62</v>
+      </c>
+      <c r="T123">
+        <v>1.42</v>
+      </c>
+      <c r="U123">
+        <v>2.65</v>
+      </c>
+      <c r="V123">
+        <v>3.04</v>
+      </c>
+      <c r="W123">
+        <v>1.33</v>
+      </c>
+      <c r="X123">
+        <v>8.5</v>
+      </c>
+      <c r="Y123">
+        <v>1.01</v>
+      </c>
+      <c r="Z123">
+        <v>2.38</v>
+      </c>
+      <c r="AA123">
+        <v>3.05</v>
+      </c>
+      <c r="AB123">
+        <v>2.69</v>
+      </c>
+      <c r="AC123">
+        <v>1.03</v>
+      </c>
+      <c r="AD123">
+        <v>9</v>
+      </c>
+      <c r="AE123">
+        <v>1.28</v>
+      </c>
+      <c r="AF123">
+        <v>3.05</v>
+      </c>
+      <c r="AG123">
+        <v>2</v>
+      </c>
+      <c r="AH123">
+        <v>1.72</v>
+      </c>
+      <c r="AI123">
+        <v>1.78</v>
+      </c>
+      <c r="AJ123">
+        <v>1.88</v>
+      </c>
+      <c r="AK123">
+        <v>1.34</v>
+      </c>
+      <c r="AL123">
+        <v>1.3</v>
+      </c>
+      <c r="AM123">
+        <v>1.52</v>
+      </c>
+      <c r="AN123">
+        <v>0.78</v>
+      </c>
+      <c r="AO123">
+        <v>0.38</v>
+      </c>
+      <c r="AP123">
+        <v>0.8</v>
+      </c>
+      <c r="AQ123">
+        <v>0.44</v>
+      </c>
+      <c r="AR123">
+        <v>1.21</v>
+      </c>
+      <c r="AS123">
+        <v>1.16</v>
+      </c>
+      <c r="AT123">
+        <v>2.37</v>
+      </c>
+      <c r="AU123">
+        <v>2</v>
+      </c>
+      <c r="AV123">
+        <v>4</v>
+      </c>
+      <c r="AW123">
+        <v>2</v>
+      </c>
+      <c r="AX123">
+        <v>5</v>
+      </c>
+      <c r="AY123">
+        <v>4</v>
+      </c>
+      <c r="AZ123">
+        <v>9</v>
+      </c>
+      <c r="BA123">
+        <v>1</v>
+      </c>
+      <c r="BB123">
+        <v>6</v>
+      </c>
+      <c r="BC123">
+        <v>7</v>
+      </c>
+      <c r="BD123">
+        <v>2.01</v>
+      </c>
+      <c r="BE123">
+        <v>5.9</v>
+      </c>
+      <c r="BF123">
+        <v>2.22</v>
+      </c>
+      <c r="BG123">
+        <v>1.51</v>
+      </c>
+      <c r="BH123">
+        <v>2.26</v>
+      </c>
+      <c r="BI123">
+        <v>1.9</v>
+      </c>
+      <c r="BJ123">
+        <v>1.9</v>
+      </c>
+      <c r="BK123">
+        <v>2.56</v>
+      </c>
+      <c r="BL123">
+        <v>1.4</v>
+      </c>
+      <c r="BM123">
+        <v>3.58</v>
+      </c>
+      <c r="BN123">
+        <v>1.21</v>
+      </c>
+      <c r="BO123">
+        <v>4.9</v>
+      </c>
+      <c r="BP123">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="124" spans="1:68">
+      <c r="A124" s="1">
+        <v>123</v>
+      </c>
+      <c r="B124">
+        <v>7813943</v>
+      </c>
+      <c r="C124" t="s">
+        <v>68</v>
+      </c>
+      <c r="D124" t="s">
+        <v>69</v>
+      </c>
+      <c r="E124" s="2">
+        <v>45836.29166666666</v>
+      </c>
+      <c r="F124">
+        <v>18</v>
+      </c>
+      <c r="G124" t="s">
+        <v>77</v>
+      </c>
+      <c r="H124" t="s">
+        <v>74</v>
+      </c>
+      <c r="I124">
+        <v>0</v>
+      </c>
+      <c r="J124">
+        <v>0</v>
+      </c>
+      <c r="K124">
+        <v>0</v>
+      </c>
+      <c r="L124">
+        <v>1</v>
+      </c>
+      <c r="M124">
+        <v>0</v>
+      </c>
+      <c r="N124">
+        <v>1</v>
+      </c>
+      <c r="O124" t="s">
+        <v>165</v>
+      </c>
+      <c r="P124" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q124">
+        <v>3.22</v>
+      </c>
+      <c r="R124">
+        <v>1.97</v>
+      </c>
+      <c r="S124">
+        <v>3.34</v>
+      </c>
+      <c r="T124">
+        <v>1.44</v>
+      </c>
+      <c r="U124">
+        <v>2.57</v>
+      </c>
+      <c r="V124">
+        <v>3.14</v>
+      </c>
+      <c r="W124">
+        <v>1.31</v>
+      </c>
+      <c r="X124">
+        <v>8.1</v>
+      </c>
+      <c r="Y124">
+        <v>1.02</v>
+      </c>
+      <c r="Z124">
+        <v>2.58</v>
+      </c>
+      <c r="AA124">
+        <v>3.09</v>
+      </c>
+      <c r="AB124">
+        <v>2.45</v>
+      </c>
+      <c r="AC124">
+        <v>1.02</v>
+      </c>
+      <c r="AD124">
+        <v>7.8</v>
+      </c>
+      <c r="AE124">
+        <v>1.34</v>
+      </c>
+      <c r="AF124">
+        <v>2.78</v>
+      </c>
+      <c r="AG124">
+        <v>1.97</v>
+      </c>
+      <c r="AH124">
+        <v>1.73</v>
+      </c>
+      <c r="AI124">
+        <v>1.85</v>
+      </c>
+      <c r="AJ124">
+        <v>1.81</v>
+      </c>
+      <c r="AK124">
+        <v>1.42</v>
+      </c>
+      <c r="AL124">
+        <v>1.3</v>
+      </c>
+      <c r="AM124">
+        <v>1.43</v>
+      </c>
+      <c r="AN124">
+        <v>1.13</v>
+      </c>
+      <c r="AO124">
+        <v>1.13</v>
+      </c>
+      <c r="AP124">
+        <v>1.33</v>
+      </c>
+      <c r="AQ124">
+        <v>1</v>
+      </c>
+      <c r="AR124">
+        <v>1.38</v>
+      </c>
+      <c r="AS124">
+        <v>1.28</v>
+      </c>
+      <c r="AT124">
+        <v>2.66</v>
+      </c>
+      <c r="AU124">
+        <v>2</v>
+      </c>
+      <c r="AV124">
+        <v>5</v>
+      </c>
+      <c r="AW124">
+        <v>4</v>
+      </c>
+      <c r="AX124">
+        <v>4</v>
+      </c>
+      <c r="AY124">
+        <v>6</v>
+      </c>
+      <c r="AZ124">
+        <v>9</v>
+      </c>
+      <c r="BA124">
+        <v>3</v>
+      </c>
+      <c r="BB124">
+        <v>3</v>
+      </c>
+      <c r="BC124">
+        <v>6</v>
+      </c>
+      <c r="BD124">
+        <v>1.84</v>
+      </c>
+      <c r="BE124">
+        <v>6.1</v>
+      </c>
+      <c r="BF124">
+        <v>2.44</v>
+      </c>
+      <c r="BG124">
+        <v>1.42</v>
+      </c>
+      <c r="BH124">
+        <v>2.49</v>
+      </c>
+      <c r="BI124">
+        <v>1.85</v>
+      </c>
+      <c r="BJ124">
+        <v>1.95</v>
+      </c>
+      <c r="BK124">
+        <v>2.28</v>
+      </c>
+      <c r="BL124">
+        <v>1.5</v>
+      </c>
+      <c r="BM124">
+        <v>3.14</v>
+      </c>
+      <c r="BN124">
+        <v>1.27</v>
+      </c>
+      <c r="BO124">
+        <v>4.1</v>
+      </c>
+      <c r="BP124">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="125" spans="1:68">
+      <c r="A125" s="1">
+        <v>124</v>
+      </c>
+      <c r="B125">
+        <v>7813944</v>
+      </c>
+      <c r="C125" t="s">
+        <v>68</v>
+      </c>
+      <c r="D125" t="s">
+        <v>69</v>
+      </c>
+      <c r="E125" s="2">
+        <v>45837.29166666666</v>
+      </c>
+      <c r="F125">
+        <v>18</v>
+      </c>
+      <c r="G125" t="s">
+        <v>79</v>
+      </c>
+      <c r="H125" t="s">
+        <v>72</v>
+      </c>
+      <c r="I125">
+        <v>1</v>
+      </c>
+      <c r="J125">
+        <v>0</v>
+      </c>
+      <c r="K125">
+        <v>1</v>
+      </c>
+      <c r="L125">
+        <v>1</v>
+      </c>
+      <c r="M125">
+        <v>1</v>
+      </c>
+      <c r="N125">
+        <v>2</v>
+      </c>
+      <c r="O125" t="s">
+        <v>166</v>
+      </c>
+      <c r="P125" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q125">
+        <v>2.5</v>
+      </c>
+      <c r="R125">
+        <v>2.3</v>
+      </c>
+      <c r="S125">
+        <v>3.8</v>
+      </c>
+      <c r="T125">
+        <v>1.3</v>
+      </c>
+      <c r="U125">
+        <v>3.2</v>
+      </c>
+      <c r="V125">
+        <v>2.5</v>
+      </c>
+      <c r="W125">
+        <v>1.44</v>
+      </c>
+      <c r="X125">
+        <v>6</v>
+      </c>
+      <c r="Y125">
+        <v>1.11</v>
+      </c>
+      <c r="Z125">
+        <v>1.9</v>
+      </c>
+      <c r="AA125">
+        <v>3.45</v>
+      </c>
+      <c r="AB125">
+        <v>3.31</v>
+      </c>
+      <c r="AC125">
+        <v>1.01</v>
+      </c>
+      <c r="AD125">
+        <v>11</v>
+      </c>
+      <c r="AE125">
+        <v>1.21</v>
+      </c>
+      <c r="AF125">
+        <v>3.58</v>
+      </c>
+      <c r="AG125">
+        <v>1.81</v>
+      </c>
+      <c r="AH125">
+        <v>1.89</v>
+      </c>
+      <c r="AI125">
+        <v>1.67</v>
+      </c>
+      <c r="AJ125">
+        <v>2.1</v>
+      </c>
+      <c r="AK125">
+        <v>1.29</v>
+      </c>
+      <c r="AL125">
+        <v>1.3</v>
+      </c>
+      <c r="AM125">
+        <v>1.8</v>
+      </c>
+      <c r="AN125">
+        <v>2.22</v>
+      </c>
+      <c r="AO125">
+        <v>2.43</v>
+      </c>
+      <c r="AP125">
+        <v>2.1</v>
+      </c>
+      <c r="AQ125">
+        <v>2.25</v>
+      </c>
+      <c r="AR125">
+        <v>1.82</v>
+      </c>
+      <c r="AS125">
+        <v>1.22</v>
+      </c>
+      <c r="AT125">
+        <v>3.04</v>
+      </c>
+      <c r="AU125">
+        <v>3</v>
+      </c>
+      <c r="AV125">
+        <v>7</v>
+      </c>
+      <c r="AW125">
+        <v>9</v>
+      </c>
+      <c r="AX125">
+        <v>5</v>
+      </c>
+      <c r="AY125">
+        <v>12</v>
+      </c>
+      <c r="AZ125">
+        <v>12</v>
+      </c>
+      <c r="BA125">
+        <v>3</v>
+      </c>
+      <c r="BB125">
+        <v>7</v>
+      </c>
+      <c r="BC125">
+        <v>10</v>
+      </c>
+      <c r="BD125">
+        <v>1.67</v>
+      </c>
+      <c r="BE125">
+        <v>8</v>
+      </c>
+      <c r="BF125">
+        <v>2.54</v>
+      </c>
+      <c r="BG125">
+        <v>1.35</v>
+      </c>
+      <c r="BH125">
+        <v>2.74</v>
+      </c>
+      <c r="BI125">
+        <v>1.66</v>
+      </c>
+      <c r="BJ125">
+        <v>2.04</v>
+      </c>
+      <c r="BK125">
+        <v>2.08</v>
+      </c>
+      <c r="BL125">
+        <v>1.6</v>
+      </c>
+      <c r="BM125">
+        <v>2.81</v>
+      </c>
+      <c r="BN125">
+        <v>1.33</v>
+      </c>
+      <c r="BO125">
+        <v>3.58</v>
+      </c>
+      <c r="BP125">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="126" spans="1:68">
+      <c r="A126" s="1">
+        <v>125</v>
+      </c>
+      <c r="B126">
+        <v>7813945</v>
+      </c>
+      <c r="C126" t="s">
+        <v>68</v>
+      </c>
+      <c r="D126" t="s">
+        <v>69</v>
+      </c>
+      <c r="E126" s="2">
+        <v>45837.29166666666</v>
+      </c>
+      <c r="F126">
+        <v>18</v>
+      </c>
+      <c r="G126" t="s">
+        <v>82</v>
+      </c>
+      <c r="H126" t="s">
+        <v>83</v>
+      </c>
+      <c r="I126">
+        <v>1</v>
+      </c>
+      <c r="J126">
+        <v>0</v>
+      </c>
+      <c r="K126">
+        <v>1</v>
+      </c>
+      <c r="L126">
+        <v>2</v>
+      </c>
+      <c r="M126">
+        <v>2</v>
+      </c>
+      <c r="N126">
+        <v>4</v>
+      </c>
+      <c r="O126" t="s">
+        <v>167</v>
+      </c>
+      <c r="P126" t="s">
+        <v>237</v>
+      </c>
+      <c r="Q126">
+        <v>3.6</v>
+      </c>
+      <c r="R126">
+        <v>2.2</v>
+      </c>
+      <c r="S126">
+        <v>2.7</v>
+      </c>
+      <c r="T126">
+        <v>1.36</v>
+      </c>
+      <c r="U126">
+        <v>2.9</v>
+      </c>
+      <c r="V126">
+        <v>2.8</v>
+      </c>
+      <c r="W126">
+        <v>1.4</v>
+      </c>
+      <c r="X126">
+        <v>7</v>
+      </c>
+      <c r="Y126">
+        <v>1.08</v>
+      </c>
+      <c r="Z126">
+        <v>2.88</v>
+      </c>
+      <c r="AA126">
+        <v>3.41</v>
+      </c>
+      <c r="AB126">
+        <v>2.08</v>
+      </c>
+      <c r="AC126">
+        <v>1.01</v>
+      </c>
+      <c r="AD126">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AE126">
+        <v>1.24</v>
+      </c>
+      <c r="AF126">
+        <v>3.34</v>
+      </c>
+      <c r="AG126">
+        <v>1.87</v>
+      </c>
+      <c r="AH126">
+        <v>1.83</v>
+      </c>
+      <c r="AI126">
+        <v>1.73</v>
+      </c>
+      <c r="AJ126">
+        <v>2.05</v>
+      </c>
+      <c r="AK126">
+        <v>1.65</v>
+      </c>
+      <c r="AL126">
+        <v>1.3</v>
+      </c>
+      <c r="AM126">
+        <v>1.36</v>
+      </c>
+      <c r="AN126">
+        <v>0.33</v>
+      </c>
+      <c r="AO126">
+        <v>1.73</v>
+      </c>
+      <c r="AP126">
+        <v>0.75</v>
+      </c>
+      <c r="AQ126">
+        <v>1.67</v>
+      </c>
+      <c r="AR126">
+        <v>1.4</v>
+      </c>
+      <c r="AS126">
+        <v>1.22</v>
+      </c>
+      <c r="AT126">
+        <v>2.62</v>
+      </c>
+      <c r="AU126">
+        <v>7</v>
+      </c>
+      <c r="AV126">
+        <v>4</v>
+      </c>
+      <c r="AW126">
+        <v>5</v>
+      </c>
+      <c r="AX126">
+        <v>4</v>
+      </c>
+      <c r="AY126">
+        <v>12</v>
+      </c>
+      <c r="AZ126">
+        <v>8</v>
+      </c>
+      <c r="BA126">
+        <v>5</v>
+      </c>
+      <c r="BB126">
+        <v>3</v>
+      </c>
+      <c r="BC126">
+        <v>8</v>
+      </c>
+      <c r="BD126">
+        <v>2.26</v>
+      </c>
+      <c r="BE126">
+        <v>5.85</v>
+      </c>
+      <c r="BF126">
+        <v>1.98</v>
+      </c>
+      <c r="BG126">
+        <v>1.49</v>
+      </c>
+      <c r="BH126">
+        <v>2.3</v>
+      </c>
+      <c r="BI126">
+        <v>1.89</v>
+      </c>
+      <c r="BJ126">
+        <v>1.77</v>
+      </c>
+      <c r="BK126">
+        <v>2.49</v>
+      </c>
+      <c r="BL126">
+        <v>1.42</v>
+      </c>
+      <c r="BM126">
+        <v>3.5</v>
+      </c>
+      <c r="BN126">
+        <v>1.22</v>
+      </c>
+      <c r="BO126">
+        <v>4.5</v>
+      </c>
+      <c r="BP126">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="127" spans="1:68">
+      <c r="A127" s="1">
+        <v>126</v>
+      </c>
+      <c r="B127">
+        <v>7813946</v>
+      </c>
+      <c r="C127" t="s">
+        <v>68</v>
+      </c>
+      <c r="D127" t="s">
+        <v>69</v>
+      </c>
+      <c r="E127" s="2">
+        <v>45837.29166666666</v>
+      </c>
+      <c r="F127">
+        <v>18</v>
+      </c>
+      <c r="G127" t="s">
+        <v>78</v>
+      </c>
+      <c r="H127" t="s">
+        <v>70</v>
+      </c>
+      <c r="I127">
+        <v>1</v>
+      </c>
+      <c r="J127">
+        <v>0</v>
+      </c>
+      <c r="K127">
+        <v>1</v>
+      </c>
+      <c r="L127">
+        <v>1</v>
+      </c>
+      <c r="M127">
+        <v>1</v>
+      </c>
+      <c r="N127">
+        <v>2</v>
+      </c>
+      <c r="O127" t="s">
+        <v>168</v>
+      </c>
+      <c r="P127" t="s">
+        <v>238</v>
+      </c>
+      <c r="Q127">
+        <v>4.33</v>
+      </c>
+      <c r="R127">
+        <v>2.1</v>
+      </c>
+      <c r="S127">
+        <v>2.5</v>
+      </c>
+      <c r="T127">
+        <v>1.4</v>
+      </c>
+      <c r="U127">
+        <v>2.75</v>
+      </c>
+      <c r="V127">
+        <v>3</v>
+      </c>
+      <c r="W127">
+        <v>1.36</v>
+      </c>
+      <c r="X127">
+        <v>8.5</v>
+      </c>
+      <c r="Y127">
+        <v>1.07</v>
+      </c>
+      <c r="Z127">
+        <v>3.69</v>
+      </c>
+      <c r="AA127">
+        <v>3.21</v>
+      </c>
+      <c r="AB127">
+        <v>1.86</v>
+      </c>
+      <c r="AC127">
+        <v>1.01</v>
+      </c>
+      <c r="AD127">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AE127">
+        <v>1.34</v>
+      </c>
+      <c r="AF127">
+        <v>2.78</v>
+      </c>
+      <c r="AG127">
+        <v>2</v>
+      </c>
+      <c r="AH127">
+        <v>1.65</v>
+      </c>
+      <c r="AI127">
+        <v>1.91</v>
+      </c>
+      <c r="AJ127">
+        <v>1.83</v>
+      </c>
+      <c r="AK127">
+        <v>1.85</v>
+      </c>
+      <c r="AL127">
+        <v>1.33</v>
+      </c>
+      <c r="AM127">
+        <v>1.22</v>
+      </c>
+      <c r="AN127">
+        <v>1.22</v>
+      </c>
+      <c r="AO127">
+        <v>2.29</v>
+      </c>
+      <c r="AP127">
+        <v>1.2</v>
+      </c>
+      <c r="AQ127">
+        <v>1.89</v>
+      </c>
+      <c r="AR127">
+        <v>1.63</v>
+      </c>
+      <c r="AS127">
+        <v>1.2</v>
+      </c>
+      <c r="AT127">
+        <v>2.83</v>
+      </c>
+      <c r="AU127">
+        <v>8</v>
+      </c>
+      <c r="AV127">
+        <v>2</v>
+      </c>
+      <c r="AW127">
+        <v>2</v>
+      </c>
+      <c r="AX127">
+        <v>8</v>
+      </c>
+      <c r="AY127">
+        <v>10</v>
+      </c>
+      <c r="AZ127">
+        <v>10</v>
+      </c>
+      <c r="BA127">
+        <v>0</v>
+      </c>
+      <c r="BB127">
+        <v>4</v>
+      </c>
+      <c r="BC127">
+        <v>4</v>
+      </c>
+      <c r="BD127">
+        <v>2.26</v>
+      </c>
+      <c r="BE127">
+        <v>5.8</v>
+      </c>
+      <c r="BF127">
+        <v>1.99</v>
+      </c>
+      <c r="BG127">
+        <v>1.57</v>
+      </c>
+      <c r="BH127">
+        <v>2.14</v>
+      </c>
+      <c r="BI127">
+        <v>2.03</v>
+      </c>
+      <c r="BJ127">
+        <v>1.67</v>
+      </c>
+      <c r="BK127">
+        <v>2.7</v>
+      </c>
+      <c r="BL127">
+        <v>1.36</v>
+      </c>
+      <c r="BM127">
+        <v>3.86</v>
+      </c>
+      <c r="BN127">
+        <v>1.18</v>
+      </c>
+      <c r="BO127">
+        <v>4.95</v>
+      </c>
+      <c r="BP127">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="128" spans="1:68">
+      <c r="A128" s="1">
+        <v>127</v>
+      </c>
+      <c r="B128">
+        <v>7813947</v>
+      </c>
+      <c r="C128" t="s">
+        <v>68</v>
+      </c>
+      <c r="D128" t="s">
+        <v>69</v>
+      </c>
+      <c r="E128" s="2">
+        <v>45843.29166666666</v>
+      </c>
+      <c r="F128">
+        <v>19</v>
+      </c>
+      <c r="G128" t="s">
+        <v>81</v>
+      </c>
+      <c r="H128" t="s">
+        <v>79</v>
+      </c>
+      <c r="I128">
+        <v>0</v>
+      </c>
+      <c r="J128">
+        <v>2</v>
+      </c>
+      <c r="K128">
+        <v>2</v>
+      </c>
+      <c r="L128">
+        <v>2</v>
+      </c>
+      <c r="M128">
+        <v>3</v>
+      </c>
+      <c r="N128">
+        <v>5</v>
+      </c>
+      <c r="O128" t="s">
+        <v>169</v>
+      </c>
+      <c r="P128" t="s">
+        <v>239</v>
+      </c>
+      <c r="Q128">
+        <v>3.5</v>
+      </c>
+      <c r="R128">
+        <v>2.25</v>
+      </c>
+      <c r="S128">
+        <v>2.7</v>
+      </c>
+      <c r="T128">
+        <v>1.33</v>
+      </c>
+      <c r="U128">
+        <v>3.1</v>
+      </c>
+      <c r="V128">
+        <v>2.6</v>
+      </c>
+      <c r="W128">
+        <v>1.44</v>
+      </c>
+      <c r="X128">
+        <v>6.5</v>
+      </c>
+      <c r="Y128">
+        <v>1.11</v>
+      </c>
+      <c r="Z128">
+        <v>2.95</v>
+      </c>
+      <c r="AA128">
+        <v>3.31</v>
+      </c>
+      <c r="AB128">
+        <v>2.09</v>
+      </c>
+      <c r="AC128">
+        <v>1.01</v>
+      </c>
+      <c r="AD128">
+        <v>11</v>
+      </c>
+      <c r="AE128">
+        <v>1.17</v>
+      </c>
+      <c r="AF128">
+        <v>4.05</v>
+      </c>
+      <c r="AG128">
+        <v>1.82</v>
+      </c>
+      <c r="AH128">
+        <v>1.88</v>
+      </c>
+      <c r="AI128">
+        <v>1.65</v>
+      </c>
+      <c r="AJ128">
+        <v>2.15</v>
+      </c>
+      <c r="AK128">
+        <v>1.62</v>
+      </c>
+      <c r="AL128">
+        <v>1.3</v>
+      </c>
+      <c r="AM128">
+        <v>1.36</v>
+      </c>
+      <c r="AN128">
+        <v>1.44</v>
+      </c>
+      <c r="AO128">
+        <v>1.75</v>
+      </c>
+      <c r="AP128">
+        <v>1.3</v>
+      </c>
+      <c r="AQ128">
+        <v>1.89</v>
+      </c>
+      <c r="AR128">
+        <v>1.71</v>
+      </c>
+      <c r="AS128">
+        <v>1.71</v>
+      </c>
+      <c r="AT128">
+        <v>3.42</v>
+      </c>
+      <c r="AU128">
+        <v>9</v>
+      </c>
+      <c r="AV128">
+        <v>9</v>
+      </c>
+      <c r="AW128">
+        <v>11</v>
+      </c>
+      <c r="AX128">
+        <v>12</v>
+      </c>
+      <c r="AY128">
+        <v>20</v>
+      </c>
+      <c r="AZ128">
+        <v>21</v>
+      </c>
+      <c r="BA128">
+        <v>7</v>
+      </c>
+      <c r="BB128">
+        <v>6</v>
+      </c>
+      <c r="BC128">
+        <v>13</v>
+      </c>
+      <c r="BD128">
+        <v>2.31</v>
+      </c>
+      <c r="BE128">
+        <v>6.59</v>
+      </c>
+      <c r="BF128">
+        <v>2.01</v>
+      </c>
+      <c r="BG128">
+        <v>1.59</v>
+      </c>
+      <c r="BH128">
+        <v>2.19</v>
+      </c>
+      <c r="BI128">
+        <v>2.01</v>
+      </c>
+      <c r="BJ128">
+        <v>1.71</v>
+      </c>
+      <c r="BK128">
+        <v>2.66</v>
+      </c>
+      <c r="BL128">
+        <v>1.39</v>
+      </c>
+      <c r="BM128">
+        <v>3.79</v>
+      </c>
+      <c r="BN128">
+        <v>1.18</v>
+      </c>
+      <c r="BO128">
+        <v>5.82</v>
+      </c>
+      <c r="BP128">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="129" spans="1:68">
+      <c r="A129" s="1">
+        <v>128</v>
+      </c>
+      <c r="B129">
+        <v>7813948</v>
+      </c>
+      <c r="C129" t="s">
+        <v>68</v>
+      </c>
+      <c r="D129" t="s">
+        <v>69</v>
+      </c>
+      <c r="E129" s="2">
+        <v>45843.29166666666</v>
+      </c>
+      <c r="F129">
+        <v>19</v>
+      </c>
+      <c r="G129" t="s">
+        <v>83</v>
+      </c>
+      <c r="H129" t="s">
+        <v>70</v>
+      </c>
+      <c r="I129">
+        <v>1</v>
+      </c>
+      <c r="J129">
+        <v>1</v>
+      </c>
+      <c r="K129">
+        <v>2</v>
+      </c>
+      <c r="L129">
+        <v>2</v>
+      </c>
+      <c r="M129">
+        <v>1</v>
+      </c>
+      <c r="N129">
+        <v>3</v>
+      </c>
+      <c r="O129" t="s">
+        <v>170</v>
+      </c>
+      <c r="P129" t="s">
+        <v>240</v>
+      </c>
+      <c r="Q129">
+        <v>4.33</v>
+      </c>
+      <c r="R129">
+        <v>2.15</v>
+      </c>
+      <c r="S129">
+        <v>2.45</v>
+      </c>
+      <c r="T129">
+        <v>1.4</v>
+      </c>
+      <c r="U129">
+        <v>2.88</v>
+      </c>
+      <c r="V129">
+        <v>2.9</v>
+      </c>
+      <c r="W129">
+        <v>1.36</v>
+      </c>
+      <c r="X129">
+        <v>8</v>
+      </c>
+      <c r="Y129">
+        <v>1.08</v>
+      </c>
+      <c r="Z129">
+        <v>3.71</v>
+      </c>
+      <c r="AA129">
+        <v>3.21</v>
+      </c>
+      <c r="AB129">
+        <v>1.86</v>
+      </c>
+      <c r="AC129">
+        <v>1</v>
+      </c>
+      <c r="AD129">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE129">
+        <v>1.24</v>
+      </c>
+      <c r="AF129">
+        <v>3.34</v>
+      </c>
+      <c r="AG129">
+        <v>1.93</v>
+      </c>
+      <c r="AH129">
+        <v>1.77</v>
+      </c>
+      <c r="AI129">
+        <v>1.83</v>
+      </c>
+      <c r="AJ129">
+        <v>1.91</v>
+      </c>
+      <c r="AK129">
+        <v>1.95</v>
+      </c>
+      <c r="AL129">
+        <v>1.3</v>
+      </c>
+      <c r="AM129">
+        <v>1.2</v>
+      </c>
+      <c r="AN129">
+        <v>1.83</v>
+      </c>
+      <c r="AO129">
+        <v>2.13</v>
+      </c>
+      <c r="AP129">
+        <v>2</v>
+      </c>
+      <c r="AQ129">
+        <v>1.89</v>
+      </c>
+      <c r="AR129">
+        <v>1.53</v>
+      </c>
+      <c r="AS129">
+        <v>1.18</v>
+      </c>
+      <c r="AT129">
+        <v>2.71</v>
+      </c>
+      <c r="AU129">
+        <v>4</v>
+      </c>
+      <c r="AV129">
+        <v>4</v>
+      </c>
+      <c r="AW129">
+        <v>3</v>
+      </c>
+      <c r="AX129">
+        <v>7</v>
+      </c>
+      <c r="AY129">
+        <v>7</v>
+      </c>
+      <c r="AZ129">
+        <v>11</v>
+      </c>
+      <c r="BA129">
+        <v>2</v>
+      </c>
+      <c r="BB129">
+        <v>9</v>
+      </c>
+      <c r="BC129">
+        <v>11</v>
+      </c>
+      <c r="BD129">
+        <v>3.16</v>
+      </c>
+      <c r="BE129">
+        <v>7.06</v>
+      </c>
+      <c r="BF129">
+        <v>1.62</v>
+      </c>
+      <c r="BG129">
+        <v>1.56</v>
+      </c>
+      <c r="BH129">
+        <v>2.25</v>
+      </c>
+      <c r="BI129">
+        <v>1.96</v>
+      </c>
+      <c r="BJ129">
+        <v>1.75</v>
+      </c>
+      <c r="BK129">
+        <v>2.57</v>
+      </c>
+      <c r="BL129">
+        <v>1.42</v>
+      </c>
+      <c r="BM129">
+        <v>3.62</v>
+      </c>
+      <c r="BN129">
+        <v>1.2</v>
+      </c>
+      <c r="BO129">
+        <v>5.5</v>
+      </c>
+      <c r="BP129">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="130" spans="1:68">
+      <c r="A130" s="1">
+        <v>129</v>
+      </c>
+      <c r="B130">
+        <v>7813949</v>
+      </c>
+      <c r="C130" t="s">
+        <v>68</v>
+      </c>
+      <c r="D130" t="s">
+        <v>69</v>
+      </c>
+      <c r="E130" s="2">
+        <v>45843.29166666666</v>
+      </c>
+      <c r="F130">
+        <v>19</v>
+      </c>
+      <c r="G130" t="s">
+        <v>82</v>
+      </c>
+      <c r="H130" t="s">
+        <v>75</v>
+      </c>
+      <c r="I130">
+        <v>0</v>
+      </c>
+      <c r="J130">
+        <v>1</v>
+      </c>
+      <c r="K130">
+        <v>1</v>
+      </c>
+      <c r="L130">
+        <v>2</v>
+      </c>
+      <c r="M130">
+        <v>1</v>
+      </c>
+      <c r="N130">
+        <v>3</v>
+      </c>
+      <c r="O130" t="s">
+        <v>171</v>
+      </c>
+      <c r="P130" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q130">
+        <v>4.2</v>
+      </c>
+      <c r="R130">
+        <v>2.2</v>
+      </c>
+      <c r="S130">
+        <v>2.45</v>
+      </c>
+      <c r="T130">
+        <v>1.35</v>
+      </c>
+      <c r="U130">
+        <v>3</v>
+      </c>
+      <c r="V130">
+        <v>2.7</v>
+      </c>
+      <c r="W130">
+        <v>1.44</v>
+      </c>
+      <c r="X130">
+        <v>7</v>
+      </c>
+      <c r="Y130">
+        <v>1.1</v>
+      </c>
+      <c r="Z130">
+        <v>3.89</v>
+      </c>
+      <c r="AA130">
+        <v>3.57</v>
+      </c>
+      <c r="AB130">
+        <v>1.72</v>
+      </c>
+      <c r="AC130">
+        <v>1.01</v>
+      </c>
+      <c r="AD130">
+        <v>11</v>
+      </c>
+      <c r="AE130">
+        <v>1.22</v>
+      </c>
+      <c r="AF130">
+        <v>3.5</v>
+      </c>
+      <c r="AG130">
+        <v>1.8</v>
+      </c>
+      <c r="AH130">
+        <v>1.9</v>
+      </c>
+      <c r="AI130">
+        <v>1.75</v>
+      </c>
+      <c r="AJ130">
+        <v>2</v>
+      </c>
+      <c r="AK130">
+        <v>1.85</v>
+      </c>
+      <c r="AL130">
+        <v>1.3</v>
+      </c>
+      <c r="AM130">
+        <v>1.25</v>
+      </c>
+      <c r="AN130">
+        <v>0.43</v>
+      </c>
+      <c r="AO130">
+        <v>1.33</v>
+      </c>
+      <c r="AP130">
+        <v>0.75</v>
+      </c>
+      <c r="AQ130">
+        <v>1.2</v>
+      </c>
+      <c r="AR130">
+        <v>1.45</v>
+      </c>
+      <c r="AS130">
+        <v>1.33</v>
+      </c>
+      <c r="AT130">
+        <v>2.78</v>
+      </c>
+      <c r="AU130">
+        <v>6</v>
+      </c>
+      <c r="AV130">
+        <v>3</v>
+      </c>
+      <c r="AW130">
+        <v>7</v>
+      </c>
+      <c r="AX130">
+        <v>8</v>
+      </c>
+      <c r="AY130">
+        <v>13</v>
+      </c>
+      <c r="AZ130">
+        <v>11</v>
+      </c>
+      <c r="BA130">
+        <v>1</v>
+      </c>
+      <c r="BB130">
+        <v>1</v>
+      </c>
+      <c r="BC130">
+        <v>2</v>
+      </c>
+      <c r="BD130">
+        <v>3.07</v>
+      </c>
+      <c r="BE130">
+        <v>6.9</v>
+      </c>
+      <c r="BF130">
+        <v>1.65</v>
+      </c>
+      <c r="BG130">
+        <v>1.64</v>
+      </c>
+      <c r="BH130">
+        <v>2.12</v>
+      </c>
+      <c r="BI130">
+        <v>2.08</v>
+      </c>
+      <c r="BJ130">
+        <v>1.66</v>
+      </c>
+      <c r="BK130">
+        <v>2.78</v>
+      </c>
+      <c r="BL130">
+        <v>1.36</v>
+      </c>
+      <c r="BM130">
+        <v>4.01</v>
+      </c>
+      <c r="BN130">
+        <v>1.16</v>
+      </c>
+      <c r="BO130">
+        <v>6.25</v>
+      </c>
+      <c r="BP130">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="131" spans="1:68">
+      <c r="A131" s="1">
+        <v>130</v>
+      </c>
+      <c r="B131">
+        <v>7813950</v>
+      </c>
+      <c r="C131" t="s">
+        <v>68</v>
+      </c>
+      <c r="D131" t="s">
+        <v>69</v>
+      </c>
+      <c r="E131" s="2">
+        <v>45843.29166666666</v>
+      </c>
+      <c r="F131">
+        <v>19</v>
+      </c>
+      <c r="G131" t="s">
+        <v>80</v>
+      </c>
+      <c r="H131" t="s">
+        <v>73</v>
+      </c>
+      <c r="I131">
+        <v>1</v>
+      </c>
+      <c r="J131">
+        <v>1</v>
+      </c>
+      <c r="K131">
+        <v>2</v>
+      </c>
+      <c r="L131">
+        <v>1</v>
+      </c>
+      <c r="M131">
+        <v>1</v>
+      </c>
+      <c r="N131">
+        <v>2</v>
+      </c>
+      <c r="O131" t="s">
+        <v>172</v>
+      </c>
+      <c r="P131" t="s">
+        <v>242</v>
+      </c>
+      <c r="Q131">
+        <v>2.8</v>
+      </c>
+      <c r="R131">
+        <v>2.1</v>
+      </c>
+      <c r="S131">
+        <v>3.6</v>
+      </c>
+      <c r="T131">
+        <v>1.4</v>
+      </c>
+      <c r="U131">
+        <v>2.8</v>
+      </c>
+      <c r="V131">
+        <v>2.9</v>
+      </c>
+      <c r="W131">
+        <v>1.36</v>
+      </c>
+      <c r="X131">
+        <v>7.5</v>
+      </c>
+      <c r="Y131">
+        <v>1.08</v>
+      </c>
+      <c r="Z131">
+        <v>2.2</v>
+      </c>
+      <c r="AA131">
+        <v>3.17</v>
+      </c>
+      <c r="AB131">
+        <v>2.86</v>
+      </c>
+      <c r="AC131">
+        <v>1.01</v>
+      </c>
+      <c r="AD131">
+        <v>8.4</v>
+      </c>
+      <c r="AE131">
+        <v>1.28</v>
+      </c>
+      <c r="AF131">
+        <v>3.08</v>
+      </c>
+      <c r="AG131">
+        <v>1.95</v>
+      </c>
+      <c r="AH131">
+        <v>1.75</v>
+      </c>
+      <c r="AI131">
+        <v>1.75</v>
+      </c>
+      <c r="AJ131">
+        <v>2</v>
+      </c>
+      <c r="AK131">
+        <v>1.36</v>
+      </c>
+      <c r="AL131">
+        <v>1.35</v>
+      </c>
+      <c r="AM131">
+        <v>1.6</v>
+      </c>
+      <c r="AN131">
+        <v>1.11</v>
+      </c>
+      <c r="AO131">
+        <v>1.13</v>
+      </c>
+      <c r="AP131">
+        <v>1.1</v>
+      </c>
+      <c r="AQ131">
+        <v>1.11</v>
+      </c>
+      <c r="AR131">
+        <v>1.67</v>
+      </c>
+      <c r="AS131">
+        <v>1.03</v>
+      </c>
+      <c r="AT131">
+        <v>2.7</v>
+      </c>
+      <c r="AU131">
+        <v>6</v>
+      </c>
+      <c r="AV131">
+        <v>6</v>
+      </c>
+      <c r="AW131">
+        <v>4</v>
+      </c>
+      <c r="AX131">
+        <v>1</v>
+      </c>
+      <c r="AY131">
+        <v>10</v>
+      </c>
+      <c r="AZ131">
+        <v>7</v>
+      </c>
+      <c r="BA131">
+        <v>2</v>
+      </c>
+      <c r="BB131">
+        <v>2</v>
+      </c>
+      <c r="BC131">
+        <v>4</v>
+      </c>
+      <c r="BD131">
+        <v>1.68</v>
+      </c>
+      <c r="BE131">
         <v>6.88</v>
       </c>
-      <c r="BF100">
+      <c r="BF131">
         <v>2.98</v>
       </c>
-      <c r="BG100">
+      <c r="BG131">
         <v>1.61</v>
       </c>
-      <c r="BH100">
+      <c r="BH131">
         <v>2.15</v>
       </c>
-      <c r="BI100">
+      <c r="BI131">
         <v>2.04</v>
       </c>
-      <c r="BJ100">
+      <c r="BJ131">
         <v>1.69</v>
       </c>
-      <c r="BK100">
+      <c r="BK131">
         <v>2.71</v>
       </c>
-      <c r="BL100">
+      <c r="BL131">
         <v>1.37</v>
       </c>
-      <c r="BM100">
+      <c r="BM131">
         <v>3.88</v>
       </c>
-      <c r="BN100">
+      <c r="BN131">
         <v>1.17</v>
       </c>
-      <c r="BO100">
+      <c r="BO131">
         <v>6.01</v>
       </c>
-      <c r="BP100">
+      <c r="BP131">
         <v>1.04</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="244">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -533,6 +533,9 @@
   </si>
   <si>
     <t>['45+5']</t>
+  </si>
+  <si>
+    <t>['32', '63', '75']</t>
   </si>
   <si>
     <t>['1', '6']</t>
@@ -1104,7 +1107,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP131"/>
+  <dimension ref="A1:BP134"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1566,7 +1569,7 @@
         <v>85</v>
       </c>
       <c r="P3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q3">
         <v>3.8</v>
@@ -2262,7 +2265,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ6">
         <v>0.44</v>
@@ -2596,7 +2599,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q8">
         <v>2.39</v>
@@ -3008,7 +3011,7 @@
         <v>85</v>
       </c>
       <c r="P10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q10">
         <v>4.3</v>
@@ -3214,7 +3217,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q11">
         <v>2.8</v>
@@ -3498,7 +3501,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ12">
         <v>1.33</v>
@@ -3626,7 +3629,7 @@
         <v>85</v>
       </c>
       <c r="P13" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q13">
         <v>2.43</v>
@@ -3832,7 +3835,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q14">
         <v>3.9</v>
@@ -3913,7 +3916,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ14">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR14">
         <v>1.15</v>
@@ -4116,7 +4119,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ15">
         <v>1</v>
@@ -4244,7 +4247,7 @@
         <v>85</v>
       </c>
       <c r="P16" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q16">
         <v>3.18</v>
@@ -4325,7 +4328,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ16">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AR16">
         <v>1.61</v>
@@ -4450,7 +4453,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q17">
         <v>3</v>
@@ -4528,7 +4531,7 @@
         <v>1.5</v>
       </c>
       <c r="AP17">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ17">
         <v>0.78</v>
@@ -4862,7 +4865,7 @@
         <v>95</v>
       </c>
       <c r="P19" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q19">
         <v>2.71</v>
@@ -4940,7 +4943,7 @@
         <v>0.5</v>
       </c>
       <c r="AP19">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ19">
         <v>1</v>
@@ -5068,7 +5071,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q20">
         <v>3.5</v>
@@ -5480,7 +5483,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q22">
         <v>5</v>
@@ -5558,7 +5561,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ22">
         <v>1.89</v>
@@ -5970,7 +5973,7 @@
         <v>1.33</v>
       </c>
       <c r="AP24">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ24">
         <v>1</v>
@@ -6176,7 +6179,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ25">
         <v>1</v>
@@ -6510,7 +6513,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q27">
         <v>2.25</v>
@@ -6591,7 +6594,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ27">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR27">
         <v>1.42</v>
@@ -6716,7 +6719,7 @@
         <v>101</v>
       </c>
       <c r="P28" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q28">
         <v>4</v>
@@ -6922,7 +6925,7 @@
         <v>102</v>
       </c>
       <c r="P29" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q29">
         <v>2.2</v>
@@ -7128,7 +7131,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q30">
         <v>3.75</v>
@@ -7334,7 +7337,7 @@
         <v>104</v>
       </c>
       <c r="P31" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q31">
         <v>3.25</v>
@@ -7746,7 +7749,7 @@
         <v>91</v>
       </c>
       <c r="P33" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q33">
         <v>2.63</v>
@@ -7827,7 +7830,7 @@
         <v>2.8</v>
       </c>
       <c r="AQ33">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AR33">
         <v>1.69</v>
@@ -7952,7 +7955,7 @@
         <v>85</v>
       </c>
       <c r="P34" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q34">
         <v>3.8</v>
@@ -8158,7 +8161,7 @@
         <v>106</v>
       </c>
       <c r="P35" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q35">
         <v>2.8</v>
@@ -8239,7 +8242,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ35">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR35">
         <v>1.05</v>
@@ -8651,7 +8654,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ37">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR37">
         <v>1.11</v>
@@ -8776,7 +8779,7 @@
         <v>85</v>
       </c>
       <c r="P38" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q38">
         <v>5</v>
@@ -8854,7 +8857,7 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ38">
         <v>1.89</v>
@@ -8982,7 +8985,7 @@
         <v>85</v>
       </c>
       <c r="P39" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q39">
         <v>3.1</v>
@@ -9394,7 +9397,7 @@
         <v>110</v>
       </c>
       <c r="P41" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q41">
         <v>3.25</v>
@@ -9472,10 +9475,10 @@
         <v>1.5</v>
       </c>
       <c r="AP41">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ41">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR41">
         <v>1.52</v>
@@ -9600,7 +9603,7 @@
         <v>111</v>
       </c>
       <c r="P42" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q42">
         <v>2.5</v>
@@ -9884,7 +9887,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ43">
         <v>1.11</v>
@@ -10012,7 +10015,7 @@
         <v>113</v>
       </c>
       <c r="P44" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q44">
         <v>3.4</v>
@@ -10090,7 +10093,7 @@
         <v>0.5</v>
       </c>
       <c r="AP44">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ44">
         <v>1.33</v>
@@ -10218,7 +10221,7 @@
         <v>113</v>
       </c>
       <c r="P45" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q45">
         <v>3.75</v>
@@ -10296,7 +10299,7 @@
         <v>1.83</v>
       </c>
       <c r="AP45">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ45">
         <v>1.67</v>
@@ -10424,7 +10427,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q46">
         <v>3.75</v>
@@ -10630,7 +10633,7 @@
         <v>85</v>
       </c>
       <c r="P47" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q47">
         <v>3</v>
@@ -11042,7 +11045,7 @@
         <v>116</v>
       </c>
       <c r="P49" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -11454,7 +11457,7 @@
         <v>85</v>
       </c>
       <c r="P51" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q51">
         <v>2.25</v>
@@ -11741,7 +11744,7 @@
         <v>2.8</v>
       </c>
       <c r="AQ52">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR52">
         <v>1.66</v>
@@ -12150,10 +12153,10 @@
         <v>2</v>
       </c>
       <c r="AP54">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ54">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR54">
         <v>1.1</v>
@@ -12278,7 +12281,7 @@
         <v>119</v>
       </c>
       <c r="P55" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q55">
         <v>5</v>
@@ -12359,7 +12362,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ55">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AR55">
         <v>1.32</v>
@@ -12690,7 +12693,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q57">
         <v>3.75</v>
@@ -12896,7 +12899,7 @@
         <v>121</v>
       </c>
       <c r="P58" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q58">
         <v>2.3</v>
@@ -13102,7 +13105,7 @@
         <v>85</v>
       </c>
       <c r="P59" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q59">
         <v>3.2</v>
@@ -13514,7 +13517,7 @@
         <v>123</v>
       </c>
       <c r="P61" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q61">
         <v>4</v>
@@ -13720,7 +13723,7 @@
         <v>124</v>
       </c>
       <c r="P62" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q62">
         <v>2.3</v>
@@ -13926,7 +13929,7 @@
         <v>85</v>
       </c>
       <c r="P63" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q63">
         <v>3.2</v>
@@ -14004,7 +14007,7 @@
         <v>1.88</v>
       </c>
       <c r="AP63">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ63">
         <v>1.67</v>
@@ -14132,7 +14135,7 @@
         <v>125</v>
       </c>
       <c r="P64" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q64">
         <v>2.5</v>
@@ -14338,7 +14341,7 @@
         <v>126</v>
       </c>
       <c r="P65" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q65">
         <v>4</v>
@@ -14416,7 +14419,7 @@
         <v>0.5</v>
       </c>
       <c r="AP65">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ65">
         <v>1.2</v>
@@ -14544,7 +14547,7 @@
         <v>127</v>
       </c>
       <c r="P66" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q66">
         <v>3</v>
@@ -14956,7 +14959,7 @@
         <v>129</v>
       </c>
       <c r="P68" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q68">
         <v>5</v>
@@ -15574,7 +15577,7 @@
         <v>132</v>
       </c>
       <c r="P71" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q71">
         <v>2.63</v>
@@ -15652,10 +15655,10 @@
         <v>0</v>
       </c>
       <c r="AP71">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ71">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR71">
         <v>1.45</v>
@@ -15858,7 +15861,7 @@
         <v>0.25</v>
       </c>
       <c r="AP72">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ72">
         <v>0.44</v>
@@ -15986,7 +15989,7 @@
         <v>85</v>
       </c>
       <c r="P73" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q73">
         <v>3.6</v>
@@ -16067,7 +16070,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ73">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR73">
         <v>1.77</v>
@@ -16192,7 +16195,7 @@
         <v>85</v>
       </c>
       <c r="P74" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q74">
         <v>4.33</v>
@@ -16398,7 +16401,7 @@
         <v>134</v>
       </c>
       <c r="P75" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q75">
         <v>1.91</v>
@@ -16604,7 +16607,7 @@
         <v>135</v>
       </c>
       <c r="P76" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q76">
         <v>2.63</v>
@@ -16810,7 +16813,7 @@
         <v>85</v>
       </c>
       <c r="P77" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q77">
         <v>4.5</v>
@@ -16891,7 +16894,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ77">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AR77">
         <v>1.89</v>
@@ -17097,7 +17100,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ78">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR78">
         <v>1.79</v>
@@ -17222,7 +17225,7 @@
         <v>137</v>
       </c>
       <c r="P79" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q79">
         <v>3.6</v>
@@ -17840,7 +17843,7 @@
         <v>140</v>
       </c>
       <c r="P82" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q82">
         <v>3.75</v>
@@ -18046,7 +18049,7 @@
         <v>85</v>
       </c>
       <c r="P83" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q83">
         <v>7.5</v>
@@ -18458,7 +18461,7 @@
         <v>142</v>
       </c>
       <c r="P85" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q85">
         <v>3.75</v>
@@ -18536,7 +18539,7 @@
         <v>1.33</v>
       </c>
       <c r="AP85">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ85">
         <v>1.2</v>
@@ -18664,7 +18667,7 @@
         <v>85</v>
       </c>
       <c r="P86" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q86">
         <v>4.2</v>
@@ -18742,7 +18745,7 @@
         <v>1.75</v>
       </c>
       <c r="AP86">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ86">
         <v>1.2</v>
@@ -19154,10 +19157,10 @@
         <v>2.5</v>
       </c>
       <c r="AP88">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ88">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AR88">
         <v>1.04</v>
@@ -19282,7 +19285,7 @@
         <v>143</v>
       </c>
       <c r="P89" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q89">
         <v>2.62</v>
@@ -19363,7 +19366,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ89">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR89">
         <v>1.79</v>
@@ -19488,7 +19491,7 @@
         <v>144</v>
       </c>
       <c r="P90" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q90">
         <v>3.1</v>
@@ -19569,7 +19572,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ90">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR90">
         <v>1.82</v>
@@ -19900,7 +19903,7 @@
         <v>146</v>
       </c>
       <c r="P92" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20106,7 +20109,7 @@
         <v>147</v>
       </c>
       <c r="P93" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q93">
         <v>2.62</v>
@@ -20187,7 +20190,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ93">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AR93">
         <v>1.35</v>
@@ -20312,7 +20315,7 @@
         <v>148</v>
       </c>
       <c r="P94" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q94">
         <v>2.4</v>
@@ -20518,7 +20521,7 @@
         <v>149</v>
       </c>
       <c r="P95" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q95">
         <v>3.1</v>
@@ -21136,7 +21139,7 @@
         <v>152</v>
       </c>
       <c r="P98" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q98">
         <v>2.3</v>
@@ -21217,7 +21220,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ98">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR98">
         <v>1.85</v>
@@ -21342,7 +21345,7 @@
         <v>153</v>
       </c>
       <c r="P99" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q99">
         <v>6.5</v>
@@ -21548,7 +21551,7 @@
         <v>154</v>
       </c>
       <c r="P100" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q100">
         <v>4.33</v>
@@ -21626,7 +21629,7 @@
         <v>1.33</v>
       </c>
       <c r="AP100">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ100">
         <v>1.89</v>
@@ -21754,7 +21757,7 @@
         <v>85</v>
       </c>
       <c r="P101" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q101">
         <v>3.88</v>
@@ -22166,7 +22169,7 @@
         <v>85</v>
       </c>
       <c r="P103" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q103">
         <v>2.14</v>
@@ -22372,7 +22375,7 @@
         <v>150</v>
       </c>
       <c r="P104" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q104">
         <v>3.4</v>
@@ -22659,7 +22662,7 @@
         <v>2.8</v>
       </c>
       <c r="AQ105">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR105">
         <v>1.75</v>
@@ -22862,10 +22865,10 @@
         <v>0</v>
       </c>
       <c r="AP106">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ106">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR106">
         <v>1.56</v>
@@ -22990,7 +22993,7 @@
         <v>85</v>
       </c>
       <c r="P107" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q107">
         <v>2.13</v>
@@ -23071,7 +23074,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ107">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR107">
         <v>1.82</v>
@@ -23196,7 +23199,7 @@
         <v>157</v>
       </c>
       <c r="P108" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q108">
         <v>3.38</v>
@@ -23689,7 +23692,7 @@
         <v>2</v>
       </c>
       <c r="AQ110">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AR110">
         <v>1.42</v>
@@ -23892,7 +23895,7 @@
         <v>1.14</v>
       </c>
       <c r="AP111">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ111">
         <v>1.11</v>
@@ -24098,7 +24101,7 @@
         <v>1</v>
       </c>
       <c r="AP112">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ112">
         <v>0.78</v>
@@ -24226,7 +24229,7 @@
         <v>159</v>
       </c>
       <c r="P113" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q113">
         <v>3.4</v>
@@ -24638,7 +24641,7 @@
         <v>161</v>
       </c>
       <c r="P115" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q115">
         <v>4.85</v>
@@ -24925,7 +24928,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ116">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR116">
         <v>1.3</v>
@@ -25050,7 +25053,7 @@
         <v>85</v>
       </c>
       <c r="P117" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q117">
         <v>3.64</v>
@@ -25128,7 +25131,7 @@
         <v>1.13</v>
       </c>
       <c r="AP117">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ117">
         <v>1.33</v>
@@ -25462,7 +25465,7 @@
         <v>92</v>
       </c>
       <c r="P119" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q119">
         <v>4.4</v>
@@ -25874,7 +25877,7 @@
         <v>163</v>
       </c>
       <c r="P121" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q121">
         <v>2.93</v>
@@ -26367,7 +26370,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ123">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR123">
         <v>1.21</v>
@@ -26570,7 +26573,7 @@
         <v>1.13</v>
       </c>
       <c r="AP124">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ124">
         <v>1</v>
@@ -26698,7 +26701,7 @@
         <v>166</v>
       </c>
       <c r="P125" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q125">
         <v>2.5</v>
@@ -26779,7 +26782,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ125">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AR125">
         <v>1.82</v>
@@ -26904,7 +26907,7 @@
         <v>167</v>
       </c>
       <c r="P126" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q126">
         <v>3.6</v>
@@ -27110,7 +27113,7 @@
         <v>168</v>
       </c>
       <c r="P127" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q127">
         <v>4.33</v>
@@ -27188,7 +27191,7 @@
         <v>2.29</v>
       </c>
       <c r="AP127">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ127">
         <v>1.89</v>
@@ -27316,7 +27319,7 @@
         <v>169</v>
       </c>
       <c r="P128" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q128">
         <v>3.5</v>
@@ -27522,7 +27525,7 @@
         <v>170</v>
       </c>
       <c r="P129" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q129">
         <v>4.33</v>
@@ -27728,7 +27731,7 @@
         <v>171</v>
       </c>
       <c r="P130" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q130">
         <v>4.2</v>
@@ -27934,7 +27937,7 @@
         <v>172</v>
       </c>
       <c r="P131" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q131">
         <v>2.8</v>
@@ -28091,6 +28094,624 @@
       </c>
       <c r="BP131">
         <v>1.04</v>
+      </c>
+    </row>
+    <row r="132" spans="1:68">
+      <c r="A132" s="1">
+        <v>131</v>
+      </c>
+      <c r="B132">
+        <v>7813952</v>
+      </c>
+      <c r="C132" t="s">
+        <v>68</v>
+      </c>
+      <c r="D132" t="s">
+        <v>69</v>
+      </c>
+      <c r="E132" s="2">
+        <v>45844.29166666666</v>
+      </c>
+      <c r="F132">
+        <v>19</v>
+      </c>
+      <c r="G132" t="s">
+        <v>77</v>
+      </c>
+      <c r="H132" t="s">
+        <v>76</v>
+      </c>
+      <c r="I132">
+        <v>0</v>
+      </c>
+      <c r="J132">
+        <v>0</v>
+      </c>
+      <c r="K132">
+        <v>0</v>
+      </c>
+      <c r="L132">
+        <v>0</v>
+      </c>
+      <c r="M132">
+        <v>1</v>
+      </c>
+      <c r="N132">
+        <v>1</v>
+      </c>
+      <c r="O132" t="s">
+        <v>85</v>
+      </c>
+      <c r="P132" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q132">
+        <v>4.2</v>
+      </c>
+      <c r="R132">
+        <v>2.1</v>
+      </c>
+      <c r="S132">
+        <v>2.6</v>
+      </c>
+      <c r="T132">
+        <v>1.4</v>
+      </c>
+      <c r="U132">
+        <v>2.75</v>
+      </c>
+      <c r="V132">
+        <v>3</v>
+      </c>
+      <c r="W132">
+        <v>1.36</v>
+      </c>
+      <c r="X132">
+        <v>8.5</v>
+      </c>
+      <c r="Y132">
+        <v>1.07</v>
+      </c>
+      <c r="Z132">
+        <v>3.29</v>
+      </c>
+      <c r="AA132">
+        <v>3.21</v>
+      </c>
+      <c r="AB132">
+        <v>1.98</v>
+      </c>
+      <c r="AC132">
+        <v>1.02</v>
+      </c>
+      <c r="AD132">
+        <v>8.1</v>
+      </c>
+      <c r="AE132">
+        <v>1.33</v>
+      </c>
+      <c r="AF132">
+        <v>2.83</v>
+      </c>
+      <c r="AG132">
+        <v>1.95</v>
+      </c>
+      <c r="AH132">
+        <v>1.75</v>
+      </c>
+      <c r="AI132">
+        <v>1.8</v>
+      </c>
+      <c r="AJ132">
+        <v>1.95</v>
+      </c>
+      <c r="AK132">
+        <v>1.75</v>
+      </c>
+      <c r="AL132">
+        <v>1.33</v>
+      </c>
+      <c r="AM132">
+        <v>1.25</v>
+      </c>
+      <c r="AN132">
+        <v>1.33</v>
+      </c>
+      <c r="AO132">
+        <v>1.56</v>
+      </c>
+      <c r="AP132">
+        <v>1.2</v>
+      </c>
+      <c r="AQ132">
+        <v>1.7</v>
+      </c>
+      <c r="AR132">
+        <v>1.32</v>
+      </c>
+      <c r="AS132">
+        <v>1.41</v>
+      </c>
+      <c r="AT132">
+        <v>2.73</v>
+      </c>
+      <c r="AU132">
+        <v>3</v>
+      </c>
+      <c r="AV132">
+        <v>3</v>
+      </c>
+      <c r="AW132">
+        <v>4</v>
+      </c>
+      <c r="AX132">
+        <v>8</v>
+      </c>
+      <c r="AY132">
+        <v>7</v>
+      </c>
+      <c r="AZ132">
+        <v>11</v>
+      </c>
+      <c r="BA132">
+        <v>5</v>
+      </c>
+      <c r="BB132">
+        <v>2</v>
+      </c>
+      <c r="BC132">
+        <v>7</v>
+      </c>
+      <c r="BD132">
+        <v>2.98</v>
+      </c>
+      <c r="BE132">
+        <v>6.94</v>
+      </c>
+      <c r="BF132">
+        <v>1.68</v>
+      </c>
+      <c r="BG132">
+        <v>1.56</v>
+      </c>
+      <c r="BH132">
+        <v>2.24</v>
+      </c>
+      <c r="BI132">
+        <v>1.97</v>
+      </c>
+      <c r="BJ132">
+        <v>1.75</v>
+      </c>
+      <c r="BK132">
+        <v>2.58</v>
+      </c>
+      <c r="BL132">
+        <v>1.42</v>
+      </c>
+      <c r="BM132">
+        <v>3.64</v>
+      </c>
+      <c r="BN132">
+        <v>1.2</v>
+      </c>
+      <c r="BO132">
+        <v>5.53</v>
+      </c>
+      <c r="BP132">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="133" spans="1:68">
+      <c r="A133" s="1">
+        <v>132</v>
+      </c>
+      <c r="B133">
+        <v>7813953</v>
+      </c>
+      <c r="C133" t="s">
+        <v>68</v>
+      </c>
+      <c r="D133" t="s">
+        <v>69</v>
+      </c>
+      <c r="E133" s="2">
+        <v>45844.29166666666</v>
+      </c>
+      <c r="F133">
+        <v>19</v>
+      </c>
+      <c r="G133" t="s">
+        <v>78</v>
+      </c>
+      <c r="H133" t="s">
+        <v>72</v>
+      </c>
+      <c r="I133">
+        <v>1</v>
+      </c>
+      <c r="J133">
+        <v>0</v>
+      </c>
+      <c r="K133">
+        <v>1</v>
+      </c>
+      <c r="L133">
+        <v>3</v>
+      </c>
+      <c r="M133">
+        <v>0</v>
+      </c>
+      <c r="N133">
+        <v>3</v>
+      </c>
+      <c r="O133" t="s">
+        <v>173</v>
+      </c>
+      <c r="P133" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q133">
+        <v>3.2</v>
+      </c>
+      <c r="R133">
+        <v>2.05</v>
+      </c>
+      <c r="S133">
+        <v>3.3</v>
+      </c>
+      <c r="T133">
+        <v>1.44</v>
+      </c>
+      <c r="U133">
+        <v>2.62</v>
+      </c>
+      <c r="V133">
+        <v>3.1</v>
+      </c>
+      <c r="W133">
+        <v>1.33</v>
+      </c>
+      <c r="X133">
+        <v>9</v>
+      </c>
+      <c r="Y133">
+        <v>1.06</v>
+      </c>
+      <c r="Z133">
+        <v>2.44</v>
+      </c>
+      <c r="AA133">
+        <v>3.09</v>
+      </c>
+      <c r="AB133">
+        <v>2.59</v>
+      </c>
+      <c r="AC133">
+        <v>1.03</v>
+      </c>
+      <c r="AD133">
+        <v>7.2</v>
+      </c>
+      <c r="AE133">
+        <v>1.36</v>
+      </c>
+      <c r="AF133">
+        <v>2.69</v>
+      </c>
+      <c r="AG133">
+        <v>2.15</v>
+      </c>
+      <c r="AH133">
+        <v>1.57</v>
+      </c>
+      <c r="AI133">
+        <v>1.91</v>
+      </c>
+      <c r="AJ133">
+        <v>1.83</v>
+      </c>
+      <c r="AK133">
+        <v>1.44</v>
+      </c>
+      <c r="AL133">
+        <v>1.36</v>
+      </c>
+      <c r="AM133">
+        <v>1.44</v>
+      </c>
+      <c r="AN133">
+        <v>1.2</v>
+      </c>
+      <c r="AO133">
+        <v>2.25</v>
+      </c>
+      <c r="AP133">
+        <v>1.36</v>
+      </c>
+      <c r="AQ133">
+        <v>2</v>
+      </c>
+      <c r="AR133">
+        <v>1.61</v>
+      </c>
+      <c r="AS133">
+        <v>1.31</v>
+      </c>
+      <c r="AT133">
+        <v>2.92</v>
+      </c>
+      <c r="AU133">
+        <v>9</v>
+      </c>
+      <c r="AV133">
+        <v>0</v>
+      </c>
+      <c r="AW133">
+        <v>4</v>
+      </c>
+      <c r="AX133">
+        <v>6</v>
+      </c>
+      <c r="AY133">
+        <v>13</v>
+      </c>
+      <c r="AZ133">
+        <v>6</v>
+      </c>
+      <c r="BA133">
+        <v>3</v>
+      </c>
+      <c r="BB133">
+        <v>3</v>
+      </c>
+      <c r="BC133">
+        <v>6</v>
+      </c>
+      <c r="BD133">
+        <v>1.98</v>
+      </c>
+      <c r="BE133">
+        <v>6.65</v>
+      </c>
+      <c r="BF133">
+        <v>2.39</v>
+      </c>
+      <c r="BG133">
+        <v>1.56</v>
+      </c>
+      <c r="BH133">
+        <v>2.25</v>
+      </c>
+      <c r="BI133">
+        <v>1.96</v>
+      </c>
+      <c r="BJ133">
+        <v>1.75</v>
+      </c>
+      <c r="BK133">
+        <v>2.58</v>
+      </c>
+      <c r="BL133">
+        <v>1.42</v>
+      </c>
+      <c r="BM133">
+        <v>3.63</v>
+      </c>
+      <c r="BN133">
+        <v>1.2</v>
+      </c>
+      <c r="BO133">
+        <v>5.51</v>
+      </c>
+      <c r="BP133">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="134" spans="1:68">
+      <c r="A134" s="1">
+        <v>133</v>
+      </c>
+      <c r="B134">
+        <v>7813951</v>
+      </c>
+      <c r="C134" t="s">
+        <v>68</v>
+      </c>
+      <c r="D134" t="s">
+        <v>69</v>
+      </c>
+      <c r="E134" s="2">
+        <v>45844.29166666666</v>
+      </c>
+      <c r="F134">
+        <v>19</v>
+      </c>
+      <c r="G134" t="s">
+        <v>74</v>
+      </c>
+      <c r="H134" t="s">
+        <v>71</v>
+      </c>
+      <c r="I134">
+        <v>0</v>
+      </c>
+      <c r="J134">
+        <v>0</v>
+      </c>
+      <c r="K134">
+        <v>0</v>
+      </c>
+      <c r="L134">
+        <v>0</v>
+      </c>
+      <c r="M134">
+        <v>0</v>
+      </c>
+      <c r="N134">
+        <v>0</v>
+      </c>
+      <c r="O134" t="s">
+        <v>85</v>
+      </c>
+      <c r="P134" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q134">
+        <v>2.5</v>
+      </c>
+      <c r="R134">
+        <v>2.15</v>
+      </c>
+      <c r="S134">
+        <v>4</v>
+      </c>
+      <c r="T134">
+        <v>1.36</v>
+      </c>
+      <c r="U134">
+        <v>2.9</v>
+      </c>
+      <c r="V134">
+        <v>2.8</v>
+      </c>
+      <c r="W134">
+        <v>1.4</v>
+      </c>
+      <c r="X134">
+        <v>7.5</v>
+      </c>
+      <c r="Y134">
+        <v>1.08</v>
+      </c>
+      <c r="Z134">
+        <v>1.93</v>
+      </c>
+      <c r="AA134">
+        <v>3.16</v>
+      </c>
+      <c r="AB134">
+        <v>3.5</v>
+      </c>
+      <c r="AC134">
+        <v>1.01</v>
+      </c>
+      <c r="AD134">
+        <v>8.6</v>
+      </c>
+      <c r="AE134">
+        <v>1.31</v>
+      </c>
+      <c r="AF134">
+        <v>2.92</v>
+      </c>
+      <c r="AG134">
+        <v>2</v>
+      </c>
+      <c r="AH134">
+        <v>1.67</v>
+      </c>
+      <c r="AI134">
+        <v>1.85</v>
+      </c>
+      <c r="AJ134">
+        <v>1.91</v>
+      </c>
+      <c r="AK134">
+        <v>1.25</v>
+      </c>
+      <c r="AL134">
+        <v>1.35</v>
+      </c>
+      <c r="AM134">
+        <v>1.75</v>
+      </c>
+      <c r="AN134">
+        <v>1.33</v>
+      </c>
+      <c r="AO134">
+        <v>0.44</v>
+      </c>
+      <c r="AP134">
+        <v>1.3</v>
+      </c>
+      <c r="AQ134">
+        <v>0.5</v>
+      </c>
+      <c r="AR134">
+        <v>1.1</v>
+      </c>
+      <c r="AS134">
+        <v>1.16</v>
+      </c>
+      <c r="AT134">
+        <v>2.26</v>
+      </c>
+      <c r="AU134">
+        <v>2</v>
+      </c>
+      <c r="AV134">
+        <v>0</v>
+      </c>
+      <c r="AW134">
+        <v>1</v>
+      </c>
+      <c r="AX134">
+        <v>2</v>
+      </c>
+      <c r="AY134">
+        <v>3</v>
+      </c>
+      <c r="AZ134">
+        <v>2</v>
+      </c>
+      <c r="BA134">
+        <v>6</v>
+      </c>
+      <c r="BB134">
+        <v>1</v>
+      </c>
+      <c r="BC134">
+        <v>7</v>
+      </c>
+      <c r="BD134">
+        <v>1.87</v>
+      </c>
+      <c r="BE134">
+        <v>7.03</v>
+      </c>
+      <c r="BF134">
+        <v>2.51</v>
+      </c>
+      <c r="BG134">
+        <v>1.33</v>
+      </c>
+      <c r="BH134">
+        <v>2.87</v>
+      </c>
+      <c r="BI134">
+        <v>1.64</v>
+      </c>
+      <c r="BJ134">
+        <v>2.12</v>
+      </c>
+      <c r="BK134">
+        <v>2.04</v>
+      </c>
+      <c r="BL134">
+        <v>1.69</v>
+      </c>
+      <c r="BM134">
+        <v>2.67</v>
+      </c>
+      <c r="BN134">
+        <v>1.39</v>
+      </c>
+      <c r="BO134">
+        <v>3.74</v>
+      </c>
+      <c r="BP134">
+        <v>1.19</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="890" uniqueCount="246">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -538,6 +538,15 @@
     <t>['32', '63', '75']</t>
   </si>
   <si>
+    <t>['87']</t>
+  </si>
+  <si>
+    <t>['78', '90+1']</t>
+  </si>
+  <si>
+    <t>['14']</t>
+  </si>
+  <si>
     <t>['1', '6']</t>
   </si>
   <si>
@@ -602,9 +611,6 @@
   </si>
   <si>
     <t>['42', '63']</t>
-  </si>
-  <si>
-    <t>['87']</t>
   </si>
   <si>
     <t>['49']</t>
@@ -745,7 +751,7 @@
     <t>['9']</t>
   </si>
   <si>
-    <t>['14']</t>
+    <t>['24', '46', '54']</t>
   </si>
 </sst>
 </file>
@@ -1107,7 +1113,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP134"/>
+  <dimension ref="A1:BP138"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1444,7 +1450,7 @@
         <v>2.8</v>
       </c>
       <c r="AQ2">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1569,7 +1575,7 @@
         <v>85</v>
       </c>
       <c r="P3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="Q3">
         <v>3.8</v>
@@ -1647,7 +1653,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AQ3">
         <v>1.67</v>
@@ -1853,7 +1859,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ4">
         <v>1.13</v>
@@ -2268,7 +2274,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ6">
-        <v>0.44</v>
+        <v>0.7</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2599,7 +2605,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="Q8">
         <v>2.39</v>
@@ -2680,7 +2686,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ8">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3011,7 +3017,7 @@
         <v>85</v>
       </c>
       <c r="P10" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Q10">
         <v>4.3</v>
@@ -3217,7 +3223,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Q11">
         <v>2.8</v>
@@ -3629,7 +3635,7 @@
         <v>85</v>
       </c>
       <c r="P13" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Q13">
         <v>2.43</v>
@@ -3707,10 +3713,10 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ13">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR13">
         <v>1.4</v>
@@ -3835,7 +3841,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="Q14">
         <v>3.9</v>
@@ -3913,7 +3919,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AQ14">
         <v>1.7</v>
@@ -4122,7 +4128,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ15">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR15">
         <v>0.82</v>
@@ -4247,7 +4253,7 @@
         <v>85</v>
       </c>
       <c r="P16" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="Q16">
         <v>3.18</v>
@@ -4453,7 +4459,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="Q17">
         <v>3</v>
@@ -4534,7 +4540,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ17">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR17">
         <v>1.52</v>
@@ -4865,7 +4871,7 @@
         <v>95</v>
       </c>
       <c r="P19" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q19">
         <v>2.71</v>
@@ -4946,7 +4952,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ19">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5071,7 +5077,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="Q20">
         <v>3.5</v>
@@ -5355,7 +5361,7 @@
         <v>0.5</v>
       </c>
       <c r="AP21">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AQ21">
         <v>1.33</v>
@@ -5483,7 +5489,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="Q22">
         <v>5</v>
@@ -5976,7 +5982,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ24">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR24">
         <v>1.41</v>
@@ -6385,7 +6391,7 @@
         <v>0.33</v>
       </c>
       <c r="AP26">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ26">
         <v>1.33</v>
@@ -6513,7 +6519,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Q27">
         <v>2.25</v>
@@ -6591,7 +6597,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ27">
         <v>0.5</v>
@@ -6719,7 +6725,7 @@
         <v>101</v>
       </c>
       <c r="P28" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="Q28">
         <v>4</v>
@@ -6925,7 +6931,7 @@
         <v>102</v>
       </c>
       <c r="P29" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q29">
         <v>2.2</v>
@@ -7131,7 +7137,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q30">
         <v>3.75</v>
@@ -7212,7 +7218,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ30">
-        <v>0.44</v>
+        <v>0.7</v>
       </c>
       <c r="AR30">
         <v>1.22</v>
@@ -7337,7 +7343,7 @@
         <v>104</v>
       </c>
       <c r="P31" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q31">
         <v>3.25</v>
@@ -7415,7 +7421,7 @@
         <v>2</v>
       </c>
       <c r="AP31">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ31">
         <v>1.67</v>
@@ -7624,7 +7630,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ32">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR32">
         <v>1.01</v>
@@ -7749,7 +7755,7 @@
         <v>91</v>
       </c>
       <c r="P33" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q33">
         <v>2.63</v>
@@ -7955,7 +7961,7 @@
         <v>85</v>
       </c>
       <c r="P34" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q34">
         <v>3.8</v>
@@ -8033,7 +8039,7 @@
         <v>2</v>
       </c>
       <c r="AP34">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AQ34">
         <v>1.13</v>
@@ -8161,7 +8167,7 @@
         <v>106</v>
       </c>
       <c r="P35" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q35">
         <v>2.8</v>
@@ -8779,7 +8785,7 @@
         <v>85</v>
       </c>
       <c r="P38" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q38">
         <v>5</v>
@@ -8985,7 +8991,7 @@
         <v>85</v>
       </c>
       <c r="P39" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q39">
         <v>3.1</v>
@@ -9063,7 +9069,7 @@
         <v>1.6</v>
       </c>
       <c r="AP39">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ39">
         <v>1.67</v>
@@ -9269,10 +9275,10 @@
         <v>1.33</v>
       </c>
       <c r="AP40">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ40">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR40">
         <v>1.62</v>
@@ -9397,7 +9403,7 @@
         <v>110</v>
       </c>
       <c r="P41" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q41">
         <v>3.25</v>
@@ -9603,7 +9609,7 @@
         <v>111</v>
       </c>
       <c r="P42" t="s">
-        <v>196</v>
+        <v>174</v>
       </c>
       <c r="Q42">
         <v>2.5</v>
@@ -9684,7 +9690,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ42">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR42">
         <v>1.85</v>
@@ -10015,7 +10021,7 @@
         <v>113</v>
       </c>
       <c r="P44" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q44">
         <v>3.4</v>
@@ -10221,7 +10227,7 @@
         <v>113</v>
       </c>
       <c r="P45" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q45">
         <v>3.75</v>
@@ -10427,7 +10433,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q46">
         <v>3.75</v>
@@ -10633,7 +10639,7 @@
         <v>85</v>
       </c>
       <c r="P47" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q47">
         <v>3</v>
@@ -10920,7 +10926,7 @@
         <v>2.8</v>
       </c>
       <c r="AQ48">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR48">
         <v>1.63</v>
@@ -11045,7 +11051,7 @@
         <v>116</v>
       </c>
       <c r="P49" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -11123,7 +11129,7 @@
         <v>0</v>
       </c>
       <c r="AP49">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ49">
         <v>1.2</v>
@@ -11329,7 +11335,7 @@
         <v>0</v>
       </c>
       <c r="AP50">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AQ50">
         <v>1.11</v>
@@ -11457,7 +11463,7 @@
         <v>85</v>
       </c>
       <c r="P51" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q51">
         <v>2.25</v>
@@ -11538,7 +11544,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ51">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR51">
         <v>1.2</v>
@@ -11947,10 +11953,10 @@
         <v>0.5</v>
       </c>
       <c r="AP53">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ53">
-        <v>0.44</v>
+        <v>0.7</v>
       </c>
       <c r="AR53">
         <v>1.75</v>
@@ -12281,7 +12287,7 @@
         <v>119</v>
       </c>
       <c r="P55" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q55">
         <v>5</v>
@@ -12693,7 +12699,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q57">
         <v>3.75</v>
@@ -12899,7 +12905,7 @@
         <v>121</v>
       </c>
       <c r="P58" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Q58">
         <v>2.3</v>
@@ -12980,7 +12986,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ58">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR58">
         <v>1.31</v>
@@ -13105,7 +13111,7 @@
         <v>85</v>
       </c>
       <c r="P59" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q59">
         <v>3.2</v>
@@ -13183,10 +13189,10 @@
         <v>0.88</v>
       </c>
       <c r="AP59">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AQ59">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR59">
         <v>1.1</v>
@@ -13517,7 +13523,7 @@
         <v>123</v>
       </c>
       <c r="P61" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q61">
         <v>4</v>
@@ -13723,7 +13729,7 @@
         <v>124</v>
       </c>
       <c r="P62" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q62">
         <v>2.3</v>
@@ -13801,7 +13807,7 @@
         <v>1.67</v>
       </c>
       <c r="AP62">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ62">
         <v>1</v>
@@ -13929,7 +13935,7 @@
         <v>85</v>
       </c>
       <c r="P63" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q63">
         <v>3.2</v>
@@ -14135,7 +14141,7 @@
         <v>125</v>
       </c>
       <c r="P64" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q64">
         <v>2.5</v>
@@ -14213,10 +14219,10 @@
         <v>0.33</v>
       </c>
       <c r="AP64">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ64">
-        <v>0.44</v>
+        <v>0.7</v>
       </c>
       <c r="AR64">
         <v>1.63</v>
@@ -14341,7 +14347,7 @@
         <v>126</v>
       </c>
       <c r="P65" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q65">
         <v>4</v>
@@ -14547,7 +14553,7 @@
         <v>127</v>
       </c>
       <c r="P66" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q66">
         <v>3</v>
@@ -14834,7 +14840,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ67">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR67">
         <v>1.4</v>
@@ -14959,7 +14965,7 @@
         <v>129</v>
       </c>
       <c r="P68" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q68">
         <v>5</v>
@@ -15449,7 +15455,7 @@
         <v>0.6</v>
       </c>
       <c r="AP70">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ70">
         <v>1.33</v>
@@ -15577,7 +15583,7 @@
         <v>132</v>
       </c>
       <c r="P71" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q71">
         <v>2.63</v>
@@ -15864,7 +15870,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ72">
-        <v>0.44</v>
+        <v>0.7</v>
       </c>
       <c r="AR72">
         <v>1.67</v>
@@ -15989,7 +15995,7 @@
         <v>85</v>
       </c>
       <c r="P73" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q73">
         <v>3.6</v>
@@ -16195,7 +16201,7 @@
         <v>85</v>
       </c>
       <c r="P74" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q74">
         <v>4.33</v>
@@ -16401,7 +16407,7 @@
         <v>134</v>
       </c>
       <c r="P75" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Q75">
         <v>1.91</v>
@@ -16607,7 +16613,7 @@
         <v>135</v>
       </c>
       <c r="P76" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q76">
         <v>2.63</v>
@@ -16685,7 +16691,7 @@
         <v>1.25</v>
       </c>
       <c r="AP76">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ76">
         <v>1</v>
@@ -16813,7 +16819,7 @@
         <v>85</v>
       </c>
       <c r="P77" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q77">
         <v>4.5</v>
@@ -17097,7 +17103,7 @@
         <v>0</v>
       </c>
       <c r="AP78">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ78">
         <v>0.5</v>
@@ -17225,7 +17231,7 @@
         <v>137</v>
       </c>
       <c r="P79" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q79">
         <v>3.6</v>
@@ -17512,7 +17518,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ80">
-        <v>0.44</v>
+        <v>0.7</v>
       </c>
       <c r="AR80">
         <v>1.42</v>
@@ -17715,7 +17721,7 @@
         <v>1</v>
       </c>
       <c r="AP81">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AQ81">
         <v>1</v>
@@ -17843,7 +17849,7 @@
         <v>140</v>
       </c>
       <c r="P82" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q82">
         <v>3.75</v>
@@ -17921,7 +17927,7 @@
         <v>1</v>
       </c>
       <c r="AP82">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ82">
         <v>1.89</v>
@@ -18049,7 +18055,7 @@
         <v>85</v>
       </c>
       <c r="P83" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q83">
         <v>7.5</v>
@@ -18333,10 +18339,10 @@
         <v>1.11</v>
       </c>
       <c r="AP84">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ84">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR84">
         <v>1.02</v>
@@ -18461,7 +18467,7 @@
         <v>142</v>
       </c>
       <c r="P85" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q85">
         <v>3.75</v>
@@ -18667,7 +18673,7 @@
         <v>85</v>
       </c>
       <c r="P86" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q86">
         <v>4.2</v>
@@ -19285,7 +19291,7 @@
         <v>143</v>
       </c>
       <c r="P89" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q89">
         <v>2.62</v>
@@ -19491,7 +19497,7 @@
         <v>144</v>
       </c>
       <c r="P90" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q90">
         <v>3.1</v>
@@ -19903,7 +19909,7 @@
         <v>146</v>
       </c>
       <c r="P92" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -19981,7 +19987,7 @@
         <v>1.4</v>
       </c>
       <c r="AP92">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ92">
         <v>1.13</v>
@@ -20109,7 +20115,7 @@
         <v>147</v>
       </c>
       <c r="P93" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q93">
         <v>2.62</v>
@@ -20315,7 +20321,7 @@
         <v>148</v>
       </c>
       <c r="P94" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q94">
         <v>2.4</v>
@@ -20393,10 +20399,10 @@
         <v>0.17</v>
       </c>
       <c r="AP94">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ94">
-        <v>0.44</v>
+        <v>0.7</v>
       </c>
       <c r="AR94">
         <v>1.56</v>
@@ -20521,7 +20527,7 @@
         <v>149</v>
       </c>
       <c r="P95" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q95">
         <v>3.1</v>
@@ -20602,7 +20608,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ95">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR95">
         <v>1.52</v>
@@ -21139,7 +21145,7 @@
         <v>152</v>
       </c>
       <c r="P98" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q98">
         <v>2.3</v>
@@ -21217,7 +21223,7 @@
         <v>1.83</v>
       </c>
       <c r="AP98">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ98">
         <v>1.7</v>
@@ -21345,7 +21351,7 @@
         <v>153</v>
       </c>
       <c r="P99" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q99">
         <v>6.5</v>
@@ -21423,7 +21429,7 @@
         <v>2.4</v>
       </c>
       <c r="AP99">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AQ99">
         <v>1.89</v>
@@ -21551,7 +21557,7 @@
         <v>154</v>
       </c>
       <c r="P100" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q100">
         <v>4.33</v>
@@ -21757,7 +21763,7 @@
         <v>85</v>
       </c>
       <c r="P101" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q101">
         <v>3.88</v>
@@ -22044,7 +22050,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ102">
-        <v>0.44</v>
+        <v>0.7</v>
       </c>
       <c r="AR102">
         <v>1.78</v>
@@ -22169,7 +22175,7 @@
         <v>85</v>
       </c>
       <c r="P103" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q103">
         <v>2.14</v>
@@ -22247,7 +22253,7 @@
         <v>0.83</v>
       </c>
       <c r="AP103">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ103">
         <v>1.11</v>
@@ -22375,7 +22381,7 @@
         <v>150</v>
       </c>
       <c r="P104" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q104">
         <v>3.4</v>
@@ -22453,7 +22459,7 @@
         <v>2</v>
       </c>
       <c r="AP104">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ104">
         <v>1.2</v>
@@ -22993,7 +22999,7 @@
         <v>85</v>
       </c>
       <c r="P107" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q107">
         <v>2.13</v>
@@ -23199,7 +23205,7 @@
         <v>157</v>
       </c>
       <c r="P108" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q108">
         <v>3.38</v>
@@ -23689,7 +23695,7 @@
         <v>2.33</v>
       </c>
       <c r="AP110">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ110">
         <v>2</v>
@@ -24104,7 +24110,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ112">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR112">
         <v>1.55</v>
@@ -24229,7 +24235,7 @@
         <v>159</v>
       </c>
       <c r="P113" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q113">
         <v>3.4</v>
@@ -24307,7 +24313,7 @@
         <v>2.17</v>
       </c>
       <c r="AP113">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ113">
         <v>1.89</v>
@@ -24516,7 +24522,7 @@
         <v>2.8</v>
       </c>
       <c r="AQ114">
-        <v>0.44</v>
+        <v>0.7</v>
       </c>
       <c r="AR114">
         <v>1.71</v>
@@ -24641,7 +24647,7 @@
         <v>161</v>
       </c>
       <c r="P115" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q115">
         <v>4.85</v>
@@ -24719,7 +24725,7 @@
         <v>1.57</v>
       </c>
       <c r="AP115">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AQ115">
         <v>1.2</v>
@@ -25053,7 +25059,7 @@
         <v>85</v>
       </c>
       <c r="P117" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q117">
         <v>3.64</v>
@@ -25337,10 +25343,10 @@
         <v>1</v>
       </c>
       <c r="AP118">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ118">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR118">
         <v>1.65</v>
@@ -25465,7 +25471,7 @@
         <v>92</v>
       </c>
       <c r="P119" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q119">
         <v>4.4</v>
@@ -25749,7 +25755,7 @@
         <v>1.14</v>
       </c>
       <c r="AP120">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ120">
         <v>1.13</v>
@@ -25877,7 +25883,7 @@
         <v>163</v>
       </c>
       <c r="P121" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q121">
         <v>2.93</v>
@@ -26164,7 +26170,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ122">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR122">
         <v>1.52</v>
@@ -26701,7 +26707,7 @@
         <v>166</v>
       </c>
       <c r="P125" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q125">
         <v>2.5</v>
@@ -26779,7 +26785,7 @@
         <v>2.43</v>
       </c>
       <c r="AP125">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ125">
         <v>2</v>
@@ -26907,7 +26913,7 @@
         <v>167</v>
       </c>
       <c r="P126" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q126">
         <v>3.6</v>
@@ -27113,7 +27119,7 @@
         <v>168</v>
       </c>
       <c r="P127" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q127">
         <v>4.33</v>
@@ -27319,7 +27325,7 @@
         <v>169</v>
       </c>
       <c r="P128" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q128">
         <v>3.5</v>
@@ -27525,7 +27531,7 @@
         <v>170</v>
       </c>
       <c r="P129" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q129">
         <v>4.33</v>
@@ -27603,7 +27609,7 @@
         <v>2.13</v>
       </c>
       <c r="AP129">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ129">
         <v>1.89</v>
@@ -27731,7 +27737,7 @@
         <v>171</v>
       </c>
       <c r="P130" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q130">
         <v>4.2</v>
@@ -27937,7 +27943,7 @@
         <v>172</v>
       </c>
       <c r="P131" t="s">
-        <v>243</v>
+        <v>176</v>
       </c>
       <c r="Q131">
         <v>2.8</v>
@@ -28712,6 +28718,830 @@
       </c>
       <c r="BP134">
         <v>1.19</v>
+      </c>
+    </row>
+    <row r="135" spans="1:68">
+      <c r="A135" s="1">
+        <v>134</v>
+      </c>
+      <c r="B135">
+        <v>7813956</v>
+      </c>
+      <c r="C135" t="s">
+        <v>68</v>
+      </c>
+      <c r="D135" t="s">
+        <v>69</v>
+      </c>
+      <c r="E135" s="2">
+        <v>45850.29166666666</v>
+      </c>
+      <c r="F135">
+        <v>20</v>
+      </c>
+      <c r="G135" t="s">
+        <v>79</v>
+      </c>
+      <c r="H135" t="s">
+        <v>82</v>
+      </c>
+      <c r="I135">
+        <v>0</v>
+      </c>
+      <c r="J135">
+        <v>0</v>
+      </c>
+      <c r="K135">
+        <v>0</v>
+      </c>
+      <c r="L135">
+        <v>1</v>
+      </c>
+      <c r="M135">
+        <v>0</v>
+      </c>
+      <c r="N135">
+        <v>1</v>
+      </c>
+      <c r="O135" t="s">
+        <v>174</v>
+      </c>
+      <c r="P135" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q135">
+        <v>1.83</v>
+      </c>
+      <c r="R135">
+        <v>2.42</v>
+      </c>
+      <c r="S135">
+        <v>6.3</v>
+      </c>
+      <c r="T135">
+        <v>1.27</v>
+      </c>
+      <c r="U135">
+        <v>3.28</v>
+      </c>
+      <c r="V135">
+        <v>2.29</v>
+      </c>
+      <c r="W135">
+        <v>1.58</v>
+      </c>
+      <c r="X135">
+        <v>4.95</v>
+      </c>
+      <c r="Y135">
+        <v>1.12</v>
+      </c>
+      <c r="Z135">
+        <v>1.34</v>
+      </c>
+      <c r="AA135">
+        <v>4.33</v>
+      </c>
+      <c r="AB135">
+        <v>7.1</v>
+      </c>
+      <c r="AC135">
+        <v>1.01</v>
+      </c>
+      <c r="AD135">
+        <v>17</v>
+      </c>
+      <c r="AE135">
+        <v>1.14</v>
+      </c>
+      <c r="AF135">
+        <v>4.45</v>
+      </c>
+      <c r="AG135">
+        <v>1.53</v>
+      </c>
+      <c r="AH135">
+        <v>2.25</v>
+      </c>
+      <c r="AI135">
+        <v>1.75</v>
+      </c>
+      <c r="AJ135">
+        <v>1.92</v>
+      </c>
+      <c r="AK135">
+        <v>1.05</v>
+      </c>
+      <c r="AL135">
+        <v>1.15</v>
+      </c>
+      <c r="AM135">
+        <v>2.82</v>
+      </c>
+      <c r="AN135">
+        <v>2.1</v>
+      </c>
+      <c r="AO135">
+        <v>1</v>
+      </c>
+      <c r="AP135">
+        <v>2.18</v>
+      </c>
+      <c r="AQ135">
+        <v>0.92</v>
+      </c>
+      <c r="AR135">
+        <v>1.78</v>
+      </c>
+      <c r="AS135">
+        <v>1.25</v>
+      </c>
+      <c r="AT135">
+        <v>3.03</v>
+      </c>
+      <c r="AU135">
+        <v>3</v>
+      </c>
+      <c r="AV135">
+        <v>0</v>
+      </c>
+      <c r="AW135">
+        <v>4</v>
+      </c>
+      <c r="AX135">
+        <v>8</v>
+      </c>
+      <c r="AY135">
+        <v>7</v>
+      </c>
+      <c r="AZ135">
+        <v>8</v>
+      </c>
+      <c r="BA135">
+        <v>8</v>
+      </c>
+      <c r="BB135">
+        <v>3</v>
+      </c>
+      <c r="BC135">
+        <v>11</v>
+      </c>
+      <c r="BD135">
+        <v>1.18</v>
+      </c>
+      <c r="BE135">
+        <v>10.5</v>
+      </c>
+      <c r="BF135">
+        <v>7.41</v>
+      </c>
+      <c r="BG135">
+        <v>1.38</v>
+      </c>
+      <c r="BH135">
+        <v>2.69</v>
+      </c>
+      <c r="BI135">
+        <v>1.71</v>
+      </c>
+      <c r="BJ135">
+        <v>2.02</v>
+      </c>
+      <c r="BK135">
+        <v>2.15</v>
+      </c>
+      <c r="BL135">
+        <v>1.61</v>
+      </c>
+      <c r="BM135">
+        <v>2.86</v>
+      </c>
+      <c r="BN135">
+        <v>1.33</v>
+      </c>
+      <c r="BO135">
+        <v>4.08</v>
+      </c>
+      <c r="BP135">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="136" spans="1:68">
+      <c r="A136" s="1">
+        <v>135</v>
+      </c>
+      <c r="B136">
+        <v>7813957</v>
+      </c>
+      <c r="C136" t="s">
+        <v>68</v>
+      </c>
+      <c r="D136" t="s">
+        <v>69</v>
+      </c>
+      <c r="E136" s="2">
+        <v>45850.29166666666</v>
+      </c>
+      <c r="F136">
+        <v>20</v>
+      </c>
+      <c r="G136" t="s">
+        <v>71</v>
+      </c>
+      <c r="H136" t="s">
+        <v>77</v>
+      </c>
+      <c r="I136">
+        <v>0</v>
+      </c>
+      <c r="J136">
+        <v>1</v>
+      </c>
+      <c r="K136">
+        <v>1</v>
+      </c>
+      <c r="L136">
+        <v>2</v>
+      </c>
+      <c r="M136">
+        <v>3</v>
+      </c>
+      <c r="N136">
+        <v>5</v>
+      </c>
+      <c r="O136" t="s">
+        <v>175</v>
+      </c>
+      <c r="P136" t="s">
+        <v>245</v>
+      </c>
+      <c r="Q136">
+        <v>3.2</v>
+      </c>
+      <c r="R136">
+        <v>2</v>
+      </c>
+      <c r="S136">
+        <v>3.3</v>
+      </c>
+      <c r="T136">
+        <v>1.43</v>
+      </c>
+      <c r="U136">
+        <v>2.76</v>
+      </c>
+      <c r="V136">
+        <v>3.2</v>
+      </c>
+      <c r="W136">
+        <v>1.34</v>
+      </c>
+      <c r="X136">
+        <v>7.9</v>
+      </c>
+      <c r="Y136">
+        <v>1.02</v>
+      </c>
+      <c r="Z136">
+        <v>2.64</v>
+      </c>
+      <c r="AA136">
+        <v>3.06</v>
+      </c>
+      <c r="AB136">
+        <v>2.42</v>
+      </c>
+      <c r="AC136">
+        <v>1.05</v>
+      </c>
+      <c r="AD136">
+        <v>8</v>
+      </c>
+      <c r="AE136">
+        <v>1.36</v>
+      </c>
+      <c r="AF136">
+        <v>2.88</v>
+      </c>
+      <c r="AG136">
+        <v>2.1</v>
+      </c>
+      <c r="AH136">
+        <v>1.61</v>
+      </c>
+      <c r="AI136">
+        <v>1.83</v>
+      </c>
+      <c r="AJ136">
+        <v>1.83</v>
+      </c>
+      <c r="AK136">
+        <v>1.38</v>
+      </c>
+      <c r="AL136">
+        <v>1.3</v>
+      </c>
+      <c r="AM136">
+        <v>1.48</v>
+      </c>
+      <c r="AN136">
+        <v>0.89</v>
+      </c>
+      <c r="AO136">
+        <v>0.44</v>
+      </c>
+      <c r="AP136">
+        <v>0.8</v>
+      </c>
+      <c r="AQ136">
+        <v>0.7</v>
+      </c>
+      <c r="AR136">
+        <v>1.23</v>
+      </c>
+      <c r="AS136">
+        <v>1.04</v>
+      </c>
+      <c r="AT136">
+        <v>2.27</v>
+      </c>
+      <c r="AU136">
+        <v>6</v>
+      </c>
+      <c r="AV136">
+        <v>5</v>
+      </c>
+      <c r="AW136">
+        <v>9</v>
+      </c>
+      <c r="AX136">
+        <v>3</v>
+      </c>
+      <c r="AY136">
+        <v>15</v>
+      </c>
+      <c r="AZ136">
+        <v>8</v>
+      </c>
+      <c r="BA136">
+        <v>5</v>
+      </c>
+      <c r="BB136">
+        <v>2</v>
+      </c>
+      <c r="BC136">
+        <v>7</v>
+      </c>
+      <c r="BD136">
+        <v>1.92</v>
+      </c>
+      <c r="BE136">
+        <v>6.73</v>
+      </c>
+      <c r="BF136">
+        <v>2.47</v>
+      </c>
+      <c r="BG136">
+        <v>1.47</v>
+      </c>
+      <c r="BH136">
+        <v>2.44</v>
+      </c>
+      <c r="BI136">
+        <v>1.88</v>
+      </c>
+      <c r="BJ136">
+        <v>1.92</v>
+      </c>
+      <c r="BK136">
+        <v>2.35</v>
+      </c>
+      <c r="BL136">
+        <v>1.51</v>
+      </c>
+      <c r="BM136">
+        <v>3.21</v>
+      </c>
+      <c r="BN136">
+        <v>1.26</v>
+      </c>
+      <c r="BO136">
+        <v>4.73</v>
+      </c>
+      <c r="BP136">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:68">
+      <c r="A137" s="1">
+        <v>136</v>
+      </c>
+      <c r="B137">
+        <v>7813954</v>
+      </c>
+      <c r="C137" t="s">
+        <v>68</v>
+      </c>
+      <c r="D137" t="s">
+        <v>69</v>
+      </c>
+      <c r="E137" s="2">
+        <v>45850.29166666666</v>
+      </c>
+      <c r="F137">
+        <v>20</v>
+      </c>
+      <c r="G137" t="s">
+        <v>83</v>
+      </c>
+      <c r="H137" t="s">
+        <v>80</v>
+      </c>
+      <c r="I137">
+        <v>1</v>
+      </c>
+      <c r="J137">
+        <v>0</v>
+      </c>
+      <c r="K137">
+        <v>1</v>
+      </c>
+      <c r="L137">
+        <v>1</v>
+      </c>
+      <c r="M137">
+        <v>0</v>
+      </c>
+      <c r="N137">
+        <v>1</v>
+      </c>
+      <c r="O137" t="s">
+        <v>176</v>
+      </c>
+      <c r="P137" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q137">
+        <v>2.22</v>
+      </c>
+      <c r="R137">
+        <v>2.25</v>
+      </c>
+      <c r="S137">
+        <v>4.5</v>
+      </c>
+      <c r="T137">
+        <v>1.29</v>
+      </c>
+      <c r="U137">
+        <v>3.26</v>
+      </c>
+      <c r="V137">
+        <v>2.46</v>
+      </c>
+      <c r="W137">
+        <v>1.48</v>
+      </c>
+      <c r="X137">
+        <v>5.9</v>
+      </c>
+      <c r="Y137">
+        <v>1.07</v>
+      </c>
+      <c r="Z137">
+        <v>1.68</v>
+      </c>
+      <c r="AA137">
+        <v>3.68</v>
+      </c>
+      <c r="AB137">
+        <v>3.96</v>
+      </c>
+      <c r="AC137">
+        <v>1.01</v>
+      </c>
+      <c r="AD137">
+        <v>11</v>
+      </c>
+      <c r="AE137">
+        <v>1.16</v>
+      </c>
+      <c r="AF137">
+        <v>4.1</v>
+      </c>
+      <c r="AG137">
+        <v>1.67</v>
+      </c>
+      <c r="AH137">
+        <v>2</v>
+      </c>
+      <c r="AI137">
+        <v>1.63</v>
+      </c>
+      <c r="AJ137">
+        <v>2.09</v>
+      </c>
+      <c r="AK137">
+        <v>1.17</v>
+      </c>
+      <c r="AL137">
+        <v>1.21</v>
+      </c>
+      <c r="AM137">
+        <v>2.03</v>
+      </c>
+      <c r="AN137">
+        <v>2</v>
+      </c>
+      <c r="AO137">
+        <v>0.78</v>
+      </c>
+      <c r="AP137">
+        <v>2.13</v>
+      </c>
+      <c r="AQ137">
+        <v>0.7</v>
+      </c>
+      <c r="AR137">
+        <v>1.46</v>
+      </c>
+      <c r="AS137">
+        <v>1.06</v>
+      </c>
+      <c r="AT137">
+        <v>2.52</v>
+      </c>
+      <c r="AU137">
+        <v>4</v>
+      </c>
+      <c r="AV137">
+        <v>4</v>
+      </c>
+      <c r="AW137">
+        <v>7</v>
+      </c>
+      <c r="AX137">
+        <v>2</v>
+      </c>
+      <c r="AY137">
+        <v>11</v>
+      </c>
+      <c r="AZ137">
+        <v>6</v>
+      </c>
+      <c r="BA137">
+        <v>6</v>
+      </c>
+      <c r="BB137">
+        <v>2</v>
+      </c>
+      <c r="BC137">
+        <v>8</v>
+      </c>
+      <c r="BD137">
+        <v>1.71</v>
+      </c>
+      <c r="BE137">
+        <v>6.86</v>
+      </c>
+      <c r="BF137">
+        <v>2.9</v>
+      </c>
+      <c r="BG137">
+        <v>1.51</v>
+      </c>
+      <c r="BH137">
+        <v>2.34</v>
+      </c>
+      <c r="BI137">
+        <v>1.95</v>
+      </c>
+      <c r="BJ137">
+        <v>1.85</v>
+      </c>
+      <c r="BK137">
+        <v>2.45</v>
+      </c>
+      <c r="BL137">
+        <v>1.46</v>
+      </c>
+      <c r="BM137">
+        <v>3.4</v>
+      </c>
+      <c r="BN137">
+        <v>1.23</v>
+      </c>
+      <c r="BO137">
+        <v>5.08</v>
+      </c>
+      <c r="BP137">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="138" spans="1:68">
+      <c r="A138" s="1">
+        <v>137</v>
+      </c>
+      <c r="B138">
+        <v>7813955</v>
+      </c>
+      <c r="C138" t="s">
+        <v>68</v>
+      </c>
+      <c r="D138" t="s">
+        <v>69</v>
+      </c>
+      <c r="E138" s="2">
+        <v>45850.29166666666</v>
+      </c>
+      <c r="F138">
+        <v>20</v>
+      </c>
+      <c r="G138" t="s">
+        <v>72</v>
+      </c>
+      <c r="H138" t="s">
+        <v>74</v>
+      </c>
+      <c r="I138">
+        <v>0</v>
+      </c>
+      <c r="J138">
+        <v>0</v>
+      </c>
+      <c r="K138">
+        <v>0</v>
+      </c>
+      <c r="L138">
+        <v>0</v>
+      </c>
+      <c r="M138">
+        <v>0</v>
+      </c>
+      <c r="N138">
+        <v>0</v>
+      </c>
+      <c r="O138" t="s">
+        <v>85</v>
+      </c>
+      <c r="P138" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q138">
+        <v>2.5</v>
+      </c>
+      <c r="R138">
+        <v>2</v>
+      </c>
+      <c r="S138">
+        <v>4.33</v>
+      </c>
+      <c r="T138">
+        <v>1.43</v>
+      </c>
+      <c r="U138">
+        <v>2.78</v>
+      </c>
+      <c r="V138">
+        <v>3.18</v>
+      </c>
+      <c r="W138">
+        <v>1.34</v>
+      </c>
+      <c r="X138">
+        <v>7.2</v>
+      </c>
+      <c r="Y138">
+        <v>1.03</v>
+      </c>
+      <c r="Z138">
+        <v>1.82</v>
+      </c>
+      <c r="AA138">
+        <v>3.33</v>
+      </c>
+      <c r="AB138">
+        <v>3.69</v>
+      </c>
+      <c r="AC138">
+        <v>1.05</v>
+      </c>
+      <c r="AD138">
+        <v>8</v>
+      </c>
+      <c r="AE138">
+        <v>1.33</v>
+      </c>
+      <c r="AF138">
+        <v>3</v>
+      </c>
+      <c r="AG138">
+        <v>2.05</v>
+      </c>
+      <c r="AH138">
+        <v>1.65</v>
+      </c>
+      <c r="AI138">
+        <v>1.91</v>
+      </c>
+      <c r="AJ138">
+        <v>1.8</v>
+      </c>
+      <c r="AK138">
+        <v>1.22</v>
+      </c>
+      <c r="AL138">
+        <v>1.27</v>
+      </c>
+      <c r="AM138">
+        <v>1.77</v>
+      </c>
+      <c r="AN138">
+        <v>1.2</v>
+      </c>
+      <c r="AO138">
+        <v>1</v>
+      </c>
+      <c r="AP138">
+        <v>1.18</v>
+      </c>
+      <c r="AQ138">
+        <v>1</v>
+      </c>
+      <c r="AR138">
+        <v>1.62</v>
+      </c>
+      <c r="AS138">
+        <v>1.29</v>
+      </c>
+      <c r="AT138">
+        <v>2.91</v>
+      </c>
+      <c r="AU138">
+        <v>3</v>
+      </c>
+      <c r="AV138">
+        <v>4</v>
+      </c>
+      <c r="AW138">
+        <v>8</v>
+      </c>
+      <c r="AX138">
+        <v>3</v>
+      </c>
+      <c r="AY138">
+        <v>11</v>
+      </c>
+      <c r="AZ138">
+        <v>7</v>
+      </c>
+      <c r="BA138">
+        <v>6</v>
+      </c>
+      <c r="BB138">
+        <v>1</v>
+      </c>
+      <c r="BC138">
+        <v>7</v>
+      </c>
+      <c r="BD138">
+        <v>1.39</v>
+      </c>
+      <c r="BE138">
+        <v>7.9</v>
+      </c>
+      <c r="BF138">
+        <v>4.36</v>
+      </c>
+      <c r="BG138">
+        <v>1.51</v>
+      </c>
+      <c r="BH138">
+        <v>2.34</v>
+      </c>
+      <c r="BI138">
+        <v>1.95</v>
+      </c>
+      <c r="BJ138">
+        <v>1.85</v>
+      </c>
+      <c r="BK138">
+        <v>2.45</v>
+      </c>
+      <c r="BL138">
+        <v>1.46</v>
+      </c>
+      <c r="BM138">
+        <v>3.4</v>
+      </c>
+      <c r="BN138">
+        <v>1.23</v>
+      </c>
+      <c r="BO138">
+        <v>5.08</v>
+      </c>
+      <c r="BP138">
+        <v>1.08</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="890" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="250">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -547,6 +547,12 @@
     <t>['14']</t>
   </si>
   <si>
+    <t>['27', '89']</t>
+  </si>
+  <si>
+    <t>['63', '83']</t>
+  </si>
+  <si>
     <t>['1', '6']</t>
   </si>
   <si>
@@ -752,6 +758,12 @@
   </si>
   <si>
     <t>['24', '46', '54']</t>
+  </si>
+  <si>
+    <t>['34']</t>
+  </si>
+  <si>
+    <t>['46', '90+1']</t>
   </si>
 </sst>
 </file>
@@ -1113,7 +1125,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP138"/>
+  <dimension ref="A1:BP141"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1447,7 +1459,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ2">
         <v>0.7</v>
@@ -1575,7 +1587,7 @@
         <v>85</v>
       </c>
       <c r="P3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q3">
         <v>3.8</v>
@@ -1862,7 +1874,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ4">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2065,7 +2077,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AQ5">
         <v>1.89</v>
@@ -2480,7 +2492,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ7">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2605,7 +2617,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q8">
         <v>2.39</v>
@@ -2683,7 +2695,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ8">
         <v>0.92</v>
@@ -2889,7 +2901,7 @@
         <v>3</v>
       </c>
       <c r="AP9">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ9">
         <v>1.89</v>
@@ -3017,7 +3029,7 @@
         <v>85</v>
       </c>
       <c r="P10" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q10">
         <v>4.3</v>
@@ -3095,10 +3107,10 @@
         <v>1</v>
       </c>
       <c r="AP10">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AQ10">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AR10">
         <v>0.82</v>
@@ -3223,7 +3235,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q11">
         <v>2.8</v>
@@ -3510,7 +3522,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ12">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3635,7 +3647,7 @@
         <v>85</v>
       </c>
       <c r="P13" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q13">
         <v>2.43</v>
@@ -3841,7 +3853,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q14">
         <v>3.9</v>
@@ -4253,7 +4265,7 @@
         <v>85</v>
       </c>
       <c r="P16" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q16">
         <v>3.18</v>
@@ -4331,7 +4343,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ16">
         <v>2</v>
@@ -4459,7 +4471,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q17">
         <v>3</v>
@@ -4743,7 +4755,7 @@
         <v>2</v>
       </c>
       <c r="AP18">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AQ18">
         <v>1.67</v>
@@ -4871,7 +4883,7 @@
         <v>95</v>
       </c>
       <c r="P19" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q19">
         <v>2.71</v>
@@ -5077,7 +5089,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q20">
         <v>3.5</v>
@@ -5364,7 +5376,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ21">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR21">
         <v>1.02</v>
@@ -5489,7 +5501,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q22">
         <v>5</v>
@@ -5773,10 +5785,10 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ23">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR23">
         <v>1.93</v>
@@ -6394,7 +6406,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ26">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR26">
         <v>0</v>
@@ -6519,7 +6531,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q27">
         <v>2.25</v>
@@ -6725,7 +6737,7 @@
         <v>101</v>
       </c>
       <c r="P28" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q28">
         <v>4</v>
@@ -6931,7 +6943,7 @@
         <v>102</v>
       </c>
       <c r="P29" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q29">
         <v>2.2</v>
@@ -7009,7 +7021,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ29">
         <v>1.11</v>
@@ -7137,7 +7149,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q30">
         <v>3.75</v>
@@ -7215,7 +7227,7 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AQ30">
         <v>0.7</v>
@@ -7343,7 +7355,7 @@
         <v>104</v>
       </c>
       <c r="P31" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q31">
         <v>3.25</v>
@@ -7755,7 +7767,7 @@
         <v>91</v>
       </c>
       <c r="P33" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q33">
         <v>2.63</v>
@@ -7833,7 +7845,7 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ33">
         <v>2</v>
@@ -7961,7 +7973,7 @@
         <v>85</v>
       </c>
       <c r="P34" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q34">
         <v>3.8</v>
@@ -8042,7 +8054,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ34">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AR34">
         <v>0.98</v>
@@ -8167,7 +8179,7 @@
         <v>106</v>
       </c>
       <c r="P35" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q35">
         <v>2.8</v>
@@ -8785,7 +8797,7 @@
         <v>85</v>
       </c>
       <c r="P38" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q38">
         <v>5</v>
@@ -8991,7 +9003,7 @@
         <v>85</v>
       </c>
       <c r="P39" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q39">
         <v>3.1</v>
@@ -9403,7 +9415,7 @@
         <v>110</v>
       </c>
       <c r="P41" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q41">
         <v>3.25</v>
@@ -10021,7 +10033,7 @@
         <v>113</v>
       </c>
       <c r="P44" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q44">
         <v>3.4</v>
@@ -10102,7 +10114,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ44">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR44">
         <v>1.43</v>
@@ -10227,7 +10239,7 @@
         <v>113</v>
       </c>
       <c r="P45" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q45">
         <v>3.75</v>
@@ -10433,7 +10445,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q46">
         <v>3.75</v>
@@ -10511,7 +10523,7 @@
         <v>1</v>
       </c>
       <c r="AP46">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ46">
         <v>1.89</v>
@@ -10639,7 +10651,7 @@
         <v>85</v>
       </c>
       <c r="P47" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q47">
         <v>3</v>
@@ -10923,7 +10935,7 @@
         <v>0.67</v>
       </c>
       <c r="AP48">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ48">
         <v>0.92</v>
@@ -11051,7 +11063,7 @@
         <v>116</v>
       </c>
       <c r="P49" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -11132,7 +11144,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ49">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR49">
         <v>1.58</v>
@@ -11463,7 +11475,7 @@
         <v>85</v>
       </c>
       <c r="P51" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q51">
         <v>2.25</v>
@@ -11747,7 +11759,7 @@
         <v>0</v>
       </c>
       <c r="AP52">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ52">
         <v>0.5</v>
@@ -12287,7 +12299,7 @@
         <v>119</v>
       </c>
       <c r="P55" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q55">
         <v>5</v>
@@ -12365,7 +12377,7 @@
         <v>2</v>
       </c>
       <c r="AP55">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AQ55">
         <v>2</v>
@@ -12699,7 +12711,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q57">
         <v>3.75</v>
@@ -12780,7 +12792,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ57">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AR57">
         <v>1.79</v>
@@ -12905,7 +12917,7 @@
         <v>121</v>
       </c>
       <c r="P58" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q58">
         <v>2.3</v>
@@ -13111,7 +13123,7 @@
         <v>85</v>
       </c>
       <c r="P59" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q59">
         <v>3.2</v>
@@ -13523,7 +13535,7 @@
         <v>123</v>
       </c>
       <c r="P61" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q61">
         <v>4</v>
@@ -13601,7 +13613,7 @@
         <v>1.5</v>
       </c>
       <c r="AP61">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ61">
         <v>1.89</v>
@@ -13729,7 +13741,7 @@
         <v>124</v>
       </c>
       <c r="P62" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q62">
         <v>2.3</v>
@@ -13935,7 +13947,7 @@
         <v>85</v>
       </c>
       <c r="P63" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q63">
         <v>3.2</v>
@@ -14141,7 +14153,7 @@
         <v>125</v>
       </c>
       <c r="P64" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q64">
         <v>2.5</v>
@@ -14347,7 +14359,7 @@
         <v>126</v>
       </c>
       <c r="P65" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q65">
         <v>4</v>
@@ -14428,7 +14440,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ65">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR65">
         <v>1.07</v>
@@ -14553,7 +14565,7 @@
         <v>127</v>
       </c>
       <c r="P66" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q66">
         <v>3</v>
@@ -14631,7 +14643,7 @@
         <v>2</v>
       </c>
       <c r="AP66">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ66">
         <v>1.67</v>
@@ -14837,7 +14849,7 @@
         <v>0.8</v>
       </c>
       <c r="AP67">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AQ67">
         <v>0.7</v>
@@ -14965,7 +14977,7 @@
         <v>129</v>
       </c>
       <c r="P68" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q68">
         <v>5</v>
@@ -15249,10 +15261,10 @@
         <v>1.75</v>
       </c>
       <c r="AP69">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ69">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AR69">
         <v>1.6</v>
@@ -15458,7 +15470,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ70">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR70">
         <v>1.72</v>
@@ -15583,7 +15595,7 @@
         <v>132</v>
       </c>
       <c r="P71" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q71">
         <v>2.63</v>
@@ -15995,7 +16007,7 @@
         <v>85</v>
       </c>
       <c r="P73" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q73">
         <v>3.6</v>
@@ -16201,7 +16213,7 @@
         <v>85</v>
       </c>
       <c r="P74" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q74">
         <v>4.33</v>
@@ -16407,7 +16419,7 @@
         <v>134</v>
       </c>
       <c r="P75" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q75">
         <v>1.91</v>
@@ -16613,7 +16625,7 @@
         <v>135</v>
       </c>
       <c r="P76" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q76">
         <v>2.63</v>
@@ -16819,7 +16831,7 @@
         <v>85</v>
       </c>
       <c r="P77" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q77">
         <v>4.5</v>
@@ -17231,7 +17243,7 @@
         <v>137</v>
       </c>
       <c r="P79" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q79">
         <v>3.6</v>
@@ -17312,7 +17324,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ79">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR79">
         <v>1.7</v>
@@ -17515,7 +17527,7 @@
         <v>0.2</v>
       </c>
       <c r="AP80">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ80">
         <v>0.7</v>
@@ -17849,7 +17861,7 @@
         <v>140</v>
       </c>
       <c r="P82" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q82">
         <v>3.75</v>
@@ -18055,7 +18067,7 @@
         <v>85</v>
       </c>
       <c r="P83" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q83">
         <v>7.5</v>
@@ -18133,7 +18145,7 @@
         <v>2.25</v>
       </c>
       <c r="AP83">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AQ83">
         <v>1.89</v>
@@ -18467,7 +18479,7 @@
         <v>142</v>
       </c>
       <c r="P85" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q85">
         <v>3.75</v>
@@ -18548,7 +18560,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ85">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR85">
         <v>1.63</v>
@@ -18673,7 +18685,7 @@
         <v>85</v>
       </c>
       <c r="P86" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q86">
         <v>4.2</v>
@@ -18754,7 +18766,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ86">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR86">
         <v>1.42</v>
@@ -19291,7 +19303,7 @@
         <v>143</v>
       </c>
       <c r="P89" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q89">
         <v>2.62</v>
@@ -19497,7 +19509,7 @@
         <v>144</v>
       </c>
       <c r="P90" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q90">
         <v>3.1</v>
@@ -19781,7 +19793,7 @@
         <v>1.9</v>
       </c>
       <c r="AP91">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ91">
         <v>1.67</v>
@@ -19909,7 +19921,7 @@
         <v>146</v>
       </c>
       <c r="P92" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -19990,7 +20002,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ92">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AR92">
         <v>1.86</v>
@@ -20115,7 +20127,7 @@
         <v>147</v>
       </c>
       <c r="P93" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q93">
         <v>2.62</v>
@@ -20321,7 +20333,7 @@
         <v>148</v>
       </c>
       <c r="P94" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q94">
         <v>2.4</v>
@@ -20527,7 +20539,7 @@
         <v>149</v>
       </c>
       <c r="P95" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q95">
         <v>3.1</v>
@@ -20811,7 +20823,7 @@
         <v>1</v>
       </c>
       <c r="AP96">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AQ96">
         <v>1</v>
@@ -21020,7 +21032,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ97">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AR97">
         <v>1.82</v>
@@ -21145,7 +21157,7 @@
         <v>152</v>
       </c>
       <c r="P98" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q98">
         <v>2.3</v>
@@ -21351,7 +21363,7 @@
         <v>153</v>
       </c>
       <c r="P99" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q99">
         <v>6.5</v>
@@ -21557,7 +21569,7 @@
         <v>154</v>
       </c>
       <c r="P100" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q100">
         <v>4.33</v>
@@ -21763,7 +21775,7 @@
         <v>85</v>
       </c>
       <c r="P101" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q101">
         <v>3.88</v>
@@ -21844,7 +21856,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ101">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR101">
         <v>1.52</v>
@@ -22175,7 +22187,7 @@
         <v>85</v>
       </c>
       <c r="P103" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q103">
         <v>2.14</v>
@@ -22381,7 +22393,7 @@
         <v>150</v>
       </c>
       <c r="P104" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q104">
         <v>3.4</v>
@@ -22462,7 +22474,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ104">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR104">
         <v>1.56</v>
@@ -22665,7 +22677,7 @@
         <v>1.57</v>
       </c>
       <c r="AP105">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ105">
         <v>1.7</v>
@@ -22999,7 +23011,7 @@
         <v>85</v>
       </c>
       <c r="P107" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q107">
         <v>2.13</v>
@@ -23205,7 +23217,7 @@
         <v>157</v>
       </c>
       <c r="P108" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q108">
         <v>3.38</v>
@@ -23283,10 +23295,10 @@
         <v>1.83</v>
       </c>
       <c r="AP108">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ108">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR108">
         <v>1.44</v>
@@ -24235,7 +24247,7 @@
         <v>159</v>
       </c>
       <c r="P113" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q113">
         <v>3.4</v>
@@ -24519,7 +24531,7 @@
         <v>0.5</v>
       </c>
       <c r="AP114">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ114">
         <v>0.7</v>
@@ -24647,7 +24659,7 @@
         <v>161</v>
       </c>
       <c r="P115" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q115">
         <v>4.85</v>
@@ -24728,7 +24740,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ115">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR115">
         <v>1.19</v>
@@ -24931,7 +24943,7 @@
         <v>1.38</v>
       </c>
       <c r="AP116">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AQ116">
         <v>1.7</v>
@@ -25059,7 +25071,7 @@
         <v>85</v>
       </c>
       <c r="P117" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q117">
         <v>3.64</v>
@@ -25140,7 +25152,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ117">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR117">
         <v>1.09</v>
@@ -25471,7 +25483,7 @@
         <v>92</v>
       </c>
       <c r="P119" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q119">
         <v>4.4</v>
@@ -25758,7 +25770,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ120">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AR120">
         <v>1.62</v>
@@ -25883,7 +25895,7 @@
         <v>163</v>
       </c>
       <c r="P121" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q121">
         <v>2.93</v>
@@ -25964,7 +25976,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ121">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR121">
         <v>1.8</v>
@@ -26167,7 +26179,7 @@
         <v>0.88</v>
       </c>
       <c r="AP122">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ122">
         <v>0.7</v>
@@ -26373,7 +26385,7 @@
         <v>0.38</v>
       </c>
       <c r="AP123">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AQ123">
         <v>0.5</v>
@@ -26707,7 +26719,7 @@
         <v>166</v>
       </c>
       <c r="P125" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q125">
         <v>2.5</v>
@@ -26913,7 +26925,7 @@
         <v>167</v>
       </c>
       <c r="P126" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q126">
         <v>3.6</v>
@@ -27119,7 +27131,7 @@
         <v>168</v>
       </c>
       <c r="P127" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q127">
         <v>4.33</v>
@@ -27325,7 +27337,7 @@
         <v>169</v>
       </c>
       <c r="P128" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q128">
         <v>3.5</v>
@@ -27531,7 +27543,7 @@
         <v>170</v>
       </c>
       <c r="P129" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q129">
         <v>4.33</v>
@@ -27737,7 +27749,7 @@
         <v>171</v>
       </c>
       <c r="P130" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q130">
         <v>4.2</v>
@@ -27818,7 +27830,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ130">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR130">
         <v>1.45</v>
@@ -28973,7 +28985,7 @@
         <v>175</v>
       </c>
       <c r="P136" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q136">
         <v>3.2</v>
@@ -29542,6 +29554,624 @@
       </c>
       <c r="BP138">
         <v>1.08</v>
+      </c>
+    </row>
+    <row r="139" spans="1:68">
+      <c r="A139" s="1">
+        <v>138</v>
+      </c>
+      <c r="B139">
+        <v>7813958</v>
+      </c>
+      <c r="C139" t="s">
+        <v>68</v>
+      </c>
+      <c r="D139" t="s">
+        <v>69</v>
+      </c>
+      <c r="E139" s="2">
+        <v>45851.29166666666</v>
+      </c>
+      <c r="F139">
+        <v>20</v>
+      </c>
+      <c r="G139" t="s">
+        <v>70</v>
+      </c>
+      <c r="H139" t="s">
+        <v>81</v>
+      </c>
+      <c r="I139">
+        <v>1</v>
+      </c>
+      <c r="J139">
+        <v>1</v>
+      </c>
+      <c r="K139">
+        <v>2</v>
+      </c>
+      <c r="L139">
+        <v>2</v>
+      </c>
+      <c r="M139">
+        <v>1</v>
+      </c>
+      <c r="N139">
+        <v>3</v>
+      </c>
+      <c r="O139" t="s">
+        <v>177</v>
+      </c>
+      <c r="P139" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q139">
+        <v>2.3</v>
+      </c>
+      <c r="R139">
+        <v>2.2</v>
+      </c>
+      <c r="S139">
+        <v>5.5</v>
+      </c>
+      <c r="T139">
+        <v>1.44</v>
+      </c>
+      <c r="U139">
+        <v>2.63</v>
+      </c>
+      <c r="V139">
+        <v>3</v>
+      </c>
+      <c r="W139">
+        <v>1.36</v>
+      </c>
+      <c r="X139">
+        <v>9</v>
+      </c>
+      <c r="Y139">
+        <v>1.07</v>
+      </c>
+      <c r="Z139">
+        <v>1.74</v>
+      </c>
+      <c r="AA139">
+        <v>3.74</v>
+      </c>
+      <c r="AB139">
+        <v>4.63</v>
+      </c>
+      <c r="AC139">
+        <v>1.01</v>
+      </c>
+      <c r="AD139">
+        <v>8.6</v>
+      </c>
+      <c r="AE139">
+        <v>1.3</v>
+      </c>
+      <c r="AF139">
+        <v>2.97</v>
+      </c>
+      <c r="AG139">
+        <v>2.08</v>
+      </c>
+      <c r="AH139">
+        <v>1.73</v>
+      </c>
+      <c r="AI139">
+        <v>2</v>
+      </c>
+      <c r="AJ139">
+        <v>1.73</v>
+      </c>
+      <c r="AK139">
+        <v>1.18</v>
+      </c>
+      <c r="AL139">
+        <v>1.3</v>
+      </c>
+      <c r="AM139">
+        <v>2</v>
+      </c>
+      <c r="AN139">
+        <v>2.8</v>
+      </c>
+      <c r="AO139">
+        <v>1.33</v>
+      </c>
+      <c r="AP139">
+        <v>2.82</v>
+      </c>
+      <c r="AQ139">
+        <v>1.2</v>
+      </c>
+      <c r="AR139">
+        <v>1.67</v>
+      </c>
+      <c r="AS139">
+        <v>1.4</v>
+      </c>
+      <c r="AT139">
+        <v>3.07</v>
+      </c>
+      <c r="AU139">
+        <v>5</v>
+      </c>
+      <c r="AV139">
+        <v>2</v>
+      </c>
+      <c r="AW139">
+        <v>8</v>
+      </c>
+      <c r="AX139">
+        <v>4</v>
+      </c>
+      <c r="AY139">
+        <v>13</v>
+      </c>
+      <c r="AZ139">
+        <v>6</v>
+      </c>
+      <c r="BA139">
+        <v>4</v>
+      </c>
+      <c r="BB139">
+        <v>3</v>
+      </c>
+      <c r="BC139">
+        <v>7</v>
+      </c>
+      <c r="BD139">
+        <v>1.58</v>
+      </c>
+      <c r="BE139">
+        <v>7.22</v>
+      </c>
+      <c r="BF139">
+        <v>3.3</v>
+      </c>
+      <c r="BG139">
+        <v>1.52</v>
+      </c>
+      <c r="BH139">
+        <v>2.33</v>
+      </c>
+      <c r="BI139">
+        <v>1.9</v>
+      </c>
+      <c r="BJ139">
+        <v>1.8</v>
+      </c>
+      <c r="BK139">
+        <v>2.48</v>
+      </c>
+      <c r="BL139">
+        <v>1.45</v>
+      </c>
+      <c r="BM139">
+        <v>3.44</v>
+      </c>
+      <c r="BN139">
+        <v>1.23</v>
+      </c>
+      <c r="BO139">
+        <v>5.16</v>
+      </c>
+      <c r="BP139">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="140" spans="1:68">
+      <c r="A140" s="1">
+        <v>139</v>
+      </c>
+      <c r="B140">
+        <v>7813959</v>
+      </c>
+      <c r="C140" t="s">
+        <v>68</v>
+      </c>
+      <c r="D140" t="s">
+        <v>69</v>
+      </c>
+      <c r="E140" s="2">
+        <v>45851.29166666666</v>
+      </c>
+      <c r="F140">
+        <v>20</v>
+      </c>
+      <c r="G140" t="s">
+        <v>76</v>
+      </c>
+      <c r="H140" t="s">
+        <v>78</v>
+      </c>
+      <c r="I140">
+        <v>1</v>
+      </c>
+      <c r="J140">
+        <v>0</v>
+      </c>
+      <c r="K140">
+        <v>1</v>
+      </c>
+      <c r="L140">
+        <v>1</v>
+      </c>
+      <c r="M140">
+        <v>1</v>
+      </c>
+      <c r="N140">
+        <v>2</v>
+      </c>
+      <c r="O140" t="s">
+        <v>154</v>
+      </c>
+      <c r="P140" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q140">
+        <v>2.88</v>
+      </c>
+      <c r="R140">
+        <v>2.1</v>
+      </c>
+      <c r="S140">
+        <v>4</v>
+      </c>
+      <c r="T140">
+        <v>1.44</v>
+      </c>
+      <c r="U140">
+        <v>2.63</v>
+      </c>
+      <c r="V140">
+        <v>3.25</v>
+      </c>
+      <c r="W140">
+        <v>1.33</v>
+      </c>
+      <c r="X140">
+        <v>9</v>
+      </c>
+      <c r="Y140">
+        <v>1.07</v>
+      </c>
+      <c r="Z140">
+        <v>2.09</v>
+      </c>
+      <c r="AA140">
+        <v>3.14</v>
+      </c>
+      <c r="AB140">
+        <v>3.09</v>
+      </c>
+      <c r="AC140">
+        <v>1.01</v>
+      </c>
+      <c r="AD140">
+        <v>8.5</v>
+      </c>
+      <c r="AE140">
+        <v>1.31</v>
+      </c>
+      <c r="AF140">
+        <v>2.92</v>
+      </c>
+      <c r="AG140">
+        <v>2</v>
+      </c>
+      <c r="AH140">
+        <v>1.67</v>
+      </c>
+      <c r="AI140">
+        <v>1.83</v>
+      </c>
+      <c r="AJ140">
+        <v>1.83</v>
+      </c>
+      <c r="AK140">
+        <v>1.3</v>
+      </c>
+      <c r="AL140">
+        <v>1.36</v>
+      </c>
+      <c r="AM140">
+        <v>1.62</v>
+      </c>
+      <c r="AN140">
+        <v>1.89</v>
+      </c>
+      <c r="AO140">
+        <v>1.13</v>
+      </c>
+      <c r="AP140">
+        <v>1.8</v>
+      </c>
+      <c r="AQ140">
+        <v>1.11</v>
+      </c>
+      <c r="AR140">
+        <v>1.63</v>
+      </c>
+      <c r="AS140">
+        <v>1.23</v>
+      </c>
+      <c r="AT140">
+        <v>2.86</v>
+      </c>
+      <c r="AU140">
+        <v>3</v>
+      </c>
+      <c r="AV140">
+        <v>3</v>
+      </c>
+      <c r="AW140">
+        <v>3</v>
+      </c>
+      <c r="AX140">
+        <v>4</v>
+      </c>
+      <c r="AY140">
+        <v>6</v>
+      </c>
+      <c r="AZ140">
+        <v>7</v>
+      </c>
+      <c r="BA140">
+        <v>6</v>
+      </c>
+      <c r="BB140">
+        <v>9</v>
+      </c>
+      <c r="BC140">
+        <v>15</v>
+      </c>
+      <c r="BD140">
+        <v>1.65</v>
+      </c>
+      <c r="BE140">
+        <v>6.97</v>
+      </c>
+      <c r="BF140">
+        <v>3.06</v>
+      </c>
+      <c r="BG140">
+        <v>1.59</v>
+      </c>
+      <c r="BH140">
+        <v>2.2</v>
+      </c>
+      <c r="BI140">
+        <v>2</v>
+      </c>
+      <c r="BJ140">
+        <v>1.72</v>
+      </c>
+      <c r="BK140">
+        <v>2.64</v>
+      </c>
+      <c r="BL140">
+        <v>1.4</v>
+      </c>
+      <c r="BM140">
+        <v>3.75</v>
+      </c>
+      <c r="BN140">
+        <v>1.19</v>
+      </c>
+      <c r="BO140">
+        <v>5.75</v>
+      </c>
+      <c r="BP140">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="141" spans="1:68">
+      <c r="A141" s="1">
+        <v>140</v>
+      </c>
+      <c r="B141">
+        <v>7813960</v>
+      </c>
+      <c r="C141" t="s">
+        <v>68</v>
+      </c>
+      <c r="D141" t="s">
+        <v>69</v>
+      </c>
+      <c r="E141" s="2">
+        <v>45851.29166666666</v>
+      </c>
+      <c r="F141">
+        <v>20</v>
+      </c>
+      <c r="G141" t="s">
+        <v>73</v>
+      </c>
+      <c r="H141" t="s">
+        <v>75</v>
+      </c>
+      <c r="I141">
+        <v>0</v>
+      </c>
+      <c r="J141">
+        <v>0</v>
+      </c>
+      <c r="K141">
+        <v>0</v>
+      </c>
+      <c r="L141">
+        <v>2</v>
+      </c>
+      <c r="M141">
+        <v>2</v>
+      </c>
+      <c r="N141">
+        <v>4</v>
+      </c>
+      <c r="O141" t="s">
+        <v>178</v>
+      </c>
+      <c r="P141" t="s">
+        <v>249</v>
+      </c>
+      <c r="Q141">
+        <v>4.75</v>
+      </c>
+      <c r="R141">
+        <v>2.1</v>
+      </c>
+      <c r="S141">
+        <v>2.6</v>
+      </c>
+      <c r="T141">
+        <v>1.44</v>
+      </c>
+      <c r="U141">
+        <v>2.63</v>
+      </c>
+      <c r="V141">
+        <v>3.25</v>
+      </c>
+      <c r="W141">
+        <v>1.33</v>
+      </c>
+      <c r="X141">
+        <v>9</v>
+      </c>
+      <c r="Y141">
+        <v>1.07</v>
+      </c>
+      <c r="Z141">
+        <v>3.84</v>
+      </c>
+      <c r="AA141">
+        <v>3.28</v>
+      </c>
+      <c r="AB141">
+        <v>1.8</v>
+      </c>
+      <c r="AC141">
+        <v>1.01</v>
+      </c>
+      <c r="AD141">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AE141">
+        <v>1.32</v>
+      </c>
+      <c r="AF141">
+        <v>2.88</v>
+      </c>
+      <c r="AG141">
+        <v>2.05</v>
+      </c>
+      <c r="AH141">
+        <v>1.65</v>
+      </c>
+      <c r="AI141">
+        <v>1.91</v>
+      </c>
+      <c r="AJ141">
+        <v>1.8</v>
+      </c>
+      <c r="AK141">
+        <v>1.83</v>
+      </c>
+      <c r="AL141">
+        <v>1.33</v>
+      </c>
+      <c r="AM141">
+        <v>1.25</v>
+      </c>
+      <c r="AN141">
+        <v>0.8</v>
+      </c>
+      <c r="AO141">
+        <v>1.2</v>
+      </c>
+      <c r="AP141">
+        <v>0.82</v>
+      </c>
+      <c r="AQ141">
+        <v>1.18</v>
+      </c>
+      <c r="AR141">
+        <v>1.16</v>
+      </c>
+      <c r="AS141">
+        <v>1.34</v>
+      </c>
+      <c r="AT141">
+        <v>2.5</v>
+      </c>
+      <c r="AU141">
+        <v>4</v>
+      </c>
+      <c r="AV141">
+        <v>4</v>
+      </c>
+      <c r="AW141">
+        <v>1</v>
+      </c>
+      <c r="AX141">
+        <v>9</v>
+      </c>
+      <c r="AY141">
+        <v>5</v>
+      </c>
+      <c r="AZ141">
+        <v>13</v>
+      </c>
+      <c r="BA141">
+        <v>2</v>
+      </c>
+      <c r="BB141">
+        <v>5</v>
+      </c>
+      <c r="BC141">
+        <v>7</v>
+      </c>
+      <c r="BD141">
+        <v>3.46</v>
+      </c>
+      <c r="BE141">
+        <v>7.11</v>
+      </c>
+      <c r="BF141">
+        <v>1.55</v>
+      </c>
+      <c r="BG141">
+        <v>1.68</v>
+      </c>
+      <c r="BH141">
+        <v>2.05</v>
+      </c>
+      <c r="BI141">
+        <v>2.15</v>
+      </c>
+      <c r="BJ141">
+        <v>1.62</v>
+      </c>
+      <c r="BK141">
+        <v>2.9</v>
+      </c>
+      <c r="BL141">
+        <v>1.32</v>
+      </c>
+      <c r="BM141">
+        <v>4.24</v>
+      </c>
+      <c r="BN141">
+        <v>1.14</v>
+      </c>
+      <c r="BO141">
+        <v>6.71</v>
+      </c>
+      <c r="BP141">
+        <v>1.02</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="255">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -553,6 +553,15 @@
     <t>['63', '83']</t>
   </si>
   <si>
+    <t>['69', '77', '90+4']</t>
+  </si>
+  <si>
+    <t>['14', '60']</t>
+  </si>
+  <si>
+    <t>['70']</t>
+  </si>
+  <si>
     <t>['1', '6']</t>
   </si>
   <si>
@@ -764,6 +773,12 @@
   </si>
   <si>
     <t>['46', '90+1']</t>
+  </si>
+  <si>
+    <t>['3', '29', '63', '73']</t>
+  </si>
+  <si>
+    <t>['45+4', '90+1']</t>
   </si>
 </sst>
 </file>
@@ -1125,7 +1140,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP141"/>
+  <dimension ref="A1:BP145"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1587,7 +1602,7 @@
         <v>85</v>
       </c>
       <c r="P3" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="Q3">
         <v>3.8</v>
@@ -2080,7 +2095,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ5">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2489,7 +2504,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AQ7">
         <v>1.2</v>
@@ -2617,7 +2632,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="Q8">
         <v>2.39</v>
@@ -2904,7 +2919,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ9">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AR9">
         <v>2.58</v>
@@ -3029,7 +3044,7 @@
         <v>85</v>
       </c>
       <c r="P10" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="Q10">
         <v>4.3</v>
@@ -3235,7 +3250,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q11">
         <v>2.8</v>
@@ -3313,7 +3328,7 @@
         <v>3</v>
       </c>
       <c r="AP11">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AQ11">
         <v>1.67</v>
@@ -3519,7 +3534,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ12">
         <v>1.2</v>
@@ -3647,7 +3662,7 @@
         <v>85</v>
       </c>
       <c r="P13" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="Q13">
         <v>2.43</v>
@@ -3853,7 +3868,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="Q14">
         <v>3.9</v>
@@ -4265,7 +4280,7 @@
         <v>85</v>
       </c>
       <c r="P16" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Q16">
         <v>3.18</v>
@@ -4346,7 +4361,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ16">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AR16">
         <v>1.61</v>
@@ -4471,7 +4486,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="Q17">
         <v>3</v>
@@ -4549,7 +4564,7 @@
         <v>1.5</v>
       </c>
       <c r="AP17">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ17">
         <v>0.7</v>
@@ -4883,7 +4898,7 @@
         <v>95</v>
       </c>
       <c r="P19" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q19">
         <v>2.71</v>
@@ -4961,7 +4976,7 @@
         <v>0.5</v>
       </c>
       <c r="AP19">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ19">
         <v>0.92</v>
@@ -5089,7 +5104,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q20">
         <v>3.5</v>
@@ -5167,10 +5182,10 @@
         <v>1.5</v>
       </c>
       <c r="AP20">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AQ20">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AR20">
         <v>1.06</v>
@@ -5501,7 +5516,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q22">
         <v>5</v>
@@ -5991,7 +6006,7 @@
         <v>1.33</v>
       </c>
       <c r="AP24">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ24">
         <v>0.92</v>
@@ -6197,10 +6212,10 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ25">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR25">
         <v>2.07</v>
@@ -6531,7 +6546,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q27">
         <v>2.25</v>
@@ -6737,7 +6752,7 @@
         <v>101</v>
       </c>
       <c r="P28" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q28">
         <v>4</v>
@@ -6943,7 +6958,7 @@
         <v>102</v>
       </c>
       <c r="P29" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q29">
         <v>2.2</v>
@@ -7024,7 +7039,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ29">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR29">
         <v>1.22</v>
@@ -7149,7 +7164,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q30">
         <v>3.75</v>
@@ -7355,7 +7370,7 @@
         <v>104</v>
       </c>
       <c r="P31" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q31">
         <v>3.25</v>
@@ -7767,7 +7782,7 @@
         <v>91</v>
       </c>
       <c r="P33" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q33">
         <v>2.63</v>
@@ -7848,7 +7863,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ33">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AR33">
         <v>1.69</v>
@@ -7973,7 +7988,7 @@
         <v>85</v>
       </c>
       <c r="P34" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q34">
         <v>3.8</v>
@@ -8179,7 +8194,7 @@
         <v>106</v>
       </c>
       <c r="P35" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q35">
         <v>2.8</v>
@@ -8257,7 +8272,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AQ35">
         <v>1.7</v>
@@ -8466,7 +8481,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ36">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR36">
         <v>0</v>
@@ -8669,7 +8684,7 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AQ37">
         <v>0.5</v>
@@ -8797,7 +8812,7 @@
         <v>85</v>
       </c>
       <c r="P38" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q38">
         <v>5</v>
@@ -8875,7 +8890,7 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ38">
         <v>1.89</v>
@@ -9003,7 +9018,7 @@
         <v>85</v>
       </c>
       <c r="P39" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q39">
         <v>3.1</v>
@@ -9415,7 +9430,7 @@
         <v>110</v>
       </c>
       <c r="P41" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q41">
         <v>3.25</v>
@@ -9493,7 +9508,7 @@
         <v>1.5</v>
       </c>
       <c r="AP41">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ41">
         <v>1.7</v>
@@ -9908,7 +9923,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ43">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR43">
         <v>1.02</v>
@@ -10033,7 +10048,7 @@
         <v>113</v>
       </c>
       <c r="P44" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q44">
         <v>3.4</v>
@@ -10111,7 +10126,7 @@
         <v>0.5</v>
       </c>
       <c r="AP44">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ44">
         <v>1.2</v>
@@ -10239,7 +10254,7 @@
         <v>113</v>
       </c>
       <c r="P45" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q45">
         <v>3.75</v>
@@ -10317,7 +10332,7 @@
         <v>1.83</v>
       </c>
       <c r="AP45">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ45">
         <v>1.67</v>
@@ -10445,7 +10460,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q46">
         <v>3.75</v>
@@ -10526,7 +10541,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ46">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AR46">
         <v>1.33</v>
@@ -10651,7 +10666,7 @@
         <v>85</v>
       </c>
       <c r="P47" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q47">
         <v>3</v>
@@ -10732,7 +10747,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ47">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR47">
         <v>1.74</v>
@@ -11063,7 +11078,7 @@
         <v>116</v>
       </c>
       <c r="P49" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -11350,7 +11365,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ50">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR50">
         <v>1.01</v>
@@ -11475,7 +11490,7 @@
         <v>85</v>
       </c>
       <c r="P51" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q51">
         <v>2.25</v>
@@ -11553,7 +11568,7 @@
         <v>0.57</v>
       </c>
       <c r="AP51">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AQ51">
         <v>0.92</v>
@@ -12299,7 +12314,7 @@
         <v>119</v>
       </c>
       <c r="P55" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q55">
         <v>5</v>
@@ -12380,7 +12395,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ55">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AR55">
         <v>1.32</v>
@@ -12711,7 +12726,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q57">
         <v>3.75</v>
@@ -12917,7 +12932,7 @@
         <v>121</v>
       </c>
       <c r="P58" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q58">
         <v>2.3</v>
@@ -12995,7 +13010,7 @@
         <v>1</v>
       </c>
       <c r="AP58">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AQ58">
         <v>0.7</v>
@@ -13123,7 +13138,7 @@
         <v>85</v>
       </c>
       <c r="P59" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q59">
         <v>3.2</v>
@@ -13410,7 +13425,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ60">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR60">
         <v>2.02</v>
@@ -13535,7 +13550,7 @@
         <v>123</v>
       </c>
       <c r="P61" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q61">
         <v>4</v>
@@ -13741,7 +13756,7 @@
         <v>124</v>
       </c>
       <c r="P62" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q62">
         <v>2.3</v>
@@ -13822,7 +13837,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ62">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR62">
         <v>1.79</v>
@@ -13947,7 +13962,7 @@
         <v>85</v>
       </c>
       <c r="P63" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q63">
         <v>3.2</v>
@@ -14025,7 +14040,7 @@
         <v>1.88</v>
       </c>
       <c r="AP63">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ63">
         <v>1.67</v>
@@ -14153,7 +14168,7 @@
         <v>125</v>
       </c>
       <c r="P64" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q64">
         <v>2.5</v>
@@ -14359,7 +14374,7 @@
         <v>126</v>
       </c>
       <c r="P65" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q65">
         <v>4</v>
@@ -14565,7 +14580,7 @@
         <v>127</v>
       </c>
       <c r="P66" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q66">
         <v>3</v>
@@ -14977,7 +14992,7 @@
         <v>129</v>
       </c>
       <c r="P68" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q68">
         <v>5</v>
@@ -15058,7 +15073,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ68">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AR68">
         <v>0</v>
@@ -15595,7 +15610,7 @@
         <v>132</v>
       </c>
       <c r="P71" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q71">
         <v>2.63</v>
@@ -15673,7 +15688,7 @@
         <v>0</v>
       </c>
       <c r="AP71">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ71">
         <v>0.5</v>
@@ -15879,7 +15894,7 @@
         <v>0.25</v>
       </c>
       <c r="AP72">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ72">
         <v>0.7</v>
@@ -16007,7 +16022,7 @@
         <v>85</v>
       </c>
       <c r="P73" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q73">
         <v>3.6</v>
@@ -16213,7 +16228,7 @@
         <v>85</v>
       </c>
       <c r="P74" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q74">
         <v>4.33</v>
@@ -16419,7 +16434,7 @@
         <v>134</v>
       </c>
       <c r="P75" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="Q75">
         <v>1.91</v>
@@ -16497,10 +16512,10 @@
         <v>0.75</v>
       </c>
       <c r="AP75">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AQ75">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR75">
         <v>1.33</v>
@@ -16625,7 +16640,7 @@
         <v>135</v>
       </c>
       <c r="P76" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q76">
         <v>2.63</v>
@@ -16703,10 +16718,10 @@
         <v>1.25</v>
       </c>
       <c r="AP76">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AQ76">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR76">
         <v>0</v>
@@ -16831,7 +16846,7 @@
         <v>85</v>
       </c>
       <c r="P77" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q77">
         <v>4.5</v>
@@ -16912,7 +16927,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ77">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AR77">
         <v>1.89</v>
@@ -17243,7 +17258,7 @@
         <v>137</v>
       </c>
       <c r="P79" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q79">
         <v>3.6</v>
@@ -17736,7 +17751,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ81">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR81">
         <v>1.17</v>
@@ -17861,7 +17876,7 @@
         <v>140</v>
       </c>
       <c r="P82" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q82">
         <v>3.75</v>
@@ -17942,7 +17957,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ82">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AR82">
         <v>1.65</v>
@@ -18067,7 +18082,7 @@
         <v>85</v>
       </c>
       <c r="P83" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q83">
         <v>7.5</v>
@@ -18351,7 +18366,7 @@
         <v>1.11</v>
       </c>
       <c r="AP84">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AQ84">
         <v>0.92</v>
@@ -18479,7 +18494,7 @@
         <v>142</v>
       </c>
       <c r="P85" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q85">
         <v>3.75</v>
@@ -18557,7 +18572,7 @@
         <v>1.33</v>
       </c>
       <c r="AP85">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ85">
         <v>1.18</v>
@@ -18685,7 +18700,7 @@
         <v>85</v>
       </c>
       <c r="P86" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q86">
         <v>4.2</v>
@@ -18763,7 +18778,7 @@
         <v>1.75</v>
       </c>
       <c r="AP86">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ86">
         <v>1.18</v>
@@ -18972,7 +18987,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ87">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR87">
         <v>1.66</v>
@@ -19178,7 +19193,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ88">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AR88">
         <v>1.04</v>
@@ -19303,7 +19318,7 @@
         <v>143</v>
       </c>
       <c r="P89" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q89">
         <v>2.62</v>
@@ -19509,7 +19524,7 @@
         <v>144</v>
       </c>
       <c r="P90" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q90">
         <v>3.1</v>
@@ -19921,7 +19936,7 @@
         <v>146</v>
       </c>
       <c r="P92" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20127,7 +20142,7 @@
         <v>147</v>
       </c>
       <c r="P93" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q93">
         <v>2.62</v>
@@ -20205,10 +20220,10 @@
         <v>2.2</v>
       </c>
       <c r="AP93">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AQ93">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AR93">
         <v>1.35</v>
@@ -20333,7 +20348,7 @@
         <v>148</v>
       </c>
       <c r="P94" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q94">
         <v>2.4</v>
@@ -20411,7 +20426,7 @@
         <v>0.17</v>
       </c>
       <c r="AP94">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AQ94">
         <v>0.7</v>
@@ -20539,7 +20554,7 @@
         <v>149</v>
       </c>
       <c r="P95" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q95">
         <v>3.1</v>
@@ -20826,7 +20841,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ96">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR96">
         <v>1.3</v>
@@ -21157,7 +21172,7 @@
         <v>152</v>
       </c>
       <c r="P98" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q98">
         <v>2.3</v>
@@ -21363,7 +21378,7 @@
         <v>153</v>
       </c>
       <c r="P99" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q99">
         <v>6.5</v>
@@ -21569,7 +21584,7 @@
         <v>154</v>
       </c>
       <c r="P100" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q100">
         <v>4.33</v>
@@ -21650,7 +21665,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ100">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AR100">
         <v>1.06</v>
@@ -21775,7 +21790,7 @@
         <v>85</v>
       </c>
       <c r="P101" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q101">
         <v>3.88</v>
@@ -22187,7 +22202,7 @@
         <v>85</v>
       </c>
       <c r="P103" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q103">
         <v>2.14</v>
@@ -22268,7 +22283,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ103">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR103">
         <v>1.65</v>
@@ -22393,7 +22408,7 @@
         <v>150</v>
       </c>
       <c r="P104" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q104">
         <v>3.4</v>
@@ -22471,7 +22486,7 @@
         <v>2</v>
       </c>
       <c r="AP104">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AQ104">
         <v>1.18</v>
@@ -22883,7 +22898,7 @@
         <v>0</v>
       </c>
       <c r="AP106">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ106">
         <v>0.5</v>
@@ -23011,7 +23026,7 @@
         <v>85</v>
       </c>
       <c r="P107" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q107">
         <v>2.13</v>
@@ -23217,7 +23232,7 @@
         <v>157</v>
       </c>
       <c r="P108" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q108">
         <v>3.38</v>
@@ -23504,7 +23519,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ109">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR109">
         <v>1.41</v>
@@ -23707,10 +23722,10 @@
         <v>2.33</v>
       </c>
       <c r="AP110">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AQ110">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AR110">
         <v>1.42</v>
@@ -23913,10 +23928,10 @@
         <v>1.14</v>
       </c>
       <c r="AP111">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ111">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR111">
         <v>1.5</v>
@@ -24119,7 +24134,7 @@
         <v>1</v>
       </c>
       <c r="AP112">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ112">
         <v>0.7</v>
@@ -24247,7 +24262,7 @@
         <v>159</v>
       </c>
       <c r="P113" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q113">
         <v>3.4</v>
@@ -24659,7 +24674,7 @@
         <v>161</v>
       </c>
       <c r="P115" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q115">
         <v>4.85</v>
@@ -25071,7 +25086,7 @@
         <v>85</v>
       </c>
       <c r="P117" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q117">
         <v>3.64</v>
@@ -25483,7 +25498,7 @@
         <v>92</v>
       </c>
       <c r="P119" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q119">
         <v>4.4</v>
@@ -25564,7 +25579,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ119">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AR119">
         <v>1.71</v>
@@ -25767,7 +25782,7 @@
         <v>1.14</v>
       </c>
       <c r="AP120">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AQ120">
         <v>1.11</v>
@@ -25895,7 +25910,7 @@
         <v>163</v>
       </c>
       <c r="P121" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q121">
         <v>2.93</v>
@@ -26591,10 +26606,10 @@
         <v>1.13</v>
       </c>
       <c r="AP124">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ124">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR124">
         <v>1.38</v>
@@ -26719,7 +26734,7 @@
         <v>166</v>
       </c>
       <c r="P125" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q125">
         <v>2.5</v>
@@ -26800,7 +26815,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ125">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AR125">
         <v>1.82</v>
@@ -26925,7 +26940,7 @@
         <v>167</v>
       </c>
       <c r="P126" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q126">
         <v>3.6</v>
@@ -27131,7 +27146,7 @@
         <v>168</v>
       </c>
       <c r="P127" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q127">
         <v>4.33</v>
@@ -27209,7 +27224,7 @@
         <v>2.29</v>
       </c>
       <c r="AP127">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ127">
         <v>1.89</v>
@@ -27337,7 +27352,7 @@
         <v>169</v>
       </c>
       <c r="P128" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q128">
         <v>3.5</v>
@@ -27418,7 +27433,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ128">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AR128">
         <v>1.71</v>
@@ -27543,7 +27558,7 @@
         <v>170</v>
       </c>
       <c r="P129" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q129">
         <v>4.33</v>
@@ -27621,7 +27636,7 @@
         <v>2.13</v>
       </c>
       <c r="AP129">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AQ129">
         <v>1.89</v>
@@ -27749,7 +27764,7 @@
         <v>171</v>
       </c>
       <c r="P130" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q130">
         <v>4.2</v>
@@ -28036,7 +28051,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ131">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR131">
         <v>1.67</v>
@@ -28239,7 +28254,7 @@
         <v>1.56</v>
       </c>
       <c r="AP132">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ132">
         <v>1.7</v>
@@ -28445,10 +28460,10 @@
         <v>2.25</v>
       </c>
       <c r="AP133">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ133">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AR133">
         <v>1.61</v>
@@ -28985,7 +29000,7 @@
         <v>175</v>
       </c>
       <c r="P136" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q136">
         <v>3.2</v>
@@ -29269,7 +29284,7 @@
         <v>0.78</v>
       </c>
       <c r="AP137">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AQ137">
         <v>0.7</v>
@@ -29478,7 +29493,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ138">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR138">
         <v>1.62</v>
@@ -29603,7 +29618,7 @@
         <v>177</v>
       </c>
       <c r="P139" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q139">
         <v>2.3</v>
@@ -30015,7 +30030,7 @@
         <v>178</v>
       </c>
       <c r="P141" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q141">
         <v>4.75</v>
@@ -30172,6 +30187,830 @@
       </c>
       <c r="BP141">
         <v>1.02</v>
+      </c>
+    </row>
+    <row r="142" spans="1:68">
+      <c r="A142" s="1">
+        <v>141</v>
+      </c>
+      <c r="B142">
+        <v>7813961</v>
+      </c>
+      <c r="C142" t="s">
+        <v>68</v>
+      </c>
+      <c r="D142" t="s">
+        <v>69</v>
+      </c>
+      <c r="E142" s="2">
+        <v>45857.29166666666</v>
+      </c>
+      <c r="F142">
+        <v>21</v>
+      </c>
+      <c r="G142" t="s">
+        <v>83</v>
+      </c>
+      <c r="H142" t="s">
+        <v>79</v>
+      </c>
+      <c r="I142">
+        <v>0</v>
+      </c>
+      <c r="J142">
+        <v>2</v>
+      </c>
+      <c r="K142">
+        <v>2</v>
+      </c>
+      <c r="L142">
+        <v>3</v>
+      </c>
+      <c r="M142">
+        <v>4</v>
+      </c>
+      <c r="N142">
+        <v>7</v>
+      </c>
+      <c r="O142" t="s">
+        <v>179</v>
+      </c>
+      <c r="P142" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q142">
+        <v>3.6</v>
+      </c>
+      <c r="R142">
+        <v>2.3</v>
+      </c>
+      <c r="S142">
+        <v>2.5</v>
+      </c>
+      <c r="T142">
+        <v>1.3</v>
+      </c>
+      <c r="U142">
+        <v>3.3</v>
+      </c>
+      <c r="V142">
+        <v>2.45</v>
+      </c>
+      <c r="W142">
+        <v>1.5</v>
+      </c>
+      <c r="X142">
+        <v>6</v>
+      </c>
+      <c r="Y142">
+        <v>1.12</v>
+      </c>
+      <c r="Z142">
+        <v>3.74</v>
+      </c>
+      <c r="AA142">
+        <v>3.5</v>
+      </c>
+      <c r="AB142">
+        <v>1.77</v>
+      </c>
+      <c r="AC142">
+        <v>1.01</v>
+      </c>
+      <c r="AD142">
+        <v>11</v>
+      </c>
+      <c r="AE142">
+        <v>1.16</v>
+      </c>
+      <c r="AF142">
+        <v>4.05</v>
+      </c>
+      <c r="AG142">
+        <v>1.65</v>
+      </c>
+      <c r="AH142">
+        <v>2</v>
+      </c>
+      <c r="AI142">
+        <v>1.62</v>
+      </c>
+      <c r="AJ142">
+        <v>2.2</v>
+      </c>
+      <c r="AK142">
+        <v>1.8</v>
+      </c>
+      <c r="AL142">
+        <v>1.29</v>
+      </c>
+      <c r="AM142">
+        <v>1.3</v>
+      </c>
+      <c r="AN142">
+        <v>2.13</v>
+      </c>
+      <c r="AO142">
+        <v>1.89</v>
+      </c>
+      <c r="AP142">
+        <v>1.89</v>
+      </c>
+      <c r="AQ142">
+        <v>2</v>
+      </c>
+      <c r="AR142">
+        <v>1.48</v>
+      </c>
+      <c r="AS142">
+        <v>1.77</v>
+      </c>
+      <c r="AT142">
+        <v>3.25</v>
+      </c>
+      <c r="AU142">
+        <v>6</v>
+      </c>
+      <c r="AV142">
+        <v>6</v>
+      </c>
+      <c r="AW142">
+        <v>7</v>
+      </c>
+      <c r="AX142">
+        <v>2</v>
+      </c>
+      <c r="AY142">
+        <v>13</v>
+      </c>
+      <c r="AZ142">
+        <v>8</v>
+      </c>
+      <c r="BA142">
+        <v>11</v>
+      </c>
+      <c r="BB142">
+        <v>2</v>
+      </c>
+      <c r="BC142">
+        <v>13</v>
+      </c>
+      <c r="BD142">
+        <v>2.49</v>
+      </c>
+      <c r="BE142">
+        <v>7.6</v>
+      </c>
+      <c r="BF142">
+        <v>1.71</v>
+      </c>
+      <c r="BG142">
+        <v>1.46</v>
+      </c>
+      <c r="BH142">
+        <v>2.38</v>
+      </c>
+      <c r="BI142">
+        <v>1.85</v>
+      </c>
+      <c r="BJ142">
+        <v>1.81</v>
+      </c>
+      <c r="BK142">
+        <v>2.42</v>
+      </c>
+      <c r="BL142">
+        <v>1.44</v>
+      </c>
+      <c r="BM142">
+        <v>3.34</v>
+      </c>
+      <c r="BN142">
+        <v>1.24</v>
+      </c>
+      <c r="BO142">
+        <v>5.34</v>
+      </c>
+      <c r="BP142">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="143" spans="1:68">
+      <c r="A143" s="1">
+        <v>142</v>
+      </c>
+      <c r="B143">
+        <v>7813962</v>
+      </c>
+      <c r="C143" t="s">
+        <v>68</v>
+      </c>
+      <c r="D143" t="s">
+        <v>69</v>
+      </c>
+      <c r="E143" s="2">
+        <v>45857.29166666666</v>
+      </c>
+      <c r="F143">
+        <v>21</v>
+      </c>
+      <c r="G143" t="s">
+        <v>78</v>
+      </c>
+      <c r="H143" t="s">
+        <v>73</v>
+      </c>
+      <c r="I143">
+        <v>1</v>
+      </c>
+      <c r="J143">
+        <v>1</v>
+      </c>
+      <c r="K143">
+        <v>2</v>
+      </c>
+      <c r="L143">
+        <v>2</v>
+      </c>
+      <c r="M143">
+        <v>2</v>
+      </c>
+      <c r="N143">
+        <v>4</v>
+      </c>
+      <c r="O143" t="s">
+        <v>180</v>
+      </c>
+      <c r="P143" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q143">
+        <v>2.4</v>
+      </c>
+      <c r="R143">
+        <v>2</v>
+      </c>
+      <c r="S143">
+        <v>5</v>
+      </c>
+      <c r="T143">
+        <v>1.48</v>
+      </c>
+      <c r="U143">
+        <v>2.56</v>
+      </c>
+      <c r="V143">
+        <v>3.34</v>
+      </c>
+      <c r="W143">
+        <v>1.28</v>
+      </c>
+      <c r="X143">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y143">
+        <v>1.02</v>
+      </c>
+      <c r="Z143">
+        <v>1.74</v>
+      </c>
+      <c r="AA143">
+        <v>3.28</v>
+      </c>
+      <c r="AB143">
+        <v>4.2</v>
+      </c>
+      <c r="AC143">
+        <v>1.05</v>
+      </c>
+      <c r="AD143">
+        <v>8</v>
+      </c>
+      <c r="AE143">
+        <v>1.5</v>
+      </c>
+      <c r="AF143">
+        <v>2.4</v>
+      </c>
+      <c r="AG143">
+        <v>2.3</v>
+      </c>
+      <c r="AH143">
+        <v>1.5</v>
+      </c>
+      <c r="AI143">
+        <v>2.2</v>
+      </c>
+      <c r="AJ143">
+        <v>1.62</v>
+      </c>
+      <c r="AK143">
+        <v>1.12</v>
+      </c>
+      <c r="AL143">
+        <v>1.26</v>
+      </c>
+      <c r="AM143">
+        <v>2.03</v>
+      </c>
+      <c r="AN143">
+        <v>1.36</v>
+      </c>
+      <c r="AO143">
+        <v>1.11</v>
+      </c>
+      <c r="AP143">
+        <v>1.33</v>
+      </c>
+      <c r="AQ143">
+        <v>1.1</v>
+      </c>
+      <c r="AR143">
+        <v>1.63</v>
+      </c>
+      <c r="AS143">
+        <v>1.02</v>
+      </c>
+      <c r="AT143">
+        <v>2.65</v>
+      </c>
+      <c r="AU143">
+        <v>6</v>
+      </c>
+      <c r="AV143">
+        <v>5</v>
+      </c>
+      <c r="AW143">
+        <v>6</v>
+      </c>
+      <c r="AX143">
+        <v>5</v>
+      </c>
+      <c r="AY143">
+        <v>12</v>
+      </c>
+      <c r="AZ143">
+        <v>10</v>
+      </c>
+      <c r="BA143">
+        <v>5</v>
+      </c>
+      <c r="BB143">
+        <v>2</v>
+      </c>
+      <c r="BC143">
+        <v>7</v>
+      </c>
+      <c r="BD143">
+        <v>1.44</v>
+      </c>
+      <c r="BE143">
+        <v>7.8</v>
+      </c>
+      <c r="BF143">
+        <v>3.38</v>
+      </c>
+      <c r="BG143">
+        <v>1.69</v>
+      </c>
+      <c r="BH143">
+        <v>2</v>
+      </c>
+      <c r="BI143">
+        <v>2.17</v>
+      </c>
+      <c r="BJ143">
+        <v>1.55</v>
+      </c>
+      <c r="BK143">
+        <v>2.97</v>
+      </c>
+      <c r="BL143">
+        <v>1.3</v>
+      </c>
+      <c r="BM143">
+        <v>4.62</v>
+      </c>
+      <c r="BN143">
+        <v>1.11</v>
+      </c>
+      <c r="BO143">
+        <v>7.14</v>
+      </c>
+      <c r="BP143">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="144" spans="1:68">
+      <c r="A144" s="1">
+        <v>143</v>
+      </c>
+      <c r="B144">
+        <v>7813963</v>
+      </c>
+      <c r="C144" t="s">
+        <v>68</v>
+      </c>
+      <c r="D144" t="s">
+        <v>69</v>
+      </c>
+      <c r="E144" s="2">
+        <v>45857.29166666666</v>
+      </c>
+      <c r="F144">
+        <v>21</v>
+      </c>
+      <c r="G144" t="s">
+        <v>75</v>
+      </c>
+      <c r="H144" t="s">
+        <v>74</v>
+      </c>
+      <c r="I144">
+        <v>0</v>
+      </c>
+      <c r="J144">
+        <v>1</v>
+      </c>
+      <c r="K144">
+        <v>1</v>
+      </c>
+      <c r="L144">
+        <v>0</v>
+      </c>
+      <c r="M144">
+        <v>1</v>
+      </c>
+      <c r="N144">
+        <v>1</v>
+      </c>
+      <c r="O144" t="s">
+        <v>85</v>
+      </c>
+      <c r="P144" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q144">
+        <v>2.5</v>
+      </c>
+      <c r="R144">
+        <v>2.2</v>
+      </c>
+      <c r="S144">
+        <v>3.75</v>
+      </c>
+      <c r="T144">
+        <v>1.37</v>
+      </c>
+      <c r="U144">
+        <v>3.01</v>
+      </c>
+      <c r="V144">
+        <v>2.84</v>
+      </c>
+      <c r="W144">
+        <v>1.4</v>
+      </c>
+      <c r="X144">
+        <v>6.5</v>
+      </c>
+      <c r="Y144">
+        <v>1.05</v>
+      </c>
+      <c r="Z144">
+        <v>1.83</v>
+      </c>
+      <c r="AA144">
+        <v>3.11</v>
+      </c>
+      <c r="AB144">
+        <v>3.97</v>
+      </c>
+      <c r="AC144">
+        <v>1.01</v>
+      </c>
+      <c r="AD144">
+        <v>11</v>
+      </c>
+      <c r="AE144">
+        <v>1.25</v>
+      </c>
+      <c r="AF144">
+        <v>3.6</v>
+      </c>
+      <c r="AG144">
+        <v>1.87</v>
+      </c>
+      <c r="AH144">
+        <v>1.83</v>
+      </c>
+      <c r="AI144">
+        <v>1.67</v>
+      </c>
+      <c r="AJ144">
+        <v>2.1</v>
+      </c>
+      <c r="AK144">
+        <v>1.26</v>
+      </c>
+      <c r="AL144">
+        <v>1.25</v>
+      </c>
+      <c r="AM144">
+        <v>1.73</v>
+      </c>
+      <c r="AN144">
+        <v>1.89</v>
+      </c>
+      <c r="AO144">
+        <v>1</v>
+      </c>
+      <c r="AP144">
+        <v>1.7</v>
+      </c>
+      <c r="AQ144">
+        <v>1.18</v>
+      </c>
+      <c r="AR144">
+        <v>1.35</v>
+      </c>
+      <c r="AS144">
+        <v>1.27</v>
+      </c>
+      <c r="AT144">
+        <v>2.62</v>
+      </c>
+      <c r="AU144">
+        <v>6</v>
+      </c>
+      <c r="AV144">
+        <v>4</v>
+      </c>
+      <c r="AW144">
+        <v>7</v>
+      </c>
+      <c r="AX144">
+        <v>2</v>
+      </c>
+      <c r="AY144">
+        <v>13</v>
+      </c>
+      <c r="AZ144">
+        <v>6</v>
+      </c>
+      <c r="BA144">
+        <v>4</v>
+      </c>
+      <c r="BB144">
+        <v>1</v>
+      </c>
+      <c r="BC144">
+        <v>5</v>
+      </c>
+      <c r="BD144">
+        <v>1.5</v>
+      </c>
+      <c r="BE144">
+        <v>7.34</v>
+      </c>
+      <c r="BF144">
+        <v>3.66</v>
+      </c>
+      <c r="BG144">
+        <v>1.59</v>
+      </c>
+      <c r="BH144">
+        <v>2.2</v>
+      </c>
+      <c r="BI144">
+        <v>2</v>
+      </c>
+      <c r="BJ144">
+        <v>1.72</v>
+      </c>
+      <c r="BK144">
+        <v>2.65</v>
+      </c>
+      <c r="BL144">
+        <v>1.39</v>
+      </c>
+      <c r="BM144">
+        <v>3.76</v>
+      </c>
+      <c r="BN144">
+        <v>1.18</v>
+      </c>
+      <c r="BO144">
+        <v>5.76</v>
+      </c>
+      <c r="BP144">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="145" spans="1:68">
+      <c r="A145" s="1">
+        <v>144</v>
+      </c>
+      <c r="B145">
+        <v>7813964</v>
+      </c>
+      <c r="C145" t="s">
+        <v>68</v>
+      </c>
+      <c r="D145" t="s">
+        <v>69</v>
+      </c>
+      <c r="E145" s="2">
+        <v>45857.29166666666</v>
+      </c>
+      <c r="F145">
+        <v>21</v>
+      </c>
+      <c r="G145" t="s">
+        <v>77</v>
+      </c>
+      <c r="H145" t="s">
+        <v>72</v>
+      </c>
+      <c r="I145">
+        <v>0</v>
+      </c>
+      <c r="J145">
+        <v>0</v>
+      </c>
+      <c r="K145">
+        <v>0</v>
+      </c>
+      <c r="L145">
+        <v>1</v>
+      </c>
+      <c r="M145">
+        <v>0</v>
+      </c>
+      <c r="N145">
+        <v>1</v>
+      </c>
+      <c r="O145" t="s">
+        <v>181</v>
+      </c>
+      <c r="P145" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q145">
+        <v>4.4</v>
+      </c>
+      <c r="R145">
+        <v>2</v>
+      </c>
+      <c r="S145">
+        <v>2.62</v>
+      </c>
+      <c r="T145">
+        <v>1.44</v>
+      </c>
+      <c r="U145">
+        <v>2.62</v>
+      </c>
+      <c r="V145">
+        <v>3.25</v>
+      </c>
+      <c r="W145">
+        <v>1.3</v>
+      </c>
+      <c r="X145">
+        <v>10</v>
+      </c>
+      <c r="Y145">
+        <v>1.05</v>
+      </c>
+      <c r="Z145">
+        <v>3.41</v>
+      </c>
+      <c r="AA145">
+        <v>3.32</v>
+      </c>
+      <c r="AB145">
+        <v>1.9</v>
+      </c>
+      <c r="AC145">
+        <v>1.04</v>
+      </c>
+      <c r="AD145">
+        <v>7.1</v>
+      </c>
+      <c r="AE145">
+        <v>1.41</v>
+      </c>
+      <c r="AF145">
+        <v>2.52</v>
+      </c>
+      <c r="AG145">
+        <v>2.2</v>
+      </c>
+      <c r="AH145">
+        <v>1.53</v>
+      </c>
+      <c r="AI145">
+        <v>2.05</v>
+      </c>
+      <c r="AJ145">
+        <v>1.73</v>
+      </c>
+      <c r="AK145">
+        <v>1.7</v>
+      </c>
+      <c r="AL145">
+        <v>1.33</v>
+      </c>
+      <c r="AM145">
+        <v>1.3</v>
+      </c>
+      <c r="AN145">
+        <v>1.2</v>
+      </c>
+      <c r="AO145">
+        <v>2</v>
+      </c>
+      <c r="AP145">
+        <v>1.36</v>
+      </c>
+      <c r="AQ145">
+        <v>1.8</v>
+      </c>
+      <c r="AR145">
+        <v>1.28</v>
+      </c>
+      <c r="AS145">
+        <v>1.24</v>
+      </c>
+      <c r="AT145">
+        <v>2.52</v>
+      </c>
+      <c r="AU145">
+        <v>2</v>
+      </c>
+      <c r="AV145">
+        <v>5</v>
+      </c>
+      <c r="AW145">
+        <v>6</v>
+      </c>
+      <c r="AX145">
+        <v>7</v>
+      </c>
+      <c r="AY145">
+        <v>8</v>
+      </c>
+      <c r="AZ145">
+        <v>12</v>
+      </c>
+      <c r="BA145">
+        <v>3</v>
+      </c>
+      <c r="BB145">
+        <v>6</v>
+      </c>
+      <c r="BC145">
+        <v>9</v>
+      </c>
+      <c r="BD145">
+        <v>2.38</v>
+      </c>
+      <c r="BE145">
+        <v>7.7</v>
+      </c>
+      <c r="BF145">
+        <v>1.76</v>
+      </c>
+      <c r="BG145">
+        <v>1.4</v>
+      </c>
+      <c r="BH145">
+        <v>2.56</v>
+      </c>
+      <c r="BI145">
+        <v>1.75</v>
+      </c>
+      <c r="BJ145">
+        <v>1.92</v>
+      </c>
+      <c r="BK145">
+        <v>2.24</v>
+      </c>
+      <c r="BL145">
+        <v>1.52</v>
+      </c>
+      <c r="BM145">
+        <v>3.05</v>
+      </c>
+      <c r="BN145">
+        <v>1.28</v>
+      </c>
+      <c r="BO145">
+        <v>4.56</v>
+      </c>
+      <c r="BP145">
+        <v>1.12</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="944" uniqueCount="258">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -562,6 +562,12 @@
     <t>['70']</t>
   </si>
   <si>
+    <t>['13', '45+2', '47', '67', '68']</t>
+  </si>
+  <si>
+    <t>['12', '68']</t>
+  </si>
+  <si>
     <t>['1', '6']</t>
   </si>
   <si>
@@ -779,6 +785,9 @@
   </si>
   <si>
     <t>['45+4', '90+1']</t>
+  </si>
+  <si>
+    <t>['3', '57', '60']</t>
   </si>
 </sst>
 </file>
@@ -1140,7 +1149,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP145"/>
+  <dimension ref="A1:BP147"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1474,10 +1483,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.82</v>
+        <v>2.4</v>
       </c>
       <c r="AQ2">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1602,7 +1611,7 @@
         <v>85</v>
       </c>
       <c r="P3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q3">
         <v>3.8</v>
@@ -1680,10 +1689,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.8</v>
+        <v>0.62</v>
       </c>
       <c r="AQ3">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1886,10 +1895,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.18</v>
+        <v>1.48</v>
       </c>
       <c r="AQ4">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2092,10 +2101,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>0.82</v>
+        <v>0.95</v>
       </c>
       <c r="AQ5">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2298,10 +2307,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AQ6">
-        <v>0.7</v>
+        <v>1.05</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2504,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.7</v>
+        <v>1.43</v>
       </c>
       <c r="AQ7">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2632,7 +2641,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q8">
         <v>2.39</v>
@@ -2710,10 +2719,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AQ8">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2916,10 +2925,10 @@
         <v>3</v>
       </c>
       <c r="AP9">
-        <v>2.82</v>
+        <v>2.4</v>
       </c>
       <c r="AQ9">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AR9">
         <v>2.58</v>
@@ -3044,7 +3053,7 @@
         <v>85</v>
       </c>
       <c r="P10" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q10">
         <v>4.3</v>
@@ -3122,10 +3131,10 @@
         <v>1</v>
       </c>
       <c r="AP10">
-        <v>0.82</v>
+        <v>0.95</v>
       </c>
       <c r="AQ10">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="AR10">
         <v>0.82</v>
@@ -3250,7 +3259,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q11">
         <v>2.8</v>
@@ -3328,10 +3337,10 @@
         <v>3</v>
       </c>
       <c r="AP11">
-        <v>1.7</v>
+        <v>1.43</v>
       </c>
       <c r="AQ11">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AR11">
         <v>1.04</v>
@@ -3534,19 +3543,19 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.36</v>
+        <v>1.05</v>
       </c>
       <c r="AQ12">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="AS12">
         <v>0.92</v>
       </c>
       <c r="AT12">
-        <v>0.92</v>
+        <v>1.72</v>
       </c>
       <c r="AU12">
         <v>6</v>
@@ -3662,7 +3671,7 @@
         <v>85</v>
       </c>
       <c r="P13" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q13">
         <v>2.43</v>
@@ -3740,10 +3749,10 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.18</v>
+        <v>1.48</v>
       </c>
       <c r="AQ13">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="AR13">
         <v>1.4</v>
@@ -3868,7 +3877,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q14">
         <v>3.9</v>
@@ -3943,22 +3952,22 @@
         <v>0</v>
       </c>
       <c r="AO14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP14">
-        <v>0.8</v>
+        <v>0.62</v>
       </c>
       <c r="AQ14">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AR14">
         <v>1.15</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AT14">
-        <v>1.15</v>
+        <v>2.76</v>
       </c>
       <c r="AU14">
         <v>3</v>
@@ -4152,10 +4161,10 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AQ15">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="AR15">
         <v>0.82</v>
@@ -4280,7 +4289,7 @@
         <v>85</v>
       </c>
       <c r="P16" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q16">
         <v>3.18</v>
@@ -4355,22 +4364,22 @@
         <v>3</v>
       </c>
       <c r="AO16">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AP16">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AQ16">
-        <v>1.8</v>
+        <v>1.48</v>
       </c>
       <c r="AR16">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AT16">
-        <v>1.61</v>
+        <v>3.06</v>
       </c>
       <c r="AU16">
         <v>2</v>
@@ -4486,7 +4495,7 @@
         <v>94</v>
       </c>
       <c r="P17" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q17">
         <v>3</v>
@@ -4558,25 +4567,25 @@
         <v>1.57</v>
       </c>
       <c r="AN17">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AO17">
         <v>1.5</v>
       </c>
       <c r="AP17">
-        <v>1.36</v>
+        <v>1.05</v>
       </c>
       <c r="AQ17">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="AR17">
-        <v>1.52</v>
+        <v>1.16</v>
       </c>
       <c r="AS17">
         <v>0.89</v>
       </c>
       <c r="AT17">
-        <v>2.41</v>
+        <v>2.05</v>
       </c>
       <c r="AU17">
         <v>4</v>
@@ -4770,10 +4779,10 @@
         <v>2</v>
       </c>
       <c r="AP18">
-        <v>0.82</v>
+        <v>0.95</v>
       </c>
       <c r="AQ18">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AR18">
         <v>1.29</v>
@@ -4898,7 +4907,7 @@
         <v>95</v>
       </c>
       <c r="P19" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q19">
         <v>2.71</v>
@@ -4970,25 +4979,25 @@
         <v>1.71</v>
       </c>
       <c r="AN19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO19">
         <v>0.5</v>
       </c>
       <c r="AP19">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AQ19">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AS19">
         <v>0.73</v>
       </c>
       <c r="AT19">
-        <v>0.73</v>
+        <v>2.16</v>
       </c>
       <c r="AU19">
         <v>9</v>
@@ -5104,7 +5113,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q20">
         <v>3.5</v>
@@ -5182,10 +5191,10 @@
         <v>1.5</v>
       </c>
       <c r="AP20">
-        <v>1.7</v>
+        <v>1.43</v>
       </c>
       <c r="AQ20">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AR20">
         <v>1.06</v>
@@ -5388,10 +5397,10 @@
         <v>0.5</v>
       </c>
       <c r="AP21">
-        <v>0.8</v>
+        <v>0.62</v>
       </c>
       <c r="AQ21">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AR21">
         <v>1.02</v>
@@ -5516,7 +5525,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q22">
         <v>5</v>
@@ -5591,22 +5600,22 @@
         <v>2</v>
       </c>
       <c r="AO22">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP22">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AQ22">
-        <v>1.89</v>
+        <v>2.4</v>
       </c>
       <c r="AR22">
         <v>0.92</v>
       </c>
       <c r="AS22">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AT22">
-        <v>0.92</v>
+        <v>2.85</v>
       </c>
       <c r="AU22">
         <v>5</v>
@@ -5794,25 +5803,25 @@
         <v>1.7</v>
       </c>
       <c r="AN23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO23">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AP23">
-        <v>2.82</v>
+        <v>2.4</v>
       </c>
       <c r="AQ23">
-        <v>1.18</v>
+        <v>1.43</v>
       </c>
       <c r="AR23">
-        <v>1.93</v>
+        <v>1.7</v>
       </c>
       <c r="AS23">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AT23">
-        <v>1.93</v>
+        <v>2.75</v>
       </c>
       <c r="AU23">
         <v>2</v>
@@ -6000,25 +6009,25 @@
         <v>1.61</v>
       </c>
       <c r="AN24">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AO24">
         <v>1.33</v>
       </c>
       <c r="AP24">
-        <v>1.36</v>
+        <v>1.05</v>
       </c>
       <c r="AQ24">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="AR24">
-        <v>1.41</v>
+        <v>1.21</v>
       </c>
       <c r="AS24">
         <v>0.87</v>
       </c>
       <c r="AT24">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="AU24">
         <v>9</v>
@@ -6206,25 +6215,25 @@
         <v>1.8</v>
       </c>
       <c r="AN25">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AO25">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AP25">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AQ25">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AR25">
-        <v>2.07</v>
+        <v>1.64</v>
       </c>
       <c r="AS25">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AT25">
-        <v>2.07</v>
+        <v>2.66</v>
       </c>
       <c r="AU25">
         <v>3</v>
@@ -6412,25 +6421,25 @@
         <v>1.75</v>
       </c>
       <c r="AN26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO26">
         <v>0.33</v>
       </c>
       <c r="AP26">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AQ26">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AR26">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AS26">
         <v>1.45</v>
       </c>
       <c r="AT26">
-        <v>1.45</v>
+        <v>3.14</v>
       </c>
       <c r="AU26">
         <v>2</v>
@@ -6546,7 +6555,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q27">
         <v>2.25</v>
@@ -6618,25 +6627,25 @@
         <v>2.2</v>
       </c>
       <c r="AN27">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AO27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP27">
-        <v>1.18</v>
+        <v>1.48</v>
       </c>
       <c r="AQ27">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="AR27">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="AS27">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="AT27">
-        <v>1.42</v>
+        <v>2.25</v>
       </c>
       <c r="AU27">
         <v>8</v>
@@ -6752,7 +6761,7 @@
         <v>101</v>
       </c>
       <c r="P28" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q28">
         <v>4</v>
@@ -6824,25 +6833,25 @@
         <v>1.3</v>
       </c>
       <c r="AN28">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AO28">
         <v>2.33</v>
       </c>
       <c r="AP28">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ28">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AR28">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AS28">
         <v>1.3</v>
       </c>
       <c r="AT28">
-        <v>1.3</v>
+        <v>2.35</v>
       </c>
       <c r="AU28">
         <v>3</v>
@@ -6958,7 +6967,7 @@
         <v>102</v>
       </c>
       <c r="P29" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q29">
         <v>2.2</v>
@@ -7030,25 +7039,25 @@
         <v>2.15</v>
       </c>
       <c r="AN29">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AO29">
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AQ29">
-        <v>1.1</v>
+        <v>0.95</v>
       </c>
       <c r="AR29">
+        <v>1.37</v>
+      </c>
+      <c r="AS29">
         <v>1.22</v>
       </c>
-      <c r="AS29">
-        <v>0</v>
-      </c>
       <c r="AT29">
-        <v>1.22</v>
+        <v>2.59</v>
       </c>
       <c r="AU29">
         <v>5</v>
@@ -7164,7 +7173,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q30">
         <v>3.75</v>
@@ -7239,22 +7248,22 @@
         <v>0</v>
       </c>
       <c r="AO30">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AP30">
-        <v>0.82</v>
+        <v>0.95</v>
       </c>
       <c r="AQ30">
-        <v>0.7</v>
+        <v>1.05</v>
       </c>
       <c r="AR30">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AS30">
-        <v>0.8</v>
+        <v>1.41</v>
       </c>
       <c r="AT30">
-        <v>2.02</v>
+        <v>2.54</v>
       </c>
       <c r="AU30">
         <v>7</v>
@@ -7370,7 +7379,7 @@
         <v>104</v>
       </c>
       <c r="P31" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q31">
         <v>3.25</v>
@@ -7448,19 +7457,19 @@
         <v>2</v>
       </c>
       <c r="AP31">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AQ31">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AR31">
-        <v>1.17</v>
+        <v>1.56</v>
       </c>
       <c r="AS31">
         <v>1.26</v>
       </c>
       <c r="AT31">
-        <v>2.43</v>
+        <v>2.82</v>
       </c>
       <c r="AU31">
         <v>8</v>
@@ -7648,25 +7657,25 @@
         <v>1.53</v>
       </c>
       <c r="AN32">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AO32">
         <v>1</v>
       </c>
       <c r="AP32">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ32">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="AR32">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AS32">
         <v>1.11</v>
       </c>
       <c r="AT32">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AU32">
         <v>9</v>
@@ -7782,7 +7791,7 @@
         <v>91</v>
       </c>
       <c r="P33" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q33">
         <v>2.63</v>
@@ -7854,25 +7863,25 @@
         <v>1.61</v>
       </c>
       <c r="AN33">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="AO33">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="AP33">
-        <v>2.82</v>
+        <v>2.4</v>
       </c>
       <c r="AQ33">
-        <v>1.8</v>
+        <v>1.48</v>
       </c>
       <c r="AR33">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AS33">
-        <v>0.97</v>
+        <v>1.44</v>
       </c>
       <c r="AT33">
-        <v>2.66</v>
+        <v>3.01</v>
       </c>
       <c r="AU33">
         <v>2</v>
@@ -7988,7 +7997,7 @@
         <v>85</v>
       </c>
       <c r="P34" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q34">
         <v>3.8</v>
@@ -8060,25 +8069,25 @@
         <v>1.29</v>
       </c>
       <c r="AN34">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AO34">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="AP34">
-        <v>0.8</v>
+        <v>0.62</v>
       </c>
       <c r="AQ34">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="AR34">
-        <v>0.98</v>
+        <v>0.87</v>
       </c>
       <c r="AS34">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AT34">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
       <c r="AU34">
         <v>3</v>
@@ -8194,7 +8203,7 @@
         <v>106</v>
       </c>
       <c r="P35" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q35">
         <v>2.8</v>
@@ -8266,25 +8275,25 @@
         <v>1.57</v>
       </c>
       <c r="AN35">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="AO35">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="AP35">
-        <v>1.7</v>
+        <v>1.43</v>
       </c>
       <c r="AQ35">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AR35">
-        <v>1.05</v>
+        <v>0.9</v>
       </c>
       <c r="AS35">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="AT35">
-        <v>2.72</v>
+        <v>2.32</v>
       </c>
       <c r="AU35">
         <v>5</v>
@@ -8472,25 +8481,25 @@
         <v>1.88</v>
       </c>
       <c r="AN36">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AO36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP36">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AQ36">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AR36">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AS36">
-        <v>0.85</v>
+        <v>0.98</v>
       </c>
       <c r="AT36">
-        <v>0.85</v>
+        <v>2.32</v>
       </c>
       <c r="AU36">
         <v>8</v>
@@ -8678,25 +8687,25 @@
         <v>0</v>
       </c>
       <c r="AN37">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AO37">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AP37">
-        <v>1.7</v>
+        <v>1.43</v>
       </c>
       <c r="AQ37">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="AR37">
-        <v>1.11</v>
+        <v>0.98</v>
       </c>
       <c r="AS37">
-        <v>0.52</v>
+        <v>0.91</v>
       </c>
       <c r="AT37">
-        <v>1.63</v>
+        <v>1.89</v>
       </c>
       <c r="AU37">
         <v>7</v>
@@ -8812,7 +8821,7 @@
         <v>85</v>
       </c>
       <c r="P38" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q38">
         <v>5</v>
@@ -8884,25 +8893,25 @@
         <v>0</v>
       </c>
       <c r="AN38">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="AO38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AP38">
-        <v>1.36</v>
+        <v>1.05</v>
       </c>
       <c r="AQ38">
-        <v>1.89</v>
+        <v>2.4</v>
       </c>
       <c r="AR38">
-        <v>1.61</v>
+        <v>1.37</v>
       </c>
       <c r="AS38">
-        <v>1.24</v>
+        <v>1.55</v>
       </c>
       <c r="AT38">
-        <v>2.85</v>
+        <v>2.92</v>
       </c>
       <c r="AU38">
         <v>4</v>
@@ -9018,7 +9027,7 @@
         <v>85</v>
       </c>
       <c r="P39" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q39">
         <v>3.1</v>
@@ -9090,25 +9099,25 @@
         <v>1.55</v>
       </c>
       <c r="AN39">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="AO39">
         <v>1.6</v>
       </c>
       <c r="AP39">
-        <v>1.18</v>
+        <v>1.48</v>
       </c>
       <c r="AQ39">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AR39">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="AS39">
         <v>1.35</v>
       </c>
       <c r="AT39">
-        <v>2.95</v>
+        <v>2.73</v>
       </c>
       <c r="AU39">
         <v>5</v>
@@ -9296,25 +9305,25 @@
         <v>2.2</v>
       </c>
       <c r="AN40">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AO40">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="AP40">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AQ40">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="AR40">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AS40">
-        <v>1.05</v>
+        <v>1.32</v>
       </c>
       <c r="AT40">
-        <v>2.67</v>
+        <v>2.98</v>
       </c>
       <c r="AU40">
         <v>8</v>
@@ -9430,7 +9439,7 @@
         <v>110</v>
       </c>
       <c r="P41" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q41">
         <v>3.25</v>
@@ -9502,25 +9511,25 @@
         <v>1.44</v>
       </c>
       <c r="AN41">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="AO41">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AP41">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AQ41">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AR41">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="AS41">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AT41">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="AU41">
         <v>5</v>
@@ -9708,25 +9717,25 @@
         <v>1.85</v>
       </c>
       <c r="AN42">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="AO42">
         <v>0.8</v>
       </c>
       <c r="AP42">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AQ42">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="AR42">
-        <v>1.85</v>
+        <v>1.44</v>
       </c>
       <c r="AS42">
         <v>1.12</v>
       </c>
       <c r="AT42">
-        <v>2.97</v>
+        <v>2.56</v>
       </c>
       <c r="AU42">
         <v>7</v>
@@ -9914,25 +9923,25 @@
         <v>1.67</v>
       </c>
       <c r="AN43">
-        <v>2.33</v>
+        <v>1.8</v>
       </c>
       <c r="AO43">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AP43">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AQ43">
-        <v>1.1</v>
+        <v>0.95</v>
       </c>
       <c r="AR43">
-        <v>1.02</v>
+        <v>0.96</v>
       </c>
       <c r="AS43">
-        <v>0.83</v>
+        <v>1.22</v>
       </c>
       <c r="AT43">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="AU43">
         <v>4</v>
@@ -10048,7 +10057,7 @@
         <v>113</v>
       </c>
       <c r="P44" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q44">
         <v>3.4</v>
@@ -10120,25 +10129,25 @@
         <v>1.44</v>
       </c>
       <c r="AN44">
-        <v>0.33</v>
+        <v>1.33</v>
       </c>
       <c r="AO44">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AP44">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AQ44">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AR44">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AS44">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="AT44">
-        <v>2.77</v>
+        <v>2.94</v>
       </c>
       <c r="AU44">
         <v>6</v>
@@ -10254,7 +10263,7 @@
         <v>113</v>
       </c>
       <c r="P45" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q45">
         <v>3.75</v>
@@ -10326,25 +10335,25 @@
         <v>1.36</v>
       </c>
       <c r="AN45">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AO45">
         <v>1.83</v>
       </c>
       <c r="AP45">
-        <v>1.36</v>
+        <v>1.05</v>
       </c>
       <c r="AQ45">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AR45">
-        <v>1.49</v>
+        <v>1.34</v>
       </c>
       <c r="AS45">
         <v>1.33</v>
       </c>
       <c r="AT45">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="AU45">
         <v>5</v>
@@ -10460,7 +10469,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q46">
         <v>3.75</v>
@@ -10535,22 +10544,22 @@
         <v>2</v>
       </c>
       <c r="AO46">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AP46">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AQ46">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AR46">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AS46">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AT46">
-        <v>3.02</v>
+        <v>3.14</v>
       </c>
       <c r="AU46">
         <v>6</v>
@@ -10666,7 +10675,7 @@
         <v>85</v>
       </c>
       <c r="P47" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q47">
         <v>3</v>
@@ -10738,25 +10747,25 @@
         <v>1.65</v>
       </c>
       <c r="AN47">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AO47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP47">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ47">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AR47">
-        <v>1.74</v>
+        <v>1.33</v>
       </c>
       <c r="AS47">
-        <v>0.86</v>
+        <v>1.02</v>
       </c>
       <c r="AT47">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="AU47">
         <v>4</v>
@@ -10944,25 +10953,25 @@
         <v>2.38</v>
       </c>
       <c r="AN48">
-        <v>2.5</v>
+        <v>2.17</v>
       </c>
       <c r="AO48">
         <v>0.67</v>
       </c>
       <c r="AP48">
-        <v>2.82</v>
+        <v>2.4</v>
       </c>
       <c r="AQ48">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="AR48">
-        <v>1.63</v>
+        <v>1.54</v>
       </c>
       <c r="AS48">
         <v>1.19</v>
       </c>
       <c r="AT48">
-        <v>2.82</v>
+        <v>2.73</v>
       </c>
       <c r="AU48">
         <v>6</v>
@@ -11078,7 +11087,7 @@
         <v>116</v>
       </c>
       <c r="P49" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -11150,25 +11159,25 @@
         <v>1.55</v>
       </c>
       <c r="AN49">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AO49">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AP49">
-        <v>1.18</v>
+        <v>1.48</v>
       </c>
       <c r="AQ49">
-        <v>1.18</v>
+        <v>1.43</v>
       </c>
       <c r="AR49">
-        <v>1.58</v>
+        <v>1.4</v>
       </c>
       <c r="AS49">
-        <v>0.43</v>
+        <v>1.07</v>
       </c>
       <c r="AT49">
-        <v>2.01</v>
+        <v>2.47</v>
       </c>
       <c r="AU49">
         <v>9</v>
@@ -11356,25 +11365,25 @@
         <v>1.67</v>
       </c>
       <c r="AN50">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="AO50">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AP50">
-        <v>0.8</v>
+        <v>0.62</v>
       </c>
       <c r="AQ50">
-        <v>1.1</v>
+        <v>0.95</v>
       </c>
       <c r="AR50">
-        <v>1.01</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AS50">
-        <v>0.96</v>
+        <v>1.2</v>
       </c>
       <c r="AT50">
-        <v>1.97</v>
+        <v>2.14</v>
       </c>
       <c r="AU50">
         <v>3</v>
@@ -11490,7 +11499,7 @@
         <v>85</v>
       </c>
       <c r="P51" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q51">
         <v>2.25</v>
@@ -11562,25 +11571,25 @@
         <v>2.2</v>
       </c>
       <c r="AN51">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="AO51">
         <v>0.57</v>
       </c>
       <c r="AP51">
-        <v>1.7</v>
+        <v>1.43</v>
       </c>
       <c r="AQ51">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="AR51">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AS51">
         <v>1.24</v>
       </c>
       <c r="AT51">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="AU51">
         <v>4</v>
@@ -11768,25 +11777,25 @@
         <v>2.7</v>
       </c>
       <c r="AN52">
-        <v>2.6</v>
+        <v>2.29</v>
       </c>
       <c r="AO52">
-        <v>0</v>
+        <v>0.43</v>
       </c>
       <c r="AP52">
-        <v>2.82</v>
+        <v>2.4</v>
       </c>
       <c r="AQ52">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="AR52">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AS52">
-        <v>0.8</v>
+        <v>1.01</v>
       </c>
       <c r="AT52">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="AU52">
         <v>6</v>
@@ -11974,25 +11983,25 @@
         <v>2.3</v>
       </c>
       <c r="AN53">
-        <v>2.33</v>
+        <v>1.57</v>
       </c>
       <c r="AO53">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="AP53">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AQ53">
-        <v>0.7</v>
+        <v>1.05</v>
       </c>
       <c r="AR53">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AS53">
-        <v>1.02</v>
+        <v>1.32</v>
       </c>
       <c r="AT53">
-        <v>2.77</v>
+        <v>3.02</v>
       </c>
       <c r="AU53">
         <v>7</v>
@@ -12180,25 +12189,25 @@
         <v>1.3</v>
       </c>
       <c r="AN54">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="AO54">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AP54">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AQ54">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AR54">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="AS54">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AT54">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="AU54">
         <v>2</v>
@@ -12314,7 +12323,7 @@
         <v>119</v>
       </c>
       <c r="P55" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q55">
         <v>5</v>
@@ -12386,25 +12395,25 @@
         <v>1.22</v>
       </c>
       <c r="AN55">
-        <v>0.25</v>
+        <v>0.57</v>
       </c>
       <c r="AO55">
-        <v>2</v>
+        <v>1.29</v>
       </c>
       <c r="AP55">
-        <v>0.82</v>
+        <v>0.95</v>
       </c>
       <c r="AQ55">
-        <v>1.8</v>
+        <v>1.48</v>
       </c>
       <c r="AR55">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="AS55">
-        <v>1.04</v>
+        <v>1.46</v>
       </c>
       <c r="AT55">
-        <v>2.36</v>
+        <v>2.64</v>
       </c>
       <c r="AU55">
         <v>5</v>
@@ -12592,25 +12601,25 @@
         <v>1.53</v>
       </c>
       <c r="AN56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO56">
         <v>2</v>
       </c>
       <c r="AP56">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AQ56">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AR56">
-        <v>1.83</v>
+        <v>1.46</v>
       </c>
       <c r="AS56">
         <v>1.29</v>
       </c>
       <c r="AT56">
-        <v>3.12</v>
+        <v>2.75</v>
       </c>
       <c r="AU56">
         <v>7</v>
@@ -12726,7 +12735,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q57">
         <v>3.75</v>
@@ -12798,25 +12807,25 @@
         <v>1.36</v>
       </c>
       <c r="AN57">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AO57">
-        <v>2.33</v>
+        <v>1.29</v>
       </c>
       <c r="AP57">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ57">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="AR57">
-        <v>1.79</v>
+        <v>1.41</v>
       </c>
       <c r="AS57">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AT57">
-        <v>3.24</v>
+        <v>2.91</v>
       </c>
       <c r="AU57">
         <v>9</v>
@@ -12932,7 +12941,7 @@
         <v>121</v>
       </c>
       <c r="P58" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q58">
         <v>2.3</v>
@@ -13004,25 +13013,25 @@
         <v>2.1</v>
       </c>
       <c r="AN58">
-        <v>2.17</v>
+        <v>1.75</v>
       </c>
       <c r="AO58">
-        <v>1</v>
+        <v>1.38</v>
       </c>
       <c r="AP58">
-        <v>1.7</v>
+        <v>1.43</v>
       </c>
       <c r="AQ58">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="AR58">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AS58">
-        <v>1.13</v>
+        <v>1.45</v>
       </c>
       <c r="AT58">
-        <v>2.44</v>
+        <v>2.73</v>
       </c>
       <c r="AU58">
         <v>4</v>
@@ -13138,7 +13147,7 @@
         <v>85</v>
       </c>
       <c r="P59" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q59">
         <v>3.2</v>
@@ -13210,25 +13219,25 @@
         <v>1.53</v>
       </c>
       <c r="AN59">
-        <v>0.6</v>
+        <v>0.38</v>
       </c>
       <c r="AO59">
         <v>0.88</v>
       </c>
       <c r="AP59">
-        <v>0.8</v>
+        <v>0.62</v>
       </c>
       <c r="AQ59">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="AR59">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AS59">
         <v>1.26</v>
       </c>
       <c r="AT59">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="AU59">
         <v>2</v>
@@ -13416,25 +13425,25 @@
         <v>2.15</v>
       </c>
       <c r="AN60">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="AO60">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AP60">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AQ60">
-        <v>1.1</v>
+        <v>0.95</v>
       </c>
       <c r="AR60">
-        <v>2.02</v>
+        <v>1.58</v>
       </c>
       <c r="AS60">
-        <v>0.99</v>
+        <v>1.24</v>
       </c>
       <c r="AT60">
-        <v>3.01</v>
+        <v>2.82</v>
       </c>
       <c r="AU60">
         <v>7</v>
@@ -13550,7 +13559,7 @@
         <v>123</v>
       </c>
       <c r="P61" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q61">
         <v>4</v>
@@ -13625,22 +13634,22 @@
         <v>1.75</v>
       </c>
       <c r="AO61">
-        <v>1.5</v>
+        <v>2.38</v>
       </c>
       <c r="AP61">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AQ61">
-        <v>1.89</v>
+        <v>2.4</v>
       </c>
       <c r="AR61">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="AS61">
-        <v>1.35</v>
+        <v>1.54</v>
       </c>
       <c r="AT61">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="AU61">
         <v>6</v>
@@ -13756,7 +13765,7 @@
         <v>124</v>
       </c>
       <c r="P62" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q62">
         <v>2.3</v>
@@ -13828,25 +13837,25 @@
         <v>2.2</v>
       </c>
       <c r="AN62">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="AO62">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AP62">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AQ62">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AR62">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="AS62">
-        <v>0.92</v>
+        <v>1.01</v>
       </c>
       <c r="AT62">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="AU62">
         <v>7</v>
@@ -13962,7 +13971,7 @@
         <v>85</v>
       </c>
       <c r="P63" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q63">
         <v>3.2</v>
@@ -14034,25 +14043,25 @@
         <v>1.5</v>
       </c>
       <c r="AN63">
-        <v>0.5</v>
+        <v>1.13</v>
       </c>
       <c r="AO63">
         <v>1.88</v>
       </c>
       <c r="AP63">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AQ63">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AR63">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AS63">
         <v>1.28</v>
       </c>
       <c r="AT63">
-        <v>2.82</v>
+        <v>2.71</v>
       </c>
       <c r="AU63">
         <v>8</v>
@@ -14168,7 +14177,7 @@
         <v>125</v>
       </c>
       <c r="P64" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q64">
         <v>2.5</v>
@@ -14240,22 +14249,22 @@
         <v>1.95</v>
       </c>
       <c r="AN64">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AO64">
-        <v>0.33</v>
+        <v>0.75</v>
       </c>
       <c r="AP64">
-        <v>1.18</v>
+        <v>1.48</v>
       </c>
       <c r="AQ64">
-        <v>0.7</v>
+        <v>1.05</v>
       </c>
       <c r="AR64">
-        <v>1.63</v>
+        <v>1.41</v>
       </c>
       <c r="AS64">
-        <v>1.09</v>
+        <v>1.31</v>
       </c>
       <c r="AT64">
         <v>2.72</v>
@@ -14374,7 +14383,7 @@
         <v>126</v>
       </c>
       <c r="P65" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q65">
         <v>4</v>
@@ -14446,25 +14455,25 @@
         <v>0</v>
       </c>
       <c r="AN65">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="AO65">
-        <v>0.5</v>
+        <v>1.89</v>
       </c>
       <c r="AP65">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AQ65">
-        <v>1.18</v>
+        <v>1.43</v>
       </c>
       <c r="AR65">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AS65">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AT65">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="AU65">
         <v>3</v>
@@ -14580,7 +14589,7 @@
         <v>127</v>
       </c>
       <c r="P66" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q66">
         <v>3</v>
@@ -14652,25 +14661,25 @@
         <v>0</v>
       </c>
       <c r="AN66">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="AO66">
         <v>2</v>
       </c>
       <c r="AP66">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AQ66">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AR66">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AS66">
         <v>1.25</v>
       </c>
       <c r="AT66">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="AU66">
         <v>4</v>
@@ -14858,25 +14867,25 @@
         <v>0</v>
       </c>
       <c r="AN67">
-        <v>0.2</v>
+        <v>0.44</v>
       </c>
       <c r="AO67">
-        <v>0.8</v>
+        <v>1.22</v>
       </c>
       <c r="AP67">
-        <v>0.82</v>
+        <v>0.95</v>
       </c>
       <c r="AQ67">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="AR67">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AS67">
-        <v>1.16</v>
+        <v>1.43</v>
       </c>
       <c r="AT67">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="AU67">
         <v>3</v>
@@ -14992,7 +15001,7 @@
         <v>129</v>
       </c>
       <c r="P68" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q68">
         <v>5</v>
@@ -15064,25 +15073,25 @@
         <v>0</v>
       </c>
       <c r="AN68">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AO68">
-        <v>1</v>
+        <v>1.89</v>
       </c>
       <c r="AP68">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="AQ68">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AR68">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AS68">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AT68">
-        <v>1.66</v>
+        <v>2.98</v>
       </c>
       <c r="AU68">
         <v>6</v>
@@ -15270,25 +15279,25 @@
         <v>0</v>
       </c>
       <c r="AN69">
-        <v>2.67</v>
+        <v>2.44</v>
       </c>
       <c r="AO69">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="AP69">
-        <v>2.82</v>
+        <v>2.4</v>
       </c>
       <c r="AQ69">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="AR69">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="AS69">
-        <v>1.31</v>
+        <v>1.51</v>
       </c>
       <c r="AT69">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="AU69">
         <v>6</v>
@@ -15476,25 +15485,25 @@
         <v>0</v>
       </c>
       <c r="AN70">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="AO70">
-        <v>0.6</v>
+        <v>1.22</v>
       </c>
       <c r="AP70">
-        <v>1.18</v>
+        <v>1.48</v>
       </c>
       <c r="AQ70">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AR70">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="AS70">
-        <v>1.32</v>
+        <v>1.61</v>
       </c>
       <c r="AT70">
-        <v>3.04</v>
+        <v>3.11</v>
       </c>
       <c r="AU70">
         <v>6</v>
@@ -15610,7 +15619,7 @@
         <v>132</v>
       </c>
       <c r="P71" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q71">
         <v>2.63</v>
@@ -15682,25 +15691,25 @@
         <v>0</v>
       </c>
       <c r="AN71">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AO71">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AP71">
+        <v>1.05</v>
+      </c>
+      <c r="AQ71">
+        <v>0.62</v>
+      </c>
+      <c r="AR71">
         <v>1.36</v>
       </c>
-      <c r="AQ71">
-        <v>0.5</v>
-      </c>
-      <c r="AR71">
-        <v>1.45</v>
-      </c>
       <c r="AS71">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="AT71">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="AU71">
         <v>5</v>
@@ -15888,25 +15897,25 @@
         <v>0</v>
       </c>
       <c r="AN72">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="AO72">
-        <v>0.25</v>
+        <v>0.9</v>
       </c>
       <c r="AP72">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AQ72">
-        <v>0.7</v>
+        <v>1.05</v>
       </c>
       <c r="AR72">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AS72">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AT72">
-        <v>2.92</v>
+        <v>2.79</v>
       </c>
       <c r="AU72">
         <v>2</v>
@@ -16022,7 +16031,7 @@
         <v>85</v>
       </c>
       <c r="P73" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q73">
         <v>3.6</v>
@@ -16094,25 +16103,25 @@
         <v>0</v>
       </c>
       <c r="AN73">
-        <v>1.75</v>
+        <v>1.1</v>
       </c>
       <c r="AO73">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AP73">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ73">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AR73">
-        <v>1.77</v>
+        <v>1.4</v>
       </c>
       <c r="AS73">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="AT73">
-        <v>3.29</v>
+        <v>2.86</v>
       </c>
       <c r="AU73">
         <v>5</v>
@@ -16228,7 +16237,7 @@
         <v>85</v>
       </c>
       <c r="P74" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q74">
         <v>4.33</v>
@@ -16300,25 +16309,25 @@
         <v>0</v>
       </c>
       <c r="AN74">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="AO74">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AP74">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AQ74">
-        <v>1.89</v>
+        <v>2.4</v>
       </c>
       <c r="AR74">
-        <v>1.98</v>
+        <v>1.57</v>
       </c>
       <c r="AS74">
-        <v>1.27</v>
+        <v>1.53</v>
       </c>
       <c r="AT74">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AU74">
         <v>3</v>
@@ -16434,7 +16443,7 @@
         <v>134</v>
       </c>
       <c r="P75" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q75">
         <v>1.91</v>
@@ -16506,25 +16515,25 @@
         <v>0</v>
       </c>
       <c r="AN75">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AO75">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="AP75">
-        <v>1.7</v>
+        <v>1.43</v>
       </c>
       <c r="AQ75">
-        <v>1.1</v>
+        <v>0.95</v>
       </c>
       <c r="AR75">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AS75">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AT75">
-        <v>2.44</v>
+        <v>2.59</v>
       </c>
       <c r="AU75">
         <v>5</v>
@@ -16640,7 +16649,7 @@
         <v>135</v>
       </c>
       <c r="P76" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q76">
         <v>2.63</v>
@@ -16712,25 +16721,25 @@
         <v>0</v>
       </c>
       <c r="AN76">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AO76">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AP76">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
       <c r="AQ76">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AR76">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AS76">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AT76">
-        <v>1.02</v>
+        <v>2.32</v>
       </c>
       <c r="AU76">
         <v>4</v>
@@ -16846,7 +16855,7 @@
         <v>85</v>
       </c>
       <c r="P77" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q77">
         <v>4.5</v>
@@ -16918,25 +16927,25 @@
         <v>0</v>
       </c>
       <c r="AN77">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AO77">
-        <v>2.33</v>
+        <v>1.8</v>
       </c>
       <c r="AP77">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="AQ77">
-        <v>1.8</v>
+        <v>1.48</v>
       </c>
       <c r="AR77">
-        <v>1.89</v>
+        <v>1.32</v>
       </c>
       <c r="AS77">
-        <v>1.05</v>
+        <v>1.47</v>
       </c>
       <c r="AT77">
-        <v>2.94</v>
+        <v>2.79</v>
       </c>
       <c r="AU77">
         <v>5</v>
@@ -17124,25 +17133,25 @@
         <v>0</v>
       </c>
       <c r="AN78">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="AO78">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="AP78">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AQ78">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="AR78">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="AS78">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AT78">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="AU78">
         <v>8</v>
@@ -17258,7 +17267,7 @@
         <v>137</v>
       </c>
       <c r="P79" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q79">
         <v>3.6</v>
@@ -17330,25 +17339,25 @@
         <v>1.38</v>
       </c>
       <c r="AN79">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AO79">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AP79">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ79">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AR79">
-        <v>1.7</v>
+        <v>1.41</v>
       </c>
       <c r="AS79">
-        <v>1.29</v>
+        <v>1.53</v>
       </c>
       <c r="AT79">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="AU79">
         <v>5</v>
@@ -17536,25 +17545,25 @@
         <v>1.83</v>
       </c>
       <c r="AN80">
-        <v>1.33</v>
+        <v>1.64</v>
       </c>
       <c r="AO80">
-        <v>0.2</v>
+        <v>0.82</v>
       </c>
       <c r="AP80">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AQ80">
-        <v>0.7</v>
+        <v>1.05</v>
       </c>
       <c r="AR80">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AS80">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AT80">
-        <v>2.58</v>
+        <v>2.76</v>
       </c>
       <c r="AU80">
         <v>3</v>
@@ -17742,25 +17751,25 @@
         <v>1.4</v>
       </c>
       <c r="AN81">
-        <v>0.5</v>
+        <v>0.27</v>
       </c>
       <c r="AO81">
-        <v>1</v>
+        <v>1.45</v>
       </c>
       <c r="AP81">
-        <v>0.8</v>
+        <v>0.62</v>
       </c>
       <c r="AQ81">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AR81">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AS81">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AT81">
-        <v>2.31</v>
+        <v>2.24</v>
       </c>
       <c r="AU81">
         <v>4</v>
@@ -17876,7 +17885,7 @@
         <v>140</v>
       </c>
       <c r="P82" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q82">
         <v>3.75</v>
@@ -17948,25 +17957,25 @@
         <v>1.36</v>
       </c>
       <c r="AN82">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AO82">
-        <v>1</v>
+        <v>1.91</v>
       </c>
       <c r="AP82">
-        <v>1.18</v>
+        <v>1.48</v>
       </c>
       <c r="AQ82">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AR82">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="AS82">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="AT82">
-        <v>3.33</v>
+        <v>3.25</v>
       </c>
       <c r="AU82">
         <v>9</v>
@@ -18082,7 +18091,7 @@
         <v>85</v>
       </c>
       <c r="P83" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q83">
         <v>7.5</v>
@@ -18154,25 +18163,25 @@
         <v>1.1</v>
       </c>
       <c r="AN83">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="AO83">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="AP83">
-        <v>0.82</v>
+        <v>0.95</v>
       </c>
       <c r="AQ83">
-        <v>1.89</v>
+        <v>2.4</v>
       </c>
       <c r="AR83">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AS83">
-        <v>1.23</v>
+        <v>1.49</v>
       </c>
       <c r="AT83">
-        <v>2.58</v>
+        <v>2.74</v>
       </c>
       <c r="AU83">
         <v>0</v>
@@ -18360,25 +18369,25 @@
         <v>2</v>
       </c>
       <c r="AN84">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO84">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AP84">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
       <c r="AQ84">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="AR84">
-        <v>1.02</v>
+        <v>1.26</v>
       </c>
       <c r="AS84">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AT84">
-        <v>2.27</v>
+        <v>2.59</v>
       </c>
       <c r="AU84">
         <v>8</v>
@@ -18494,7 +18503,7 @@
         <v>142</v>
       </c>
       <c r="P85" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q85">
         <v>3.75</v>
@@ -18566,25 +18575,25 @@
         <v>1.36</v>
       </c>
       <c r="AN85">
-        <v>0.83</v>
+        <v>1.09</v>
       </c>
       <c r="AO85">
-        <v>1.33</v>
+        <v>1.91</v>
       </c>
       <c r="AP85">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AQ85">
-        <v>1.18</v>
+        <v>1.43</v>
       </c>
       <c r="AR85">
-        <v>1.63</v>
+        <v>1.45</v>
       </c>
       <c r="AS85">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AT85">
-        <v>2.99</v>
+        <v>2.8</v>
       </c>
       <c r="AU85">
         <v>4</v>
@@ -18700,7 +18709,7 @@
         <v>85</v>
       </c>
       <c r="P86" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q86">
         <v>4.2</v>
@@ -18772,25 +18781,25 @@
         <v>1.25</v>
       </c>
       <c r="AN86">
-        <v>1.33</v>
+        <v>0.75</v>
       </c>
       <c r="AO86">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AP86">
-        <v>1.36</v>
+        <v>1.05</v>
       </c>
       <c r="AQ86">
-        <v>1.18</v>
+        <v>1.43</v>
       </c>
       <c r="AR86">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="AS86">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AT86">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="AU86">
         <v>7</v>
@@ -18978,25 +18987,25 @@
         <v>1.75</v>
       </c>
       <c r="AN87">
-        <v>0.5</v>
+        <v>0.92</v>
       </c>
       <c r="AO87">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AP87">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="AQ87">
-        <v>1.1</v>
+        <v>0.95</v>
       </c>
       <c r="AR87">
-        <v>1.66</v>
+        <v>1.32</v>
       </c>
       <c r="AS87">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AT87">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="AU87">
         <v>2</v>
@@ -19184,25 +19193,25 @@
         <v>1.3</v>
       </c>
       <c r="AN88">
-        <v>1.83</v>
+        <v>1.42</v>
       </c>
       <c r="AO88">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="AP88">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AQ88">
-        <v>1.8</v>
+        <v>1.48</v>
       </c>
       <c r="AR88">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AS88">
-        <v>1.16</v>
+        <v>1.49</v>
       </c>
       <c r="AT88">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="AU88">
         <v>2</v>
@@ -19318,7 +19327,7 @@
         <v>143</v>
       </c>
       <c r="P89" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q89">
         <v>2.62</v>
@@ -19390,25 +19399,25 @@
         <v>1.73</v>
       </c>
       <c r="AN89">
+        <v>0.92</v>
+      </c>
+      <c r="AO89">
+        <v>0.33</v>
+      </c>
+      <c r="AP89">
+        <v>0.9</v>
+      </c>
+      <c r="AQ89">
+        <v>0.62</v>
+      </c>
+      <c r="AR89">
+        <v>1.48</v>
+      </c>
+      <c r="AS89">
         <v>1.17</v>
       </c>
-      <c r="AO89">
-        <v>0</v>
-      </c>
-      <c r="AP89">
-        <v>1.1</v>
-      </c>
-      <c r="AQ89">
-        <v>0.5</v>
-      </c>
-      <c r="AR89">
-        <v>1.79</v>
-      </c>
-      <c r="AS89">
-        <v>1.14</v>
-      </c>
       <c r="AT89">
-        <v>2.93</v>
+        <v>2.65</v>
       </c>
       <c r="AU89">
         <v>7</v>
@@ -19524,7 +19533,7 @@
         <v>144</v>
       </c>
       <c r="P90" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q90">
         <v>3.1</v>
@@ -19596,25 +19605,25 @@
         <v>1.53</v>
       </c>
       <c r="AN90">
-        <v>1.6</v>
+        <v>1.17</v>
       </c>
       <c r="AO90">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AP90">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AQ90">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AR90">
-        <v>1.82</v>
+        <v>1.58</v>
       </c>
       <c r="AS90">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="AT90">
-        <v>3.33</v>
+        <v>3.05</v>
       </c>
       <c r="AU90">
         <v>4</v>
@@ -19802,25 +19811,25 @@
         <v>2</v>
       </c>
       <c r="AN91">
-        <v>2.71</v>
+        <v>2.58</v>
       </c>
       <c r="AO91">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="AP91">
+        <v>2.4</v>
+      </c>
+      <c r="AQ91">
+        <v>1.76</v>
+      </c>
+      <c r="AR91">
+        <v>1.49</v>
+      </c>
+      <c r="AS91">
+        <v>1.33</v>
+      </c>
+      <c r="AT91">
         <v>2.82</v>
-      </c>
-      <c r="AQ91">
-        <v>1.67</v>
-      </c>
-      <c r="AR91">
-        <v>1.64</v>
-      </c>
-      <c r="AS91">
-        <v>1.29</v>
-      </c>
-      <c r="AT91">
-        <v>2.93</v>
       </c>
       <c r="AU91">
         <v>8</v>
@@ -19936,7 +19945,7 @@
         <v>146</v>
       </c>
       <c r="P92" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20008,25 +20017,25 @@
         <v>1.95</v>
       </c>
       <c r="AN92">
-        <v>2.67</v>
+        <v>2</v>
       </c>
       <c r="AO92">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AP92">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AQ92">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="AR92">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="AS92">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="AT92">
-        <v>3.08</v>
+        <v>3.21</v>
       </c>
       <c r="AU92">
         <v>6</v>
@@ -20142,7 +20151,7 @@
         <v>147</v>
       </c>
       <c r="P93" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q93">
         <v>2.62</v>
@@ -20214,25 +20223,25 @@
         <v>1.62</v>
       </c>
       <c r="AN93">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="AO93">
-        <v>2.2</v>
+        <v>1.69</v>
       </c>
       <c r="AP93">
-        <v>1.7</v>
+        <v>1.43</v>
       </c>
       <c r="AQ93">
-        <v>1.8</v>
+        <v>1.48</v>
       </c>
       <c r="AR93">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AS93">
-        <v>1.12</v>
+        <v>1.45</v>
       </c>
       <c r="AT93">
-        <v>2.47</v>
+        <v>2.73</v>
       </c>
       <c r="AU93">
         <v>5</v>
@@ -20348,7 +20357,7 @@
         <v>148</v>
       </c>
       <c r="P94" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q94">
         <v>2.4</v>
@@ -20420,25 +20429,25 @@
         <v>1.95</v>
       </c>
       <c r="AN94">
-        <v>3</v>
+        <v>1.92</v>
       </c>
       <c r="AO94">
-        <v>0.17</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AP94">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
       <c r="AQ94">
-        <v>0.7</v>
+        <v>1.05</v>
       </c>
       <c r="AR94">
-        <v>1.56</v>
+        <v>1.27</v>
       </c>
       <c r="AS94">
-        <v>1.09</v>
+        <v>1.31</v>
       </c>
       <c r="AT94">
-        <v>2.65</v>
+        <v>2.58</v>
       </c>
       <c r="AU94">
         <v>7</v>
@@ -20554,7 +20563,7 @@
         <v>149</v>
       </c>
       <c r="P95" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q95">
         <v>3.1</v>
@@ -20626,25 +20635,25 @@
         <v>1.5</v>
       </c>
       <c r="AN95">
-        <v>0.67</v>
+        <v>0.92</v>
       </c>
       <c r="AO95">
-        <v>0.67</v>
+        <v>1.08</v>
       </c>
       <c r="AP95">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="AQ95">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="AR95">
-        <v>1.52</v>
+        <v>1.31</v>
       </c>
       <c r="AS95">
-        <v>1.16</v>
+        <v>1.5</v>
       </c>
       <c r="AT95">
-        <v>2.68</v>
+        <v>2.81</v>
       </c>
       <c r="AU95">
         <v>5</v>
@@ -20832,25 +20841,25 @@
         <v>1.35</v>
       </c>
       <c r="AN96">
-        <v>0.57</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AO96">
-        <v>1</v>
+        <v>1.38</v>
       </c>
       <c r="AP96">
-        <v>0.82</v>
+        <v>0.95</v>
       </c>
       <c r="AQ96">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AR96">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AS96">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AT96">
-        <v>2.51</v>
+        <v>2.36</v>
       </c>
       <c r="AU96">
         <v>5</v>
@@ -21038,25 +21047,25 @@
         <v>1.65</v>
       </c>
       <c r="AN97">
-        <v>1.5</v>
+        <v>1.15</v>
       </c>
       <c r="AO97">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AP97">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AQ97">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="AR97">
-        <v>1.82</v>
+        <v>1.59</v>
       </c>
       <c r="AS97">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="AT97">
-        <v>3.13</v>
+        <v>3.03</v>
       </c>
       <c r="AU97">
         <v>5</v>
@@ -21172,7 +21181,7 @@
         <v>152</v>
       </c>
       <c r="P98" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q98">
         <v>2.3</v>
@@ -21244,25 +21253,25 @@
         <v>2</v>
       </c>
       <c r="AN98">
-        <v>2.43</v>
+        <v>1.92</v>
       </c>
       <c r="AO98">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AP98">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AQ98">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AR98">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AS98">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AT98">
-        <v>3.49</v>
+        <v>3.31</v>
       </c>
       <c r="AU98">
         <v>8</v>
@@ -21378,7 +21387,7 @@
         <v>153</v>
       </c>
       <c r="P99" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q99">
         <v>6.5</v>
@@ -21450,25 +21459,25 @@
         <v>1.08</v>
       </c>
       <c r="AN99">
-        <v>0.57</v>
+        <v>0.31</v>
       </c>
       <c r="AO99">
+        <v>2.62</v>
+      </c>
+      <c r="AP99">
+        <v>0.62</v>
+      </c>
+      <c r="AQ99">
         <v>2.4</v>
       </c>
-      <c r="AP99">
-        <v>0.8</v>
-      </c>
-      <c r="AQ99">
-        <v>1.89</v>
-      </c>
       <c r="AR99">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AS99">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="AT99">
-        <v>2.48</v>
+        <v>2.8</v>
       </c>
       <c r="AU99">
         <v>6</v>
@@ -21584,7 +21593,7 @@
         <v>154</v>
       </c>
       <c r="P100" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q100">
         <v>4.33</v>
@@ -21656,25 +21665,25 @@
         <v>1.17</v>
       </c>
       <c r="AN100">
-        <v>1.71</v>
+        <v>1.29</v>
       </c>
       <c r="AO100">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="AP100">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AQ100">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AR100">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AS100">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AT100">
-        <v>2.77</v>
+        <v>2.91</v>
       </c>
       <c r="AU100">
         <v>5</v>
@@ -21790,7 +21799,7 @@
         <v>85</v>
       </c>
       <c r="P101" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q101">
         <v>3.88</v>
@@ -21862,25 +21871,25 @@
         <v>1.28</v>
       </c>
       <c r="AN101">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="AO101">
-        <v>0.86</v>
+        <v>1.29</v>
       </c>
       <c r="AP101">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="AQ101">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AR101">
-        <v>1.52</v>
+        <v>1.31</v>
       </c>
       <c r="AS101">
-        <v>1.4</v>
+        <v>1.59</v>
       </c>
       <c r="AT101">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="AU101">
         <v>0</v>
@@ -22068,25 +22077,25 @@
         <v>1.57</v>
       </c>
       <c r="AN102">
-        <v>1.43</v>
+        <v>1.21</v>
       </c>
       <c r="AO102">
-        <v>0.14</v>
+        <v>0.64</v>
       </c>
       <c r="AP102">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ102">
-        <v>0.7</v>
+        <v>1.05</v>
       </c>
       <c r="AR102">
-        <v>1.78</v>
+        <v>1.5</v>
       </c>
       <c r="AS102">
-        <v>1.09</v>
+        <v>1.31</v>
       </c>
       <c r="AT102">
-        <v>2.87</v>
+        <v>2.81</v>
       </c>
       <c r="AU102">
         <v>6</v>
@@ -22202,7 +22211,7 @@
         <v>85</v>
       </c>
       <c r="P103" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q103">
         <v>2.14</v>
@@ -22274,25 +22283,25 @@
         <v>2.22</v>
       </c>
       <c r="AN103">
-        <v>1.38</v>
+        <v>1.79</v>
       </c>
       <c r="AO103">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AP103">
-        <v>1.18</v>
+        <v>1.48</v>
       </c>
       <c r="AQ103">
-        <v>1.1</v>
+        <v>0.95</v>
       </c>
       <c r="AR103">
-        <v>1.65</v>
+        <v>1.45</v>
       </c>
       <c r="AS103">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AT103">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="AU103">
         <v>4</v>
@@ -22408,7 +22417,7 @@
         <v>150</v>
       </c>
       <c r="P104" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q104">
         <v>3.4</v>
@@ -22480,25 +22489,25 @@
         <v>1.42</v>
       </c>
       <c r="AN104">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO104">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AP104">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
       <c r="AQ104">
-        <v>1.18</v>
+        <v>1.43</v>
       </c>
       <c r="AR104">
-        <v>1.56</v>
+        <v>1.27</v>
       </c>
       <c r="AS104">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AT104">
-        <v>2.74</v>
+        <v>2.55</v>
       </c>
       <c r="AU104">
         <v>4</v>
@@ -22686,25 +22695,25 @@
         <v>2.05</v>
       </c>
       <c r="AN105">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="AO105">
         <v>1.57</v>
       </c>
       <c r="AP105">
-        <v>2.82</v>
+        <v>2.4</v>
       </c>
       <c r="AQ105">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AR105">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AS105">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AT105">
-        <v>3.39</v>
+        <v>3.1</v>
       </c>
       <c r="AU105">
         <v>6</v>
@@ -22892,25 +22901,25 @@
         <v>1.85</v>
       </c>
       <c r="AN106">
-        <v>0.71</v>
+        <v>0.93</v>
       </c>
       <c r="AO106">
-        <v>0</v>
+        <v>0.36</v>
       </c>
       <c r="AP106">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AQ106">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="AR106">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AS106">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AT106">
-        <v>2.83</v>
+        <v>2.67</v>
       </c>
       <c r="AU106">
         <v>3</v>
@@ -23026,7 +23035,7 @@
         <v>85</v>
       </c>
       <c r="P107" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q107">
         <v>2.13</v>
@@ -23098,25 +23107,25 @@
         <v>2.3</v>
       </c>
       <c r="AN107">
-        <v>1.71</v>
+        <v>1.4</v>
       </c>
       <c r="AO107">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AP107">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AQ107">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="AR107">
-        <v>1.82</v>
+        <v>1.57</v>
       </c>
       <c r="AS107">
         <v>1.19</v>
       </c>
       <c r="AT107">
-        <v>3.01</v>
+        <v>2.76</v>
       </c>
       <c r="AU107">
         <v>5</v>
@@ -23232,7 +23241,7 @@
         <v>157</v>
       </c>
       <c r="P108" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q108">
         <v>3.38</v>
@@ -23304,25 +23313,25 @@
         <v>1.44</v>
       </c>
       <c r="AN108">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AO108">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AP108">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AQ108">
-        <v>1.18</v>
+        <v>1.43</v>
       </c>
       <c r="AR108">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AS108">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AT108">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="AU108">
         <v>9</v>
@@ -23510,25 +23519,25 @@
         <v>1.41</v>
       </c>
       <c r="AN109">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="AO109">
-        <v>0.86</v>
+        <v>1.2</v>
       </c>
       <c r="AP109">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="AQ109">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AR109">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="AS109">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="AT109">
-        <v>2.62</v>
+        <v>2.43</v>
       </c>
       <c r="AU109">
         <v>4</v>
@@ -23716,25 +23725,25 @@
         <v>1.44</v>
       </c>
       <c r="AN110">
-        <v>2.5</v>
+        <v>1.93</v>
       </c>
       <c r="AO110">
-        <v>2.33</v>
+        <v>1.67</v>
       </c>
       <c r="AP110">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
       <c r="AQ110">
-        <v>1.8</v>
+        <v>1.48</v>
       </c>
       <c r="AR110">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="AS110">
-        <v>1.12</v>
+        <v>1.46</v>
       </c>
       <c r="AT110">
-        <v>2.54</v>
+        <v>2.72</v>
       </c>
       <c r="AU110">
         <v>6</v>
@@ -23922,25 +23931,25 @@
         <v>1.73</v>
       </c>
       <c r="AN111">
-        <v>1.14</v>
+        <v>0.8</v>
       </c>
       <c r="AO111">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AP111">
-        <v>1.36</v>
+        <v>1.05</v>
       </c>
       <c r="AQ111">
-        <v>1.1</v>
+        <v>0.95</v>
       </c>
       <c r="AR111">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AS111">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AT111">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="AU111">
         <v>2</v>
@@ -24128,25 +24137,25 @@
         <v>1.77</v>
       </c>
       <c r="AN112">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="AO112">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AP112">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AQ112">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="AR112">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="AS112">
-        <v>1.16</v>
+        <v>1.47</v>
       </c>
       <c r="AT112">
-        <v>2.71</v>
+        <v>2.92</v>
       </c>
       <c r="AU112">
         <v>10</v>
@@ -24262,7 +24271,7 @@
         <v>159</v>
       </c>
       <c r="P113" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q113">
         <v>3.4</v>
@@ -24334,25 +24343,25 @@
         <v>1.46</v>
       </c>
       <c r="AN113">
-        <v>2.5</v>
+        <v>2.07</v>
       </c>
       <c r="AO113">
-        <v>2.17</v>
+        <v>2.53</v>
       </c>
       <c r="AP113">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AQ113">
-        <v>1.89</v>
+        <v>2.4</v>
       </c>
       <c r="AR113">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AS113">
-        <v>1.29</v>
+        <v>1.56</v>
       </c>
       <c r="AT113">
-        <v>3.14</v>
+        <v>3.34</v>
       </c>
       <c r="AU113">
         <v>6</v>
@@ -24540,25 +24549,25 @@
         <v>3.02</v>
       </c>
       <c r="AN114">
-        <v>2.78</v>
+        <v>2.56</v>
       </c>
       <c r="AO114">
-        <v>0.5</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AP114">
-        <v>2.82</v>
+        <v>2.4</v>
       </c>
       <c r="AQ114">
-        <v>0.7</v>
+        <v>1.05</v>
       </c>
       <c r="AR114">
-        <v>1.71</v>
+        <v>1.51</v>
       </c>
       <c r="AS114">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="AT114">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="AU114">
         <v>5</v>
@@ -24674,7 +24683,7 @@
         <v>161</v>
       </c>
       <c r="P115" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q115">
         <v>4.85</v>
@@ -24746,25 +24755,25 @@
         <v>1.15</v>
       </c>
       <c r="AN115">
-        <v>0.63</v>
+        <v>0.5</v>
       </c>
       <c r="AO115">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AP115">
-        <v>0.8</v>
+        <v>0.62</v>
       </c>
       <c r="AQ115">
-        <v>1.18</v>
+        <v>1.43</v>
       </c>
       <c r="AR115">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AS115">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AT115">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="AU115">
         <v>7</v>
@@ -24952,25 +24961,25 @@
         <v>1.22</v>
       </c>
       <c r="AN116">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AO116">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AP116">
-        <v>0.82</v>
+        <v>0.95</v>
       </c>
       <c r="AQ116">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AR116">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AS116">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AT116">
-        <v>2.77</v>
+        <v>2.66</v>
       </c>
       <c r="AU116">
         <v>2</v>
@@ -25086,7 +25095,7 @@
         <v>85</v>
       </c>
       <c r="P117" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q117">
         <v>3.64</v>
@@ -25158,25 +25167,25 @@
         <v>1.33</v>
       </c>
       <c r="AN117">
-        <v>1.5</v>
+        <v>1.31</v>
       </c>
       <c r="AO117">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="AP117">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AQ117">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AR117">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="AS117">
-        <v>1.39</v>
+        <v>1.58</v>
       </c>
       <c r="AT117">
-        <v>2.48</v>
+        <v>2.76</v>
       </c>
       <c r="AU117">
         <v>2</v>
@@ -25364,25 +25373,25 @@
         <v>2.1</v>
       </c>
       <c r="AN118">
-        <v>1.22</v>
+        <v>1.75</v>
       </c>
       <c r="AO118">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AP118">
-        <v>1.18</v>
+        <v>1.48</v>
       </c>
       <c r="AQ118">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="AR118">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="AS118">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AT118">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="AU118">
         <v>7</v>
@@ -25498,7 +25507,7 @@
         <v>92</v>
       </c>
       <c r="P119" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q119">
         <v>4.4</v>
@@ -25570,25 +25579,25 @@
         <v>1.17</v>
       </c>
       <c r="AN119">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AO119">
-        <v>1.57</v>
+        <v>1.94</v>
       </c>
       <c r="AP119">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ119">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AR119">
-        <v>1.71</v>
+        <v>1.42</v>
       </c>
       <c r="AS119">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AT119">
-        <v>3.41</v>
+        <v>3.18</v>
       </c>
       <c r="AU119">
         <v>5</v>
@@ -25776,25 +25785,25 @@
         <v>1.57</v>
       </c>
       <c r="AN120">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="AO120">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AP120">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
       <c r="AQ120">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="AR120">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="AS120">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="AT120">
-        <v>2.93</v>
+        <v>2.83</v>
       </c>
       <c r="AU120">
         <v>3</v>
@@ -25910,7 +25919,7 @@
         <v>163</v>
       </c>
       <c r="P121" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q121">
         <v>2.93</v>
@@ -25982,25 +25991,25 @@
         <v>1.5</v>
       </c>
       <c r="AN121">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AO121">
-        <v>1.38</v>
+        <v>1.65</v>
       </c>
       <c r="AP121">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AQ121">
-        <v>1.18</v>
+        <v>1.43</v>
       </c>
       <c r="AR121">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="AS121">
         <v>1.35</v>
       </c>
       <c r="AT121">
-        <v>3.15</v>
+        <v>2.93</v>
       </c>
       <c r="AU121">
         <v>5</v>
@@ -26188,25 +26197,25 @@
         <v>2.04</v>
       </c>
       <c r="AN122">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AO122">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AP122">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AQ122">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="AR122">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="AS122">
-        <v>1.1</v>
+        <v>1.42</v>
       </c>
       <c r="AT122">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AU122">
         <v>9</v>
@@ -26394,25 +26403,25 @@
         <v>1.52</v>
       </c>
       <c r="AN123">
-        <v>0.78</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AO123">
-        <v>0.38</v>
+        <v>0.65</v>
       </c>
       <c r="AP123">
-        <v>0.82</v>
+        <v>0.95</v>
       </c>
       <c r="AQ123">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="AR123">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="AS123">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AT123">
-        <v>2.37</v>
+        <v>2.32</v>
       </c>
       <c r="AU123">
         <v>2</v>
@@ -26600,25 +26609,25 @@
         <v>1.43</v>
       </c>
       <c r="AN124">
-        <v>1.13</v>
+        <v>0.76</v>
       </c>
       <c r="AO124">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AP124">
-        <v>1.36</v>
+        <v>1.05</v>
       </c>
       <c r="AQ124">
+        <v>1.24</v>
+      </c>
+      <c r="AR124">
+        <v>1.21</v>
+      </c>
+      <c r="AS124">
         <v>1.18</v>
       </c>
-      <c r="AR124">
-        <v>1.38</v>
-      </c>
-      <c r="AS124">
-        <v>1.28</v>
-      </c>
       <c r="AT124">
-        <v>2.66</v>
+        <v>2.39</v>
       </c>
       <c r="AU124">
         <v>2</v>
@@ -26734,7 +26743,7 @@
         <v>166</v>
       </c>
       <c r="P125" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q125">
         <v>2.5</v>
@@ -26806,25 +26815,25 @@
         <v>1.8</v>
       </c>
       <c r="AN125">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AO125">
-        <v>2.43</v>
+        <v>1.71</v>
       </c>
       <c r="AP125">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AQ125">
-        <v>1.8</v>
+        <v>1.48</v>
       </c>
       <c r="AR125">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="AS125">
-        <v>1.22</v>
+        <v>1.47</v>
       </c>
       <c r="AT125">
-        <v>3.04</v>
+        <v>3.23</v>
       </c>
       <c r="AU125">
         <v>3</v>
@@ -26940,7 +26949,7 @@
         <v>167</v>
       </c>
       <c r="P126" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q126">
         <v>3.6</v>
@@ -27012,22 +27021,22 @@
         <v>1.36</v>
       </c>
       <c r="AN126">
-        <v>0.33</v>
+        <v>0.76</v>
       </c>
       <c r="AO126">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AP126">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="AQ126">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AR126">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AS126">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AT126">
         <v>2.62</v>
@@ -27146,7 +27155,7 @@
         <v>168</v>
       </c>
       <c r="P127" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q127">
         <v>4.33</v>
@@ -27218,25 +27227,25 @@
         <v>1.22</v>
       </c>
       <c r="AN127">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AO127">
-        <v>2.29</v>
+        <v>2.59</v>
       </c>
       <c r="AP127">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AQ127">
-        <v>1.89</v>
+        <v>2.4</v>
       </c>
       <c r="AR127">
-        <v>1.63</v>
+        <v>1.46</v>
       </c>
       <c r="AS127">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AT127">
-        <v>2.83</v>
+        <v>2.96</v>
       </c>
       <c r="AU127">
         <v>8</v>
@@ -27352,7 +27361,7 @@
         <v>169</v>
       </c>
       <c r="P128" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q128">
         <v>3.5</v>
@@ -27424,25 +27433,25 @@
         <v>1.36</v>
       </c>
       <c r="AN128">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AO128">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="AP128">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AQ128">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AR128">
-        <v>1.71</v>
+        <v>1.55</v>
       </c>
       <c r="AS128">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="AT128">
-        <v>3.42</v>
+        <v>3.29</v>
       </c>
       <c r="AU128">
         <v>9</v>
@@ -27558,7 +27567,7 @@
         <v>170</v>
       </c>
       <c r="P129" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q129">
         <v>4.33</v>
@@ -27630,25 +27639,25 @@
         <v>1.2</v>
       </c>
       <c r="AN129">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AO129">
-        <v>2.13</v>
+        <v>2.5</v>
       </c>
       <c r="AP129">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
       <c r="AQ129">
-        <v>1.89</v>
+        <v>2.4</v>
       </c>
       <c r="AR129">
-        <v>1.53</v>
+        <v>1.32</v>
       </c>
       <c r="AS129">
-        <v>1.18</v>
+        <v>1.47</v>
       </c>
       <c r="AT129">
-        <v>2.71</v>
+        <v>2.79</v>
       </c>
       <c r="AU129">
         <v>4</v>
@@ -27764,7 +27773,7 @@
         <v>171</v>
       </c>
       <c r="P130" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q130">
         <v>4.2</v>
@@ -27836,25 +27845,25 @@
         <v>1.25</v>
       </c>
       <c r="AN130">
-        <v>0.43</v>
+        <v>0.78</v>
       </c>
       <c r="AO130">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="AP130">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="AQ130">
-        <v>1.18</v>
+        <v>1.43</v>
       </c>
       <c r="AR130">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="AS130">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AT130">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="AU130">
         <v>6</v>
@@ -28042,25 +28051,25 @@
         <v>1.6</v>
       </c>
       <c r="AN131">
-        <v>1.11</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AO131">
-        <v>1.13</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AP131">
+        <v>0.9</v>
+      </c>
+      <c r="AQ131">
+        <v>0.95</v>
+      </c>
+      <c r="AR131">
+        <v>1.39</v>
+      </c>
+      <c r="AS131">
         <v>1.1</v>
       </c>
-      <c r="AQ131">
-        <v>1.1</v>
-      </c>
-      <c r="AR131">
-        <v>1.67</v>
-      </c>
-      <c r="AS131">
-        <v>1.03</v>
-      </c>
       <c r="AT131">
-        <v>2.7</v>
+        <v>2.49</v>
       </c>
       <c r="AU131">
         <v>6</v>
@@ -28248,25 +28257,25 @@
         <v>1.25</v>
       </c>
       <c r="AN132">
-        <v>1.33</v>
+        <v>0.89</v>
       </c>
       <c r="AO132">
-        <v>1.56</v>
+        <v>1.72</v>
       </c>
       <c r="AP132">
-        <v>1.36</v>
+        <v>1.05</v>
       </c>
       <c r="AQ132">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AR132">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="AS132">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="AT132">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="AU132">
         <v>3</v>
@@ -28454,25 +28463,25 @@
         <v>1.44</v>
       </c>
       <c r="AN133">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AO133">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="AP133">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AQ133">
-        <v>1.8</v>
+        <v>1.48</v>
       </c>
       <c r="AR133">
-        <v>1.61</v>
+        <v>1.45</v>
       </c>
       <c r="AS133">
-        <v>1.31</v>
+        <v>1.49</v>
       </c>
       <c r="AT133">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="AU133">
         <v>9</v>
@@ -28660,25 +28669,25 @@
         <v>1.75</v>
       </c>
       <c r="AN134">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AO134">
-        <v>0.44</v>
+        <v>0.67</v>
       </c>
       <c r="AP134">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AQ134">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="AR134">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="AS134">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AT134">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="AU134">
         <v>2</v>
@@ -28866,25 +28875,25 @@
         <v>2.82</v>
       </c>
       <c r="AN135">
+        <v>2</v>
+      </c>
+      <c r="AO135">
+        <v>0.89</v>
+      </c>
+      <c r="AP135">
         <v>2.1</v>
       </c>
-      <c r="AO135">
-        <v>1</v>
-      </c>
-      <c r="AP135">
-        <v>2.18</v>
-      </c>
       <c r="AQ135">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="AR135">
         <v>1.78</v>
       </c>
       <c r="AS135">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AT135">
-        <v>3.03</v>
+        <v>3.13</v>
       </c>
       <c r="AU135">
         <v>3</v>
@@ -29000,7 +29009,7 @@
         <v>175</v>
       </c>
       <c r="P136" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q136">
         <v>3.2</v>
@@ -29072,25 +29081,25 @@
         <v>1.48</v>
       </c>
       <c r="AN136">
-        <v>0.89</v>
+        <v>0.68</v>
       </c>
       <c r="AO136">
-        <v>0.44</v>
+        <v>0.84</v>
       </c>
       <c r="AP136">
-        <v>0.8</v>
+        <v>0.62</v>
       </c>
       <c r="AQ136">
-        <v>0.7</v>
+        <v>1.05</v>
       </c>
       <c r="AR136">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AS136">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="AT136">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="AU136">
         <v>6</v>
@@ -29278,25 +29287,25 @@
         <v>2.03</v>
       </c>
       <c r="AN137">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AO137">
-        <v>0.78</v>
+        <v>0.95</v>
       </c>
       <c r="AP137">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
       <c r="AQ137">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="AR137">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="AS137">
-        <v>1.06</v>
+        <v>1.38</v>
       </c>
       <c r="AT137">
-        <v>2.52</v>
+        <v>2.68</v>
       </c>
       <c r="AU137">
         <v>4</v>
@@ -29484,25 +29493,25 @@
         <v>1.77</v>
       </c>
       <c r="AN138">
-        <v>1.2</v>
+        <v>1.58</v>
       </c>
       <c r="AO138">
-        <v>1</v>
+        <v>1.16</v>
       </c>
       <c r="AP138">
-        <v>1.18</v>
+        <v>1.48</v>
       </c>
       <c r="AQ138">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AR138">
-        <v>1.62</v>
+        <v>1.45</v>
       </c>
       <c r="AS138">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AT138">
-        <v>2.91</v>
+        <v>2.6</v>
       </c>
       <c r="AU138">
         <v>3</v>
@@ -29618,7 +29627,7 @@
         <v>177</v>
       </c>
       <c r="P139" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q139">
         <v>2.3</v>
@@ -29690,25 +29699,25 @@
         <v>2</v>
       </c>
       <c r="AN139">
-        <v>2.8</v>
+        <v>2.37</v>
       </c>
       <c r="AO139">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AP139">
-        <v>2.82</v>
+        <v>2.4</v>
       </c>
       <c r="AQ139">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AR139">
-        <v>1.67</v>
+        <v>1.47</v>
       </c>
       <c r="AS139">
-        <v>1.4</v>
+        <v>1.59</v>
       </c>
       <c r="AT139">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="AU139">
         <v>5</v>
@@ -29896,25 +29905,25 @@
         <v>1.62</v>
       </c>
       <c r="AN140">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="AO140">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="AP140">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AQ140">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="AR140">
-        <v>1.63</v>
+        <v>1.51</v>
       </c>
       <c r="AS140">
-        <v>1.23</v>
+        <v>1.47</v>
       </c>
       <c r="AT140">
-        <v>2.86</v>
+        <v>2.98</v>
       </c>
       <c r="AU140">
         <v>3</v>
@@ -30030,7 +30039,7 @@
         <v>178</v>
       </c>
       <c r="P141" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q141">
         <v>4.75</v>
@@ -30102,25 +30111,25 @@
         <v>1.25</v>
       </c>
       <c r="AN141">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="AO141">
-        <v>1.2</v>
+        <v>1.53</v>
       </c>
       <c r="AP141">
-        <v>0.82</v>
+        <v>0.95</v>
       </c>
       <c r="AQ141">
-        <v>1.18</v>
+        <v>1.43</v>
       </c>
       <c r="AR141">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="AS141">
         <v>1.34</v>
       </c>
       <c r="AT141">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="AU141">
         <v>4</v>
@@ -30236,7 +30245,7 @@
         <v>179</v>
       </c>
       <c r="P142" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q142">
         <v>3.6</v>
@@ -30308,25 +30317,25 @@
         <v>1.3</v>
       </c>
       <c r="AN142">
-        <v>2.13</v>
+        <v>1.85</v>
       </c>
       <c r="AO142">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="AP142">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
       <c r="AQ142">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AR142">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="AS142">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="AT142">
-        <v>3.25</v>
+        <v>3.06</v>
       </c>
       <c r="AU142">
         <v>6</v>
@@ -30442,7 +30451,7 @@
         <v>180</v>
       </c>
       <c r="P143" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q143">
         <v>2.4</v>
@@ -30514,25 +30523,25 @@
         <v>2.03</v>
       </c>
       <c r="AN143">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AO143">
-        <v>1.11</v>
+        <v>0.95</v>
       </c>
       <c r="AP143">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AQ143">
-        <v>1.1</v>
+        <v>0.95</v>
       </c>
       <c r="AR143">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AS143">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AT143">
-        <v>2.65</v>
+        <v>2.52</v>
       </c>
       <c r="AU143">
         <v>6</v>
@@ -30720,25 +30729,25 @@
         <v>1.73</v>
       </c>
       <c r="AN144">
-        <v>1.89</v>
+        <v>1.5</v>
       </c>
       <c r="AO144">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AP144">
-        <v>1.7</v>
+        <v>1.43</v>
       </c>
       <c r="AQ144">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AR144">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AS144">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="AT144">
-        <v>2.62</v>
+        <v>2.51</v>
       </c>
       <c r="AU144">
         <v>6</v>
@@ -30926,25 +30935,25 @@
         <v>1.3</v>
       </c>
       <c r="AN145">
-        <v>1.2</v>
+        <v>0.95</v>
       </c>
       <c r="AO145">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="AP145">
-        <v>1.36</v>
+        <v>1.05</v>
       </c>
       <c r="AQ145">
-        <v>1.8</v>
+        <v>1.48</v>
       </c>
       <c r="AR145">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AS145">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="AT145">
-        <v>2.52</v>
+        <v>2.61</v>
       </c>
       <c r="AU145">
         <v>2</v>
@@ -31011,6 +31020,418 @@
       </c>
       <c r="BP145">
         <v>1.12</v>
+      </c>
+    </row>
+    <row r="146" spans="1:68">
+      <c r="A146" s="1">
+        <v>145</v>
+      </c>
+      <c r="B146">
+        <v>7813965</v>
+      </c>
+      <c r="C146" t="s">
+        <v>68</v>
+      </c>
+      <c r="D146" t="s">
+        <v>69</v>
+      </c>
+      <c r="E146" s="2">
+        <v>45858.29166666666</v>
+      </c>
+      <c r="F146">
+        <v>21</v>
+      </c>
+      <c r="G146" t="s">
+        <v>76</v>
+      </c>
+      <c r="H146" t="s">
+        <v>81</v>
+      </c>
+      <c r="I146">
+        <v>2</v>
+      </c>
+      <c r="J146">
+        <v>1</v>
+      </c>
+      <c r="K146">
+        <v>3</v>
+      </c>
+      <c r="L146">
+        <v>5</v>
+      </c>
+      <c r="M146">
+        <v>3</v>
+      </c>
+      <c r="N146">
+        <v>8</v>
+      </c>
+      <c r="O146" t="s">
+        <v>182</v>
+      </c>
+      <c r="P146" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q146">
+        <v>2.9</v>
+      </c>
+      <c r="R146">
+        <v>2.15</v>
+      </c>
+      <c r="S146">
+        <v>3.4</v>
+      </c>
+      <c r="T146">
+        <v>1.36</v>
+      </c>
+      <c r="U146">
+        <v>2.9</v>
+      </c>
+      <c r="V146">
+        <v>2.8</v>
+      </c>
+      <c r="W146">
+        <v>1.4</v>
+      </c>
+      <c r="X146">
+        <v>7</v>
+      </c>
+      <c r="Y146">
+        <v>1.08</v>
+      </c>
+      <c r="Z146">
+        <v>2.16</v>
+      </c>
+      <c r="AA146">
+        <v>3.32</v>
+      </c>
+      <c r="AB146">
+        <v>3.08</v>
+      </c>
+      <c r="AC146">
+        <v>1</v>
+      </c>
+      <c r="AD146">
+        <v>9.1</v>
+      </c>
+      <c r="AE146">
+        <v>1.26</v>
+      </c>
+      <c r="AF146">
+        <v>3.22</v>
+      </c>
+      <c r="AG146">
+        <v>1.9</v>
+      </c>
+      <c r="AH146">
+        <v>1.81</v>
+      </c>
+      <c r="AI146">
+        <v>1.75</v>
+      </c>
+      <c r="AJ146">
+        <v>2</v>
+      </c>
+      <c r="AK146">
+        <v>1.36</v>
+      </c>
+      <c r="AL146">
+        <v>1.33</v>
+      </c>
+      <c r="AM146">
+        <v>1.62</v>
+      </c>
+      <c r="AN146">
+        <v>1.75</v>
+      </c>
+      <c r="AO146">
+        <v>1.25</v>
+      </c>
+      <c r="AP146">
+        <v>1.81</v>
+      </c>
+      <c r="AQ146">
+        <v>1.19</v>
+      </c>
+      <c r="AR146">
+        <v>1.48</v>
+      </c>
+      <c r="AS146">
+        <v>1.55</v>
+      </c>
+      <c r="AT146">
+        <v>3.03</v>
+      </c>
+      <c r="AU146">
+        <v>7</v>
+      </c>
+      <c r="AV146">
+        <v>7</v>
+      </c>
+      <c r="AW146">
+        <v>10</v>
+      </c>
+      <c r="AX146">
+        <v>8</v>
+      </c>
+      <c r="AY146">
+        <v>17</v>
+      </c>
+      <c r="AZ146">
+        <v>15</v>
+      </c>
+      <c r="BA146">
+        <v>3</v>
+      </c>
+      <c r="BB146">
+        <v>5</v>
+      </c>
+      <c r="BC146">
+        <v>8</v>
+      </c>
+      <c r="BD146">
+        <v>1.78</v>
+      </c>
+      <c r="BE146">
+        <v>7.8</v>
+      </c>
+      <c r="BF146">
+        <v>2.34</v>
+      </c>
+      <c r="BG146">
+        <v>1.36</v>
+      </c>
+      <c r="BH146">
+        <v>2.7</v>
+      </c>
+      <c r="BI146">
+        <v>1.68</v>
+      </c>
+      <c r="BJ146">
+        <v>2.01</v>
+      </c>
+      <c r="BK146">
+        <v>2.14</v>
+      </c>
+      <c r="BL146">
+        <v>1.57</v>
+      </c>
+      <c r="BM146">
+        <v>2.88</v>
+      </c>
+      <c r="BN146">
+        <v>1.32</v>
+      </c>
+      <c r="BO146">
+        <v>4.36</v>
+      </c>
+      <c r="BP146">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="147" spans="1:68">
+      <c r="A147" s="1">
+        <v>146</v>
+      </c>
+      <c r="B147">
+        <v>7813966</v>
+      </c>
+      <c r="C147" t="s">
+        <v>68</v>
+      </c>
+      <c r="D147" t="s">
+        <v>69</v>
+      </c>
+      <c r="E147" s="2">
+        <v>45858.29166666666</v>
+      </c>
+      <c r="F147">
+        <v>21</v>
+      </c>
+      <c r="G147" t="s">
+        <v>82</v>
+      </c>
+      <c r="H147" t="s">
+        <v>71</v>
+      </c>
+      <c r="I147">
+        <v>1</v>
+      </c>
+      <c r="J147">
+        <v>1</v>
+      </c>
+      <c r="K147">
+        <v>2</v>
+      </c>
+      <c r="L147">
+        <v>2</v>
+      </c>
+      <c r="M147">
+        <v>1</v>
+      </c>
+      <c r="N147">
+        <v>3</v>
+      </c>
+      <c r="O147" t="s">
+        <v>183</v>
+      </c>
+      <c r="P147" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q147">
+        <v>2.8</v>
+      </c>
+      <c r="R147">
+        <v>2.1</v>
+      </c>
+      <c r="S147">
+        <v>3.7</v>
+      </c>
+      <c r="T147">
+        <v>1.4</v>
+      </c>
+      <c r="U147">
+        <v>2.8</v>
+      </c>
+      <c r="V147">
+        <v>2.9</v>
+      </c>
+      <c r="W147">
+        <v>1.36</v>
+      </c>
+      <c r="X147">
+        <v>8.5</v>
+      </c>
+      <c r="Y147">
+        <v>1.07</v>
+      </c>
+      <c r="Z147">
+        <v>2.18</v>
+      </c>
+      <c r="AA147">
+        <v>3.12</v>
+      </c>
+      <c r="AB147">
+        <v>2.93</v>
+      </c>
+      <c r="AC147">
+        <v>1.03</v>
+      </c>
+      <c r="AD147">
+        <v>9</v>
+      </c>
+      <c r="AE147">
+        <v>1.28</v>
+      </c>
+      <c r="AF147">
+        <v>3.08</v>
+      </c>
+      <c r="AG147">
+        <v>1.95</v>
+      </c>
+      <c r="AH147">
+        <v>1.75</v>
+      </c>
+      <c r="AI147">
+        <v>1.75</v>
+      </c>
+      <c r="AJ147">
+        <v>1.95</v>
+      </c>
+      <c r="AK147">
+        <v>1.36</v>
+      </c>
+      <c r="AL147">
+        <v>1.35</v>
+      </c>
+      <c r="AM147">
+        <v>1.62</v>
+      </c>
+      <c r="AN147">
+        <v>0.85</v>
+      </c>
+      <c r="AO147">
+        <v>0.65</v>
+      </c>
+      <c r="AP147">
+        <v>0.95</v>
+      </c>
+      <c r="AQ147">
+        <v>0.62</v>
+      </c>
+      <c r="AR147">
+        <v>1.32</v>
+      </c>
+      <c r="AS147">
+        <v>1.19</v>
+      </c>
+      <c r="AT147">
+        <v>2.51</v>
+      </c>
+      <c r="AU147">
+        <v>3</v>
+      </c>
+      <c r="AV147">
+        <v>3</v>
+      </c>
+      <c r="AW147">
+        <v>3</v>
+      </c>
+      <c r="AX147">
+        <v>3</v>
+      </c>
+      <c r="AY147">
+        <v>6</v>
+      </c>
+      <c r="AZ147">
+        <v>6</v>
+      </c>
+      <c r="BA147">
+        <v>5</v>
+      </c>
+      <c r="BB147">
+        <v>6</v>
+      </c>
+      <c r="BC147">
+        <v>11</v>
+      </c>
+      <c r="BD147">
+        <v>2</v>
+      </c>
+      <c r="BE147">
+        <v>5.9</v>
+      </c>
+      <c r="BF147">
+        <v>2.23</v>
+      </c>
+      <c r="BG147">
+        <v>1.48</v>
+      </c>
+      <c r="BH147">
+        <v>2.33</v>
+      </c>
+      <c r="BI147">
+        <v>1.87</v>
+      </c>
+      <c r="BJ147">
+        <v>1.79</v>
+      </c>
+      <c r="BK147">
+        <v>2.46</v>
+      </c>
+      <c r="BL147">
+        <v>1.43</v>
+      </c>
+      <c r="BM147">
+        <v>3.42</v>
+      </c>
+      <c r="BN147">
+        <v>1.23</v>
+      </c>
+      <c r="BO147">
+        <v>5.18</v>
+      </c>
+      <c r="BP147">
+        <v>1.08</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 2_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="944" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="259">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -789,6 +789,9 @@
   <si>
     <t>['3', '57', '60']</t>
   </si>
+  <si>
+    <t>['86', '90+8']</t>
+  </si>
 </sst>
 </file>
 
@@ -1149,7 +1152,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP147"/>
+  <dimension ref="A1:BP148"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1483,10 +1486,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="AQ2">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2925,7 +2928,7 @@
         <v>3</v>
       </c>
       <c r="AP9">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="AQ9">
         <v>2.1</v>
@@ -3752,7 +3755,7 @@
         <v>1.48</v>
       </c>
       <c r="AQ13">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="AR13">
         <v>1.4</v>
@@ -4576,7 +4579,7 @@
         <v>1.05</v>
       </c>
       <c r="AQ17">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="AR17">
         <v>1.16</v>
@@ -5606,7 +5609,7 @@
         <v>1.24</v>
       </c>
       <c r="AQ22">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="AR22">
         <v>0.92</v>
@@ -5809,7 +5812,7 @@
         <v>2.33</v>
       </c>
       <c r="AP23">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="AQ23">
         <v>1.43</v>
@@ -6839,7 +6842,7 @@
         <v>2.33</v>
       </c>
       <c r="AP28">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="AQ28">
         <v>1.76</v>
@@ -7663,7 +7666,7 @@
         <v>1</v>
       </c>
       <c r="AP32">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="AQ32">
         <v>0.95</v>
@@ -7869,7 +7872,7 @@
         <v>1.75</v>
       </c>
       <c r="AP33">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="AQ33">
         <v>1.48</v>
@@ -8902,7 +8905,7 @@
         <v>1.05</v>
       </c>
       <c r="AQ38">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="AR38">
         <v>1.37</v>
@@ -9314,7 +9317,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ40">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="AR40">
         <v>1.66</v>
@@ -10753,7 +10756,7 @@
         <v>2</v>
       </c>
       <c r="AP47">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="AQ47">
         <v>1.24</v>
@@ -10959,7 +10962,7 @@
         <v>0.67</v>
       </c>
       <c r="AP48">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="AQ48">
         <v>0.95</v>
@@ -11783,7 +11786,7 @@
         <v>0.43</v>
       </c>
       <c r="AP52">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="AQ52">
         <v>0.62</v>
@@ -12813,7 +12816,7 @@
         <v>1.29</v>
       </c>
       <c r="AP57">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="AQ57">
         <v>1.24</v>
@@ -13022,7 +13025,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ58">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="AR58">
         <v>1.28</v>
@@ -13640,7 +13643,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ61">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="AR61">
         <v>1.46</v>
@@ -14876,7 +14879,7 @@
         <v>0.95</v>
       </c>
       <c r="AQ67">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="AR67">
         <v>1.27</v>
@@ -15285,7 +15288,7 @@
         <v>1</v>
       </c>
       <c r="AP69">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="AQ69">
         <v>1.24</v>
@@ -16109,7 +16112,7 @@
         <v>1.5</v>
       </c>
       <c r="AP73">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="AQ73">
         <v>1.81</v>
@@ -16318,7 +16321,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ74">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="AR74">
         <v>1.57</v>
@@ -17345,7 +17348,7 @@
         <v>1</v>
       </c>
       <c r="AP79">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="AQ79">
         <v>1.19</v>
@@ -18172,7 +18175,7 @@
         <v>0.95</v>
       </c>
       <c r="AQ83">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="AR83">
         <v>1.25</v>
@@ -19405,7 +19408,7 @@
         <v>0.33</v>
       </c>
       <c r="AP89">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="AQ89">
         <v>0.62</v>
@@ -19817,7 +19820,7 @@
         <v>2.08</v>
       </c>
       <c r="AP91">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="AQ91">
         <v>1.76</v>
@@ -20644,7 +20647,7 @@
         <v>0.95</v>
       </c>
       <c r="AQ95">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="AR95">
         <v>1.31</v>
@@ -21468,7 +21471,7 @@
         <v>0.62</v>
       </c>
       <c r="AQ99">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="AR99">
         <v>1.23</v>
@@ -22083,7 +22086,7 @@
         <v>0.64</v>
       </c>
       <c r="AP102">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="AQ102">
         <v>1.05</v>
@@ -22701,7 +22704,7 @@
         <v>1.57</v>
       </c>
       <c r="AP105">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="AQ105">
         <v>1.81</v>
@@ -24146,7 +24149,7 @@
         <v>1.24</v>
       </c>
       <c r="AQ112">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="AR112">
         <v>1.45</v>
@@ -24352,7 +24355,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ113">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="AR113">
         <v>1.78</v>
@@ -24555,7 +24558,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="AP114">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="AQ114">
         <v>1.05</v>
@@ -25585,7 +25588,7 @@
         <v>1.94</v>
       </c>
       <c r="AP119">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="AQ119">
         <v>2.1</v>
@@ -26206,7 +26209,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ122">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="AR122">
         <v>1.46</v>
@@ -27236,7 +27239,7 @@
         <v>1.24</v>
       </c>
       <c r="AQ127">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="AR127">
         <v>1.46</v>
@@ -27648,7 +27651,7 @@
         <v>1.76</v>
       </c>
       <c r="AQ129">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="AR129">
         <v>1.32</v>
@@ -28057,7 +28060,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AP131">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="AQ131">
         <v>0.95</v>
@@ -29296,7 +29299,7 @@
         <v>1.76</v>
       </c>
       <c r="AQ137">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="AR137">
         <v>1.3</v>
@@ -29705,7 +29708,7 @@
         <v>1.32</v>
       </c>
       <c r="AP139">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="AQ139">
         <v>1.19</v>
@@ -31432,6 +31435,212 @@
       </c>
       <c r="BP147">
         <v>1.08</v>
+      </c>
+    </row>
+    <row r="148" spans="1:68">
+      <c r="A148" s="1">
+        <v>147</v>
+      </c>
+      <c r="B148">
+        <v>7813967</v>
+      </c>
+      <c r="C148" t="s">
+        <v>68</v>
+      </c>
+      <c r="D148" t="s">
+        <v>69</v>
+      </c>
+      <c r="E148" s="2">
+        <v>45858.29166666666</v>
+      </c>
+      <c r="F148">
+        <v>21</v>
+      </c>
+      <c r="G148" t="s">
+        <v>80</v>
+      </c>
+      <c r="H148" t="s">
+        <v>70</v>
+      </c>
+      <c r="I148">
+        <v>0</v>
+      </c>
+      <c r="J148">
+        <v>0</v>
+      </c>
+      <c r="K148">
+        <v>0</v>
+      </c>
+      <c r="L148">
+        <v>0</v>
+      </c>
+      <c r="M148">
+        <v>2</v>
+      </c>
+      <c r="N148">
+        <v>2</v>
+      </c>
+      <c r="O148" t="s">
+        <v>85</v>
+      </c>
+      <c r="P148" t="s">
+        <v>258</v>
+      </c>
+      <c r="Q148">
+        <v>5.5</v>
+      </c>
+      <c r="R148">
+        <v>2.38</v>
+      </c>
+      <c r="S148">
+        <v>2</v>
+      </c>
+      <c r="T148">
+        <v>1.3</v>
+      </c>
+      <c r="U148">
+        <v>3.25</v>
+      </c>
+      <c r="V148">
+        <v>2.45</v>
+      </c>
+      <c r="W148">
+        <v>1.5</v>
+      </c>
+      <c r="X148">
+        <v>6</v>
+      </c>
+      <c r="Y148">
+        <v>1.12</v>
+      </c>
+      <c r="Z148">
+        <v>5.5</v>
+      </c>
+      <c r="AA148">
+        <v>4.1</v>
+      </c>
+      <c r="AB148">
+        <v>1.44</v>
+      </c>
+      <c r="AC148">
+        <v>1.01</v>
+      </c>
+      <c r="AD148">
+        <v>13</v>
+      </c>
+      <c r="AE148">
+        <v>1.17</v>
+      </c>
+      <c r="AF148">
+        <v>4.05</v>
+      </c>
+      <c r="AG148">
+        <v>1.71</v>
+      </c>
+      <c r="AH148">
+        <v>2.01</v>
+      </c>
+      <c r="AI148">
+        <v>1.85</v>
+      </c>
+      <c r="AJ148">
+        <v>1.85</v>
+      </c>
+      <c r="AK148">
+        <v>2.62</v>
+      </c>
+      <c r="AL148">
+        <v>1.22</v>
+      </c>
+      <c r="AM148">
+        <v>1.11</v>
+      </c>
+      <c r="AN148">
+        <v>0.9</v>
+      </c>
+      <c r="AO148">
+        <v>2.4</v>
+      </c>
+      <c r="AP148">
+        <v>0.86</v>
+      </c>
+      <c r="AQ148">
+        <v>2.43</v>
+      </c>
+      <c r="AR148">
+        <v>1.37</v>
+      </c>
+      <c r="AS148">
+        <v>1.48</v>
+      </c>
+      <c r="AT148">
+        <v>2.85</v>
+      </c>
+      <c r="AU148">
+        <v>2</v>
+      </c>
+      <c r="AV148">
+        <v>3</v>
+      </c>
+      <c r="AW148">
+        <v>6</v>
+      </c>
+      <c r="AX148">
+        <v>2</v>
+      </c>
+      <c r="AY148">
+        <v>8</v>
+      </c>
+      <c r="AZ148">
+        <v>5</v>
+      </c>
+      <c r="BA148">
+        <v>2</v>
+      </c>
+      <c r="BB148">
+        <v>5</v>
+      </c>
+      <c r="BC148">
+        <v>7</v>
+      </c>
+      <c r="BD148">
+        <v>3.3</v>
+      </c>
+      <c r="BE148">
+        <v>8</v>
+      </c>
+      <c r="BF148">
+        <v>1.45</v>
+      </c>
+      <c r="BG148">
+        <v>1.51</v>
+      </c>
+      <c r="BH148">
+        <v>2.26</v>
+      </c>
+      <c r="BI148">
+        <v>1.92</v>
+      </c>
+      <c r="BJ148">
+        <v>1.75</v>
+      </c>
+      <c r="BK148">
+        <v>2.52</v>
+      </c>
+      <c r="BL148">
+        <v>1.41</v>
+      </c>
+      <c r="BM148">
+        <v>3.5</v>
+      </c>
+      <c r="BN148">
+        <v>1.22</v>
+      </c>
+      <c r="BO148">
+        <v>5.62</v>
+      </c>
+      <c r="BP148">
+        <v>1.06</v>
       </c>
     </row>
   </sheetData>
